--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C48E6C-60C2-4123-B649-8A304492DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3AF420-8497-4882-9A4D-331301633FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="2489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="2554">
   <si>
     <t>No</t>
   </si>
@@ -8162,12 +8162,267 @@
   <si>
     <t>Progressive Metal, Ambient Metal [Instrumental Outro, Atmospheric Dissonance, Cinematic Metal]</t>
   </si>
+  <si>
+    <t>Caligula's Horse</t>
+  </si>
+  <si>
+    <t>Bloom</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Ffy_EUNh07S-ZdXc84eL_BvLf4jP00TemYexrcBjOQQ/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIzNTEw/MTkyLTE2NTQ3MTE3/MzAtNTY0MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/23510192-Caligulas-Horse-Bloom</t>
+  </si>
+  <si>
+    <t>Svart Records – SRE558, Europe, 2022 (LP, Album, Reissue, Clear Vinyl)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European 2022 reissue on clear vinyl by Svart Records. Pressed with a gatefold cover. Runouts are stamped (SRE 558 LP - A1 / SRE 558 LP - B1). Original release date: 2015.</t>
+  </si>
+  <si>
+    <t>Marigold</t>
+  </si>
+  <si>
+    <t>Firelight</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Turntail</t>
+  </si>
+  <si>
+    <t>Daughter of the Mountain</t>
+  </si>
+  <si>
+    <t>Dragonfly (Piano – Holly Terrens)</t>
+  </si>
+  <si>
+    <t>Η εισαγωγή λειτουργεί ως άνοιγμα χώρου και όχι ως άμεση επίθεση. Ακουστικές υφές, ατμόσφαιρα και η καθαρή φωνή του Jim Grey χτίζουν ένα pastoral περιβάλλον, πριν οι ηλεκτρικές κιθάρες αρχίσουν να μεταβάλλουν τη διάθεση. Το τραγούδι ορίζει το κεντρικό μοτίβο, ανάπτυξη και αναγέννηση δεν είναι εύκολη ή γραμμική διαδικασία.</t>
+  </si>
+  <si>
+    <t>Από τα πιο αποτελεσματικά Caligula’s Horse tracks. Συνδυάζει σύνθετες κιθαριστικές κινήσεις με άμεσο, μελωδικό refrain, κάτι που εξηγεί γιατί ξεχωρίζει στις κριτικές ως key track. Δεν χρησιμοποιεί τη τεχνικότητα ως αυτοσκοπό, οι syncopated riffs υπηρετούν μια έντονα συναισθηματική σύνθεση, όπου η φωνή του Grey γίνεται το κέντρο της δραματικής έντασης.</t>
+  </si>
+  <si>
+    <t>Το πρώτο μεγάλο prog-metal epic. Η λιβελούλα του τίτλου λειτουργεί σαν εικόνα μεταβολής και εύθραυστης ελευθερίας, ενώ η σύνθεση αλλάζει διαρκώς ένταση. Οι κιθάρες του Vallen και του Greensill περνούν από καθαρά motifs σε τεχνικά heavy riffs, το rhythm section μετακινεί τα μέτρα με ακρίβεια και το πιάνο της Holly Terrens προσθέτει έναν πιο λυρικό αντίποδα.</t>
+  </si>
+  <si>
+    <t>Πιο ατμοσφαιρικό και less riff-dominant, με έμφαση στην ευαισθησία και στην εσωτερική κίνηση. Η “φωτιά” του τίτλου δεν ακούγεται σαν εξωτερική καταστροφή αλλά σαν μικρή πηγή αντοχής ή μνήμης. Οι καθαρές κιθάρες και οι μελωδικές φωνητικές γραμμές δείχνουν την alternative-rock πλευρά της μπάντας.</t>
+  </si>
+  <si>
+    <t>Πιο σύντομο, μελωδικό και εκφραστικό. Ο τίτλος υπονοεί υποχώρηση, φυγή ή αδυναμία να αντιμετωπίσεις μια κατάσταση· μουσικά το κομμάτι διατηρεί ισορροπία ανάμεσα σε alternative-rock προσβασιμότητα και progressive λεπτομέρεια. Η φωνή του Grey είναι ιδιαίτερα καθαρή και δραματική, χωρίς να βασίζεται σε υπερβολικά harsh στοιχεία.</t>
+  </si>
+  <si>
+    <t>Σκοτεινότερο και πιο groove-oriented track. Η “σκουριά” υποδηλώνει φθορά, ακινησία ή συναισθηματική παραμέληση, και η μπάντα απαντά με πιο παχύ riffing και ελεγχόμενη ένταση. Είναι λιγότερο άμεσο από το “Marigold”, αλλά λειτουργεί σωστά ως γείωση μετά την πολυπλοκότητα του “Dragonfly”.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη συναισθηματική κορύφωση. Ο τίτλος δημιουργεί εικόνα φύσης, μνήμης και καταγωγής, και η σύνθεση αναπτύσσεται σαν οκτάλεπτη progressive suite, σιωπηλά/μελωδικά sections, βαριές κιθάρες, ανοιχτά refrains και μεγάλα instrumental περάσματα. Δεν κερδίζει μόνο από διάρκεια, αλλά από τον τρόπο με τον οποίο η μπάντα αφήνει τις ιδέες να αναπτυχθούν χωρίς να τις κάνει επίδειξη.</t>
+  </si>
+  <si>
+    <t>Ακουστικό και ατμοσφαιρικό φινάλε. Το “υπόστρωμα” του τίτλου ταιριάζει στο ρόλο του, μετά τα μεγάλα metal sections, ο δίσκος επιστρέφει σε χαμηλή ένταση και φυσική/οργανική αίσθηση. Δεν επιδιώκει θεαματικό τέλος· προτιμά να αφήσει το album να υποχωρήσει σε ηρεμία, ολοκληρώνοντας κυκλικά το ταξίδι που άρχισε στο “Bloom”.</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Djent, Melodic Prog Metal, Modern Progressive Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Progressive Rock [Atmospheric Prog Metal, Acoustic-to-Electric Opener]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Melodic Djent, Anthemic Prog Metal, Modern Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Rock [Melodic Prog Rock, Atmospheric Metal, Emotional Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Metal [Technical Prog Metal, Djent, Dynamic Epic]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Groove Prog Metal, Dark Melodic Metal, Modern Djent]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Rock [Melodic Prog Metal, Post-Alternative Metal, Emotional Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Progressive Rock [Progressive Metal Epic, Atmospheric Rock, Dynamic Suite]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Ambient Rock [Acoustic Outro, Atmospheric Prog, Reflective Coda]</t>
+  </si>
+  <si>
+    <t>In Contact</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/RUY2hagOrjn-R77ypauG0Qb4xvrJVuLIraMFeMJZ97k/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIzNTA2/NTUzLTE3MDg5NTc5/OTMtNDQ4MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/23506553-Caligulas-Horse-In-Contact</t>
+  </si>
+  <si>
+    <t>Dream the Dead</t>
+  </si>
+  <si>
+    <t>Will’s Song (Let the Colours Run)</t>
+  </si>
+  <si>
+    <t>The Hands Are the Hardest</t>
+  </si>
+  <si>
+    <t>Love Conquers All</t>
+  </si>
+  <si>
+    <t>Songs for No One</t>
+  </si>
+  <si>
+    <t>Capulet</t>
+  </si>
+  <si>
+    <t>Fill My Heart</t>
+  </si>
+  <si>
+    <t>Inertia and the Weapon of the Wall</t>
+  </si>
+  <si>
+    <t>The Cannon’s Mouth</t>
+  </si>
+  <si>
+    <t>Graves</t>
+  </si>
+  <si>
+    <t>Μεγάλο, οκτάλεπτο ξεκίνημα που καθορίζει αμέσως την κλίμακα του δίσκου. Οι καθαρές κιθάρες και η μελωδική φωνητική είσοδος του Jim Grey ανοίγουν έναν ατμοσφαιρικό χώρο, πριν η σύνθεση περάσει σε τεχνικά riffs και δυναμικά breaks. Ο τίτλος δίνει μια εικόνα επικοινωνίας με το παρελθόν ή με νεκρές μνήμες· μουσικά, το τραγούδι κινείται από στοχασμό σε επιθετικότητα χωρίς να χάνει το κεντρικό μελωδικό του νήμα.</t>
+  </si>
+  <si>
+    <t>Πιο κοφτό και riff-driven, με έντονα syncopated patterns και πιο σφιχτή technical-metal λογική. Ο τίτλος μπορεί να διαβαστεί ως σχόλιο για τα χέρια που δημιουργούν, αγγίζουν αλλά και δυσκολεύονται να εκφράσουν όσα αισθάνονται. Η μπάντα παίζει με ακρίβεια, αλλά δεν είναι το πιο μελωδικά άμεσο track του δίσκου.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Συντομότερο και πιο σκιερό, με ονομαστική αναφορά στον κόσμο του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Romeo and Juliet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Δεν λειτουργεί ως κυριολεκτική διασκευή Shakespeare, αλλά σαν σύντομο art-metal portrait για σύγκρουση, κοινωνικό ρόλο και ανθρώπους παγιδευμένους σε δομές που δεν έχουν επιλέξει. Τα riffs είναι πιο κοφτά και η σύνθεση διατηρεί tension χωρίς να ακολουθεί τη μεγάλη, επική φόρμα των προηγούμενων tracks.</t>
+    </r>
+  </si>
+  <si>
+    <t>Από τα πλέον ισχυρά tracks του album. Ξεκινά με προσωπικό, σχεδόν ευάλωτο τόνο και εξελίσσεται σε μεγάλη progressive-metal κλιμάκωση. Ο τίτλος περιγράφει την εμπειρία ενός δημιουργού που φτιάχνει τέχνη χωρίς βεβαιότητα ότι κάποιος θα την ακούσει ή θα την καταλάβει. Οι αλλαγές δυναμικής, τα μελωδικά riffs και η φωνή του Grey δίνουν στο τραγούδι αίσθηση πραγματικής συναισθηματικής αναζήτησης.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Πιο άμεσο και συναισθηματικό. Το τραγούδι αφηγείται τη ζωή του καλλιτέχνη </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>William Robinson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ο οποίος έζησε με παραληγία μετά από ατύχημα και συνέχισε να ζωγραφίζει. Η φράση “let the colours run” λειτουργεί ως επιμονή της δημιουργίας ακόμη και όταν το σώμα περιορίζεται. Η δυνατή μελωδία και το chorus δικαιολογούν γιατί ξεχωρίζει στα review ως βασικό track.</t>
+    </r>
+  </si>
+  <si>
+    <t>Spoken-word ενότητα με sound design, όχι πλήρες metal τραγούδι. Η “αδράνεια” και ο “τοίχος” λειτουργούν ως εικόνες ψυχολογικής απομόνωσης και αδυναμίας κίνησης. Η βαθμολογία του είναι χαμηλότερη επειδή αξιολογείται ως αυτόνομο audio piece· μέσα στο album όμως είναι απαραίτητη γέφυρα που μεταφέρει το concept προς το πιο επιθετικό τελευταίο κεφάλαιο.</t>
+  </si>
+  <si>
+    <t>Επιθετικότερο και πιο κοφτερό, με τεχνικά riffs που πλησιάζουν progressive thrash. Η “κάννη του κανονιού” δημιουργεί εικόνα σύγκρουσης, κινδύνου και μηχανικής βίας. Η μπάντα αυξάνει την ένταση μετά το spoken interlude, με τα drums του Griffin και τις κιθάρες να δημιουργούν σύγκρουση πριν από την τελική συναισθηματική έκρηξη.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μελωδικό και ανοιχτό, με το βάρος να πέφτει στις κιθάρες και στο καθαρό vocal hook. Είναι ένα από τα τραγούδια που εξισορροπούν την πολυπλοκότητα με αμεσότητα. Στο πλαίσιο του concept, λειτουργεί σαν ανάγκη για συναισθηματική επαφή ,η δημιουργία δεν αρκεί από μόνη της, αν δεν υπάρχει κάποιος να μοιραστείς την εμπειρία. Αναφέρεται επίσης ως key track από το Prog Report. </t>
+  </si>
+  <si>
+    <t>Σύντομο acoustic interlude που λειτουργεί σαν συναισθηματική αποσυμπίεση. Ο τίτλος είναι σκόπιμα απλός και σχεδόν ειρωνικά μεγάλος για τη μικρή διάρκειά του, μέσα σε ένα album που μιλά για δημιουργία και οδύνη, η αγάπη προσφέρεται ως απλή αλλά δύσκολη απάντηση. Δεν διεκδικεί θέση μεγάλου single· ο ρόλος του είναι να δημιουργήσει χώρο πριν από το “Songs For No One”.</t>
+  </si>
+  <si>
+    <t>Το δεκαπεντάλεπτο κλείσιμο είναι η κορυφαία σύνθεση του δίσκου. Βασίζεται σε μια ιστορία έμπνευσης από τον Vincent van Gogh και μετατρέπει την ένταση ανάμεσα στην αναγνώριση, την απόρριψη και τη δημιουργική ανάγκη σε πολυμερές prog-metal epic. Η εμφάνιση του Jørgen Munkeby στο saxophone και τα πρόσθετα φωνητικά διευρύνουν την παλέτα πέρα από την τυπική prog-metal γραφή. Το κομμάτι δεν είναι μεγάλο απλώς για να είναι μεγάλο, ενσωματώνει επαναφορές θεμάτων, ακουστικές παύσεις, βαριά riffs και καθαρές vocal κορυφώσεις, δίνοντας στο concept το πιο συγκινητικό του κλείσιμο.</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Modern Prog Metal, Djent, Concept Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Metal [Progressive Metal Epic, Djent, Dynamic Opener]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Rock [Melodic Prog Metal, Emotional Rock, Anthemic Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Technical Prog Metal, Groove Metal, Modern Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Acoustic Rock [Acoustic Interlude, Art Rock, Reflective Ballad]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Metal [Emotional Prog Metal, Dynamic Epic, Art Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Rock [Melodic Prog Metal, Dark Alternative Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Alternative Rock [Melodic Prog Metal, Atmospheric Rock, Emotional Metal]</t>
+  </si>
+  <si>
+    <t>Spoken Word, Ambient Rock [Narrative Interlude, Sound Design, Concept Transition]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Technical Metal [Progressive Thrash, Djent, Aggressive Prog Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Post-Metal [Progressive Metal Suite, Emotional Epic, Dynamic Finale]</t>
+  </si>
+  <si>
+    <t>Svart Records – SRE559, Europe, 2022 (2 x Vinyl, LP, Album, Limited Edition, Reissue, Blue / Green Marble)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European 2022 limited "seashore marble" edition 2LP reissue by Svart Records. Gatefold cover. Runouts are stamped (SRE 559 LP - A1 / B1 / C1 / D1). Original release date: 2017.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8251,6 +8506,37 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -8309,7 +8595,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8376,6 +8662,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8687,7 +8982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -11071,6 +11366,70 @@
       <c r="K74" s="6"/>
       <c r="L74" s="11"/>
       <c r="M74" s="11"/>
+    </row>
+    <row r="75" spans="1:13" ht="42" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D75" s="6">
+        <v>2015</v>
+      </c>
+      <c r="E75" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>2509</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>2494</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>2493</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>2492</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="42" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D76" s="6">
+        <v>2017</v>
+      </c>
+      <c r="E76" s="10">
+        <v>3.68</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>2541</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>2553</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>2552</v>
+      </c>
+      <c r="I76" s="11" t="s">
+        <v>2520</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>2519</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11218,6 +11577,10 @@
     <hyperlink ref="J73" r:id="rId142" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
     <hyperlink ref="I74" r:id="rId143" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
     <hyperlink ref="J74" r:id="rId144" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
+    <hyperlink ref="J75" r:id="rId145" xr:uid="{0EA49793-A85B-4792-89B2-B1C8F3B131B4}"/>
+    <hyperlink ref="I75" r:id="rId146" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
+    <hyperlink ref="J76" r:id="rId147" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
+    <hyperlink ref="I76" r:id="rId148" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11225,7 +11588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I689"/>
+  <dimension ref="A1:I707"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -29967,6 +30330,492 @@
       </c>
       <c r="I689" s="6"/>
     </row>
+    <row r="690" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A690" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B690" s="6">
+        <v>1</v>
+      </c>
+      <c r="C690" s="22" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D690" s="7" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E690" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F690" s="12">
+        <v>4</v>
+      </c>
+      <c r="G690" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H690" s="7" t="s">
+        <v>2501</v>
+      </c>
+      <c r="I690" s="6"/>
+    </row>
+    <row r="691" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A691" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B691" s="6">
+        <v>2</v>
+      </c>
+      <c r="C691" s="22" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D691" s="7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="E691" s="20">
+        <v>4.2</v>
+      </c>
+      <c r="F691" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G691" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H691" s="7" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I691" s="6"/>
+    </row>
+    <row r="692" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A692" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B692" s="6">
+        <v>3</v>
+      </c>
+      <c r="C692" s="22" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D692" s="7" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E692" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F692" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G692" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H692" s="7" t="s">
+        <v>2504</v>
+      </c>
+      <c r="I692" s="6"/>
+    </row>
+    <row r="693" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A693" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B693" s="6">
+        <v>4</v>
+      </c>
+      <c r="C693" s="22" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D693" s="7" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E693" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F693" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G693" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H693" s="7" t="s">
+        <v>2503</v>
+      </c>
+      <c r="I693" s="6"/>
+    </row>
+    <row r="694" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A694" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B694" s="6">
+        <v>5</v>
+      </c>
+      <c r="C694" s="22" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D694" s="7" t="s">
+        <v>2514</v>
+      </c>
+      <c r="E694" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F694" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G694" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H694" s="7" t="s">
+        <v>2506</v>
+      </c>
+      <c r="I694" s="6"/>
+    </row>
+    <row r="695" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A695" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B695" s="6">
+        <v>6</v>
+      </c>
+      <c r="C695" s="22" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D695" s="7" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E695" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F695" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G695" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H695" s="7" t="s">
+        <v>2505</v>
+      </c>
+      <c r="I695" s="6"/>
+    </row>
+    <row r="696" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A696" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B696" s="6">
+        <v>7</v>
+      </c>
+      <c r="C696" s="22" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D696" s="7" t="s">
+        <v>2516</v>
+      </c>
+      <c r="E696" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="F696" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G696" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H696" s="7" t="s">
+        <v>2507</v>
+      </c>
+      <c r="I696" s="6"/>
+    </row>
+    <row r="697" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A697" s="6">
+        <v>23510192</v>
+      </c>
+      <c r="B697" s="6">
+        <v>8</v>
+      </c>
+      <c r="C697" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="D697" s="7" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E697" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F697" s="12">
+        <v>4</v>
+      </c>
+      <c r="G697" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H697" s="7" t="s">
+        <v>2508</v>
+      </c>
+      <c r="I697" s="6"/>
+    </row>
+    <row r="698" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A698" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B698" s="6">
+        <v>1</v>
+      </c>
+      <c r="C698" s="22" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D698" s="7" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E698" s="20">
+        <v>4.24</v>
+      </c>
+      <c r="F698" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G698" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H698" s="23" t="s">
+        <v>2531</v>
+      </c>
+      <c r="I698" s="6"/>
+    </row>
+    <row r="699" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A699" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B699" s="6">
+        <v>2</v>
+      </c>
+      <c r="C699" s="22" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D699" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E699" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F699" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G699" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H699" s="24" t="s">
+        <v>2535</v>
+      </c>
+      <c r="I699" s="6"/>
+    </row>
+    <row r="700" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A700" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B700" s="6">
+        <v>3</v>
+      </c>
+      <c r="C700" s="22" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D700" s="7" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E700" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F700" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G700" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H700" s="23" t="s">
+        <v>2532</v>
+      </c>
+      <c r="I700" s="6"/>
+    </row>
+    <row r="701" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A701" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B701" s="6">
+        <v>4</v>
+      </c>
+      <c r="C701" s="22" t="s">
+        <v>2524</v>
+      </c>
+      <c r="D701" s="7" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E701" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F701" s="12">
+        <v>4</v>
+      </c>
+      <c r="G701" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H701" s="23" t="s">
+        <v>2539</v>
+      </c>
+      <c r="I701" s="6"/>
+    </row>
+    <row r="702" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A702" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B702" s="6">
+        <v>5</v>
+      </c>
+      <c r="C702" s="22" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D702" s="7" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E702" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F702" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G702" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H702" s="23" t="s">
+        <v>2534</v>
+      </c>
+      <c r="I702" s="6"/>
+    </row>
+    <row r="703" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A703" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B703" s="6">
+        <v>6</v>
+      </c>
+      <c r="C703" s="22" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D703" s="7" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E703" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F703" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G703" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H703" s="23" t="s">
+        <v>2533</v>
+      </c>
+      <c r="I703" s="6"/>
+    </row>
+    <row r="704" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A704" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B704" s="6">
+        <v>7</v>
+      </c>
+      <c r="C704" s="22" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D704" s="7" t="s">
+        <v>2548</v>
+      </c>
+      <c r="E704" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F704" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G704" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H704" s="23" t="s">
+        <v>2538</v>
+      </c>
+      <c r="I704" s="6"/>
+    </row>
+    <row r="705" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A705" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B705" s="6">
+        <v>8</v>
+      </c>
+      <c r="C705" s="22" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D705" s="7" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E705" s="20">
+        <v>2.71</v>
+      </c>
+      <c r="F705" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G705" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H705" s="23" t="s">
+        <v>2536</v>
+      </c>
+      <c r="I705" s="6"/>
+    </row>
+    <row r="706" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A706" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B706" s="6">
+        <v>9</v>
+      </c>
+      <c r="C706" s="22" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D706" s="7" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E706" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F706" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G706" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H706" s="23" t="s">
+        <v>2537</v>
+      </c>
+      <c r="I706" s="6"/>
+    </row>
+    <row r="707" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A707" s="6">
+        <v>23506553</v>
+      </c>
+      <c r="B707" s="6">
+        <v>10</v>
+      </c>
+      <c r="C707" s="22" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D707" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E707" s="20">
+        <v>4.17</v>
+      </c>
+      <c r="F707" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G707" s="12">
+        <v>5</v>
+      </c>
+      <c r="H707" s="25" t="s">
+        <v>2540</v>
+      </c>
+      <c r="I707" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3AF420-8497-4882-9A4D-331301633FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66942842-06E2-48E2-A88A-8541D357FBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="2590">
   <si>
     <t>No</t>
   </si>
@@ -8416,6 +8416,114 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European 2022 limited "seashore marble" edition 2LP reissue by Svart Records. Gatefold cover. Runouts are stamped (SRE 559 LP - A1 / B1 / C1 / D1). Original release date: 2017.</t>
+  </si>
+  <si>
+    <t>Bad Seed – BS023V, Play It Again Sam – BS023V, Play It Again Sam – 29472, Worldwide, 2024 (LP, Album, Stereo)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Worldwide 2024 release. Pressed by Optimal Media GmbH (BO10757). Lacquer cut at Sterling Sound by Joe Nino-Hernes. Mixed at Tarbox Road Studios. Recorded across Soundtree Studios, Studio Miraval, Poons Head, and Air Studios.</t>
+  </si>
+  <si>
+    <t>Song of the Lake</t>
+  </si>
+  <si>
+    <t>Wild God</t>
+  </si>
+  <si>
+    <t>Frogs</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
+    <t>Final Rescue Attempt</t>
+  </si>
+  <si>
+    <t>Conversion</t>
+  </si>
+  <si>
+    <t>Cinnamon Horses</t>
+  </si>
+  <si>
+    <t>Long Dark Night</t>
+  </si>
+  <si>
+    <t>O Wow O Wow (How Wonderful She Is)</t>
+  </si>
+  <si>
+    <t>As the Waters Cover the Sea</t>
+  </si>
+  <si>
+    <t>Art Rock, Gospel Rock [Chamber Rock, Post-Punk, Spiritual Rock]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Cave &amp; The Bad Seeds </t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31604863-Nick-Cave-The-Bad-Seeds-Wild-God?redirected=true</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/QC6YVC5o8nI_25N_Y5lX2FW48LqSwNPbfEdKaE8jRzw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxNjA0/ODYzLTE3MjU0MTcy/OTMtMzQ4Mi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Art Rock, Chamber Pop [Piano Ballad, Spiritual Rock, Atmospheric Opener]</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Art Rock [Hymnal Rock, Post-Punk, Orchestral Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Gospel Rock [Dream Rock, Spiritual Ballad, Chamber Rock]</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Art Rock [Ecstatic Rock, Spiritual Rock, Brass-led Art Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Chamber Rock [Narrative Rock, Piano Rock, Reflective Art Pop]</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Art Rock [Hymnal Rock, Spiritual Rock, Dynamic Art Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Alternative Rock [Atmospheric Rock, Narrative Song, Chamber Rock]</t>
+  </si>
+  <si>
+    <t>Chamber Pop, Art Rock [Piano Ballad, Melancholic Pop, Intimate Rock]</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Art Rock [Exultant Rock, Choral Rock, Spiritual Pop]</t>
+  </si>
+  <si>
+    <t>Gospel Rock, Chamber Rock [Choral Coda, Sacred Pop, Album Epilogue]</t>
+  </si>
+  <si>
+    <t>Σύντομο, ατμοσφαιρικό άνοιγμα που δεν λειτουργεί ως conventional rocker αλλά ως είσοδος σε έναν πνευματικό, ονειρικό χώρο. Το πιάνο και η φωνή του Cave δημιουργούν μια ήρεμη, σχεδόν υδάτινη κίνηση. Η λίμνη του τίτλου γίνεται τόπος μνήμης και εσωτερικής αναμονής, πριν το album ανοίξει σε μεγαλύτερη ένταση.</t>
+  </si>
+  <si>
+    <t>Από τις πιο προσωπικές και εύθραυστες στιγμές. Οι βάτραχοι λειτουργούν σαν φυσικός, χαμηλός ήχος μέσα στη νύχτα, ενώ ο Cave περνά από παρατήρηση σε μεταφυσική σκέψη. Το τραγούδι δεν κυνηγά άμεσο chorus· χτίζει αργά μια αίσθηση θαύματος και θλίψης, πριν καταλήξει σε πλούσια, σχεδόν χορωδιακή ανακούφιση.</t>
+  </si>
+  <si>
+    <t>Η πιο καθαρή διακήρυξη του δίσκου. Η χαρά δεν παρουσιάζεται σαν μόνιμη ευφορία αλλά σαν πράξη αντίστασης απέναντι στον φόβο και στην απώλεια. Η μίξη του Fridmann επιτρέπει στα πνευστά και στις φωνές να φτάνουν σε μεγάλη κορύφωση, χωρίς να χαθεί η εκφραστικότητα του Cave. Είναι από τα tracks που εξηγούν γιατί οι κριτικοί βλέπουν το album ως “triumphant light”. 1261</t>
+  </si>
+  <si>
+    <t>Πιο αφηγηματικό και συγκρατημένο. Ο τίτλος παραπέμπει σε τελευταία απόπειρα σωτηρίας, όμως ο Cave αποφεύγει την εύκολη δραματοποίηση. Η σύνθεση κρατά χαμηλότερη ένταση και δίνει έμφαση στην αμφιβολία, στην ανθρώπινη αδυναμία και στην ανάγκη για σύνδεση. Λειτουργεί ως ανάσα μετά τις υψηλές κορυφώσεις των προηγούμενων tracks.</t>
+  </si>
+  <si>
+    <t>Ατμοσφαιρικό, αφηγηματικό και γεμάτο παράξενες, σχεδόν παιδικές εικόνες. Τα “κανέλα άλογα” λειτουργούν σαν ονειρικό σύμβολο κίνησης, μνήμης και φαντασίας. Η παραγωγή δεν είναι τόσο εκρηκτική όσο στο “Wild God”, αλλά είναι πλούσια σε textures και αφήνει τον Cave να κινείται ανάμεσα σε ψίθυρο και δραματική απαγγελία.</t>
+  </si>
+  <si>
+    <t>Το πιο καθαρά gospel-oriented κομμάτι μετά το title track. Η “μεταστροφή” δεν πρέπει να διαβαστεί στενά ως θρησκευτική αλλαγή· είναι η εμπειρία του να αλλάζεις εσωτερικά, να αποδέχεσαι τη ζωή ή να βλέπεις τον κόσμο από νέα οπτική. Η μπάντα μετατρέπει αυτή την ιδέα σε δυναμική art-rock κλιμάκωση με hymn-like χρώμα.</t>
+  </si>
+  <si>
+    <t>Σύντομο, χορωδιακό epilogue. Η βιβλική εικόνα του νερού που καλύπτει τη θάλασσα χρησιμοποιείται ως τελικό σύμβολο πληρότητας, αγάπης και διάλυσης των ορίων. Δεν κλείνει με rock climax· προτιμά μια ήρεμη, σχεδόν ιερή αποχώρηση, αφήνοντας τον ακροατή σε κατάσταση αποδοχής.</t>
+  </si>
+  <si>
+    <t>Το title track είναι το πιο άμεσο και εκρηκτικό statement του δίσκου. Brass, χορωδιακές φωνές, κιθάρες και ρυθμός μετατρέπουν την ιδέα ενός “άγριου θεού” σε κάτι διφορούμενο, δύναμη που απειλεί αλλά και απελευθερώνει. Ο Cave δεν παρουσιάζει μια οργανωμένη θρησκευτική βεβαιότητα· χρησιμοποιεί θρησκευτική γλώσσα για να περιγράψει ένα ξέσπασμα ζωής. Ήταν το πρώτο single του album. 1256</t>
+  </si>
+  <si>
+    <t>Εξωστρεφής, σχεδόν ecstatic σύνθεση. Ο επαναλαμβανόμενος τίτλος μοιάζει σαν έκρηξη θαυμασμού, αλλά διατηρεί την ιδιαίτερη Cave αμφισημία, η ομορφιά είναι πάντα περαστική, εύθραυστη και συνδεδεμένη με τη μνήμη. Οι φωνές και οι ενορχηστρωτικές κορυφώσεις το κάνουν από τα πιο “ζωντανά” tracks του δίσκου.</t>
+  </si>
+  <si>
+    <t>Η πιο εύθραυστη και άμεση μπαλάντα του δίσκου. Αντί για εκρηκτική λύτρωση, προσφέρει ήσυχη συνοδεία μέσα σε μια “μακρά σκοτεινή νύχτα”. Το πιάνο και η φωνή είναι στο κέντρο, με την ενορχήστρωση να λειτουργεί υποστηρικτικά. Δείχνει ότι το album δεν εγκαταλείπει τη θλίψη ,απλώς την περιβάλλει με μεγαλύτερη τρυφερότητα.</t>
   </si>
 </sst>
 </file>
@@ -8982,7 +9090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -11429,6 +11537,38 @@
       </c>
       <c r="J76" s="11" t="s">
         <v>2519</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="42" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D77" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E77" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>2566</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>2554</v>
+      </c>
+      <c r="I77" s="11" t="s">
+        <v>2568</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>2569</v>
       </c>
     </row>
   </sheetData>
@@ -11581,6 +11721,7 @@
     <hyperlink ref="I75" r:id="rId146" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
     <hyperlink ref="J76" r:id="rId147" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
     <hyperlink ref="I76" r:id="rId148" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
+    <hyperlink ref="I77" r:id="rId149" xr:uid="{764AE888-2456-4D6C-B45F-9B2E88E39CFB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11588,7 +11729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I707"/>
+  <dimension ref="A1:I717"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -30816,6 +30957,276 @@
       </c>
       <c r="I707" s="6"/>
     </row>
+    <row r="708" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A708" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B708" s="6">
+        <v>1</v>
+      </c>
+      <c r="C708" s="22" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D708" s="7" t="s">
+        <v>2570</v>
+      </c>
+      <c r="E708" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F708" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G708" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H708" s="25" t="s">
+        <v>2580</v>
+      </c>
+      <c r="I708" s="6"/>
+    </row>
+    <row r="709" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A709" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B709" s="6">
+        <v>2</v>
+      </c>
+      <c r="C709" s="22" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D709" s="7" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E709" s="20">
+        <v>3.99</v>
+      </c>
+      <c r="F709" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G709" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H709" s="25" t="s">
+        <v>2587</v>
+      </c>
+      <c r="I709" s="6"/>
+    </row>
+    <row r="710" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A710" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B710" s="6">
+        <v>3</v>
+      </c>
+      <c r="C710" s="22" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D710" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="E710" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F710" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G710" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H710" s="25" t="s">
+        <v>2581</v>
+      </c>
+      <c r="I710" s="6"/>
+    </row>
+    <row r="711" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A711" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B711" s="6">
+        <v>4</v>
+      </c>
+      <c r="C711" s="22" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D711" s="7" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E711" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F711" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G711" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H711" s="25" t="s">
+        <v>2582</v>
+      </c>
+      <c r="I711" s="6"/>
+    </row>
+    <row r="712" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A712" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B712" s="6">
+        <v>5</v>
+      </c>
+      <c r="C712" s="22" t="s">
+        <v>2560</v>
+      </c>
+      <c r="D712" s="7" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E712" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F712" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G712" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H712" s="25" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I712" s="6"/>
+    </row>
+    <row r="713" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A713" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B713" s="6">
+        <v>6</v>
+      </c>
+      <c r="C713" s="22" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D713" s="7" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E713" s="20">
+        <v>4</v>
+      </c>
+      <c r="F713" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G713" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H713" s="25" t="s">
+        <v>2585</v>
+      </c>
+      <c r="I713" s="6"/>
+    </row>
+    <row r="714" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A714" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B714" s="6">
+        <v>7</v>
+      </c>
+      <c r="C714" s="22" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D714" s="7" t="s">
+        <v>2576</v>
+      </c>
+      <c r="E714" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F714" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G714" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H714" s="25" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I714" s="6"/>
+    </row>
+    <row r="715" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A715" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B715" s="6">
+        <v>8</v>
+      </c>
+      <c r="C715" s="22" t="s">
+        <v>2563</v>
+      </c>
+      <c r="D715" s="7" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E715" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F715" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G715" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H715" s="25" t="s">
+        <v>2589</v>
+      </c>
+      <c r="I715" s="6"/>
+    </row>
+    <row r="716" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A716" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B716" s="6">
+        <v>9</v>
+      </c>
+      <c r="C716" s="22" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D716" s="7" t="s">
+        <v>2578</v>
+      </c>
+      <c r="E716" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F716" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G716" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H716" s="25" t="s">
+        <v>2588</v>
+      </c>
+      <c r="I716" s="6"/>
+    </row>
+    <row r="717" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A717" s="6">
+        <v>31604863</v>
+      </c>
+      <c r="B717" s="6">
+        <v>10</v>
+      </c>
+      <c r="C717" s="22" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D717" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E717" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F717" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G717" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H717" s="25" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I717" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C711D33-BBF5-4A7C-8E7B-BC4F7FBB8E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D4244C-8843-43FB-A920-143C64EFF60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="2666">
   <si>
     <t>No</t>
   </si>
@@ -8491,6 +8491,144 @@
   </si>
   <si>
     <t>Polydor / DeAgostini (Italian Repress 2023 - 180g / SST Kr Cut / MPO)</t>
+  </si>
+  <si>
+    <t>Billy Cobham</t>
+  </si>
+  <si>
+    <t>Spectrum</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/12282039-Billy-Cobham-Spectrum</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qn2Ct1bPF8a-CJzyIurxQpC5OyfbTzLZGs7gSbQbayc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEyMjgy/MDM5LTE1MzQ1OTA2/NzMtOTU2OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP2167, Atlantic – MOVLP2167 (Europe, Jul 20, 2018, 150 gr, Gatefold).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Issued in a gatefold cover. There is no acoustic piano on "Red Baron". Moog sample and hold devices were used on drum solos on "Stratus" and "Snoopy's Search". Originally released ℗ &amp; © 1973 Atlantic Recording Corporation, manufactured and distributed 2018, made in EU.</t>
+  </si>
+  <si>
+    <t>Quadrant 4</t>
+  </si>
+  <si>
+    <t>Searching For The Right Door</t>
+  </si>
+  <si>
+    <t>Anxiety</t>
+  </si>
+  <si>
+    <t>Taurian Matador</t>
+  </si>
+  <si>
+    <t>Stratus</t>
+  </si>
+  <si>
+    <t>To The Women In My Life</t>
+  </si>
+  <si>
+    <t>Le Lis</t>
+  </si>
+  <si>
+    <t>Snoopy’s Search</t>
+  </si>
+  <si>
+    <t>Red Baron</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Rock [Electric Jazz, Funk Fusion, Progressive Jazz]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Rock [High-Energy Fusion, Jazz-Funk, Drum-Guitar Showcase]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Ambient Jazz [Solo Drum Interlude, Free-Form Percussion]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Post-Bop [Electric-Acoustic Fusion, Modal Jazz, Horn-led Ensemble]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Free Jazz [Solo Drum Interlude, Avant-Jazz Percussion]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Rock [Latin-tinged Fusion, Horn-driven Jazz, Dynamic Ensemble]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Funk [Funk Fusion, Electric Jazz, Groove Epic]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Ambient Jazz [Solo Drum Meditation, Percussion Interlude]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Post-Bop [Acoustic-Electric Fusion, Lyrical Jazz, Horn Arrangement]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Free Jazz [Solo Drum Interlude, Percussive Transition]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Funk [Funk Rock, Jazz-Rock, Guitar-led Fusion]</t>
+  </si>
+  <si>
+    <t>Δεύτερη solo drum miniature, πιο νευρική και fragmented. Η “αγωνία” δεν περιγράφεται στιχουργικά αλλά μέσα από κομμένες φράσεις, αιφνίδιες παύσεις και αίσθηση ότι ο ρυθμός προσπαθεί να σταθεροποιηθεί χωρίς να το καταφέρνει. Έχει μικρότερη αυτόνομη replay value από το “Searching…”, αλλά λειτουργεί αποτελεσματικά ως ψυχολογική προετοιμασία για την πιο εκρηκτική συνέχεια.</t>
+  </si>
+  <si>
+    <t>Εδώ η μπάντα επανέρχεται με πιο έντονο, φουσκωμένο ensemble sound. Ο τίτλος συνδυάζει ταυρική δύναμη και matador δραματικότητα, και η μουσική το υπηρετεί με κοφτά riffs, πνευστά που ανεβάζουν την ένταση και drums που κινούνται σαν διαρκής πρόκληση. Είναι λιγότερο “funk anthem” από το “Stratus”, αλλά πιο πολυσύνθετο σε διάλογο οργάνων και αλλαγές μορφής.</t>
+  </si>
+  <si>
+    <t>Πολύ σύντομη, τρυφερή solo-percussion αφιέρωση. Μετά το μεγάλο ηλεκτρικό τοπίο του “Stratus”, ο Cobham κατεβάζει την ένταση και εστιάζει σε υφή, αντήχηση και ήπια κίνηση. Είναι λιγότερο αυτάρκες από τα μεγάλα tracks, αλλά είναι απαραίτητη παύση ώστε το “Le Lis” να ακούγεται σαν νέα αρχή.</t>
+  </si>
+  <si>
+    <t>Η τελευταία solo drum γέφυρα. Με παιχνιδιάρικο τίτλο αλλά τεταμένη εκτέλεση, οδηγεί οργανικά στο “Red Baron”. Είναι σχεδόν σαν ο Cobham να καθαρίζει τον ρυθμικό ορίζοντα πριν την τελική επίθεση. Ως μεμονωμένο track είναι σύντομο και ελλειπτικό· ως μετάβαση είναι ιδιαίτερα αποτελεσματικό.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η πιο λυρική και refined ensemble σύνθεση της B πλευράς. Η ακουστική βάση με Ron Carter, το flute και τα saxophones του Joe Farrell, τα πνευστά του Jimmy Owens και η κιθάρα του John Tropea δημιουργούν χώρο περισσότερο κοντά σε post-bop και chamber-jazz παρά σε fusion-rock. Το electric στοιχείο παραμένει, αλλά υπηρετεί μια μελωδία με λεπτότητα και άρωμα. Είναι το κομμάτι που αποδεικνύει πως το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Spectrum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> δεν είναι μονοδιάστατο “drum-and-guitar blast”.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το άλμπουμ ανοίγει με απόλυτη ένταση. Είναι γρήγορο, κοφτό και σχεδόν rock στη δύναμή του, αλλά η εσωτερική του λειτουργία είναι jazz fusion, σύνθετα accents, μετακινήσεις δυναμικής και συνεχής διάλογος ανάμεσα σε drums, κιθάρα και ηλεκτρικό πιάνο. Ο Cobham δεν παίζει απλώς γρήγορα· οργανώνει τα breaks και τις τονισμένες χτυπήσεις σαν βασικά συνθετικά motifs. Η κιθάρα του Tommy Bolin δίνει σκληρή, σχεδόν proto-metal edge, ενώ ο Jan Hammer απαντά με ηλεκτρικό πιάνο και synthesizer υφές.</t>
+  </si>
+  <si>
+    <t>Σύντομη solo-percussion είσοδος που μετατρέπει την ταχύτητα του “Quadrant 4” σε ανοιχτό ρυθμικό χώρο. Ο τίτλος ταιριάζει απόλυτα, ο Cobham μοιάζει να ψάχνει την “πόρτα” που οδηγεί στο επόμενο μουσικό περιβάλλον. Δεν πρόκειται για τραγούδι με συμβατική μελωδία· είναι ρυθμική αφήγηση, με κάθε χτύπημα να μετακινεί την ένταση και την κατεύθυνση.</t>
+  </si>
+  <si>
+    <t>Το κεντρικό ομώνυμο μέρος δίνει στον δίσκο πιο πολυεπίπεδη, modal jazz-fusion διάσταση. Η παρουσία ακουστικού μπάσου από τον Ron Carter, congas από τον Ray Barretto και πνευστών από Joe Farrell/Jimmy Owens διαφοροποιεί το κομμάτι από το electric-rock attack της πρώτης σύνθεσης. Το “Spectrum” δικαιολογεί το όνομα του album, παρουσιάζει ευρύ φάσμα χρωμάτων, jazz αυτοσχεδιασμό, latin percussion, electric piano, horns και προσεκτικά οργανωμένη δυναμική.</t>
+  </si>
+  <si>
+    <t>Η κορυφή του album και ένα από τα μεγάλα grooves στην ιστορία του jazz fusion. Σχεδόν δέκα λεπτά, χτίζεται πάνω σε ηλεκτρικό bass vamp, σταθερό αλλά περίπλοκο drum pocket, ηλεκτρικό πιάνο και κιθάρες που κινούνται με υπομονή. Η ιδιοφυΐα του είναι η οικονομία, δεν χρειάζεται γρήγορα breaks ή συνεχείς αλλαγές για να κρατήσει ενδιαφέρον. Οι μουσικοί προσθέτουν μικρές μεταβολές, εναλλάσσοντας ένταση και χώρο, μέχρι το groove να γίνει σχεδόν υπνωτικό. Το “Stratus” δείχνει γιατί ο Cobham είναι μεγάλος συνθέτης και bandleader, όχι μόνο τεχνικός drummer.</t>
+  </si>
+  <si>
+    <t>Το άλλο μεγάλο fusion anthem του δίσκου. Η κιθάρα του Bolin, τα Rhodes/Moog του Hammer, το μπάσο του Sklar και το drumming του Cobham δημιουργούν ένα funk-rock groove με αίσθηση ταχύτητας και ελέγχου. Ο τίτλος παραπέμπει στον θρυλικό πιλότο του Α’ Παγκοσμίου Πολέμου, αλλά η μουσική δεν αφηγείται κυριολεκτικά μια αερομαχία, μεταφέρει κίνηση, άνοδο, ακρίβεια και νευρική ενέργεια. Είναι θριαμβευτικό κλείσιμο, με riff που μένει αμέσως στη μνήμη και παραγωγή που κρατά κάθε όργανο σε διακριτό ρόλο.</t>
   </si>
 </sst>
 </file>
@@ -9017,7 +9155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -11557,6 +11695,38 @@
       </c>
       <c r="J79" s="11" t="s">
         <v>2517</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>2630</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D80" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E80" s="10">
+        <v>3.79</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>2645</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>2634</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>2632</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>2633</v>
       </c>
     </row>
   </sheetData>
@@ -11714,6 +11884,8 @@
     <hyperlink ref="J78" r:id="rId151" xr:uid="{C8E04EB8-2ACF-4142-A3C6-5AE9F3584ECD}"/>
     <hyperlink ref="J79" r:id="rId152" xr:uid="{878F8657-2717-44A5-8B6C-025F2EE420EB}"/>
     <hyperlink ref="I79" r:id="rId153" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
+    <hyperlink ref="I80" r:id="rId154" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
+    <hyperlink ref="J80" r:id="rId155" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11721,7 +11893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I737"/>
+  <dimension ref="A1:I747"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -31763,6 +31935,270 @@
       </c>
       <c r="I737" s="6"/>
     </row>
+    <row r="738" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A738" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B738" s="6">
+        <v>1</v>
+      </c>
+      <c r="C738" s="22" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D738" s="7" t="s">
+        <v>2646</v>
+      </c>
+      <c r="E738" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F738" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G738" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H738" s="7" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I738" s="6"/>
+    </row>
+    <row r="739" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A739" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B739" s="6">
+        <v>2</v>
+      </c>
+      <c r="C739" s="22" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D739" s="7" t="s">
+        <v>2647</v>
+      </c>
+      <c r="E739" s="20">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F739" s="12">
+        <v>4</v>
+      </c>
+      <c r="G739" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H739" s="7" t="s">
+        <v>2662</v>
+      </c>
+      <c r="I739" s="6"/>
+    </row>
+    <row r="740" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A740" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B740" s="6">
+        <v>3</v>
+      </c>
+      <c r="C740" s="22" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D740" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="E740" s="20"/>
+      <c r="F740" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G740" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H740" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="I740" s="6"/>
+    </row>
+    <row r="741" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A741" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B741" s="6">
+        <v>4</v>
+      </c>
+      <c r="C741" s="22" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D741" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="E741" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F741" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G741" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H741" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I741" s="6"/>
+    </row>
+    <row r="742" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A742" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B742" s="6">
+        <v>5</v>
+      </c>
+      <c r="C742" s="22" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D742" s="7" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E742" s="20"/>
+      <c r="F742" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G742" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H742" s="7" t="s">
+        <v>2657</v>
+      </c>
+      <c r="I742" s="6"/>
+    </row>
+    <row r="743" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A743" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B743" s="6">
+        <v>6</v>
+      </c>
+      <c r="C743" s="22" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D743" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="E743" s="20">
+        <v>4.2</v>
+      </c>
+      <c r="F743" s="12">
+        <v>5</v>
+      </c>
+      <c r="G743" s="12">
+        <v>5</v>
+      </c>
+      <c r="H743" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="I743" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="744" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A744" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B744" s="6">
+        <v>7</v>
+      </c>
+      <c r="C744" s="22" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D744" s="7" t="s">
+        <v>2652</v>
+      </c>
+      <c r="E744" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F744" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G744" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H744" s="7" t="s">
+        <v>2658</v>
+      </c>
+      <c r="I744" s="6"/>
+    </row>
+    <row r="745" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A745" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B745" s="6">
+        <v>8</v>
+      </c>
+      <c r="C745" s="22" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D745" s="7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="E745" s="20"/>
+      <c r="F745" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G745" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H745" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="I745" s="6"/>
+    </row>
+    <row r="746" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A746" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B746" s="6">
+        <v>9</v>
+      </c>
+      <c r="C746" s="22" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D746" s="7" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E746" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F746" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G746" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H746" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="I746" s="6"/>
+    </row>
+    <row r="747" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="6">
+        <v>12282039</v>
+      </c>
+      <c r="B747" s="6">
+        <v>10</v>
+      </c>
+      <c r="C747" s="22" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D747" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="E747" s="20"/>
+      <c r="F747" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G747" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H747" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="I747" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D4244C-8843-43FB-A920-143C64EFF60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F6D08D-E94C-4CDF-A80D-8FD456460C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="2666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="2700">
   <si>
     <t>No</t>
   </si>
@@ -8629,6 +8629,108 @@
   </si>
   <si>
     <t>Το άλλο μεγάλο fusion anthem του δίσκου. Η κιθάρα του Bolin, τα Rhodes/Moog του Hammer, το μπάσο του Sklar και το drumming του Cobham δημιουργούν ένα funk-rock groove με αίσθηση ταχύτητας και ελέγχου. Ο τίτλος παραπέμπει στον θρυλικό πιλότο του Α’ Παγκοσμίου Πολέμου, αλλά η μουσική δεν αφηγείται κυριολεκτικά μια αερομαχία, μεταφέρει κίνηση, άνοδο, ακρίβεια και νευρική ενέργεια. Είναι θριαμβευτικό κλείσιμο, με riff που μένει αμέσως στη μνήμη και παραγωγή που κρατά κάθε όργανο σε διακριτό ρόλο.</t>
+  </si>
+  <si>
+    <t>Million Mile Reflections</t>
+  </si>
+  <si>
+    <t>The Charlie Daniels Band</t>
+  </si>
+  <si>
+    <t>Epic – JE 35751 (US, 1979, Terre Haute Pressing, Mastered at Capitol Mastering).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded at Woodland Sound Studios, Nashville, Tennessee. Mixed at Westlake Sound, Los Angeles, California. Mastered by Wally Traugott at Capitol Mastering. Features the legendary runout inscriptions dedicated to Ronnie Van Zant.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/8816501-The-Charlie-Daniels-Band-Million-Mile-Reflections</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/0IPV3OU36c9rWorTc2XXn8asLRDNBb9-4eh0wpC455E/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTg4MTY1/MDEtMTQ2OTM4Mjg0/My05OTY0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Passing Lane</t>
+  </si>
+  <si>
+    <t>Blue Star</t>
+  </si>
+  <si>
+    <t>Jitterbug</t>
+  </si>
+  <si>
+    <t>Behind Your Eyes</t>
+  </si>
+  <si>
+    <t>Reflections</t>
+  </si>
+  <si>
+    <t>The Devil Went Down To Georgia</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Blind Man</t>
+  </si>
+  <si>
+    <t>Rainbow Ride</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Boogie Rock, Outlaw Country, Fiddle Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Driving Boogie, Road Rock, Fiddle Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Melodic Southern Rock, Country Blues]</t>
+  </si>
+  <si>
+    <t>Country Rock, Rock &amp; Roll [Western Swing, Boogie, Roots Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Country-Rock Ballad, Melodic Roots Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Roots Rock [Memorial Ballad, Heartland Rock, Southern Tribute]</t>
+  </si>
+  <si>
+    <t>Country Rock, Southern Rock [Fiddle Duel, Southern Boogie, Narrative Novelty Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Blues Rock [Swamp Rock, Southern Blues, Roots Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Country Rock [Story Song, Bluesy Country Rock, Moral Narrative]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Progressive Country Rock [Extended Southern Rock, Psychedelic Roots, Fiddle Jam]</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό και λιγότερο επιθετικό από το “Passing Lane”, με southern-rock βάση και blues χρώμα. Ο τίτλος δημιουργεί νυχτερινή, σχεδόν ονειρική εικόνα, ενώ η μπάντα δίνει χώρο σε keyboards και κιθάρες να χτίσουν πιο ανοιχτό ηχητικό πεδίο. Το fiddle δεν λειτουργεί μόνο ως country διακόσμηση· εμφανίζεται σαν δεύτερη lead φωνή δίπλα στον Daniels. Το κομμάτι βοηθά την πρώτη πλευρά να αποφύγει τη μονοτονία, περνώντας από την οδήγηση και το boogie σε πιο στοχαστικό southern-rock κλίμα.</t>
+  </si>
+  <si>
+    <t>Η πιο ρητή σύνδεση του album με παλαιότερες αμερικανικές χορευτικές φόρμες. Η λέξη “jitterbug” παραπέμπει σε swing dance, αλλά οι Charlie Daniels Band δεν κάνουν revival swing· μετατρέπουν την ιδέα σε ζωηρό country-rock/boogie track. Το rhythm section έχει ελαστικότητα, τα keys προσθέτουν χρώμα και το fiddle δίνει την αναγνωρίσιμη southern ταυτότητα. Λειτουργεί σαν ανάλαφρη, σχεδόν live-set στιγμή, χωρίς να διακόπτει την οργανική ροή του δίσκου.</t>
+  </si>
+  <si>
+    <t>Story-song με moral/blues-rock χαρακτήρα. Η μορφή του τυφλού δεν χρησιμοποιείται απλώς κυριολεκτικά· λειτουργεί και ως εικόνα κάποιου που ίσως βλέπει βαθύτερα από τους ανθρώπους που θεωρούν ότι έχουν καθαρή όραση. Η μπάντα κρατά μεσαία ένταση, αφήνοντας τον Daniels να δουλέψει σαν αφηγητής. Το τραγούδι έχει πιο σκοτεινή και στοχαστική αίσθηση, αποτελώντας την αναγκαία μετάβαση από τον μύθο και τη γεωγραφική ατμόσφαιρα του “Mississippi” προς την ανοιχτή κορύφωση του τελευταίου track.</t>
+  </si>
+  <si>
+    <t>Το άλμπουμ ανοίγει με road-rock κίνηση και southern boogie ενέργεια. Ο τίτλος, η «λωρίδα προσπέρασης», ταιριάζει απόλυτα στον ρόλο του τραγουδιού, η Charlie Daniels Band μπαίνει στο album με ταχύτητα, fiddle lines που κόβουν πάνω από τις κιθάρες και ένα rhythm section που δεν βαραίνει υπερβολικά το groove. Δεν είναι το πιο σύνθετο κομμάτι του δίσκου, αλλά είναι σωστή εισαγωγή στο ταξιδιωτικό, κινητικό πνεύμα του album. Η φωνή του Daniels ακούγεται άμεση και γήινη, σαν αφηγητής που ξεκινά διαδρομή και όχι σαν frontman που αναζητά θεαματική κορύφωση.</t>
+  </si>
+  <si>
+    <t>Πιο ήσυχο και εσωτερικό τραγούδι. Εδώ η μπάντα περιορίζει την εξωστρεφή boogie ενέργεια και δίνει μεγαλύτερο βάρος στη φωνή του Daniels και στη μελωδία. Ο τίτλος υπονοεί μια προσπάθεια να δεις τι κρύβεται πίσω από την εξωτερική όψη ενός ανθρώπου, μνήμη, φόβος, αγάπη ή εσωτερική σύγκρουση. Δεν είναι μπαλάντα με αυστηρά country τρόπο· διατηρεί την electric southern-rock βάση, αλλά με μεγαλύτερη συναισθηματική συγκράτηση.</t>
+  </si>
+  <si>
+    <t>Το συναισθηματικό κέντρο της A πλευράς. Είναι τραγούδι μνήμης και αποχαιρετισμού, αφιερωμένο σε χαμένους μουσικούς ,ιδιαίτερα στους Elvis Presley, Janis Joplin και Ronnie Van Zant. Ο Daniels είχε γράψει ποίημα μετά τον θάνατο του Van Zant στο αεροπορικό δυστύχημα των Lynyrd Skynyrd και η θλίψη αυτής της απώλειας περνά στο τραγούδι. Δεν πρόκειται για θεατρικό memorial, η ερμηνεία είναι απλή, άμεση και πικρή, με τη μπάντα να προτιμά συναισθηματική καθαρότητα αντί για υπερβολική δραματοποίηση. Στη δική σου Wally/Capitol cut, είναι track που αξίζει να ακούσεις για καθαρότητα φωνής, βάθος στα keyboards και χαμηλό surface noise.</t>
+  </si>
+  <si>
+    <t>Το defining τραγούδι της Charlie Daniels Band και ένα από τα πιο αναγνωρίσιμα country-rock singles όλων των εποχών. Η πλοκή είναι λαϊκός μύθος, ο Διάβολος, πίσω στη Georgia, αναζητά μια ψυχή για να κερδίσει και προκαλεί τον νεαρό fiddler Johnny σε μονομαχία. Το στοίχημα είναι ένα χρυσό fiddle απέναντι στην ψυχή του Johnny. Η δύναμη του τραγουδιού βρίσκεται στο ότι η αφήγηση δεν σταματά τη μουσική· το fiddle contest είναι η ίδια η δράση της ιστορίας. Ο Daniels φέρνει καθαρή southern αφήγηση, η μπάντα παίζει με boogie ένταση και το βιολί μετατρέπεται σε όργανο μονομαχίας. Το τραγούδι έγινε το μεγαλύτερο hit του Daniels και καθόρισε τη δημόσια εικόνα του ως fiddle-driven southern-rock storyteller.</t>
+  </si>
+  <si>
+    <t>Μετά την εκρηκτική “Georgia”, η B πλευρά περνά σε πιο βαριά, swampy southern-blues περιοχή. Το Mississippi είναι κάτι περισσότερο από γεωγραφικό όνομα, συμβολίζει τον ποταμό, τη νότια ιστορία, τη διαδρομή του blues και έναν κόσμο όπου το ταξίδι και η επιβίωση είναι δεμένα. Η κιθάρα και τα keys χτίζουν πιο σκοτεινό, υγρό groove, ενώ ο Daniels τραγουδά με τη χαμηλή, βραχνή πλευρά της φωνής του. Είναι από τα tracks όπου φαίνεται πιο καθαρά ότι η Charlie Daniels Band δεν είναι μόνο country act αλλά πλήρης southern-rock/blues μπάντα.</t>
+  </si>
+  <si>
+    <t>Το εκτεταμένο φινάλε του album, διάρκειας περίπου επτάμισι λεπτών. Σε αντίθεση με το compact storytelling του “Devil…”, εδώ οι Charlie Daniels Band αφήνουν τη μουσική να αναπτυχθεί, fiddle, κιθάρες, keys και rhythm section παίρνουν περισσότερο χώρο, μετατρέποντας το southern rock σε ανοιχτή jam φόρμα. Ο τίτλος φέρνει μια σχεδόν ψυχεδελική εικόνα φυγής και υπέρβασης ,μια βόλτα στο ουράνιο τόξο, και η μουσική αντιστοιχεί σε αυτή την αίσθηση με σταδιακή κλιμάκωση και μεγαλύτερο ηχητικό ορίζοντα. Είναι το κομμάτι που δείχνει την πιο adventurous πλευρά της μπάντας και κλείνει τον δίσκο όχι με τελεία, αλλά με διαδρομή που συνεχίζεται. Στη δική σου pressing, είναι το βασικό τεστ για inner-groove distortion, επειδή βρίσκεται στο τέλος της B πλευράς και συνδυάζει διάρκεια, δυναμική και υψηλές συχνότητες από το fiddle.</t>
   </si>
 </sst>
 </file>
@@ -9155,7 +9257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -11727,6 +11829,38 @@
       </c>
       <c r="J80" s="11" t="s">
         <v>2633</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D81" s="6">
+        <v>1979</v>
+      </c>
+      <c r="E81" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>2681</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>2668</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>2670</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>2671</v>
       </c>
     </row>
   </sheetData>
@@ -11886,6 +12020,8 @@
     <hyperlink ref="I79" r:id="rId153" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
     <hyperlink ref="I80" r:id="rId154" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
     <hyperlink ref="J80" r:id="rId155" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
+    <hyperlink ref="I81" r:id="rId156" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
+    <hyperlink ref="J81" r:id="rId157" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11893,7 +12029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I747"/>
+  <dimension ref="A1:I756"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -32199,6 +32335,251 @@
       </c>
       <c r="I747" s="6"/>
     </row>
+    <row r="748" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A748" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B748" s="6">
+        <v>1</v>
+      </c>
+      <c r="C748" s="22" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D748" s="7" t="s">
+        <v>2682</v>
+      </c>
+      <c r="E748" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F748" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G748" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H748" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="I748" s="6"/>
+    </row>
+    <row r="749" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A749" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B749" s="6">
+        <v>2</v>
+      </c>
+      <c r="C749" s="22" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D749" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="E749" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F749" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G749" s="12">
+        <v>4</v>
+      </c>
+      <c r="H749" s="7" t="s">
+        <v>2691</v>
+      </c>
+      <c r="I749" s="6"/>
+    </row>
+    <row r="750" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A750" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B750" s="6">
+        <v>3</v>
+      </c>
+      <c r="C750" s="22" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D750" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="E750" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="F750" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G750" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H750" s="7" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I750" s="6"/>
+    </row>
+    <row r="751" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A751" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B751" s="6">
+        <v>4</v>
+      </c>
+      <c r="C751" s="22" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D751" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E751" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F751" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G751" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H751" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="I751" s="6"/>
+    </row>
+    <row r="752" spans="1:9" ht="92.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B752" s="6">
+        <v>5</v>
+      </c>
+      <c r="C752" s="22" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D752" s="7" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E752" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F752" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G752" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H752" s="7" t="s">
+        <v>2696</v>
+      </c>
+      <c r="I752" s="6"/>
+    </row>
+    <row r="753" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A753" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B753" s="6">
+        <v>6</v>
+      </c>
+      <c r="C753" s="22" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D753" s="7" t="s">
+        <v>2687</v>
+      </c>
+      <c r="E753" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F753" s="12">
+        <v>5</v>
+      </c>
+      <c r="G753" s="12">
+        <v>5</v>
+      </c>
+      <c r="H753" s="7" t="s">
+        <v>2697</v>
+      </c>
+      <c r="I753" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="754" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B754" s="6">
+        <v>7</v>
+      </c>
+      <c r="C754" s="22" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D754" s="7" t="s">
+        <v>2688</v>
+      </c>
+      <c r="E754" s="20">
+        <v>3.06</v>
+      </c>
+      <c r="F754" s="12">
+        <v>4</v>
+      </c>
+      <c r="G754" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H754" s="7" t="s">
+        <v>2698</v>
+      </c>
+      <c r="I754" s="6"/>
+    </row>
+    <row r="755" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B755" s="6">
+        <v>8</v>
+      </c>
+      <c r="C755" s="22" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D755" s="7" t="s">
+        <v>2689</v>
+      </c>
+      <c r="E755" s="20">
+        <v>3.28</v>
+      </c>
+      <c r="F755" s="12">
+        <v>4</v>
+      </c>
+      <c r="G755" s="12">
+        <v>4</v>
+      </c>
+      <c r="H755" s="7" t="s">
+        <v>2693</v>
+      </c>
+      <c r="I755" s="6"/>
+    </row>
+    <row r="756" spans="1:9" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="6">
+        <v>8816501</v>
+      </c>
+      <c r="B756" s="6">
+        <v>9</v>
+      </c>
+      <c r="C756" s="22" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D756" s="7" t="s">
+        <v>2690</v>
+      </c>
+      <c r="E756" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F756" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G756" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H756" s="7" t="s">
+        <v>2699</v>
+      </c>
+      <c r="I756" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F6D08D-E94C-4CDF-A80D-8FD456460C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E57417-8B87-4EAE-AFA8-A66D3597E90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="2700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="2756">
   <si>
     <t>No</t>
   </si>
@@ -8731,6 +8731,294 @@
   </si>
   <si>
     <t>Το εκτεταμένο φινάλε του album, διάρκειας περίπου επτάμισι λεπτών. Σε αντίθεση με το compact storytelling του “Devil…”, εδώ οι Charlie Daniels Band αφήνουν τη μουσική να αναπτυχθεί, fiddle, κιθάρες, keys και rhythm section παίρνουν περισσότερο χώρο, μετατρέποντας το southern rock σε ανοιχτή jam φόρμα. Ο τίτλος φέρνει μια σχεδόν ψυχεδελική εικόνα φυγής και υπέρβασης ,μια βόλτα στο ουράνιο τόξο, και η μουσική αντιστοιχεί σε αυτή την αίσθηση με σταδιακή κλιμάκωση και μεγαλύτερο ηχητικό ορίζοντα. Είναι το κομμάτι που δείχνει την πιο adventurous πλευρά της μπάντας και κλείνει τον δίσκο όχι με τελεία, αλλά με διαδρομή που συνεχίζεται. Στη δική σου pressing, είναι το βασικό τεστ για inner-groove distortion, επειδή βρίσκεται στο τέλος της B πλευράς και συνδυάζει διάρκεια, δυναμική και υψηλές συχνότητες από το fiddle.</t>
+  </si>
+  <si>
+    <t>Heaven’s Not Overflowing</t>
+  </si>
+  <si>
+    <t>Albatross</t>
+  </si>
+  <si>
+    <t>Clean My Wounds</t>
+  </si>
+  <si>
+    <t>Without Wings</t>
+  </si>
+  <si>
+    <t>Broken Man</t>
+  </si>
+  <si>
+    <t>Señor Limpio</t>
+  </si>
+  <si>
+    <t>Mano De Mono</t>
+  </si>
+  <si>
+    <t>Seven Days</t>
+  </si>
+  <si>
+    <t>My Grain</t>
+  </si>
+  <si>
+    <t>Deliverance</t>
+  </si>
+  <si>
+    <t>Shake Like You</t>
+  </si>
+  <si>
+    <t>Shelter</t>
+  </si>
+  <si>
+    <t>Pearls Before Swine</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lord Of This World </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>(bonus)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Big Problems </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>(bonus)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fuel (Jam-Box Tape) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>(bonus)</t>
+    </r>
+  </si>
+  <si>
+    <t>Corrosion Of Conformity</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/6W72Z4yYFgbIGfEsT4PRyLfBltIFjE7balwykvpLGpE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIyMjk2/NjQzLTE2NDU3ODM0/NDItNzQ3MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/22296643-Corrosion-Of-Conformity-Deliverance</t>
+  </si>
+  <si>
+    <t>Century Media – 19549792740 (Europe, Feb 18, 2022 reissue, 2 x LP, Gatefold, Black 180 gram).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Remastered 180g 2LP edition featuring gatefold jacket with printed inner sleeves and hype sticker. Lacquer cut by FK at Celebrate Records GmbH, vinyl mastering by Will Borza at Will Borza Mastering, with original digital mastering by Bob Ludwig at Gateway Mastering. Includes 3 bonus tracks (D2 to D4), featuring a Black Sabbath cover ("Lord Of This World" on D2). Features the classic typography/spelling error on the back sleeve and side B label where track B3 is misspelled as "Mano De Mano". Notable runout quirk: Side B has a mistaken '7' in the etching that is scratched out, reading 1255757 corrected to 125575.</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Southern Metal [Stoner Metal, Heavy Rock, Crossover Metal]</t>
+  </si>
+  <si>
+    <t>Southern Metal, Sludge Metal [Heavy Southern Rock, Stoner Metal, Mid-tempo Riff Metal]</t>
+  </si>
+  <si>
+    <t>Southern Metal, Hard Rock [Melodic Heavy Rock, Stoner Rock, Southern Ballad]</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Southern Metal [Heavy Groove Metal, Stoner Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Acoustic Rock [Acoustic Interlude, Southern Folk, Dark Ballad]</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Southern Metal [Doom-tinged Heavy Rock, Blues Metal, Slow Groove]</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Hardcore Punk [Crossover Metal, Aggressive Stoner Rock, Punk Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Experimental Rock [Instrumental Interlude, Noise Rock, Guitar Texture]</t>
+  </si>
+  <si>
+    <t>Southern Metal, Sludge Metal [Dark Heavy Rock, Groove Metal, Bluesy Metal]</t>
+  </si>
+  <si>
+    <t>Experimental Metal, Ambient Rock [Sound Collage, Short Interlude, Transition]</t>
+  </si>
+  <si>
+    <t>Southern Metal, Stoner Rock [Heavy Blues, Groove Metal, Southern Riff Rock]</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Southern Metal [Doom Metal, Bass-led Heavy Rock, Dark Metal]</t>
+  </si>
+  <si>
+    <t>Southern Metal, Hard Rock [Boogie Metal, Heavy Rock, Southern Groove]</t>
+  </si>
+  <si>
+    <t>Southern Rock, Stoner Rock [Atmospheric Heavy Rock, Pedal-Steel Southern Rock]</t>
+  </si>
+  <si>
+    <t>Sludge Metal, Doom Metal [Heavy Doom, Southern Sludge, Epic Album Closer]</t>
+  </si>
+  <si>
+    <t>Doom Metal, Heavy Metal [Black Sabbath Cover, Proto-Doom, Heavy Blues]</t>
+  </si>
+  <si>
+    <t>Hardcore Punk, Crossover Thrash [Punk Metal, Early C.O.C. Throwback]</t>
+  </si>
+  <si>
+    <t>Stoner Rock, Jam Rock [Demo Jam, Riff Sketch, Archival Bonus]</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο υποτιμημένα κομμάτια του δίσκου. Με πιο αργή, βαρύτερη και πιο απειλητική κίνηση, μοιάζει να καταγράφει έναν κύκλο πίεσης, αναμονής ή επανάληψης. Οι κιθάρες κρατούν πυκνό southern-sludge riff, ενώ η φωνή του Keenan ακούγεται πιο κουρασμένη και σκοτεινή. Δεν έχει το άμεσο hook του “Clean My Wounds”, αλλά ανταμείβει την προσεκτική ακρόαση επειδή δίνει χώρο στο rhythm section και στις μικρές κιθαριστικές μεταβολές. Αναφέρεται συχνά μεταξύ των δυνατών deep cuts του album.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Σύντομη, σκληρή επιστροφή στο hardcore/crossover παρελθόν των C.O.C., με τον </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Reed Mullin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> στα lead vocals. Το κομμάτι υπενθυμίζει πόσο μεγάλη ήταν η απόσταση που κάλυψε η μπάντα από την αρχική punk/thrash περίοδο προς το southern metal του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Deliverance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>. Η ωμή ενέργειά του λειτουργεί καλά ως bonus, αλλά θα έσπαζε τη βαριά, μεθοδική ροή της αρχικής album sequence αν βρισκόταν μέσα σε αυτή.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Το title track είναι μία από τις πιο σκοτεινές στιγμές του δίσκου και δίνει χώρο στον </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Mike Dean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> στα lead vocals. Η “λύτρωση” του τίτλου δεν παρουσιάζεται ως θριαμβευτική απελευθέρωση· ακούγεται περισσότερο σαν κάτι αβέβαιο, βαρύ και ίσως ανέφικτο. Το μπάσο έχει κεντρικό ρόλο, η κιθάρα χτίζει doom ατμόσφαιρα και η αλλαγή φωνής από τον Keenan στον Dean μεταβάλλει όλο το χρώμα του album. Η κριτική έχει περιγράψει το κομμάτι ως “greasy” και βαριά southern-doom στιγμή, με το χαρακτηριστικό molten guitar texture του δίσκου.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ένα από τα πιο ατμοσφαιρικά και southern-tinged tracks της μπάντας. Η ανάγκη για “καταφύγιο” ακούγεται όχι ως ασφαλής λύση αλλά ως αναζήτηση μέσα σε σκοτεινή, ασταθή πραγματικότητα. Η χαμηλότερη ένταση, οι ανοιχτές κιθαριστικές υφές και τα πιο μελωδικά στοιχεία δίνουν χώρο στην ερμηνεία. Είναι από τις σύνθεσεις που υπογραμμίζουν ότι οι C.O.C. δεν είναι μόνο sludge riff machine· έχουν και τη δυνατότητα να γράφουν dark southern rock με πραγματική αίσθηση τοπίου και απομόνωσης. Οι κριτικές συχνά το αναφέρουν ως highlight.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεση ανάμνηση του crossover/hardcore παρελθόντος της μπάντας μέσα στο βασικό album. Γρήγορο, κοφτό και επιθετικό, αφήνει λιγότερο χώρο για southern-rock μελωδία και περισσότερη για punk-metal ένταση. Ο ισπανικός τίτλος ,“Κύριος Καθαρός”, ακούγεται ειρωνικός μέσα σε ένα τραγούδι που είναι βρώμικο, τραχύ και γεμάτο παραμόρφωση. Το track λειτουργεί σαν ξαφνική έκρηξη μετά το βαρύ “Broken Man” και θυμίζει ότι οι C.O.C. δεν εγκατέλειψαν το παρελθόν τους· το ενσωμάτωσαν σε ένα νέο heavy-rock σώμα.</t>
+  </si>
+  <si>
+    <t>Σύντομο αλλά πυκνό southern heavy-rock κομμάτι. Ο τίτλος παραπέμπει σε προσωπική υφή, σκληρότητα ή ιδιαιτερότητα χαρακτήρα ,“το δικό μου νεύρο/το δικό μου υλικό”. Η κιθάρα κινείται σε riff που έχει και bluesy λυγισμό και stoner βάρος, ενώ η μπάντα επαναφέρει πιο άμεσο groove μετά τα δύο interludes. Δεν είναι track που ζητά μεγάλη ανάπτυξη· λειτουργεί σαν compact, βρώμικο heavy-rock statement.</t>
+  </si>
+  <si>
+    <t>Το άλμπουμ ανοίγει με ένα mid-tempo riff που συνδυάζει Black Sabbath βάρος με southern-rock groove. Δεν βιάζεται να αποδείξει πόσο γρήγορο ή ακραίο είναι το συγκρότημα· αντίθετα, χτίζει μια μεγάλη, “λιωμένη” κιθαριστική μάζα πάνω στην οποία η βραχνή φωνή του Pepper Keenan ακούγεται σαν προειδοποίηση. Ο τίτλος δηλώνει ότι ο παράδεισος δεν είναι ένας εύκολος, απεριόριστος χώρος διαφυγής· η μουσική αντιστοιχεί σε αυτή τη δυσπιστία με αργή, γήινη και ασφυκτική κίνηση. Είναι ιδανικό opening statement, επειδή παρουσιάζει αμέσως τη νέα ταυτότητα των C.O.C., heavy metal με southern ψυχή και hardcore αποφασιστικότητα.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο αναγνωρίσιμα και μελωδικά τραγούδια των Corrosion Of Conformity. Το “albatross” είναι το βάρος που κουβαλά ένας άνθρωπος ,ενοχή, μοίρα, αποτυχία ή δεσμός που δεν μπορεί να αποτινάξει. Η σύνθεση λειτουργεί σαν “heavy dirge”, δηλαδή σαν αργή, βαριά μπαλάντα χωρίς να γίνεται soft rock. Το riff έχει μολυβένια κίνηση, η ερμηνεία του Keenan είναι πικρή αλλά συγκρατημένη και το refrain μετατρέπει την αποξένωση σε κάτι σχεδόν ύμνιο. Η επιτυχία του βρίσκεται στην ισορροπία, έχει αρκετή μελωδία για να μείνει, αλλά δεν χάνει ποτέ το sludge βάρος του.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο hard-rock anthem του δίσκου. Το riff έχει κοφτό, σχεδόν Thin Lizzy–τύπου διπλοκιθαριστικό χαρακτήρα, αλλά περνά μέσα από C.O.C. distortion και βαρύ groove. Ο στίχος “Help me Jesus, help me clean my wounds / He said he cannot heal that kind” δίνει στην σύνθεση ψυχικό και πνευματικό βάρος, ο αφηγητής δεν ζητά απλή λύτρωση, αλλά αναγνωρίζει τραύματα που δεν θεραπεύονται εύκολα ούτε από πίστη ούτε από εξωτερική βοήθεια. Είναι το πιο “single-ready” τραγούδι της μπάντας, χωρίς να έχει υποστεί εμπορική εξομάλυνση. Η κριτική έχει συχνά τονίσει το anthemic chug του κομματιού και τη θέση του ως μία από τις δύο μεγάλες πύλες εισόδου στο album.</t>
+  </si>
+  <si>
+    <t>Σύντομο ακουστικό instrumental interlude. Μετά το πυκνό riffing του “Clean My Wounds”, λειτουργεί σαν αποσυμπίεση και υπενθύμιση ότι η μπάντα δεν στηρίζεται μόνο στο distortion. Ο τίτλος ,“χωρίς φτερά”, έχει αίσθηση αδυναμίας ή πτώσης, και η μουσική δεν προσπαθεί να το μετατρέψει σε μεγάλο δράμα, μένει λιτή, γυμνή και μελαγχολική. Δεν είναι αυτόνομη κορυφή, αλλά είναι κρίσιμο για την αλληλουχία, επειδή προετοιμάζει τη βαρύτερη, πιο αργή διάθεση του “Broken Man”.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε βαριά, doom-tinged φόρμα. Ο “σπασμένος άνθρωπος” του τίτλου δεν παρουσιάζεται με λύπηση· η σύνθεση έχει θυμό, τριβή και εξάντληση. Τα riffs έχουν αργή, πυκνή κίνηση και τα drums κρατούν το groove χαμηλά, σχεδόν σαν να σέρνονται. Η κριτική του Lollipop ξεχωρίζει το κομμάτι για τις “anthemic, sludgy guitars”, κάτι που περιγράφει σωστά τη δύναμή του, δεν είναι απλώς αργό, αλλά χτίζει μία μελωδική, σχεδόν τελετουργική βαρύτητα.</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental του Woody Weatherman. Ο τίτλος σημαίνει περίπου “χέρι πιθήκου”, και η μουσική αντιστοιχεί σε μια παράξενη, νευρική κιθαριστική υφή αντί για κανονική σύνθεση. Λειτουργεί σαν θορυβώδης μετάβαση, διακόπτει την ευθεία πορεία του δίσκου, αφήνει τον ήχο να γίνει πιο αφηρημένος και ανοίγει τον δρόμο για το πιο σκοτεινό δεύτερο μισό. Η χαμηλότερη βαθμολογία του αφορά την αυτονομία του ως track, όχι τη χρησιμότητά του μέσα στη σειρά. 1346</t>
+  </si>
+  <si>
+    <t>Σύντομο sound-collage interlude, σχεδόν σαν κωδικός ή θραύσμα μετάδοσης. Η ακολουθία αριθμών αποφεύγει κάθε προφανή αφηγηματική εξήγηση· αυτό που έχει σημασία είναι η λειτουργία του ως ηχητικό σπάσιμο. Μετακινεί το album από την οργανική sludge αίσθηση του “Seven Days” προς το πιο συμπαγές riffing του “My Grain”. Η αξία του είναι καθαρά δομική, δίνει στο άλμπουμ την αίσθηση ότι δεν είναι μόνο live-in-room rock record αλλά έχει και πιο πειραματικές, collage στιγμές.</t>
+  </si>
+  <si>
+    <t>Πιο κινητικό, boogie-driven track μετά τη σκοτεινή βαρύτητα του title song. Ο τίτλος δίνει φυσική, σωματική κίνηση και το rhythm section ανταποκρίνεται με πιο ανοιχτό, rocking pulse. Δεν είναι carefree party track, η παραμόρφωση και η φωνή του Keenan διατηρούν την απειλητική χροιά του album. Όμως λειτουργεί ως αναγκαίο lift πριν από την πιο ατμοσφαιρική τελική δυάδα.</t>
+  </si>
+  <si>
+    <t>Το αληθινό τέλος του original album και μία από τις πιο μεγάλες C.O.C. συνθέσεις. Ο τίτλος χρησιμοποιεί τη βιβλική φράση για το να προσφέρεις κάτι πολύτιμο σε ανθρώπους που δεν μπορούν ή δεν θέλουν να το αναγνωρίσουν. Η μουσική είναι σχεδόν επτά λεπτά stoner/sludge doom, αργά riffs, βαριές μετατοπίσεις, σκοτεινή φωνητική παρουσία και σταδιακή κλιμάκωση. Δεν επιχειρεί να δώσει εύκολη catharsis· αφήνει την ένταση να συσσωρευτεί και να βαρύνει. Είναι το τέλειο closing statement, επειδή συγκεντρώνει όλα τα στοιχεία του Deliverance ,southern swing, Sabbath βάρος, punk αποφασιστικότητα και bluesy κιθάρα, σε ένα αργό, τελετουργικό τέλος. Το Louder Sound το χαρακτηρίζει “nearly seven-minute stoner freak-out”, ισάξιο με τα πιο γνωστά τραγούδια της μπάντας.</t>
+  </si>
+  <si>
+    <t>Διασκευή Black Sabbath από το Master Of Reality. Είναι ιδανική επιλογή για C.O.C., επειδή αποκαλύπτει ξεκάθαρα μία από τις βασικές ρίζες του Deliverance, αργό doom riffing, bluesy βαρύτητα και σκοτεινή φωνητική ένταση. Δεν ανήκει στο αρχικό album arc, αλλά λειτουργεί σαν ειλικρινής φόρος τιμής στη γλώσσα από την οποία άντλησαν πολλά από τα δικά τους riffs. Στη δική σου 2LP έκδοση, το bonus έχει περισσότερο archival/expanded χαρακτήρα παρά δραματουργική αναγκαιότητα.</t>
+  </si>
+  <si>
+    <t>Αρχειακό jam/demo document και όχι ολοκληρωμένη studio σύνθεση με την ίδια έννοια όπως το “Albatross” ή το “Deliverance”. Η αξία του είναι ότι αφήνει να ακουστεί η πιο ακατέργαστη, riff-first διαδικασία της μπάντας, groove, κιθάρα, texture και ιδέες πριν αποκτήσουν τελική μορφή. Κράτησέ το εκτός της αυστηρής αξιολόγησης του αρχικού album, αλλά ως bonus εξηγεί όμορφα τη heavy, αυτοσχεδιαστική βάση από την οποία χτίστηκε ο ήχος των C.O.C.</t>
   </si>
 </sst>
 </file>
@@ -9257,7 +9545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -11861,6 +12149,38 @@
       </c>
       <c r="J81" s="11" t="s">
         <v>2671</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D82" s="6">
+        <v>1994</v>
+      </c>
+      <c r="E82" s="10">
+        <v>3.64</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>2721</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>2720</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>2719</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>2718</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>2717</v>
       </c>
     </row>
   </sheetData>
@@ -12022,6 +12342,8 @@
     <hyperlink ref="J80" r:id="rId155" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
     <hyperlink ref="I81" r:id="rId156" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
     <hyperlink ref="J81" r:id="rId157" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
+    <hyperlink ref="J82" r:id="rId158" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
+    <hyperlink ref="I82" r:id="rId159" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12029,7 +12351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I756"/>
+  <dimension ref="A1:I773"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -32580,6 +32902,465 @@
       </c>
       <c r="I756" s="6"/>
     </row>
+    <row r="757" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B757" s="6">
+        <v>1</v>
+      </c>
+      <c r="C757" s="22" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D757" s="7" t="s">
+        <v>2722</v>
+      </c>
+      <c r="E757" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F757" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G757" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H757" s="7" t="s">
+        <v>2745</v>
+      </c>
+      <c r="I757" s="6"/>
+    </row>
+    <row r="758" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B758" s="6">
+        <v>2</v>
+      </c>
+      <c r="C758" s="22" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D758" s="7" t="s">
+        <v>2723</v>
+      </c>
+      <c r="E758" s="20">
+        <v>4.28</v>
+      </c>
+      <c r="F758" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G758" s="12">
+        <v>5</v>
+      </c>
+      <c r="H758" s="7" t="s">
+        <v>2746</v>
+      </c>
+      <c r="I758" s="6"/>
+    </row>
+    <row r="759" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B759" s="6">
+        <v>3</v>
+      </c>
+      <c r="C759" s="22" t="s">
+        <v>2702</v>
+      </c>
+      <c r="D759" s="7" t="s">
+        <v>2724</v>
+      </c>
+      <c r="E759" s="20">
+        <v>4.12</v>
+      </c>
+      <c r="F759" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G759" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H759" s="7" t="s">
+        <v>2747</v>
+      </c>
+      <c r="I759" s="6"/>
+    </row>
+    <row r="760" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A760" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B760" s="6">
+        <v>4</v>
+      </c>
+      <c r="C760" s="22" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D760" s="7" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E760" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F760" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G760" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H760" s="7" t="s">
+        <v>2748</v>
+      </c>
+      <c r="I760" s="6"/>
+    </row>
+    <row r="761" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A761" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B761" s="6">
+        <v>5</v>
+      </c>
+      <c r="C761" s="22" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D761" s="7" t="s">
+        <v>2726</v>
+      </c>
+      <c r="E761" s="20">
+        <v>3.87</v>
+      </c>
+      <c r="F761" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G761" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H761" s="7" t="s">
+        <v>2749</v>
+      </c>
+      <c r="I761" s="6"/>
+    </row>
+    <row r="762" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A762" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B762" s="6">
+        <v>6</v>
+      </c>
+      <c r="C762" s="22" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D762" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E762" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F762" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G762" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H762" s="7" t="s">
+        <v>2743</v>
+      </c>
+      <c r="I762" s="6"/>
+    </row>
+    <row r="763" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A763" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B763" s="6">
+        <v>7</v>
+      </c>
+      <c r="C763" s="22" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D763" s="7" t="s">
+        <v>2728</v>
+      </c>
+      <c r="E763" s="20">
+        <v>3.28</v>
+      </c>
+      <c r="F763" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G763" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H763" s="7" t="s">
+        <v>2750</v>
+      </c>
+      <c r="I763" s="6"/>
+    </row>
+    <row r="764" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A764" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B764" s="6">
+        <v>8</v>
+      </c>
+      <c r="C764" s="22" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D764" s="7" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E764" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F764" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G764" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H764" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="I764" s="6"/>
+    </row>
+    <row r="765" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A765" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B765" s="6">
+        <v>9</v>
+      </c>
+      <c r="C765" s="22">
+        <v>2121313</v>
+      </c>
+      <c r="D765" s="7" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E765" s="20">
+        <v>3.04</v>
+      </c>
+      <c r="F765" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G765" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H765" s="7" t="s">
+        <v>2751</v>
+      </c>
+      <c r="I765" s="6"/>
+    </row>
+    <row r="766" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A766" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B766" s="6">
+        <v>10</v>
+      </c>
+      <c r="C766" s="22" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D766" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="E766" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F766" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G766" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H766" s="7" t="s">
+        <v>2744</v>
+      </c>
+      <c r="I766" s="6"/>
+    </row>
+    <row r="767" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A767" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B767" s="6">
+        <v>11</v>
+      </c>
+      <c r="C767" s="22" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D767" s="7" t="s">
+        <v>2732</v>
+      </c>
+      <c r="E767" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F767" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G767" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H767" s="21" t="s">
+        <v>2741</v>
+      </c>
+      <c r="I767" s="6"/>
+    </row>
+    <row r="768" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A768" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B768" s="6">
+        <v>12</v>
+      </c>
+      <c r="C768" s="22" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D768" s="7" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E768" s="20">
+        <v>3.52</v>
+      </c>
+      <c r="F768" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G768" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H768" s="7" t="s">
+        <v>2752</v>
+      </c>
+      <c r="I768" s="6"/>
+    </row>
+    <row r="769" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A769" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B769" s="6">
+        <v>13</v>
+      </c>
+      <c r="C769" s="22" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D769" s="7" t="s">
+        <v>2734</v>
+      </c>
+      <c r="E769" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F769" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G769" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H769" s="7" t="s">
+        <v>2742</v>
+      </c>
+      <c r="I769" s="6"/>
+    </row>
+    <row r="770" spans="1:9" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B770" s="6">
+        <v>14</v>
+      </c>
+      <c r="C770" s="22" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D770" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="E770" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F770" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G770" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H770" s="7" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I770" s="6"/>
+    </row>
+    <row r="771" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A771" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B771" s="6">
+        <v>15</v>
+      </c>
+      <c r="C771" s="22" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D771" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="E771" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="F771" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G771" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H771" s="7" t="s">
+        <v>2754</v>
+      </c>
+      <c r="I771" s="6"/>
+    </row>
+    <row r="772" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A772" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B772" s="6">
+        <v>16</v>
+      </c>
+      <c r="C772" s="22" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D772" s="7" t="s">
+        <v>2737</v>
+      </c>
+      <c r="E772" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="F772" s="12">
+        <v>4</v>
+      </c>
+      <c r="G772" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H772" s="21" t="s">
+        <v>2740</v>
+      </c>
+      <c r="I772" s="6"/>
+    </row>
+    <row r="773" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A773" s="6">
+        <v>22296643</v>
+      </c>
+      <c r="B773" s="6">
+        <v>17</v>
+      </c>
+      <c r="C773" s="22" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D773" s="7" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E773" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F773" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G773" s="12">
+        <v>4</v>
+      </c>
+      <c r="H773" s="7" t="s">
+        <v>2755</v>
+      </c>
+      <c r="I773" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E57417-8B87-4EAE-AFA8-A66D3597E90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA2094-6DDD-477C-84F4-75065581655C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="2756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="2781">
   <si>
     <t>No</t>
   </si>
@@ -9019,6 +9019,81 @@
   </si>
   <si>
     <t>Αρχειακό jam/demo document και όχι ολοκληρωμένη studio σύνθεση με την ίδια έννοια όπως το “Albatross” ή το “Deliverance”. Η αξία του είναι ότι αφήνει να ακουστεί η πιο ακατέργαστη, riff-first διαδικασία της μπάντας, groove, κιθάρα, texture και ιδέες πριν αποκτήσουν τελική μορφή. Κράτησέ το εκτός της αυστηρής αξιολόγησης του αρχικού album, αλλά ως bonus εξηγεί όμορφα τη heavy, αυτοσχεδιαστική βάση από την οποία χτίστηκε ο ήχος των C.O.C.</t>
+  </si>
+  <si>
+    <t>Prelude</t>
+  </si>
+  <si>
+    <t>Eumir Deodato</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/29667079-Deodato-Prelude</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/g3gxHycrSf65Fgw5n_H73eVDx6ubuluU2PaYcInZ61c/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI5NjY3/MDc5LTE3MDg2MDcy/MzAtMjcyOS5wbmc.jpeg</t>
+  </si>
+  <si>
+    <t>Also Sprach Zarathustra (2001)</t>
+  </si>
+  <si>
+    <t>Spirit Of Summer</t>
+  </si>
+  <si>
+    <t>Carly &amp; Carole</t>
+  </si>
+  <si>
+    <t>Baubles, Bangles And Beads</t>
+  </si>
+  <si>
+    <t>Prelude To Afternoon Of A Faun</t>
+  </si>
+  <si>
+    <t>September 13</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP214, Masterworks Jazz – MOVLP214, CTI Records – CTI 6021 (Europe, Feb 2, 2024 reissue, Limited Edition, Numbered, Gatefold, Green &amp; Yellow Marbled, 180g).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Released in a gatefold sleeve, limited edition of 1,000 individually numbered copies on 180 gram audiophile green &amp; yellow marbled vinyl. Recorded at Van Gelder Studio, Englewood Cliffs, New Jersey, engineered by the legendary Rudy Van Gelder. Lacquer cut by Ray Janos at Sterling Sound, with vinyl mastering by Mark Wilder. Features a stellar line-up including Billy Cobham on drums, Ron Carter &amp; Stanley Clarke on bass, and John Tropea on electric guitar.</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Jazz Fusion [CTI Jazz, Orchestral Fusion, Classical Crossover]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Jazz Fusion [Classical-Funk Crossover, Electric Jazz, Orchestral Funk]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Latin Jazz [Electric Jazz, Brazilian Jazz, Guitar-led Fusion]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Smooth Jazz [Fender Rhodes Jazz, CTI Groove, Orchestral Jazz]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Jazz-Funk [Orchestral Jazz, Electric Bass Feature, Jazz Standard Rework]</t>
+  </si>
+  <si>
+    <t>Jazz Fusion, Third Stream [Classical Jazz, Orchestral Fusion, Flute-led Jazz]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Jazz Fusion [Drum-led Fusion, Latin Jazz, Electric Groove]</t>
+  </si>
+  <si>
+    <t>Η απόλυτη κορυφή του δίσκου. Ο Deodato παίρνει το πιο αναγνωρίσιμο θέμα του Richard Strauss και, αντί να το αναπαραγάγει με rock drums, το μετατρέπει σε σκληρό, ελαστικό funk groove. Η αρχική μεγαλοπρέπεια του θέματος μένει, αλλά μόλις μπει το rhythm section, η σύνθεση αποκτά σώμα και κίνηση: electric bass του Stanley Clarke, κιθάρα του John Tropea, drums του Billy Cobham και Fender Rhodes/Moog του Deodato. Η ιδιοφυΐα είναι ότι το κλασικό θέμα δεν φαίνεται ξένο πάνω στο funk· ακούγεται σαν να είχε πάντα αυτή τη ρυθμική δυνατότητα. Το κομμάτι δεν είναι novelty cover: είναι πλήρης ανακατασκευή που γεφυρώνει κινηματογραφική μεγαλοπρέπεια, jazz-fusion τεχνική και danceable groove.</t>
+  </si>
+  <si>
+    <t>Μετά την κοσμική ένταση της A1, ο δίσκος αλλάζει κλίμα και γίνεται πιο ανάλαφρος, βραζιλιάνικος και ανοιχτός. Είναι original σύνθεση του Deodato, με κιθαριστικό solo του Jay Berliner, και λειτουργεί σαν μεσογειακή/τροπική ανάσα. Δεν έχει το τεράστιο hook του opener, αλλά δείχνει την ικανότητα του Deodato να γράφει melodic fusion όπου το rhythm section διατηρεί μικρές κινήσεις αντί να επιβάλλεται. Η “καλοκαιρινή” αίσθηση δεν είναι φθηνή ευφορία· είναι χτισμένη μέσα από ελαφρύ latin swing, καθαρές κιθάρες και λεπτές ενορχηστρωτικές πινελιές.</t>
+  </si>
+  <si>
+    <t>Το πιο σύντομο και πιο understated track της A πλευράς. Η σύνθεση κινείται γύρω από Fender Rhodes, πλούσιες harmony κινήσεις και CTI-style studio polish. Σε σχέση με την ορμή του “Also Sprach…” και τη φωτεινότητα του “Spirit Of Summer”, είναι λιγότερο θεαματικό· η αξία του βρίσκεται στο ότι ξεκουράζει το αυτί και αφήνει την ενορχηστρωτική λεπτομέρεια να ακουστεί. Είναι σαν μικρή, sophisticated jazz-funk vignette: όχι μεγάλη κορύφωση, αλλά σωστή αλλαγή κλίμακας πριν από τη B πλευρά.</t>
+  </si>
+  <si>
+    <t>Η δεύτερη μεγάλη διασκευή του album παίρνει το τραγούδι των Robert Wright και George Forrest, που έχει μελωδικές ρίζες στον Borodin, και το μετατρέπει σε αργό, βαρύ orchestral jazz-funk. Ο Ron Carter έχει electric-bass solo, ενώ ο John Tropea δίνει κιθαριστικό solo, και οι δύο κινούνται μέσα σε μια παραγωγή όπου strings και πνευστά δεν λειτουργούν ως γυαλιστικό layer αλλά ως μέρος της ρυθμικής έντασης. Η διάρκεια της συγκεκριμένης έκδοσης είναι περίπου επτά λεπτά, άρα η σύνθεση έχει χρόνο να αναπτύξει το groove της πιο υπομονετικά από ό,τι στις τυπικές jazz-standard εκτελέσεις.</t>
+  </si>
+  <si>
+    <t>Η διασκευή Debussy είναι η πιο “third-stream” στιγμή του δίσκου: κλασική μελωδική ευαισθησία μετατρέπεται σε ατμοσφαιρική jazz-fusion ενορχήστρωση. Το flute solo του Hubert Laws και το trumpet solo του Marvin Stamm έχουν κεντρικό ρόλο, ενώ οι strings διατηρούν το αίσθημα ρευστής, ονειρικής κίνησης που υπάρχει στο πρωτότυπο του Debussy. Ο Deodato δεν προσπαθεί να κάνει τον Debussy funky με τον ίδιο άμεσο τρόπο που έκανε τον Strauss· τον χρησιμοποιεί για να δημιουργήσει χώρους, χρώματα και λεπτές δυναμικές. Είναι από τα πιο κομψά arrangements του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο της ημέρας ηχογράφησης του δίσκου και το πιο “band-driven” original φινάλε. Συνυπογράφεται από Deodato και Billy Cobham, και αυτό φαίνεται: τα drums έχουν κεντρική θέση, το groove είναι πιο δυναμικό και η σύνθεση δίνει μεγαλύτερη ελευθερία στο rhythm section. Ο John Tropea προσθέτει electric-guitar solo, ενώ τα latin κρουστά των Airto Moreira και Ray Barretto δίνουν κίνηση χωρίς να μετατρέπουν το track σε απλή latin-jazz επίδειξη. Μετά τις κλασικές μεταμορφώσεις της B πλευράς, το “September 13” κλείνει το album με καθαρό fusion statement: σύνθεση από το εσωτερικό της μπάντας, ρυθμική ενέργεια και ενορχήστρωση που εξακολουθεί να έχει CTI πολυτέλεια.</t>
   </si>
 </sst>
 </file>
@@ -9545,7 +9620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12181,6 +12256,38 @@
       </c>
       <c r="J82" s="11" t="s">
         <v>2717</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D83" s="6">
+        <v>1973</v>
+      </c>
+      <c r="E83" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>2768</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>2766</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>2758</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>2759</v>
       </c>
     </row>
   </sheetData>
@@ -12344,6 +12451,8 @@
     <hyperlink ref="J81" r:id="rId157" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
     <hyperlink ref="J82" r:id="rId158" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
     <hyperlink ref="I82" r:id="rId159" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
+    <hyperlink ref="I83" r:id="rId160" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
+    <hyperlink ref="J83" r:id="rId161" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12351,13 +12460,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I773"/>
+  <dimension ref="A1:I779"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -33360,6 +33469,170 @@
         <v>2755</v>
       </c>
       <c r="I773" s="6"/>
+    </row>
+    <row r="774" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B774" s="6">
+        <v>1</v>
+      </c>
+      <c r="C774" s="22" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D774" s="7" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E774" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F774" s="12">
+        <v>5</v>
+      </c>
+      <c r="G774" s="12">
+        <v>5</v>
+      </c>
+      <c r="H774" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="I774" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="775" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B775" s="6">
+        <v>2</v>
+      </c>
+      <c r="C775" s="22" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D775" s="7" t="s">
+        <v>2770</v>
+      </c>
+      <c r="E775" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F775" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G775" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H775" s="7" t="s">
+        <v>2776</v>
+      </c>
+      <c r="I775" s="6"/>
+    </row>
+    <row r="776" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B776" s="6">
+        <v>3</v>
+      </c>
+      <c r="C776" s="22" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D776" s="7" t="s">
+        <v>2771</v>
+      </c>
+      <c r="E776" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F776" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G776" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H776" s="7" t="s">
+        <v>2777</v>
+      </c>
+      <c r="I776" s="6"/>
+    </row>
+    <row r="777" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A777" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B777" s="6">
+        <v>4</v>
+      </c>
+      <c r="C777" s="22" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D777" s="7" t="s">
+        <v>2772</v>
+      </c>
+      <c r="E777" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F777" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G777" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H777" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="I777" s="6"/>
+    </row>
+    <row r="778" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A778" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B778" s="6">
+        <v>5</v>
+      </c>
+      <c r="C778" s="22" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D778" s="7" t="s">
+        <v>2773</v>
+      </c>
+      <c r="E778" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F778" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G778" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H778" s="7" t="s">
+        <v>2779</v>
+      </c>
+      <c r="I778" s="6"/>
+    </row>
+    <row r="779" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A779" s="6">
+        <v>29667079</v>
+      </c>
+      <c r="B779" s="6">
+        <v>6</v>
+      </c>
+      <c r="C779" s="22" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D779" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="E779" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F779" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G779" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H779" s="7" t="s">
+        <v>2780</v>
+      </c>
+      <c r="I779" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBA2094-6DDD-477C-84F4-75065581655C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD4A6FB-8CB4-4370-A480-0AEB363CC959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="2781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="2821">
   <si>
     <t>No</t>
   </si>
@@ -9094,6 +9094,216 @@
   </si>
   <si>
     <t>Το ομώνυμο της ημέρας ηχογράφησης του δίσκου και το πιο “band-driven” original φινάλε. Συνυπογράφεται από Deodato και Billy Cobham, και αυτό φαίνεται: τα drums έχουν κεντρική θέση, το groove είναι πιο δυναμικό και η σύνθεση δίνει μεγαλύτερη ελευθερία στο rhythm section. Ο John Tropea προσθέτει electric-guitar solo, ενώ τα latin κρουστά των Airto Moreira και Ray Barretto δίνουν κίνηση χωρίς να μετατρέπουν το track σε απλή latin-jazz επίδειξη. Μετά τις κλασικές μεταμορφώσεις της B πλευράς, το “September 13” κλείνει το album με καθαρό fusion statement: σύνθεση από το εσωτερικό της μπάντας, ρυθμική ενέργεια και ενορχήστρωση που εξακολουθεί να έχει CTI πολυτέλεια.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28729798-Robert-Finley-Black-Bayou</t>
+  </si>
+  <si>
+    <t>Black Bayou</t>
+  </si>
+  <si>
+    <t>Robert Finley</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/c3mirUdVrdyk0fWfZHHSHVAB0yYLgvCTr6VSqMEaDzk/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4NzI5/Nzk4LTE2OTg1MTE3/MTAtMzY3MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Easy Eye Sound – EES-033, Easy Eye Sound – 0088072552593 (Europe, Oct 27, 2023, Limited Edition, Olive Green And Black Splatter Vinyl, Indie Store Exclusive).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Limited edition indie record store exclusive on olive green and black splatter vinyl, pressed by Optimal Media GmbH (BN96708). Recorded at Easy Eye Sound Studios, Nashville, TN, produced, mixed, and featuring guitar/percussion by Dan Auerbach (The Black Keys). Lacquer cut by ST at Optimal Media, with digital mastering by Ryan Smith at Sterling Sound Nashville.</t>
+  </si>
+  <si>
+    <t>Livin’ Out A Suitcase</t>
+  </si>
+  <si>
+    <t>Sneakin’ Around</t>
+  </si>
+  <si>
+    <t>Miss Kitty</t>
+  </si>
+  <si>
+    <t>Waste Of Time</t>
+  </si>
+  <si>
+    <t>Can’t Blame Me For Trying</t>
+  </si>
+  <si>
+    <t>Gospel Blues</t>
+  </si>
+  <si>
+    <t>Nobody Wants To Be Lonely</t>
+  </si>
+  <si>
+    <t>What Goes Around (Comes Around)</t>
+  </si>
+  <si>
+    <t>Lucky Day</t>
+  </si>
+  <si>
+    <t>You Got It (And I Need It)</t>
+  </si>
+  <si>
+    <t>Alligator Bait</t>
+  </si>
+  <si>
+    <t>Soul Blues, Swamp Funk [Southern Soul, Louisiana Blues, Gospel Blues]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Southern Rock [Road Blues, Swamp Soul, Working-Class Blues]</t>
+  </si>
+  <si>
+    <t>Swamp Funk, Soul Blues [Up-tempo Funk Blues, Southern Groove, Danceable R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Southern Soul [Storytelling Blues, Gospel Soul, Louisiana R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Blues Rock [Slow-Burning Blues, Southern Soul, Heavy Groove]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Funk [Mid-tempo Soul Funk, Romantic Blues, Southern R&amp;B]</t>
+  </si>
+  <si>
+    <t>Gospel Blues, Soul Blues [Sacred-Secular Blues, Churchy Soul, Roots Gospel]</t>
+  </si>
+  <si>
+    <t>Southern Soul, Soul Blues [Soul Ballad, Gospel-tinged R&amp;B, Late-Night Blues]</t>
+  </si>
+  <si>
+    <t>Swamp Funk, Soul Blues [Slow Funk, Karma Blues, Heavy Southern Groove]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Southern Rock [Optimistic Roots Rock, Swamp Soul, Upbeat Blues]</t>
+  </si>
+  <si>
+    <t>Soul Blues, Funk [Deep Soul, Funk Blues, Vocal Showcase]</t>
+  </si>
+  <si>
+    <t>Swamp Blues, Soul Blues [Louisiana Story Song, Extended Swamp Funk, Southern Gothic Blues]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Από τα πιο άμεσα και χορευτικά tracks του δίσκου. Το groove είναι ζωηρό, funky και σχεδόν παιχνιδιάρικο, ενώ η φωνή του Finley δίνει στο θέμα της μυστικής ερωτικής κίνησης χιούμορ και swagger αντί για βαριά ενοχή. Το Easy Eye Sound το προβάλλει ως upbeat, groovy στιγμή, και η </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Blues Rock Review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> το αναφέρει ως “big hit” του album. Είναι η πιο καθαρή απόδειξη ότι ο Finley μπορεί να κάνει vintage-minded soul/blues που ακούγεται ζωντανό και όχι σαν αναπαράσταση.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Slow-burning, βαρύ soul-blues τραγούδι για μια σχέση ή συνθήκη που καταναλώνει ενέργεια χωρίς να επιστρέφει τίποτα. Ο τίτλος είναι απλός, αλλά ο Finley τον τραγουδά με βιωμένη αγανάκτηση, όχι με αφηρημένη πίκρα. Το rhythm section κρατά υπομονετικό, βαθύ groove, ενώ η ενορχήστρωση αφήνει χώρο στα φωνητικά να γίνουν το κέντρο. Η </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Blues Rock Review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> το κατατάσσει επίσης στα can’t-miss tracks· είναι από τις καλύτερες στιγμές όπου η Easy Eye παραγωγή συνδυάζει modern low-end με παλιά southern-soul δραματικότητα.</t>
+    </r>
+  </si>
+  <si>
+    <t>Μεσαίου tempo soul-funk κομμάτι, πιο ανάλαφρο στην εξωτερική του κίνηση αλλά με πεισματική φωνητική στάση. Η φράση του τίτλου εκφράζει κάποιον που ίσως δεν κερδίζει, αλλά δεν δέχεται ότι η προσπάθεια ήταν λάθος. Η μπάντα κρατά το track compact, με groove που λειτουργεί σαν συνέχεια της αρχής του δίσκου χωρίς να προσπαθεί να την ξεπεράσει. Το ενδιαφέρον είναι στη φωνή του Finley, η οποία μετατρέπει ένα απλό ερωτικό/σχεσιακό refrain σε δήλωση αξιοπρέπειας.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Soul-ballad στιγμή που μετακινεί τον δίσκο από το swagger στη vulnerabilty. Ο τίτλος εκφράζει μια απλή, καθολική αλήθεια, και η δύναμή του προκύπτει ακριβώς από αυτή την απλότητα. Τα backing vocals της οικογένειας του Finley δίνουν μεγαλύτερη ζεστασιά, ενώ η ενορχήστρωση κρατά late-night R&amp;B αίσθηση. Δεν επιδιώκει να γίνει μεγάλη δραματική μπαλάντα· είναι πιο πολύ μια χαμηλόφωνη παραδοχή ανάγκης για σύνδεση. Η </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Americana Highways</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> τη συγκαταλέγει στα highlights.</t>
+    </r>
+  </si>
+  <si>
+    <t>Αλλαγή χρώματος προς μια πιο φωτεινή, σχεδόν celebratory πλευρά. Η “τυχερή μέρα” δεν παρουσιάζεται ως αφηρημένη ευτυχία αλλά ως μικρή νίκη μέσα σε μια ζωή με δυσκολίες. Μετά τη βαριά ηθική ένταση του προηγούμενου track, το κομμάτι λειτουργεί ως ελαφρύτερη ανάσα, με upbeat roots-rock groove και πιο ανοιχτή ερμηνεία.</t>
+  </si>
+  <si>
+    <t>Το άλμπουμ ανοίγει με travel/working-class blues. Η βαλίτσα του τίτλου είναι σύμβολο ζωής σε μετακίνηση, άνθρωπος που δεν έχει σταθερή βάση, είτε επειδή κυνηγά εργασία, είτε επειδή η ζωή τον σπρώχνει διαρκώς αλλού. Η μουσική κρατά road-rock κίνηση, με την κιθάρα και το rhythm section να δίνουν την αίσθηση τροχών πάνω σε δρόμο. Η φωνή του Finley δεν παραπονιέται· αφηγείται με τον τρόπο κάποιου που έχει αποδεχτεί την περιπλάνηση ως κομμάτι της ταυτότητάς του.</t>
+  </si>
+  <si>
+    <t>Story-song με ιδιαίτερη παρουσία. Η “Miss Kitty” γίνεται χαρακτήρας southern-blues αφήγησης, επιθυμητή, αινιγματική και τοποθετημένη μέσα σε ένα περιβάλλον όπου η έλξη και ο κίνδυνος μπορεί να συνυπάρχουν. Η ερμηνεία του Finley είναι πιο θεατρική και η παραγωγή αφήνει χώρο στις φωνητικές αποχρώσεις. Η Blues Rock Review την ξεχωρίζει ρητά στα can’t-miss tracks, και αυτό δικαιολογεί την υψηλή της βαθμολογία, δεν είναι απλώς good-time blues, αλλά κομμάτι με χαρακτήρα και αφήγηση.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεση συνάντηση ιερής και κοσμικής μουσικής. Ο Finley δεν διαχωρίζει αυστηρά gospel από blues, και τα δύο είδη χρησιμοποιούν φωνή, επανάληψη, μαρτυρία και συλλογική ανταπόκριση για να μιλήσουν για πόνο και επιβίωση. Η παραγωγή δίνει churchy χρώμα χωρίς να μετατρέπεται σε καθαρό εκκλησιαστικό τραγούδι. Είναι σύντομο, συμπυκνωμένο και λειτουργεί σαν πνευματικό διάλειμμα πριν από τη πιο νυχτερινή B πλευρά.</t>
+  </si>
+  <si>
+    <t>Το βαρύτερο funk groove του album. Η ιδέα της ηθικής επιστροφής ,ό,τι κάνεις γυρίζει σε σένα, αποδίδεται με αργή, σχεδόν απειλητική ρυθμική βάση. Το Easy Eye Sound το περιγράφει ως slow-burning funk, και αυτή είναι η ουσία του, δεν βιάζεται, αφήνει το μπάσο, τα drums και τα keyboards να δημιουργήσουν μόνιμη ένταση. Η φωνή του Finley έχει αυστηρότητα, σαν προειδοποίηση που δεν χρειάζεται να φωνάξει. Είναι μία από τις κορυφές του δίσκου και εμφανίζεται στα can’t-miss tracks της Blues Rock Review.</t>
+  </si>
+  <si>
+    <t>Deep-soul ερωτικό τραγούδι με funk-blues βάση. Ο τίτλος είναι άμεσος και σχεδόν ωμός, αλλά ο Finley δεν το αποδίδει ως απλή σεξουαλική πρόταση· το κάνει δήλωση έλλειψης, επιθυμίας και ανάγκης. Η μπάντα αφήνει αρκετό χώρο για τη φωνή, και η ενορχήστρωση διατηρεί πιο σκοτεινό late-night χρώμα από το αισιόδοξο “Lucky Day”. Η Americana Highways το αναφέρει στα highlights, και δικαιολογημένα, είναι από τα tracks όπου η soul πλευρά του Finley βρίσκεται σε πολύ καλή ισορροπία με το swampy rhythm.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, εξάλεπτο κλείσιμο και το πιο καθαρά Louisiana/southern-gothic κομμάτι του album. Ο τίτλος φέρνει εικόνες Bayou, κινδύνου και τοπικού θρύλου, ενώ η μουσική αφήνει περισσότερο χώρο στο groove και στην ατμόσφαιρα από ό,τι τα προηγούμενα compact tracks. Η μπάντα δεν βιάζεται να φτάσει σε chorus· χτίζει υπομονετικά την ένταση, με τον Finley να λειτουργεί σαν storyteller που σε βάζει σε έναν τόπο όπου η φύση, η επιβίωση και η ανθρώπινη παραξενιά είναι δεμένα. Η Blues Rock Review τη συμπεριλαμβάνει στα can’t-miss tracks και η Americana Highways στα highlights. Είναι το σωστό φινάλε, επειδή συγκεντρώνει όλα τα βασικά στοιχεία του album, swamp blues, funk, αφήγηση, χιούμορ, απειλή και τραχιά φωνητική αυθεντία.</t>
   </si>
 </sst>
 </file>
@@ -9620,7 +9830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12288,6 +12498,38 @@
       </c>
       <c r="J83" s="11" t="s">
         <v>2759</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D84" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E84" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>2798</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>2785</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>2781</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>2784</v>
       </c>
     </row>
   </sheetData>
@@ -12453,6 +12695,8 @@
     <hyperlink ref="I82" r:id="rId159" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
     <hyperlink ref="I83" r:id="rId160" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
     <hyperlink ref="J83" r:id="rId161" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
+    <hyperlink ref="I84" r:id="rId162" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
+    <hyperlink ref="J84" r:id="rId163" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12460,7 +12704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I779"/>
+  <dimension ref="A1:I790"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -33634,6 +33878,303 @@
       </c>
       <c r="I779" s="6"/>
     </row>
+    <row r="780" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A780" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B780" s="6">
+        <v>1</v>
+      </c>
+      <c r="C780" s="22" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D780" s="7" t="s">
+        <v>2799</v>
+      </c>
+      <c r="E780" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F780" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G780" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H780" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="I780" s="6"/>
+    </row>
+    <row r="781" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A781" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B781" s="6">
+        <v>2</v>
+      </c>
+      <c r="C781" s="22" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D781" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E781" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F781" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G781" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H781" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="I781" s="6"/>
+    </row>
+    <row r="782" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A782" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B782" s="6">
+        <v>3</v>
+      </c>
+      <c r="C782" s="22" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D782" s="7" t="s">
+        <v>2801</v>
+      </c>
+      <c r="E782" s="20">
+        <v>3.27</v>
+      </c>
+      <c r="F782" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G782" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H782" s="7" t="s">
+        <v>2816</v>
+      </c>
+      <c r="I782" s="6"/>
+    </row>
+    <row r="783" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A783" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B783" s="6">
+        <v>4</v>
+      </c>
+      <c r="C783" s="22" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D783" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E783" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F783" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G783" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H783" s="7" t="s">
+        <v>2811</v>
+      </c>
+      <c r="I783" s="6"/>
+    </row>
+    <row r="784" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A784" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B784" s="6">
+        <v>5</v>
+      </c>
+      <c r="C784" s="22" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D784" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E784" s="20">
+        <v>3.45</v>
+      </c>
+      <c r="F784" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G784" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H784" s="7" t="s">
+        <v>2812</v>
+      </c>
+      <c r="I784" s="6"/>
+    </row>
+    <row r="785" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A785" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B785" s="6">
+        <v>6</v>
+      </c>
+      <c r="C785" s="22" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D785" s="7" t="s">
+        <v>2804</v>
+      </c>
+      <c r="E785" s="20">
+        <v>3.41</v>
+      </c>
+      <c r="F785" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G785" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H785" s="7" t="s">
+        <v>2817</v>
+      </c>
+      <c r="I785" s="6"/>
+    </row>
+    <row r="786" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A786" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B786" s="6">
+        <v>7</v>
+      </c>
+      <c r="C786" s="22" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D786" s="7" t="s">
+        <v>2805</v>
+      </c>
+      <c r="E786" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F786" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G786" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H786" s="7" t="s">
+        <v>2813</v>
+      </c>
+      <c r="I786" s="6"/>
+    </row>
+    <row r="787" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A787" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B787" s="6">
+        <v>8</v>
+      </c>
+      <c r="C787" s="22" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D787" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E787" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F787" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G787" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H787" s="7" t="s">
+        <v>2818</v>
+      </c>
+      <c r="I787" s="6"/>
+    </row>
+    <row r="788" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A788" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B788" s="6">
+        <v>9</v>
+      </c>
+      <c r="C788" s="22" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D788" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="E788" s="20">
+        <v>3.45</v>
+      </c>
+      <c r="F788" s="12">
+        <v>4</v>
+      </c>
+      <c r="G788" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H788" s="7" t="s">
+        <v>2814</v>
+      </c>
+      <c r="I788" s="6"/>
+    </row>
+    <row r="789" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B789" s="6">
+        <v>10</v>
+      </c>
+      <c r="C789" s="22" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D789" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E789" s="20">
+        <v>3.27</v>
+      </c>
+      <c r="F789" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G789" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H789" s="7" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I789" s="6"/>
+    </row>
+    <row r="790" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A790" s="6">
+        <v>28729798</v>
+      </c>
+      <c r="B790" s="6">
+        <v>11</v>
+      </c>
+      <c r="C790" s="22" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D790" s="7" t="s">
+        <v>2809</v>
+      </c>
+      <c r="E790" s="20">
+        <v>3.32</v>
+      </c>
+      <c r="F790" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G790" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H790" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="I790" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD4A6FB-8CB4-4370-A480-0AEB363CC959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D7C07-C59D-4285-8AEB-2FBB83A26A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="2821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2848">
   <si>
     <t>No</t>
   </si>
@@ -9304,6 +9304,87 @@
   </si>
   <si>
     <t>Το μεγάλο, εξάλεπτο κλείσιμο και το πιο καθαρά Louisiana/southern-gothic κομμάτι του album. Ο τίτλος φέρνει εικόνες Bayou, κινδύνου και τοπικού θρύλου, ενώ η μουσική αφήνει περισσότερο χώρο στο groove και στην ατμόσφαιρα από ό,τι τα προηγούμενα compact tracks. Η μπάντα δεν βιάζεται να φτάσει σε chorus· χτίζει υπομονετικά την ένταση, με τον Finley να λειτουργεί σαν storyteller που σε βάζει σε έναν τόπο όπου η φύση, η επιβίωση και η ανθρώπινη παραξενιά είναι δεμένα. Η Blues Rock Review τη συμπεριλαμβάνει στα can’t-miss tracks και η Americana Highways στα highlights. Είναι το σωστό φινάλε, επειδή συγκεντρώνει όλα τα βασικά στοιχεία του album, swamp blues, funk, αφήγηση, χιούμορ, απειλή και τραχιά φωνητική αυθεντία.</t>
+  </si>
+  <si>
+    <t>Funkadelic</t>
+  </si>
+  <si>
+    <t>Maggot Brain</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/KyzImXOqEF9HwQ5HuNQiw-KL_jWXy6iuU4CIoOa1qk4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3NjYz/ODU1LTE3MjI2NjMy/MTQtNjI5OC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/27663855-Funkadelic-Maggot-Brain</t>
+  </si>
+  <si>
+    <t>Westbound Records – SEW 002, Westbound Records – WB 2007 (Europe, 2023 reissue, Stereo, Pressed by GZ Media).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** European reissue manufactured and distributed by Ace Records Ltd., with licensing from Westbound Records. Pressed at GZ Media (indicated by the 262313E matrix formatting). Features the legendary cover photography by Joel Brodsky and art direction by David Krieger, immortalizing Eddie Hazel's iconic guitar opus.</t>
+  </si>
+  <si>
+    <t>Can You Get To That</t>
+  </si>
+  <si>
+    <t>Hit It And Quit It</t>
+  </si>
+  <si>
+    <t>You And Your Folks, Me And My Folks</t>
+  </si>
+  <si>
+    <t>Super Stupid</t>
+  </si>
+  <si>
+    <t>Back In Our Minds</t>
+  </si>
+  <si>
+    <t>Wars Of Armageddon</t>
+  </si>
+  <si>
+    <t>Funk Rock, Psychedelic Soul [P-Funk, Psychedelic Rock, Acid Funk]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Funk Rock [Psychedelic Guitar Improvisation, Soul Rock, Acid Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Folk Rock [Gospel Soul, Acoustic Funk, Communal Soul]</t>
+  </si>
+  <si>
+    <t>Funk Rock, P-Funk [Raw Funk, Organ Funk, Jam Funk]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Psychedelic Soul [Political Funk, Acid Soul, Group Chant]</t>
+  </si>
+  <si>
+    <t>Funk Rock, Hard Rock [Acid Rock, Heavy Funk, Hendrixian Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Soul, Funk Rock [Soul Rock, Doo-Wop Psych, Vocal Funk]</t>
+  </si>
+  <si>
+    <t>P-Funk, Psychedelic Rock [Experimental Funk, Sound Collage, Free Funk Jam]</t>
+  </si>
+  <si>
+    <t>Πιο σύντομο και παράξενο, με vocal focus και psychedelic doo-wop/soul χαρακτήρα. Το τραγούδι λειτουργεί σαν εσωτερική επιστροφή μετά την εξωστρεφή βία του “Super Stupid”. Ο Tawl Ross και ο George Clinton μοιράζονται τα lead vocals, ενώ τα backing harmonies διατηρούν το P-Funk στοιχείο της συλλογικής φωνής. Δεν διαθέτει το μνημειώδες riff ή το hook των προηγούμενων tracks, αλλά είναι αναγκαίο ως χαμηλότερης έντασης μετάβαση προς το τελικό “Wars Of Armageddon”.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία στιγμή του album και ένα από τα σπουδαιότερα electric-guitar tracks που ηχογραφήθηκαν ποτέ. Πριν μπει η κιθάρα, ο George Clinton απαγγέλλει μια surreal εισαγωγή για μια μέρα όπου “όλα τα πράγματα που οι άνθρωποι πίστευαν ότι ήταν καλά” είχαν πεθάνει, εκτός από τον νου του αφηγητή. Ο Eddie Hazel απαντά με δεκάλεπτο σχεδόν μοναχικό solo, όχι επίδειξη ταχύτητας, αλλά αφήγηση πένθους. Το vibrato, οι μεγάλες παύσεις, τα blues bends και η σταδιακή άνοδος της έντασης κάνουν την κιθάρα να ακούγεται σαν φωνή που προσπαθεί να μιλήσει μετά από απώλεια. Η λιτή συνοδεία αφήνει χώρο ώστε κάθε νότα να έχει βάρος. Η σύνδεση rock κιθάρας, soul ευαισθησίας και ψυχεδελικής ελευθερίας ορίζει όλο το P-Funk σύμπαν.</t>
+  </si>
+  <si>
+    <t>Από το προσωπικό πένθος, ο δίσκος περνά σε communal soul. Ακουστική κιθάρα, handclaps, gospel-like call-and-response και πολυφωνίες δημιουργούν μία από τις πιο ζεστές στιγμές των Funkadelic. Η βασική ερώτηση του τίτλου δεν είναι απλό hook, ρωτά αν ο ακροατής μπορεί να φτάσει σε κατανόηση, ενότητα ή πνευματική καθαρότητα. Η σύνθεση δείχνει ότι οι Funkadelic μπορούσαν να είναι εξίσου ισχυροί χωρίς παραμόρφωση ή heavy groove. Ο Ray Davis έχει lead vocals, ενώ Fuzzy Haskins προσθέτει drums, με τα backing voices να μετατρέπουν το τραγούδι σε μικρή gospel κοινότητα.</t>
+  </si>
+  <si>
+    <t>Ωμό, λιτό και βασισμένο στο organ-driven groove. Ο τίτλος φέρει ερωτικό/σεξουαλικό double entendre, αλλά το ουσιαστικό είναι η μουσική οικονομία, ένα επαναλαμβανόμενο funk μοτίβο, drums που “σπρώχνουν” αντί να στολίζουν, μπάσο που κρατά το κέντρο και ένα ensemble που προτιμά την αίσθηση από την καθαρή pop δομή. Ο Bernie Worrell έχει τα lead vocals και τα keyboards είναι καθοριστικά, το organ χτίζει ατμόσφαιρα που είναι ταυτόχρονα churchy, greasy και ψυχεδελική.</t>
+  </si>
+  <si>
+    <t>Πολιτικό και κοινοτικό τραγούδι, με τίτλο που αρνείται τη διαίρεση ανάμεσα σε “εσάς” και “εμάς”. Η σύνθεση συνδέει τη φυλετική/κοινωνική ένταση της εποχής με ένα funk groove που ακούγεται σαν συλλογική δήλωση. Ο Billy Nelson κρατά lead vocals, ο Bernie Worrell δίνει keyboards και οι φωνές δημιουργούν αίσθηση ομάδας αντί για μεμονωμένου τραγουδιστή. Η μουσική έχει psychedelic θόλωση, αλλά το μήνυμα είναι αρκετά άμεσο, οι κοινότητες δεν μπορούν να επιβιώσουν αν αντιμετωπίζουν η μία την άλλη ως εχθρό.</t>
+  </si>
+  <si>
+    <t>Το πιο hard-rock κομμάτι των Funkadelic. Η κιθάρα του Hazel πλησιάζει τη Hendrixian ένταση, αλλά η ρυθμική βάση παραμένει funk, δεν γίνεται ποτέ συμβατικό blues-rock. Ο τίτλος δηλώνει συνειδητά μια άρνηση της σοβαροφάνειας, όμως η μουσική είναι τεράστια, fuzz, wah, feedback, βαριά riffs και φωνητικά που δίνουν στο track σχεδόν garage-rock αγριάδα. Ο Hazel τραγουδά lead, προσθέτοντας μια πιο ωμή, σχεδόν απελπισμένη ποιότητα. Είναι βασικός κρίκος ανάμεσα στην acid rock της δεκαετίας του ’60 και στο funk metal/alternative hard rock που θα εμφανιζόταν πολύ αργότερα.</t>
+  </si>
+  <si>
+    <t>Το εννιάλεπτο, ανοργάνωτα οργανωμένο φινάλε. Δεν είναι “τραγούδι” με συμβατική μορφή, είναι P-Funk collage, με riffs, φωνές, drums, noise, αλλαγές groove και ηχητικά γεγονότα να εμφανίζονται σαν σκηνές ενός κόσμου που έχει αρχίσει να καταρρέει. Ο τίτλος παραπέμπει σε κοσμική σύγκρουση, αλλά η μουσική ακούγεται ταυτόχρονα σαν κοινωνικός πανικός, street party και studio experiment. Η συμμετοχή των Clinton, Ross, Worrell και Fulwood στη σύνθεση αντιστοιχεί στη συλλογική του φύση. Κλείνει το album χωρίς καθαρή απάντηση ή ηρεμία, μετά τον προσωπικό θρήνο του title track και την υπόσχεση ενότητας στο “Can You Get To That”, το album καταλήγει σε ένα τελετουργικό χάος.</t>
   </si>
 </sst>
 </file>
@@ -9830,7 +9911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12530,6 +12611,38 @@
       </c>
       <c r="J84" s="11" t="s">
         <v>2784</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D85" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E85" s="10">
+        <v>3.99</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>2833</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>2826</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>2825</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>2823</v>
       </c>
     </row>
   </sheetData>
@@ -12697,6 +12810,8 @@
     <hyperlink ref="J83" r:id="rId161" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
     <hyperlink ref="I84" r:id="rId162" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
     <hyperlink ref="J84" r:id="rId163" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
+    <hyperlink ref="J85" r:id="rId164" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
+    <hyperlink ref="I85" r:id="rId165" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12704,7 +12819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I790"/>
+  <dimension ref="A1:I797"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -34175,6 +34290,195 @@
       </c>
       <c r="I790" s="6"/>
     </row>
+    <row r="791" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A791" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B791" s="6">
+        <v>1</v>
+      </c>
+      <c r="C791" s="22" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D791" s="7" t="s">
+        <v>2834</v>
+      </c>
+      <c r="E791" s="20">
+        <v>4.5430000000000001</v>
+      </c>
+      <c r="F791" s="12">
+        <v>5</v>
+      </c>
+      <c r="G791" s="12">
+        <v>5</v>
+      </c>
+      <c r="H791" s="7" t="s">
+        <v>2842</v>
+      </c>
+      <c r="I791" s="6"/>
+    </row>
+    <row r="792" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A792" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B792" s="6">
+        <v>2</v>
+      </c>
+      <c r="C792" s="22" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D792" s="7" t="s">
+        <v>2835</v>
+      </c>
+      <c r="E792" s="20">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F792" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G792" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H792" s="7" t="s">
+        <v>2843</v>
+      </c>
+      <c r="I792" s="6"/>
+    </row>
+    <row r="793" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A793" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B793" s="6">
+        <v>3</v>
+      </c>
+      <c r="C793" s="22" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D793" s="7" t="s">
+        <v>2836</v>
+      </c>
+      <c r="E793" s="20">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F793" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G793" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H793" s="7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="I793" s="6"/>
+    </row>
+    <row r="794" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A794" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B794" s="6">
+        <v>4</v>
+      </c>
+      <c r="C794" s="22" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D794" s="7" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E794" s="20">
+        <v>4</v>
+      </c>
+      <c r="F794" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G794" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H794" s="7" t="s">
+        <v>2845</v>
+      </c>
+      <c r="I794" s="6"/>
+    </row>
+    <row r="795" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A795" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B795" s="6">
+        <v>5</v>
+      </c>
+      <c r="C795" s="22" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D795" s="7" t="s">
+        <v>2838</v>
+      </c>
+      <c r="E795" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="F795" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G795" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H795" s="7" t="s">
+        <v>2846</v>
+      </c>
+      <c r="I795" s="6"/>
+    </row>
+    <row r="796" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A796" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B796" s="6">
+        <v>6</v>
+      </c>
+      <c r="C796" s="22" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D796" s="7" t="s">
+        <v>2839</v>
+      </c>
+      <c r="E796" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F796" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G796" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H796" s="7" t="s">
+        <v>2841</v>
+      </c>
+      <c r="I796" s="6"/>
+    </row>
+    <row r="797" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A797" s="6">
+        <v>27663855</v>
+      </c>
+      <c r="B797" s="6">
+        <v>7</v>
+      </c>
+      <c r="C797" s="22" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D797" s="7" t="s">
+        <v>2840</v>
+      </c>
+      <c r="E797" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F797" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G797" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H797" s="7" t="s">
+        <v>2847</v>
+      </c>
+      <c r="I797" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D7C07-C59D-4285-8AEB-2FBB83A26A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3DCF22-801D-4B7C-B56B-D10A8329EB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="2885">
   <si>
     <t>No</t>
   </si>
@@ -9385,6 +9385,117 @@
   </si>
   <si>
     <t>Το εννιάλεπτο, ανοργάνωτα οργανωμένο φινάλε. Δεν είναι “τραγούδι” με συμβατική μορφή, είναι P-Funk collage, με riffs, φωνές, drums, noise, αλλαγές groove και ηχητικά γεγονότα να εμφανίζονται σαν σκηνές ενός κόσμου που έχει αρχίσει να καταρρέει. Ο τίτλος παραπέμπει σε κοσμική σύγκρουση, αλλά η μουσική ακούγεται ταυτόχρονα σαν κοινωνικός πανικός, street party και studio experiment. Η συμμετοχή των Clinton, Ross, Worrell και Fulwood στη σύνθεση αντιστοιχεί στη συλλογική του φύση. Κλείνει το album χωρίς καθαρή απάντηση ή ηρεμία, μετά τον προσωπικό θρήνο του title track και την υπόσχεση ενότητας στο “Can You Get To That”, το album καταλήγει σε ένα τελετουργικό χάος.</t>
+  </si>
+  <si>
+    <t>We've Been Going About This All Wrong</t>
+  </si>
+  <si>
+    <t>Sharon Van Etten</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/23148584-Sharon-Van-Etten-Weve-Been-Going-About-This-All-Wrong</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/rYpNK2CTCreoYtzp7m3AcCWrgxBg0Pe7hoG9FR46-SE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTIzMTQ4/NTg0LTE2NTE5OTQw/NzMtNjc1MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Jagjaguwar – JAG395 (Worldwide, May 6, 2022, Gatefold, Black Vinyl).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Heavy cardboard gatefold sleeve with artist photo, lyrics inside, and cardboard inner-sleeve containing b/w artist photo and credits on backside, plus yellow hype sticker and white download card. Mastered at GZ Media (236891E) and vinyl mastering by Joe LaPorta at Sterling Sound, with lacquer cutting/plating components associated with Precision Record Pressing (10-93974). Recorded across multiple studios including Balboa Recording Studio, Invert Studio, and The Village Recorder, produced by Daniel Knowles and Sharon Van Etten.</t>
+  </si>
+  <si>
+    <t>Darkness Fades</t>
+  </si>
+  <si>
+    <t>Home To Me</t>
+  </si>
+  <si>
+    <t>I’ll Try</t>
+  </si>
+  <si>
+    <t>Anything</t>
+  </si>
+  <si>
+    <t>Born</t>
+  </si>
+  <si>
+    <t>Headspace</t>
+  </si>
+  <si>
+    <t>Come Back</t>
+  </si>
+  <si>
+    <t>Darkish</t>
+  </si>
+  <si>
+    <t>Mistakes</t>
+  </si>
+  <si>
+    <t>Far Away</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Synth Rock, Gothic Indie, Dream Pop]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Cinematic Synth Rock, Dark Indie, Album Opener]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Dream Pop [Atmospheric Indie, Synth Pop, Intimate Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Post-Punk [Dark Synth Rock, Tense Alternative, Slow Build]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Rock [Emotional Indie Rock, Post-Punk, Guitar-Synth Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Indie Rock [Experimental Synth Rock, Tense Art Pop, Rhythmic Indie]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Dream Pop [Ambient Indie, Shoegaze-tinged Rock, Atmospheric Ballad]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Post-Punk [Driving Alternative Rock, Synth Rock, Emotional Urgency]</t>
+  </si>
+  <si>
+    <t>Art Rock, Gothic Rock [Dark Wave, Atmospheric Rock, Cinematic Indie]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Slow-Burn Indie, Piano-Synth Ballad, Intimate Alternative]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Dream Pop [Ambient Rock, Cinematic Coda, Reflective Indie]</t>
+  </si>
+  <si>
+    <t>Σκοτεινό slow-burn track όπου η πιο απλή φράση γίνεται υπόσχεση χωρίς εγγύηση. Η Van Etten δεν λέει ότι θα λύσει τα πάντα· λέει μόνο ότι θα προσπαθήσει. Αυτή η μετριοπαθής υπόσχεση ταιριάζει στον post-pandemic τόνο του δίσκου, όπου η επιβίωση είναι συχνά μικρή καθημερινή πράξη. Μουσικά, η ένταση ανεβαίνει αργά με post-punk κιθάρες, υποβόσκοντα synths και ένα rhythm pattern που δεν αφήνει το τραγούδι να χαλαρώσει πραγματικά.</t>
+  </si>
+  <si>
+    <t>Το album κλείνει με απόσταση αντί για λύση. Η “μακρινή” κατάσταση μπορεί να αφορά άνθρωπο, τόπο, παρελθόν ή τη δική της αίσθηση εαυτού. Η ενορχήστρωση μειώνει σταδιακά την ένταση, με ambient-rock υφές και μια φωνή που ακούγεται σαν να απομακρύνεται μέσα στο ίδιο της το mix. Είναι σωστή coda, επειδή ο δίσκος δεν προσποιείται ότι η σκοτεινή διαδρομή έληξε· απλώς αφήνει τον ακροατή με περισσότερο χώρο για αναπνοή.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο κινητικά τραγούδια του δίσκου. Η προστακτική “come back” μπορεί να απευθύνεται σε πρόσωπο, σε παλιότερο εαυτό, σε αίσθηση ασφάλειας ή σε μια εποχή πριν από την κρίση. Η ρυθμική βάση είναι πιο driving και τα synths αποκτούν μεγαλύτερη ένταση, δημιουργώντας post-punk αίσθηση κίνησης. Η Van Etten δεν ζητά απλώς επιστροφή· η φωνή της φέρνει τον φόβο ότι αυτή η επιστροφή ίσως να μην είναι πλέον δυνατή.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεση και εκρηκτική rock κορύφωση του album. Η βασική ιδέα είναι ότι η αγάπη ή η απώλεια μπορεί να σε κάνει να νιώθεις ικανός για “οτιδήποτε” ,ακόμη και για κάτι επικίνδυνο, απελπισμένο ή ακατανόητο. Οι κιθάρες είναι πιο μπροστά, τα drums έχουν μεγαλύτερη ένταση και η Van Etten τραγουδά με φωνή που κινείται από τρυφερότητα σε απειλή. Η σύνθεση συνδυάζει post-punk νεύρο με emotional indie-rock catharsis και είναι το track που λειτουργεί πιο άμεσα ακόμη και εκτός του full-album πλαισίου.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με αίσθηση ότι κάτι τελειώνει ή απομακρύνεται, αλλά δεν υπάρχει άμεση ανακούφιση. Η Van Etten χτίζει την εισαγωγή με synth-based ατμόσφαιρα και πυκνές φωνητικές στρώσεις, πριν η σύνθεση αποκτήσει μεγαλύτερη σωματική κίνηση. Ο τίτλος υπονοεί φως μετά το σκοτάδι, όμως η μουσική δεν είναι αισιόδοξη, το σκοτάδι μπορεί να “ξεθωριάζει”, αλλά οι συνέπειές του παραμένουν. Είναι σωστό opener επειδή εισάγει τόσο την κλειστοφοβική παραγωγή όσο και την επιμονή για επιβίωση που διαπερνά όλο τον δίσκο.</t>
+  </si>
+  <si>
+    <t>Πιο προσωπικό και εσωτερικό, με τη λέξη “home” να λειτουργεί ως ερώτημα και όχι ως βεβαιότητα. Το σπίτι μπορεί να είναι καταφύγιο, μια σχέση, η οικογένεια ή κάτι που δεν υπάρχει πια με τον τρόπο που το θυμάσαι. Τα synths και το rhythm section δημιουργούν ονειρικό αλλά ελαφρώς ανήσυχο πλαίσιο, ενώ η φωνή της Van Etten παραμένει συγκρατημένη. Η δύναμή του βρίσκεται στην αμφισημία, δεν δηλώνει καθαρά “ανήκω εδώ”, αλλά προσπαθεί να καταλάβει τι σημαίνει να ανήκεις.</t>
+  </si>
+  <si>
+    <t>Πιο αφηρημένο και ρυθμικά νευρικό, με τη λέξη “born” να παραπέμπει σε γέννηση, αλλαγή ή την αδυναμία να ξεφύγεις από τον εαυτό σου. Η ενορχήστρωση είναι σπασμένη, με synth pulses και κιθαριστικές υφές που δεν σταθεροποιούνται σε εύκολο groove. Το κομμάτι λειτουργεί σαν μεταβατική στιγμή, μετά τη μεγάλη κορύφωση του “Anything”, δεν προσφέρει λύση, αλλά δείχνει ότι κάθε αναγέννηση είναι αβέβαιη και συχνά συνοδεύεται από σύγχυση.</t>
+  </si>
+  <si>
+    <t>Το πιο αιωρούμενο και εσωστρεφές track της B πλευράς. Ο τίτλος δηλώνει τον νοητικό χώρο που κατοικεί κανείς όταν είναι απομονωμένος ή υπερφορτωμένος, σκέψεις που γυρίζουν, φόβοι που μεγαλώνουν, εικόνες που δεν μπορείς να σβήσεις. Η μουσική δίνει προτεραιότητα στις ατμοσφαιρικές υφές και στα reverbed vocals, με στοιχεία dream pop και shoegaze. Δεν κυνηγά κορύφωση· σε βάζει μέσα σε μια κατάσταση αιώρησης.</t>
+  </si>
+  <si>
+    <t>Από τα πιο ατμοσφαιρικά και gothic στιγμιότυπα. Ο τίτλος δεν λέει “dark” αλλά “darkish”, κάτι που αφήνει χώρο για αμφισημία, το σκοτάδι δεν είναι απόλυτο, αλλά παραμένει παρόν σαν φίλτρο πάνω σε όλα. Η παραγωγή χρησιμοποιεί χαμηλά synths, ασαφείς κιθαριστικές σκιές και φωνητικές στρώσεις για να δημιουργήσει μια κινηματογραφική αίσθηση νύχτας. Είναι track που λειτουργεί κυρίως με το mood και λιγότερο με ένα μεγάλο melodic hook.</t>
+  </si>
+  <si>
+    <t>Η συναισθηματική καρδιά της τελευταίας διαδρομής. Η Van Etten μετατρέπει τα λάθη σε κάτι που δεν χρειάζεται να κρυφτεί ή να διαγραφεί, είναι μέρος της ιστορίας που διαμορφώνει έναν άνθρωπο. Το τραγούδι είναι αργό, πιανιστικό/synth-driven και σταδιακά ανοίγει σε μεγαλύτερη φωνητική ένταση. Δεν έχει τη σκληρότητα του “Anything”, αλλά έχει ίσως μεγαλύτερη ευαλωτότητα. Η δύναμή του είναι ότι αποφεύγει το εύκολο μήνυμα “όλα θα πάνε καλά” και προτιμά την αποδοχή μιας δύσκολης πραγματικότητας.</t>
   </si>
 </sst>
 </file>
@@ -9911,7 +10022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12643,6 +12754,38 @@
       </c>
       <c r="J85" s="11" t="s">
         <v>2823</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D86" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E86" s="10">
+        <v>3.39</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>2864</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>2853</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>2852</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>2850</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>2851</v>
       </c>
     </row>
   </sheetData>
@@ -12812,6 +12955,8 @@
     <hyperlink ref="J84" r:id="rId163" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
     <hyperlink ref="J85" r:id="rId164" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
     <hyperlink ref="I85" r:id="rId165" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
+    <hyperlink ref="I86" r:id="rId166" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
+    <hyperlink ref="J86" r:id="rId167" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12819,7 +12964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I797"/>
+  <dimension ref="A1:I807"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -34479,6 +34624,276 @@
       </c>
       <c r="I797" s="6"/>
     </row>
+    <row r="798" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A798" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B798" s="6">
+        <v>1</v>
+      </c>
+      <c r="C798" s="22" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D798" s="7" t="s">
+        <v>2865</v>
+      </c>
+      <c r="E798" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="F798" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G798" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H798" s="7" t="s">
+        <v>2879</v>
+      </c>
+      <c r="I798" s="6"/>
+    </row>
+    <row r="799" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A799" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B799" s="6">
+        <v>2</v>
+      </c>
+      <c r="C799" s="22" t="s">
+        <v>2855</v>
+      </c>
+      <c r="D799" s="7" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E799" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F799" s="12">
+        <v>4</v>
+      </c>
+      <c r="G799" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H799" s="7" t="s">
+        <v>2880</v>
+      </c>
+      <c r="I799" s="6"/>
+    </row>
+    <row r="800" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A800" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B800" s="6">
+        <v>3</v>
+      </c>
+      <c r="C800" s="22" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D800" s="7" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E800" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F800" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G800" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H800" s="7" t="s">
+        <v>2875</v>
+      </c>
+      <c r="I800" s="6"/>
+    </row>
+    <row r="801" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A801" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B801" s="6">
+        <v>4</v>
+      </c>
+      <c r="C801" s="22" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D801" s="7" t="s">
+        <v>2868</v>
+      </c>
+      <c r="E801" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F801" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G801" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H801" s="7" t="s">
+        <v>2878</v>
+      </c>
+      <c r="I801" s="6"/>
+    </row>
+    <row r="802" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A802" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B802" s="6">
+        <v>5</v>
+      </c>
+      <c r="C802" s="22" t="s">
+        <v>2858</v>
+      </c>
+      <c r="D802" s="7" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E802" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F802" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G802" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H802" s="7" t="s">
+        <v>2881</v>
+      </c>
+      <c r="I802" s="6"/>
+    </row>
+    <row r="803" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A803" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B803" s="6">
+        <v>6</v>
+      </c>
+      <c r="C803" s="22" t="s">
+        <v>2859</v>
+      </c>
+      <c r="D803" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="E803" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F803" s="12">
+        <v>4</v>
+      </c>
+      <c r="G803" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H803" s="7" t="s">
+        <v>2882</v>
+      </c>
+      <c r="I803" s="6"/>
+    </row>
+    <row r="804" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A804" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B804" s="6">
+        <v>7</v>
+      </c>
+      <c r="C804" s="22" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D804" s="7" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E804" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F804" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G804" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H804" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="I804" s="6"/>
+    </row>
+    <row r="805" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A805" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B805" s="6">
+        <v>8</v>
+      </c>
+      <c r="C805" s="22" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D805" s="7" t="s">
+        <v>2872</v>
+      </c>
+      <c r="E805" s="20">
+        <v>3.31</v>
+      </c>
+      <c r="F805" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G805" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H805" s="7" t="s">
+        <v>2883</v>
+      </c>
+      <c r="I805" s="6"/>
+    </row>
+    <row r="806" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A806" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B806" s="6">
+        <v>9</v>
+      </c>
+      <c r="C806" s="22" t="s">
+        <v>2862</v>
+      </c>
+      <c r="D806" s="7" t="s">
+        <v>2873</v>
+      </c>
+      <c r="E806" s="20">
+        <v>3.87</v>
+      </c>
+      <c r="F806" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G806" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H806" s="7" t="s">
+        <v>2884</v>
+      </c>
+      <c r="I806" s="6"/>
+    </row>
+    <row r="807" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A807" s="6">
+        <v>23148584</v>
+      </c>
+      <c r="B807" s="6">
+        <v>10</v>
+      </c>
+      <c r="C807" s="22" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D807" s="7" t="s">
+        <v>2874</v>
+      </c>
+      <c r="E807" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F807" s="12">
+        <v>4</v>
+      </c>
+      <c r="G807" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H807" s="7" t="s">
+        <v>2876</v>
+      </c>
+      <c r="I807" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3DCF22-801D-4B7C-B56B-D10A8329EB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E0C3BF-B9FA-46E3-81B2-9099A02A119E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="2885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="2924">
   <si>
     <t>No</t>
   </si>
@@ -9496,6 +9496,183 @@
   </si>
   <si>
     <t>Η συναισθηματική καρδιά της τελευταίας διαδρομής. Η Van Etten μετατρέπει τα λάθη σε κάτι που δεν χρειάζεται να κρυφτεί ή να διαγραφεί, είναι μέρος της ιστορίας που διαμορφώνει έναν άνθρωπο. Το τραγούδι είναι αργό, πιανιστικό/synth-driven και σταδιακά ανοίγει σε μεγαλύτερη φωνητική ένταση. Δεν έχει τη σκληρότητα του “Anything”, αλλά έχει ίσως μεγαλύτερη ευαλωτότητα. Η δύναμή του είναι ότι αποφεύγει το εύκολο μήνυμα “όλα θα πάνε καλά” και προτιμά την αποδοχή μιας δύσκολης πραγματικότητας.</t>
+  </si>
+  <si>
+    <t>The Sure Fire Soul Ensemble</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Colemine Records – CLMN 12070, Colemine Records – 12070LP (US, Mar 28, 2025, Black Vinyl Edition, Pressed by Gotta Groove Records).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Black vinyl edition issued with a branded Colemine poly inner sleeve and a collectible "trading card" featuring one of the group's members. Recorded and mixed at The Kitchen II (with additional tracking at SPC 166), produced by Tim Felten. Mastered by Doug Krebs, with lacquer cutting handled by DP at Well Made Music and pressing executed by Gotta Groove Records.</t>
+  </si>
+  <si>
+    <t>Makin’ Moves</t>
+  </si>
+  <si>
+    <t>Las Olas</t>
+  </si>
+  <si>
+    <t>The Grifter</t>
+  </si>
+  <si>
+    <t>Mother Earth</t>
+  </si>
+  <si>
+    <t>Freddie</t>
+  </si>
+  <si>
+    <t>Don’t Trip</t>
+  </si>
+  <si>
+    <t>The Alliance</t>
+  </si>
+  <si>
+    <t>The Lemon Groove</t>
+  </si>
+  <si>
+    <t>Contemplation</t>
+  </si>
+  <si>
+    <t>Corporatocracy</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/33527013-The-Sure-Fire-Soul-Ensemble-Gemini</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/cRV-58prMCRkiPhgLeaKcWEePVrGYz9u6lbV8ff_Y14/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMzNTI3/MDEzLTE3NDMwNzIz/MjctODIxMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul-Jazz [Cinematic Funk, Library Music, Spiritual Jazz]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul-Jazz [Cinematic Funk, Groove Jazz, Album Opener]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Latin Jazz [Latin Soul, Breezy Jazz-Funk, Instrumental Groove]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Library Music [Noir Funk, Cinematic Jazz, Horn-led Groove]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Spiritual Jazz [Flute-led Jazz, Reflective Funk, Ambient Soul]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul-Jazz [Horn-driven Funk, Modal Jazz, Extended Groove]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Funk [Up-tempo Funk, Breakbeat Soul, Instrumental Groove]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Jazz-Funk [Cinematic Soul, Ensemble Jazz, Mid-tempo Groove]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul [West Coast Funk, Organ Groove, Library Soul]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Spiritual Jazz [Dynamic Funk, Modal Soul-Jazz, Cinematic Instrumental]</t>
+  </si>
+  <si>
+    <t>Spiritual Jazz, Soul-Jazz [Reflective Jazz, Atmospheric Soul, Modal Interlude]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Afro-Latin Jazz [Modal Funk, Tabla Groove, Cinematic Finale]</t>
+  </si>
+  <si>
+    <t>Πιο ανοιχτό, αέρινο και latin-tinged. Ο τίτλος “τα κύματα” ταιριάζει στη ρευστή ρυθμική κίνηση και στις μελωδικές γραμμές που μοιάζουν να ανεβαίνουν και να υποχωρούν. Η μπάντα χαμηλώνει την ένταση του opener και δίνει περισσότερο χώρο στην ατμόσφαιρα. Δεν είναι track που βασίζεται σε ένα τεράστιο hook· λειτουργεί ως transition από το urban funk προς πιο ηλιόλουστη, coastal jazz-soul διάθεση.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η μεγαλύτερη groove κορύφωση του πρώτου μισού. Η σύνθεση παίρνει περισσότερο χρόνο για να αναπτυχθεί και επιτρέπει στα horns να αποκτήσουν ουσιαστικό δραματικό ρόλο. Το mid-track horn burst, που το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Fire Note</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> αποκαλεί “pure electricity”, είναι η στιγμή όπου το track μετατρέπεται από tight instrumental funk σε μικρή, εκρηκτική soul-jazz σκηνή. Ο τίτλος ίσως είναι αφιέρωση ή character reference, αλλά χωρίς επίσημη εξήγηση δεν χρειάζεται να αποδώσουμε συγκεκριμένο βιογραφικό νόημα.</t>
+    </r>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο άμεση, up-tempo funk ενέργεια. Η φράση του τίτλου σημαίνει “μην αγχώνεσαι / μην κολλάς”, και η σύνθεση πράγματι έχει πιο ανάλαφρη, χορευτική κίνηση. Το rhythm section κρατά σταθερό pocket, ενώ οι μελωδικές φράσεις έρχονται γρήγορα και καθαρά. Δεν είναι τόσο πολυσύνθετο όσο το “Freddie”, αλλά λειτουργεί σωστά ως reset μετά την extended horn κορύφωση.</t>
+  </si>
+  <si>
+    <t>Μετά το title track, η μπάντα χαμηλώνει ταχύτητα και δημιουργεί χώρο για σιωπή, αρμονία και modal ατμόσφαιρα. Η “περισυλλογή” του τίτλου δεν σημαίνει πλήρη ακινησία· το rhythm section εξακολουθεί να κινείται, αλλά διακριτικά, σαν σκέψη που συνεχίζει κάτω από την επιφάνεια. Είναι πιο αποτελεσματικό μέσα στο album sequence από ό,τι ως αυτόνομο “single”, επειδή προετοιμάζει τη διαφορετική percussion/ρυθμική γλώσσα του κλεισίματος.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Το title track είναι το πιο καθαρό μουσικό μοντέλο της διπλότητας που προτείνει το album. Ξεκινά πιο μελωδικά και εσωτερικά, αλλά περνά σε πιο έντονα funk passages, εναλλάσσοντας συγκράτηση και έκρηξη. Το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Fire Note</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> το ξεχωρίζει ως σύνθεση που ισορροπεί “subtle melodic introspection” με “explosive funk sections”. Δεν είναι απλώς το κεντρικό track επειδή φέρει το όνομα του album· είναι η πιο πλήρης σύνοψη του sound του.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το εναρκτήριο track ορίζει αμέσως τον χαρακτήρα του δίσκου, κοφτό, σίγουρο funk groove με jazz-soul λεπτομέρεια. Δεν προσπαθεί να εντυπωσιάσει με μεγάλη εισαγωγή· μπαίνει άμεσα στην κίνηση, εξού και ο τίτλος. Η διαθέσιμη κριτική το ξεχωρίζει επειδή “sets the tone from the jump”, με purposeful playing και σταθερή δέσμευση στο groove. Λειτουργεί σαν soundtrack για νυχτερινή πόλη ή για σκηνή όπου κάτι αρχίζει να κινείται χωρίς να ξέρεις ακόμη προς τα που.</t>
+  </si>
+  <si>
+    <t>Από τις πιο κινηματογραφικές συνθέσεις του δίσκου. Ο “grifter” είναι ο απατεώνας/μικροκομπιναδόρος του noir κόσμου, και η μουσική ακολουθεί με tense horn lines, μυστήριο και cool, υπόγειο swing. Δεν χρειάζεται στίχους για να χτίσει χαρακτήρα, τα πνευστά, οι μικρές παύσεις και το rhythm section δημιουργούν την αίσθηση ότι παρακολουθείς κάποιον να κινείται προσεκτικά σε επικίνδυνο περιβάλλον. Η κριτική το ξεχωρίζει ακριβώς για αυτή τη noir ποιότητα.</t>
+  </si>
+  <si>
+    <t>Το πρώτο σημαντικό slowdown. Flute και percussion έρχονται μπροστά, ενώ το groove γίνεται λιγότερο επιθετικό και πιο στοχαστικό. Η “Μητέρα Γη” δεν αντιμετωπίζεται με new-age μεγαλοστομία· η μουσική επιλέγει λεπτές υφές, χώρο και οργανική κίνηση. Η κριτική του Fire Note το περιγράφει ως soft, reflective mood με gentle flute/percussion interplay, και αυτό είναι ο σωστός τρόπος να το ακούσεις, ως μικρή στιγμή ηρεμίας μέσα στη funk ενέργεια του album.</t>
+  </si>
+  <si>
+    <t>Πιο συλλογικό, ensemble-driven mid-tempo track. Ο τίτλος υποδηλώνει συνεργασία και η ενορχήστρωση λειτουργεί ανάλογα, δεν υπάρχει ένα όργανο που κυριαρχεί απόλυτα, αλλά horns, keys, bass και drums μοιράζονται το κέντρο. Η σύνθεση έχει cinematic-soul ποιότητα, σαν μουσική για σκηνή όπου διαφορετικοί χαρακτήρες συναντιούνται και αποφασίζουν να κινηθούν μαζί.</t>
+  </si>
+  <si>
+    <t>Τοπική, west-coast soul αναφορά στο Lemon Grove, την περιοχή όπου ηχογραφήθηκε το album. Εδώ η μπάντα παίζει με πιο χαλαρό organ-funk χαρακτήρα, επιλέγοντας θερμότητα και ρευστό groove αντί για noir ένταση. Είναι κομμάτι που λειτουργεί ως μουσικό “σπίτι” του δίσκου, πιο απλό στη δομή, αλλά με αρκετό βάθος στην αλληλεπίδραση των οργάνων ώστε να μην γίνεται filler.</t>
+  </si>
+  <si>
+    <t>Το φινάλε ενώνει funk, modal jazz και παγκόσμιες percussion επιρροές. Ο τίτλος ,“corporatocracy”, εξουσία των εταιρικών συμφερόντων, δίνει κοινωνικοπολιτική σκιά, ακόμη κι αν δεν υπάρχουν στίχοι. Τα tabla και η modal φρασεολογία που ξεχωρίζει η κριτική δημιουργούν πιο ανοικτό, λιγότερο συμβατικό funk περιβάλλον. Δεν τελειώνει με απλό party groove, αφήνει τον δίσκο να αποχωρήσει με ρυθμική ένταση, προβληματισμό και μια αίσθηση ότι η cinematic ιστορία συνεχίζεται πέρα από την τελευταία νότα.</t>
   </si>
 </sst>
 </file>
@@ -10022,7 +10199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12786,6 +12963,38 @@
       </c>
       <c r="J86" s="11" t="s">
         <v>2851</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D87" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E87" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>2901</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>2888</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>2887</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>2899</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>2900</v>
       </c>
     </row>
   </sheetData>
@@ -12957,6 +13166,8 @@
     <hyperlink ref="I85" r:id="rId165" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
     <hyperlink ref="I86" r:id="rId166" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
     <hyperlink ref="J86" r:id="rId167" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
+    <hyperlink ref="I87" r:id="rId168" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
+    <hyperlink ref="J87" r:id="rId169" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12964,7 +13175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I807"/>
+  <dimension ref="A1:I818"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -34894,6 +35105,303 @@
       </c>
       <c r="I807" s="6"/>
     </row>
+    <row r="808" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A808" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B808" s="6">
+        <v>1</v>
+      </c>
+      <c r="C808" s="22" t="s">
+        <v>2889</v>
+      </c>
+      <c r="D808" s="7" t="s">
+        <v>2902</v>
+      </c>
+      <c r="E808" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F808" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G808" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H808" s="7" t="s">
+        <v>2918</v>
+      </c>
+      <c r="I808" s="6"/>
+    </row>
+    <row r="809" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A809" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B809" s="6">
+        <v>2</v>
+      </c>
+      <c r="C809" s="22" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D809" s="7" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E809" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F809" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G809" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H809" s="7" t="s">
+        <v>2913</v>
+      </c>
+      <c r="I809" s="6"/>
+    </row>
+    <row r="810" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A810" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B810" s="6">
+        <v>3</v>
+      </c>
+      <c r="C810" s="22" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D810" s="7" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E810" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F810" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G810" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H810" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="I810" s="6"/>
+    </row>
+    <row r="811" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A811" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B811" s="6">
+        <v>4</v>
+      </c>
+      <c r="C811" s="22" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D811" s="7" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E811" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F811" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G811" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H811" s="7" t="s">
+        <v>2920</v>
+      </c>
+      <c r="I811" s="6"/>
+    </row>
+    <row r="812" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A812" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B812" s="6">
+        <v>5</v>
+      </c>
+      <c r="C812" s="22" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D812" s="7" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E812" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F812" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G812" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H812" s="7" t="s">
+        <v>2914</v>
+      </c>
+      <c r="I812" s="6"/>
+    </row>
+    <row r="813" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A813" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B813" s="6">
+        <v>6</v>
+      </c>
+      <c r="C813" s="22" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D813" s="7" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E813" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F813" s="12">
+        <v>4</v>
+      </c>
+      <c r="G813" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H813" s="7" t="s">
+        <v>2915</v>
+      </c>
+      <c r="I813" s="6"/>
+    </row>
+    <row r="814" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A814" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B814" s="6">
+        <v>7</v>
+      </c>
+      <c r="C814" s="22" t="s">
+        <v>2895</v>
+      </c>
+      <c r="D814" s="7" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E814" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F814" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G814" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H814" s="7" t="s">
+        <v>2921</v>
+      </c>
+      <c r="I814" s="6"/>
+    </row>
+    <row r="815" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A815" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B815" s="6">
+        <v>8</v>
+      </c>
+      <c r="C815" s="22" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D815" s="7" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E815" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F815" s="12">
+        <v>4</v>
+      </c>
+      <c r="G815" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H815" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="I815" s="6"/>
+    </row>
+    <row r="816" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A816" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B816" s="6">
+        <v>9</v>
+      </c>
+      <c r="C816" s="22" t="s">
+        <v>2886</v>
+      </c>
+      <c r="D816" s="7" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E816" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F816" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G816" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H816" s="7" t="s">
+        <v>2917</v>
+      </c>
+      <c r="I816" s="6"/>
+    </row>
+    <row r="817" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A817" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B817" s="6">
+        <v>10</v>
+      </c>
+      <c r="C817" s="22" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D817" s="7" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E817" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F817" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G817" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H817" s="7" t="s">
+        <v>2916</v>
+      </c>
+      <c r="I817" s="6"/>
+    </row>
+    <row r="818" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A818" s="6">
+        <v>33527013</v>
+      </c>
+      <c r="B818" s="6">
+        <v>11</v>
+      </c>
+      <c r="C818" s="22" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D818" s="7" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E818" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F818" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G818" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H818" s="7" t="s">
+        <v>2923</v>
+      </c>
+      <c r="I818" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E0C3BF-B9FA-46E3-81B2-9099A02A119E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193F735C-2E05-4605-B8B5-863A57D7E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="2924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3215" uniqueCount="2954">
   <si>
     <t>No</t>
   </si>
@@ -9673,6 +9673,126 @@
   </si>
   <si>
     <t>Το φινάλε ενώνει funk, modal jazz και παγκόσμιες percussion επιρροές. Ο τίτλος ,“corporatocracy”, εξουσία των εταιρικών συμφερόντων, δίνει κοινωνικοπολιτική σκιά, ακόμη κι αν δεν υπάρχουν στίχοι. Τα tabla και η modal φρασεολογία που ξεχωρίζει η κριτική δημιουργούν πιο ανοικτό, λιγότερο συμβατικό funk περιβάλλον. Δεν τελειώνει με απλό party groove, αφήνει τον δίσκο να αποχωρήσει με ρυθμική ένταση, προβληματισμό και μια αίσθηση ότι η cinematic ιστορία συνεχίζεται πέρα από την τελευταία νότα.</t>
+  </si>
+  <si>
+    <t>Technical Ecstasy</t>
+  </si>
+  <si>
+    <t>Vertigo – 9124 100 (Greece, 1976 1st Press, LP, Album, Stereo, Pressed by Columbia, Athens).</t>
+  </si>
+  <si>
+    <t>Back Street Kids</t>
+  </si>
+  <si>
+    <t>You Won’t Change Me</t>
+  </si>
+  <si>
+    <t>It’s Alright</t>
+  </si>
+  <si>
+    <t>Gypsy</t>
+  </si>
+  <si>
+    <t>All Moving Parts (Stand Still)</t>
+  </si>
+  <si>
+    <t>Rock ’N’ Roll Doctor</t>
+  </si>
+  <si>
+    <t>She’s Gone</t>
+  </si>
+  <si>
+    <t>Dirty Women</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Progressive Heavy Rock, Arena Rock, Keyboard-Driven Metal]</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/t4_fNU5BcV3nihl2GyQhL2FdLgwDPc68-QgVF6_eu6w/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTkzNzY0/NDktMTQ3OTQ5NjMx/OC0yMzg1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/9376449-Black-Sabbath-Technical-Ecstasy</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Rare Greek first pressing with the characteristic fully laminated cover and translated Greek rights/rim text on labels. Pressed at Columbia, Athens (identifiable by the 5314 pressing plant ID and the A/A matrix numbering format). Captures the band's experimental mid-70s hard rock/heavy metal transition, featuring production by the band members themselves.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Up-tempo Heavy Rock, Proto-Speed Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Doom Metal [Slow Heavy Metal, Doom Ballad, Keyboard Metal]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Hard Rock [Piano Rock, AOR Ballad, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Keyboard-Driven Heavy Rock, Dark Arena Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Funky Hard Rock, Progressive Rock, Groove Metal Prototype]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Boogie Rock, Classic Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Soft Rock [Orchestral Ballad, Piano Rock, Melancholic Art Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Heavy Blues, Dark Metal, Extended Riff Rock]</t>
+  </si>
+  <si>
+    <t>Γρήγορο, κοφτό και επιθετικό άνοιγμα. Το riff του Tony Iommi έχει μεγαλύτερη ταχύτητα από την κλασική doom πλευρά των Sabbath, ενώ τα drums του Bill Ward δίνουν nervous hard-rock κίνηση. Οι στίχοι κοιτούν προς την αστική νεολαία, τους ανθρώπους του δρόμου και όσους ζουν έξω από την κοινωνική “κανονικότητα”. Δεν είναι από τα πιο σύνθετα τραγούδια του συγκροτήματος, αλλά λειτουργεί πολύ καλά ως opening burst και θυμίζει ότι οι Sabbath εξακολουθούσαν να μπορούν να γράψουν compact heavy rock με πραγματικό momentum.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η πρώτη μεγάλη κορυφή. Αργό, σκοτεινό και σχεδόν funeral στη ρυθμική του αίσθηση, χτίζεται πάνω σε ένα από τα πιο βαριά late-Ozzy riffs του Iommi. Τα keyboards του Jezz Woodruffe δεν μαλακώνουν το κομμάτι· το κάνουν πιο υπόγειο και απειλητικό. Η ερμηνεία του Ozzy έχει απομόνωση και απελπισία, ενώ ο τίτλος ακούγεται σαν άρνηση απέναντι σε μια δύναμη που προσπαθεί να αλλάξει ή να ελέγξει τον αφηγητή. Είναι από τα τραγούδια που αποδεικνύουν ότι το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Technical Ecstasy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> δεν εγκατέλειψε το doom DNA του.</t>
+    </r>
+  </si>
+  <si>
+    <t>Επιστροφή στη βαριά πλευρά, αλλά με keyboards να έχουν πλέον κεντρικό ρόλο. Το κομμάτι κινείται ανάμεσα σε dark hard rock και πιο μελωδικό, σχεδόν arena-metal ύφος. Η “gypsy” φιγούρα χρησιμοποιείται με την παλιά, ρομαντικοποιημένη γλώσσα του rock της δεκαετίας του ’70 για να δηλώσει μια μυστηριώδη, περιπλανώμενη γυναίκα· δεν είναι ακριβής ή σύγχρονη εθνοτική περιγραφή. Το riff, οι keyboard υφές και το παρατεταμένο instrumental χτίζουν ένα track που είναι πιο φιλόδοξο από το “Back Street Kids”, έστω κι αν δεν διαθέτει την απόλυτη συνθετική σφιχτότητα του “You Won’t Change Me”.</t>
+  </si>
+  <si>
+    <t>Η πιο δραματική μπαλάντα της late-Ozzy περιόδου. Πιάνο, strings του Mike Lewis και η φωνή του Ozzy δημιουργούν σχεδόν theatrical, orchestral rock ατμόσφαιρα. Η απώλεια του τίτλου δεν έχει απλώς ερωτικό χαρακτήρα· παρουσιάζεται σαν πλήρης συναισθηματική κατάρρευση. Η σύνθεση κινδυνεύει να ακούγεται υπερβολικά “soft” για Sabbath, αλλά η ερμηνεία και οι μελωδικές επιλογές τη διατηρούν μελαγχολική και ειλικρινή. Είναι πολύ χρήσιμη για να καταλάβεις πόσο μακριά ήθελε να πάει το συγκρότημα από το αυστηρό doom template.</t>
+  </si>
+  <si>
+    <t>Η μεγαλύτερη αισθητική στροφή του album. Ο Bill Ward αναλαμβάνει τα lead vocals, σε ένα piano-led τραγούδι με soft-rock/AOR επιρροές και πολύ πιο φωτεινή μελωδική γραμμή από ό,τι περιμένει κανείς από Sabbath. Η φωνή του Ward δεν έχει τη στοιχειωμένη ποιότητα του Ozzy, αλλά αυτό είναι μέρος της γοητείας, ακούγεται ευάλωτος και ανθρώπινος. Το τραγούδι διχάζει επειδή βρίσκεται μέσα σε Sabbath δίσκο, όμως ως 70s rock ballad έχει πραγματική μελωδική ζεστασιά και δείχνει πόσο πλατιά μπορούσε να ανοίξει η μπάντα τη φόρμα της.</t>
+  </si>
+  <si>
+    <t>Το πιο απλό τραγούδι του δίσκου, boogie riff, rock ’n’ roll τίτλος και περισσότερο ελαφριά, live-band διάθεση. Ο “doctor” του τίτλου μπορεί να είναι κάποιος που θεραπεύει μέσω μουσικής ή κάποιος που πουλά την υπόσχεση του rock ’n’ roll ως φάρμακο. Παρότι έχει ωραία ενέργεια και παίζεται αποτελεσματικά, φαίνεται μικρότερο δίπλα στις μεγάλες ιδέες του δίσκου. Είναι καλύτερο ως σύντομη ανάσα πριν από την μπαλάντα και το finale παρά ως αυτόνομη κορυφή.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, επτάλεπτο κλείσιμο και η σαφέστερη Sabbath κορυφή του album. Ξεκινά με ατμόσφαιρα αστικής νύχτας και σύντομα ανοίγει σε βαρύ, bluesy riff που έχει όλη την υπογραφή του Iommi, απλό, δυσοίωνο, με χώρο για swing και για κιθαριστική ένταση. Οι στίχοι κοιτούν τον κόσμο των sex workers μέσα από τη 1976 rock γλώσσα, η οποία σήμερα είναι προβληματική/παρωχημένη σε ορισμένες διατυπώσεις· μουσικά όμως το κομμάτι είναι πολύ ισχυρότερο από την επιφανειακή του αφήγηση. Το rhythm section έχει πραγματικό βάρος, τα keyboards προσθέτουν σκοτεινό βάθος και το instrumental μέρος θυμίζει γιατί η μπάντα μπορούσε ακόμη να επεκτείνει ένα riff σε ολόκληρο ηχητικό κόσμο. Είναι ένα από τα καλύτερα late-’70s Ozzy-era Sabbath tracks.</t>
+  </si>
+  <si>
+    <t>Παράξενο και ενδιαφέρον deep cut. Το rhythm section φλερτάρει με funkier pulse, ενώ η κιθάρα του Iommi προσθέτει βαριά riffs και οι στίχοι εξετάζουν έναν κόσμο που μοιάζει να κινείται συνεχώς χωρίς να προοδεύει. Η αντίθεση του τίτλου ,όλα κινούνται, αλλά τίποτα δεν μεταβάλλεται, αποδίδει καλά την αίσθηση κοινωνικής/προσωπικής στασιμότητας. Δεν είναι Sabbath classic, αλλά δείχνει την περιέργεια της μπάντας για διαφορετικά grooves και προαναγγέλλει στοιχεία του πιο απρόβλεπτου Never Say Die!.</t>
   </si>
 </sst>
 </file>
@@ -10199,7 +10319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12995,6 +13115,38 @@
       </c>
       <c r="J87" s="11" t="s">
         <v>2900</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>2924</v>
+      </c>
+      <c r="D88" s="6">
+        <v>1976</v>
+      </c>
+      <c r="E88" s="10">
+        <v>3.03</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>2934</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>2937</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>2925</v>
+      </c>
+      <c r="I88" s="11" t="s">
+        <v>2936</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>2935</v>
       </c>
     </row>
   </sheetData>
@@ -13168,6 +13320,8 @@
     <hyperlink ref="J86" r:id="rId167" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
     <hyperlink ref="I87" r:id="rId168" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
     <hyperlink ref="J87" r:id="rId169" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
+    <hyperlink ref="J88" r:id="rId170" xr:uid="{76D67995-A6ED-43F5-90F5-FB88B787D5F1}"/>
+    <hyperlink ref="I88" r:id="rId171" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13175,7 +13329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I818"/>
+  <dimension ref="A1:I826"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -35402,6 +35556,222 @@
       </c>
       <c r="I818" s="6"/>
     </row>
+    <row r="819" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A819" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B819" s="6">
+        <v>1</v>
+      </c>
+      <c r="C819" s="22" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D819" s="7" t="s">
+        <v>2938</v>
+      </c>
+      <c r="E819" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F819" s="12">
+        <v>4</v>
+      </c>
+      <c r="G819" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H819" s="7" t="s">
+        <v>2946</v>
+      </c>
+      <c r="I819" s="6"/>
+    </row>
+    <row r="820" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A820" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B820" s="6">
+        <v>2</v>
+      </c>
+      <c r="C820" s="22" t="s">
+        <v>2927</v>
+      </c>
+      <c r="D820" s="7" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E820" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F820" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G820" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H820" s="7" t="s">
+        <v>2947</v>
+      </c>
+      <c r="I820" s="6"/>
+    </row>
+    <row r="821" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A821" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B821" s="6">
+        <v>3</v>
+      </c>
+      <c r="C821" s="22" t="s">
+        <v>2928</v>
+      </c>
+      <c r="D821" s="7" t="s">
+        <v>2940</v>
+      </c>
+      <c r="E821" s="20">
+        <v>3.14</v>
+      </c>
+      <c r="F821" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G821" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H821" s="7" t="s">
+        <v>2950</v>
+      </c>
+      <c r="I821" s="6"/>
+    </row>
+    <row r="822" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A822" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B822" s="6">
+        <v>4</v>
+      </c>
+      <c r="C822" s="22" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D822" s="7" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E822" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F822" s="12">
+        <v>4</v>
+      </c>
+      <c r="G822" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H822" s="7" t="s">
+        <v>2948</v>
+      </c>
+      <c r="I822" s="6"/>
+    </row>
+    <row r="823" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A823" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B823" s="6">
+        <v>5</v>
+      </c>
+      <c r="C823" s="22" t="s">
+        <v>2930</v>
+      </c>
+      <c r="D823" s="7" t="s">
+        <v>2942</v>
+      </c>
+      <c r="E823" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F823" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G823" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H823" s="7" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I823" s="6"/>
+    </row>
+    <row r="824" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A824" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B824" s="6">
+        <v>6</v>
+      </c>
+      <c r="C824" s="22" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D824" s="7" t="s">
+        <v>2943</v>
+      </c>
+      <c r="E824" s="20">
+        <v>2.86</v>
+      </c>
+      <c r="F824" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G824" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H824" s="7" t="s">
+        <v>2951</v>
+      </c>
+      <c r="I824" s="6"/>
+    </row>
+    <row r="825" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A825" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B825" s="6">
+        <v>7</v>
+      </c>
+      <c r="C825" s="22" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D825" s="7" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E825" s="20">
+        <v>3.09</v>
+      </c>
+      <c r="F825" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G825" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H825" s="7" t="s">
+        <v>2949</v>
+      </c>
+      <c r="I825" s="6"/>
+    </row>
+    <row r="826" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A826" s="6">
+        <v>9376449</v>
+      </c>
+      <c r="B826" s="6">
+        <v>8</v>
+      </c>
+      <c r="C826" s="22" t="s">
+        <v>2933</v>
+      </c>
+      <c r="D826" s="7" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E826" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F826" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G826" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H826" s="7" t="s">
+        <v>2952</v>
+      </c>
+      <c r="I826" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193F735C-2E05-4605-B8B5-863A57D7E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BB977C-51FC-498A-8D0C-C37B0A40A50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3215" uniqueCount="2954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="2991">
   <si>
     <t>No</t>
   </si>
@@ -9793,6 +9793,117 @@
   </si>
   <si>
     <t>Παράξενο και ενδιαφέρον deep cut. Το rhythm section φλερτάρει με funkier pulse, ενώ η κιθάρα του Iommi προσθέτει βαριά riffs και οι στίχοι εξετάζουν έναν κόσμο που μοιάζει να κινείται συνεχώς χωρίς να προοδεύει. Η αντίθεση του τίτλου ,όλα κινούνται, αλλά τίποτα δεν μεταβάλλεται, αποδίδει καλά την αίσθηση κοινωνικής/προσωπικής στασιμότητας. Δεν είναι Sabbath classic, αλλά δείχνει την περιέργεια της μπάντας για διαφορετικά grooves και προαναγγέλλει στοιχεία του πιο απρόβλεπτου Never Say Die!.</t>
+  </si>
+  <si>
+    <t>Thin White Rope</t>
+  </si>
+  <si>
+    <t>In The Spanish Cave</t>
+  </si>
+  <si>
+    <t>Mr. Limpet</t>
+  </si>
+  <si>
+    <t>Ring</t>
+  </si>
+  <si>
+    <t>It’s OK</t>
+  </si>
+  <si>
+    <t>Ahr-Skidar</t>
+  </si>
+  <si>
+    <t>Red Sun</t>
+  </si>
+  <si>
+    <t>Elsie Crashed The Party</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>Astronomy</t>
+  </si>
+  <si>
+    <t>Wand</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Psychedelic Rock [Desert Rock, Post-Punk, Paisley Underground]</t>
+  </si>
+  <si>
+    <t>Frontier Records – FLP 1027 (US, Mar 1988, LP, Album, Stereo). Pressed by Rainbo Records / Alied Record Company, with metal parts/plating handled by Sheffield Lab Matrix (Delta number △ 19689) and master lacquer cut at K Disc Mastering.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Original US first pressing featuring the distinctive Allied "ɑ" logo and the characteristic delta symbol (△) in the runouts indicating Sheffield Lab Matrix plating. Lacquer cut at K Disc Mastering, bearing the iconic deadwax etching "SO LONG, KEVIN" on Side A (a tribute/farewell message customary of their vinyl pressings of that era). Produced by Paul McKenna and Thin White Rope, capturing their signature desert-rock, neo-psychedelic, and post-punk tension with Guy Kyser and Roger Kunkel on dual guitars.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2598614-Thin-White-Rope-In-The-Spanish-Cave</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/c63Pb-E4LcCWNyePglZWAYaUBFyHqQJk05Z6BjcWjSM/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1OTg2/MTQtMTUzMzY4Nzk5/MS04MjI5LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Dark Alternative, Angular Guitar Rock, Desert Post-Punk]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Psychedelic Rock [Psychedelic Post-Punk, Tense Guitar Rock, Dark Jangle]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Melodic Post-Punk, Dark Indie, Guitar-Driven Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Alternative Rock [Desert Psych, Experimental Rock, Atmospheric Guitar Track]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Alternative Rock [Cinematic Desert Rock, Trumpet-led Psych, Dark Western Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Narrative Rock, Dark Jangle, Tense Indie Rock]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Alternative Rock [Angular Rock, Nervous Groove, Dark Alternative]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Alternative Rock [Spacey Psych Rock, Dark Indie, Backing-Vocal Atmosphere]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Psychedelic Rock [Dissonant Guitar Rock, Desert Psych, Post-Punk]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Folk Rock [Melancholic Desert Rock, Psychedelic Folk, Atmospheric Closer]</t>
+  </si>
+  <si>
+    <t>Πιο ψυχεδελικό, με τις κιθάρες να αφήνουν μεγαλύτερη αντήχηση και να χτίζουν κυκλική αίσθηση. Το “ring” μπορεί να είναι ήχος, δαχτυλίδι, κύκλος ή απειλή που επαναλαμβάνεται· η μπάντα δεν το εξηγεί, αλλά χρησιμοποιεί την επανάληψη και τη νευρική μελωδία για να δημιουργήσει αίσθηση παγίδευσης. Η φωνή του Kyser είναι συγκρατημένη, κάτι που κάνει το τραγούδι πιο ανήσυχο αντί για θεατρικό.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με narrative τραγούδι, όπου η “Elsie” μπαίνει σε μια κοινωνική σκηνή αλλά η μουσική υπονοεί ότι η παρουσία της δεν είναι ανάλαφρη. Οι Thin White Rope χρησιμοποιούν το party ως χώρο αμηχανίας, απόστασης και άγνωσων κινήτρων. Το rhythm section κρατά ρυθμική κίνηση, αλλά οι κιθάρες έχουν γωνίες και μικρές παραμορφώσεις που εμποδίζουν το τραγούδι να γίνει pop-rock ιστορία.</t>
+  </si>
+  <si>
+    <t>Εστιάζει περισσότερο στο νευρικό groove και στη λειτουργία της μπάντας ως ενιαίου μηχανισμού. Ο τίτλος υποδηλώνει σωστή ή λανθασμένη στιγμή, και το track διατηρεί μια αίσθηση πως τα πράγματα είναι μισό βήμα εκτός συγχρονισμού. Τα drums του Becker δεν επιδιώκουν μεγάλη επίδειξη, αλλά κρατούν την ένταση κοφτή και ανήσυχη, ενώ οι κιθάρες αφήνουν μικρές ψυχεδελικές ρωγμές στο post-punk πλαίσιο.</t>
+  </si>
+  <si>
+    <t>Το πιο “spacey” track της B πλευράς. Τα backing vocals της Jan Potzmann προσθέτουν χρώμα και απόσταση, δίνοντας στο τραγούδι αίσθηση ότι η φωνή του Kyser απευθύνεται σε κάτι που είναι πολύ μακριά ή πολύ μεγάλο για να οριστεί. Η “αστρονομία” λειτουργεί ως εικόνα προσανατολισμού, αλλά και ως υπενθύμιση της ανθρώπινης μικρότητας. Η μπάντα δεν το μετατρέπει σε space-rock cliché· κρατά τον ήχο γήινο, τραχύ και ψυχικά ανήσυχο.</t>
+  </si>
+  <si>
+    <t>Μελαγχολικό, ατμοσφαιρικό κλείσιμο. Ο τίτλος δημιουργεί καλοκαιρινή εικόνα, αλλά το κομμάτι δεν έχει φωτεινή διάθεση· η “July” εδώ μοιάζει με ζεστή, ακινητοποιημένη και κάπως μοναχική περίοδο. Η μπάντα χαμηλώνει ελαφρά την επιθετικότητα και αφήνει περισσότερο χώρο στη μελωδία, στις κιθάρες και στη φωνή. Το album κλείνει χωρίς θριαμβευτικό riff ή καθαρή απάντηση, αλλά με την αίσθηση ότι ο ακροατής βγαίνει από τη σπηλιά σε ένα τοπίο εξίσου παράξενο.</t>
+  </si>
+  <si>
+    <t>Το άλμπουμ ανοίγει με άμεση, κοφτή κιθαριστική ένταση. Η σύνθεση βασίζεται στο post-punk σφίξιμο του rhythm section και στις δύο κιθάρες, που δεν λειτουργούν σαν παραδοσιακή rhythm/lead διάκριση αλλά σαν δύο φωνές με διαφορετικές γωνίες. Ο τίτλος φέρνει αλλόκοτη, σχεδόν cartoon εικόνα, όμως η μουσική είναι σκοτεινή και νευρική. Λειτουργεί ως σωστή εισαγωγή στον κόσμο των Thin White Rope, χαρακτήρες που μοιάζουν ελαφρώς παράξενοι, αλλά κατοικούν σε πραγματική συναισθηματική ένταση.</t>
+  </si>
+  <si>
+    <t>Η ειρωνεία του τίτλου είναι κεντρική. Το τραγούδι δεν ακούγεται ιδιαίτερα “OK”, η κιθάρα, το μπάσο και η φωνητική γραμμή έχουν μικρή αλλά επίμονη ένταση. Μουσικά είναι ένα από τα πιο μελωδικά tracks της A πλευράς, όμως η μελωδία δεν λύνει τη δυσφορία· απλώς την κάνει πιο προσιτή. Λειτουργεί σαν σύντομη, σχεδόν false reassurance στιγμή πριν η μπάντα ανοίξει περισσότερο τον χώρο στο “Ahr-Skidar”.</t>
+  </si>
+  <si>
+    <t>Από τις πιο ατμοσφαιρικές και ανοιχτές συνθέσεις του δίσκου. Ο παράξενος τίτλος δημιουργεί αίσθηση τοπίου ή φαντασιακού τόπου, και η μουσική λειτουργεί σαν διαδρομή μέσα σε ξένο έδαφος, ψυχεδελικές κιθάρες, πιο αργή ανάπτυξη και αίσθηση ότι το riff μετακινείται αντί να επαναλαμβάνεται απλώς. Η δύναμή του είναι ότι δεν επιδιώκει συνηθισμένο verse/chorus payoff· αφήνει το mood να διαμορφώσει τη σύνθεση.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορυφή της A πλευράς. Η τρομπέτα των Dave Muller και Mike Connelly προσθέτει κινηματογραφική, almost desert-western χροιά, ενώ οι κιθάρες και το rhythm section κρατούν το κομμάτι σε σκοτεινό alternative-rock έδαφος. Ο “κόκκινος ήλιος” είναι εικόνα θερμότητας, απειλής, απογευματινής εξάντλησης ή ουράνιου οιωνού. Δεν χρειάζεται να επιλέξεις μία ερμηνεία, η μουσική δημιουργεί τόση ατμόσφαιρα ώστε ο τίτλος γίνεται κυρίως χρώμα και θερμοκρασία. Η χρήση τρομπέτας δεν είναι απλό στολίδι· μετατρέπει το track σε κάτι μεγαλύτερο από τυπικό guitar song.</t>
+  </si>
+  <si>
+    <t>Πιο dissonant και ψυχεδελικό, με τίτλο που μπορεί να σημαίνει ραβδί, μαγικό αντικείμενο ή πράξη περιπλάνησης. Η μουσική χτίζει αστάθεια, οι κιθάρες δεν συμφωνούν απόλυτα, οι ρυθμοί μοιάζουν να αλλάζουν οπτική και η φωνή δεν προσφέρει καθαρή λύση. Είναι ένα από τα tracks που δείχνουν καλύτερα τη δυνατότητα των Thin White Rope να κάνουν alternative rock που έχει πραγματικό μυστήριο, όχι μόνο “quirky” στιχουργία.</t>
   </si>
 </sst>
 </file>
@@ -10319,7 +10430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13147,6 +13258,38 @@
       </c>
       <c r="J88" s="11" t="s">
         <v>2935</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D89" s="6">
+        <v>1988</v>
+      </c>
+      <c r="E89" s="10">
+        <v>3.59</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>2966</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>2967</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>2969</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>2970</v>
       </c>
     </row>
   </sheetData>
@@ -13322,6 +13465,8 @@
     <hyperlink ref="J87" r:id="rId169" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
     <hyperlink ref="J88" r:id="rId170" xr:uid="{76D67995-A6ED-43F5-90F5-FB88B787D5F1}"/>
     <hyperlink ref="I88" r:id="rId171" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
+    <hyperlink ref="I89" r:id="rId172" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
+    <hyperlink ref="J89" r:id="rId173" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13329,7 +13474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I826"/>
+  <dimension ref="A1:I836"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -35772,6 +35917,276 @@
       </c>
       <c r="I826" s="6"/>
     </row>
+    <row r="827" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A827" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B827" s="6">
+        <v>1</v>
+      </c>
+      <c r="C827" s="22" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D827" s="7" t="s">
+        <v>2971</v>
+      </c>
+      <c r="E827" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F827" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G827" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H827" s="7" t="s">
+        <v>2986</v>
+      </c>
+      <c r="I827" s="6"/>
+    </row>
+    <row r="828" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A828" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B828" s="6">
+        <v>2</v>
+      </c>
+      <c r="C828" s="22" t="s">
+        <v>2957</v>
+      </c>
+      <c r="D828" s="7" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E828" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F828" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G828" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H828" s="7" t="s">
+        <v>2981</v>
+      </c>
+      <c r="I828" s="6"/>
+    </row>
+    <row r="829" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A829" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B829" s="6">
+        <v>3</v>
+      </c>
+      <c r="C829" s="22" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D829" s="7" t="s">
+        <v>2973</v>
+      </c>
+      <c r="E829" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F829" s="12">
+        <v>4</v>
+      </c>
+      <c r="G829" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H829" s="7" t="s">
+        <v>2987</v>
+      </c>
+      <c r="I829" s="6"/>
+    </row>
+    <row r="830" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A830" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B830" s="6">
+        <v>4</v>
+      </c>
+      <c r="C830" s="22" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D830" s="7" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E830" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="F830" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G830" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H830" s="7" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I830" s="6"/>
+    </row>
+    <row r="831" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A831" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B831" s="6">
+        <v>5</v>
+      </c>
+      <c r="C831" s="22" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D831" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="E831" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F831" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G831" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H831" s="7" t="s">
+        <v>2989</v>
+      </c>
+      <c r="I831" s="6"/>
+    </row>
+    <row r="832" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A832" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B832" s="6">
+        <v>6</v>
+      </c>
+      <c r="C832" s="22" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D832" s="7" t="s">
+        <v>2976</v>
+      </c>
+      <c r="E832" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F832" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G832" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H832" s="7" t="s">
+        <v>2982</v>
+      </c>
+      <c r="I832" s="6"/>
+    </row>
+    <row r="833" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A833" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B833" s="6">
+        <v>7</v>
+      </c>
+      <c r="C833" s="22" t="s">
+        <v>2962</v>
+      </c>
+      <c r="D833" s="7" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E833" s="20">
+        <v>3.58</v>
+      </c>
+      <c r="F833" s="12">
+        <v>4</v>
+      </c>
+      <c r="G833" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H833" s="7" t="s">
+        <v>2983</v>
+      </c>
+      <c r="I833" s="6"/>
+    </row>
+    <row r="834" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A834" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B834" s="6">
+        <v>8</v>
+      </c>
+      <c r="C834" s="22" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D834" s="7" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E834" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F834" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G834" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H834" s="7" t="s">
+        <v>2984</v>
+      </c>
+      <c r="I834" s="6"/>
+    </row>
+    <row r="835" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A835" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B835" s="6">
+        <v>9</v>
+      </c>
+      <c r="C835" s="22" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D835" s="7" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E835" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F835" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G835" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H835" s="7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="I835" s="6"/>
+    </row>
+    <row r="836" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A836" s="6">
+        <v>2598614</v>
+      </c>
+      <c r="B836" s="6">
+        <v>10</v>
+      </c>
+      <c r="C836" s="22" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D836" s="7" t="s">
+        <v>2980</v>
+      </c>
+      <c r="E836" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F836" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G836" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H836" s="7" t="s">
+        <v>2985</v>
+      </c>
+      <c r="I836" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BB977C-51FC-498A-8D0C-C37B0A40A50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34329CC5-8053-40AD-9CBB-7824A5CADCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="2991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="3037">
   <si>
     <t>No</t>
   </si>
@@ -9904,6 +9904,144 @@
   </si>
   <si>
     <t>Πιο dissonant και ψυχεδελικό, με τίτλο που μπορεί να σημαίνει ραβδί, μαγικό αντικείμενο ή πράξη περιπλάνησης. Η μουσική χτίζει αστάθεια, οι κιθάρες δεν συμφωνούν απόλυτα, οι ρυθμοί μοιάζουν να αλλάζουν οπτική και η φωνή δεν προσφέρει καθαρή λύση. Είναι ένα από τα tracks που δείχνουν καλύτερα τη δυνατότητα των Thin White Rope να κάνουν alternative rock που έχει πραγματικό μυστήριο, όχι μόνο “quirky” στιχουργία.</t>
+  </si>
+  <si>
+    <t>Mother Love Bone</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Mercury – 00602478357541, UMe – 00602478357541 (Europe, Sep 26, 2025, LP, Album, Reissue, Remastered, 180g Eco-Vinyl).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Official European remastered reissue on 180g black Eco-Vinyl, featuring hype sticker details noting the anniversary remastered campaign. Vinyl mastering executed by Levi Seitz at Black Belt Mastering, working from the master sources originally overseen by Bob Ludwig. Captures the definitive Seattle pre-grunge / glam-metal crossover masterpiece, blending Andrew Wood's theatrical charisma with Stone Gossard and Jeff Ament's gritty guitar-driven architecture (prior to the formation of Pearl Jam).</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/-rmF1i5endvY2zwie1O34ThuYezqc4MmlYSn150OT3k/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MTg3/ODc3LTE3NTg4Nzk0/MjgtODExMi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35187877-Mother-Love-Bone-Apple</t>
+  </si>
+  <si>
+    <t>This Is Shangrila</t>
+  </si>
+  <si>
+    <t>Stardog Champion</t>
+  </si>
+  <si>
+    <t>Holy Roller</t>
+  </si>
+  <si>
+    <t>Bone China</t>
+  </si>
+  <si>
+    <t>Come Bite The Apple</t>
+  </si>
+  <si>
+    <t>Stargazer</t>
+  </si>
+  <si>
+    <t>Heartshine</t>
+  </si>
+  <si>
+    <t>Captain Hi-Top</t>
+  </si>
+  <si>
+    <t>Man Of Golden Words</t>
+  </si>
+  <si>
+    <t>Capricorn Sister</t>
+  </si>
+  <si>
+    <t>Gentle Groove</t>
+  </si>
+  <si>
+    <t>Mr. Danny Boy</t>
+  </si>
+  <si>
+    <t>Crown Of Thorns</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Pre-Grunge, Glam-Grunge, Seattle Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Glam-Grunge, Psychedelic Hard Rock, Album Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Alternative Rock [Glam Rock, Seattle Rock, Anthemic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Heavy Rock, Psychedelic Grunge, Groove Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Dark Seattle Rock, Heavy Alternative, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Slow-Burn Hard Rock, Glam-Grunge, Heavy Groove]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Glam Rock [Psychedelic Rock, Glam-Grunge, Dreamy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Melodic Seattle Rock, Soulful Grunge, Emotional Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Narrative Rock, Psychedelic Hard Rock, Glam Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Folk Rock [Acoustic Grunge, Psychedelic Folk, Intimate Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Dark Glam Rock, Heavy Alternative, Character Song]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Funk Rock [Funky Grunge, Groove Rock, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Dark Rock, Heavy Ballad, Seattle Alternative]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Hard Rock [Epic Grunge Ballad, Seattle Rock, Emotional Finale]</t>
+  </si>
+  <si>
+    <t>Μεγάλο hard-rock anthem με χαρακτηριστική swagger ερμηνεία. Ο “stardog” είναι μια φιγούρα rock-star fantasy, αλλά ο Wood δεν τον αντιμετωπίζει εντελώς ειρωνικά ούτε εντελώς σοβαρά. Η μπάντα παίζει με ρυθμικό βάρος και κιθαριστικά hooks που θυμίζουν classic rock, ενώ ο Wood τραγουδά σαν κάποιος που έχει ήδη χτίσει τον δικό του προσωπικό μύθο. Είναι από τα κομμάτια που δείχνουν πόσο πιθανό ήταν να εξελιχθούν σε μεγάλη μπάντα πριν τον θάνατό του.</t>
+  </si>
+  <si>
+    <t>Πιο βαρύ και πιο ψυχεδελικό, με riff που φέρνει την μπάντα πιο κοντά σε early Seattle heaviness. Ο τίτλος παραπέμπει σε θρησκευτικό φανατισμό ή σε κάποιον που “κυλά” μέσα σε πνευματική/κοινωνική υποκρισία. Η μουσική έχει groove και σκοτεινή κιθαριστική υφή, ενώ η φωνή του Wood ισορροπεί ανάμεσα σε ειρωνεία και αληθινή ένταση. Δεν έχει το άμεσο chorus του “Stardog Champion”, όμως χτίζει πιο βαθύ mood.</t>
+  </si>
+  <si>
+    <t>Από τις πιο ονειρικές και ψυχεδελικές συνθέσεις του album. Ο “stargazer” κοιτάζει προς κάτι μακρινό, ίσως ελπίδα, ίσως φαντασίωση, ίσως απόδραση από μια δύσκολη πραγματικότητα. Η μπάντα χαμηλώνει τη σκληρότητα, χωρίς να χάνει την ένταση, και ο Wood τραγουδά με περισσότερο χώρο και μελωδική χάρη. Είναι ένα από τα καλύτερα παραδείγματα της ικανότητάς τους να συνδυάζουν heavy rock με αίσθηση αιώρησης.</t>
+  </si>
+  <si>
+    <t>Μελωδικό, soulful και πιο ανθρώπινο. Ο τίτλος υπονοεί το φως ή την ενέργεια που έρχεται από την καρδιά, όμως η ερμηνεία δεν γίνεται αφελής. Οι κιθάρες και το μπάσο κρατούν τη σύνθεση σε Seattle-rock έδαφος, ενώ ο Wood δίνει στο refrain ζεστασιά. Είναι μια γέφυρα ανάμεσα στη φαντασία του “Stargazer” και στους πιο προσωπικούς χαρακτήρες της επόμενης ενότητας.</t>
+  </si>
+  <si>
+    <t>Δεύτερο CD-era bonus track, πιο σκοτεινό και heavy από το “Gentle Groove”. Η προσθήκη του στο 2025 LP αυξάνει την αίσθηση βάρους πριν από το “Crown Of Thorns”. Ως αυτόνομο κομμάτι έχει ενδιαφέρον επειδή διατηρεί τη βαριά κιθαριστική ατμόσφαιρα, αλλά δεν είναι το ίδιο αναπόφευκτο ή κομβικό για το αρχικό 1990 arc.</t>
+  </si>
+  <si>
+    <t>Αρχικά CD bonus track, έχει περισσότερο χαλαρό, funk-tinged χαρακτήρα. Η θέση του στη σύγχρονη 13-track sequence λειτουργεί σαν μικρή αλλαγή πίεσης πριν από το “Mr. Danny Boy”. Δεν έχει το ίδιο καθοριστικό βάρος με τα κεντρικά album tracks, αλλά δείχνει την groove πλευρά της μπάντας και τη δυνατότητα του Wood να κινείται με άνεση σε πιο soulful/funky phrasing.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό character piece, με astrology imagery και heavy alternative rock βάση. Η “Capricorn sister” παρουσιάζεται ως αινιγματική φιγούρα, ισχυρή αλλά απόμακρη. Οι κιθάρες γίνονται ξανά πιο βαριές, όμως η μελωδία παραμένει σημαντική. Είναι το σημείο όπου η μπάντα αρχίζει να οδεύει προς το τραγικό κλείσιμο, αφήνοντας πίσω την πιο ανοιχτή fun πλευρά της A πλευράς.</t>
+  </si>
+  <si>
+    <t>Character song με bizarre, σχεδόν comic-book όνομα και ψυχεδελικό hard-rock πλαίσιο. Ο “Captain” είναι άλλη μία Wood φιγούρα ,ταυτόχρονα μεγάλος, γελοίος, θεατρικός και πιθανώς ευάλωτος. Η μπάντα διατηρεί rock momentum, αλλά αφήνει μικρές παράξενες γωνίες στην κιθάρα και στη δομή, κάτι που εμποδίζει το κομμάτι να γίνει απλό glam parody.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση και το πιο διαχρονικό Mother Love Bone τραγούδι. Το στέμμα από αγκάθια δίνει αμέσως θρησκευτική/μαρτυρική εικόνα, αλλά το τραγούδι αφορά ευρύτερα πόνο, απομόνωση, επιθυμία για λύτρωση και την αδυναμία να βρεις εύκολη ειρήνη. Η σύνθεση αναπτύσσεται αργά, δίνοντας χώρο στη φωνή του Wood να περάσει από ευαισθησία σε τεράστια συναισθηματική ένταση. Οι κιθάρες, το μπάσο του Ament και τα drums του Gilmore χτίζουν μια epic Seattle-rock μπαλάντα χωρίς να γίνεται υπερβολική. Είναι το τραγούδι που, μετά τον θάνατο του Wood, ακούγεται σχεδόν προφητικό ,αλλά η δύναμή του δεν εξαρτάται από την τραγωδία. Είναι απλώς μια σπουδαία rock σύνθεση.</t>
+  </si>
+  <si>
+    <t>Το ιδανικό άνοιγμα και μία από τις πιο αντιπροσωπευτικές Mother Love Bone συνθέσεις. Το “Shangrila” είναι φαντασιακός τόπος διαφυγής, επιθυμίας και rock ’n’ roll υπερβολής. Οι κιθάρες των Gossard και Fairweather έχουν βαρύτητα, αλλά ο Andrew Wood μετατρέπει το τραγούδι σε κάτι μεγαλύτερο από ένα hard-rock opener, η φωνή του είναι θεατρική, παιχνιδιάρικη και ταυτόχρονα ελαφρώς στοιχειωμένη. Η μπάντα ακούγεται σαν να έχει ένα πόδι στο glam/sleaze της προηγούμενης δεκαετίας και το άλλο στο επερχόμενο Seattle alternative rock.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, πιο κοφτό και λιγότερο glam. Ο τίτλος ,πορσελάνη που είναι όμορφη αλλά εύθραυστη, ταιριάζει με τη μουσική ισορροπία, heavy κιθάρες, νευρικό rhythm section και μια φωνητική γραμμή που μοιάζει να κινείται πάνω σε κάτι που μπορεί εύκολα να σπάσει. Είναι track που δείχνει την πιο alternative πλευρά της μπάντας, με λιγότερη εκτόνωση και περισσότερο tension.</t>
+  </si>
+  <si>
+    <t>Slow-burn hard-rock track που χρησιμοποιεί το μήλο ως εικόνα πειρασμού, επιθυμίας και επικίνδυνης πρόσκλησης. Η μουσική δεν βιάζεται, αφήνει το groove να εγκατασταθεί, τις κιθάρες να δημιουργήσουν χώρο και τον Wood να μετατρέψει το ερωτικό κάλεσμα σε σχεδόν μυθολογική σκηνή. Είναι πιο βαρύ και πιο υπνωτικό από το γρήγορο πρώτο μέρος του δίσκου.</t>
+  </si>
+  <si>
+    <t>Η ακουστική, εύθραυστη καρδιά του album. Με λιγότερη ηλεκτρική κάλυψη, η φωνή του Wood γίνεται πιο άμεση και εκτεθειμένη. Ο “άνθρωπος των χρυσών λέξεων” μπορεί να είναι ποιητής, γκουρού, εραστής ή ο ίδιος ο αφηγητής που αναζητά σωστή γλώσσα για να εκφράσει κάτι που δεν μπορεί να ειπωθεί απλά. Η συναισθηματική αξία του κομματιού προκύπτει από την οικονομία του, δεν χρειάζεται μεγάλο riff για να αφήσει βάρος. Είναι από τα tracks που κάνουν το Apple κάτι πολύ περισσότερο από ένα lost glam-grunge album.</t>
   </si>
 </sst>
 </file>
@@ -10430,7 +10568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13290,6 +13428,38 @@
       </c>
       <c r="J89" s="11" t="s">
         <v>2970</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="D90" s="6">
+        <v>1990</v>
+      </c>
+      <c r="E90" s="10">
+        <v>3.44</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>3010</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>2994</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>2993</v>
+      </c>
+      <c r="I90" s="11" t="s">
+        <v>2996</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>2995</v>
       </c>
     </row>
   </sheetData>
@@ -13467,6 +13637,8 @@
     <hyperlink ref="I88" r:id="rId171" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
     <hyperlink ref="I89" r:id="rId172" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
     <hyperlink ref="J89" r:id="rId173" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
+    <hyperlink ref="J90" r:id="rId174" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
+    <hyperlink ref="I90" r:id="rId175" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13474,7 +13646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I836"/>
+  <dimension ref="A1:I849"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -36187,6 +36359,357 @@
       </c>
       <c r="I836" s="6"/>
     </row>
+    <row r="837" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A837" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B837" s="6">
+        <v>1</v>
+      </c>
+      <c r="C837" s="22" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D837" s="7" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E837" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F837" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G837" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H837" s="7" t="s">
+        <v>3033</v>
+      </c>
+      <c r="I837" s="6"/>
+    </row>
+    <row r="838" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A838" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B838" s="6">
+        <v>2</v>
+      </c>
+      <c r="C838" s="22" t="s">
+        <v>2998</v>
+      </c>
+      <c r="D838" s="7" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E838" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F838" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G838" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H838" s="7" t="s">
+        <v>3024</v>
+      </c>
+      <c r="I838" s="6"/>
+    </row>
+    <row r="839" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A839" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B839" s="6">
+        <v>3</v>
+      </c>
+      <c r="C839" s="22" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D839" s="7" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E839" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F839" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G839" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H839" s="7" t="s">
+        <v>3025</v>
+      </c>
+      <c r="I839" s="6"/>
+    </row>
+    <row r="840" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A840" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B840" s="6">
+        <v>4</v>
+      </c>
+      <c r="C840" s="22" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D840" s="7" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E840" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F840" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G840" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H840" s="7" t="s">
+        <v>3034</v>
+      </c>
+      <c r="I840" s="6"/>
+    </row>
+    <row r="841" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A841" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B841" s="6">
+        <v>5</v>
+      </c>
+      <c r="C841" s="22" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D841" s="7" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E841" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F841" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G841" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H841" s="7" t="s">
+        <v>3035</v>
+      </c>
+      <c r="I841" s="6"/>
+    </row>
+    <row r="842" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A842" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B842" s="6">
+        <v>6</v>
+      </c>
+      <c r="C842" s="22" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D842" s="7" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E842" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F842" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G842" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H842" s="7" t="s">
+        <v>3026</v>
+      </c>
+      <c r="I842" s="6"/>
+    </row>
+    <row r="843" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A843" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B843" s="6">
+        <v>7</v>
+      </c>
+      <c r="C843" s="22" t="s">
+        <v>3003</v>
+      </c>
+      <c r="D843" s="7" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E843" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F843" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G843" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H843" s="7" t="s">
+        <v>3027</v>
+      </c>
+      <c r="I843" s="6"/>
+    </row>
+    <row r="844" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A844" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B844" s="6">
+        <v>8</v>
+      </c>
+      <c r="C844" s="22" t="s">
+        <v>3004</v>
+      </c>
+      <c r="D844" s="7" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E844" s="20">
+        <v>3.36</v>
+      </c>
+      <c r="F844" s="12">
+        <v>4</v>
+      </c>
+      <c r="G844" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H844" s="7" t="s">
+        <v>3031</v>
+      </c>
+      <c r="I844" s="6"/>
+    </row>
+    <row r="845" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A845" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B845" s="6">
+        <v>9</v>
+      </c>
+      <c r="C845" s="22" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D845" s="7" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E845" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F845" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G845" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H845" s="7" t="s">
+        <v>3036</v>
+      </c>
+      <c r="I845" s="6"/>
+    </row>
+    <row r="846" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A846" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B846" s="6">
+        <v>10</v>
+      </c>
+      <c r="C846" s="22" t="s">
+        <v>3006</v>
+      </c>
+      <c r="D846" s="7" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E846" s="20">
+        <v>3.36</v>
+      </c>
+      <c r="F846" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G846" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H846" s="7" t="s">
+        <v>3030</v>
+      </c>
+      <c r="I846" s="6"/>
+    </row>
+    <row r="847" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A847" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B847" s="6">
+        <v>11</v>
+      </c>
+      <c r="C847" s="22" t="s">
+        <v>3007</v>
+      </c>
+      <c r="D847" s="7" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E847" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F847" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G847" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H847" s="7" t="s">
+        <v>3029</v>
+      </c>
+      <c r="I847" s="6"/>
+    </row>
+    <row r="848" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A848" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B848" s="6">
+        <v>12</v>
+      </c>
+      <c r="C848" s="22" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D848" s="7" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E848" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F848" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G848" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H848" s="7" t="s">
+        <v>3028</v>
+      </c>
+      <c r="I848" s="6"/>
+    </row>
+    <row r="849" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A849" s="6">
+        <v>35187877</v>
+      </c>
+      <c r="B849" s="6">
+        <v>13</v>
+      </c>
+      <c r="C849" s="22" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D849" s="7" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E849" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F849" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G849" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H849" s="7" t="s">
+        <v>3032</v>
+      </c>
+      <c r="I849" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34329CC5-8053-40AD-9CBB-7824A5CADCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5545780C-BEB5-48FF-838F-1F29660D18DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="3037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3335" uniqueCount="3073">
   <si>
     <t>No</t>
   </si>
@@ -10042,6 +10042,114 @@
   </si>
   <si>
     <t>Η ακουστική, εύθραυστη καρδιά του album. Με λιγότερη ηλεκτρική κάλυψη, η φωνή του Wood γίνεται πιο άμεση και εκτεθειμένη. Ο “άνθρωπος των χρυσών λέξεων” μπορεί να είναι ποιητής, γκουρού, εραστής ή ο ίδιος ο αφηγητής που αναζητά σωστή γλώσσα για να εκφράσει κάτι που δεν μπορεί να ειπωθεί απλά. Η συναισθηματική αξία του κομματιού προκύπτει από την οικονομία του, δεν χρειάζεται μεγάλο riff για να αφήσει βάρος. Είναι από τα tracks που κάνουν το Apple κάτι πολύ περισσότερο από ένα lost glam-grunge album.</t>
+  </si>
+  <si>
+    <t>Magma</t>
+  </si>
+  <si>
+    <t>Gojira</t>
+  </si>
+  <si>
+    <t>Roadrunner Records – RR7479-1, Roadrunner Records – 1686-174791 (USA, Canada &amp; Europe, 2025 Reissue, LP, Album). Pressed by GZ Media (Plant ID: 142956E...).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Official 2025 vinyl reissue pressed at GZ Media, distributed internationally by Atlantic / WEA International. Recorded and mixed at Silver Cloud Studio, NY, with mixing duties handled by Johann Meyer and Joe Duplantier. Mastered at Sterling Sound, New York, by Ted Jensen. Captures Gojira's emotional, Grammy-nominated progressive/death metal masterpiece, shaped heavily by the personal loss experienced by Joe and Mario Duplantier during its creation.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/34750368-Gojira-Magma</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/rhUlmR9dCOveYX7-0k6zpwnY26jCcJI8PdNSzDL6TWc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0NzUw/MzY4LTE3NTQ1MDIx/NTctNDMzNS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>The Shooting Star</t>
+  </si>
+  <si>
+    <t>Silvera</t>
+  </si>
+  <si>
+    <t>The Cell</t>
+  </si>
+  <si>
+    <t>Stranded</t>
+  </si>
+  <si>
+    <t>Yellow Stone</t>
+  </si>
+  <si>
+    <t>Pray</t>
+  </si>
+  <si>
+    <t>Only Pain</t>
+  </si>
+  <si>
+    <t>Low Lands</t>
+  </si>
+  <si>
+    <t>Liberation</t>
+  </si>
+  <si>
+    <t>Metal [Progressive Metal, Groove Metal, Alternative Metal, Post-Metal, Death Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Atmospheric Metal, Post-Metal, Progressive Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Groove Metal, Technical Death Metal, Progressive Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Death Metal, Thrash-infused Groove Metal, Technical Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Groove Metal, Alternative Metal, Industrial-leaning Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Ambient Instrumental, Drone Metal, Post-Rock]</t>
+  </si>
+  <si>
+    <t>Metal [Alternative Metal, Sludge-tinged Atmospheric Metal, Progressive Rock]</t>
+  </si>
+  <si>
+    <t>Metal [Progressive Metal, Epic Groove Metal, Post-Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Death Metal, Thrash Metal, Aggressive Groove Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Post-Metal, Atmospheric Progressive Metal, Doom-influenced Metal]</t>
+  </si>
+  <si>
+    <t>Metal [Acoustic Instrumental, Neofolk, Ambient Rock]</t>
+  </si>
+  <si>
+    <t>Υπνωτικό, ατμοσφαιρικό άνοιγμα με τεράστιο ηχητικό πλάτος. Το GZ Media pressing αποδίδει υποδειγματικά τον βαρύ, κιθαριστικό όγκο και την echo-laden παραγωγή.</t>
+  </si>
+  <si>
+    <t>Ένας από τους πιο εμβληματικούς ύμνους του δίσκου. Κοφτερά riffs, τεράστια δυναμική και εξαιρετική απόδοση στα τύμπανα του Mario Duplantier, με καθαρότατη διαχωριστική ικανότητα.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, επιθετικό κομμάτι με αδυσώπητο ρυθμό· η λακέρ κοπή διαχειρίζεται τα transient χτυπήματα χωρίς καμία παραμόρφωση.</t>
+  </si>
+  <si>
+    <t>Βαρύ, ασφυκτικό groove με κυκλώpεια κιθαριστικά τείχη. Το mastering του Ted Jensen λάμπει στη μεσαία και χαμηλή περιοχή.</t>
+  </si>
+  <si>
+    <t>Οργανικό, εσωτερικό instrumental πέρασμα που λειτουργεί ως τέλεια ηχητική γέφυρα, αποδιδόμενο με απόλυτη ησυχία αυλακιού (low noise floor).</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, μελαγχολικό και βαθιά συναισθηματικό κομμάτι· τα καθαρότερα φωνητικά του Joe αναπνέουν ιδανικά στο ηχητικό πεδίο.</t>
+  </si>
+  <si>
+    <t>Έπος προοδευτικού metal με τεράστια κλιμάκωση και εκρηκτικό φινάλε που απαιτεί δυναμικό εύρος από το βινύλιο.</t>
+  </si>
+  <si>
+    <t>Ωμή ενέργεια και κοφτερά thrash/death στοιχεία, αποτυπωμένα με διαύγεια και κοφτερό punch.</t>
+  </si>
+  <si>
+    <t>Το απόλυτο συναισθηματικό και ηχητικό αριστούργημα του άλμπουμ. Από τα απαλά κιθαριστικά arpeggios μέχρι το τιτάνιο, λυτρωτικό φινάλε, η πίεση του βινυλίου αποδίδει το μεγαλείο της σύνθεσης.</t>
+  </si>
+  <si>
+    <t>Ακουστικό, διαλογιστικό κλείσιμο. Τα φυσικά έγχορδα και τα κρουστά ακούγονται με εξαιρετική ζεστασιά και ξύλινη υφή.</t>
   </si>
 </sst>
 </file>
@@ -10568,7 +10676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13460,6 +13568,38 @@
       </c>
       <c r="J90" s="11" t="s">
         <v>2995</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D91" s="6">
+        <v>2016</v>
+      </c>
+      <c r="E91" s="10">
+        <v>3.52</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>3040</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>3039</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>3041</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>3042</v>
       </c>
     </row>
   </sheetData>
@@ -13639,6 +13779,8 @@
     <hyperlink ref="J89" r:id="rId173" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
     <hyperlink ref="J90" r:id="rId174" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
     <hyperlink ref="I90" r:id="rId175" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
+    <hyperlink ref="I91" r:id="rId176" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
+    <hyperlink ref="J91" r:id="rId177" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13646,7 +13788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I849"/>
+  <dimension ref="A1:I859"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -36710,6 +36852,276 @@
       </c>
       <c r="I849" s="6"/>
     </row>
+    <row r="850" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A850" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B850" s="6">
+        <v>1</v>
+      </c>
+      <c r="C850" s="22" t="s">
+        <v>3043</v>
+      </c>
+      <c r="D850" s="7" t="s">
+        <v>3053</v>
+      </c>
+      <c r="E850" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F850" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G850" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H850" s="7" t="s">
+        <v>3063</v>
+      </c>
+      <c r="I850" s="6"/>
+    </row>
+    <row r="851" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A851" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B851" s="6">
+        <v>2</v>
+      </c>
+      <c r="C851" s="22" t="s">
+        <v>3044</v>
+      </c>
+      <c r="D851" s="7" t="s">
+        <v>3054</v>
+      </c>
+      <c r="E851" s="20">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F851" s="12">
+        <v>5</v>
+      </c>
+      <c r="G851" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H851" s="7" t="s">
+        <v>3064</v>
+      </c>
+      <c r="I851" s="6"/>
+    </row>
+    <row r="852" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A852" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B852" s="6">
+        <v>3</v>
+      </c>
+      <c r="C852" s="22" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D852" s="7" t="s">
+        <v>3055</v>
+      </c>
+      <c r="E852" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F852" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G852" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H852" s="7" t="s">
+        <v>3065</v>
+      </c>
+      <c r="I852" s="6"/>
+    </row>
+    <row r="853" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A853" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B853" s="6">
+        <v>4</v>
+      </c>
+      <c r="C853" s="22" t="s">
+        <v>3046</v>
+      </c>
+      <c r="D853" s="7" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E853" s="20">
+        <v>4.18</v>
+      </c>
+      <c r="F853" s="12">
+        <v>5</v>
+      </c>
+      <c r="G853" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H853" s="7" t="s">
+        <v>3066</v>
+      </c>
+      <c r="I853" s="6"/>
+    </row>
+    <row r="854" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A854" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B854" s="6">
+        <v>5</v>
+      </c>
+      <c r="C854" s="22" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D854" s="7" t="s">
+        <v>3057</v>
+      </c>
+      <c r="E854" s="20">
+        <v>3.18</v>
+      </c>
+      <c r="F854" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G854" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H854" s="7" t="s">
+        <v>3067</v>
+      </c>
+      <c r="I854" s="6"/>
+    </row>
+    <row r="855" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A855" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B855" s="6">
+        <v>6</v>
+      </c>
+      <c r="C855" s="22" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D855" s="7" t="s">
+        <v>3058</v>
+      </c>
+      <c r="E855" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F855" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="G855" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H855" s="7" t="s">
+        <v>3068</v>
+      </c>
+      <c r="I855" s="6"/>
+    </row>
+    <row r="856" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A856" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B856" s="6">
+        <v>7</v>
+      </c>
+      <c r="C856" s="22" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D856" s="7" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E856" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F856" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G856" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H856" s="7" t="s">
+        <v>3069</v>
+      </c>
+      <c r="I856" s="6"/>
+    </row>
+    <row r="857" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A857" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B857" s="6">
+        <v>8</v>
+      </c>
+      <c r="C857" s="22" t="s">
+        <v>3049</v>
+      </c>
+      <c r="D857" s="7" t="s">
+        <v>3060</v>
+      </c>
+      <c r="E857" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F857" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G857" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H857" s="7" t="s">
+        <v>3070</v>
+      </c>
+      <c r="I857" s="6"/>
+    </row>
+    <row r="858" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A858" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B858" s="6">
+        <v>9</v>
+      </c>
+      <c r="C858" s="22" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D858" s="7" t="s">
+        <v>3061</v>
+      </c>
+      <c r="E858" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F858" s="12">
+        <v>5</v>
+      </c>
+      <c r="G858" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H858" s="7" t="s">
+        <v>3071</v>
+      </c>
+      <c r="I858" s="6"/>
+    </row>
+    <row r="859" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A859" s="6">
+        <v>34750368</v>
+      </c>
+      <c r="B859" s="6">
+        <v>10</v>
+      </c>
+      <c r="C859" s="22" t="s">
+        <v>3051</v>
+      </c>
+      <c r="D859" s="7" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E859" s="20">
+        <v>3</v>
+      </c>
+      <c r="F859" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G859" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H859" s="7" t="s">
+        <v>3072</v>
+      </c>
+      <c r="I859" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5545780C-BEB5-48FF-838F-1F29660D18DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11201301-F402-42C2-B4BB-3FA6B9798C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3335" uniqueCount="3073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="3118">
   <si>
     <t>No</t>
   </si>
@@ -10089,67 +10089,202 @@
     <t>Liberation</t>
   </si>
   <si>
-    <t>Metal [Progressive Metal, Groove Metal, Alternative Metal, Post-Metal, Death Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Atmospheric Metal, Post-Metal, Progressive Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Groove Metal, Technical Death Metal, Progressive Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Death Metal, Thrash-infused Groove Metal, Technical Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Groove Metal, Alternative Metal, Industrial-leaning Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Ambient Instrumental, Drone Metal, Post-Rock]</t>
-  </si>
-  <si>
-    <t>Metal [Alternative Metal, Sludge-tinged Atmospheric Metal, Progressive Rock]</t>
-  </si>
-  <si>
-    <t>Metal [Progressive Metal, Epic Groove Metal, Post-Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Death Metal, Thrash Metal, Aggressive Groove Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Post-Metal, Atmospheric Progressive Metal, Doom-influenced Metal]</t>
-  </si>
-  <si>
-    <t>Metal [Acoustic Instrumental, Neofolk, Ambient Rock]</t>
-  </si>
-  <si>
-    <t>Υπνωτικό, ατμοσφαιρικό άνοιγμα με τεράστιο ηχητικό πλάτος. Το GZ Media pressing αποδίδει υποδειγματικά τον βαρύ, κιθαριστικό όγκο και την echo-laden παραγωγή.</t>
-  </si>
-  <si>
-    <t>Ένας από τους πιο εμβληματικούς ύμνους του δίσκου. Κοφτερά riffs, τεράστια δυναμική και εξαιρετική απόδοση στα τύμπανα του Mario Duplantier, με καθαρότατη διαχωριστική ικανότητα.</t>
-  </si>
-  <si>
-    <t>Γρήγορο, επιθετικό κομμάτι με αδυσώπητο ρυθμό· η λακέρ κοπή διαχειρίζεται τα transient χτυπήματα χωρίς καμία παραμόρφωση.</t>
-  </si>
-  <si>
-    <t>Βαρύ, ασφυκτικό groove με κυκλώpεια κιθαριστικά τείχη. Το mastering του Ted Jensen λάμπει στη μεσαία και χαμηλή περιοχή.</t>
-  </si>
-  <si>
-    <t>Οργανικό, εσωτερικό instrumental πέρασμα που λειτουργεί ως τέλεια ηχητική γέφυρα, αποδιδόμενο με απόλυτη ησυχία αυλακιού (low noise floor).</t>
-  </si>
-  <si>
-    <t>Σκοτεινό, μελαγχολικό και βαθιά συναισθηματικό κομμάτι· τα καθαρότερα φωνητικά του Joe αναπνέουν ιδανικά στο ηχητικό πεδίο.</t>
-  </si>
-  <si>
-    <t>Έπος προοδευτικού metal με τεράστια κλιμάκωση και εκρηκτικό φινάλε που απαιτεί δυναμικό εύρος από το βινύλιο.</t>
-  </si>
-  <si>
-    <t>Ωμή ενέργεια και κοφτερά thrash/death στοιχεία, αποτυπωμένα με διαύγεια και κοφτερό punch.</t>
-  </si>
-  <si>
-    <t>Το απόλυτο συναισθηματικό και ηχητικό αριστούργημα του άλμπουμ. Από τα απαλά κιθαριστικά arpeggios μέχρι το τιτάνιο, λυτρωτικό φινάλε, η πίεση του βινυλίου αποδίδει το μεγαλείο της σύνθεσης.</t>
-  </si>
-  <si>
-    <t>Ακουστικό, διαλογιστικό κλείσιμο. Τα φυσικά έγχορδα και τα κρουστά ακούγονται με εξαιρετική ζεστασιά και ξύλινη υφή.</t>
+    <t>Romance</t>
+  </si>
+  <si>
+    <t>Starburster</t>
+  </si>
+  <si>
+    <t>Here’s the Thing</t>
+  </si>
+  <si>
+    <t>Desire</t>
+  </si>
+  <si>
+    <t>In the Modern World</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>Motorcycle Boy</t>
+  </si>
+  <si>
+    <t>Sundowner</t>
+  </si>
+  <si>
+    <t>Horseness Is the Whatness</t>
+  </si>
+  <si>
+    <t>Death Kink</t>
+  </si>
+  <si>
+    <t>Favourite</t>
+  </si>
+  <si>
+    <t>It’s Amazing To Be Young</t>
+  </si>
+  <si>
+    <t>Before You Just Forget</t>
+  </si>
+  <si>
+    <t>Fontaines D.C.</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Art Rock, Dream-Pop, Shoegaze, Orchestral Rock, Nu-Metal influences]</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/34571488-Fontaines-DC-Romance</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/62tPNjKwmMT2NINtU4RZkyEpMlkUVognqM7VlG-4TK4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0NTcx/NDg4LTE3NTI4MTk4/OTAtOTY2Mi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Art Rock [Cinematic Synth Rock, Ambient Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Rap Rock, Trip-Hop pulse, Nu-Metal influence]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Jangle Pop, Grunge-Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Dream Pop [Shoegaze-inflected, Melancholic Indie Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Art Rock [Orchestral Rock, Cinematic Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Dark Indie Rock, Tense Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Neo-Psychedelia [Motorik Rock, Dreamy Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Dream Pop [Nocturnal Indie Rock, Shoegaze]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Art Rock [Literary Rock, Experimental Indie Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Post-Punk [Dark Alternative Rock, Brooding Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Jangle Pop, Britpop revival, Nostalgic Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Indie Rock [Anthemic Alternative Rock, Jangle Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Rock, Dream Pop [Melancholic Indie Rock, Atmospheric Rock]</t>
+  </si>
+  <si>
+    <t>XL Recordings – XL1535LPX, XL Recordings – XL1517S (Worldwide, Jul 18, 2025 Reissue/Expanded Edition, LP, Album, Limited Edition, Turquoise Blue + 7", Single, Black). Pressed by Optimal Media GmbH (Matrix IDs: BO12999 / BO26070).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Limited expanded version on turquoise blue vinyl (LP) including an exclusive bonus 7" single on standard black vinyl featuring two extra tracks (It's Amazing To Be Young / Before You I Just Forget). Lacquer cut and vinyl mastering executed by Matt Colton at Metropolis Mastering (=MATT @ METROPOLIS). Produced and mixed by James Ford, capturing their bold stylistic evolution toward cinematic indie-rock, post-punk, and alternative pop textures with string arrangements by Animesh Raval and performances by the core band (Grian Chatten, Conor Deegan, Conor Curley, Tom Coll, Carlos O'Connell).</t>
+  </si>
+  <si>
+    <t>Η σύντομη εισαγωγή λειτουργεί ως κινηματογραφικό προοίμιο. Synths, αποστασιοποιημένη μελωδία και αίσθηση υπόγειας απειλής παρουσιάζουν τον «ρομαντισμό» όχι ως γλυκιά ασφάλεια, αλλά ως πεδίο επιθυμίας, αβεβαιότητας και αυτοεξαπάτησης.</t>
+  </si>
+  <si>
+    <t>Το “Desire” αντιμετωπίζει την επιθυμία ως κάτι ταυτόχρονα ζωτικό και επικίνδυνο. Η ατμόσφαιρα είναι πιο αιωρούμενη, σχεδόν dream-pop, με κιθάρες που λειτουργούν σαν ομίχλη γύρω από τη φωνή. Δεν είναι τραγούδι κατάκτησης· είναι τραγούδι για την έλλειψη, τη λαχτάρα και την ψυχολογική φθορά που αφήνει η αδυναμία εκπλήρωσης.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο φιλόδοξα κομμάτια του άλμπουμ, χτισμένο με ορχηστρική κλίμακα και σχεδόν μπαλαντική δραματικότητα. Αναζητά μια μορφή καθαρότητας, αλήθειας ή συναισθηματικής επιβεβαίωσης μέσα σε ένα περιβάλλον αποξένωσης. Η παραγωγή διογκώνει το προσωπικό δράμα έως ότου πάρει χαρακτήρα αστικής, κινηματογραφικής μελαγχολίας.</t>
+  </si>
+  <si>
+    <t>Το “Motorcycle Boy” ανοίγει τον ορίζοντα του δίσκου. Αντί να λειτουργεί ως σφιχτό post-punk ξέσπασμα, κινείται πιο ονειρικά και κυκλικά, με αίσθηση φυγής, μετακίνησης και νεανικής μυθολογίας. Η «μοτοσικλέτα» λειτουργεί λιγότερο ως κυριολεκτική εικόνα και περισσότερο ως σύμβολο ελευθερίας, ταχύτητας και αναζήτησης μιας ταυτότητας εκτός στασιμότητας.</t>
+  </si>
+  <si>
+    <t>Το δεύτερο κομμάτι του 7″ λειτουργεί σαν πιο ήσυχη επίλογος. Με μελαγχολική, ατμοσφαιρική χροιά, ασχολείται με τη μνήμη, την απώλεια και την αγωνία να ειπωθεί ή να κρατηθεί κάτι πριν σβήσει. Αν το “Favourite” προσφέρει το αισιόδοξο κλείσιμο του αρχικού άλμπουμ, το “Before You Just Forget” επαναφέρει μια πιο εύθραυστη, αποχαιρετιστήρια διάσταση.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο σοκ του δίσκου, ασθματικό φωνητικό delivery, ελαστικό groove και post-punk ένταση που συναντά rap-rock και nu-metal αναφορές. Οι στίχοι περιστρέφονται γύρω από παρόρμηση, σωματική ανάγκη, άγχος και την αμφίσημη έλξη της υπερβολής. Είναι το κομμάτι που δηλώνει καθαρά πως οι Fontaines D.C. δεν θέλουν να επαναλάβουν απλώς το παλιό post-punk μοντέλο τους.</t>
+  </si>
+  <si>
+    <t>Πιο άμεσο, μελωδικό και φωτεινό από το προηγούμενο, χωρίς να στερείται συναισθηματικής αστάθειας. Οι jangly κιθάρες και το μεγάλο refrain φέρνουν στο προσκήνιο μια pop ευαισθησία, το τραγούδι εκφράζει τη δυσκολία του να παραδεχθείς μια αλήθεια σε κάποιον όταν η σχέση ή η επιθυμία έχει ήδη περιπλέξει τα πάντα.</t>
+  </si>
+  <si>
+    <t>Εδώ επιστρέφει πιο έντονα ο νευρικός, κοφτός πυρήνας των Fontaines D.C. Οι κιθάρες, η ρυθμική πίεση και η καχύποπτη φωνητική ερμηνεία δημιουργούν ένα τραγούδι για κάτι μικρό αλλά επίμονο που «κολλά» στο μυαλό και στη ζωή, μια ενόχληση, μια ανάμνηση, μια εσωτερική διατάραξη.</t>
+  </si>
+  <si>
+    <t>Νυχτερινό και μελαγχολικό, το “Sundowner” είναι από τις πιο ατμοσφαιρικές στιγμές του LP. Η δύση του ήλιου γίνεται ψυχική κατάσταση, το σημείο στο οποίο το φως αποσύρεται και ο άνθρωπος μένει με τις σκέψεις του. Ο ήχος είναι μαλακός, dream-pop και σχεδόν υπνωτικός, αλλά η αίσθηση που αφήνει είναι υπαρξιακά ανήσυχη.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό και πιεστικό, με πιο αδρές κιθάρες και απειλητικό χώρο στην παραγωγή. Το τραγούδι ακουμπά τη σχέση έλξης, αυτοκαταστροφής και θνητότητας, τον τρόπο με τον οποίο η επιθυμία μπορεί να αναμιγνύεται με φόβο, βία ή την ανάγκη να ξεπεραστεί ένα προσωπικό όριο.</t>
+  </si>
+  <si>
+    <t>Το ιδανικό κλείσιμο, μελωδικό, θερμό και τελικά λυτρωτικό. Η pop καθαρότητα του refrain και η jangle-rock κιθάρα δεν ακυρώνουν τη μελαγχολία· τη μετατρέπουν σε ανάμνηση που μπορεί να αντέξει. Μετά τη νευρικότητα, τη σκοτεινιά και τις ρωγμές των προηγούμενων κομματιών, το “Favourite” αφήνει την αίσθηση ότι η αγάπη, η φιλία ή η κοινή μνήμη παραμένουν μια πιθανή έξοδος.</t>
+  </si>
+  <si>
+    <t>Το πρώτο bonus track μεταφέρει πιο καθαρά μια αίσθηση νεανικής ορμής και προσδοκίας. Έχει πιο εξωστρεφή, anthemic χαρακτήρα από αρκετές στιγμές του βασικού LP, η νεότητα παρουσιάζεται ως κατάσταση έντασης, πιθανότητας και αυταπάτης μαζί. Δεν είναι bonus που αλλάζει τη δραματουργία του Romance, αλλά ταιριάζει με τον κόσμο του, επειδή συνδέει την επιθυμία με την ανάγκη για κίνηση και διαφυγή.</t>
+  </si>
+  <si>
+    <t>Ο τίτλος παραπέμπει στη λογοτεχνική γλώσσα του James Joyce και η σύνθεση αξιοποιεί αυτή την ελλειπτικότητα. Είναι από τα πιο art-rock και πειραματικά τραγούδια του δίσκου, δεν προσφέρει ευθύγραμμη αφήγηση, αλλά θραύσματα εικόνων, συνειρμούς και μια ερώτηση για το πώς η γλώσσα ,και κατ’ επέκταση η τέχνη, προσπαθεί να ονομάσει κάτι που ξεφεύγει από τον ορισμό του.</t>
+  </si>
+  <si>
+    <t>Εναρκτήριο κομμάτι με αργή, τελετουργική κίνηση και καθαρές φωνητικές γραμμές. Η εικόνα του πεφταστεριού γίνεται όχημα για στοχασμό πάνω στην απώλεια, τη φθαρτότητα και την αποδοχή της μετάβασης. Η μελωδική είσοδος δηλώνει αμέσως ότι το Magma θα εκφραστεί περισσότερο με ατμόσφαιρα και συγκράτηση παρά με διαρκή τεχνική επίδειξη.</t>
+  </si>
+  <si>
+    <t>Η πιο εκρηκτική, άμεση και ρυθμικά εθιστική στιγμή του άλμπουμ. Το βασικό riff, οι κοφτές αλλαγές και η επιθετική ερμηνεία του Joe αναδεικνύουν το DNA της μπάντας, αλλά η δομή είναι ασυνήθιστα περιεκτική και αποτελεσματική. Θεματικά αντιπαραθέτει την ανθρώπινη αδράνεια με την ανάγκη για αλλαγή και προσωπική αφύπνιση. Υπήρξε επίσης Grammy-nominated στην κατηγορία Best Metal Performance.</t>
+  </si>
+  <si>
+    <t>Η καρδιά του δίσκου. Αργό, βαρύ και σχεδόν κατακλυσμιαίο, το title track χρησιμοποιεί το μάγμα ως εικόνα καταπίεσης που συσσωρεύεται κάτω από την επιφάνεια ώσπου να εκραγεί. Εδώ η μπάντα προσεγγίζει post-metal και sludge αίσθηση χωρίς να εγκαταλείπει το χαρακτηριστικό της groove. Η ερμηνεία είναι περισσότερο στοιχειωμένη παρά επιθετική.</t>
+  </si>
+  <si>
+    <t>Κοφτό, επίμονο και σχεδόν αφαιρετικά βίαιο. Στη στιχουργική του λογική, ο πόνος δεν αντιμετωπίζεται ως κάτι που εξιδανικεύεται, αλλά ως αναπόφευκτο βίωμα που απαιτεί αναγνώριση. Η πιο ευθύγραμμη modern-metal γραφή του το καθιστά ένα από τα λιγότερο σύνθετα, αλλά ιδιαίτερα λειτουργικά, tracks του άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Οργανικό φινάλε με ελευθερωτική, σχεδόν ambient-post-metal διάθεση. Μετά την ένταση του Low Lands, δεν προσφέρει θριαμβευτικό τέλος· προσφέρει μια ήσυχη έξοδο, σαν άδειασμα του πένθους και επιστροφή στην αναπνοή. Η θέση του στον δίσκο είναι καθοριστική, γιατί κάνει το Magma να κλείνει με αποδοχή αντί για σύγκρουση.</t>
+  </si>
+  <si>
+    <t>Μια μεταλλική αλληγορία εγκλωβισμού. Ο «θάλαμος» δεν χρειάζεται να είναι κυριολεκτικός, μπορεί να είναι ο νους, ο φόβος, ο κοινωνικός ρόλος ή η προσωπική επανάληψη. Τα νευρικά, σχεδόν μηχανικά riffs και η μεταβλητή ρυθμική αγωγή μεταφέρουν ακριβώς αυτή την αίσθηση πίεσης και αδυναμίας διαφυγής.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, μελωδικό metal single του δίσκου. Η προσβασιμότητά του δεν είναι παραχώρηση, βασίζεται σε ένα στιβαρό groove, στα καθαρά hooks και σε μια ερμηνεία που προβάλλει την απομόνωση ως υπαρξιακή κατάσταση. Το “Stranded in the dark” δεν περιγράφει απλώς μοναξιά· περιγράφει το σημείο στο οποίο ο άνθρωπος χρειάζεται να κινηθεί ενώ δεν έχει πλήρη εικόνα του δρόμου.</t>
+  </si>
+  <si>
+    <t>Σύντομο οργανικό interlude, με λειτουργία καθαρισμού του χώρου πριν από το βαρύτερο δεύτερο μισό. Δεν επιδιώκει να σταθεί ως κανονικό τραγούδι, αλλά να μετατρέψει την ένταση σε τοπίο, ανοιχτός χώρος, ηρεμία, προσωρινή αποφόρτιση.</t>
+  </si>
+  <si>
+    <t>Από τα πιο τελετουργικά κομμάτια του δίσκου, με ρυθμική βαρύτητα που θυμίζει πορεία ή invocation. Αντιμετωπίζει την προσευχή όχι κατ’ ανάγκη ως θρησκευτική βεβαιότητα, αλλά ως ανθρώπινη κίνηση προς κάτι μεγαλύτερο από το άτομο, παραδοχή αδυναμίας, ανάγκη για συγχώρεση και αναζήτηση νοήματος.</t>
+  </si>
+  <si>
+    <t>Το πιο συγκινητικό και συναισθηματικά ανοιχτό τραγούδι των Gojira έως τότε. Η απουσία εδώ αποκτά προσωπική μορφή, θλίψη, μνήμη, απώλεια και η οδυνηρή ανάγκη να συνεχίσει κανείς. Η κλιμάκωσή του είναι υποδειγματική, επειδή δεν στηρίζεται στην τεχνική επίδειξη αλλά στην υπομονή, την ενορχηστρωτική αύξηση και την ειλικρίνεια της μελωδίας.</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Groove Metal [Atmospheric Metal, Post-Metal, Alternative Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Post-Metal [Atmospheric Metal, Melodic Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Groove Metal, Progressive Metal [Technical Metal, Modern Metal]</t>
+  </si>
+  <si>
+    <t>Groove Metal, Progressive Metal [Polyrhythmic Metal, Alternative Metal]</t>
+  </si>
+  <si>
+    <t>Groove Metal, Alternative Metal [Modern Metal, Melodic Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal [Ambient Interlude (Instrumental)]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Post-Metal [Atmospheric Sludge Metal, Slow-Burn Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Post-Metal [Atmospheric Metal, Tribal Percussion]</t>
+  </si>
+  <si>
+    <t>Groove Metal, Alternative Metal [Melodic Modern Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Post-Metal [Atmospheric Metal, Grief Ballad]</t>
+  </si>
+  <si>
+    <t>Progressive Metal [Ambient, Orchestral Post-Metal (Instrumental)]</t>
   </si>
 </sst>
 </file>
@@ -10676,7 +10811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13587,7 +13722,7 @@
         <v>3.52</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>3052</v>
+        <v>3107</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>3040</v>
@@ -13600,6 +13735,38 @@
       </c>
       <c r="J91" s="11" t="s">
         <v>3042</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D92" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E92" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>3083</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>3082</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>3067</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>3068</v>
       </c>
     </row>
   </sheetData>
@@ -13781,6 +13948,8 @@
     <hyperlink ref="I90" r:id="rId175" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
     <hyperlink ref="I91" r:id="rId176" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
     <hyperlink ref="J91" r:id="rId177" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
+    <hyperlink ref="I92" r:id="rId178" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
+    <hyperlink ref="J92" r:id="rId179" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13788,7 +13957,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I859"/>
+  <dimension ref="A1:I872"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -36852,7 +37021,7 @@
       </c>
       <c r="I849" s="6"/>
     </row>
-    <row r="850" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A850" s="6">
         <v>34750368</v>
       </c>
@@ -36863,23 +37032,23 @@
         <v>3043</v>
       </c>
       <c r="D850" s="7" t="s">
-        <v>3053</v>
+        <v>3108</v>
       </c>
       <c r="E850" s="20">
         <v>3.86</v>
       </c>
       <c r="F850" s="12">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="G850" s="12">
         <v>4.7</v>
       </c>
       <c r="H850" s="7" t="s">
-        <v>3063</v>
+        <v>3097</v>
       </c>
       <c r="I850" s="6"/>
     </row>
-    <row r="851" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A851" s="6">
         <v>34750368</v>
       </c>
@@ -36890,23 +37059,23 @@
         <v>3044</v>
       </c>
       <c r="D851" s="7" t="s">
-        <v>3054</v>
+        <v>3109</v>
       </c>
       <c r="E851" s="20">
         <v>4.3099999999999996</v>
       </c>
       <c r="F851" s="12">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G851" s="12">
         <v>4.8</v>
       </c>
       <c r="H851" s="7" t="s">
-        <v>3064</v>
+        <v>3098</v>
       </c>
       <c r="I851" s="6"/>
     </row>
-    <row r="852" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A852" s="6">
         <v>34750368</v>
       </c>
@@ -36917,23 +37086,23 @@
         <v>3045</v>
       </c>
       <c r="D852" s="7" t="s">
-        <v>3055</v>
+        <v>3110</v>
       </c>
       <c r="E852" s="20">
         <v>3.9</v>
       </c>
       <c r="F852" s="12">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G852" s="12">
         <v>4.7</v>
       </c>
       <c r="H852" s="7" t="s">
-        <v>3065</v>
+        <v>3102</v>
       </c>
       <c r="I852" s="6"/>
     </row>
-    <row r="853" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A853" s="6">
         <v>34750368</v>
       </c>
@@ -36944,23 +37113,23 @@
         <v>3046</v>
       </c>
       <c r="D853" s="7" t="s">
-        <v>3056</v>
+        <v>3111</v>
       </c>
       <c r="E853" s="20">
         <v>4.18</v>
       </c>
       <c r="F853" s="12">
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G853" s="12">
         <v>4.8</v>
       </c>
       <c r="H853" s="7" t="s">
-        <v>3066</v>
+        <v>3103</v>
       </c>
       <c r="I853" s="6"/>
     </row>
-    <row r="854" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A854" s="6">
         <v>34750368</v>
       </c>
@@ -36971,23 +37140,23 @@
         <v>3047</v>
       </c>
       <c r="D854" s="7" t="s">
-        <v>3057</v>
+        <v>3112</v>
       </c>
       <c r="E854" s="20">
         <v>3.18</v>
       </c>
       <c r="F854" s="12">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="G854" s="12">
         <v>4.5999999999999996</v>
       </c>
       <c r="H854" s="7" t="s">
-        <v>3067</v>
+        <v>3104</v>
       </c>
       <c r="I854" s="6"/>
     </row>
-    <row r="855" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A855" s="6">
         <v>34750368</v>
       </c>
@@ -36998,23 +37167,23 @@
         <v>3037</v>
       </c>
       <c r="D855" s="7" t="s">
-        <v>3058</v>
+        <v>3113</v>
       </c>
       <c r="E855" s="20">
         <v>3.81</v>
       </c>
       <c r="F855" s="12">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G855" s="12">
         <v>4.7</v>
       </c>
       <c r="H855" s="7" t="s">
-        <v>3068</v>
+        <v>3099</v>
       </c>
       <c r="I855" s="6"/>
     </row>
-    <row r="856" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A856" s="6">
         <v>34750368</v>
       </c>
@@ -37025,23 +37194,23 @@
         <v>3048</v>
       </c>
       <c r="D856" s="7" t="s">
-        <v>3059</v>
+        <v>3114</v>
       </c>
       <c r="E856" s="20">
         <v>3.76</v>
       </c>
       <c r="F856" s="12">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="G856" s="12">
         <v>4.8</v>
       </c>
       <c r="H856" s="7" t="s">
-        <v>3069</v>
+        <v>3105</v>
       </c>
       <c r="I856" s="6"/>
     </row>
-    <row r="857" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A857" s="6">
         <v>34750368</v>
       </c>
@@ -37052,23 +37221,23 @@
         <v>3049</v>
       </c>
       <c r="D857" s="7" t="s">
-        <v>3060</v>
+        <v>3115</v>
       </c>
       <c r="E857" s="20">
         <v>3.76</v>
       </c>
       <c r="F857" s="12">
-        <v>4.5999999999999996</v>
+        <v>4</v>
       </c>
       <c r="G857" s="12">
         <v>4.5999999999999996</v>
       </c>
       <c r="H857" s="7" t="s">
-        <v>3070</v>
+        <v>3100</v>
       </c>
       <c r="I857" s="6"/>
     </row>
-    <row r="858" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A858" s="6">
         <v>34750368</v>
       </c>
@@ -37079,23 +37248,23 @@
         <v>3050</v>
       </c>
       <c r="D858" s="7" t="s">
-        <v>3061</v>
+        <v>3116</v>
       </c>
       <c r="E858" s="20">
         <v>3.65</v>
       </c>
       <c r="F858" s="12">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G858" s="12">
         <v>4.9000000000000004</v>
       </c>
       <c r="H858" s="7" t="s">
-        <v>3071</v>
+        <v>3106</v>
       </c>
       <c r="I858" s="6"/>
     </row>
-    <row r="859" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A859" s="6">
         <v>34750368</v>
       </c>
@@ -37106,21 +37275,372 @@
         <v>3051</v>
       </c>
       <c r="D859" s="7" t="s">
-        <v>3062</v>
+        <v>3117</v>
       </c>
       <c r="E859" s="20">
         <v>3</v>
       </c>
       <c r="F859" s="12">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G859" s="12">
         <v>4.7</v>
       </c>
       <c r="H859" s="7" t="s">
+        <v>3101</v>
+      </c>
+      <c r="I859" s="6"/>
+    </row>
+    <row r="860" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A860" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B860" s="6">
+        <v>1</v>
+      </c>
+      <c r="C860" s="22" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D860" s="7" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E860" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F860" s="12">
+        <v>4</v>
+      </c>
+      <c r="G860" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H860" s="9" t="s">
+        <v>3084</v>
+      </c>
+      <c r="I860" s="6"/>
+    </row>
+    <row r="861" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A861" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B861" s="6">
+        <v>2</v>
+      </c>
+      <c r="C861" s="22" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D861" s="7" t="s">
+        <v>3070</v>
+      </c>
+      <c r="E861" s="20">
+        <v>4.32</v>
+      </c>
+      <c r="F861" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G861" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H861" s="9" t="s">
+        <v>3089</v>
+      </c>
+      <c r="I861" s="6"/>
+    </row>
+    <row r="862" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A862" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B862" s="6">
+        <v>3</v>
+      </c>
+      <c r="C862" s="22" t="s">
+        <v>3054</v>
+      </c>
+      <c r="D862" s="7" t="s">
+        <v>3071</v>
+      </c>
+      <c r="E862" s="20">
+        <v>3.77</v>
+      </c>
+      <c r="F862" s="12">
+        <v>4</v>
+      </c>
+      <c r="G862" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H862" s="9" t="s">
+        <v>3090</v>
+      </c>
+      <c r="I862" s="6"/>
+    </row>
+    <row r="863" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A863" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B863" s="6">
+        <v>4</v>
+      </c>
+      <c r="C863" s="22" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D863" s="7" t="s">
         <v>3072</v>
       </c>
-      <c r="I859" s="6"/>
+      <c r="E863" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F863" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G863" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H863" s="9" t="s">
+        <v>3085</v>
+      </c>
+      <c r="I863" s="6"/>
+    </row>
+    <row r="864" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A864" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B864" s="6">
+        <v>5</v>
+      </c>
+      <c r="C864" s="22" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D864" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="E864" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F864" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G864" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H864" s="9" t="s">
+        <v>3086</v>
+      </c>
+      <c r="I864" s="6"/>
+    </row>
+    <row r="865" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A865" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B865" s="6">
+        <v>6</v>
+      </c>
+      <c r="C865" s="22" t="s">
+        <v>3057</v>
+      </c>
+      <c r="D865" s="7" t="s">
+        <v>3074</v>
+      </c>
+      <c r="E865" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F865" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G865" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H865" s="9" t="s">
+        <v>3091</v>
+      </c>
+      <c r="I865" s="6"/>
+    </row>
+    <row r="866" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A866" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B866" s="6">
+        <v>7</v>
+      </c>
+      <c r="C866" s="22" t="s">
+        <v>3058</v>
+      </c>
+      <c r="D866" s="7" t="s">
+        <v>3075</v>
+      </c>
+      <c r="E866" s="20">
+        <v>3.38</v>
+      </c>
+      <c r="F866" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G866" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H866" s="9" t="s">
+        <v>3087</v>
+      </c>
+      <c r="I866" s="6"/>
+    </row>
+    <row r="867" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A867" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B867" s="6">
+        <v>8</v>
+      </c>
+      <c r="C867" s="22" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D867" s="7" t="s">
+        <v>3076</v>
+      </c>
+      <c r="E867" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F867" s="12">
+        <v>4</v>
+      </c>
+      <c r="G867" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H867" s="9" t="s">
+        <v>3092</v>
+      </c>
+      <c r="I867" s="6"/>
+    </row>
+    <row r="868" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A868" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B868" s="6">
+        <v>9</v>
+      </c>
+      <c r="C868" s="22" t="s">
+        <v>3060</v>
+      </c>
+      <c r="D868" s="7" t="s">
+        <v>3077</v>
+      </c>
+      <c r="E868" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F868" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G868" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H868" s="9" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I868" s="6"/>
+    </row>
+    <row r="869" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A869" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B869" s="6">
+        <v>10</v>
+      </c>
+      <c r="C869" s="22" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D869" s="7" t="s">
+        <v>3078</v>
+      </c>
+      <c r="E869" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F869" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G869" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H869" s="9" t="s">
+        <v>3093</v>
+      </c>
+      <c r="I869" s="6"/>
+    </row>
+    <row r="870" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A870" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B870" s="6">
+        <v>11</v>
+      </c>
+      <c r="C870" s="22" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D870" s="7" t="s">
+        <v>3079</v>
+      </c>
+      <c r="E870" s="20">
+        <v>4.33</v>
+      </c>
+      <c r="F870" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G870" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H870" s="9" t="s">
+        <v>3094</v>
+      </c>
+      <c r="I870" s="6"/>
+    </row>
+    <row r="871" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A871" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B871" s="6">
+        <v>12</v>
+      </c>
+      <c r="C871" s="22" t="s">
+        <v>3063</v>
+      </c>
+      <c r="D871" s="7" t="s">
+        <v>3080</v>
+      </c>
+      <c r="E871" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F871" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G871" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H871" s="9" t="s">
+        <v>3095</v>
+      </c>
+      <c r="I871" s="6"/>
+    </row>
+    <row r="872" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A872" s="6">
+        <v>34571488</v>
+      </c>
+      <c r="B872" s="6">
+        <v>13</v>
+      </c>
+      <c r="C872" s="22" t="s">
+        <v>3064</v>
+      </c>
+      <c r="D872" s="7" t="s">
+        <v>3081</v>
+      </c>
+      <c r="E872" s="20" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F872" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G872" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H872" s="9" t="s">
+        <v>3088</v>
+      </c>
+      <c r="I872" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11201301-F402-42C2-B4BB-3FA6B9798C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AE1C39-9637-45E4-B34C-15AD372386CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="3118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="3154">
   <si>
     <t>No</t>
   </si>
@@ -10285,6 +10285,114 @@
   </si>
   <si>
     <t>Progressive Metal [Ambient, Orchestral Post-Metal (Instrumental)]</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/m36118vV4frCARWmTwWl1StUlE5HdGzYfR1y7OBQIro/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE4ODEz/NjQ2LTE2MjE1NTkz/NzctMTI2NC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/18813646-Robert-Finley-Sharecroppers-Son</t>
+  </si>
+  <si>
+    <t>Sharecropper's Son</t>
+  </si>
+  <si>
+    <t>Souled Out On You</t>
+  </si>
+  <si>
+    <t>Make Me Feel Alright</t>
+  </si>
+  <si>
+    <t>Country Child</t>
+  </si>
+  <si>
+    <t>Sharecropper’s Son</t>
+  </si>
+  <si>
+    <t>My Story</t>
+  </si>
+  <si>
+    <t>Starting To See</t>
+  </si>
+  <si>
+    <t>I Can Feel Your Pain</t>
+  </si>
+  <si>
+    <t>Better Than I Treat Myself</t>
+  </si>
+  <si>
+    <t>Country Boy</t>
+  </si>
+  <si>
+    <t>All My Hope</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Louisiana Blues, Southern Soul, Gospel, R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Louisiana Soul, Electric Blues]</t>
+  </si>
+  <si>
+    <t>Soul, Blues [Southern Soul, Upbeat R&amp;B]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Autobiographical Louisiana Blues, Swamp Soul]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Autobiographical Soul-Blues, Southern Storytelling]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Spoken-Sung Autobiographical Blues, Southern Soul]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Slow Soul-Blues, Reflective R&amp;B]</t>
+  </si>
+  <si>
+    <t>Soul, Blues [Deep Soul Ballad, Gospel-inflected Blues]</t>
+  </si>
+  <si>
+    <t>Soul, Blues [Southern R&amp;B, Relationship Soul]</t>
+  </si>
+  <si>
+    <t>Blues, Soul [Swamp Blues, Funky Southern Soul]</t>
+  </si>
+  <si>
+    <t>Gospel, Soul [Gospel Soul, Spiritual Ballad]</t>
+  </si>
+  <si>
+    <t>Easy Eye Sound – EES-015 (US, 2021, LP, Album, Stereo). Manufactured and distributed by Concord.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded, engineered, and mixed at Easy Eye Sound Studios in Nashville, TN, by Allen Parker and Dan Auerbach (along with additional mixing by M. Allen Parker). Produced by Dan Auerbach. Lacquer cut and mastered at Sterling Sound Nashville by Ryan Smith (RKS). Captures Robert Finley's deeply personal soulful, blues, and rhythm &amp; blues masterpiece, backed by stellar session musicians assembled by Auerbach (including Nick Movshon, Gene Chrisman, Bobby Wood, and Kenny Brown).</t>
+  </si>
+  <si>
+    <t>Δυναμικό άνοιγμα που παντρεύει electric blues riffing με Southern-soul βηματισμό. Η φράση του τίτλου αποδίδει την απόλυτη συναισθηματική παράδοση σε έναν άνθρωπο—μια αγάπη που έχει ήδη καταλάβει κάθε άμυνα. Ο Finley τραγουδά με την ορμή του παλιού juke-joint performer, ενώ η μπάντα διατηρεί το groove σφιχτό και γήινο.</t>
+  </si>
+  <si>
+    <t>Εδώ η καταγωγή γίνεται ταυτότητα. Ο Finley μιλά ως άνθρωπος της υπαίθρου, όχι ως περσόνα που «φορά» το Southern ύφος. Το κομμάτι δένει blues λεκτικό ιδίωμα, swampy κιθάρες και soul γείωση, φτιάχνοντας μια μικρή δήλωση υπερηφάνειας για τον τόπο, τη δουλειά και τη διαδρομή του.</t>
+  </si>
+  <si>
+    <t>Σχεδόν προφορική αφήγηση πάνω σε soul-blues συνοδεία. Ο Finley υπενθυμίζει ότι η ιστορία του δεν είναι μια αφηρημένη αφήγηση «θριάμβου επί της δυσκολίας», αλλά μια σειρά πραγματικών εμπειριών. Η πιο ελεύθερη, conversational προσέγγιση αναδεικνύει τη χάρη του ως storyteller.</t>
+  </si>
+  <si>
+    <t>Deep-soul μπαλάντα ενσυναίσθησης, με gospel σκιά. Εδώ ο Finley δεν μιλά αποκλειστικά για τη δική του πορεία· αναγνωρίζει τον πόνο του άλλου, χρησιμοποιώντας τη φωνή του σαν όργανο παρηγοριάς. Η οικονομία της ενορχήστρωσης αφήνει το συναίσθημα να έρθει από την άρθρωση και το grain του τραγουδιστή.</t>
+  </si>
+  <si>
+    <t>Ένα τραγούδι ερωτικής και προσωπικής αυτογνωσίας. Ο αφηγητής αναγνωρίζει ότι συχνά οι άνθρωποι είναι πιο επιεικείς με τους άλλους παρά με τον εαυτό τους. Με πιο άμεση soul-R&amp;B φόρμα, λειτουργεί ως προσβάσιμο διάλειμμα μέσα στον βαρύτερο αυτοβιογραφικό κορμό του δίσκου.</t>
+  </si>
+  <si>
+    <t>Funky, γήινο και σχεδόν παιχνιδιάρικα περήφανο. Επιστρέφει στην εικόνα του ανθρώπου της Louisiana, αυτή τη φορά με μεγαλύτερο emphasis στο groove και λιγότερο στο βάρος της αφήγησης. Ο Finley αξιοποιεί την απλή γλώσσα του blues για να δώσει χαρακτήρα, κίνηση και χιούμορ.</t>
+  </si>
+  <si>
+    <t>Πιο φωτεινή και παιχνιδιάρικη στιγμή, με soul/R&amp;B χρώμα και αίσθηση παλιάς Southern dancefloor μπάντας. Δεν ενδιαφέρεται για υπερβολικές δραματουργικές ανατροπές, η δύναμή του είναι η σωματικότητα του ρυθμού και η άμεση επιθυμία για ανακούφιση, συντροφικότητα και καλό συναίσθημα.</t>
+  </si>
+  <si>
+    <t>Το κομμάτι-κλειδί και η αυτοβιογραφική ραχοκοκαλιά του LP. Ο Finley τοποθετεί τον εαυτό του μέσα στην ιστορία της αγροτικής Louisiana, με τρόπο προσωπικό αλλά και κοινωνικά φορτισμένο, εργασία στη γη, στέρηση, οικογενειακή κληρονομιά και η ανάγκη να χτιστεί ζωή από ελάχιστα μέσα. Η ερμηνεία του δεν εκβιάζει συγκίνηση· γι’ αυτό και λειτουργεί τόσο δυνατά.</t>
+  </si>
+  <si>
+    <t>Αργόσυρτο και πιο εσωτερικό. Ο τίτλος αποκτά επιπλέον βάρος λόγω της τύφλωσης του Finley, αλλά το τραγούδι δεν εξαντλείται σε κυριολεξία, αφορά την καθυστερημένη διαύγεια, τη στιγμή κατά την οποία ο άνθρωπος αρχίζει να καταλαβαίνει σχέσεις, επιλογές και εαυτό. Η soul μελωδία αφήνει χώρο στη φωνητική φθορά να λειτουργήσει ως εκφραστικό στοιχείο.</t>
+  </si>
+  <si>
+    <t>Κλείσιμο με gospel-soul πνεύμα, που συγκεντρώνει τα θέματα του δίσκου, πίστη, αντοχή, ελπίδα και η άρνηση της παραίτησης. Δεν προσφέρει εύκολη «happy ending» λύση· παρουσιάζει την ελπίδα ως καθημερινή πράξη επιβίωσης. Είναι ταιριαστός επίλογος για ένα άλμπουμ που βλέπει την προσωπική ιστορία ως πηγή αξιοπρέπειας.</t>
   </si>
 </sst>
 </file>
@@ -10811,7 +10919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13767,6 +13875,38 @@
       </c>
       <c r="J92" s="11" t="s">
         <v>3068</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>3120</v>
+      </c>
+      <c r="D93" s="6">
+        <v>2021</v>
+      </c>
+      <c r="E93" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>3131</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>3143</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>3142</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>3119</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>3118</v>
       </c>
     </row>
   </sheetData>
@@ -13950,6 +14090,8 @@
     <hyperlink ref="J91" r:id="rId177" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
     <hyperlink ref="I92" r:id="rId178" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
     <hyperlink ref="J92" r:id="rId179" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
+    <hyperlink ref="J93" r:id="rId180" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
+    <hyperlink ref="I93" r:id="rId181" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13957,7 +14099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I872"/>
+  <dimension ref="A1:I882"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -37642,6 +37784,276 @@
       </c>
       <c r="I872" s="6"/>
     </row>
+    <row r="873" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A873" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B873" s="6">
+        <v>1</v>
+      </c>
+      <c r="C873" s="22" t="s">
+        <v>3121</v>
+      </c>
+      <c r="D873" s="7" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E873" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F873" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G873" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H873" s="9" t="s">
+        <v>3144</v>
+      </c>
+      <c r="I873" s="6"/>
+    </row>
+    <row r="874" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A874" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B874" s="6">
+        <v>2</v>
+      </c>
+      <c r="C874" s="22" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D874" s="7" t="s">
+        <v>3133</v>
+      </c>
+      <c r="E874" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F874" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G874" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H874" s="9" t="s">
+        <v>3150</v>
+      </c>
+      <c r="I874" s="6"/>
+    </row>
+    <row r="875" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A875" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B875" s="6">
+        <v>3</v>
+      </c>
+      <c r="C875" s="22" t="s">
+        <v>3123</v>
+      </c>
+      <c r="D875" s="7" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E875" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F875" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G875" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H875" s="9" t="s">
+        <v>3145</v>
+      </c>
+      <c r="I875" s="6"/>
+    </row>
+    <row r="876" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A876" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B876" s="6">
+        <v>4</v>
+      </c>
+      <c r="C876" s="22" t="s">
+        <v>3124</v>
+      </c>
+      <c r="D876" s="7" t="s">
+        <v>3135</v>
+      </c>
+      <c r="E876" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F876" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G876" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H876" s="9" t="s">
+        <v>3151</v>
+      </c>
+      <c r="I876" s="6"/>
+    </row>
+    <row r="877" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A877" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B877" s="6">
+        <v>5</v>
+      </c>
+      <c r="C877" s="22" t="s">
+        <v>3125</v>
+      </c>
+      <c r="D877" s="7" t="s">
+        <v>3136</v>
+      </c>
+      <c r="E877" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F877" s="12">
+        <v>4</v>
+      </c>
+      <c r="G877" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H877" s="9" t="s">
+        <v>3146</v>
+      </c>
+      <c r="I877" s="6"/>
+    </row>
+    <row r="878" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A878" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B878" s="6">
+        <v>6</v>
+      </c>
+      <c r="C878" s="22" t="s">
+        <v>3126</v>
+      </c>
+      <c r="D878" s="7" t="s">
+        <v>3137</v>
+      </c>
+      <c r="E878" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F878" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G878" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H878" s="9" t="s">
+        <v>3152</v>
+      </c>
+      <c r="I878" s="6"/>
+    </row>
+    <row r="879" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A879" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B879" s="6">
+        <v>7</v>
+      </c>
+      <c r="C879" s="22" t="s">
+        <v>3127</v>
+      </c>
+      <c r="D879" s="7" t="s">
+        <v>3138</v>
+      </c>
+      <c r="E879" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F879" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G879" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H879" s="9" t="s">
+        <v>3147</v>
+      </c>
+      <c r="I879" s="6"/>
+    </row>
+    <row r="880" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A880" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B880" s="6">
+        <v>8</v>
+      </c>
+      <c r="C880" s="22" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D880" s="7" t="s">
+        <v>3139</v>
+      </c>
+      <c r="E880" s="20">
+        <v>3.77</v>
+      </c>
+      <c r="F880" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G880" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H880" s="9" t="s">
+        <v>3148</v>
+      </c>
+      <c r="I880" s="6"/>
+    </row>
+    <row r="881" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A881" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B881" s="6">
+        <v>9</v>
+      </c>
+      <c r="C881" s="22" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D881" s="7" t="s">
+        <v>3140</v>
+      </c>
+      <c r="E881" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F881" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G881" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H881" s="9" t="s">
+        <v>3149</v>
+      </c>
+      <c r="I881" s="6"/>
+    </row>
+    <row r="882" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A882" s="6">
+        <v>18813646</v>
+      </c>
+      <c r="B882" s="6">
+        <v>10</v>
+      </c>
+      <c r="C882" s="22" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D882" s="7" t="s">
+        <v>3141</v>
+      </c>
+      <c r="E882" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F882" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G882" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H882" s="9" t="s">
+        <v>3153</v>
+      </c>
+      <c r="I882" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AE1C39-9637-45E4-B34C-15AD372386CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889BEF53-D9DE-467A-8B78-58B1A8C1F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="3154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="3185">
   <si>
     <t>No</t>
   </si>
@@ -10393,6 +10393,99 @@
   </si>
   <si>
     <t>Κλείσιμο με gospel-soul πνεύμα, που συγκεντρώνει τα θέματα του δίσκου, πίστη, αντοχή, ελπίδα και η άρνηση της παραίτησης. Δεν προσφέρει εύκολη «happy ending» λύση· παρουσιάζει την ελπίδα ως καθημερινή πράξη επιβίωσης. Είναι ταιριαστός επίλογος για ένα άλμπουμ που βλέπει την προσωπική ιστορία ως πηγή αξιοπρέπειας.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Finley </t>
+  </si>
+  <si>
+    <t>Hallelujah! Don't Let The Devil Fool Ya</t>
+  </si>
+  <si>
+    <t>I Wanna Thank You</t>
+  </si>
+  <si>
+    <t>Praise Him</t>
+  </si>
+  <si>
+    <t>Holy Ghost Party</t>
+  </si>
+  <si>
+    <t>His Love</t>
+  </si>
+  <si>
+    <t>Helping Hand</t>
+  </si>
+  <si>
+    <t>Can’t Take My Joy</t>
+  </si>
+  <si>
+    <t>On The Battlefield</t>
+  </si>
+  <si>
+    <t>I Am A Witness</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/bzlgPr6BkdO-MQTxfrFu23H4ktw53UndP7gyF2n-rc4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MzQy/MDQxLTE3NjAxNTkx/OTQtNDYxMi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35342041-Robert-Finley-Hallelujah-Dont-Let-The-Devil-Fool-Ya</t>
+  </si>
+  <si>
+    <t>Easy Eye Sound – EES-045 (Europe, Oct 2025, LP, Album, Stereo, Yellow &amp; Black Marbled).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Latest album from Robert Finley, marking a powerful return to his gospel roots, produced by Dan Auerbach with backing vocals by Christy Johnson. Lacquer cut and mastering handled with signature RKS precision (Ryan Smith) at Sterling Sound, combined with pressing plant identifiers from MRP.</t>
+  </si>
+  <si>
+    <t>Gospel, Soul [Gospel-soul, bluesy R&amp;B, raw testimonial vocal]</t>
+  </si>
+  <si>
+    <t>Gospel, R&amp;B [Extended gospel groove, deep soul, call-and-response feeling]</t>
+  </si>
+  <si>
+    <t>Gospel, Funk [Up-tempo gospel-funk, celebratory R&amp;B, revival energy]</t>
+  </si>
+  <si>
+    <t>Gospel, Soul [Devotional soul ballad, Southern gospel, warm spiritual blues]</t>
+  </si>
+  <si>
+    <t>Gospel, Funk [Deep gospel groove, funk bass, soul-blues]</t>
+  </si>
+  <si>
+    <t>Gospel, Soul [Defiant gospel-soul, resilient R&amp;B, uplifting roots music]</t>
+  </si>
+  <si>
+    <t>Blues, Gospel [Gospel-blues, Southern soul, spiritual struggle song]</t>
+  </si>
+  <si>
+    <t>Soul, Gospel [Testimonial soul, R&amp;B, closing affirmation]</t>
+  </si>
+  <si>
+    <t>Το ιδανικό άνοιγμα, γιατί καθορίζει αμέσως τη βασική χειρονομία του δίσκου, όχι επίδειξη θρησκευτικής ευσέβειας, αλλά ευγνωμοσύνη που βγαίνει από μια φωνή η οποία ακούγεται σαν να έχει περάσει πράγματα. Το “I Wanna Thank You” λειτουργεί σαν προσωπική μαρτυρία. Ο Finley δεν τραγουδά με την τεχνικά «καθαρή» ευγένεια ενός contemporary gospel τραγουδιστή· η βραχνάδα, οι μικρές ρωγμές και η blues αίσθηση της φωνής του κάνουν το ευχαριστώ να ακούγεται κερδισμένο, όχι διακοσμητικό. Η funky, R&amp;B ρυθμική κίνηση κρατά το τραγούδι γήινο και σωματικό, σαν ευχαριστία που μπορεί να παιχτεί σε εκκλησία αλλά και σε μικρό Louisiana club.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη, πιο εκτεταμένη πνευματική κατάθεση του album. Με διάρκεια επτά λεπτών, δεν αντιμετωπίζεται σαν απλό refrain αλλά σαν groove που χρειάζεται χρόνο για να εγκατασταθεί και να μετατραπεί σε συλλογικό κάλεσμα. Ο τίτλος είναι απλός, όμως η δύναμη προκύπτει από τη σταδιακή επανάληψη, η πίστη παρουσιάζεται ως πράξη, ως επιμονή στον ρυθμό και ως άρνηση της απομόνωσης. Εδώ φαίνεται πιο καθαρά το σημείο όπου soul, R&amp;B και gospel παύουν να είναι χωριστές κατηγορίες. Η ερμηνεία του Finley μοιάζει λιγότερο με διάλεξη και περισσότερο με άνθρωπο που παρασύρει το δωμάτιο να σηκωθεί όρθιο.</t>
+  </si>
+  <si>
+    <t>Ο τίτλος λέει ακριβώς τι προσφέρει το τραγούδι, η πνευματικότητα δεν παρουσιάζεται ως αυστηρή ή πένθιμη, αλλά ως γιορτή. Είναι από τα πιο άμεσα, ανάλαφρα και ρυθμικά σημεία του δίσκου, με gospel-funk αίσθηση που επιτρέπει στο σώμα να ακολουθήσει το μήνυμα. Αν το “Praise Him” λειτουργεί σαν τελετή, το “Holy Ghost Party” είναι η στιγμή όπου η τελετή ξεσπά σε χορό. Η μπάντα δίνει μια στιβαρή R&amp;B βάση και ο Finley τραγουδά με το γνώριμο μείγμα σοβαρότητας, χιούμορ και νότιας ευκολίας. Δεν προσπαθεί να εκσυγχρονίσει επιφανειακά το gospel· το συνδέει με τη διαχρονική λειτουργία της soul μουσικής ως κοινότητας, απελευθέρωσης και χαράς.</t>
+  </si>
+  <si>
+    <t>Μετά το εξωστρεφές ξέσπασμα του “Holy Ghost Party”, το “His Love” κατεβάζει την ένταση και μεταφέρει το album σε πιο ζεστό, προσωπικό πεδίο. Πρόκειται για devotional soul τραγούδι, όπου η αγάπη του Θεού παρουσιάζεται σαν καταφύγιο και σταθερότητα, όχι σαν αφηρημένη ιδέα. Η ερμηνεία του Finley έχει χώρο να αναπνεύσει· οι λέξεις δεν πιέζονται από ένα υπερφορτωμένο arrangement και έτσι η συναισθηματική αξία έρχεται από την απλότητα. Το κομμάτι λειτουργεί ως ήσυχο κέντρο της A πλευράς, δείχνει ότι ο δίσκος έχει θέση και για την εσωτερική περισυλλογή, όχι μόνο για το revival groove.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο crossover σημείο ανάμεσα σε gospel, funk και soul-blues. Η «βοηθητική χείρα» δεν είναι απλώς θρησκευτική εικόνα· υποδηλώνει αλληλεγγύη, προστασία και πρακτική φροντίδα. Το groove είναι βαθύ, με funk μπάσο που δίνει στο κομμάτι προωθητική δύναμη, ενώ ο Finley τοποθετεί τη φωνή του μέσα στον ρυθμό αντί να στέκεται από πάνω του. Αυτή είναι βασική αρετή του album, η πίστη δεν διατυπώνεται από απόσταση, αλλά κινείται μαζί με την ανθρώπινη καθημερινότητα. Το “Helping Hand” θα μπορούσε να λειτουργήσει και ως soul-funk single χωρίς να χάνει τη spiritual ουσία του.</t>
+  </si>
+  <si>
+    <t>Από τις πιο καθαρές δηλώσεις αντοχής του δίσκου. Το τραγούδι παίρνει τη χαρά όχι ως αφέλεια αλλά ως κάτι που κατακτιέται και υπερασπίζεται απέναντι στη δυσκολία. Το “can’t take” έχει χαρακτήρα αντίστασης, μπορεί να υπάρχουν απώλεια, πόνος και φόβος, αλλά δεν έχουν το δικαίωμα να αφαιρέσουν την εσωτερική δύναμη του αφηγητή. Η gospel-soul φόρμα δίνει στο μήνυμα συλλογική διάσταση, ενώ η φωνή του Finley το γειώνει σε πραγματική εμπειρία. Είναι από τα κομμάτια που αποτυπώνουν καλύτερα γιατί η gospel γλώσσα του Finley λειτουργεί, δεν εξωραΐζει τη ζωή, αλλά επιμένει να βρει χαρά μέσα στην πραγματικότητά της.</t>
+  </si>
+  <si>
+    <t>Η πιο blues-προσανατολισμένη στιγμή του album και, θεματικά, το πιο καθαρό τραγούδι πνευματικής πάλης. Το «πεδίο μάχης» μπορεί να διαβαστεί θρησκευτικά, αλλά και ως εικόνα μιας ζωής με δυσκολίες, πειρασμούς, ταξικές πιέσεις και προσωπικούς αγώνες. Η blues βάση είναι σημαντική επειδή δεν αφήνει το τραγούδι να γίνει απρόσωπος ύμνος, θυμίζει ότι το gospel και το blues μοιράζονται ιστορικά τη γλώσσα της επιβίωσης, της απώλειας και της ελπίδας. Ο Finley προσεγγίζει το θέμα με αποφασιστικότητα, όχι με ηρωική πόζα. Η αίσθηση είναι ότι η μάχη συνεχίζεται, όμως η φωνή έχει ήδη αποφασίσει να μην υποχωρήσει.</t>
+  </si>
+  <si>
+    <t>Το σωστό κλείσιμο, γιατί δεν προσφέρει μια τεράστια τελική λύτρωση αλλά μια διαβεβαίωση, «είμαι μάρτυρας». Το τραγούδι συνοψίζει το πνεύμα του άλμπουμ ως προσωπική αφήγηση πίστης, επιβίωσης και ευγνωμοσύνης. Ο Finley δεν ισχυρίζεται ότι κατέχει όλες τις απαντήσεις· επιβεβαιώνει ότι έχει δει και ζήσει αρκετά ώστε να μιλήσει με πεποίθηση. Η soul πλευρά της σύνθεσης της δίνει μια αίσθηση κλεισίματος που είναι ζεστή και ανθρώπινη, αντί για υπερβολικά θριαμβευτική. Μετά από την ευχαριστία, τη γιορτή, την αγάπη, την αλληλεγγύη και τη μάχη των προηγούμενων τραγουδιών, το “I Am A Witness” αφήνει τον δίσκο να τελειώσει ως κατάθεση ζωής.</t>
+  </si>
+  <si>
+    <t>Gospel, Soul, Blues, R&amp;B [Gospel Soul, Soul Blues, Southern Soul, Gospel-Blues, Funk-infused R&amp;B]</t>
   </si>
 </sst>
 </file>
@@ -10919,12 +11012,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" style="1" customWidth="1"/>
@@ -13907,6 +14000,38 @@
       </c>
       <c r="J93" s="11" t="s">
         <v>3118</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>3155</v>
+      </c>
+      <c r="D94" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E94" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>3184</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>3167</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>3166</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>3165</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>3164</v>
       </c>
     </row>
   </sheetData>
@@ -14092,6 +14217,8 @@
     <hyperlink ref="J92" r:id="rId179" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
     <hyperlink ref="J93" r:id="rId180" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
     <hyperlink ref="I93" r:id="rId181" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
+    <hyperlink ref="J94" r:id="rId182" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
+    <hyperlink ref="I94" r:id="rId183" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14099,7 +14226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I882"/>
+  <dimension ref="A1:I890"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -38054,6 +38181,222 @@
       </c>
       <c r="I882" s="6"/>
     </row>
+    <row r="883" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A883" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B883" s="6">
+        <v>1</v>
+      </c>
+      <c r="C883" s="22" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D883" s="7" t="s">
+        <v>3168</v>
+      </c>
+      <c r="E883" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F883" s="12">
+        <v>4</v>
+      </c>
+      <c r="G883" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H883" s="9" t="s">
+        <v>3176</v>
+      </c>
+      <c r="I883" s="6"/>
+    </row>
+    <row r="884" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A884" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B884" s="6">
+        <v>2</v>
+      </c>
+      <c r="C884" s="22" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D884" s="7" t="s">
+        <v>3169</v>
+      </c>
+      <c r="E884" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F884" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G884" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H884" s="9" t="s">
+        <v>3177</v>
+      </c>
+      <c r="I884" s="6"/>
+    </row>
+    <row r="885" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A885" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B885" s="6">
+        <v>3</v>
+      </c>
+      <c r="C885" s="22" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D885" s="7" t="s">
+        <v>3170</v>
+      </c>
+      <c r="E885" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="F885" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G885" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H885" s="9" t="s">
+        <v>3178</v>
+      </c>
+      <c r="I885" s="6"/>
+    </row>
+    <row r="886" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A886" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B886" s="6">
+        <v>4</v>
+      </c>
+      <c r="C886" s="22" t="s">
+        <v>3159</v>
+      </c>
+      <c r="D886" s="7" t="s">
+        <v>3171</v>
+      </c>
+      <c r="E886" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="F886" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G886" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H886" s="9" t="s">
+        <v>3179</v>
+      </c>
+      <c r="I886" s="6"/>
+    </row>
+    <row r="887" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A887" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B887" s="6">
+        <v>5</v>
+      </c>
+      <c r="C887" s="22" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D887" s="7" t="s">
+        <v>3172</v>
+      </c>
+      <c r="E887" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="F887" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G887" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H887" s="9" t="s">
+        <v>3180</v>
+      </c>
+      <c r="I887" s="6"/>
+    </row>
+    <row r="888" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A888" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B888" s="6">
+        <v>6</v>
+      </c>
+      <c r="C888" s="22" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D888" s="7" t="s">
+        <v>3173</v>
+      </c>
+      <c r="E888" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F888" s="12">
+        <v>4</v>
+      </c>
+      <c r="G888" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H888" s="9" t="s">
+        <v>3181</v>
+      </c>
+      <c r="I888" s="6"/>
+    </row>
+    <row r="889" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A889" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B889" s="6">
+        <v>7</v>
+      </c>
+      <c r="C889" s="22" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D889" s="7" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E889" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F889" s="12">
+        <v>4</v>
+      </c>
+      <c r="G889" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H889" s="9" t="s">
+        <v>3182</v>
+      </c>
+      <c r="I889" s="6"/>
+    </row>
+    <row r="890" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A890" s="6">
+        <v>35342041</v>
+      </c>
+      <c r="B890" s="6">
+        <v>8</v>
+      </c>
+      <c r="C890" s="22" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D890" s="7" t="s">
+        <v>3175</v>
+      </c>
+      <c r="E890" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="F890" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G890" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H890" s="9" t="s">
+        <v>3183</v>
+      </c>
+      <c r="I890" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889BEF53-D9DE-467A-8B78-58B1A8C1F506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812D977A-67FF-4E8D-B606-20D6F961F63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="3185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="3221">
   <si>
     <t>No</t>
   </si>
@@ -10486,6 +10486,114 @@
   </si>
   <si>
     <t>Gospel, Soul, Blues, R&amp;B [Gospel Soul, Soul Blues, Southern Soul, Gospel-Blues, Funk-infused R&amp;B]</t>
+  </si>
+  <si>
+    <t>Toto</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/LJffOobQVupNYYF6yctIDxjZxZvjVn5zbhib0I6Oa6s/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY3NDg5/ODQtMTQyNjEwMzQ1/Ni0zMDA1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/6748984-Toto-Toto</t>
+  </si>
+  <si>
+    <t>CBS – CBS 83148 (UK, 1978, LP, Album, Stereo). Made in England. Label Code: LC 0149.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Original UK pressing with etched runouts. Recorded and engineered by Dana Latham and Gabe Veltri, mixed by Tom Knox. Mastered by Mike Reese and Ron Hitchcock. Produced by the band members themselves, showcasing studio-session elite musicianship (David Paich, Steve Lukather, Jeff Porcaro, Bobby Kimball, Steve Porcaro, David Hungate).</t>
+  </si>
+  <si>
+    <t>Child’s Anthem</t>
+  </si>
+  <si>
+    <t>I’ll Supply the Love</t>
+  </si>
+  <si>
+    <t>Georgy Porgy</t>
+  </si>
+  <si>
+    <t>Manuela Run</t>
+  </si>
+  <si>
+    <t>You Are the Flower</t>
+  </si>
+  <si>
+    <t>Girl Goodbye</t>
+  </si>
+  <si>
+    <t>Takin’ It Back</t>
+  </si>
+  <si>
+    <t>Rockmaker</t>
+  </si>
+  <si>
+    <t>Hold the Line</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>AOR, Pop Rock, Soft Rock, Hard Rock [West Coast Rock, Jazz-Rock, Blue-Eyed Soul, R&amp;B]</t>
+  </si>
+  <si>
+    <t>Rock, Jazz-Rock [Instrumental AOR, Keyboard-led Rock, Fusion touches]</t>
+  </si>
+  <si>
+    <t>Pop Rock, AOR [Soft Rock, West Coast Pop, Yacht Rock-adjacent]</t>
+  </si>
+  <si>
+    <t>R&amp;B, Soul [Philadelphia Soul, Funk Rock, Blue-Eyed Soul]</t>
+  </si>
+  <si>
+    <t>Rock, AOR [Guitar-driven Pop Rock, Jazz-Rock details]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Soul [West Coast Soft Rock, Blue-Eyed Soul, Harmony Pop]</t>
+  </si>
+  <si>
+    <t>Rock, Jazz-Rock [Hard Rock, Progressive Rock elements, Fusion-influenced AOR]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Piano Ballad, West Coast Pop, Singer-Songwriter touch]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Guitar-led Arena Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Arena Rock, Piano Rock, AOR Anthem]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [AOR Ballad, West Coast Pop, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Σύντομο οργανικό άνοιγμα, αλλά όχι απλό intro. Το track τοποθετεί αμέσως την ταυτότητα του Toto ανάμεσα σε studio-rock ακρίβεια, keyboard-led μελωδία και μουσικούς που σκέφτονται σαν session players χωρίς να χάνουν τη δύναμη ενός rock band. Το πιάνο και τα keyboards του David Paich δίνουν την αρχική φανφάρα, ενώ η κιθάρα του Steve Lukather κρατά το κομμάτι σε πιο σκληρό έδαφος. Είναι η σωστή «είσοδος» στον κόσμο του δίσκου: τεχνικό, αλλά σύντομο· polished, αλλά με πραγματικό drive.</t>
+  </si>
+  <si>
+    <t>Μετά το instrumental άνοιγμα, το album περνά σε πιο καθαρό AOR / pop-rock τραγούδι. Η σύνθεση έχει χαρακτηριστικό late-’70s West Coast αέρα: άμεση μελωδία, καθαρή φωνητική γραμμή, ελεγχόμενη κιθαριστική ένταση και παραγωγή που αφήνει κάθε όργανο να ακούγεται με ακρίβεια. Το τραγούδι εκφράζει ερωτική διαθεσιμότητα χωρίς δράμα ή μυστικισμό· ο αφηγητής υπόσχεται αγάπη και σταθερότητα, με μια ελαφρώς «επαγγελματική» αυτοπεποίθηση που ταιριάζει απόλυτα στο στιλ του δίσκου. Δεν έχει το μνημονικό riff του “Hold the Line”, όμως καθιερώνει τη melodic-pop πλευρά των Toto.</t>
+  </si>
+  <si>
+    <t>Η πιο σαφής R&amp;B και soul στιγμή του δίσκου. Το groove του Jeff Porcaro βασίζεται σε λεπτομερές 16th-note feel και ο ίδιος έχει αναφέρει ως αναφορές μουσικούς όπως ο Paul Humphrey, ο Earl Palmer, ο Ed Greene και ο James Gadson. Οι κιθάρες, το μπάσο και τα keyboards δεν πιέζουν το τραγούδι προς hard rock· το αφήνουν να κινείται με άνεση, σχεδόν σαν smooth Philadelphia-soul single. Η συμμετοχή της Cheryl Lynn στο refrain ενισχύει αυτή τη soul αίσθηση. Θεματικά, το “Georgy Porgy” είναι η αφήγηση ενός άνδρα που αποφεύγει τη δέσμευση και παίζει με τις σχέσεις, πάνω σε μουσική τόσο ελκυστική και γυαλιστερή ώστε το ηθικά αμφίσημο περιεχόμενο να ακούγεται σχεδόν ανάλαφρο. Ήταν Top 20 επιτυχία στα αμερικανικά R&amp;B charts, κάτι ασυνήθιστο για λευκή rock μπάντα της περιόδου.</t>
+  </si>
+  <si>
+    <t>Πιο guitar-forward και πιο νευρικό από τα δύο προηγούμενα τραγούδια. Εδώ η μπάντα πλησιάζει περισσότερο στον AOR rock χαρακτήρα που αργότερα θα εξελιχθεί σε βασικό στοιχείο του καταλόγου της. Το “run” του τίτλου δίνει την αίσθηση φυγής και κίνησης, και η μουσική ακολουθεί με σφιχτή ρυθμική βάση και κιθαριστικές αιχμές. Δεν είναι από τα πιο διάσημα τραγούδια του δίσκου, αλλά λειτουργεί ως χρήσιμη αντίθεση μετά τη χαλαρή soul κύλιση του “Georgy Porgy”: υπενθυμίζει ότι οι Toto μπορούν να περάσουν από R&amp;B σε πιο σκληρό rock χωρίς να διαλυθεί η ενότητα της παραγωγής.</t>
+  </si>
+  <si>
+    <t>Η πιο ζεστή και ανοιχτά τρυφερή στιγμή της A πλευράς. Η φωνητική παρουσία του Bobby Kimball και οι αρμονίες μεταφέρουν το τραγούδι σε soft-rock / blue-eyed-soul πεδίο, με την παραγωγή να προτιμά χώρο, μελωδία και χρώμα αντί για επιθετικό riffing. Ο τίτλος χρησιμοποιεί την εικόνα του λουλουδιού ως σύμβολο θαυμασμού και συναισθηματικής αφοσίωσης. Σημαντικό είναι ότι η μπαλάντα δεν γίνεται υπερβολικά γλυκερή: το λεπτομερές rhythm section και η προσεκτική ενορχήστρωση διατηρούν την αίσθηση ότι ακούς μουσικούς με fusion παιδεία να υπηρετούν μια απλή pop σύνθεση.</t>
+  </si>
+  <si>
+    <t>Η πιο φιλόδοξη και από τις πιο δυνατές deep-cut συνθέσεις του album. Με διάρκεια πάνω από έξι λεπτά, είναι ο χώρος όπου η μπάντα αφήνει το hard rock, το progressive rock και το jazz-rock υπόβαθρο των μελών της να συναντηθούν. Το rhythm section του Jeff Porcaro και του David Hungate δεν λειτουργεί απλώς ως συνοδεία: διαμορφώνει διαρκή ένταση και μετακινεί το τραγούδι με ακρίβεια. Η κιθάρα του Lukather έχει μεγαλύτερη ελευθερία, ενώ τα keyboards πυκνώνουν τη σύνθεση χωρίς να την πνίγουν. Ο τίτλος και το refrain χτίζουν μια κλασική rock ιστορία χωρισμού, αλλά το arrangement ξεπερνά εύκολα το επίπεδο ενός συμβατικού breakup song. Είναι το track που αποδεικνύει καλύτερα γιατί το Toto δεν ήταν απλώς ένα συγκρότημα radio hits.</t>
+  </si>
+  <si>
+    <t>Πιο ήρεμο και εσωστρεφές, με lead vocals και σύνθεση από τον Steve Porcaro. Μετά την ένταση του “Girl Goodbye”, λειτουργεί ως αλλαγή θερμοκρασίας: πιάνο, πιο συγκρατημένη ερμηνεία και soft-rock ατμόσφαιρα. Ο τίτλος υποδηλώνει επιστροφή ή αναθεώρηση — μια σχέση ή μια στάση που δεν μπορεί πλέον να υποστηριχθεί — και η μουσική έχει αντίστοιχη αίσθηση απολογισμού. Δεν προσπαθεί να γίνει μεγάλο anthem. Η αξία του βρίσκεται στην οικονομία και στη διαφορετική φωνητική/συνθετική οπτική που προσφέρει μέσα στο album.</t>
+  </si>
+  <si>
+    <t>Το πιο ξεκάθαρα classic / hard-rock κομμάτι της B πλευράς. Με guitar-led δομή και πιο άμεση ένταση, λειτουργεί σαν σύντομη επαναφόρτιση πριν από το μεγάλο single. Ο “rockmaker” του τίτλου είναι σχεδόν meta-φιγούρα: μια αναφορά στη διαδικασία του να δημιουργείς rock μύθο, riffs και σκληρή στάση. Το Toto δεν εγκαταλείπει τη studio finesse, αλλά εδώ τη χρησιμοποιεί για να κάνει το κομμάτι πιο σφιχτό και ακαριαίο. Ακούγεται σαν πρόγευση του arena-rock ύφους που θα ακολουθούσε πιο έντονα στη δεκαετία του 1980.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση και η πιο αναγνωρίσιμη σύνθεση του δίσκου. Το τραγούδι χτίζεται γύρω από ένα από τα αποτελεσματικότερα piano-rock riffs της εποχής, ένα pattern που έχει σχεδόν κρουστική λειτουργία, και πάνω του προστίθενται hard-rock κιθάρες, φωνητικά μεγάλης κλίμακας και η αλάνθαστη drive του Jeff Porcaro. Ο Porcaro περιέγραψε τη συνταγή ως συνδυασμό Sly Stone groove και πιο πρωτόγονης hard-rock κιθαριστικής προσέγγισης. Θεματικά, το “love isn’t always on time” ανατρέπει το ρομαντικό κλισέ: η αγάπη υπάρχει, αλλά το timing, η ετοιμότητα και η πραγματικότητα των σχέσεων μπορεί να την κάνουν αδύνατη. Έφτασε στο Νο. 5 του Billboard Hot 100 και έπαιξε καθοριστικό ρόλο στο να οδηγήσει το album στο Top 10. Δεν είναι απλώς hit· είναι ένα υπόδειγμα AOR songwriting, όπου η pop αμεσότητα και το rock βάρος λειτουργούν ως ένα.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο επιστρέφει στη μαλακότερη, μελωδική πλευρά του δίσκου. Μετά το θριαμβευτικό “Hold the Line”, το “Angela” δεν προσπαθεί να το ανταγωνιστεί — σωστά επιλέγει να λειτουργήσει ως afterglow. Είναι AOR ballad με καθαρό melodic-rock σκελετό, λεπτές harmony κινήσεις και αίσθηση προσωπικής αφιέρωσης. Ως τελευταία πράξη, συνοψίζει μια βασική δύναμη του debut: η μπάντα μπορεί να διασχίσει το σκληρό rock, τη soul, το jazz-rock και το soft pop χωρίς το album να μοιάζει με τυχαία συλλογή ειδών. Το “Angela” κλείνει πιο διακριτικά, αφήνοντας την ακρόαση με μελωδία αντί με επίδειξη.</t>
   </si>
 </sst>
 </file>
@@ -11012,7 +11120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -12820,7 +12928,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>27606564</v>
       </c>
@@ -14032,6 +14140,38 @@
       </c>
       <c r="J94" s="11" t="s">
         <v>3164</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>3185</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>3185</v>
+      </c>
+      <c r="D95" s="6">
+        <v>1978</v>
+      </c>
+      <c r="E95" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>3200</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>3189</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>3188</v>
+      </c>
+      <c r="I95" s="11" t="s">
+        <v>3187</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>3186</v>
       </c>
     </row>
   </sheetData>
@@ -14219,6 +14359,8 @@
     <hyperlink ref="I93" r:id="rId181" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
     <hyperlink ref="J94" r:id="rId182" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
     <hyperlink ref="I94" r:id="rId183" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
+    <hyperlink ref="J95" r:id="rId184" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
+    <hyperlink ref="I95" r:id="rId185" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14226,7 +14368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I890"/>
+  <dimension ref="A1:I900"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -38397,6 +38539,280 @@
       </c>
       <c r="I890" s="6"/>
     </row>
+    <row r="891" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A891" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B891" s="6">
+        <v>1</v>
+      </c>
+      <c r="C891" s="22" t="s">
+        <v>3190</v>
+      </c>
+      <c r="D891" s="7" t="s">
+        <v>3201</v>
+      </c>
+      <c r="E891" s="20">
+        <v>3.79</v>
+      </c>
+      <c r="F891" s="12">
+        <v>4</v>
+      </c>
+      <c r="G891" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H891" s="9" t="s">
+        <v>3211</v>
+      </c>
+      <c r="I891" s="6"/>
+    </row>
+    <row r="892" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A892" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B892" s="6">
+        <v>2</v>
+      </c>
+      <c r="C892" s="22" t="s">
+        <v>3191</v>
+      </c>
+      <c r="D892" s="7" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E892" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F892" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G892" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H892" s="9" t="s">
+        <v>3212</v>
+      </c>
+      <c r="I892" s="6"/>
+    </row>
+    <row r="893" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A893" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B893" s="6">
+        <v>3</v>
+      </c>
+      <c r="C893" s="22" t="s">
+        <v>3192</v>
+      </c>
+      <c r="D893" s="7" t="s">
+        <v>3203</v>
+      </c>
+      <c r="E893" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F893" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G893" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H893" s="9" t="s">
+        <v>3213</v>
+      </c>
+      <c r="I893" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A894" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B894" s="6">
+        <v>4</v>
+      </c>
+      <c r="C894" s="22" t="s">
+        <v>3193</v>
+      </c>
+      <c r="D894" s="7" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E894" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F894" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G894" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H894" s="9" t="s">
+        <v>3214</v>
+      </c>
+      <c r="I894" s="6"/>
+    </row>
+    <row r="895" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A895" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B895" s="6">
+        <v>5</v>
+      </c>
+      <c r="C895" s="22" t="s">
+        <v>3194</v>
+      </c>
+      <c r="D895" s="7" t="s">
+        <v>3205</v>
+      </c>
+      <c r="E895" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F895" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G895" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H895" s="9" t="s">
+        <v>3215</v>
+      </c>
+      <c r="I895" s="6"/>
+    </row>
+    <row r="896" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A896" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B896" s="6">
+        <v>6</v>
+      </c>
+      <c r="C896" s="22" t="s">
+        <v>3195</v>
+      </c>
+      <c r="D896" s="7" t="s">
+        <v>3206</v>
+      </c>
+      <c r="E896" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F896" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G896" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H896" s="9" t="s">
+        <v>3216</v>
+      </c>
+      <c r="I896" s="6"/>
+    </row>
+    <row r="897" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A897" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B897" s="6">
+        <v>7</v>
+      </c>
+      <c r="C897" s="22" t="s">
+        <v>3196</v>
+      </c>
+      <c r="D897" s="7" t="s">
+        <v>3207</v>
+      </c>
+      <c r="E897" s="20">
+        <v>3.58</v>
+      </c>
+      <c r="F897" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G897" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H897" s="9" t="s">
+        <v>3217</v>
+      </c>
+      <c r="I897" s="6"/>
+    </row>
+    <row r="898" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A898" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B898" s="6">
+        <v>8</v>
+      </c>
+      <c r="C898" s="22" t="s">
+        <v>3197</v>
+      </c>
+      <c r="D898" s="7" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E898" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F898" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G898" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H898" s="9" t="s">
+        <v>3218</v>
+      </c>
+      <c r="I898" s="6"/>
+    </row>
+    <row r="899" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A899" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B899" s="6">
+        <v>9</v>
+      </c>
+      <c r="C899" s="22" t="s">
+        <v>3198</v>
+      </c>
+      <c r="D899" s="7" t="s">
+        <v>3209</v>
+      </c>
+      <c r="E899" s="20">
+        <v>4.38</v>
+      </c>
+      <c r="F899" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G899" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H899" s="9" t="s">
+        <v>3219</v>
+      </c>
+      <c r="I899" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="900" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A900" s="6">
+        <v>6748984</v>
+      </c>
+      <c r="B900" s="6">
+        <v>10</v>
+      </c>
+      <c r="C900" s="22" t="s">
+        <v>3199</v>
+      </c>
+      <c r="D900" s="7" t="s">
+        <v>3210</v>
+      </c>
+      <c r="E900" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F900" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G900" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H900" s="9" t="s">
+        <v>3220</v>
+      </c>
+      <c r="I900" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812D977A-67FF-4E8D-B606-20D6F961F63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F8C40B-E8EA-48D4-AF4D-195A8B7E64CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="3254">
   <si>
     <t>No</t>
   </si>
@@ -10594,6 +10594,105 @@
   </si>
   <si>
     <t>Το κλείσιμο επιστρέφει στη μαλακότερη, μελωδική πλευρά του δίσκου. Μετά το θριαμβευτικό “Hold the Line”, το “Angela” δεν προσπαθεί να το ανταγωνιστεί — σωστά επιλέγει να λειτουργήσει ως afterglow. Είναι AOR ballad με καθαρό melodic-rock σκελετό, λεπτές harmony κινήσεις και αίσθηση προσωπικής αφιέρωσης. Ως τελευταία πράξη, συνοψίζει μια βασική δύναμη του debut: η μπάντα μπορεί να διασχίσει το σκληρό rock, τη soul, το jazz-rock και το soft pop χωρίς το album να μοιάζει με τυχαία συλλογή ειδών. Το “Angela” κλείνει πιο διακριτικά, αφήνοντας την ακρόαση με μελωδία αντί με επίδειξη.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1939062-Yellow-Dog-Yellow-Dog</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/GgBIm4DYyFK_BuLH9nRzD9Eb7MhZeiaTnMeqf2dmyV8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE5Mzkw/NjItMTQ1MjYzMjY1/Ny0xMDQwLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Yellow Dog</t>
+  </si>
+  <si>
+    <t>Virgin – V 2083 (UK, 1977, LP, Album, Stereo). Made in England on labels. Printed by Robor Ltd.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:**Recorded at Lazy Sounds, featuring core members Kenny Young and Herbie Armstrong alongside guest session musicians like Jim Horn, Pete Solley, and Gerry Conway. Comes with a lyrics insert. Made in England, on labels.</t>
+  </si>
+  <si>
+    <t>Stood Up</t>
+  </si>
+  <si>
+    <t>Gypsy Soul</t>
+  </si>
+  <si>
+    <t>The Green Lizard</t>
+  </si>
+  <si>
+    <t>Flash Gordon</t>
+  </si>
+  <si>
+    <t>Indian Summer Rain</t>
+  </si>
+  <si>
+    <t>My Lady</t>
+  </si>
+  <si>
+    <t>City Bird</t>
+  </si>
+  <si>
+    <t>For Whatever It’s Worth</t>
+  </si>
+  <si>
+    <t>Nobody Got So Much Soul</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soft Rock [British Pop Rock, Glam-Pop roots, Pub Rock, Soul-R&amp;B touches]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Rock ’n’ Roll [Brisk British pop-rock, retro rock ’n’ roll]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soul [Blue-eyed soul, melodic soft rock, late-’70s radio pop]</t>
+  </si>
+  <si>
+    <t>Rock, Pop Rock [Eccentric art-pop, glam-pop, guitar-led British rock]</t>
+  </si>
+  <si>
+    <t>Rock, Pop Rock [Theatrical pop rock, glam-rock residue, sci-fi character song]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Melodic soft rock, harmony pop, West Coast-inflected pop]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soul [Blue-eyed soul, romantic soft rock, harmony-led pop]</t>
+  </si>
+  <si>
+    <t>Rock, Pop Rock [Atmospheric pop rock, art-rock coloration, late-’70s British rock]</t>
+  </si>
+  <si>
+    <t>Soul, Pop Rock [Blue-eyed soul, R&amp;B-pop, upbeat rock-soul]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Pop Rock [Reflective melodic rock, harmony pop, singer-songwriter pop]</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με ένα άμεσο romantic pop-rock τραγούδι. Ο τίτλος υπόσχεται προσωπική αφιέρωση και το κομμάτι μένει σε πιο οικείο, blue-eyed-soul / soft-rock έδαφος. Δεν επιδιώκει την ιδιορρυθμία του “The Green Lizard” ούτε την έκταση του “Flash Gordon”. Αντίθετα, επιλέγει καθαρή songcraft δομή, ζεστές φωνητικές γραμμές και προσβασιμότητα. Είναι λειτουργικό στο sequence, αλλά λιγότερο διακριτό από τα tracks με πιο έντονη προσωπικότητα.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με σύντομο, άμεσο pop-rock momentum. Ο τίτλος παραπέμπει στο κλασικό rock ’n’ roll μοτίβο της ερωτικής απογοήτευσης , κάποιος σε αφήνει να περιμένεις, δεν εμφανίζεται, σε «στήνει» , και το κομμάτι αξιοποιεί αυτή την καθημερινή ιστορία χωρίς μεγάλη δραματοποίηση. Η αξία του βρίσκεται στην οικονομία, γρήγορη είσοδος, καθαρό hook και μια ρετρό rock ’n’ roll ενέργεια που συνδέει τη μπάντα με την προ-punk βρετανική pop-rock παράδοση. Είναι περισσότερο σκηνικό άνοιγμα παρά καθοριστική καλλιτεχνική δήλωση, αλλά θέτει σωστά τον φωτεινό και melody-first τόνο του LP.</t>
+  </si>
+  <si>
+    <t>Πιο ανοιχτό και μελωδικό, με τίτλο που συνδέει την εικόνα της περιπλάνησης με μια «ελεύθερη ψυχή». Το “Gypsy Soul” μετακινεί το album από το καθαρό rock ’n’ roll προς blue-eyed soul και polished late-’70s pop. Ο ρυθμός παραμένει ελαφρύς, όμως η ερμηνεία και το arrangement αφήνουν περισσότερο χώρο σε αρμονίες και σε πιο ομαλή, ραδιοφωνική μελωδία. Δεν χρειάζεται να ακούγεται σαν αυθεντικό soul για να λειτουργήσει, η χρήση της soul χροιάς εδώ υπηρετεί την τρυφερότητα και τη ρομαντική αίσθηση του τραγουδιού.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο παράξενα, εικονοκεντρικά τραγούδια του δίσκου, ήδη από τον τίτλο του. Η «πράσινη σαύρα» λειτουργεί ως pop-art ή character-song εικόνα, ταιριαστή με τη glam-pop κληρονομιά της μπάντας. Το κομμάτι έχει πιο eccentric γωνίες από τα προηγούμενα, κιθαριστική κίνηση, θεατρικότητα και μια ελαφρά art-pop διάθεση που εμποδίζει το album να περιοριστεί σε εύκολα soft-rock hooks. Στην A πλευρά είναι μια χρήσιμη αλλαγή χρώματος, γιατί φέρνει χιούμορ και ιδιορρυθμία εκεί όπου το “Gypsy Soul” είχε προσφέρει ρομαντική ομαλότητα.</t>
+  </si>
+  <si>
+    <t>Το μεγαλύτερο track της A πλευράς και η πιο εμφανώς θεατρική pop-rock στιγμή του album. Η αναφορά στον Flash Gordon ενεργοποιεί την pulp sci-fi και comic-strip φαντασία, ήρωας, διαστημική περιπέτεια, υπερβολή και camp glamour. Η μπάντα έχει τον χώρο να χτίσει πιο εκτεταμένη δομή από ένα τυπικό τρίλεπτο single, διατηρώντας όμως τη μελωδική προσβασιμότητα. Είναι το σημείο όπου η προέλευση του Yellow Dog από τους Fox φαίνεται πιο έντονα, βρετανική pop με αφηγηματική φαντασία, όχι σύγχρονο punk realism. Ως centerpiece, δικαιολογεί το ελαφρώς υψηλότερο score του πίνακα.</t>
+  </si>
+  <si>
+    <t>Με το τέλος της A πλευράς, το album παίρνει πιο ήπιο, ατμοσφαιρικό χαρακτήρα. Η «καλοκαιρινή βροχή» είναι από μόνη της εικόνα νοσταλγίας και παροδικότητας, ζεστασιά, αλλαγή εποχής και κάτι όμορφο που δεν κρατά. Η σύνθεση έχει soft-rock και harmony-pop λογική, με πιο ήρεμη ρυθμική πίεση και έμφαση στη μελωδία. Λειτουργεί σαν ανάσα μετά την εξωστρέφεια του “Flash Gordon”, και ως κλείσιμο της πλευράς δημιουργεί αίσθηση ήρεμης, ελαφρά μελαγχολικής απομάκρυνσης.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο κινηματογραφική και ατμοσφαιρική εικόνα. Το “City Bird” υποδηλώνει έναν παρατηρητή που κινείται ή πετά πάνω από την πόλη , ελευθερία, μοναξιά ή αστική απόσταση , και η μουσική έχει χώρο για πιο ανοιχτή pop-rock ανάπτυξη. Ως μία από τις μεγαλύτερες συνθέσεις του δίσκου, λειτουργεί σαν B-side counterpart του “Flash Gordon”, λιγότερο camp και πιο ατμοσφαιρικό, με art-pop χρωματισμό. Δείχνει ότι η μπάντα είχε ενδιαφέρον για εικόνες και αφηγήσεις πέρα από τις συμβατικές ερωτικές pop φόρμες.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο soul statement του τίτλου και από τις πιο ενεργητικές στιγμές του δίσκου. Η φράση δεν χρειάζεται να ληφθεί κυριολεκτικά· είναι μια καυχησιολογική, celebratory pop-soul χειρονομία. Το groove, οι φωνητικές αρμονίες και το ρυθμικό drive συνδέουν το τραγούδι με blue-eyed soul και R&amp;B-pop παράδοση, ενώ το rock πλαίσιο το εμποδίζει να γίνει υπερβολικά smooth. Είναι αποτελεσματικό επειδή η μπάντα δεν «παριστάνει» soul act, χρησιμοποιεί τη soul ενέργεια ως ένα ακόμη εργαλείο μέσα σε ένα πολύ βρετανικό pop-rock πλαίσιο.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο επιλέγει πιο ήπια, αναστοχαστική μελωδική διάθεση αντί για μεγάλο φινάλε. Ο τίτλος υποδηλώνει κάτι που λέγεται με επιφύλαξη , «για ό,τι αξίζει» , και αυτή η αμφιβολία ταιριάζει με τον πιο συγκρατημένο soft-rock χαρακτήρα του τραγουδιού. Ως album closer, δεν επιδιώκει θεαματική κορύφωση· αφήνει την μπάντα να φύγει με αρμονίες και μελωδία. Αυτό είναι αντιπροσωπευτικό του δίσκου συνολικά, ένα pop-rock album όπου η λεπτομέρεια του τραγουδιού και η ευκολία της ερμηνείας έχουν μεγαλύτερη σημασία από την επιθετικότητα ή την πρωτοπορία.</t>
   </si>
 </sst>
 </file>
@@ -11120,7 +11219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14172,6 +14271,38 @@
       </c>
       <c r="J95" s="11" t="s">
         <v>3186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>3223</v>
+      </c>
+      <c r="D96" s="6">
+        <v>1977</v>
+      </c>
+      <c r="E96" s="10">
+        <v>3.21</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>3235</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>3225</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>3224</v>
+      </c>
+      <c r="I96" s="11" t="s">
+        <v>3221</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>3222</v>
       </c>
     </row>
   </sheetData>
@@ -14361,6 +14492,8 @@
     <hyperlink ref="I94" r:id="rId183" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
     <hyperlink ref="J95" r:id="rId184" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
     <hyperlink ref="I95" r:id="rId185" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
+    <hyperlink ref="I96" r:id="rId186" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
+    <hyperlink ref="J96" r:id="rId187" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14368,7 +14501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I900"/>
+  <dimension ref="A1:I909"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -38813,6 +38946,251 @@
       </c>
       <c r="I900" s="6"/>
     </row>
+    <row r="901" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A901" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B901" s="6">
+        <v>1</v>
+      </c>
+      <c r="C901" s="22" t="s">
+        <v>3226</v>
+      </c>
+      <c r="D901" s="7" t="s">
+        <v>3236</v>
+      </c>
+      <c r="E901" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F901" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G901" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H901" s="9" t="s">
+        <v>3246</v>
+      </c>
+      <c r="I901" s="6"/>
+    </row>
+    <row r="902" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A902" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B902" s="6">
+        <v>2</v>
+      </c>
+      <c r="C902" s="22" t="s">
+        <v>3227</v>
+      </c>
+      <c r="D902" s="7" t="s">
+        <v>3237</v>
+      </c>
+      <c r="E902" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F902" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G902" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H902" s="9" t="s">
+        <v>3247</v>
+      </c>
+      <c r="I902" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="903" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A903" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B903" s="6">
+        <v>3</v>
+      </c>
+      <c r="C903" s="22" t="s">
+        <v>3228</v>
+      </c>
+      <c r="D903" s="7" t="s">
+        <v>3238</v>
+      </c>
+      <c r="E903" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F903" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G903" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H903" s="9" t="s">
+        <v>3248</v>
+      </c>
+      <c r="I903" s="6"/>
+    </row>
+    <row r="904" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A904" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B904" s="6">
+        <v>4</v>
+      </c>
+      <c r="C904" s="22" t="s">
+        <v>3229</v>
+      </c>
+      <c r="D904" s="7" t="s">
+        <v>3239</v>
+      </c>
+      <c r="E904" s="20">
+        <v>3.24</v>
+      </c>
+      <c r="F904" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G904" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H904" s="9" t="s">
+        <v>3249</v>
+      </c>
+      <c r="I904" s="6"/>
+    </row>
+    <row r="905" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A905" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B905" s="6">
+        <v>5</v>
+      </c>
+      <c r="C905" s="22" t="s">
+        <v>3230</v>
+      </c>
+      <c r="D905" s="7" t="s">
+        <v>3240</v>
+      </c>
+      <c r="E905" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F905" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G905" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H905" s="9" t="s">
+        <v>3250</v>
+      </c>
+      <c r="I905" s="6"/>
+    </row>
+    <row r="906" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A906" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B906" s="6">
+        <v>6</v>
+      </c>
+      <c r="C906" s="22" t="s">
+        <v>3231</v>
+      </c>
+      <c r="D906" s="7" t="s">
+        <v>3241</v>
+      </c>
+      <c r="E906" s="20">
+        <v>2.71</v>
+      </c>
+      <c r="F906" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G906" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H906" s="9" t="s">
+        <v>3245</v>
+      </c>
+      <c r="I906" s="6"/>
+    </row>
+    <row r="907" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A907" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B907" s="6">
+        <v>7</v>
+      </c>
+      <c r="C907" s="22" t="s">
+        <v>3232</v>
+      </c>
+      <c r="D907" s="7" t="s">
+        <v>3242</v>
+      </c>
+      <c r="E907" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F907" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G907" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H907" s="9" t="s">
+        <v>3251</v>
+      </c>
+      <c r="I907" s="6"/>
+    </row>
+    <row r="908" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A908" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B908" s="6">
+        <v>8</v>
+      </c>
+      <c r="C908" s="22" t="s">
+        <v>3234</v>
+      </c>
+      <c r="D908" s="7" t="s">
+        <v>3243</v>
+      </c>
+      <c r="E908" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F908" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G908" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H908" s="9" t="s">
+        <v>3252</v>
+      </c>
+      <c r="I908" s="6"/>
+    </row>
+    <row r="909" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A909" s="6">
+        <v>1939062</v>
+      </c>
+      <c r="B909" s="6">
+        <v>9</v>
+      </c>
+      <c r="C909" s="22" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D909" s="7" t="s">
+        <v>3244</v>
+      </c>
+      <c r="E909" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F909" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G909" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="H909" s="9" t="s">
+        <v>3253</v>
+      </c>
+      <c r="I909" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F8C40B-E8EA-48D4-AF4D-195A8B7E64CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328CFFEA-B042-464D-AB6E-93403CC6632F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="3254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3559" uniqueCount="3287">
   <si>
     <t>No</t>
   </si>
@@ -10693,6 +10693,105 @@
   </si>
   <si>
     <t>Το κλείσιμο επιλέγει πιο ήπια, αναστοχαστική μελωδική διάθεση αντί για μεγάλο φινάλε. Ο τίτλος υποδηλώνει κάτι που λέγεται με επιφύλαξη , «για ό,τι αξίζει» , και αυτή η αμφιβολία ταιριάζει με τον πιο συγκρατημένο soft-rock χαρακτήρα του τραγουδιού. Ως album closer, δεν επιδιώκει θεαματική κορύφωση· αφήνει την μπάντα να φύγει με αρμονίες και μελωδία. Αυτό είναι αντιπροσωπευτικό του δίσκου συνολικά, ένα pop-rock album όπου η λεπτομέρεια του τραγουδιού και η ευκολία της ερμηνείας έχουν μεγαλύτερη σημασία από την επιθετικότητα ή την πρωτοπορία.</t>
+  </si>
+  <si>
+    <t>Black Tiger</t>
+  </si>
+  <si>
+    <t>Y &amp; T</t>
+  </si>
+  <si>
+    <t>A&amp;M Records – SP-4910 (US, 1982, LP, Album, Stereo, Monarch pressing). "C" printed on labels left of A&amp;M logo, denoting a pressing variant by Monarch Record Mfg. Co.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/12520978-Y-T-Black-Tiger</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/V2pIcog7w1t_J5eH06pJZfInPNnu4Yn54PgP6Q4QEG4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEyNTIw/OTc4LTE1ODA0Mjky/NTctNzc4Ny5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded at Ridge Farm Studios, mixed at Ridge Farm Studios and Record Plant, Los Angeles. Produced and engineered by Max Norman. Features cover illustration by John Taylor DisMukes and art direction by Chuck Beeson.</t>
+  </si>
+  <si>
+    <t>From the Moon</t>
+  </si>
+  <si>
+    <t>Open Fire</t>
+  </si>
+  <si>
+    <t>Winds of Change</t>
+  </si>
+  <si>
+    <t>My Way or the Highway</t>
+  </si>
+  <si>
+    <t>Forever</t>
+  </si>
+  <si>
+    <t>Barroom Boogie</t>
+  </si>
+  <si>
+    <t>Hell or High Water</t>
+  </si>
+  <si>
+    <t>Don’t Wanna Lose</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Hard Rock, Arena Rock, Early ’80s American Metal]</t>
+  </si>
+  <si>
+    <t>Rock, Instrumental Rock [Atmospheric Intro, Guitar Instrumental, Space-Rock touch]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fast Melodic Metal, Guitar-driven Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Melodic Hard Rock, Radio Rock, AOR edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock [Mid-tempo Melodic Hard Rock, Blues-Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Arena Ballad, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Classic Heavy Metal, Guitar-driven Arena Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Boogie Rock, Blues-Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Driving Melodic Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Dramatic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental άνοιγμα που λειτουργεί σαν κινηματογραφική προετοιμασία πριν από την έκρηξη του “Open Fire”. Δεν είναι πλήρες τραγούδι με verse/chorus δομή, αλλά χτίζει ατμόσφαιρα μέσα από κιθάρα και space-like αίσθηση. Η εικόνα της σελήνης δίνει μια νυχτερινή, σχεδόν κοσμική εισαγωγή, όμως η λειτουργία του είναι κυρίως πρακτική: ανεβάζει την αναμονή και εισάγει τον ακροατή στον μεγάλο, θεατρικό hard-rock ήχο των Y&amp;T. Ως αυτόνομη σύνθεση είναι περιορισμένο, ως album opener όμως είναι αποτελεσματικό.</t>
+  </si>
+  <si>
+    <t>Η πρώτη μεγάλη κορύφωση. Γρήγορο, επιθετικό και κιθαριστικά πυκνό, το “Open Fire” δείχνει τους Y&amp;T στο σημείο όπου το hard rock αγγίζει το heavy metal χωρίς να χάνει το refrain. Τα riffs έχουν ταχύτητα και βάρος, ενώ η φωνή του Dave Meniketti κρατά το τραγούδι μελωδικό αντί να το αφήσει να γίνει απλό speed-metal ξέσπασμα. Η σύνθεση είναι φτιαγμένη για live εκτέλεση: άμεση είσοδος, υψηλή ενέργεια και riff που μένει. Δικαίως θεωρείται ένα από τα βασικά highlights του album και μία από τις πιο δυνατές στιγμές του πρώιμου καταλόγου τους.</t>
+  </si>
+  <si>
+    <t>Πιο προσβάσιμο και radio-oriented από το “Open Fire”, με μελωδικό hard-rock σκελετό και πιο καθαρή εμπορική στόχευση. Το θέμα είναι η αγωνία της απώλειας μιας σχέσης, όμως η μπάντα το μετατρέπει σε δυναμικό arena-rock τραγούδι αντί για ήσυχη μπαλάντα. Οι κιθάρες παραμένουν παρούσες, αλλά η σύνθεση βασίζεται περισσότερο στο chorus και στην άμεση αναγνωρισιμότητα. Είναι σημαντικό για την ισορροπία της A πλευράς: μετά την επίθεση του opener, προσφέρει melodic relief χωρίς να χαμηλώνει υπερβολικά την ένταση.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, δραματικό φινάλε. Το τραγούδι χρησιμοποιεί την εικόνα των «ανέμων της αλλαγής» για να μιλήσει για μετάβαση, αβεβαιότητα και συναισθηματική αναζήτηση. Η σύνθεση ξεκινά σε πιο μελωδικό, power-ballad πεδίο και αποκτά σταδιακά arena-rock διάσταση, με το refrain να ανοίγει τον ήχο. Η κιθάρα δεν λειτουργεί μόνο ως επίδειξη τεχνικής· ενισχύει την αίσθηση κορύφωσης και αφήνει την τελευταία εντύπωση να είναι επική, όχι απλώς βαριά. Μαζί με τα “Forever” και “Open Fire”, είναι το τραγούδι που αντιπροσωπεύει καλύτερα τη διπλή ταυτότητα των Y&amp;T: hard rock δύναμη και μελωδικό συναίσθημα.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στο driving hard rock, με τίτλο που δηλώνει αδιαπραγμάτευτη στάση: ή ακολουθείς τον δρόμο μου ή φεύγεις. Το riffing είναι πιο ευθύ και αποφασιστικό, με έμφαση στο momentum και όχι σε περίπλοκες μεταβάσεις. Η μπάντα κρατά τη μελωδικότητα του AOR, αλλά η κιθάρα και τα drums δίνουν αρκετή πίεση ώστε το track να παραμένει στο heavy side του album. Δεν έχει τον ιδιαίτερο χαρακτήρα του title track, όμως λειτουργεί ως δυναμικό bridge πριν από το δραματικό κλείσιμο.</t>
+  </si>
+  <si>
+    <t>Η πιο χαλαρή και party-oriented στιγμή του album. Το boogie riff και η εικόνα του barroom μεταφέρουν το τραγούδι σε blues-rock και rock ’n’ roll έδαφος, μακριά από τη δραματικότητα των power ballads. Οι Y&amp;T ακούγονται σαν μπάντα που παίζει για το κοινό της χωρίς να χρειάζεται μεγάλο concept: groove, ποτό, θόρυβος και άμεση διασκέδαση. Αυτή η αλλαγή είναι χρήσιμη στη σειρά, αλλά ως σύνθεση έχει μικρότερο βάρος από τα βασικά highlights. Η κριτική του Louder Sound το αναγνωρίζει ως τη «boozy» και rowdy πλευρά του δίσκου.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τη δεύτερη πλευρά με αποφασιστικότητα και επιστρέφει στον βαρύτερο πυρήνα του δίσκου. Ο “black tiger” είναι εικόνα δύναμης, κινδύνου και ελεγχόμενης αγριότητας, και η μουσική ανταποκρίνεται με κλασικό heavy-metal riffing και δυναμικό chorus. Δεν είναι ακραίο metal· είναι η αμερικανική, μελωδική εκδοχή του heavy ήχου, με καθαρή παραγωγή και έμφαση στο hook. Η σύνθεση έχει μεγαλύτερη ταυτότητα από ένα απλό album filler και μαζί με το “Open Fire” αποτελεί τον μεταλλικό άξονα του LP.</t>
+  </si>
+  <si>
+    <t>Mid-tempo hard rock με πιο «πηδηχτό» riff και έντονο shout-along χαρακτήρα. Η φράση “hell or high water” σημαίνει αποφασιστικότητα απέναντι σε κάθε εμπόδιο, και το τραγούδι υιοθετεί ακριβώς αυτή τη στάση: όχι σκοτεινό metal, αλλά επίμονο, forward-moving rock. Το κιθαριστικό solo προσθέτει την απαραίτητη έκρηξη, ενώ το refrain έχει σχεδιαστεί για να επιστρέφει εύκολα σε live περιβάλλον. Δεν είναι τόσο γρήγορο όσο το “Open Fire” ούτε τόσο συναισθηματικό όσο το “Forever”, όμως λειτουργεί ως σταθερό κεντρικό κομμάτι της πλευράς.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη power ballad της A πλευράς και ένα από τα πιο μελωδικά τραγούδια του δίσκου. Το “Forever” χρησιμοποιεί την υπόσχεση αιώνιας αγάπης ως κλασικό arena-rock θέμα, αλλά η ερμηνεία του Meniketti δίνει περισσότερη ευαισθησία από μια απλή glam-metal μπαλάντα. Η κιθάρα και το rhythm section κρατούν το τραγούδι δεμένο με το hard-rock σώμα των Y&amp;T, ενώ η ανάπτυξη προς το refrain προσφέρει την αναμενόμενη συναισθηματική κορύφωση. Είναι από τα tracks που εξηγούν γιατί το album μπορεί να λειτουργήσει και έξω από το καθαρά metal κοινό. Το Metal Kingdom το καταγράφει ως ένα από τα κορυφαία τραγούδια των Y&amp;T.</t>
   </si>
 </sst>
 </file>
@@ -11219,7 +11318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14303,6 +14402,38 @@
       </c>
       <c r="J96" s="11" t="s">
         <v>3222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>3254</v>
+      </c>
+      <c r="D97" s="6">
+        <v>1982</v>
+      </c>
+      <c r="E97" s="10">
+        <v>3.57</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>3268</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>3259</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>3256</v>
+      </c>
+      <c r="I97" s="11" t="s">
+        <v>3257</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>3258</v>
       </c>
     </row>
   </sheetData>
@@ -14494,6 +14625,8 @@
     <hyperlink ref="I95" r:id="rId185" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
     <hyperlink ref="I96" r:id="rId186" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
     <hyperlink ref="J96" r:id="rId187" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
+    <hyperlink ref="I97" r:id="rId188" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
+    <hyperlink ref="J97" r:id="rId189" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14501,7 +14634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I909"/>
+  <dimension ref="A1:I918"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -39191,6 +39324,251 @@
       </c>
       <c r="I909" s="6"/>
     </row>
+    <row r="910" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A910" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B910" s="6">
+        <v>1</v>
+      </c>
+      <c r="C910" s="22" t="s">
+        <v>3260</v>
+      </c>
+      <c r="D910" s="7" t="s">
+        <v>3269</v>
+      </c>
+      <c r="E910" s="20">
+        <v>3.28</v>
+      </c>
+      <c r="F910" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G910" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H910" s="9" t="s">
+        <v>3278</v>
+      </c>
+      <c r="I910" s="6"/>
+    </row>
+    <row r="911" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A911" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B911" s="6">
+        <v>2</v>
+      </c>
+      <c r="C911" s="22" t="s">
+        <v>3261</v>
+      </c>
+      <c r="D911" s="7" t="s">
+        <v>3270</v>
+      </c>
+      <c r="E911" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F911" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G911" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H911" s="9" t="s">
+        <v>3279</v>
+      </c>
+      <c r="I911" s="6"/>
+    </row>
+    <row r="912" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A912" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B912" s="6">
+        <v>3</v>
+      </c>
+      <c r="C912" s="22" t="s">
+        <v>3267</v>
+      </c>
+      <c r="D912" s="7" t="s">
+        <v>3271</v>
+      </c>
+      <c r="E912" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F912" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G912" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H912" s="9" t="s">
+        <v>3280</v>
+      </c>
+      <c r="I912" s="6"/>
+    </row>
+    <row r="913" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A913" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B913" s="6">
+        <v>4</v>
+      </c>
+      <c r="C913" s="22" t="s">
+        <v>3266</v>
+      </c>
+      <c r="D913" s="7" t="s">
+        <v>3272</v>
+      </c>
+      <c r="E913" s="20">
+        <v>3.22</v>
+      </c>
+      <c r="F913" s="12">
+        <v>4</v>
+      </c>
+      <c r="G913" s="12">
+        <v>4</v>
+      </c>
+      <c r="H913" s="9" t="s">
+        <v>3285</v>
+      </c>
+      <c r="I913" s="6"/>
+    </row>
+    <row r="914" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A914" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B914" s="6">
+        <v>5</v>
+      </c>
+      <c r="C914" s="22" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D914" s="7" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E914" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F914" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G914" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H914" s="9" t="s">
+        <v>3286</v>
+      </c>
+      <c r="I914" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A915" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B915" s="6">
+        <v>6</v>
+      </c>
+      <c r="C915" s="22" t="s">
+        <v>3254</v>
+      </c>
+      <c r="D915" s="7" t="s">
+        <v>3274</v>
+      </c>
+      <c r="E915" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F915" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G915" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H915" s="9" t="s">
+        <v>3284</v>
+      </c>
+      <c r="I915" s="6"/>
+    </row>
+    <row r="916" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A916" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B916" s="6">
+        <v>7</v>
+      </c>
+      <c r="C916" s="22" t="s">
+        <v>3265</v>
+      </c>
+      <c r="D916" s="7" t="s">
+        <v>3275</v>
+      </c>
+      <c r="E916" s="20">
+        <v>3.33</v>
+      </c>
+      <c r="F916" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G916" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H916" s="9" t="s">
+        <v>3283</v>
+      </c>
+      <c r="I916" s="6"/>
+    </row>
+    <row r="917" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A917" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B917" s="6">
+        <v>8</v>
+      </c>
+      <c r="C917" s="22" t="s">
+        <v>3263</v>
+      </c>
+      <c r="D917" s="7" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E917" s="20">
+        <v>3.19</v>
+      </c>
+      <c r="F917" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G917" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H917" s="9" t="s">
+        <v>3282</v>
+      </c>
+      <c r="I917" s="6"/>
+    </row>
+    <row r="918" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A918" s="6">
+        <v>12520978</v>
+      </c>
+      <c r="B918" s="6">
+        <v>9</v>
+      </c>
+      <c r="C918" s="22" t="s">
+        <v>3262</v>
+      </c>
+      <c r="D918" s="7" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E918" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F918" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G918" s="12">
+        <v>4</v>
+      </c>
+      <c r="H918" s="9" t="s">
+        <v>3281</v>
+      </c>
+      <c r="I918" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328CFFEA-B042-464D-AB6E-93403CC6632F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00919DF-4129-4600-8954-B65D23179477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3559" uniqueCount="3287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="3363">
   <si>
     <t>No</t>
   </si>
@@ -10792,6 +10792,234 @@
   </si>
   <si>
     <t>Η μεγάλη power ballad της A πλευράς και ένα από τα πιο μελωδικά τραγούδια του δίσκου. Το “Forever” χρησιμοποιεί την υπόσχεση αιώνιας αγάπης ως κλασικό arena-rock θέμα, αλλά η ερμηνεία του Meniketti δίνει περισσότερη ευαισθησία από μια απλή glam-metal μπαλάντα. Η κιθάρα και το rhythm section κρατούν το τραγούδι δεμένο με το hard-rock σώμα των Y&amp;T, ενώ η ανάπτυξη προς το refrain προσφέρει την αναμενόμενη συναισθηματική κορύφωση. Είναι από τα tracks που εξηγούν γιατί το album μπορεί να λειτουργήσει και έξω από το καθαρά metal κοινό. Το Metal Kingdom το καταγράφει ως ένα από τα κορυφαία τραγούδια των Y&amp;T.</t>
+  </si>
+  <si>
+    <t>Skid Row</t>
+  </si>
+  <si>
+    <t>Big Guns</t>
+  </si>
+  <si>
+    <t>Sweet Little Sister</t>
+  </si>
+  <si>
+    <t>Can’t Stand the Heartache</t>
+  </si>
+  <si>
+    <t>Piece of Me</t>
+  </si>
+  <si>
+    <t>18 and Life</t>
+  </si>
+  <si>
+    <t>Rattlesnake Shake</t>
+  </si>
+  <si>
+    <t>Youth Gone Wild</t>
+  </si>
+  <si>
+    <t>Here I Am</t>
+  </si>
+  <si>
+    <t>Makin’ a Mess</t>
+  </si>
+  <si>
+    <t>I Remember You</t>
+  </si>
+  <si>
+    <t>Midnight / Tornado</t>
+  </si>
+  <si>
+    <t>Atlantic – 781936-1 (Greece, 1989, LP, Album, Stereo). Manufactured by G.P.I. S.A. Printed by Ορφανός - Σκαλτσάς. Lacquer Cut At G.P.I. S.A. – W706. Record Company: WEA Records S.A.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Produced, recorded &amp; mixed for Double Trouble Productions Inc. by Michael Wagener. Includes a double-sided insert. Rights Society: AEPI. Barcode: 0 7567-81936-1 3.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2782114-Skid-Row-Skid-Row</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qWpBh-Vik26adyYR-DD7nyEkr-N42E12XGqYk_d0O2k/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTU2ODU5/MC0xMzIxMTU3MDQ1/LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Heavy Glam Metal, Sleaze Metal, Arena Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Metal, Heavy Opener, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Sleaze Rock, Up-tempo Hair Metal, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Melodic Hard Rock, Relationship Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Aggressive Sleaze Metal, Punky Hard Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Power Ballad, Narrative Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Bluesy Sleaze Rock, Boogie Metal]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Arena Metal, Anthemic Sleaze Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Melodic Arena Rock, Hair Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Fast Sleaze Rock, Punk-influenced Metal]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Soft Rock [Power Ballad, Melodic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Heavy Rock, Dramatic Album Closer]</t>
+  </si>
+  <si>
+    <t>Γρήγορο, swaggering και πιο καθαρά hair-metal, με έμφαση στη ρυθμική κίνηση και στο άμεσο hook. Η αντίθεση ανάμεσα στο “sweet” και στο “sister” δημιουργεί έναν χαρακτήρα που φαίνεται αθώος μόνο επιφανειακά· η μουσική υποδηλώνει πείρα, πρόκληση και party-rock διάθεση. Οι κιθάρες κινούνται με άνεση ανάμεσα σε riff και refrain, ενώ ο Bach προσθέτει υπερβολή χωρίς να χάνει τον έλεγχο. Είναι από τα τραγούδια που υπηρετούν το glam περιβάλλον της εποχής περισσότερο από τα κοινωνικά ή δραματικά κομμάτια του album, αλλά το κάνει με ενέργεια και επαγγελματισμό.</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό και λιγότερο επιθετικό, με θέμα την εξάντληση που προκαλεί ένας επώδυνος χωρισμός ή μια σχέση που δεν μπορεί πλέον να συνεχιστεί. Οι κιθάρες κρατούν το τραγούδι σε hard-rock έδαφος, όμως το βάρος πέφτει περισσότερο στη φωνητική μελωδία και στο συναίσθημα. Ο Bach δεν χρειάζεται εδώ να ουρλιάζει σε κάθε φράση· η ένταση έρχεται από το refrain και από την αίσθηση ότι η αντοχή έχει τελειώσει. Είναι σταθερό album track, αλλά όχι τόσο ιδιαίτερο όσο τα κομμάτια όπου η μπάντα συνδυάζει κοινωνικό περιεχόμενο με πραγματικά βαριά μουσική.</t>
+  </si>
+  <si>
+    <t>Από τα πιο επιθετικά κομμάτια της A πλευράς. Ο τίτλος και το riffing παραπέμπουν σε μια σχέση σύγκρουσης, όπου ο αφηγητής αρνείται να προσφέρει άλλο κομμάτι του εαυτού του σε κάποιον που απαιτεί ή εκμεταλλεύεται. Η κιθάρα έχει πιο punky, κοφτή αίσθηση, ενώ ο ρυθμός είναι αρκετά γρήγορος ώστε το τραγούδι να ξεφεύγει από τη συμβατική power-pop πλευρά του glam metal. Ο Bach ακούγεται ιδιαίτερα άγριος, σχεδόν προκλητικός, και αυτό δίνει στο track περισσότερο χαρακτήρα από ένα συνηθισμένο party anthem.</t>
+  </si>
+  <si>
+    <t>Bluesy και πιο χαλαρό, με boogie αίσθηση και τίτλο που παραπέμπει σε ζωώδη, σεξουαλική και party-rock ενέργεια. Το riff έχει groove αντί για την καθαρή επιθετικότητα του “Piece of Me”, και η μπάντα ακούγεται σαν να παίζει ένα βρώμικο bar-rock κομμάτι μέσα σε μεγάλο studio. Ο Bach χρησιμοποιεί περισσότερο swagger και λιγότερη δραματική ένταση. Είναι σημαντικό ως αλλαγή ρυθμού πριν από τη B πλευρά, αλλά βρίσκεται πιο κοντά στη συμβατική hard-rock παράδοση και έχει λιγότερο μοναδικό βάρος από τα highlights.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο καθαρό melodic hard rock, με στίχο που δηλώνει παρουσία, διαθεσιμότητα και αυτοπεποίθηση. Είναι λιγότερο σκοτεινό από το “18 and Life” και λιγότερο επιθετικό από το “Youth Gone Wild”, λειτουργώντας σαν συνδετικός κρίκος ανάμεσα στα διαφορετικά πρόσωπα του album. Το refrain είναι άμεσο, οι κιθάρες γυαλισμένες αλλά όχι υπερβολικά pop και η ερμηνεία κρατά την απαραίτητη ένταση. Δεν είναι από τα πιο χαρακτηριστικά tracks, αλλά ενισχύει τη συνοχή του B-side.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, θορυβώδες και πιο punk-influenced από αρκετά άλλα τραγούδια του δίσκου. Ο τίτλος αποτυπώνει την εικόνα ενός ατόμου που κινείται μέσα στο χάος χωρίς να ενδιαφέρεται να ζητήσει άδεια ή συγγνώμη. Η μπάντα αφήνει το sleaze attitude να γίνει πιο άμεσο και επιθετικό, με κοφτά riffs και φωνητική ερμηνεία που μοιάζει έτοιμη να ξεσπάσει σε live χώρο. Είναι από τα tracks που προσθέτουν βρωμιά και κίνηση στο album, αποτρέποντάς το από το να γίνει απλή συλλογή polished power ballads και singles.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο είναι πιο μεγάλο, σκοτεινό και δραματικό, με δύο εικόνες που παραπέμπουν σε νύχτα, αναστάτωση και ανεξέλεγκτη ενέργεια. Η σύνθεση έχει περισσότερο epic hard-rock χαρακτήρα από τα σύντομα party tracks και λειτουργεί σαν τελευταία υπενθύμιση ότι οι Skid Row μπορούσαν να γράψουν κάτι βαρύτερο και πιο θεατρικό από το τυπικό glam-metal single. Η κιθάρα και τα drums δίνουν αίσθηση κλιμάκωσης, ενώ η φωνή του Bach διατηρεί το album σε υψηλή ένταση μέχρι το τέλος. Δεν είναι τόσο άμεσα αναγνωρίσιμο όσο το “Youth Gone Wild” ή το “I Remember You”, όμως ως closer προσφέρει πιο σκοτεινή και βαριά έξοδο.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη power ballad και η πιο καθαρή εμπορική κορύφωση της B πλευράς. Το τραγούδι ξεκινά με νοσταλγική, σχεδόν εύθραυστη ατμόσφαιρα και εξελίσσεται σε arena-rock refrain, όπου η φωνή του Bach ανεβαίνει από την προσωπική ανάμνηση στη δραματική εξομολόγηση. Σε αντίθεση με το “18 and Life”, εδώ η ιστορία είναι ερωτική και όχι κοινωνική, όμως η μπάντα την αντιμετωπίζει με αρκετή ένταση ώστε να μη γίνει απλώς slow dance. Οι κιθάρες, το solo και η φωνητική κορύφωση εξηγούν τη διαχρονικότητα του κομματιού. Είναι λιγότερο σκληρό από το υπόλοιπο album, αλλά εξαιρετικά αποτελεσματικό στο να αποκαλύπτει τη μελωδική πλευρά των Skid Row.</t>
+  </si>
+  <si>
+    <t>Atlantic – 781256-1, Atlantic – 781256 (Greece, 1985, LP, Album, Promo, Reissue, Repress, White Label, Stereo, Remixed). Record Company: Atlantic Records. Phonographic Copyright / Copyright by Atlantic Recording Corporation &amp; Snidest Music Company, Inc.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/10933246-Twisted-Sister-Under-The-Blade</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/a1ILYpbkmw6y6MK8m5lLMZDd76BsffiKXkUptmCeLmU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEyMzU5/NjQtMTY0NjgzMzQz/Mi0zMzM1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Under The Blade</t>
+  </si>
+  <si>
+    <t>Twisted Sister</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** 1st catalogue number on cover, 2nd catalogue number on label (handwritten). Barcode (Text): 0 7567-81256-1.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Early ’80s Heavy Metal, Glam Metal roots, Street Metal, NWOBHM-influenced Hard Rock]</t>
+  </si>
+  <si>
+    <t>What You Don’t Know (Sure Can Hurt You)</t>
+  </si>
+  <si>
+    <t>Bad Boys (Of Rock ’n’ Roll)</t>
+  </si>
+  <si>
+    <t>Run for Your Life</t>
+  </si>
+  <si>
+    <t>Sin After Sin</t>
+  </si>
+  <si>
+    <t>Shoot ’Em Down</t>
+  </si>
+  <si>
+    <t>Destroyer</t>
+  </si>
+  <si>
+    <t>Under the Blade</t>
+  </si>
+  <si>
+    <t>Tear It Loose</t>
+  </si>
+  <si>
+    <t>I’ll Never Grow Up, Now</t>
+  </si>
+  <si>
+    <t>Day of the Rocker</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Anthemic Heavy Metal, Street Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Glam Hard Rock, Party Rock, Bar-band Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Heavy Rock, Melodic Metal, Street Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Riff Metal, Glam-metal edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Aggressive Riff Rock, Street Metal, Live-energy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dramatic Heavy Metal, Theatrical Metal, Dark Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Surgical Horror Metal, Classic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Metal, Live Anthem, NWOBHM-influenced Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Melodic Hard Rock, Youth Anthem, Reissue-only track]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Rock ’n’ Roll Anthem, Bar-band Heavy Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Ιδανικό άνοιγμα, γιατί παρουσιάζει τους Skid Row ως πολύ πιο σκληρούς από ένα τυπικό glam-metal σχήμα. Το riff είναι άμεσο και βαρύ, με sleaze-rock swagger, ενώ ο Sebastian Bach μπαίνει από την αρχή με φωνή που δεν χαρίζεται, ψηλή, κραυγαλέα και επιθετική. Ο τίτλος χρησιμοποιεί τη γνωστή rock εικόνα των “big guns”, δηλαδή δύναμη, υπερβολή και σεξουαλική αυτοπεποίθηση, αλλά η μπάντα δεν μένει στη θεατρικότητα. Το rhythm section χτυπά με πραγματικό βάρος και το τραγούδι λειτουργεί σαν δήλωση, αυτό δεν είναι απλώς glossy MTV metal, αλλά hard rock με δόντια.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη αφηγηματική σύνθεση του album και το πιο ουσιαστικό τραγούδι της A πλευράς. Η ιστορία του Ricky, ενός νεαρού που οδηγείται σε φόνο και καταδίκη, δίνει στο glam-metal πλαίσιο κοινωνικό και δραματικό βάρος. Η μουσική ξεκινά ως melodic hard rock και χτίζει ένταση γύρω από το refrain, χωρίς να μετατρέπει την ιστορία σε απλό ηθικό μάθημα. Ο Bach τραγουδά με θεατρική δύναμη, αλλά το αποτέλεσμα δεν είναι καρικατούρα, η φωνή του δίνει στον χαρακτήρα τραγωδία, ενώ οι κιθάρες κρατούν τη σύνθεση αρκετά βαριά. Είναι ένα από τα τραγούδια που έκαναν το debut να ξεχωρίσει από τον σωρό των late-’80s hair-metal κυκλοφοριών.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο anthem της μπάντας και ίσως η πιο καθαρή συμπύκνωση της late-’80s νεανικής hard-rock κουλτούρας. Το τραγούδι μιλά για outsiders, rebellious identity και μια γενιά που αρνείται να συμμορφωθεί με την εικόνα που της επιβάλλουν. Το riff είναι απλό αλλά εξαιρετικά αποτελεσματικό, το chorus σχεδιασμένο για μαζικό sing-along και η φωνή του Bach δίνει στο μήνυμα πραγματική επιθετικότητα. Παρότι εμπορικά προσβάσιμο, δεν ακούγεται αποστειρωμένο, οι κιθάρες έχουν crunch, το rhythm section σπρώχνει το τραγούδι και το attitude είναι πιο πειστικό από το συνηθισμένο glam posturing.</t>
+  </si>
+  <si>
+    <t>Το σωστό άνοιγμα για τους πρώιμους Twisted Sister, ένα riff-driven heavy-rock anthem που προειδοποιεί ότι η άγνοια δεν προστατεύει κανέναν. Η φράση του τίτλου λειτουργεί σχεδόν σαν streetwise κανόνας επιβίωσης, και η μπάντα τη μεταφέρει με χοντρή κιθάρα, σταθερό backbeat και φωνητική αυτοπεποίθηση. Ο Dee Snider δεν τραγουδά σαν polished AOR frontman· ακούγεται σαν κάποιος που μιλά απευθείας σε live κοινό, με προσταγή, ειρωνεία και απειλή. Η σύνθεση δεν είναι περίπλοκη, αλλά είναι αποτελεσματική, πιάνει αμέσως το glam/street persona της μπάντας και το μεταφράζει σε πραγματικό hard rock, όχι απλή εικόνα.</t>
+  </si>
+  <si>
+    <t>Το πιο ξεκάθαρο statement ταυτότητας του δίσκου. Οι Twisted Sister παρουσιάζονται ως «κακά παιδιά» όχι με τη σκοτεινή, αυτοκαταστροφική έννοια, αλλά ως outcasts της rock ’n’ roll κουλτούρας, δυνατοί, θορυβώδεις και αδιάφοροι για την αποδοχή του mainstream. Η μουσική έχει περισσότερο glam-hard-rock χαρακτήρα, με catchy chorus και party-rock κίνηση. Δεν είναι από τα βαρύτερα τραγούδια του album, όμως είναι σημαντικό επειδή εξηγεί την καταγωγή τους από τη Long Island / New York club σκηνή, μια μπάντα που χτίστηκε στην επαφή με το κοινό, στα chants και στη θεατρική πρόκληση.</t>
+  </si>
+  <si>
+    <t>Γρήγορο και νευρικό, με τίτλο που παραπέμπει σε καταδίωξη, φυγή και άμεσο κίνδυνο. Το τραγούδι χτίζει την ένταση περισσότερο με το momentum παρά με πολύπλοκες αλλαγές, οι κιθάρες κινούνται ευθύγραμμα, το rhythm section σπρώχνει και ο Snider κρατά μια φωνητική αίσθηση επείγοντος. Η σύνθεση δείχνει την επιρροή του βρετανικού heavy metal πάνω στη μπάντα, αλλά δεν χάνει την αμερικανική bar-band αμεσότητα. Δεν φτάνει το ιδιαίτερο σκοτάδι του title track, ωστόσο είναι αποτελεσματικό fast heavy-rock cut και προσθέτει σημαντική ενέργεια στην A πλευρά.</t>
+  </si>
+  <si>
+    <t>Πιο βαρύ και σκοτεινό, με τίτλο που παραπέμπει σε έναν φαύλο κύκλο ενοχής, επιθυμίας και επανάληψης. Η μουσική πατά σε riff metal και πιο απειλητική ατμόσφαιρα από το party χαρακτήρα των προηγούμενων τραγουδιών. Η ερμηνεία του Snider δίνει στο “sin” θεατρικότητα, αλλά όχι απλώς shock value, η φωνή του μεταφέρει την αίσθηση ότι ο αφηγητής ξέρει πως κινείται σε λάθος δρόμο και παρ’ όλα αυτά δεν σταματά. Είναι από τα σημεία όπου το album απομακρύνεται από το glam εξωτερικό του περίβλημα και πλησιάζει περισσότερο την old-school heavy-metal δραματικότητα.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο άμεσο και πολεμικό hard rock. Η διατύπωση του τίτλου έχει τυπική heavy-metal υπερβολή, αλλά το κομμάτι λειτουργεί περισσότερο ως adrenaline rush παρά ως κυριολεκτικό αφήγημα. Τα riffs είναι κοφτά, η ρυθμική βάση σκληρή και η ερμηνεία του Snider σχεδόν διατακτική. Η δύναμη του τραγουδιού είναι ότι διατηρεί live αίσθηση, μπορείς εύκολα να το φανταστείς μέσα σε club set, με κοινό να απαντά σε κάθε chorus. Είναι ένα από τα καλύτερα παραδείγματα του τρόπου με τον οποίο οι Twisted Sister ένωναν την απλότητα του rock ’n’ roll με τη βαρύτητα του metal.</t>
+  </si>
+  <si>
+    <t>Το B-side ανοίγει με πιο θεατρικό και απειλητικό heavy-metal τόνο. Ο “destroyer” είναι μια φιγούρα καταστροφής, αλλά και μια προσωποποίηση της έντασης που η μπάντα θέλει να μεταδώσει, μεγάλη κιθάρα, δυναμικό chorus και στάση χωρίς συμβιβασμό. Το τραγούδι δεν έχει την ταχύτητα του “Tear It Loose”, αλλά χρησιμοποιεί mid-tempo βάρος για να χτίσει δραματικότητα. Είναι χαρακτηριστικό της εποχής πριν οι Twisted Sister γίνουν pop-culture εικόνα, η μουσική εξακολουθεί να έχει σκοτάδι και δόντια, ακόμη κι όταν η παρουσίαση παραμένει θεατρική.</t>
+  </si>
+  <si>
+    <t>Η άμεση απάντηση στην ασφυξία του title track, ένα γρήγορο, απελευθερωτικό heavy-metal anthem. Το “tear it loose” σημαίνει να σπάσεις δεσμά, περιορισμούς ή κοινωνικές επιταγές, και το riffing λειτουργεί ακριβώς έτσι — με ταχύτητα, ευθύτητα και live-ready κίνηση. Οι κιθάρες θυμίζουν επιρροές NWOBHM, ενώ η φωνή του Snider μετατρέπει την απλή φράση σε κάλεσμα προς το κοινό. Είναι από τις πιο καθαρές, ενεργητικές στιγμές του album και δείχνει γιατί η μπάντα είχε ήδη χτίσει αφοσιωμένο fanbase πριν αποκτήσει major-label επιτυχία.</t>
+  </si>
+  <si>
+    <t>Το closing anthem κλείνει τον δίσκο με αυτοαναφορικό τρόπο, η «μέρα του rocker» είναι στιγμή επιβεβαίωσης για μια κοινότητα που ορίζει τον εαυτό της μέσα από τη μουσική, το live show και τη συλλογική ένταση. Η σύνθεση δεν χρειάζεται την ψυχολογική ένταση του “Under the Blade”· επιλέγει chant-like ενέργεια και classic hard-rock γραμμές. Είναι η σωστή έξοδος για ένα album που είναι, στον πυρήνα του, προϊόν μιας μπάντας χτισμένης στη συναυλιακή εμπειρία. Μπορεί να μην είναι η πιο ευρηματική σύνθεση του LP, αλλά αφήνει το album να κλείσει με θόρυβο, υπερηφάνεια και την αίσθηση ότι το rock ’n’ roll είναι ταυτότητα, όχι απλώς είδος μουσικής.</t>
+  </si>
+  <si>
+    <t>Το track που διαφοροποιεί τη δική σου Atlantic επανέκδοση από το αρχικό LP του 1982. Μετά το σκοτεινό heavy-metal βάρος της προηγούμενης ενότητας, το τραγούδι επαναφέρει την πιο νεανική, glam-hard-rock πλευρά των Twisted Sister. Η άρνηση της ενηλικίωσης δεν παρουσιάζεται ως παιδικότητα, αλλά ως αντίσταση στην κανονικότητα, η ταυτότητα του rocker ορίζεται από το δικαίωμα να παραμένει θορυβώδης, θεατρικός και ανυπάκουος. Είναι λιγότερο καθοριστικό από τα αρχικά album peaks, όμως ταιριάζει με το persona της μπάντας και λειτουργεί φυσικά ως reissue-era προσθήκη. Η παρουσία του επιβεβαιώνεται ως Atlantic-reissue-only track στις διαθέσιμες καταγραφές.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση και η πιο σκοτεινή σύνθεση του album. Ο τίτλος συνδέεται με την εμπειρία του Dee Snider όταν η τότε σύζυγός του υποβλήθηκε σε χειρουργική επέμβαση, κάτι που εξηγεί τη surgical/horror εικόνα της «λεπίδας» χωρίς να μετατρέπει το τραγούδι σε απλό gore concept. Η μουσική είναι βαριά, απειλητική και δομημένη γύρω από riff που έχει πραγματικό heavy-metal βάρος. Ο Snider παίζει τον ρόλο του τρομαγμένου, εγκλωβισμένου αφηγητή με θεατρική ένταση, ενώ η μπάντα χτίζει αίσθηση πίεσης αντί για απλή ταχύτητα. Οι μεταγενέστερες κριτικές το περιγράφουν ως το πιο sinister τραγούδι του 1982 και, για αρκετούς, ως το καλύτερο Twisted Sister song.</t>
   </si>
 </sst>
 </file>
@@ -11318,7 +11546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14434,6 +14662,70 @@
       </c>
       <c r="J97" s="11" t="s">
         <v>3258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>3287</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>3287</v>
+      </c>
+      <c r="D98" s="6">
+        <v>1989</v>
+      </c>
+      <c r="E98" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>3303</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>3300</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>3299</v>
+      </c>
+      <c r="I98" s="11" t="s">
+        <v>3301</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D99" s="6">
+        <v>1982</v>
+      </c>
+      <c r="E99" s="10">
+        <v>3.41</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>3329</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>3328</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>3323</v>
+      </c>
+      <c r="I99" s="11" t="s">
+        <v>3324</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>3325</v>
       </c>
     </row>
   </sheetData>
@@ -14627,6 +14919,10 @@
     <hyperlink ref="J96" r:id="rId187" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
     <hyperlink ref="I97" r:id="rId188" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
     <hyperlink ref="J97" r:id="rId189" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
+    <hyperlink ref="I98" r:id="rId190" xr:uid="{83583B05-7171-47AC-AF11-32B133FFE3DA}"/>
+    <hyperlink ref="J98" r:id="rId191" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
+    <hyperlink ref="I99" r:id="rId192" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
+    <hyperlink ref="J99" r:id="rId193" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14634,7 +14930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I918"/>
+  <dimension ref="A1:I939"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -39569,6 +39865,575 @@
       </c>
       <c r="I918" s="6"/>
     </row>
+    <row r="919" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A919" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B919" s="6">
+        <v>1</v>
+      </c>
+      <c r="C919" s="22" t="s">
+        <v>3288</v>
+      </c>
+      <c r="D919" s="7" t="s">
+        <v>3304</v>
+      </c>
+      <c r="E919" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F919" s="12">
+        <v>4</v>
+      </c>
+      <c r="G919" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H919" s="9" t="s">
+        <v>3350</v>
+      </c>
+      <c r="I919" s="6"/>
+    </row>
+    <row r="920" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A920" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B920" s="6">
+        <v>2</v>
+      </c>
+      <c r="C920" s="22" t="s">
+        <v>3289</v>
+      </c>
+      <c r="D920" s="7" t="s">
+        <v>3305</v>
+      </c>
+      <c r="E920" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F920" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G920" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H920" s="9" t="s">
+        <v>3315</v>
+      </c>
+      <c r="I920" s="6"/>
+    </row>
+    <row r="921" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A921" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B921" s="6">
+        <v>3</v>
+      </c>
+      <c r="C921" s="22" t="s">
+        <v>3290</v>
+      </c>
+      <c r="D921" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="E921" s="20">
+        <v>3.44</v>
+      </c>
+      <c r="F921" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G921" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H921" s="9" t="s">
+        <v>3316</v>
+      </c>
+      <c r="I921" s="6"/>
+    </row>
+    <row r="922" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A922" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B922" s="6">
+        <v>4</v>
+      </c>
+      <c r="C922" s="22" t="s">
+        <v>3291</v>
+      </c>
+      <c r="D922" s="7" t="s">
+        <v>3307</v>
+      </c>
+      <c r="E922" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="F922" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G922" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H922" s="9" t="s">
+        <v>3317</v>
+      </c>
+      <c r="I922" s="6"/>
+    </row>
+    <row r="923" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A923" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B923" s="6">
+        <v>5</v>
+      </c>
+      <c r="C923" s="22" t="s">
+        <v>3292</v>
+      </c>
+      <c r="D923" s="7" t="s">
+        <v>3308</v>
+      </c>
+      <c r="E923" s="20">
+        <v>4.29</v>
+      </c>
+      <c r="F923" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G923" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H923" s="9" t="s">
+        <v>3351</v>
+      </c>
+      <c r="I923" s="6"/>
+    </row>
+    <row r="924" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A924" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B924" s="6">
+        <v>6</v>
+      </c>
+      <c r="C924" s="22" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D924" s="7" t="s">
+        <v>3309</v>
+      </c>
+      <c r="E924" s="20">
+        <v>3.32</v>
+      </c>
+      <c r="F924" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G924" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H924" s="9" t="s">
+        <v>3318</v>
+      </c>
+      <c r="I924" s="6"/>
+    </row>
+    <row r="925" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A925" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B925" s="6">
+        <v>7</v>
+      </c>
+      <c r="C925" s="22" t="s">
+        <v>3294</v>
+      </c>
+      <c r="D925" s="7" t="s">
+        <v>3310</v>
+      </c>
+      <c r="E925" s="20">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F925" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G925" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H925" s="9" t="s">
+        <v>3352</v>
+      </c>
+      <c r="I925" s="6"/>
+    </row>
+    <row r="926" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A926" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B926" s="6">
+        <v>8</v>
+      </c>
+      <c r="C926" s="22" t="s">
+        <v>3295</v>
+      </c>
+      <c r="D926" s="7" t="s">
+        <v>3311</v>
+      </c>
+      <c r="E926" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F926" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G926" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H926" s="9" t="s">
+        <v>3319</v>
+      </c>
+      <c r="I926" s="6"/>
+    </row>
+    <row r="927" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A927" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B927" s="6">
+        <v>9</v>
+      </c>
+      <c r="C927" s="22" t="s">
+        <v>3296</v>
+      </c>
+      <c r="D927" s="7" t="s">
+        <v>3312</v>
+      </c>
+      <c r="E927" s="20">
+        <v>3.38</v>
+      </c>
+      <c r="F927" s="12">
+        <v>4</v>
+      </c>
+      <c r="G927" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H927" s="9" t="s">
+        <v>3320</v>
+      </c>
+      <c r="I927" s="6"/>
+    </row>
+    <row r="928" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A928" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B928" s="6">
+        <v>10</v>
+      </c>
+      <c r="C928" s="22" t="s">
+        <v>3297</v>
+      </c>
+      <c r="D928" s="7" t="s">
+        <v>3313</v>
+      </c>
+      <c r="E928" s="20">
+        <v>4</v>
+      </c>
+      <c r="F928" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G928" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H928" s="9" t="s">
+        <v>3322</v>
+      </c>
+      <c r="I928" s="6"/>
+    </row>
+    <row r="929" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A929" s="6">
+        <v>2782114</v>
+      </c>
+      <c r="B929" s="6">
+        <v>11</v>
+      </c>
+      <c r="C929" s="22" t="s">
+        <v>3298</v>
+      </c>
+      <c r="D929" s="7" t="s">
+        <v>3314</v>
+      </c>
+      <c r="E929" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F929" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G929" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H929" s="9" t="s">
+        <v>3321</v>
+      </c>
+      <c r="I929" s="6"/>
+    </row>
+    <row r="930" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A930" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B930" s="6">
+        <v>1</v>
+      </c>
+      <c r="C930" s="22" t="s">
+        <v>3330</v>
+      </c>
+      <c r="D930" s="7" t="s">
+        <v>3340</v>
+      </c>
+      <c r="E930" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F930" s="12">
+        <v>4</v>
+      </c>
+      <c r="G930" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H930" s="9" t="s">
+        <v>3353</v>
+      </c>
+      <c r="I930" s="6"/>
+    </row>
+    <row r="931" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A931" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B931" s="6">
+        <v>2</v>
+      </c>
+      <c r="C931" s="22" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D931" s="7" t="s">
+        <v>3341</v>
+      </c>
+      <c r="E931" s="20">
+        <v>3.19</v>
+      </c>
+      <c r="F931" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G931" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H931" s="9" t="s">
+        <v>3354</v>
+      </c>
+      <c r="I931" s="6"/>
+    </row>
+    <row r="932" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A932" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B932" s="6">
+        <v>3</v>
+      </c>
+      <c r="C932" s="22" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D932" s="7" t="s">
+        <v>3342</v>
+      </c>
+      <c r="E932" s="20">
+        <v>3.52</v>
+      </c>
+      <c r="F932" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G932" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H932" s="9" t="s">
+        <v>3355</v>
+      </c>
+      <c r="I932" s="6"/>
+    </row>
+    <row r="933" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A933" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B933" s="6">
+        <v>4</v>
+      </c>
+      <c r="C933" s="22" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D933" s="7" t="s">
+        <v>3343</v>
+      </c>
+      <c r="E933" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F933" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G933" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H933" s="9" t="s">
+        <v>3356</v>
+      </c>
+      <c r="I933" s="6"/>
+    </row>
+    <row r="934" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A934" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B934" s="6">
+        <v>5</v>
+      </c>
+      <c r="C934" s="22" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D934" s="7" t="s">
+        <v>3344</v>
+      </c>
+      <c r="E934" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F934" s="12">
+        <v>4</v>
+      </c>
+      <c r="G934" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H934" s="9" t="s">
+        <v>3357</v>
+      </c>
+      <c r="I934" s="6"/>
+    </row>
+    <row r="935" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A935" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B935" s="6">
+        <v>6</v>
+      </c>
+      <c r="C935" s="22" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D935" s="7" t="s">
+        <v>3345</v>
+      </c>
+      <c r="E935" s="20">
+        <v>3.41</v>
+      </c>
+      <c r="F935" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G935" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H935" s="9" t="s">
+        <v>3358</v>
+      </c>
+      <c r="I935" s="6"/>
+    </row>
+    <row r="936" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A936" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B936" s="6">
+        <v>7</v>
+      </c>
+      <c r="C936" s="22" t="s">
+        <v>3336</v>
+      </c>
+      <c r="D936" s="7" t="s">
+        <v>3346</v>
+      </c>
+      <c r="E936" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="F936" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G936" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H936" s="9" t="s">
+        <v>3362</v>
+      </c>
+      <c r="I936" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A937" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B937" s="6">
+        <v>8</v>
+      </c>
+      <c r="C937" s="22" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D937" s="7" t="s">
+        <v>3347</v>
+      </c>
+      <c r="E937" s="20">
+        <v>3.52</v>
+      </c>
+      <c r="F937" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G937" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H937" s="9" t="s">
+        <v>3359</v>
+      </c>
+      <c r="I937" s="6"/>
+    </row>
+    <row r="938" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A938" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B938" s="6">
+        <v>9</v>
+      </c>
+      <c r="C938" s="22" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D938" s="7" t="s">
+        <v>3348</v>
+      </c>
+      <c r="E938" s="20">
+        <v>3.32</v>
+      </c>
+      <c r="F938" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G938" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H938" s="9" t="s">
+        <v>3361</v>
+      </c>
+      <c r="I938" s="6"/>
+    </row>
+    <row r="939" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A939" s="6">
+        <v>10933246</v>
+      </c>
+      <c r="B939" s="6">
+        <v>10</v>
+      </c>
+      <c r="C939" s="22" t="s">
+        <v>3339</v>
+      </c>
+      <c r="D939" s="7" t="s">
+        <v>3349</v>
+      </c>
+      <c r="E939" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F939" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G939" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H939" s="9" t="s">
+        <v>3360</v>
+      </c>
+      <c r="I939" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00919DF-4129-4600-8954-B65D23179477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6753521-C44F-411F-90C8-9727C0CDBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="3363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="3395">
   <si>
     <t>No</t>
   </si>
@@ -10917,9 +10917,6 @@
     <t>Twisted Sister</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** 1st catalogue number on cover, 2nd catalogue number on label (handwritten). Barcode (Text): 0 7567-81256-1.</t>
-  </si>
-  <si>
     <t>Heavy Metal, Hard Rock [Early ’80s Heavy Metal, Glam Metal roots, Street Metal, NWOBHM-influenced Hard Rock]</t>
   </si>
   <si>
@@ -11020,6 +11017,165 @@
   </si>
   <si>
     <t>Η μεγάλη κορύφωση και η πιο σκοτεινή σύνθεση του album. Ο τίτλος συνδέεται με την εμπειρία του Dee Snider όταν η τότε σύζυγός του υποβλήθηκε σε χειρουργική επέμβαση, κάτι που εξηγεί τη surgical/horror εικόνα της «λεπίδας» χωρίς να μετατρέπει το τραγούδι σε απλό gore concept. Η μουσική είναι βαριά, απειλητική και δομημένη γύρω από riff που έχει πραγματικό heavy-metal βάρος. Ο Snider παίζει τον ρόλο του τρομαγμένου, εγκλωβισμένου αφηγητή με θεατρική ένταση, ενώ η μπάντα χτίζει αίσθηση πίεσης αντί για απλή ταχύτητα. Οι μεταγενέστερες κριτικές το περιγράφουν ως το πιο sinister τραγούδι του 1982 και, για αρκετούς, ως το καλύτερο Twisted Sister song.</t>
+  </si>
+  <si>
+    <t>Stay Hungry</t>
+  </si>
+  <si>
+    <t>We’re Not Gonna Take It</t>
+  </si>
+  <si>
+    <t>Burn in Hell</t>
+  </si>
+  <si>
+    <t>Horror-Teria (The Beginning): Captain Howdy / Street Justice</t>
+  </si>
+  <si>
+    <t>I Wanna Rock</t>
+  </si>
+  <si>
+    <t>The Price</t>
+  </si>
+  <si>
+    <t>Don’t Let Me Down</t>
+  </si>
+  <si>
+    <t>The Beast</t>
+  </si>
+  <si>
+    <t>S.M.F.</t>
+  </si>
+  <si>
+    <t>Atlantic – 78 01561 (Canada, 1984, LP, Album, Stereo). Manufactured and Distributed by WEA Music of Canada, Ltd. Pressed by Cinram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded at Record Plant (New York), Westlake Audio (Los Angeles) and Cherokee Studios (Los Angeles) in February-March 1984. Produced by Tom Werman.   Mastered by George Marino at Sterling Sound. Runouts all etched except for stamped encircled Cinram symbol - CR. </t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** (Ελληνική έκδοση του 1985 για το άλμπουμ του 1982, Remixed έκδοση). 1st catalogue number on cover, 2nd catalogue number on label (handwritten). Barcode (Text): 0 7567-81256-1.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1382323-Twisted-Sister-Stay-Hungry</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/n3kNL7svWrXJVCkNwtEbdrt05ok0YRgNVqzTmy9t1XU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEzODIz/MjMtMTIyMTc1MDk4/OC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Glam Metal, Hair Metal, Arena Metal, Shock Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Melodic Heavy Metal, Arena Rock, Album Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Arena Anthem, Pop Metal, Rebellion Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Theatrical Metal, Shock Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Horror Metal, Mini-Concept Suite, Theatrical Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Arena Rock Anthem, Pop Metal, Party Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Melodic Hard Rock, Reflective Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Heavy Rock, Arena Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Metal, Horror Rock, Riff Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Street Metal, Fan Anthem, Live-style Hard Rock]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η πιο φιλόδοξη σύνθεση του δίσκου, μια mini-suite με horror αφήγηση και θεατρική δομή. Το “Captain Howdy” και το “Street Justice” δημιουργούν μια ιστορία φόβου, τιμωρίας και βίας, θυμίζοντας την αισθητική horror cinema που ο Snider θα συνέχιζε να εξερευνά αργότερα στο </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Strangeland</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>. Η μουσική αφήνει λίγο περισσότερο χώρο σε αλλαγές mood και δραματική κορύφωση από τα σύντομα anthems του δίσκου. Δεν είναι το πιο άμεσο κομμάτι, αλλά είναι το σημείο που αποκαλύπτει πως οι Twisted Sister ήθελαν να είναι και theatrical metal act, όχι μόνο hit machine.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Επιστροφή στη horror-metal πλευρά του album. Η «θηρία» του τίτλου μπορεί να διαβαστεί ως εξωτερική απειλή ή ως καταστροφικό ένστικτο μέσα στον άνθρωπο, και η μουσική προτιμά βαριά riffs και πιο απειλητική ατμόσφαιρα. Δεν έχει την αφηγηματική ανάπτυξη του “Horror-Teria”, όμως λειτουργεί σαν σύντομη, σκοτεινή ενίσχυση πριν το κλείσιμο. Είναι ένα από τα κομμάτια που δίνουν στο </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Stay Hungry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> περισσότερο βάθος από την εικόνα ενός album χτισμένου μόνο πάνω σε χιουμοριστικά rebellion hits.</t>
+    </r>
+  </si>
+  <si>
+    <t>Μετά τη συναισθηματική ένταση του “The Price”, το track επιστρέφει σε πιο ευθύ melodic hard rock. Ο τίτλος αφορά εμπιστοσύνη και την αγωνία ότι ένα πρόσωπο ή μια σχέση μπορεί να αποτύχει την κρίσιμη στιγμή. Οι κιθάρες των Jay Jay French και Eddie Ojeda αλληλεπιδρούν πιο έντονα, ενώ το τραγούδι διατηρεί arena-ready chorus και σταθερό, mid-tempo drive. Δεν διαθέτει τη μοναδικότητα των τριών singles ούτε τη σκοτεινή ατμόσφαιρα του “Burn in Hell”, όμως λειτουργεί ως στιβαρό deep cut και κρατά τη δεύτερη πλευρά σε ισορροπία μεταξύ μπαλάντας και heavy rock.</t>
+  </si>
+  <si>
+    <t>Η power ballad του δίσκου και το πιο εσωστρεφές κομμάτι του. Το “price” είναι το τίμημα της φιλοδοξίας, της ανεξαρτησίας ή της επιλογής να ζεις έξω από τους κανόνες που οι άλλοι θεωρούν ασφαλείς. Η σύνθεση χτίζει πάνω σε melodic hard-rock βάση, αλλά δεν φτάνει στην υπερβολική γλυκύτητα πολλών μεταγενέστερων hair-metal ballads. Ο Snider ακούγεται πιο ευάλωτος, χωρίς να εγκαταλείπει το δραματικό ύφος του, και η κιθάρα προσφέρει κορύφωση αντί για απλό slow-dance φόντο. Το “The Price” λειτουργεί ως σημαντική απόδειξη ότι η μπάντα μπορούσε να αφήσει κάτω το θεατρικό makeup και να γράψει ανθρώπινο, μελαγχολικό τραγούδι. Ήταν το τρίτο single του album.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει το album με πιο σοβαρό και αποφασιστικό τόνο από αυτόν που θα περίμενε κανείς γνωρίζοντας μόνο τα MTV singles. Το “stay hungry” δεν αφορά κυριολεκτικά την πείνα, αλλά την ανάγκη να κρατήσεις την επιθυμία, τη φιλοδοξία και την εσωτερική σου ορμή ζωντανές. Οι κιθάρες έχουν καθαρό hard-metal βάρος, ενώ ο Dee Snider τραγουδά σαν να δίνει εντολή σε μια κοινότητα outsiders να μη βολευτεί. Δεν είναι το πιο άμεσο hook του δίσκου, αλλά λειτουργεί σωστά ως πρόγραμμα-δήλωση, πριν από την εξέγερση, τη φρίκη και την party-metal χαρά, υπάρχει η απόφαση να μην αφήσεις τον εαυτό σου να αδρανοποιηθεί.</t>
+  </si>
+  <si>
+    <t>Η πιο σκοτεινή και βαριά πλευρά του album. Η απειλή του τίτλου δεν αντιμετωπίζεται ως χαριτωμένο glam-metal shock, αλλά ως δραματική, σχεδόν θεατρική καταδίκη. Το riff είναι πιο βαρύ, ο ρυθμός πιο απειλητικός και η φωνή του Snider έχει λιγότερη party διάθεση και περισσότερη επιβολή. Το τραγούδι δείχνει τι χάνεται όταν οι Twisted Sister παρουσιάζονται αποκλειστικά ως comic MTV μπάντα, είχαν δυνατότητα να γράψουν dark, riff-centered heavy metal με αληθινή ένταση. Κριτικές για το album το περιλαμβάνουν στα heavier numbers όπου η μπάντα υπερέχει.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με το δεύτερο μεγάλο anthem. Σε αντίθεση με το συλλογικό, αντιεξουσιαστικό “We’re Not Gonna Take It”, το “I Wanna Rock” είναι πιο προσωπική και πιο στοιχειώδης δήλωση, η μουσική δεν χρειάζεται να δικαιολογηθεί· το rock ’n’ roll είναι δικαίωμα και ανάγκη. Το riff είναι απλό, το chorus τεράστιο και η ερμηνεία του Snider χτίζεται για crowds που φωνάζουν την τελευταία λέξη κάθε φράσης. Είναι arena rock στην καθαρότερη μορφή του, αλλά η αποφασιστικότητα του παίξιμου το σώζει από το να γίνει απλή novelty. Ήταν το δεύτερο single του album και έφτασε στο Νο. 68 του Billboard Hot 100.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη, παγκόσμια κορύφωση του album και ένα από τα καθοριστικά anthems του 1980s hard rock. Το τραγούδι μετατρέπει μια απλή άρνηση , «δεν θα το δεχτούμε» , σε καθολικό σύνθημα ενάντια στην αυθεντία, τον έλεγχο και την περιφρόνηση. Η μουσική είναι σκόπιμα απλή, ένα ευθύ riff, καθαρή pop-metal μελωδία, chorus σχεδιασμένο για να τραγουδιέται από πλήθος και ρυθμός που δεν χάνει ποτέ την ορμή του. Αυτή η απλότητα είναι η δύναμή του. Το τραγούδι μπορεί να λειτουργήσει ως teen rebellion, workplace protest ή γενική δήλωση αξιοπρέπειας, γι’ αυτό και ξεπέρασε το στενό heavy-metal κοινό. Έφτασε στο Νο. 21 του Billboard Hot 100 και έγινε το defining single των Twisted Sister.</t>
+  </si>
+  <si>
+    <t>Το τελικό fan anthem, με αρχικά που παραπέμπουν στους “Sick Motherfuckers” , το όνομα που χρησιμοποιούσε το αφοσιωμένο κοινό της μπάντας. Η τραχιά γλώσσα δεν λειτουργεί απλώς προκλητικά, εκφράζει τη σχέση των Twisted Sister με τους fans που τους ακολουθούσαν από τα club χρόνια. Η μουσική είναι απλή, δυναμική και live-oriented, σχεδιασμένη για συλλογικό chant περισσότερο από για πολυπλοκότητα. Ως κλείσιμο, έχει νόημα, μετά την πείνα, την εξέγερση, τον φόβο και την προσωπική αμφιβολία, το album τελειώνει μέσα στην κοινότητα που έκανε την μπάντα αυτό που έγινε.</t>
   </si>
 </sst>
 </file>
@@ -11546,7 +11702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14696,7 +14852,7 @@
         <v>3302</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>10933246</v>
       </c>
@@ -14713,10 +14869,10 @@
         <v>3.41</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>3328</v>
+        <v>3373</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>3323</v>
@@ -14726,6 +14882,38 @@
       </c>
       <c r="J99" s="11" t="s">
         <v>3325</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D100" s="6">
+        <v>1984</v>
+      </c>
+      <c r="E100" s="10">
+        <v>3.51</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>3376</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>3372</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>3371</v>
+      </c>
+      <c r="I100" s="11" t="s">
+        <v>3374</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>3375</v>
       </c>
     </row>
   </sheetData>
@@ -14923,6 +15111,8 @@
     <hyperlink ref="J98" r:id="rId191" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
     <hyperlink ref="I99" r:id="rId192" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
     <hyperlink ref="J99" r:id="rId193" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
+    <hyperlink ref="I100" r:id="rId194" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
+    <hyperlink ref="J100" r:id="rId195" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14930,7 +15120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I939"/>
+  <dimension ref="A1:I948"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -39483,7 +39673,9 @@
       <c r="H904" s="9" t="s">
         <v>3249</v>
       </c>
-      <c r="I904" s="6"/>
+      <c r="I904" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="905" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A905" s="6">
@@ -39888,7 +40080,7 @@
         <v>3.6</v>
       </c>
       <c r="H919" s="9" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="I919" s="6"/>
     </row>
@@ -39996,7 +40188,7 @@
         <v>4.3</v>
       </c>
       <c r="H923" s="9" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="I923" s="6"/>
     </row>
@@ -40050,7 +40242,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H925" s="9" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="I925" s="6"/>
     </row>
@@ -40170,10 +40362,10 @@
         <v>1</v>
       </c>
       <c r="C930" s="22" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="D930" s="7" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="E930" s="20">
         <v>3.82</v>
@@ -40185,9 +40377,11 @@
         <v>3.7</v>
       </c>
       <c r="H930" s="9" t="s">
-        <v>3353</v>
-      </c>
-      <c r="I930" s="6"/>
+        <v>3352</v>
+      </c>
+      <c r="I930" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="931" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A931" s="6">
@@ -40197,10 +40391,10 @@
         <v>2</v>
       </c>
       <c r="C931" s="22" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="D931" s="7" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="E931" s="20">
         <v>3.19</v>
@@ -40212,7 +40406,7 @@
         <v>3.6</v>
       </c>
       <c r="H931" s="9" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="I931" s="6"/>
     </row>
@@ -40224,10 +40418,10 @@
         <v>3</v>
       </c>
       <c r="C932" s="22" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="D932" s="7" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="E932" s="20">
         <v>3.52</v>
@@ -40239,7 +40433,7 @@
         <v>3.7</v>
       </c>
       <c r="H932" s="9" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="I932" s="6"/>
     </row>
@@ -40251,10 +40445,10 @@
         <v>4</v>
       </c>
       <c r="C933" s="22" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="D933" s="7" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="E933" s="20">
         <v>3.51</v>
@@ -40266,7 +40460,7 @@
         <v>3.8</v>
       </c>
       <c r="H933" s="9" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="I933" s="6"/>
     </row>
@@ -40278,10 +40472,10 @@
         <v>5</v>
       </c>
       <c r="C934" s="22" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="D934" s="7" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="E934" s="20">
         <v>3.69</v>
@@ -40293,7 +40487,7 @@
         <v>3.7</v>
       </c>
       <c r="H934" s="9" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="I934" s="6"/>
     </row>
@@ -40305,10 +40499,10 @@
         <v>6</v>
       </c>
       <c r="C935" s="22" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="D935" s="7" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E935" s="20">
         <v>3.41</v>
@@ -40320,9 +40514,11 @@
         <v>3.9</v>
       </c>
       <c r="H935" s="9" t="s">
-        <v>3358</v>
-      </c>
-      <c r="I935" s="6"/>
+        <v>3357</v>
+      </c>
+      <c r="I935" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="936" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A936" s="6">
@@ -40332,10 +40528,10 @@
         <v>7</v>
       </c>
       <c r="C936" s="22" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="D936" s="7" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E936" s="20">
         <v>3.96</v>
@@ -40347,7 +40543,7 @@
         <v>4.3</v>
       </c>
       <c r="H936" s="9" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="I936" s="6" t="s">
         <v>240</v>
@@ -40361,10 +40557,10 @@
         <v>8</v>
       </c>
       <c r="C937" s="22" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="D937" s="7" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E937" s="20">
         <v>3.52</v>
@@ -40376,7 +40572,7 @@
         <v>3.6</v>
       </c>
       <c r="H937" s="9" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="I937" s="6"/>
     </row>
@@ -40388,10 +40584,10 @@
         <v>9</v>
       </c>
       <c r="C938" s="22" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="D938" s="7" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E938" s="20">
         <v>3.32</v>
@@ -40403,7 +40599,7 @@
         <v>3.7</v>
       </c>
       <c r="H938" s="9" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="I938" s="6"/>
     </row>
@@ -40415,10 +40611,10 @@
         <v>10</v>
       </c>
       <c r="C939" s="22" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="D939" s="7" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="E939" s="20">
         <v>3.21</v>
@@ -40430,9 +40626,262 @@
         <v>3.7</v>
       </c>
       <c r="H939" s="9" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="I939" s="6"/>
+    </row>
+    <row r="940" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A940" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B940" s="6">
+        <v>1</v>
+      </c>
+      <c r="C940" s="22" t="s">
+        <v>3362</v>
+      </c>
+      <c r="D940" s="7" t="s">
+        <v>3377</v>
+      </c>
+      <c r="E940" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F940" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G940" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H940" s="9" t="s">
+        <v>3390</v>
+      </c>
+      <c r="I940" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A941" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B941" s="6">
+        <v>2</v>
+      </c>
+      <c r="C941" s="22" t="s">
+        <v>3363</v>
+      </c>
+      <c r="D941" s="7" t="s">
+        <v>3378</v>
+      </c>
+      <c r="E941" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F941" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G941" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H941" s="9" t="s">
+        <v>3393</v>
+      </c>
+      <c r="I941" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A942" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B942" s="6">
+        <v>3</v>
+      </c>
+      <c r="C942" s="22" t="s">
+        <v>3364</v>
+      </c>
+      <c r="D942" s="7" t="s">
+        <v>3379</v>
+      </c>
+      <c r="E942" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F942" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G942" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H942" s="9" t="s">
+        <v>3391</v>
+      </c>
+      <c r="I942" s="6"/>
+    </row>
+    <row r="943" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A943" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B943" s="6">
+        <v>4</v>
+      </c>
+      <c r="C943" s="7" t="s">
+        <v>3365</v>
+      </c>
+      <c r="D943" s="7" t="s">
+        <v>3380</v>
+      </c>
+      <c r="E943" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F943" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G943" s="12">
+        <v>4</v>
+      </c>
+      <c r="H943" s="9" t="s">
+        <v>3386</v>
+      </c>
+      <c r="I943" s="6"/>
+    </row>
+    <row r="944" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A944" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B944" s="6">
+        <v>5</v>
+      </c>
+      <c r="C944" s="22" t="s">
+        <v>3366</v>
+      </c>
+      <c r="D944" s="7" t="s">
+        <v>3381</v>
+      </c>
+      <c r="E944" s="20">
+        <v>3.99</v>
+      </c>
+      <c r="F944" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G944" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H944" s="9" t="s">
+        <v>3392</v>
+      </c>
+      <c r="I944" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A945" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B945" s="6">
+        <v>6</v>
+      </c>
+      <c r="C945" s="22" t="s">
+        <v>3367</v>
+      </c>
+      <c r="D945" s="7" t="s">
+        <v>3382</v>
+      </c>
+      <c r="E945" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F945" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G945" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H945" s="9" t="s">
+        <v>3389</v>
+      </c>
+      <c r="I945" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A946" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B946" s="6">
+        <v>7</v>
+      </c>
+      <c r="C946" s="22" t="s">
+        <v>3368</v>
+      </c>
+      <c r="D946" s="7" t="s">
+        <v>3383</v>
+      </c>
+      <c r="E946" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F946" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G946" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H946" s="9" t="s">
+        <v>3388</v>
+      </c>
+      <c r="I946" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A947" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B947" s="6">
+        <v>8</v>
+      </c>
+      <c r="C947" s="22" t="s">
+        <v>3369</v>
+      </c>
+      <c r="D947" s="7" t="s">
+        <v>3384</v>
+      </c>
+      <c r="E947" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F947" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G947" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H947" s="9" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I947" s="6"/>
+    </row>
+    <row r="948" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A948" s="6">
+        <v>1382323</v>
+      </c>
+      <c r="B948" s="6">
+        <v>9</v>
+      </c>
+      <c r="C948" s="22" t="s">
+        <v>3370</v>
+      </c>
+      <c r="D948" s="7" t="s">
+        <v>3385</v>
+      </c>
+      <c r="E948" s="20">
+        <v>3.44</v>
+      </c>
+      <c r="F948" s="12">
+        <v>4</v>
+      </c>
+      <c r="G948" s="12">
+        <v>4</v>
+      </c>
+      <c r="H948" s="9" t="s">
+        <v>3394</v>
+      </c>
+      <c r="I948" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6753521-C44F-411F-90C8-9727C0CDBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373681C1-F0A0-4C76-86F2-0BE42A14AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="3395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="3431">
   <si>
     <t>No</t>
   </si>
@@ -11176,6 +11176,114 @@
   </si>
   <si>
     <t>Το τελικό fan anthem, με αρχικά που παραπέμπουν στους “Sick Motherfuckers” , το όνομα που χρησιμοποιούσε το αφοσιωμένο κοινό της μπάντας. Η τραχιά γλώσσα δεν λειτουργεί απλώς προκλητικά, εκφράζει τη σχέση των Twisted Sister με τους fans που τους ακολουθούσαν από τα club χρόνια. Η μουσική είναι απλή, δυναμική και live-oriented, σχεδιασμένη για συλλογικό chant περισσότερο από για πολυπλοκότητα. Ως κλείσιμο, έχει νόημα, μετά την πείνα, την εξέγερση, τον φόβο και την προσωπική αμφιβολία, το album τελειώνει μέσα στην κοινότητα που έκανε την μπάντα αυτό που έγινε.</t>
+  </si>
+  <si>
+    <t>You Can't Stop Rock 'N' Roll</t>
+  </si>
+  <si>
+    <t>Atlantic – 78-0074-1 (Europe, 1983, LP, Album, Stereo). Pressed by Record Service Alsdorf. Made in Germany with UK, French, and German price codes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded and mixed at The Sol Studio, Cookham, Berkshire. Mastered at The Town House. Produced, engineered, and mixed by Stuart Epps.   Issued with a printed inner sleeve with lyrics and credits. Rights Society (Boxed): GEMA/Biem. Label Code: LC 0121. </t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/caXaG7QfvhRJ4evD1dJ2ujL0sMmRyhgh5vvv2K2LOGI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY0Njkz/NC0xMjg5OTEwOTgz/LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/646934-Twisted-Sister-You-Cant-Stop-Rock-N-Roll</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Glam Metal [Hard Rock, Street Metal, Early ’80s Metal, NWOBHM-influenced Heavy Rock</t>
+  </si>
+  <si>
+    <t>The Kids Are Back</t>
+  </si>
+  <si>
+    <t>Like a Knife in the Back</t>
+  </si>
+  <si>
+    <t>Ride to Live, Live to Ride</t>
+  </si>
+  <si>
+    <t>I Am (I’m Me)</t>
+  </si>
+  <si>
+    <t>The Power and the Glory</t>
+  </si>
+  <si>
+    <t>We’re Gonna Make It</t>
+  </si>
+  <si>
+    <t>You Can’t Stop Rock ’N’ Roll</t>
+  </si>
+  <si>
+    <t>You’re Not Alone (Suzette’s Song)</t>
+  </si>
+  <si>
+    <t>I’ll Take You Alive</t>
+  </si>
+  <si>
+    <t>I’ve Had Enough</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Street-Metal Anthem, Melodic Metal, Live-Ready Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Riff Metal, Melodic Heavy Rock, Betrayal Song]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Biker Rock, Fast Metal, Road Anthem]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Identity Anthem, Melodic Heavy Metal, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Metal, Theatrical Heavy Rock, Anthemic Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Street Rock, Defiant Metal Anthem, Working-Class Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Aggressive Riff Rock, Frustration Anthem, Fast Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Menacing Heavy Rock, Dark Glam Metal, Riff Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Melodic Hard Rock, Romantic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Rock ’n’ Roll Anthem, Glam Metal, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Σκοτεινότερο και απειλητικό, με τον τίτλο να χρησιμοποιεί την υπερβολή του horror/metal λεξιλογίου. Ο αφηγητής δεν εμφανίζεται σαν ρομαντικός ήρωας, αλλά ως καταδιωκτική, θεατρική φιγούρα, κάτι που ταιριάζει με το visual persona των Twisted Sister. Η μουσική είναι βαρύτερη και πιο riff-centric, χωρίς να χάνει την προσιτή δομή του album. Το τραγούδι δεν φτάνει τη συνθετική δύναμη του “Like a Knife in the Back”, αλλά κρατά την B πλευρά μακριά από υπερβολικά smooth hard rock και υπενθυμίζει ότι η μπάντα εξακολουθεί να έχει σκοτεινή, street-metal πλευρά.</t>
+  </si>
+  <si>
+    <t>Πιο κοφτό και επιθετικό, ένα τραγούδι κορεσμού που αρνείται να ανεχθεί άλλη πίεση, υποκρισία ή απογοήτευση. Ο τίτλος είναι απλός, αλλά ο Snider τον χρησιμοποιεί ως αφετηρία για hard-rock εκτόνωση. Τα riffs έχουν μεγαλύτερη urgency και το rhythm section δεν αφήνει το τραγούδι να χαλαρώσει. Αυτή η αμεσότητα συνδέει το album με το punky street χαρακτήρα της μπάντας, χωρίς να την απομακρύνει από το heavy-metal πλαίσιο. Δεν είναι η πιο ιδιαίτερη μελωδία του δίσκου, όμως λειτουργεί ως αποτελεσματικό, θυμωμένο deep cut που διατηρεί την πίεση της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με ένα από τα πιο άμεσα street-metal anthems των Twisted Sister. Ο τίτλος δηλώνει επιστροφή , όχι απλώς της μπάντας, αλλά μιας ολόκληρης κοινότητας outsiders που επιστρέφει για να απαιτήσει χώρο. Το τραγούδι βασίζεται σε καθαρό, ανεβαστικό riff, στο σταθερό drive του A.J. Pero και σε refrain που είναι φτιαγμένο για συναυλιακό sing-along. Η συγγένεια με το “The Boys Are Back in Town” των Thin Lizzy είναι προφανής ως ιδέα, αλλά οι Twisted Sister το κάνουν πιο σκληρό και πιο θεατρικό. Δεν είναι το πιο περίπλοκο ή το πιο σκοτεινό track του δίσκου, αλλά είναι αποτελεσματικό statement εισόδου και ένα από τα τρία βασικά singles της περιόδου.</t>
+  </si>
+  <si>
+    <t>Ένα από τα ισχυρότερα heavy tracks του δίσκου, με τίτλο που μετατρέπει την προδοσία σε φυσική αίσθηση πόνου. Ο Dee Snider δεν γράφει μια λεπτή, εσωτερική εξομολόγηση· αντιμετωπίζει το χτύπημα πισώπλατα με οργή, θεατρικότητα και μεγάλη φωνητική επιβολή. Η μουσική έχει σκοτεινότερο riffing από το opener και κρατά μια σαφή μελωδική γραμμή, χωρίς να μαλακώνει το βάρος της. Είναι πολύ χαρακτηριστικό της εποχής πριν από το Stay Hungry, η μπάντα έχει ήδη τα μεγάλα refrains, αλλά τα χρησιμοποιεί μέσα σε πιο τραχύ, λιγότερο pop πλαίσιο. Το track είναι κομβικό γιατί δίνει αμέσως βάθος στην A πλευρά μετά την εξωστρέφεια του “The Kids Are Back”.</t>
+  </si>
+  <si>
+    <t>Κλασικό road/biker hard-rock τραγούδι με τον τίτλο να δηλώνει μια ζωή ορισμένη από την κίνηση, την ταχύτητα και την ανάγκη να μη μένεις ακίνητος. Είναι η πιο παραδοσιακή metal-rock στιγμή της A πλευράς, ευθύ riff, γρήγορο momentum, όχι ιδιαίτερα πολύπλοκη αφήγηση. Η αξία του βρίσκεται στην ενέργεια και στο live-friendly drive, όχι στην πρωτοτυπία. Οι Twisted Sister αξιοποιούν το μοτίβο της μηχανής και του δρόμου ως σύμβολο ελευθερίας, αλλά η εκτέλεση παραμένει αρκετά σφιχτή ώστε να μην πέφτει σε τυπικό filler. Λειτουργεί σαν ανάσα αδρεναλίνης πριν από το πιο προσωπικό “I Am (I’m Me)”.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση της A πλευράς και μία από τις ουσιαστικότερες δηλώσεις ταυτότητας του Dee Snider. Το “I Am (I’m Me)” απορρίπτει την ανάγκη κοινωνικής αποδοχής, ο αφηγητής δεν ζητά άδεια να υπάρχει, ούτε εξηγεί την εμφάνιση, τη στάση ή τον τρόπο ζωής του. Αυτή η άμεση αυτοεπιβεβαίωση εξηγεί γιατί το τραγούδι έγινε κεντρικό για τους fans της μπάντας. Μουσικά, συνδυάζει μελωδικό heavy-metal chorus με κιθάρες που έχουν αρκετό bite ώστε να μην ακούγεται σαν απλό glam-pop single. Η έκδοσή σου είχε μάλιστα κυκλοφορήσει με hype sticker που το αναφέρει ως hit single. Είναι ένα από τα tracks που καθιέρωσαν τη φόρμουλα την οποία οι Twisted Sister θα μετέφεραν σε ακόμη μεγαλύτερη κλίμακα στο Stay Hungry.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο της A πλευράς κινείται σε πιο epic heavy-metal πεδίο. Ο τίτλος , «η δύναμη και η δόξα» , αντλεί από μια σχεδόν τελετουργική γλώσσα, αλλά οι Twisted Sister τη μετατρέπουν σε rock ’n’ roll proclamation. Το κομμάτι δεν κυνηγά την pop αμεσότητα του “I Am (I’m Me)”, χτίζει μεγαλύτερη δραματικότητα, με riff που έχει βάρος και chorus που ακούγεται σχεδιασμένο σαν ομαδικό σύνθημα. Η θεατρικότητα δεν είναι εδώ απλό visual gimmick· είναι μέρος του τρόπου με τον οποίο η μπάντα μετατρέπει μια club-hard-rock ταυτότητα σε μεγαλύτερο heavy-metal θέαμα. Είναι από τα σημεία που στηρίζουν τη φήμη του album ως συνεκτικότερο από το συχνά πιο άνισο debut.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με τραγούδι επιμονής και επιβίωσης. Το “we’re gonna make it” είναι η φράση μιας μπάντας που πέρασε χρόνια στα Long Island clubs και τώρα βλέπει την πιθανότητα να προχωρήσει, όχι μια εύκολη νίκη, αλλά ένα πείσμα να συνεχίσει. Η μουσική έχει working-class / street-rock αίσθηση, με riff που προχωρά σαν βήμα προς τα εμπρός και φωνητικά που λειτουργούν σαν συλλογικό κάλεσμα. Δεν είναι τόσο αναγνωρίσιμο όσο τα singles, αλλά είναι σημαντικό για τη δραματουργία του δίσκου, μεταφέρει την individual identity του “I Am (I’m Me)” σε κοινό σκοπό.</t>
+  </si>
+  <si>
+    <t>Η μπαλάντα του δίσκου, γραμμένη για τη Suzette, σύζυγο του Dee Snider και υπεύθυνη για το costume/makeup design της μπάντας. Ο τίτλος προσφέρει στήριξη και συντροφικότητα, δεν είσαι μόνος/μόνη, ακόμη και όταν η ζωή ή η απόσταση δημιουργεί ανασφάλεια. Η μουσική χαμηλώνει την επιθετικότητα, αλλά δεν γίνεται εντελώς soft rock· οι κιθάρες και οι φωνητικές κορυφώσεις τη διατηρούν μέσα στο melodic heavy-rock πλαίσιο. Η αξία της είναι ότι δείχνει μια ανθρώπινη, μη επιθετική πλευρά του Snider πριν οι power ballads γίνουν τυποποιημένο εμπορικό εργαλείο του late-’80s glam metal. Στη συγκεκριμένη έκδοση, οι κιθάρες πιστώνονται αποκλειστικά στον Eddie Ojeda.</t>
+  </si>
+  <si>
+    <t>Το title track και η σωστή κατακλείδα. Μετά από τραγούδια ταυτότητας, προδοσίας, δρόμου, επιμονής και συντροφικότητας, η μπάντα παρουσιάζει το rock ’n’ roll ως δύναμη που δεν περιορίζεται από μόδες, κοινωνική αποδοκιμασία ή επιχείρηση καταστολής. Το riff είναι άμεσο, το chorus σχεδιασμένο για συμμετοχή και η ερμηνεία του Snider έχει την απαραίτητη θεατρική αποφασιστικότητα. Το τραγούδι έγινε το τρίτο και τελευταίο single του δίσκου, και αποτέλεσε το πρώτο βίντεο των Twisted Sister που έπαιξε στο MTV. Δεν είναι απλώς self-referential rocker, συμπυκνώνει τη θέση της μπάντας ως club survivors που μετατρέπουν την outsider ταυτότητα σε μαζικό hard-rock σύνθημα.</t>
   </si>
 </sst>
 </file>
@@ -11324,7 +11432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11391,6 +11499,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11702,7 +11813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14914,6 +15025,38 @@
       </c>
       <c r="J100" s="11" t="s">
         <v>3375</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D101" s="6">
+        <v>1983</v>
+      </c>
+      <c r="E101" s="10">
+        <v>3.46</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>3400</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>3397</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>3396</v>
+      </c>
+      <c r="I101" s="11" t="s">
+        <v>3399</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>3398</v>
       </c>
     </row>
   </sheetData>
@@ -15113,6 +15256,8 @@
     <hyperlink ref="J99" r:id="rId193" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
     <hyperlink ref="I100" r:id="rId194" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
     <hyperlink ref="J100" r:id="rId195" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
+    <hyperlink ref="J101" r:id="rId196" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
+    <hyperlink ref="I101" r:id="rId197" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15120,7 +15265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I948"/>
+  <dimension ref="A1:I958"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -40883,6 +41028,280 @@
       </c>
       <c r="I948" s="6"/>
     </row>
+    <row r="949" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A949" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B949" s="6">
+        <v>1</v>
+      </c>
+      <c r="C949" s="22" t="s">
+        <v>3401</v>
+      </c>
+      <c r="D949" s="7" t="s">
+        <v>3411</v>
+      </c>
+      <c r="E949" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F949" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G949" s="12">
+        <v>4</v>
+      </c>
+      <c r="H949" s="23" t="s">
+        <v>3423</v>
+      </c>
+      <c r="I949" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A950" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B950" s="6">
+        <v>2</v>
+      </c>
+      <c r="C950" s="22" t="s">
+        <v>3402</v>
+      </c>
+      <c r="D950" s="7" t="s">
+        <v>3412</v>
+      </c>
+      <c r="E950" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F950" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G950" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H950" s="23" t="s">
+        <v>3424</v>
+      </c>
+      <c r="I950" s="6"/>
+    </row>
+    <row r="951" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A951" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B951" s="6">
+        <v>3</v>
+      </c>
+      <c r="C951" s="22" t="s">
+        <v>3403</v>
+      </c>
+      <c r="D951" s="7" t="s">
+        <v>3413</v>
+      </c>
+      <c r="E951" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F951" s="12">
+        <v>4</v>
+      </c>
+      <c r="G951" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H951" s="23" t="s">
+        <v>3425</v>
+      </c>
+      <c r="I951" s="6"/>
+    </row>
+    <row r="952" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+      <c r="A952" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B952" s="6">
+        <v>4</v>
+      </c>
+      <c r="C952" s="22" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D952" s="7" t="s">
+        <v>3414</v>
+      </c>
+      <c r="E952" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F952" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G952" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H952" s="23" t="s">
+        <v>3426</v>
+      </c>
+      <c r="I952" s="6"/>
+    </row>
+    <row r="953" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A953" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B953" s="6">
+        <v>5</v>
+      </c>
+      <c r="C953" s="22" t="s">
+        <v>3405</v>
+      </c>
+      <c r="D953" s="7" t="s">
+        <v>3415</v>
+      </c>
+      <c r="E953" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F953" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G953" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H953" s="23" t="s">
+        <v>3427</v>
+      </c>
+      <c r="I953" s="6"/>
+    </row>
+    <row r="954" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A954" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B954" s="6">
+        <v>6</v>
+      </c>
+      <c r="C954" s="22" t="s">
+        <v>3406</v>
+      </c>
+      <c r="D954" s="7" t="s">
+        <v>3416</v>
+      </c>
+      <c r="E954" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F954" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G954" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H954" s="23" t="s">
+        <v>3428</v>
+      </c>
+      <c r="I954" s="6"/>
+    </row>
+    <row r="955" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A955" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B955" s="6">
+        <v>7</v>
+      </c>
+      <c r="C955" s="22" t="s">
+        <v>3410</v>
+      </c>
+      <c r="D955" s="7" t="s">
+        <v>3417</v>
+      </c>
+      <c r="E955" s="20">
+        <v>3.33</v>
+      </c>
+      <c r="F955" s="12">
+        <v>4</v>
+      </c>
+      <c r="G955" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H955" s="23" t="s">
+        <v>3422</v>
+      </c>
+      <c r="I955" s="6"/>
+    </row>
+    <row r="956" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A956" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B956" s="6">
+        <v>8</v>
+      </c>
+      <c r="C956" s="22" t="s">
+        <v>3409</v>
+      </c>
+      <c r="D956" s="7" t="s">
+        <v>3418</v>
+      </c>
+      <c r="E956" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F956" s="12">
+        <v>4</v>
+      </c>
+      <c r="G956" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H956" s="23" t="s">
+        <v>3421</v>
+      </c>
+      <c r="I956" s="6"/>
+    </row>
+    <row r="957" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A957" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B957" s="6">
+        <v>9</v>
+      </c>
+      <c r="C957" s="22" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D957" s="7" t="s">
+        <v>3419</v>
+      </c>
+      <c r="E957" s="20">
+        <v>3.09</v>
+      </c>
+      <c r="F957" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G957" s="12">
+        <v>4</v>
+      </c>
+      <c r="H957" s="23" t="s">
+        <v>3429</v>
+      </c>
+      <c r="I957" s="6"/>
+    </row>
+    <row r="958" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A958" s="6">
+        <v>646934</v>
+      </c>
+      <c r="B958" s="6">
+        <v>10</v>
+      </c>
+      <c r="C958" s="22" t="s">
+        <v>3407</v>
+      </c>
+      <c r="D958" s="7" t="s">
+        <v>3420</v>
+      </c>
+      <c r="E958" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F958" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G958" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H958" s="23" t="s">
+        <v>3430</v>
+      </c>
+      <c r="I958" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373681C1-F0A0-4C76-86F2-0BE42A14AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846622B3-2BFA-4B38-AFAE-B1BBBC97B803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="3431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="3466">
   <si>
     <t>No</t>
   </si>
@@ -11284,6 +11284,111 @@
   </si>
   <si>
     <t>Το title track και η σωστή κατακλείδα. Μετά από τραγούδια ταυτότητας, προδοσίας, δρόμου, επιμονής και συντροφικότητας, η μπάντα παρουσιάζει το rock ’n’ roll ως δύναμη που δεν περιορίζεται από μόδες, κοινωνική αποδοκιμασία ή επιχείρηση καταστολής. Το riff είναι άμεσο, το chorus σχεδιασμένο για συμμετοχή και η ερμηνεία του Snider έχει την απαραίτητη θεατρική αποφασιστικότητα. Το τραγούδι έγινε το τρίτο και τελευταίο single του δίσκου, και αποτέλεσε το πρώτο βίντεο των Twisted Sister που έπαιξε στο MTV. Δεν είναι απλώς self-referential rocker, συμπυκνώνει τη θέση της μπάντας ως club survivors που μετατρέπουν την outsider ταυτότητα σε μαζικό hard-rock σύνθημα.</t>
+  </si>
+  <si>
+    <t>Love Is For Suckers</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4116216-Twisted-Sister-Love-Is-For-Suckers</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/XxUXnm64eqcN-8Ex6uu1GtvlLXsYj0moY9c6vvdH7f0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQxMTYy/MTYtMTcyMjE4NTA1/Mi03Njg1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Metal [Pop Rock, Glam Metal, Melodic Hard Rock, ’80s Arena Rock]</t>
+  </si>
+  <si>
+    <t>Atlantic – 78 17721 (Canada, 1987, LP, Album, Stereo). Pressed at Specialty Records Corporation (indicated by "SP" and the characteristic stamp/etchings in the runout). Direct Metal Mastering (DMM) cut mastered at Sterling Sound by Ted Jensen / TJ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Recorded and mixed at Atlantic Studios, NYC. Mastered at Sterling Sound. Produced and arranged by Beau Hill.   Issued with printed inner sleeve containing credits and lyrics. Note on release: Although listed on sleeve, Eddie Ojeda, Jay Jay French, and Mark Mendoza reportedly do not play on this record; Love Is For Suckers was originally intended to be Dee Snider's solo album before the label mandated a Twisted Sister release.   </t>
+  </si>
+  <si>
+    <t>Wake Up (The Sleeping Giant)</t>
+  </si>
+  <si>
+    <t>Hot Love</t>
+  </si>
+  <si>
+    <t>I’m So Hot For You</t>
+  </si>
+  <si>
+    <t>Tonight</t>
+  </si>
+  <si>
+    <t>One Bad Habit</t>
+  </si>
+  <si>
+    <t>Me And The Boys</t>
+  </si>
+  <si>
+    <t>Yeah Right!</t>
+  </si>
+  <si>
+    <t>You Are All That I Need</t>
+  </si>
+  <si>
+    <t>I Want This Night (To Last Forever)</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Anthemic Metal, Protest Rock, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Pop Metal, Melodic Rock, Radio Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Rock, Pop Metal, Attitude Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Glam Hard Rock, Party Rock, Hair-Metal edge]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Hard Rock [Melodic Rock, ’80s Arena Pop, Power-pop edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Party Rock, Bar-Rock, Glam Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Metal [Melodic Hard Rock, Mid-tempo Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Melodic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soft Rock [Power Ballad, AOR, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Up-tempo Pop Metal, Sarcastic Rock Closer]</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο της A πλευράς προτιμά πιο μελωδικό, radio-oriented δρόμο. Η νύχτα του τίτλου παρουσιάζεται ως πεδίο άμεσης επιθυμίας και προσωρινής απόδρασης, με την μπάντα να στηρίζεται σε ρυθμική σταθερότητα και melodic chorus αντί για βαριά riffs. Το τραγούδι λειτουργεί μέσα στην pop-rock κατεύθυνση του δίσκου, αλλά δεν δίνει αρκετή δραματική ή συνθετική εξέλιξη ώστε να αποκτήσει ξεχωριστή προσωπικότητα. Σε άλλο album, ως δευτερεύον cut, θα ήταν απολύτως λειτουργικό· εδώ όμως κάνει πιο φανερή την απόσταση από τη δύναμη των προηγούμενων Twisted Sister records.</t>
+  </si>
+  <si>
+    <t>Η βασική power-ballad προσπάθεια του album. Ο τίτλος παρουσιάζει την ερωτική νύχτα ως στιγμή που ο αφηγητής δεν θέλει να τελειώσει , μια τυπική αλλά αποτελεσματική late-’80s melodic-rock φόρμα. Οι κιθάρες και τα φωνητικά χτίζουν σταδιακά προς arena-ready refrain, όμως το τραγούδι δεν έχει την ευαισθησία του “The Price” ούτε την άμεση μελωδική επιτυχία του “I Remember You”. Παρ’ όλα αυτά, είναι μία από τις καλύτερα δομημένες πιο soft στιγμές του album, επειδή έχει καθαρή κορύφωση και δεν προσπαθεί να προσποιηθεί ότι είναι heavy metal.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο επιστρέφει σε ειρωνεία και up-tempo attitude. Η φράση του τίτλου , «ναι, καλά!» , λειτουργεί ως σαρκαστική απόρριψη μιας υπόσχεσης ή μιας δικαιολογίας, και η μπάντα την τοποθετεί πάνω σε γρήγορο pop-metal πλαίσιο. Είναι πιο ελαφρύ και λιγότερο βαρύ από ένα παραδοσιακό Twisted Sister finale, αλλά προσφέρει λίγη απαραίτητη κίνηση μετά τις πιο soft B-side στιγμές. Δεν κλείνει το album με πραγματική κορύφωση· περισσότερο επιβεβαιώνει την άνιση, radio-oriented φύση του. Ως αυτόνομο τραγούδι έχει ενέργεια, ως album closer όμως δεν διαθέτει το βάρος που είχαν τα “S.M.F.” ή “You Can’t Stop Rock ’N’ Roll”.</t>
+  </si>
+  <si>
+    <t>Το καθαρό standout και το τραγούδι που πλησιάζει περισσότερο την παλιά δύναμη των Twisted Sister. Ο «κοιμισμένος γίγαντας» λειτουργεί ως εικόνα συλλογικής αφύπνισης, άνθρωποι που έχουν ανεχθεί αρκετά, συνειδητοποιούν τη δύναμή τους και αρνούνται να παραμείνουν παθητικοί. Το track έχει βαριά, stomp-like ρυθμική βάση, μεγάλα κιθαριστικά accents και refrain που θυμίζει την αντιεξουσιαστική ενέργεια του “We’re Not Gonna Take It”, αλλά με πιο σκοτεινή και επιθετική παραγωγή. Η σύνδεση με την εποχή των PMRC debates είναι εμφανής στην ανάγνωσή του ως αντίδραση στη λογοκρισία και στον έλεγχο της rock κουλτούρας. Είναι το μοναδικό κομμάτι που ακόμη και πιο αυστηρές κριτικές συχνά αναγνωρίζουν ως Twisted Sister classic.</t>
+  </si>
+  <si>
+    <t>Το lead single και το πιο καθαρά εμπορικό τραγούδι του δίσκου. Η μελωδία, τα πολυεπίπεδα φωνητικά και το καθαρό radio-rock chorus δείχνουν τη μετατόπιση προς pop metal. Ο τίτλος φέρνει τη familiar Twisted Sister ερωτική υπερβολή, αλλά η μουσική είναι πιο λεία, περισσότερο AOR/glam-pop και λιγότερο επιθετική από τα κλασικά τους anthems. Αυτό ακριβώς ήταν και το πρόβλημα για ένα μέρος του κοινού, η raw εικόνα των Twisted Sister έμοιαζε να συγκρούεται με ένα τραγούδι που διεκδικούσε mainstream airplay. Ωστόσο, η σύνθεση είναι αποτελεσματική και η μπάντα παίζει με ακρίβεια· η Chicago Tribune το χαρακτήρισε το καλύτερο τραγούδι του δίσκου, ενώ το AllMusic το ξεχώρισε αναδρομικά ως standout.</t>
+  </si>
+  <si>
+    <t>Το title track συνοψίζει το πιο αδύναμο σημείο του δίσκου, η old-school anti-romance posture δεν μετατρέπεται σε ιδιαίτερα δυνατό μουσικό σχόλιο. Η φράση «η αγάπη είναι για κορόιδα» προσπαθεί να λειτουργήσει ως σαρκαστική, macho rock ’n’ roll πρόκληση, όμως το τραγούδι κινείται σε αρκετά προβλέψιμη glam-hard-rock φόρμα. Οι κιθάρες έχουν σωστή ένταση και η φωνή του Snider παραμένει πειστική, αλλά το hook δεν είναι αρκετά μεγάλο ώστε να αντισταθμίσει την απλούστερη στιχουργική ιδέα. Είναι χαρακτηριστικό του τρόπου με τον οποίο το album συχνά μοιάζει να επιδιώκει ’80s radio rock χωρίς την ιδιαίτερη street-metal ταυτότητα που έκανε την μπάντα ξεχωριστή.</t>
+  </si>
+  <si>
+    <t>Party-rock track με ερωτική θεματική και glam/hair-metal αυτοπεποίθηση. Η ιδέα είναι εσκεμμένα υπερβολική, επιθυμία, έλξη και rock-star swagger. Η μουσική είναι γρήγορη και επαγγελματικά παιγμένη, αλλά το κομμάτι δεν έχει τη βρωμιά ή τη live ένταση που θα το έκανε πραγματικά πειστικό ως sleaze-rock τραγούδι. Ακούγεται περισσότερο σαν pop-metal κατασκευή της εποχής παρά σαν natural έκρηξη των Twisted Sister. Δεν είναι κακό ή αμήχανο από τεχνική πλευρά, αλλά συμβάλλει στην αίσθηση ότι ο δίσκος ακολουθεί την αγορά του 1987 αντί να επιβάλλει το δικό του ύφος.</t>
+  </si>
+  <si>
+    <t>Μια επιστροφή στο πιο γνώριμο bar-rock/party-rock πλαίσιο, η μπάντα, η παρέα, η νύχτα και η συλλογική ενέργεια. Έχει κλασική rock ’n’ roll λογική, με straightforward riff, sing-along διάθεση και ελαφρά glam λάμψη. Το πρόβλημα δεν είναι η φόρμα , οι Twisted Sister πάντα αξιοποιούσαν καλά τα community anthems , αλλά ότι εδώ η σύνθεση δεν φτάνει την ένταση ή το personality του “S.M.F.” ή του “The Kids Are Back”. Παρ’ όλα αυτά, λειτουργεί ως ευχάριστη, πιο οργανική στιγμή του album και δίνει στη B πλευρά λίγη από την παλιά live-band ταυτότητα.</t>
+  </si>
+  <si>
+    <t>Mid-tempo melodic hard rock με τον τίτλο να αναφέρεται σε μια συνήθεια που είναι δύσκολο να εγκαταλειφθεί , πιθανώς ερωτική, πιθανώς η ίδια η rock ’n’ roll ζωή. Η σύνθεση πατά σε σταθερό arena-rock groove και έχει αρκετή μελωδική ικανότητα ώστε να μη χαθεί, όμως δεν διαθέτει ιδιαίτερα έντονο riff ή chorus. Ο Snider τραγουδά με συνέπεια, αλλά η φωνή του δεν αρκεί πάντα για να μετατρέψει μια απλή pop-metal φόρμα σε θεατρική εμπειρία. Είναι αντιπροσωπευτικό album track, σωστό, ακίνδυνο και καλοπαιγμένο, χωρίς να δικαιολογεί υψηλότερη θέση.</t>
+  </si>
+  <si>
+    <t>Η πιο καθαρή AOR / soft-rock στιγμή του δίσκου. Ο τίτλος είναι ευθύς και ρομαντικός, σχεδόν το αντίθετο του “Love Is For Suckers”, κάτι που αποκαλύπτει μια ασυνέπεια στον θεματικό τόνο, από την ειρωνική άρνηση της αγάπης, ο δίσκος περνά σε ανοιχτή ερωτική αφοσίωση. Μουσικά, αυτό δεν είναι απαραίτητα πρόβλημα· οι αρμονίες και η πιο ευάλωτη φωνητική προσέγγιση δείχνουν ότι ο Snider μπορούσε να υπηρετήσει softer material. Ωστόσο, το τραγούδι είναι αρκετά γενικό ώστε να θυμίζει περισσότερο τυπική power ballad της εποχής παρά κομμάτι με αναγνωρίσιμη Twisted Sister ταυτότητα.</t>
   </si>
 </sst>
 </file>
@@ -11813,7 +11918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15057,6 +15162,38 @@
       </c>
       <c r="J101" s="11" t="s">
         <v>3398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>3431</v>
+      </c>
+      <c r="D102" s="6">
+        <v>1987</v>
+      </c>
+      <c r="E102" s="10">
+        <v>3</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>3434</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>3435</v>
+      </c>
+      <c r="I102" s="11" t="s">
+        <v>3432</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>3433</v>
       </c>
     </row>
   </sheetData>
@@ -15258,6 +15395,8 @@
     <hyperlink ref="J100" r:id="rId195" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
     <hyperlink ref="J101" r:id="rId196" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
     <hyperlink ref="I101" r:id="rId197" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
+    <hyperlink ref="I102" r:id="rId198" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
+    <hyperlink ref="J102" r:id="rId199" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15265,7 +15404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I958"/>
+  <dimension ref="A1:I968"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -41302,6 +41441,276 @@
         <v>240</v>
       </c>
     </row>
+    <row r="959" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A959" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B959" s="6">
+        <v>1</v>
+      </c>
+      <c r="C959" s="22" t="s">
+        <v>3437</v>
+      </c>
+      <c r="D959" s="7" t="s">
+        <v>3446</v>
+      </c>
+      <c r="E959" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F959" s="12">
+        <v>4</v>
+      </c>
+      <c r="G959" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H959" s="9" t="s">
+        <v>3459</v>
+      </c>
+      <c r="I959" s="6"/>
+    </row>
+    <row r="960" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A960" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B960" s="6">
+        <v>2</v>
+      </c>
+      <c r="C960" s="22" t="s">
+        <v>3438</v>
+      </c>
+      <c r="D960" s="7" t="s">
+        <v>3447</v>
+      </c>
+      <c r="E960" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F960" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G960" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H960" s="9" t="s">
+        <v>3460</v>
+      </c>
+      <c r="I960" s="6"/>
+    </row>
+    <row r="961" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A961" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B961" s="6">
+        <v>3</v>
+      </c>
+      <c r="C961" s="22" t="s">
+        <v>3431</v>
+      </c>
+      <c r="D961" s="7" t="s">
+        <v>3448</v>
+      </c>
+      <c r="E961" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F961" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="G961" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H961" s="9" t="s">
+        <v>3461</v>
+      </c>
+      <c r="I961" s="6"/>
+    </row>
+    <row r="962" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A962" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B962" s="6">
+        <v>4</v>
+      </c>
+      <c r="C962" s="22" t="s">
+        <v>3439</v>
+      </c>
+      <c r="D962" s="7" t="s">
+        <v>3449</v>
+      </c>
+      <c r="E962" s="20">
+        <v>2.99</v>
+      </c>
+      <c r="F962" s="12">
+        <v>3</v>
+      </c>
+      <c r="G962" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H962" s="9" t="s">
+        <v>3462</v>
+      </c>
+      <c r="I962" s="6"/>
+    </row>
+    <row r="963" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A963" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B963" s="6">
+        <v>5</v>
+      </c>
+      <c r="C963" s="22" t="s">
+        <v>3440</v>
+      </c>
+      <c r="D963" s="7" t="s">
+        <v>3450</v>
+      </c>
+      <c r="E963" s="20">
+        <v>3.47</v>
+      </c>
+      <c r="F963" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="G963" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H963" s="9" t="s">
+        <v>3456</v>
+      </c>
+      <c r="I963" s="6"/>
+    </row>
+    <row r="964" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A964" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B964" s="6">
+        <v>6</v>
+      </c>
+      <c r="C964" s="22" t="s">
+        <v>3442</v>
+      </c>
+      <c r="D964" s="7" t="s">
+        <v>3451</v>
+      </c>
+      <c r="E964" s="20">
+        <v>3.26</v>
+      </c>
+      <c r="F964" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G964" s="12">
+        <v>4</v>
+      </c>
+      <c r="H964" s="9" t="s">
+        <v>3463</v>
+      </c>
+      <c r="I964" s="6"/>
+    </row>
+    <row r="965" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A965" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B965" s="6">
+        <v>7</v>
+      </c>
+      <c r="C965" s="22" t="s">
+        <v>3441</v>
+      </c>
+      <c r="D965" s="7" t="s">
+        <v>3452</v>
+      </c>
+      <c r="E965" s="20">
+        <v>3.19</v>
+      </c>
+      <c r="F965" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G965" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H965" s="9" t="s">
+        <v>3464</v>
+      </c>
+      <c r="I965" s="6"/>
+    </row>
+    <row r="966" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A966" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B966" s="6">
+        <v>8</v>
+      </c>
+      <c r="C966" s="22" t="s">
+        <v>3445</v>
+      </c>
+      <c r="D966" s="7" t="s">
+        <v>3453</v>
+      </c>
+      <c r="E966" s="20">
+        <v>3.16</v>
+      </c>
+      <c r="F966" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G966" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H966" s="9" t="s">
+        <v>3457</v>
+      </c>
+      <c r="I966" s="6"/>
+    </row>
+    <row r="967" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A967" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B967" s="6">
+        <v>9</v>
+      </c>
+      <c r="C967" s="22" t="s">
+        <v>3444</v>
+      </c>
+      <c r="D967" s="7" t="s">
+        <v>3454</v>
+      </c>
+      <c r="E967" s="20">
+        <v>2.95</v>
+      </c>
+      <c r="F967" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G967" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H967" s="9" t="s">
+        <v>3465</v>
+      </c>
+      <c r="I967" s="6"/>
+    </row>
+    <row r="968" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A968" s="6">
+        <v>4116216</v>
+      </c>
+      <c r="B968" s="6">
+        <v>10</v>
+      </c>
+      <c r="C968" s="22" t="s">
+        <v>3443</v>
+      </c>
+      <c r="D968" s="7" t="s">
+        <v>3455</v>
+      </c>
+      <c r="E968" s="20">
+        <v>3.14</v>
+      </c>
+      <c r="F968" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="G968" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H968" s="9" t="s">
+        <v>3458</v>
+      </c>
+      <c r="I968" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846622B3-2BFA-4B38-AFAE-B1BBBC97B803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD3D804-2D7F-4216-88ED-7B50B403F839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="3466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="3501">
   <si>
     <t>No</t>
   </si>
@@ -11389,6 +11389,255 @@
   </si>
   <si>
     <t>Η πιο καθαρή AOR / soft-rock στιγμή του δίσκου. Ο τίτλος είναι ευθύς και ρομαντικός, σχεδόν το αντίθετο του “Love Is For Suckers”, κάτι που αποκαλύπτει μια ασυνέπεια στον θεματικό τόνο, από την ειρωνική άρνηση της αγάπης, ο δίσκος περνά σε ανοιχτή ερωτική αφοσίωση. Μουσικά, αυτό δεν είναι απαραίτητα πρόβλημα· οι αρμονίες και η πιο ευάλωτη φωνητική προσέγγιση δείχνουν ότι ο Snider μπορούσε να υπηρετήσει softer material. Ωστόσο, το τραγούδι είναι αρκετά γενικό ώστε να θυμίζει περισσότερο τυπική power ballad της εποχής παρά κομμάτι με αναγνωρίσιμη Twisted Sister ταυτότητα.</t>
+  </si>
+  <si>
+    <t>Atlantic – 81275-1-E, Atlantic – 7 81275-1-E (US, 1985, LP, Album, Limited Edition, Special Edition, Stereo, Pop-Up Sleeve, Specialty Pressing). Mastered at Masterdisk by Bob Ludwig (marked as RL in the runout). Pressed at Specialty Records Corporation (indicated by the SRC logo in the deadwax).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Features the iconic limited edition pop-up die-cut sewer lid sleeve and custom printed inner sleeve with lyrics and photos.   Lacquer cut by Bob Ludwig (RL) at Masterdisk, ensuring exceptional dynamic range and audiophile punch.</t>
+  </si>
+  <si>
+    <t>Come Out And Play</t>
+  </si>
+  <si>
+    <t>Leader Of The Pack</t>
+  </si>
+  <si>
+    <t>You Want What We Got</t>
+  </si>
+  <si>
+    <t>I Believe In Rock ’N’ Roll</t>
+  </si>
+  <si>
+    <t>The Fire Still Burns</t>
+  </si>
+  <si>
+    <t>Be Chrool To Your Scuel</t>
+  </si>
+  <si>
+    <t>I Believe In You</t>
+  </si>
+  <si>
+    <t>Out On The Streets</t>
+  </si>
+  <si>
+    <t>Lookin’ Out For #1</t>
+  </si>
+  <si>
+    <t>Kill Or Be Killed</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1414305-Twisted-Sister-Come-Out-And-Play</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/3kTBlqW9KXrgEIeDONx062gM90z0jDCQVeaIVRe-Upw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE0MTQz/MDUtMTM2OTUwMTQ1/NS0yOTU2LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Glam Metal, Pop Metal, Arena Rock, Theatrical Shock Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Arena Metal, Theatrical Hard Rock, Anthemic Opener]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Glam Metal [’60s Pop Cover, Pop Metal, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fan Anthem, Street Metal, Arena Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Rock ’n’ Roll Anthem, Melodic Metal, Party Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Dramatic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Rock ’n’ Roll, Hard Rock [Novelty Rock, Horn-Driven Party Rock, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Melodic Arena Rock, Glam Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Street Metal, Urban Hard Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Melodic Hard Rock, Arena Rock, Radio Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Heavy Metal, Aggressive Riff Rock, Album Closer]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η μεγάλη power ballad του δίσκου. Μετά την καρτουνίστικη ένταση του “Be Chrool…”, το τραγούδι προσφέρει πιο προσωπικό και συναισθηματικό χώρο. Ο τίτλος είναι απλή διαβεβαίωση εμπιστοσύνης, αλλά ο Snider την τραγουδά με αρκετή δραματικότητα ώστε να μην ακούγεται σαν άδειο ρομαντικό cliché. Οι harmony vocals του </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Don Dokken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> και του </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Gary Holland</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> ενισχύουν τη melodic-metal αίσθηση, ενώ η κιθάρα κινείται ανάμεσα σε ευαισθησία και arena-rock κορύφωση. Δεν είναι τόσο αναγνωρίσιμο όσο το “The Price” ή το “I Remember You”, αλλά είναι μία από τις καλύτερα δουλεμένες συνθέσεις του δίσκου.</t>
+    </r>
+  </si>
+  <si>
+    <t>Επιστροφή στη street-metal λογική, με τον δρόμο ως τόπο ελευθερίας, κινδύνου και ταυτότητας. Το riff είναι πιο γυμνό και άμεσο, οι κιθάρες λιγότερο pop-oriented και ο Snider ανακτά μέρος της παλιάς, επιθετικής frontman παρουσίας του. Το track δεν έχει το χτύπημα του “You Want What We Got” ούτε το συναισθηματικό βάρος του “The Fire Still Burns”, αλλά λειτουργεί ως χρήσιμη υπενθύμιση ότι η μπάντα είχε roots σε live clubs και όχι μόνο στα set των video clips. Είναι ένα καλό, άμεσο hard-rock κομμάτι, με λιγότερη συνθετική ιδιαιτερότητα.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία heavy-metal στιγμή του δίσκου και ένα από τα tracks που δικαιολογούν να επιστρέφει κανείς στο album. Ο «φωτιά που ακόμη καίει» είναι η επιμονή, η δημιουργική ορμή και η αίσθηση ότι η μπάντα ,παρά τη φήμη, τις πιέσεις και την εμπορική αλλαγή, εξακολουθεί να έχει κάτι να αποδείξει. Η μουσική είναι πιο σκοτεινή και περισσότερο riff-centered, με δράμα που δεν χρειάζεται novelty στοιχεία για να λειτουργήσει. Ο Snider τραγουδά με πλήρη ένταση, οι κιθάρες έχουν πραγματικό bite και το arrangement επιτρέπει στο κομμάτι να χτίσει κορύφωση. Είναι η πιο πειστική σύνδεση του Come Out And Play με την πιο σκληρή περίοδο των Twisted Sister.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τον δίσκο με θεατρική πρόθεση και arena-metal κλίμακα. Η φράση «come out and play» μπορεί να ακούγεται σαν παιδική πρόσκληση, αλλά στους Twisted Sister λειτουργεί σαν κάλεσμα προς τους outsiders να βγουν από την κρυψώνα, να ενωθούν και να διεκδικήσουν χώρο. Οι κιθάρες έχουν καθαρό hard-metal βάρος, η παραγωγή είναι πιο γυαλισμένη από το Stay Hungry και ο Dee Snider δίνει στο chorus τον επιτακτικό χαρακτήρα που απαιτεί ο τίτλος. Δεν φτάνει την ακαριαία δύναμη του “I Wanna Rock”, αλλά είναι αποτελεσματικό opener και σωστή εισαγωγή στη μεγαλόπνοη, pop-up αισθητι+H969,H972κή του album.</t>
+  </si>
+  <si>
+    <t>Η διασκευή στο ’60s hit των Shangri-Las είναι η πιο αμφιλεγόμενη επιλογή του δίσκου. Το αρχικό τραγούδι είναι teen-tragedy pop, μια ιστορία έρωτα, κοινωνικής απόστασης και θανάτου του Jimmy, του αρχηγού μιας μηχανόβιας παρέας. Οι Twisted Sister δεν το μετατρέπουν πλήρως σε heavy-metal κομμάτι· κρατούν τη θεατρικότητα, το μελόδραμα και την pop αφήγηση, προσθέτοντας glam-metal κιθάρες και μεγαλύτερο ρυθμικό βάρος. Αυτό το κάνει ενδιαφέρον ως camp performance, αλλά όχι απόλυτα φυσικό μέσα στο album. Η συμμετοχή του ρόλου/εικόνας της μπάντας το στηρίζει, όμως η διασκευή συχνά ακούγεται περισσότερο σαν στρατηγική MTV hit παρά σαν οργανικό μέρος της δισκογραφικής εξέλιξής τους.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο καθαρά και δυνατά Twisted Sister anthems του δίσκου. Ο τίτλος είναι απάντηση προς όσους θέλουν την επιτυχία, τη φήμη ή την ενέργεια της μπάντας χωρίς να έχουν περάσει τις ίδιες δυσκολίες. Η μουσική είναι riff-driven, με street-metal attitude και refrain φτιαγμένο για να απαντά το κοινό. Εδώ η μπάντα επιστρέφει στην καλύτερη πλευρά της, σκληρό hard rock, απλό αλλά αποτελεσματικό hook και αίσθηση live ενότητας. Δεν έχει το ίδιο ιστορικό βάρος με το “We’re Not Gonna Take It”, όμως θα μπορούσε να σταθεί δίπλα στα προηγούμενα fan anthems τους. Η λογική του είναι «δεν μας χαρίστηκε τίποτα» , και η εκτέλεση το κάνει πειστικό.</t>
+  </si>
+  <si>
+    <t>Αυτοαναφορικό anthem που αντιμετωπίζει το rock ’n’ roll ως πίστη, τρόπο ζωής και κοινότητα. Η θεματική είναι γνώριμη για τους Twisted Sister , είχε ήδη εμφανιστεί στο “You Can’t Stop Rock ’N’ Roll” , αλλά εδώ η προσέγγιση είναι πιο glossy και πιο pop-metal. Η μπάντα δεν γράφει κάτι κακό, το chorus είναι άμεσο και η κιθάρα κρατά την ένταση. Ωστόσο, συγκρινόμενο με το title track του 1983, μοιάζει με δεύτερη, λιγότερο επείγουσα διατύπωση της ίδιας ιδέας. Λειτουργεί ως album track και ως live sing-along, όχι όμως ως ένα νέο, αδιαμφισβήτητο classic.</t>
+  </si>
+  <si>
+    <t>Μελωδικό hard rock με θέμα την αυτοπροστασία και το δικαίωμα να βάζεις τον εαυτό σου πρώτο. Το track κινείται σε mid-tempo arena-rock ρυθμό, με καθαρά ’80s production στοιχεία και chorus που θέλει να είναι ραδιοφωνικό. Δεν είναι αδύναμο, αλλά η γενική ιδέα και η μελωδική γραμμή ακούγονται πιο προβλέψιμες από τα καλύτερα tracks του album. Η θέση του πριν το φινάλε τον κάνει να λειτουργεί σαν μεταβατικό κομμάτι, προσφέρει σταθερό groove, αλλά δεν δημιουργεί την αίσθηση μεγάλης προτελευταίας κορύφωσης.</t>
+  </si>
+  <si>
+    <t>Το album τελειώνει με επιστροφή στην ταχύτητα και την απειλή. Ο τίτλος χρησιμοποιεί την υπερβολή του classic heavy metal , επιβίωση σε ένα περιβάλλον όπου ή επιβάλλεσαι ή σε καταπίνουν , και η μουσική ανταποκρίνεται με σύντομο, γρήγορο και riff-heavy κλείσιμο. Το track είναι λιγότερο elaborate από το “The Fire Still Burns”, αλλά η οικονομία του δουλεύει, μετά τις ballads, τα pop hooks και τα novelty στοιχεία, το album φεύγει με κάτι απλούστερο και σκληρότερο. Δεν μετατρέπει το Come Out And Play σε μεγάλο heavy-metal statement, όμως προσφέρει την κατάλληλη τελευταία δόση αδρεναλίνης.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η πιο εξωστρεφής και παράξενη στιγμή του album, ένα horn-driven, school-themed novelty rocker που παίζει με το “be cool to your school” και τη σκόπιμα ανορθόγραφη “chrool”. Οι Twisted Sister μετατρέπουν το σχολείο σε cartoon rock ’n’ roll σκηνικό, με χιούμορ, party αισθητική και αίσθηση μουσικού θεάτρου. Οι συμμετοχές είναι εντυπωσιακές, ο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Billy Joel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> στο πιάνο, ο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Clarence Clemons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> σε σαξόφωνο solo, ο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Brian Setzer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> σε κιθάρα solo, ο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Alice Cooper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> σε συνοδευτικά φωνητικά, οι Waters sisters στα backing vocals και οι Uptown Horns στα πνευστά. Το πρόβλημα δεν είναι η εκτέλεση, είναι γεμάτη χαρακτήρα και μουσικούς υψηλού επιπέδου, αλλά η θέση της, απομακρύνεται τόσο από το heavy-metal σώμα του album ώστε να ακούγεται σαν ξεχωριστό novelty single.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -11537,7 +11786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -11607,6 +11856,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11918,7 +12170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15194,6 +15446,38 @@
       </c>
       <c r="J102" s="11" t="s">
         <v>3433</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>3468</v>
+      </c>
+      <c r="D103" s="6">
+        <v>1985</v>
+      </c>
+      <c r="E103" s="10">
+        <v>3.27</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>3480</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>3467</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>3466</v>
+      </c>
+      <c r="I103" s="11" t="s">
+        <v>3478</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>3479</v>
       </c>
     </row>
   </sheetData>
@@ -15397,6 +15681,8 @@
     <hyperlink ref="I101" r:id="rId197" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
     <hyperlink ref="I102" r:id="rId198" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
     <hyperlink ref="J102" r:id="rId199" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
+    <hyperlink ref="I103" r:id="rId200" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
+    <hyperlink ref="J103" r:id="rId201" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15404,7 +15690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I968"/>
+  <dimension ref="A1:I978"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -41711,6 +41997,280 @@
       </c>
       <c r="I968" s="6"/>
     </row>
+    <row r="969" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A969" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B969" s="6">
+        <v>1</v>
+      </c>
+      <c r="C969" s="22" t="s">
+        <v>3468</v>
+      </c>
+      <c r="D969" s="7" t="s">
+        <v>3481</v>
+      </c>
+      <c r="E969" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F969" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G969" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H969" s="9" t="s">
+        <v>3494</v>
+      </c>
+      <c r="I969" s="6"/>
+    </row>
+    <row r="970" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A970" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B970" s="6">
+        <v>2</v>
+      </c>
+      <c r="C970" s="22" t="s">
+        <v>3469</v>
+      </c>
+      <c r="D970" s="7" t="s">
+        <v>3482</v>
+      </c>
+      <c r="E970" s="20">
+        <v>3.21</v>
+      </c>
+      <c r="F970" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G970" s="12">
+        <v>4</v>
+      </c>
+      <c r="H970" s="9" t="s">
+        <v>3495</v>
+      </c>
+      <c r="I970" s="6"/>
+    </row>
+    <row r="971" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A971" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B971" s="6">
+        <v>3</v>
+      </c>
+      <c r="C971" s="22" t="s">
+        <v>3470</v>
+      </c>
+      <c r="D971" s="7" t="s">
+        <v>3483</v>
+      </c>
+      <c r="E971" s="20">
+        <v>3.18</v>
+      </c>
+      <c r="F971" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G971" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H971" s="9" t="s">
+        <v>3496</v>
+      </c>
+      <c r="I971" s="6"/>
+    </row>
+    <row r="972" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A972" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B972" s="6">
+        <v>4</v>
+      </c>
+      <c r="C972" s="22" t="s">
+        <v>3471</v>
+      </c>
+      <c r="D972" s="7" t="s">
+        <v>3484</v>
+      </c>
+      <c r="E972" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F972" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G972" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H972" s="9" t="s">
+        <v>3497</v>
+      </c>
+      <c r="I972" s="6"/>
+    </row>
+    <row r="973" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A973" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B973" s="6">
+        <v>5</v>
+      </c>
+      <c r="C973" s="22" t="s">
+        <v>3472</v>
+      </c>
+      <c r="D973" s="7" t="s">
+        <v>3485</v>
+      </c>
+      <c r="E973" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F973" s="12">
+        <v>4</v>
+      </c>
+      <c r="G973" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H973" s="9" t="s">
+        <v>3493</v>
+      </c>
+      <c r="I973" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A974" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B974" s="6">
+        <v>6</v>
+      </c>
+      <c r="C974" s="22" t="s">
+        <v>3473</v>
+      </c>
+      <c r="D974" s="7" t="s">
+        <v>3486</v>
+      </c>
+      <c r="E974" s="20">
+        <v>3.11</v>
+      </c>
+      <c r="F974" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G974" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H974" s="24" t="s">
+        <v>3500</v>
+      </c>
+      <c r="I974" s="6"/>
+    </row>
+    <row r="975" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A975" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B975" s="6">
+        <v>7</v>
+      </c>
+      <c r="C975" s="22" t="s">
+        <v>3474</v>
+      </c>
+      <c r="D975" s="7" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E975" s="20">
+        <v>3.55</v>
+      </c>
+      <c r="F975" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G975" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H975" s="24" t="s">
+        <v>3491</v>
+      </c>
+      <c r="I975" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A976" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B976" s="6">
+        <v>8</v>
+      </c>
+      <c r="C976" s="22" t="s">
+        <v>3475</v>
+      </c>
+      <c r="D976" s="7" t="s">
+        <v>3488</v>
+      </c>
+      <c r="E976" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F976" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G976" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H976" s="9" t="s">
+        <v>3492</v>
+      </c>
+      <c r="I976" s="6"/>
+    </row>
+    <row r="977" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A977" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B977" s="6">
+        <v>9</v>
+      </c>
+      <c r="C977" s="22" t="s">
+        <v>3476</v>
+      </c>
+      <c r="D977" s="7" t="s">
+        <v>3489</v>
+      </c>
+      <c r="E977" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F977" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G977" s="12">
+        <v>4</v>
+      </c>
+      <c r="H977" s="9" t="s">
+        <v>3498</v>
+      </c>
+      <c r="I977" s="6"/>
+    </row>
+    <row r="978" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A978" s="6">
+        <v>1414305</v>
+      </c>
+      <c r="B978" s="6">
+        <v>10</v>
+      </c>
+      <c r="C978" s="22" t="s">
+        <v>3477</v>
+      </c>
+      <c r="D978" s="7" t="s">
+        <v>3490</v>
+      </c>
+      <c r="E978" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F978" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G978" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H978" s="9" t="s">
+        <v>3499</v>
+      </c>
+      <c r="I978" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD3D804-2D7F-4216-88ED-7B50B403F839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DADF39-5555-4F80-8E2A-F3688A1F4AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="3501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="3530">
   <si>
     <t>No</t>
   </si>
@@ -11638,6 +11638,93 @@
       </rPr>
       <t xml:space="preserve"> σε συνοδευτικά φωνητικά, οι Waters sisters στα backing vocals και οι Uptown Horns στα πνευστά. Το πρόβλημα δεν είναι η εκτέλεση, είναι γεμάτη χαρακτήρα και μουσικούς υψηλού επιπέδου, αλλά η θέση της, απομακρύνεται τόσο από το heavy-metal σώμα του album ώστε να ακούγεται σαν ξεχωριστό novelty single.</t>
     </r>
+  </si>
+  <si>
+    <t>Iron Maiden</t>
+  </si>
+  <si>
+    <t>Seventh Son Of A Seventh Son</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2661964-Iron-Maiden-Seventh-Son-Of-A-Seventh-Son</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/NiEjB9ShNDCyfTZy2SejR3v_Jn-UtOd2P2gUk8BGha8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI2NjE5/NjQtMTY1MTg1MjI4/OS0xMTI4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>EMI – 062-7902581 (Greece, 1988, LP, Album, Stereo). Pressed at Columbia, Athens (indicated by the 14797 numbering and manufacturing by EMI Greece / EMIAL S.A.). Direct Metal Mastering (DMM) cut with Sterling Sound metal parts.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** 1st Greek pressing. Issued with a double-sided printed inner sleeve containing lyrics and artwork. Χαρακτηριστικά runout μηνύματα: Side A διαθέτει την επιγραφή "VERY DIRECT METAL" STERLING D και Side B "IF YOU DON'T LIKE IT BOLLOCKS" D.</t>
+  </si>
+  <si>
+    <t>Infinite Dreams</t>
+  </si>
+  <si>
+    <t>Can I Play With Madness</t>
+  </si>
+  <si>
+    <t>The Evil That Men Do</t>
+  </si>
+  <si>
+    <t>The Prophecy</t>
+  </si>
+  <si>
+    <t>The Clairvoyant</t>
+  </si>
+  <si>
+    <t>Only The Good Die Young</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [NWOBHM, Concept Metal, Symphonic-Keyboard Metal, Epic Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Epic Metal, Atmospheric Opener, Occult Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Heavy Metal [Epic Prog Metal, Dynamic Metal, Psychological Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Melodic Metal, Arena Metal, Pop-Metal Single]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Melodic Heavy Metal, Dark Epic Metal, NWOBHM]</t>
+  </si>
+  <si>
+    <t>Progressive Metal, Heavy Metal [Concept Metal, Epic Metal, Keyboard-Driven Prog Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Acoustic Metal, Folk-tinged Metal, Theatrical Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Prophetic Metal, Melodic Metal, Synth-Enhanced NWOBHM]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Melodic Metal, Concept Finale, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Από τα πιο σύνθετα και ψυχολογικά τραγούδια του δίσκου. Ο αφηγητής βασανίζεται από οράματα που δεν μπορεί να αποκρυπτογραφήσει και από την αβεβαιότητα αν είναι όνειρα, προφητείες ή παραίσθηση. Η μουσική ακολουθεί αυτή την αστάθεια, ξεκινά σε πιο μελωδικό, σχεδόν αιωρούμενο πεδίο, περνά σε γρήγορα Maiden gallops και ξαναγυρίζει σε σκοτεινότερα, εσωστρεφή μέρη. Το βασικό του επίτευγμα είναι ότι οι αλλαγές δεν ακούγονται σαν τεχνική επίδειξη· είναι οργανικό μέρος της αίσθησης ότι ο χαρακτήρας χάνει τη βεβαιότητά του για την πραγματικότητα. Ο Steve Harris γράφει μία από τις καλύτερες long-form συνθέσεις της κλασικής εποχής και η μπάντα την υπηρετεί με ακρίβεια, χωρίς να χάνει το συναισθηματικό της βάρος.</t>
+  </si>
+  <si>
+    <t>Μετά την επική έκταση του title track, το “The Prophecy” αλλάζει υφή, πιο ακουστική εισαγωγή, folk-like μελωδική κίνηση και αίσθηση αρχαίου μύθου. Η προφητεία είναι η γνώση που ο κόσμος είτε αγνοεί είτε παρερμηνεύει, και η φωνή του Dickinson ακούγεται εδώ πιο αφηγηματική. Στη συνέχεια, το τραγούδι ανοίγει σε πλήρη metal μορφή, αλλά διατηρεί μια αίσθηση περιπλάνησης και πένθους. Είναι λιγότερο άμεσο από τα singles και λιγότερο τεράστιο από το title track, όμως έχει κομβική ρόλο στη ροή του concept, εκφράζει το παράδοξο ενός προφήτη που βλέπει τι έρχεται, αλλά δεν μπορεί να πείσει ή να σώσει όσους τον περιβάλλουν.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο μελωδικά και προωθητικά τραγούδια της B πλευράς. Ο “clairvoyant” είναι η φιγούρα που βλέπει πέρα από το παρόν, αλλά η δύναμή του μετατρέπεται σε βάρος, γνωρίζει την αλήθεια και, παρ’ όλα αυτά, παραμένει παρεξηγημένος ή απομονωμένος. Η μουσική ισορροπεί εξαιρετικά μεταξύ κλασικού Maiden gallop, synth χρωμάτων και μεγάλου chorus. Δεν έχει την έκταση του title track, αλλά η οικονομία του είναι αρετή, αποδίδει όλη την προφητική και τραγική ατμόσφαιρα του δίσκου σε λίγο περισσότερο από τέσσερα λεπτά. Το AllMusic το αναφέρει ως δείγμα “brilliant musicianship”, και η θέση του πριν από το finale το κάνει το πιο καθαρό melodic peak της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο δεν είναι απλή γιορτή ή λύτρωση. Η φράση του τίτλου λειτουργεί με ειρωνεία, μέσα στον κόσμο του concept, το καλό μπορεί να χαθεί νωρίς, ενώ το κακό έχει τρόπο να επιβιώνει. Το τραγούδι είναι γρήγορο, με δυναμικό chorus και επιστροφή σε πιο άμεσο heavy-metal momentum μετά την ατμοσφαιρική B πλευρά. Ως finale, έχει τη σωστή ενέργεια, αλλά αφήνει σκόπιμα το τέλος ηθικά ανοιχτό και κάπως πικρό. Δεν προσπαθεί να υπερκεράσει το title track σε κλίμακα· λειτουργεί ως τελική, πιο απλή, αλλά αποτελεσματική διατύπωση του διλήμματος που έχει χτίσει όλο το album. Η tracklist και η θέση του ως όγδοο/τελευταίο κομμάτι επιβεβαιώνονται από την πρώτη ελληνική έκδοση.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με ατμοσφαιρική, σχεδόν τελετουργική εισαγωγή, ακουστική κιθάρα, χαμηλή φωνή και η αίσθηση ότι κάποια σκοτεινή δύναμη απευθύνεται σε μια μητέρα ή σε ένα παιδί που δεν έχει ακόμη γεννηθεί. Ο “Moonchild” δεν είναι απλώς occult διακόσμηση· μέσα στο concept γίνεται η αρχή της μοίρας του έβδομου γιου, μιας φιγούρας προορισμένης για οράματα και σύγκρουση. Όταν το τραγούδι περνά στο πλήρες Maiden riffing, η μετάβαση δημιουργεί εντυπωσιακή αντίθεση, από ψίθυρο σε επικό heavy metal. Η φωνή του Bruce Dickinson κινείται ανάμεσα σε απειλή και αφήγηση, ενώ τα synths προσθέτουν βάθος χωρίς να αντικαθιστούν τις κιθάρες. Είναι ιδανικό concept opener , χτίζει αμέσως μυθολογία και ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Το πιο σύντομο και πιο άμεσα εμπορικό τραγούδι του album, αλλά όχι άσχετο με το concept. Ο ήρωας αναζητά απαντήσεις από έναν προφήτη ή σοφό , “Can I play with madness?” , και λαμβάνει αινιγματικές, αποθαρρυντικές απαντήσεις. Η μελωδία, το πιασάρικο chorus και η καθαρή δομή το κάνουν πιο κοντά σε arena-metal single, όμως τα keyboards και οι σκοτεινές εικόνες εμποδίζουν να ακουστεί σαν απλό pop-metal τραγούδι. Η θέση του μετά το “Infinite Dreams” είναι έξυπνη, χαλαρώνει την πυκνότητα της ακρόασης χωρίς να εγκαταλείπει τη θεματική. Το AllMusic το χαρακτηρίζει τραγούδι με “pitch perfect chorus”, κάτι που εξηγεί τη διαχρονική του απήχηση.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεσα σκοτεινή heavy-metal στιγμή της A πλευράς. Ο τίτλος αντλεί τη φράση του από τον Shakespeare , το κακό που κάνουν οι άνθρωποι ζει μετά από αυτούς , και το τραγούδι εξετάζει την ηθική ευθύνη, την καταδίκη και τις συνέπειες πράξεων που δεν μπορούν να ανακληθούν. Το riffing είναι γρήγορο αλλά ελεγχόμενο, ο Dickinson τραγουδά με δραματική καθαρότητα και οι κιθάρες των Dave Murray και Adrian Smith δίνουν στη σύνθεση οξύτητα και μελωδικότητα μαζί. Παρότι λειτούργησε ως single, είναι πιο πυκνό και πιο σκοτεινό από το “Can I Play With Madness”. Αποτελεί γέφυρα προς τη μεγάλη B πλευρά, από την ατομική σύγχυση του ήρωα, περνά στο ερώτημα του κακού και στη μεγαλύτερη μυθολογική σύγκρουση.</t>
+  </si>
+  <si>
+    <t>Η καρδιά του album, η μεγαλύτερη σύνθεση και η πιο καθαρή δήλωση της progressive ambition των Iron Maiden. Με σχεδόν δέκα λεπτά διάρκεια, το title track δεν βασίζεται σε ένα riff ή ένα απλό verse-chorus μοτίβο. Χτίζει σε διαδοχικές ενότητες, ατμοσφαιρική εισαγωγή, synth-led ύφανση, βαρύτερα riffs, ρυθμικές μετατοπίσεις, instrumental ανάπτυξη και μεγάλες φωνητικές κορυφώσεις. Ο “seventh son” είναι ταυτόχρονα προικισμένος και καταραμένος, έχει τη δύναμη να προβλέπει, αλλά η γνώση αυτή τον απομονώνει από τους άλλους. Η μουσική αποδίδει ακριβώς αυτή τη διπλή φύση , μεγαλείο και απειλή, προφητική δύναμη και μοναξιά. Είναι η πιο κοντινή στιγμή των Maiden σε πλήρες progressive metal, και για αυτό δικαίως είναι το υψηλότερα βαθμολογημένο track του album. Η σύνθετη δομή του τίτλου αναφέρεται συχνά ως βασικό στοιχείο της progressive ταξινόμησης του δίσκου.</t>
   </si>
 </sst>
 </file>
@@ -12170,7 +12257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15478,6 +15565,38 @@
       </c>
       <c r="J103" s="11" t="s">
         <v>3479</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>3502</v>
+      </c>
+      <c r="D104" s="6">
+        <v>1988</v>
+      </c>
+      <c r="E104" s="10">
+        <v>4</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>3513</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>3506</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>3505</v>
+      </c>
+      <c r="I104" s="11" t="s">
+        <v>3503</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>3504</v>
       </c>
     </row>
   </sheetData>
@@ -15683,6 +15802,8 @@
     <hyperlink ref="J102" r:id="rId199" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
     <hyperlink ref="I103" r:id="rId200" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
     <hyperlink ref="J103" r:id="rId201" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
+    <hyperlink ref="I104" r:id="rId202" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
+    <hyperlink ref="J104" r:id="rId203" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15690,7 +15811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I978"/>
+  <dimension ref="A1:I986"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -42271,6 +42392,222 @@
       </c>
       <c r="I978" s="6"/>
     </row>
+    <row r="979" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A979" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B979" s="6">
+        <v>1</v>
+      </c>
+      <c r="C979" s="22" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D979" s="7" t="s">
+        <v>3514</v>
+      </c>
+      <c r="E979" s="20">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F979" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G979" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H979" s="9" t="s">
+        <v>3526</v>
+      </c>
+      <c r="I979" s="6"/>
+    </row>
+    <row r="980" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A980" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B980" s="6">
+        <v>2</v>
+      </c>
+      <c r="C980" s="22" t="s">
+        <v>3507</v>
+      </c>
+      <c r="D980" s="7" t="s">
+        <v>3515</v>
+      </c>
+      <c r="E980" s="20">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F980" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G980" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H980" s="9" t="s">
+        <v>3522</v>
+      </c>
+      <c r="I980" s="6"/>
+    </row>
+    <row r="981" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A981" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B981" s="6">
+        <v>3</v>
+      </c>
+      <c r="C981" s="22" t="s">
+        <v>3508</v>
+      </c>
+      <c r="D981" s="7" t="s">
+        <v>3516</v>
+      </c>
+      <c r="E981" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F981" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G981" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H981" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="I981" s="6"/>
+    </row>
+    <row r="982" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A982" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B982" s="6">
+        <v>4</v>
+      </c>
+      <c r="C982" s="22" t="s">
+        <v>3509</v>
+      </c>
+      <c r="D982" s="7" t="s">
+        <v>3517</v>
+      </c>
+      <c r="E982" s="20">
+        <v>4.45</v>
+      </c>
+      <c r="F982" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G982" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H982" s="9" t="s">
+        <v>3528</v>
+      </c>
+      <c r="I982" s="6"/>
+    </row>
+    <row r="983" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A983" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B983" s="6">
+        <v>5</v>
+      </c>
+      <c r="C983" s="22" t="s">
+        <v>3502</v>
+      </c>
+      <c r="D983" s="7" t="s">
+        <v>3518</v>
+      </c>
+      <c r="E983" s="20">
+        <v>4.45</v>
+      </c>
+      <c r="F983" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G983" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H983" s="9" t="s">
+        <v>3529</v>
+      </c>
+      <c r="I983" s="6"/>
+    </row>
+    <row r="984" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A984" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B984" s="6">
+        <v>6</v>
+      </c>
+      <c r="C984" s="22" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D984" s="7" t="s">
+        <v>3519</v>
+      </c>
+      <c r="E984" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F984" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G984" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H984" s="9" t="s">
+        <v>3523</v>
+      </c>
+      <c r="I984" s="6"/>
+    </row>
+    <row r="985" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A985" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B985" s="6">
+        <v>7</v>
+      </c>
+      <c r="C985" s="22" t="s">
+        <v>3511</v>
+      </c>
+      <c r="D985" s="7" t="s">
+        <v>3520</v>
+      </c>
+      <c r="E985" s="20">
+        <v>4.32</v>
+      </c>
+      <c r="F985" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G985" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H985" s="9" t="s">
+        <v>3524</v>
+      </c>
+      <c r="I985" s="6"/>
+    </row>
+    <row r="986" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A986" s="6">
+        <v>2661964</v>
+      </c>
+      <c r="B986" s="6">
+        <v>8</v>
+      </c>
+      <c r="C986" s="22" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D986" s="7" t="s">
+        <v>3521</v>
+      </c>
+      <c r="E986" s="20">
+        <v>4.18</v>
+      </c>
+      <c r="F986" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G986" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H986" s="9" t="s">
+        <v>3525</v>
+      </c>
+      <c r="I986" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DADF39-5555-4F80-8E2A-F3688A1F4AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D8EC13-C99F-470C-AC06-6911881B4A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="3530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3863" uniqueCount="3567">
   <si>
     <t>No</t>
   </si>
@@ -11725,6 +11725,117 @@
   </si>
   <si>
     <t>Η καρδιά του album, η μεγαλύτερη σύνθεση και η πιο καθαρή δήλωση της progressive ambition των Iron Maiden. Με σχεδόν δέκα λεπτά διάρκεια, το title track δεν βασίζεται σε ένα riff ή ένα απλό verse-chorus μοτίβο. Χτίζει σε διαδοχικές ενότητες, ατμοσφαιρική εισαγωγή, synth-led ύφανση, βαρύτερα riffs, ρυθμικές μετατοπίσεις, instrumental ανάπτυξη και μεγάλες φωνητικές κορυφώσεις. Ο “seventh son” είναι ταυτόχρονα προικισμένος και καταραμένος, έχει τη δύναμη να προβλέπει, αλλά η γνώση αυτή τον απομονώνει από τους άλλους. Η μουσική αποδίδει ακριβώς αυτή τη διπλή φύση , μεγαλείο και απειλή, προφητική δύναμη και μοναξιά. Είναι η πιο κοντινή στιγμή των Maiden σε πλήρες progressive metal, και για αυτό δικαίως είναι το υψηλότερα βαθμολογημένο track του album. Η σύνθετη δομή του τίτλου αναφέρεται συχνά ως βασικό στοιχείο της progressive ταξινόμησης του δίσκου.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitesnake </t>
+  </si>
+  <si>
+    <t>Come An' Get It</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4428247-Whitesnake-Come-An-Get-It</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/rP91e6YsNwnQTOqkEueH7PJ8nQutJNVHEE7TT-muaVk/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ0Mjgy/NDctMTU1ODQ3Mjgw/OS02ODE0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Liberty – 14C 062-83134, Sunburst – LBG 30327 (Greece, 1981, LP, Album). Pressed at Columbia, Athens (EMI Greece). Features Sterling Sound metal parts.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** 1st Greek pressing distributed by EMIAL S.A. / EMI Greece. Runouts utilize UK Sterling Sound stampers (LBG 30327 A-1U STERLING A / LBG 30327 B-1U B STERLING), εξασφαλίζοντας εξαιρετική δυναμική συμπεριφορά.</t>
+  </si>
+  <si>
+    <t>Come An’ Get It</t>
+  </si>
+  <si>
+    <t>Don’t Break My Heart Again</t>
+  </si>
+  <si>
+    <t>Hot Stuff</t>
+  </si>
+  <si>
+    <t>Child Of Babylon</t>
+  </si>
+  <si>
+    <t>Till The Day I Die</t>
+  </si>
+  <si>
+    <t>Hit An’ Run</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>Would I Lie To You</t>
+  </si>
+  <si>
+    <t>Wine, Women An’ Song</t>
+  </si>
+  <si>
+    <t>Lonely Days, Lonely Nights</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [British Blues Rock, Classic Hard Rock, Soulful Hard Rock, Pub Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Up-tempo British Hard Rock, Boogie Rock, Album Opener]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Boogie Rock, Bluesy Hard Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Melodic Hard Rock, Blues Ballad, Heartbreak Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Slow Blues Rock, Soulful Rock, Melancholic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Rock ’n’ Roll, Blues Rock [Boogie Rock, Pub Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Dark Hard Rock, Hammond-driven Rock, Dramatic Blues Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Bluesy Riff Rock, Soulful Hard Rock, Groove Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Melodic Hard Rock, Romantic Rock, AOR-adjacent]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Fast Boogie Rock, Pub Rock, Party Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Dramatic Hard Rock, Melodic Blues Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ξεκινά με πιο σκοτεινό, δραματικό hard rock. Η “Βαβυλώνα” του τίτλου λειτουργεί σαν εικόνα διαφθοράς, πειρασμού, υπερβολής και ηθικής πτώσης. Ο Bernie Marsden συνυπογράφει τη σύνθεση, και οι κιθάρες έχουν μεγαλύτερη παρουσία, ενώ το Hammond του Jon Lord δίνει εκκλησιαστική, σχεδόν apocalyptic αίσθηση. Δεν είναι το πιο άμεσο τραγούδι του album, αλλά είναι σημαντικό γιατί διευρύνει τη θεματική πέρα από τις σχέσεις και το party rock. Η μουσική συνδέει τον blues-rock πυρήνα της μπάντας με το πιο σκοτεινό, theatrical hard-rock ύφος που θα εμφανιζόταν συχνότερα αργότερα στον κατάλογό τους.</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό, πιο μαλακό και πιο κοντά σε romantic hard rock. Η απλή προσφώνηση του τίτλου επιτρέπει στον Coverdale να κινηθεί σε άμεση, ερωτική ερμηνεία, ενώ η μπάντα επιλέγει καθαρότερα melodic hooks αντί για βαριά blues riffs. Είναι από τις στιγμές όπου ο δίσκος φλερτάρει με AOR / soft-rock προσβασιμότητα, χωρίς ακόμη να φτάνει τη μεταγενέστερη αμερικανική παραγωγή των Whitesnake. Το τραγούδι λειτουργεί ως ανάπαυλα, όμως συγκρινόμενο με τις ισχυρότερες συνθέσεις της δισκογραφίας τους, δεν διαθέτει τον ίδιο ιδιαίτερο χαρακτήρα.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο δίνει στον δίσκο μια πιο αποφασιστική και δραματική έξοδο. Ο τίτλος δηλώνει πίστη ή δέσμευση που αντέχει «ως τη μέρα που θα πεθάνω», και η μουσική χτίζει πάνω σε πιο μελωδικό hard-rock πλαίσιο, με το Coverdale να ανεβαίνει σε ένταση χωρίς να χάνει τη χαρακτηριστική bluesy χροιά του. Δεν είναι το πιο θεαματικό finale της πρώιμης Whitesnake εποχής, όμως λειτουργεί σωστά ως κατακλείδα επειδή συνδυάζει τη συναισθηματική πλευρά του album με το βασικό hard-rock drive. Αφήνει μια αίσθηση συνέχειας και αντοχής, αντί να τελειώνει απλώς σε party mood.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει με τον τρόπο που πρέπει να ανοίγει ένας δίσκος της πρώτης Whitesnake εποχής, άμεσο riff, boogie κίνηση και η φωνή του David Coverdale να αντιμετωπίζει το κομμάτι ως πρόσκληση, πρόκληση και rock ’n’ roll χειρονομία μαζί. Το “come and get it” δεν είναι βαθύ φιλοσοφικό μήνυμα· είναι η δήλωση μιας μπάντας που έχει αυτοπεποίθηση στο groove της και θέλει να τραβήξει τον ακροατή μέσα στο club-like κλίμα της. Οι δύο κιθάρες των Moody και Marsden δίνουν πάχος χωρίς να βαραίνουν υπερβολικά, το Hammond του Jon Lord προσθέτει το Deep Purple DNA και ο Ian Paice κρατά το τραγούδι σε σταθερή, προωθητική κίνηση. Είναι αποτελεσματικό opener, όχι από τα πιο βαθιά τραγούδια του album, αλλά αντιπροσωπευτικό του hard/boogie χαρακτήρα του.</t>
+  </si>
+  <si>
+    <t>Πιο κοφτό και riff-driven, με τίτλο που ανήκει καθαρά στη γλώσσα του bluesy hard rock, πάθος, swagger και σωματική ένταση. Το κομμάτι δεν προσπαθεί να κρυφτεί πίσω από σύνθετη σύνθεση· στηρίζεται στο groove, στη σχέση κιθάρας και rhythm section και στην ικανότητα του Coverdale να δίνει σε απλές φράσεις sexy, gritty βάρος. Ο Micky Moody συνυπογράφει τη σύνθεση, κάτι που ταιριάζει με την κεντρική θέση της κιθάρας. Ακούγεται σαν τραγούδι φτιαγμένο για να λειτουργεί εξίσου καλά σε studio και πάνω στη σκηνή , σύντομο, σφιχτό, με αρκετό riff ώστε να διατηρεί ενδιαφέρον χωρίς να χάνει το bar-room feel.</t>
+  </si>
+  <si>
+    <t>Το σαφέστερο highlight της A πλευράς και μία από τις καλύτερες early-Whitesnake συνθέσεις. Ο Coverdale έγραψε το τραγούδι μέσα από τη διάλυση του πρώτου του γάμου, γεγονός που εξηγεί γιατί η ερμηνεία έχει πιο άμεση και προσωπική ένταση από τα party-rock tracks γύρω της. Η μπάντα δεν το αντιμετωπίζει ως ήσυχη μπαλάντα, οι κιθάρες κρατούν σκληρή γραμμή, το Hammond πυκνώνει το δράμα και ο Paice ανεβάζει την ένταση χωρίς να καταστρέφει τη μελωδία. Ο συνδυασμός ευάλωτου στίχου και δυνατής rock εκτέλεσης κάνει το track πιο διαχρονικό από έναν τυπικό heartbreak anthem. Κυκλοφόρησε ως lead single και το B-side του ήταν το “Child of Babylon”.</t>
+  </si>
+  <si>
+    <t>Η πιο μελαγχολική και slow-burning στιγμή της A πλευράς. Ο τίτλος λέει ακριβώς την ψυχολογική κατάσταση, μοναχικές μέρες και νύχτες, όπου η απουσία ενός προσώπου μετατρέπεται σε επαναλαμβανόμενο μοτίβο. Η μπάντα χαμηλώνει την ταχύτητα, αφήνει χώρο στη φωνή του Coverdale και αξιοποιεί το blues λεξιλόγιο χωρίς να γίνεται παραδοσιακό twelve-bar blues. Η αξία του βρίσκεται στο mood, το track δεν διεκδικεί μεγάλο chorus ή θεαματική κορύφωση, αλλά δημιουργεί χώρο για τη soulful πλευρά του συγκροτήματος. Είναι παράδειγμα του γιατί η πρώιμη Whitesnake περίοδος ξεχωρίζει από την αργότερη arena-rock φάση.</t>
+  </si>
+  <si>
+    <t>Το κλασικό “τριάδα των απολαύσεων” τραγούδι, με boogie και pub-rock διάθεση. Η συλλογική σύνθεση από όλα τα μέλη του line-up έχει σημασία, ακούγεται σαν μια μπάντα που αποτυπώνει τη live χημεία της, όχι σαν ένα αυστηρά ελεγχόμενο songwriting project. Η θεματική είναι αναμενόμενα rock ’n’ roll, ποτό, ερωτική περιπέτεια και μουσική ως τρόπος διαφυγής. Το κομμάτι δεν στοχεύει στο βάθος, αλλά στη συμμετοχή· έχει απλή, ανοιχτή ρυθμική βάση και chorus που λειτουργεί σαν bar-room chant. Ως κλείσιμο της A πλευράς, αφήνει τον ακροατή με ενέργεια και όχι με τη μελαγχολία του “Lonely Days, Lonely Nights”.</t>
+  </si>
+  <si>
+    <t>Bluesy mid-tempo rocker που βασίζεται στο ερώτημα της εμπιστοσύνης μέσα σε μια σχέση. Ο τίτλος θέτει τη δραματική ένταση, ο αφηγητής προσπαθεί να πείσει ή να αμφισβητήσει, χωρίς να είναι ποτέ βέβαιο αν λέει την αλήθεια. Το groove είναι το βασικό στοιχείο, με το rhythm section να κρατά low-slung κίνηση και τις κιθάρες να προσθέτουν φράσεις αντί να κυριαρχούν. Δεν έχει την προσωπική αμεσότητα του “Don’t Break My Heart Again”, όμως δείχνει καλά την blues/soul πλευρά του Coverdale ως τραγουδιστή, λιγότερο δραματική κραυγή, περισσότερο φωνητικό παιχνίδι και ερωτική αμφισημία.</t>
+  </si>
+  <si>
+    <t>Γρήγορη επιστροφή στο boogie-rock momentum, με τίτλο που υποδηλώνει γρήγορη ερωτική ή κοινωνική συνάντηση χωρίς δέσμευση. Η μπάντα χρησιμοποιεί το πιο βασικό hard-rock λεξιλόγιό της, driving riff, σταθερά drums, κιθάρες που συνοδεύουν με μικρά bluesy περάσματα και φωνητική αυτοπεποίθηση. Είναι κομμάτι ενέργειας, όχι δραματικής ανάπτυξης. Λειτουργεί καλύτερα μέσα στη σειρά του δίσκου, όπου αναζωογονεί τη B πλευρά μετά το πιο ήπιο “Girl”, παρά ως ιδιαίτερα σημαντικό αυτόνομο τραγούδι.</t>
   </si>
 </sst>
 </file>
@@ -12257,7 +12368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15597,6 +15708,38 @@
       </c>
       <c r="J104" s="11" t="s">
         <v>3504</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>3531</v>
+      </c>
+      <c r="D105" s="6">
+        <v>1981</v>
+      </c>
+      <c r="E105" s="10">
+        <v>3.39</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>3546</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>3535</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>3534</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>3532</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>3533</v>
       </c>
     </row>
   </sheetData>
@@ -15804,6 +15947,8 @@
     <hyperlink ref="J103" r:id="rId201" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
     <hyperlink ref="I104" r:id="rId202" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
     <hyperlink ref="J104" r:id="rId203" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
+    <hyperlink ref="I105" r:id="rId204" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
+    <hyperlink ref="J105" r:id="rId205" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15811,7 +15956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I986"/>
+  <dimension ref="A1:I996"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -42608,6 +42753,278 @@
       </c>
       <c r="I986" s="6"/>
     </row>
+    <row r="987" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A987" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B987" s="6">
+        <v>1</v>
+      </c>
+      <c r="C987" s="22" t="s">
+        <v>3536</v>
+      </c>
+      <c r="D987" s="7" t="s">
+        <v>3547</v>
+      </c>
+      <c r="E987" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F987" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G987" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H987" s="9" t="s">
+        <v>3560</v>
+      </c>
+      <c r="I987" s="6"/>
+    </row>
+    <row r="988" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A988" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B988" s="6">
+        <v>2</v>
+      </c>
+      <c r="C988" s="22" t="s">
+        <v>3538</v>
+      </c>
+      <c r="D988" s="7" t="s">
+        <v>3548</v>
+      </c>
+      <c r="E988" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F988" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G988" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H988" s="9" t="s">
+        <v>3561</v>
+      </c>
+      <c r="I988" s="6"/>
+    </row>
+    <row r="989" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A989" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B989" s="6">
+        <v>3</v>
+      </c>
+      <c r="C989" s="22" t="s">
+        <v>3537</v>
+      </c>
+      <c r="D989" s="7" t="s">
+        <v>3549</v>
+      </c>
+      <c r="E989" s="20">
+        <v>4.07</v>
+      </c>
+      <c r="F989" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G989" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H989" s="9" t="s">
+        <v>3562</v>
+      </c>
+      <c r="I989" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A990" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B990" s="6">
+        <v>4</v>
+      </c>
+      <c r="C990" s="22" t="s">
+        <v>3545</v>
+      </c>
+      <c r="D990" s="7" t="s">
+        <v>3550</v>
+      </c>
+      <c r="E990" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F990" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G990" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H990" s="9" t="s">
+        <v>3563</v>
+      </c>
+      <c r="I990" s="6"/>
+    </row>
+    <row r="991" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A991" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B991" s="6">
+        <v>5</v>
+      </c>
+      <c r="C991" s="22" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D991" s="7" t="s">
+        <v>3551</v>
+      </c>
+      <c r="E991" s="20">
+        <v>3.36</v>
+      </c>
+      <c r="F991" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G991" s="12">
+        <v>4</v>
+      </c>
+      <c r="H991" s="9" t="s">
+        <v>3564</v>
+      </c>
+      <c r="I991" s="6"/>
+    </row>
+    <row r="992" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A992" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B992" s="6">
+        <v>6</v>
+      </c>
+      <c r="C992" s="22" t="s">
+        <v>3539</v>
+      </c>
+      <c r="D992" s="7" t="s">
+        <v>3552</v>
+      </c>
+      <c r="E992" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F992" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G992" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H992" s="9" t="s">
+        <v>3557</v>
+      </c>
+      <c r="I992" s="6"/>
+    </row>
+    <row r="993" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A993" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B993" s="6">
+        <v>7</v>
+      </c>
+      <c r="C993" s="22" t="s">
+        <v>3543</v>
+      </c>
+      <c r="D993" s="7" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E993" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F993" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G993" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H993" s="9" t="s">
+        <v>3565</v>
+      </c>
+      <c r="I993" s="6"/>
+    </row>
+    <row r="994" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A994" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B994" s="6">
+        <v>8</v>
+      </c>
+      <c r="C994" s="22" t="s">
+        <v>3542</v>
+      </c>
+      <c r="D994" s="7" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E994" s="20">
+        <v>3.24</v>
+      </c>
+      <c r="F994" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G994" s="12">
+        <v>4</v>
+      </c>
+      <c r="H994" s="9" t="s">
+        <v>3558</v>
+      </c>
+      <c r="I994" s="6"/>
+    </row>
+    <row r="995" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A995" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B995" s="6">
+        <v>9</v>
+      </c>
+      <c r="C995" s="22" t="s">
+        <v>3541</v>
+      </c>
+      <c r="D995" s="7" t="s">
+        <v>3555</v>
+      </c>
+      <c r="E995" s="20">
+        <v>3.41</v>
+      </c>
+      <c r="F995" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G995" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H995" s="9" t="s">
+        <v>3566</v>
+      </c>
+      <c r="I995" s="6"/>
+    </row>
+    <row r="996" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A996" s="6">
+        <v>4428247</v>
+      </c>
+      <c r="B996" s="6">
+        <v>10</v>
+      </c>
+      <c r="C996" s="22" t="s">
+        <v>3540</v>
+      </c>
+      <c r="D996" s="7" t="s">
+        <v>3556</v>
+      </c>
+      <c r="E996" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F996" s="12">
+        <v>4</v>
+      </c>
+      <c r="G996" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H996" s="9" t="s">
+        <v>3559</v>
+      </c>
+      <c r="I996" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D8EC13-C99F-470C-AC06-6911881B4A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E9B32C-13FA-4AC0-82C0-928739E41C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3863" uniqueCount="3567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="3567">
   <si>
     <t>No</t>
   </si>
@@ -42778,7 +42778,9 @@
       <c r="H987" s="9" t="s">
         <v>3560</v>
       </c>
-      <c r="I987" s="6"/>
+      <c r="I987" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="988" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A988" s="6">

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E9B32C-13FA-4AC0-82C0-928739E41C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C810543F-BC45-4110-AAE4-7A764E1C6C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="3567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="3603">
   <si>
     <t>No</t>
   </si>
@@ -11837,12 +11837,120 @@
   <si>
     <t>Γρήγορη επιστροφή στο boogie-rock momentum, με τίτλο που υποδηλώνει γρήγορη ερωτική ή κοινωνική συνάντηση χωρίς δέσμευση. Η μπάντα χρησιμοποιεί το πιο βασικό hard-rock λεξιλόγιό της, driving riff, σταθερά drums, κιθάρες που συνοδεύουν με μικρά bluesy περάσματα και φωνητική αυτοπεποίθηση. Είναι κομμάτι ενέργειας, όχι δραματικής ανάπτυξης. Λειτουργεί καλύτερα μέσα στη σειρά του δίσκου, όπου αναζωογονεί τη B πλευρά μετά το πιο ήπιο “Girl”, παρά ως ιδιαίτερα σημαντικό αυτόνομο τραγούδι.</t>
   </si>
+  <si>
+    <t>The Headless Children</t>
+  </si>
+  <si>
+    <t>W.A.S.P.</t>
+  </si>
+  <si>
+    <t>Capitol Records – EST 2087, Capitol Records – 74 8942 1, Capitol Records – 062-7489421, Capitol Records – 15561 (Greece, 1989, LP, Album).</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2903507-WASP-The-Headless-Children</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/xKcrMsdV4IYa5ecvIl7QhoS8mDh6bpfqF0r793dODqA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI5MDM1/MDctMTMwNjUwOTUz/My5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Συνοδεύεται από ασπρόμαυρο εσωτερικό φάκελο (inner sleeve) με τους στίχους.   Φέρει διαφορετικούς κωδικούς στο εξώφυλλο (1st &amp; 2nd Cat#) σε σχέση με τις ετικέτες του δίσκου (3rd &amp; 4th Cat#).</t>
+  </si>
+  <si>
+    <t>The Heretic (The Lost Child)</t>
+  </si>
+  <si>
+    <t>The Real Me</t>
+  </si>
+  <si>
+    <t>Thunderhead</t>
+  </si>
+  <si>
+    <t>Rebel In The F.D.G.</t>
+  </si>
+  <si>
+    <t>Forever Free</t>
+  </si>
+  <si>
+    <t>Maneater</t>
+  </si>
+  <si>
+    <t>Mean Man</t>
+  </si>
+  <si>
+    <t>The Neutron Bomber</t>
+  </si>
+  <si>
+    <t>Mephisto Waltz</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Progressive Heavy Metal, Shock Rock, Power Ballad, Political Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Epic Metal, Dark Metal, Social-Political Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Hard Rock Cover, Mod Rock reworked as Metal, High-energy Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Metal [Political Metal, Epic Heavy Metal, Conceptual Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Apocalyptic Metal, Theatrical Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Bluesy Hard Rock, Sleaze Metal roots, Character Song]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Political Heavy Metal, Riff Metal, Nuclear-War Rock]</t>
+  </si>
+  <si>
+    <t>Classical, Progressive Rock [Piano Interlude, Neoclassical Rock, Gothic Interlude]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Power Ballad, Epic Ballad, Melodic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Hard Rock, Theatrical Metal, Predatory Character Song]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Political Metal, Anti-totalitarian Rock, Epic Album Closer]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το album ανοίγει με μια από τις πιο σκοτεινές και φιλόδοξες συνθέσεις των W.A.S.P. Η αρχή με χορωδιακές φωνές, καθαρή πένθιμη κιθάρα και αργή συσσώρευση έντασης δείχνει αμέσως ότι ο δίσκος δεν θα κινηθεί στο ίδιο πεδίο με το πρώιμο shock-rock υλικό τους. Το “lost child” συνδέεται με κοινωνική εγκατάλειψη, βία συμμοριών και την καταστροφική επίδραση των ναρκωτικών, όχι με φανταστικό horror concept. Όταν μπαίνει το πλήρες heavy-metal riffing, το κομμάτι μετατρέπεται σε επικό, επτάλεπτο statement με αλλαγές, extended solos και πραγματικό δραματικό βάρος. Ο Blackie Lawless τραγουδά σαν αφηγητής που βλέπει μια κοινωνία να εγκαταλείπει τους νεότερους ανθρώπους της. Είναι από τα tracks που δείχνουν το μεγαλύτερο δημιουργικό άλμα των W.A.S.P. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η διασκευή στο κλασικό τραγούδι των The Who είναι η πιο άμεση και εκρηκτική στιγμή της A πλευράς. Οι W.A.S.P. δεν προσπαθούν να αναπαράγουν το mod-rock νεύρο του πρωτοτύπου· το μετατρέπουν σε γρήγορο, επιθετικό heavy-rock κομμάτι. Ο τίτλος αφορά την αγωνία να καταλάβεις ή να αποκαλύψεις τον αληθινό εαυτό σου, και η ερμηνεία του Lawless δίνει στη φράση μεγαλύτερη rage και ένταση. Η μπάντα παίζει με ακρίβεια, αλλά διατηρεί αρκετή ακατέργαστη ενέργεια ώστε η διασκευή να έχει δική της ταυτότητα. Είναι από τις σπάνιες περιπτώσεις όπου ένα cover στέκεται ισότιμα με τα originals ενός album· μάλιστα, ορισμένες κριτικές το θεωρούν το καλύτερο track του δίσκου. </t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο πολιτικό/πολεμικό τραγούδι του δίσκου. Ο τίτλος αναφέρεται στη βόμβα νετρονίων, ένα όπλο συνδεδεμένο με την ψυχροπολεμική φαντασίωση της μαζικής καταστροφής με διατήρηση υλικών δομών. Η μουσική επιλέγει πιο compact, riff-centered heavy metal, με σαφές urgency και λιγότερη ατμοσφαιρική ανάπτυξη. Δεν έχει το βάθος του “The Headless Children”, αλλά λειτουργεί σαν σύντομη, οργισμένη καταγγελία απέναντι στην τεχνολογική και πολιτική παράνοια του πολέμου. Η παραγωγή κρατά τα riffs μπροστά και η ερμηνεία του Lawless είναι κοφτή, σχεδόν σαν κατηγορώ.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο σκοτεινό, χαρακτήρα-κεντρικό hard rock. Ο “maneater” είναι μια απειλητική, σαγηνευτική φιγούρα που καταναλώνει ή καταστρέφει τους ανθρώπους γύρω της. Η μουσική αξιοποιεί theatrical metal στοιχεία και heavy-rock riffing, χωρίς να φτάνει το πιο βαθύ πολιτικό περιεχόμενο των προηγούμενων tracks. Είναι χρήσιμο στη σειρά επειδή ξαναφέρνει κίνηση μετά τη δραματική κάθαρση του “Forever Free”, αλλά ως σύνθεση δεν έχει την ίδια πρωτοτυπία ή συναισθηματικό βάρος. Παραμένει, ωστόσο, σταθερό δείγμα του σκοτεινού, narrative τρόπου με τον οποίο ο Lawless χειρίζεται χαρακτήρες.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η θεματική και μουσική καρδιά του album. Τα “headless children” δεν είναι κυριολεκτικά πλάσματα αλλά άνθρωποι ή κοινωνίες χωρίς μνήμη, ιστορική επίγνωση και ανεξάρτητη σκέψη , εύκολα χειραγωγήσιμοι από πολιτική εξουσία, πολέμους και ιδεολογίες. Ο Lawless ενσωματώνει πολιτικό σχόλιο χωρίς να εγκαταλείπει το heavy-metal βάρος, οι κιθάρες έχουν προωθητικό riffing, τα keyboards του Ken Hensley προσθέτουν σκοτεινή μεγαλοπρέπεια και η σύνθεση χτίζει σαν προειδοποιητική ομιλία. Το track είναι πιο δομημένο και πιο φιλόδοξο από τα κλασικά W.A.S.P. anthems, αλλά δεν χάνει την αμεσότητα του refrain. Δικαίως έχει την υψηλότερη βαθμολογία στον πίνακα, συνοψίζει τη μετάβαση της μπάντας από το sleaze/shock metal σε πολιτικό, θεατρικό heavy metal. </t>
+  </si>
+  <si>
+    <t>Βαρύ, δραματικό και πιο απειλητικό, με τον τίτλο να λειτουργεί ως εικόνα μιας θύελλας που πλησιάζει , εξωτερικής ή εσωτερικής. Η μουσική χτίζει πάνω σε mid-tempo riffs και σε πιο εκτεταμένη δομή, κάτι που ταιριάζει με τη γενική προοδευτική στροφή του δίσκου. Η φωνή του Lawless έχει θεατρική ένταση και τα backing vocals δίνουν επιπλέον όγκο, ενώ η κιθάρα του Chris Holmes κρατά το τραγούδι συνδεδεμένο με το hard-rock παρελθόν των W.A.S.P. Δεν είναι τόσο άμεσα μνημονικό όσο το title track ή το “The Real Me”, αλλά είναι ουσιώδες για την ατμόσφαιρα του album, διατηρεί το αίσθημα απειλής και επικείμενης καταστροφής.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μετά το βαρύ και πολιτικό πρώτο μέρος, το “Mean Man” επιστρέφει σε πιο προσωπική, bluesy hard-rock γλώσσα. Η σύνθεση είναι αφιερωμένη στον πατέρα του Blackie Lawless και ο “mean man” δεν παρουσιάζεται απλώς σαν μονοδιάστατος κακός χαρακτήρας· είναι μια μορφή αυστηρότητας, πειθαρχίας, σύγκρουσης και, τελικά, περίπλοκης οικογενειακής μνήμης. Το groove είναι πιο γήινο, οι κιθάρες έχουν blues-rock κίνηση και η ερμηνεία του Lawless έχει λιγότερη πολιτική καταγγελία και περισσότερο προσωπικό βάρος. Η θέση του στη B πλευρά είναι σημαντική, αποδεικνύει ότι η ωριμότητα του δίσκου δεν προκύπτει μόνο από μεγάλα θέματα, αλλά και από πιο συγκεκριμένες, ανθρώπινες ιστορίες. Οι δημόσιες user αξιολογήσεις το τοποθετούν ανάμεσα στα υψηλότερα βαθμολογημένα τραγούδια του δίσκου. </t>
+  </si>
+  <si>
+    <t>Σύντομο πιανιστικό interlude που διακόπτει σκόπιμα την κιθαριστική ένταση. Ο τίτλος παραπέμπει στον Mephistopheles του θρύλου του Faust , άρα σε πειρασμό, συμφωνία με το κακό και ηθική φθορά , ενώ η μορφή του βαλς δίνει μια γοτθική, σχεδόν σαρκαστική κομψότητα. Δεν λειτουργεί ως ανεξάρτητο τραγούδι με την πλήρη έννοια, γι’ αυτό και η βαθμολογία του είναι χαμηλότερη. Όμως μέσα στη ροή του album είναι πολύ αποτελεσματικό, δημιουργεί χώρο πριν από το “Forever Free” και ενισχύει την αίσθηση ότι ο δίσκος έχει ενιαία θεατρική/σκοτεινή δραματουργία.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η μεγάλη power ballad και μία από τις καλύτερες συναισθηματικές συνθέσεις στην καριέρα των W.A.S.P. Ξεκινά πιο ήπια και ευάλωτα, ανοίγει σε γρήγορο και βαρύτερο mid-section και επιστρέφει στη μελαγχολική της βάση , μια δομή που αποτυπώνει την πάλη μεταξύ επιθυμίας για ελευθερία και του πόνου που συνεπάγεται η απώλεια ή η απόσταση. Ο τίτλος μπορεί να ακούγεται σαν απλή romantic υπόσχεση, αλλά η ερμηνεία του Lawless το μεταφέρει σε ευρύτερο πεδίο, επιβίωση, λύτρωση και ανάγκη να απελευθερωθείς. Η κιθάρα του Holmes προσφέρει μελωδικό βάρος χωρίς να μετατρέπει το τραγούδι σε glossy late-’80s ballad. Είναι αποδεδειγμένα ένα από τα πιο αγαπητά tracks του album στις user αξιολογήσεις και συχνά αναφέρεται ως κορυφαία W.A.S.P. μπαλάντα. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το κλείσιμο έχει πραγματική ιστορική και πολιτική βάση, το F.D.G. αναφέρεται στη Federal Republic of Germany / Δυτική Γερμανία, και το τραγούδι συνδέεται με την εμπειρία ενός ανατολικογερμανού αντιφρονούντα που επιχειρεί να ξεφύγει από τον περιορισμό του ανατολικού μπλοκ. Η ένταση δεν είναι αφηρημένη, ο «rebel» παλεύει για ελευθερία απέναντι σε κρατικό έλεγχο και πολιτική καταπίεση. Το τραγούδι εξελίσσεται σε επικό heavy-metal closer, με δυνατή κιθάρα, προωθητικό ρυθμό και δραματική ερμηνεία. Δεν έχει το ίδιο άμεσο hook με το “Mean Man” ή το title track, αλλά κλείνει τον δίσκο σωστά, μετά από πόλεμο, κοινωνική παρακμή και προσωπική απώλεια, η τελευταία λέξη είναι η αντίσταση. Οι user scores το καταγράφουν επίσης ως ένα από τα υψηλότερα αξιολογημένα tracks του album. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11926,6 +12034,13 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -11984,7 +12099,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12056,6 +12171,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12368,7 +12486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15740,6 +15858,38 @@
       </c>
       <c r="J105" s="11" t="s">
         <v>3533</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>3567</v>
+      </c>
+      <c r="D106" s="6">
+        <v>1989</v>
+      </c>
+      <c r="E106" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>3582</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>3572</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>3569</v>
+      </c>
+      <c r="I106" s="11" t="s">
+        <v>3570</v>
+      </c>
+      <c r="J106" s="11" t="s">
+        <v>3571</v>
       </c>
     </row>
   </sheetData>
@@ -15949,6 +16099,8 @@
     <hyperlink ref="J104" r:id="rId203" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
     <hyperlink ref="I105" r:id="rId204" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
     <hyperlink ref="J105" r:id="rId205" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
+    <hyperlink ref="I106" r:id="rId206" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
+    <hyperlink ref="J106" r:id="rId207" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15956,7 +16108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I996"/>
+  <dimension ref="A1:I1006"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -43027,6 +43179,276 @@
       </c>
       <c r="I996" s="6"/>
     </row>
+    <row r="997" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A997" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B997" s="6">
+        <v>1</v>
+      </c>
+      <c r="C997" s="22" t="s">
+        <v>3573</v>
+      </c>
+      <c r="D997" s="7" t="s">
+        <v>3583</v>
+      </c>
+      <c r="E997" s="20">
+        <v>4.24</v>
+      </c>
+      <c r="F997" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G997" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H997" s="25" t="s">
+        <v>3593</v>
+      </c>
+      <c r="I997" s="6"/>
+    </row>
+    <row r="998" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A998" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B998" s="6">
+        <v>2</v>
+      </c>
+      <c r="C998" s="22" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D998" s="7" t="s">
+        <v>3584</v>
+      </c>
+      <c r="E998" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F998" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G998" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H998" s="25" t="s">
+        <v>3594</v>
+      </c>
+      <c r="I998" s="6"/>
+    </row>
+    <row r="999" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A999" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B999" s="6">
+        <v>3</v>
+      </c>
+      <c r="C999" s="22" t="s">
+        <v>3567</v>
+      </c>
+      <c r="D999" s="7" t="s">
+        <v>3585</v>
+      </c>
+      <c r="E999" s="20">
+        <v>4.17</v>
+      </c>
+      <c r="F999" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G999" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H999" s="25" t="s">
+        <v>3597</v>
+      </c>
+      <c r="I999" s="6"/>
+    </row>
+    <row r="1000" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1000" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1000" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1000" s="22" t="s">
+        <v>3575</v>
+      </c>
+      <c r="D1000" s="7" t="s">
+        <v>3586</v>
+      </c>
+      <c r="E1000" s="20">
+        <v>3.99</v>
+      </c>
+      <c r="F1000" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1000" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1000" s="25" t="s">
+        <v>3598</v>
+      </c>
+      <c r="I1000" s="6"/>
+    </row>
+    <row r="1001" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1001" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1001" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1001" s="22" t="s">
+        <v>3579</v>
+      </c>
+      <c r="D1001" s="7" t="s">
+        <v>3587</v>
+      </c>
+      <c r="E1001" s="20">
+        <v>4.07</v>
+      </c>
+      <c r="F1001" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1001" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1001" s="25" t="s">
+        <v>3599</v>
+      </c>
+      <c r="I1001" s="6"/>
+    </row>
+    <row r="1002" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1002" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1002" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1002" s="22" t="s">
+        <v>3580</v>
+      </c>
+      <c r="D1002" s="7" t="s">
+        <v>3588</v>
+      </c>
+      <c r="E1002" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1002" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1002" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1002" s="25" t="s">
+        <v>3595</v>
+      </c>
+      <c r="I1002" s="6"/>
+    </row>
+    <row r="1003" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1003" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1003" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1003" s="22" t="s">
+        <v>3581</v>
+      </c>
+      <c r="D1003" s="7" t="s">
+        <v>3589</v>
+      </c>
+      <c r="E1003" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F1003" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1003" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1003" s="25" t="s">
+        <v>3600</v>
+      </c>
+      <c r="I1003" s="6"/>
+    </row>
+    <row r="1004" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1004" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1004" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1004" s="22" t="s">
+        <v>3577</v>
+      </c>
+      <c r="D1004" s="7" t="s">
+        <v>3590</v>
+      </c>
+      <c r="E1004" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1004" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1004" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1004" s="25" t="s">
+        <v>3601</v>
+      </c>
+      <c r="I1004" s="6"/>
+    </row>
+    <row r="1005" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1005" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1005" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1005" s="22" t="s">
+        <v>3578</v>
+      </c>
+      <c r="D1005" s="7" t="s">
+        <v>3591</v>
+      </c>
+      <c r="E1005" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F1005" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1005" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1005" s="25" t="s">
+        <v>3596</v>
+      </c>
+      <c r="I1005" s="6"/>
+    </row>
+    <row r="1006" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1006" s="6">
+        <v>2903507</v>
+      </c>
+      <c r="B1006" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1006" s="22" t="s">
+        <v>3576</v>
+      </c>
+      <c r="D1006" s="7" t="s">
+        <v>3592</v>
+      </c>
+      <c r="E1006" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1006" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1006" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1006" s="25" t="s">
+        <v>3602</v>
+      </c>
+      <c r="I1006" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C810543F-BC45-4110-AAE4-7A764E1C6C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1E0D2-FA7D-4B9D-953B-658F1D11ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="3603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3941" uniqueCount="3641">
   <si>
     <t>No</t>
   </si>
@@ -11945,12 +11945,126 @@
   <si>
     <t xml:space="preserve">Το κλείσιμο έχει πραγματική ιστορική και πολιτική βάση, το F.D.G. αναφέρεται στη Federal Republic of Germany / Δυτική Γερμανία, και το τραγούδι συνδέεται με την εμπειρία ενός ανατολικογερμανού αντιφρονούντα που επιχειρεί να ξεφύγει από τον περιορισμό του ανατολικού μπλοκ. Η ένταση δεν είναι αφηρημένη, ο «rebel» παλεύει για ελευθερία απέναντι σε κρατικό έλεγχο και πολιτική καταπίεση. Το τραγούδι εξελίσσεται σε επικό heavy-metal closer, με δυνατή κιθάρα, προωθητικό ρυθμό και δραματική ερμηνεία. Δεν έχει το ίδιο άμεσο hook με το “Mean Man” ή το title track, αλλά κλείνει τον δίσκο σωστά, μετά από πόλεμο, κοινωνική παρακμή και προσωπική απώλεια, η τελευταία λέξη είναι η αντίσταση. Οι user scores το καταγράφουν επίσης ως ένα από τα υψηλότερα αξιολογημένα tracks του album. </t>
   </si>
+  <si>
+    <t>https://i.discogs.com/W834OQjSzszk_ccKb4LvugwDWT78B5cTlTqy9l5VLoc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MjQ1/NTYtMTUyMzQzNTAx/MC01MjAyLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Live... In The Raw</t>
+  </si>
+  <si>
+    <t>Capitol Records – 062 7480531, Capitol Records – EST-2040 (Greece, 1987, LP, Album). Pressed at Columbia, Athens (EMI Greece / EMIAL S.A.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Πρώτη ελληνική κοπή (1987) με καταχώριση matrix/runout στα στοιχεία της συλλογής σου.   Τυπωμένο από την EMI Greece με αριθμό μητρώου κοπής (Pressing plant master tape/cover): MT 14294 και A/A 14294 στις ετικέτες.   </t>
+  </si>
+  <si>
+    <t>Inside The Electric Circus</t>
+  </si>
+  <si>
+    <t>I Don’t Need No Doctor</t>
+  </si>
+  <si>
+    <t>L.O.V.E. Machine</t>
+  </si>
+  <si>
+    <t>Wild Child</t>
+  </si>
+  <si>
+    <t>9.5. – N.A.S.T.Y.</t>
+  </si>
+  <si>
+    <t>Scream Until You Like It</t>
+  </si>
+  <si>
+    <t>Blind In Texas</t>
+  </si>
+  <si>
+    <t>I Wanna Be Somebody</t>
+  </si>
+  <si>
+    <t>The Manimal</t>
+  </si>
+  <si>
+    <t>Sleeping (In The Fire)</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Live Heavy Metal, Shock Rock, Glam Metal, Sleaze Metal, Arena Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Theatrical Metal, Live Opener, Shock Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soul Rock [Heavy Rock Cover, Bluesy Hard Rock, Live R&amp;B Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Sleaze Metal, Shock Rock, Classic W.A.S.P. Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Heavy Rock, Power Ballad elements, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Sleaze Metal, Shock Rock, Aggressive Live Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Power Ballad, Melodic Metal, Live Epic]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [New Song, Riff Metal, Aggressive Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Identity Anthem, Glam Metal, Crowd Chant Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [New Song, Fast Metal, Live-Driven Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Party Metal, Boogie Hard Rock, Crowd Anthem]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Horror Metal, Soundtrack Rock, Studio Bonus Track]</t>
+  </si>
+  <si>
+    <t>Harder Faster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η πιο μελωδική και συναισθηματικά ανοιχτή κορύφωση της A πλευράς. Το “wild child” είναι μια φιγούρα ελευθερίας, κινδύνου και ακατάτακτης επιθυμίας· η μουσική μεταφέρει αυτή τη διπλή όψη με σκληρό riffing, αλλά και με chorus που έχει πραγματική δραματική έκταση. Η live εκτέλεση διαρκεί πάνω από έξι λεπτά, δίνοντας στις κιθάρες και στον Lawless χώρο να χτίσουν μεγαλύτερη κορύφωση. Το κομμάτι δείχνει ότι οι W.A.S.P. μπορούσαν να έχουν μελωδική μεγαλοπρέπεια χωρίς να εγκαταλείπουν τον heavy-rock πυρήνα τους. Είναι δικαίως από τα καλύτερα tracks της συλλογής και μία από τις πιο ανθεκτικές συνθέσεις της μπάντας. </t>
+  </si>
+  <si>
+    <t>Επιστροφή στο shock/sleaze ύφος με τραγούδι που βασίζεται περισσότερο στο attitude και στην πρόκληση από ό,τι στη λεπτή σύνθεση. Ο τίτλος χρησιμοποιεί αριθμητική και ακρωνύμιο σαν υπερβολικό, cartoonish sexual boast, κάτι χαρακτηριστικό της περιόδου. Η μπάντα το παίζει με live ένταση και άμεσο riffing, ενώ ο Lawless το αντιμετωπίζει σαν μέρος του stage persona του. Δεν έχει την ατμοσφαιρική ανάπτυξη του “Wild Child”, αλλά λειτουργεί αποτελεσματικά ως adrenaline track και υπενθυμίζει την ακατέργαστη, προκλητική ενέργεια των πρώτων δίσκων.</t>
+  </si>
+  <si>
+    <t>Η συναισθηματική κορύφωση της A πλευράς και μία από τις καλύτερες W.A.S.P. μπαλάντες. Ο τίτλος συνδυάζει τον ύπνο με τη φωτιά — μια εικόνα επιθυμίας τόσο έντονης ώστε να γίνεται επικίνδυνη. Η live εκτέλεση διατηρεί την αργή, δραματική ανάπτυξη του original, ενώ η κιθάρα αναλαμβάνει μεγαλύτερο ρόλο στο χτίσιμο της έντασης. Ο Lawless τραγουδά λιγότερο σαν shock-rock χαρακτήρας και περισσότερο σαν κλασικός hard-rock vocalist, κάτι που δίνει στο τραγούδι διαχρονική αξία. Μετά την sleaze πλευρά των προηγούμενων tracks, λειτουργεί ως απόδειξη ότι η μπάντα είχε και πραγματική μελωδική ευαισθησία.</t>
+  </si>
+  <si>
+    <t>Το live album ανοίγει με το σωστό είδος θεατρικής υπερβολής. Το “Electric Circus” είναι ο κόσμος των W.A.S.P. ως αποπροσανατολιστικό, επικίνδυνο θέαμα, ένταση, σεξουαλικότητα, βία, φώτα και μια μπάντα που μετατρέπει το metal show σε carnival. Η live εκτέλεση δίνει στο τραγούδι περισσότερο βάρος από τη studio version, κυρίως λόγω του ρυθμικού drive και της αίσθησης ότι ο Blackie Lawless απευθύνεται άμεσα στο κοινό. Δεν είναι το πιο βαθύ τραγούδι του συγκροτήματος, αλλά είναι ιδανικό opener, παρουσιάζει αμέσως τη shock-rock πλευρά τους και δημιουργεί την αίσθηση ότι η συναυλία ξεκινά ως παράσταση, όχι απλώς ως playlist.</t>
+  </si>
+  <si>
+    <t>Η διασκευή στο Ashford–Simpson–Armstead soul/R&amp;B τραγούδι, γνωστό και από την hard-rock εκδοχή των Humble Pie, μεταφέρει προσωρινά το set σε πιο bluesy territory. Οι W.A.S.P. δεν επιχειρούν να αναπαραστήσουν soul ατμόσφαιρα· το κάνουν σκληρότερο, πιο γρήγορο και πιο κιθαριστικό. Ο τίτλος γίνεται μια κλασική hard-rock δήλωση άρνησης, ο αφηγητής δεν θέλει θεραπεία ή διόρθωση, θέλει να ζήσει στο δικό του, υπερβολικό rock ’n’ roll πλαίσιο. Λειτουργεί καλά ως αλλαγή χρώματος μετά το “Electric Circus”, αν και η επιλογή του ως cover μειώνει ελαφρώς τη συνοχή του set σε σχέση με τα αυθεντικά W.A.S.P. anthems.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο καθαρά early-W.A.S.P. signatures. Ο τίτλος είναι σκόπιμα μηχανικός και σεξουαλικός, η αγάπη παρουσιάζεται όχι ως τρυφερό συναίσθημα, αλλά ως ανυπόμονη, σχεδόν βιομηχανική επιθυμία. Η live εκτέλεση κρατά τη sleaze-metal ένταση του original, με το riff να επιτρέπει στο κοινό να συμμετέχει και τη φωνή του Lawless να ακούγεται πιο τραχιά και λιγότερο studio-controlled. Το τραγούδι συμπυκνώνει την περίοδο όπου οι W.A.S.P. χρησιμοποιούσαν shock, χιούμορ και υπερβολή ως βασικές μουσικές και σκηνικές ταυτότητες. Είναι από τα tracks που δικαιολογούν την υψηλή θέση του δίσκου στην αρχική τους fanbase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ένα από τα δύο νέα live κομμάτια της περιόδου και σημαντικός σύνδεσμος ανάμεσα στον παλιό W.A.S.P. ήχο και την πιο σκοτεινή κατεύθυνση που θα ακολουθούσε. Ο “manimal” είναι υβριδική φιγούρα — άνθρωπος και ζώο, λογική και ένστικτο — και το riffing ανταποκρίνεται με βαρύτερη, πιο απειλητική διάθεση. Η σύνθεση δεν έχει τη λάμψη των παλιών singles, αλλά έχει καθαρή live λειτουργία, mid-tempo βάρος, απειλητικό refrain και χώρο για το κοινό να παρακολουθήσει το σκοτεινότερο persona της μπάντας. Η παρουσία του είναι πολύτιμη, επειδή δεν υπάρχει σε κανονικό studio album της εποχής. </t>
+  </si>
+  <si>
+    <t>Η απόλυτη δήλωση ταυτότητας των W.A.S.P. και το φυσικότερο crowd anthem του set. Η φράση “I wanna be somebody” συνοψίζει την ανάγκη να βγεις από την αφάνεια, να αποκτήσεις φωνή και να αρνηθείς να μείνεις αόρατος. Μουσικά είναι απλό, γρήγορο και ακριβώς όσο θεατρικό χρειάζεται, riff που μπαίνει αμέσως, chorus που δεν χρειάζεται εξήγηση και ερμηνεία που μετατρέπει τον προσωπικό πόθο σε συλλογική κραυγή. Η live εκτέλεση διαρκεί σχεδόν επτά λεπτά, ώστε η μπάντα να αξιοποιήσει την αντίδραση του κοινού. Είναι το κορυφαίο track του δίσκου όχι λόγω τεχνικής πολυπλοκότητας, αλλά επειδή συλλαμβάνει τέλεια τη σχέση ανάμεσα σε W.A.S.P. και fans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το δεύτερο νέο live track και ίσως το πιο άμεσο, fast-metal σημείο της B πλευράς. Ο τίτλος δεν κρύβει τις προθέσεις, η μπάντα παίζει πιο σκληρά, πιο γρήγορα και με έμφαση στο momentum. Η σύνθεση μοιάζει φτιαγμένη για live performance, με riff που επιτρέπει crowd response και drums που κρατούν την πίεση ψηλά. Δεν είναι τόσο θεματικά ολοκληρωμένο όσο το “The Manimal”, αλλά λειτουργεί εξαιρετικά ως έκρηξη ενέργειας μετά το μαζικό chant του “I Wanna Be Somebody”. Το ότι παρέμεινε ένα από τα λίγα νέα songs της live κυκλοφορίας του δίνει συλλεκτική αξία για τον κατάλογο των W.A.S.P. </t>
+  </si>
+  <si>
+    <t>Το party-metal κλείσιμο της live setlist πριν από το studio bonus. Ο τίτλος μετατρέπει το Texas σε υπερβολικό rock ’n’ roll χώρο, αλκοόλ, ταχύτητα, νύχτα και απόλυτη έλλειψη αυτοσυγκράτησης. Το κομμάτι έχει boogie hard-rock βάση και chorus φτιαγμένο για φωνές από το κοινό. Δεν προσπαθεί να είναι βαθύ· επιδιώκει να αφήσει τον ακροατή με αίσθηση χαοτικής διασκέδασης. Ως τραγούδι δεν έχει τη μελωδική δραματικότητα του “Wild Child” ή την ταυτότητα του “I Wanna Be Somebody”, αλλά ως live staple λειτουργεί άψογα — είναι η απλή, θορυβώδης διασκέδαση που είναι αναγκαία σε μια W.A.S.P. συναυλία.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το μοναδικό studio track της δικής σου έκδοσης και, επομένως, το κομμάτι που διακόπτει τη φυσική συναυλιακή ροή. Γραμμένο για το Ghoulies II, αξιοποιεί horror-comedy ατμόσφαιρα, heavy-metal riffing και τη χαρακτηριστική W.A.S.P. υπερβολή. Ο τίτλος είναι καθαρό shock-rock σύνθημα, φώναξε μέχρι να σου αρέσει. Ως soundtrack song είναι διασκεδαστικό, γρήγορο και ταιριαστό με την camp αισθητική της μπάντας, αλλά δεν έχει το ιστορικό ή συναισθηματικό βάρος των live classics που προηγούνται. Γι’ αυτό η θέση του ως bonus, μετά το set-closing “Blind In Texas”, είναι σωστή. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12041,6 +12155,13 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -12099,7 +12220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12174,6 +12295,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12486,7 +12610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -15889,6 +16013,38 @@
         <v>3570</v>
       </c>
       <c r="J106" s="11" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D107" s="6">
+        <v>1987</v>
+      </c>
+      <c r="E107" s="10">
+        <v>3.57</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>3617</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>3606</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>3605</v>
+      </c>
+      <c r="I107" s="11" t="s">
+        <v>3603</v>
+      </c>
+      <c r="J107" s="11" t="s">
         <v>3571</v>
       </c>
     </row>
@@ -16101,6 +16257,8 @@
     <hyperlink ref="J105" r:id="rId205" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
     <hyperlink ref="I106" r:id="rId206" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
     <hyperlink ref="J106" r:id="rId207" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
+    <hyperlink ref="J107" r:id="rId208" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
+    <hyperlink ref="I107" r:id="rId209" xr:uid="{EF8A629E-3733-475B-9310-6FA2999BA7DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16108,7 +16266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1006"/>
+  <dimension ref="A1:I1017"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -43449,6 +43607,303 @@
       </c>
       <c r="I1006" s="6"/>
     </row>
+    <row r="1007" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1007" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1007" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1007" s="22" t="s">
+        <v>3607</v>
+      </c>
+      <c r="D1007" s="7" t="s">
+        <v>3618</v>
+      </c>
+      <c r="E1007" s="20">
+        <v>3.87</v>
+      </c>
+      <c r="F1007" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1007" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1007" s="26" t="s">
+        <v>3633</v>
+      </c>
+      <c r="I1007" s="6"/>
+    </row>
+    <row r="1008" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1008" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1008" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1008" s="22" t="s">
+        <v>3608</v>
+      </c>
+      <c r="D1008" s="7" t="s">
+        <v>3619</v>
+      </c>
+      <c r="E1008" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F1008" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1008" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1008" s="26" t="s">
+        <v>3634</v>
+      </c>
+      <c r="I1008" s="6"/>
+    </row>
+    <row r="1009" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1009" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1009" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1009" s="22" t="s">
+        <v>3609</v>
+      </c>
+      <c r="D1009" s="7" t="s">
+        <v>3620</v>
+      </c>
+      <c r="E1009" s="20">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F1009" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1009" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1009" s="26" t="s">
+        <v>3635</v>
+      </c>
+      <c r="I1009" s="6"/>
+    </row>
+    <row r="1010" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1010" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1010" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1010" s="22" t="s">
+        <v>3610</v>
+      </c>
+      <c r="D1010" s="7" t="s">
+        <v>3621</v>
+      </c>
+      <c r="E1010" s="20">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="F1010" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1010" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1010" s="26" t="s">
+        <v>3630</v>
+      </c>
+      <c r="I1010" s="6"/>
+    </row>
+    <row r="1011" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1011" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1011" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1011" s="22" t="s">
+        <v>3611</v>
+      </c>
+      <c r="D1011" s="7" t="s">
+        <v>3622</v>
+      </c>
+      <c r="E1011" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F1011" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1011" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1011" s="26" t="s">
+        <v>3631</v>
+      </c>
+      <c r="I1011" s="6"/>
+    </row>
+    <row r="1012" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1012" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1012" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1012" s="22" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D1012" s="7" t="s">
+        <v>3623</v>
+      </c>
+      <c r="E1012" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F1012" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1012" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1012" s="26" t="s">
+        <v>3632</v>
+      </c>
+      <c r="I1012" s="6"/>
+    </row>
+    <row r="1013" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1013" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1013" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1013" s="22" t="s">
+        <v>3615</v>
+      </c>
+      <c r="D1013" s="7" t="s">
+        <v>3624</v>
+      </c>
+      <c r="E1013" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F1013" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1013" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1013" s="26" t="s">
+        <v>3636</v>
+      </c>
+      <c r="I1013" s="6"/>
+    </row>
+    <row r="1014" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1014" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1014" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1014" s="22" t="s">
+        <v>3614</v>
+      </c>
+      <c r="D1014" s="7" t="s">
+        <v>3625</v>
+      </c>
+      <c r="E1014" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F1014" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1014" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1014" s="26" t="s">
+        <v>3637</v>
+      </c>
+      <c r="I1014" s="6"/>
+    </row>
+    <row r="1015" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1015" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1015" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1015" s="22" t="s">
+        <v>3629</v>
+      </c>
+      <c r="D1015" s="7" t="s">
+        <v>3626</v>
+      </c>
+      <c r="E1015" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F1015" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1015" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1015" s="26" t="s">
+        <v>3638</v>
+      </c>
+      <c r="I1015" s="6"/>
+    </row>
+    <row r="1016" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1016" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1016" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1016" s="22" t="s">
+        <v>3613</v>
+      </c>
+      <c r="D1016" s="7" t="s">
+        <v>3627</v>
+      </c>
+      <c r="E1016" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F1016" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1016" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1016" s="26" t="s">
+        <v>3639</v>
+      </c>
+      <c r="I1016" s="6"/>
+    </row>
+    <row r="1017" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1017" s="6">
+        <v>4000501</v>
+      </c>
+      <c r="B1017" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1017" s="22" t="s">
+        <v>3612</v>
+      </c>
+      <c r="D1017" s="7" t="s">
+        <v>3628</v>
+      </c>
+      <c r="E1017" s="20">
+        <v>3.36</v>
+      </c>
+      <c r="F1017" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1017" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1017" s="26" t="s">
+        <v>3640</v>
+      </c>
+      <c r="I1017" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1E0D2-FA7D-4B9D-953B-658F1D11ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55647B5C-C999-4578-A4E3-25F1E57F74E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3941" uniqueCount="3641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="3678">
   <si>
     <t>No</t>
   </si>
@@ -12033,9 +12033,6 @@
     <t>Επιστροφή στο shock/sleaze ύφος με τραγούδι που βασίζεται περισσότερο στο attitude και στην πρόκληση από ό,τι στη λεπτή σύνθεση. Ο τίτλος χρησιμοποιεί αριθμητική και ακρωνύμιο σαν υπερβολικό, cartoonish sexual boast, κάτι χαρακτηριστικό της περιόδου. Η μπάντα το παίζει με live ένταση και άμεσο riffing, ενώ ο Lawless το αντιμετωπίζει σαν μέρος του stage persona του. Δεν έχει την ατμοσφαιρική ανάπτυξη του “Wild Child”, αλλά λειτουργεί αποτελεσματικά ως adrenaline track και υπενθυμίζει την ακατέργαστη, προκλητική ενέργεια των πρώτων δίσκων.</t>
   </si>
   <si>
-    <t>Η συναισθηματική κορύφωση της A πλευράς και μία από τις καλύτερες W.A.S.P. μπαλάντες. Ο τίτλος συνδυάζει τον ύπνο με τη φωτιά — μια εικόνα επιθυμίας τόσο έντονης ώστε να γίνεται επικίνδυνη. Η live εκτέλεση διατηρεί την αργή, δραματική ανάπτυξη του original, ενώ η κιθάρα αναλαμβάνει μεγαλύτερο ρόλο στο χτίσιμο της έντασης. Ο Lawless τραγουδά λιγότερο σαν shock-rock χαρακτήρας και περισσότερο σαν κλασικός hard-rock vocalist, κάτι που δίνει στο τραγούδι διαχρονική αξία. Μετά την sleaze πλευρά των προηγούμενων tracks, λειτουργεί ως απόδειξη ότι η μπάντα είχε και πραγματική μελωδική ευαισθησία.</t>
-  </si>
-  <si>
     <t>Το live album ανοίγει με το σωστό είδος θεατρικής υπερβολής. Το “Electric Circus” είναι ο κόσμος των W.A.S.P. ως αποπροσανατολιστικό, επικίνδυνο θέαμα, ένταση, σεξουαλικότητα, βία, φώτα και μια μπάντα που μετατρέπει το metal show σε carnival. Η live εκτέλεση δίνει στο τραγούδι περισσότερο βάρος από τη studio version, κυρίως λόγω του ρυθμικού drive και της αίσθησης ότι ο Blackie Lawless απευθύνεται άμεσα στο κοινό. Δεν είναι το πιο βαθύ τραγούδι του συγκροτήματος, αλλά είναι ιδανικό opener, παρουσιάζει αμέσως τη shock-rock πλευρά τους και δημιουργεί την αίσθηση ότι η συναυλία ξεκινά ως παράσταση, όχι απλώς ως playlist.</t>
   </si>
   <si>
@@ -12045,19 +12042,133 @@
     <t>Ένα από τα πιο καθαρά early-W.A.S.P. signatures. Ο τίτλος είναι σκόπιμα μηχανικός και σεξουαλικός, η αγάπη παρουσιάζεται όχι ως τρυφερό συναίσθημα, αλλά ως ανυπόμονη, σχεδόν βιομηχανική επιθυμία. Η live εκτέλεση κρατά τη sleaze-metal ένταση του original, με το riff να επιτρέπει στο κοινό να συμμετέχει και τη φωνή του Lawless να ακούγεται πιο τραχιά και λιγότερο studio-controlled. Το τραγούδι συμπυκνώνει την περίοδο όπου οι W.A.S.P. χρησιμοποιούσαν shock, χιούμορ και υπερβολή ως βασικές μουσικές και σκηνικές ταυτότητες. Είναι από τα tracks που δικαιολογούν την υψηλή θέση του δίσκου στην αρχική τους fanbase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ένα από τα δύο νέα live κομμάτια της περιόδου και σημαντικός σύνδεσμος ανάμεσα στον παλιό W.A.S.P. ήχο και την πιο σκοτεινή κατεύθυνση που θα ακολουθούσε. Ο “manimal” είναι υβριδική φιγούρα — άνθρωπος και ζώο, λογική και ένστικτο — και το riffing ανταποκρίνεται με βαρύτερη, πιο απειλητική διάθεση. Η σύνθεση δεν έχει τη λάμψη των παλιών singles, αλλά έχει καθαρή live λειτουργία, mid-tempo βάρος, απειλητικό refrain και χώρο για το κοινό να παρακολουθήσει το σκοτεινότερο persona της μπάντας. Η παρουσία του είναι πολύτιμη, επειδή δεν υπάρχει σε κανονικό studio album της εποχής. </t>
-  </si>
-  <si>
     <t>Η απόλυτη δήλωση ταυτότητας των W.A.S.P. και το φυσικότερο crowd anthem του set. Η φράση “I wanna be somebody” συνοψίζει την ανάγκη να βγεις από την αφάνεια, να αποκτήσεις φωνή και να αρνηθείς να μείνεις αόρατος. Μουσικά είναι απλό, γρήγορο και ακριβώς όσο θεατρικό χρειάζεται, riff που μπαίνει αμέσως, chorus που δεν χρειάζεται εξήγηση και ερμηνεία που μετατρέπει τον προσωπικό πόθο σε συλλογική κραυγή. Η live εκτέλεση διαρκεί σχεδόν επτά λεπτά, ώστε η μπάντα να αξιοποιήσει την αντίδραση του κοινού. Είναι το κορυφαίο track του δίσκου όχι λόγω τεχνικής πολυπλοκότητας, αλλά επειδή συλλαμβάνει τέλεια τη σχέση ανάμεσα σε W.A.S.P. και fans.</t>
   </si>
   <si>
     <t xml:space="preserve">Το δεύτερο νέο live track και ίσως το πιο άμεσο, fast-metal σημείο της B πλευράς. Ο τίτλος δεν κρύβει τις προθέσεις, η μπάντα παίζει πιο σκληρά, πιο γρήγορα και με έμφαση στο momentum. Η σύνθεση μοιάζει φτιαγμένη για live performance, με riff που επιτρέπει crowd response και drums που κρατούν την πίεση ψηλά. Δεν είναι τόσο θεματικά ολοκληρωμένο όσο το “The Manimal”, αλλά λειτουργεί εξαιρετικά ως έκρηξη ενέργειας μετά το μαζικό chant του “I Wanna Be Somebody”. Το ότι παρέμεινε ένα από τα λίγα νέα songs της live κυκλοφορίας του δίνει συλλεκτική αξία για τον κατάλογο των W.A.S.P. </t>
   </si>
   <si>
-    <t>Το party-metal κλείσιμο της live setlist πριν από το studio bonus. Ο τίτλος μετατρέπει το Texas σε υπερβολικό rock ’n’ roll χώρο, αλκοόλ, ταχύτητα, νύχτα και απόλυτη έλλειψη αυτοσυγκράτησης. Το κομμάτι έχει boogie hard-rock βάση και chorus φτιαγμένο για φωνές από το κοινό. Δεν προσπαθεί να είναι βαθύ· επιδιώκει να αφήσει τον ακροατή με αίσθηση χαοτικής διασκέδασης. Ως τραγούδι δεν έχει τη μελωδική δραματικότητα του “Wild Child” ή την ταυτότητα του “I Wanna Be Somebody”, αλλά ως live staple λειτουργεί άψογα — είναι η απλή, θορυβώδης διασκέδαση που είναι αναγκαία σε μια W.A.S.P. συναυλία.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Το μοναδικό studio track της δικής σου έκδοσης και, επομένως, το κομμάτι που διακόπτει τη φυσική συναυλιακή ροή. Γραμμένο για το Ghoulies II, αξιοποιεί horror-comedy ατμόσφαιρα, heavy-metal riffing και τη χαρακτηριστική W.A.S.P. υπερβολή. Ο τίτλος είναι καθαρό shock-rock σύνθημα, φώναξε μέχρι να σου αρέσει. Ως soundtrack song είναι διασκεδαστικό, γρήγορο και ταιριαστό με την camp αισθητική της μπάντας, αλλά δεν έχει το ιστορικό ή συναισθηματικό βάρος των live classics που προηγούνται. Γι’ αυτό η θέση του ως bonus, μετά το set-closing “Blind In Texas”, είναι σωστή. </t>
+  </si>
+  <si>
+    <t>Η συναισθηματική κορύφωση της A πλευράς και μία από τις καλύτερες W.A.S.P. μπαλάντες. Ο τίτλος συνδυάζει τον ύπνο με τη φωτιά , μια εικόνα επιθυμίας τόσο έντονης ώστε να γίνεται επικίνδυνη. Η live εκτέλεση διατηρεί την αργή, δραματική ανάπτυξη του original, ενώ η κιθάρα αναλαμβάνει μεγαλύτερο ρόλο στο χτίσιμο της έντασης. Ο Lawless τραγουδά λιγότερο σαν shock-rock χαρακτήρας και περισσότερο σαν κλασικός hard-rock vocalist, κάτι που δίνει στο τραγούδι διαχρονική αξία. Μετά την sleaze πλευρά των προηγούμενων tracks, λειτουργεί ως απόδειξη ότι η μπάντα είχε και πραγματική μελωδική ευαισθησία.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ένα από τα δύο νέα live κομμάτια της περιόδου και σημαντικός σύνδεσμος ανάμεσα στον παλιό W.A.S.P. ήχο και την πιο σκοτεινή κατεύθυνση που θα ακολουθούσε. Ο “manimal” είναι υβριδική φιγούρα , άνθρωπος και ζώο, λογική και ένστικτο , και το riffing ανταποκρίνεται με βαρύτερη, πιο απειλητική διάθεση. Η σύνθεση δεν έχει τη λάμψη των παλιών singles, αλλά έχει καθαρή live λειτουργία, mid-tempo βάρος, απειλητικό refrain και χώρο για το κοινό να παρακολουθήσει το σκοτεινότερο persona της μπάντας. Η παρουσία του είναι πολύτιμη, επειδή δεν υπάρχει σε κανονικό studio album της εποχής. </t>
+  </si>
+  <si>
+    <t>Το party-metal κλείσιμο της live setlist πριν από το studio bonus. Ο τίτλος μετατρέπει το Texas σε υπερβολικό rock ’n’ roll χώρο, αλκοόλ, ταχύτητα, νύχτα και απόλυτη έλλειψη αυτοσυγκράτησης. Το κομμάτι έχει boogie hard-rock βάση και chorus φτιαγμένο για φωνές από το κοινό. Δεν προσπαθεί να είναι βαθύ· επιδιώκει να αφήσει τον ακροατή με αίσθηση χαοτικής διασκέδασης. Ως τραγούδι δεν έχει τη μελωδική δραματικότητα του “Wild Child” ή την ταυτότητα του “I Wanna Be Somebody”, αλλά ως live staple λειτουργεί άψογα , είναι η απλή, θορυβώδης διασκέδαση που είναι αναγκαία σε μια W.A.S.P. συναυλία.</t>
+  </si>
+  <si>
+    <t>Warlock</t>
+  </si>
+  <si>
+    <t>Triumph And Agony</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/JKetj96MFUPR3Ew2-tL6atsgS-7SkAhU2G-X3kiWbjY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTg4NjQz/OTMtMTc4ODcxMjc0/My00NTU0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/8864393-Warlock-Triumph-And-Agony</t>
+  </si>
+  <si>
+    <t>All We Are</t>
+  </si>
+  <si>
+    <t>Three Minute Warning</t>
+  </si>
+  <si>
+    <t>I Rule The Ruins</t>
+  </si>
+  <si>
+    <t>Kiss Of Death</t>
+  </si>
+  <si>
+    <t>Make Time For Love</t>
+  </si>
+  <si>
+    <t>Für Immer</t>
+  </si>
+  <si>
+    <t>Cold, Cold World</t>
+  </si>
+  <si>
+    <t>Metal Tango</t>
+  </si>
+  <si>
+    <t>Touch Of Evil</t>
+  </si>
+  <si>
+    <t>East Meets West</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και θεατρικό, με vampiric/horror εικόνα και μελωδίες που λειτουργούν σαν δραματικός μονόλογος. Ο «φιλί του θανάτου» είναι η στιγμή όπου η έλξη και ο κίνδυνος γίνονται αδιαχώριστα, και η μπάντα το ντύνει με heavy riffs, έντονη κλιμάκωση και φωνητική ερμηνεία που αποφεύγει τη μονοτονία. Δεν έχει το άμεσο crowd-chant του “All We Are”, αλλά χτίζει πολύ ισχυρό mood και αξιοποιεί την ικανότητα της Doro να συνδυάζει μελωδία με επιθετική άρθρωση. Η κριτική για τον δίσκο το περιγράφει ως «tragic vampire soliloquy», διατύπωση που αποδίδει καλά την gothic δραματουργία του.</t>
+  </si>
+  <si>
+    <t>Η power-ballad στιγμή της A πλευράς. Μετά τη γρήγορη και σκοτεινή ακολουθία των προηγούμενων τραγουδιών, το κομμάτι επιβραδύνει και στρέφεται σε ρομαντική, πιο ευάλωτη έκφραση. Ο τίτλος υποστηρίζει ότι η αγάπη χρειάζεται χώρο και χρόνο μέσα σε έναν κόσμο πίεσης, και η Doro το τραγουδά με ειλικρινή, soulful χροιά. Οι κιθάρες παραμένουν παρούσες, αλλά δεν κυριαρχούν· η σύνθεση βασίζεται στη μελωδία και στην αναμονή της κορύφωσης. Δεν έχει τη διαχρονική ιδιαιτερότητα του “Für Immer”, όμως είναι σημαντικό για την ισορροπία της A πλευράς και προετοιμάζει τον ακροατή για το πιο μελωδικό B-side.</t>
+  </si>
+  <si>
+    <t>Ένα melodic metal τραγούδι που χρησιμοποιεί την ιδέα συνάντησης Ανατολής και Δύσης ως μήνυμα επικοινωνίας και σύνδεσης, με ιαπωνικές/ανατολικές εικόνες στη θεματική του. Το riffing παραμένει κλασικά ευρωπαϊκό heavy metal, αλλά η μελωδική γραμμή και το chorus είναι πιο ανοιχτά και arena-ready. Η σύνθεση δεν βασίζεται σε εξωτισμό ως μουσικό gimmick· η «Ανατολή» λειτουργεί περισσότερο ως αφηγηματικός τόπος, και η πραγματική δύναμη βρίσκεται στη σχέση κιθάρας, ρυθμού και φωνής. Είναι από τα tracks που επιβεβαιώνουν ότι το album μπορεί να είναι προσβάσιμο χωρίς να νερώνει τη metal ταυτότητά του.</t>
+  </si>
+  <si>
+    <t>Απότομη επιτάχυνση μετά το sing-along opener. Ο τίτλος λειτουργεί σαν countdown, και η μουσική ανταποκρίνεται με σύντομη διάρκεια, γρήγορο riffing και αποφασιστικό Teutonic-metal drive. Η σύνθεση δεν προσπαθεί να γίνει τεχνική επίδειξη· χρησιμοποιεί την ταχύτητα για να αποδείξει ότι η μπάντα δεν είναι μόνο melodic anthem act. Τα drums και οι κιθάρες πιέζουν συνεχώς προς τα εμπρός, ενώ η Doro διατηρεί τη μελωδικότητα της φωνής της μέσα σε πολύ πιο επιθετικό πλαίσιο. Κριτικές την έχουν παρομοιάσει με κάτι που θα μπορούσαν να γράψουν οι Accept , δηλαδή γερμανικό traditional metal με speed-metal νεύρο και κοφτά riffs.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη anthem στιγμή των Warlock και το τραγούδι που συνοψίζει ιδανικά τη δύναμη του δίσκου. Το “All We Are” δεν βασίζεται σε σύνθετη αφήγηση, μιλά για ενότητα, αυτοπεποίθηση και τη συλλογική ταυτότητα του metal κοινού. Η απλότητα είναι ακριβώς η δύναμή του , το riff είναι άμεσο, ο ρυθμός σταθερός και το chorus φτιαγμένο για να το τραγουδά ένα ολόκληρο venue. Η Doro Pesch δεν προσπαθεί να μιμηθεί ανδρική heavy-metal φωνή· δίνει στο κομμάτι δική της, καθαρή και αποφασιστική παρουσία, με φωνητική ένταση που κρατά το anthem από το να γίνει απλώς radio rock. Η Decibel το περιγράφει ως αληθινό ’80s hard-rock anthem και ένα από τα δύο διαχρονικά bookends του album.</t>
+  </si>
+  <si>
+    <t>Από τα πιο επικά και πιο ολοκληρωμένα tracks του δίσκου. Ο τίτλος δηλώνει κυριαρχία μέσα σε έναν κόσμο καταστροφής, η αφηγήτρια δεν εμφανίζεται ως θύμα, αλλά ως δύναμη που επιβιώνει και ελέγχει τα συντρίμμια. Η μουσική κινείται με μεγαλύτερη δραματική έκταση από το “Three Minute Warning”, συνδυάζοντας βαριά riffs, μελωδικές κιθάρες και μια φωνητική γραμμή που περνά από απειλή σε ύμνο. Η Doro τραγουδά με πραγματική command, ενώ τα solo και οι μεταβάσεις δίνουν στο κομμάτι αίσθηση μεγάλης κλίμακας. Είναι μία από τις συνθέσεις που αναφέρονται συχνά ως κορυφαίο Warlock anthem και αποτελεί βασικό λόγο που το album ξεχωρίζει από μια τυπική 1987 metal κυκλοφορία.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο σκούρο και απειλητικό heavy metal. Η «επαφή του κακού» είναι μια στιγμή πειρασμού ή διαφθοράς, και το τραγούδι χρησιμοποιεί βαρύτερα riffs, πιο κοφτή ρυθμική κίνηση και υψίφωνες κορυφώσεις από τη Doro. Εδώ η φωνή της λειτουργεί σχεδόν σαν όπλο, οι κραυγές στο τέλος δεν είναι διακοσμητικές, αλλά κλείνουν το κομμάτι με αίσθηση αστάθειας και κινδύνου. Είναι λιγότερο θεατρικό από το “Kiss Of Death” και λιγότερο επικό από το “I Rule The Ruins”, αλλά αποτελεί σταθερό, σκοτεινό album cut. Η Decibel/Capital Chaos αποτίμηση το ξεχωρίζει ακριβώς για την ακραία φωνητική του κατάληξη.</t>
+  </si>
+  <si>
+    <t>Ο τίτλος προϊδεάζει για υβρίδιο, tango ως ιδέα πάθους, έντασης και χορού, metal ως βάρος και riff. Η μπάντα δεν γίνεται πραγματικά latin/tango σχήμα· χρησιμοποιεί τον τίτλο ως θεατρική εικόνα και μεταφέρει τη λογική του χορού σε mid-tempo, δραματικό heavy-rock groove. Η Doro τραγουδά με πιο παιχνιδιάρικη αυτοπεποίθηση, ενώ οι κιθάρες κρατούν το κομμάτι σε καθαρά metal έδαφος. Είναι ένα από τα πιο ιδιαίτερα tracks του δίσκου, όχι επειδή επανεφευρίσκει το είδος, αλλά επειδή δίνει σε μια κλασική hard-rock φόρμα ξεκάθαρο χαρακτήρα. Η κριτική το αναφέρει χαρακτηριστικά ως το πιθανώς μοναδικό «metal tango».</t>
+  </si>
+  <si>
+    <t>Μελωδικό, σκοτεινό και πιο εσωστρεφές, με τον τίτλο να παρουσιάζει έναν κόσμο συναισθηματικής αποξένωσης. Η μουσική δεν εγκαταλείπει την ένταση, αλλά αφήνει περισσότερο χώρο στη φωνητική μελωδία και σε μια αίσθηση παγώματος/απόστασης. Η Doro κρατά το τραγούδι ανθρώπινο, δεν τραγουδά μια γενική metal καταγγελία, αλλά μεταφέρει την εμπειρία της μοναξιάς μέσα σε σκληρό περιβάλλον. Είναι λιγότερο άμεσο από τα βασικά hits, όμως η θέση του πριν από το “Für Immer” είναι λειτουργική, βυθίζει τη B πλευρά σε πιο μελαγχολικό mood και κάνει το τελικό ballad να ακούγεται πιο απελευθερωτικό.</t>
+  </si>
+  <si>
+    <t>Το ιδανικό κλείσιμο και μία από τις πιο αγαπητές Doro/Warlock μπαλάντες. Ο γερμανικός τίτλος σημαίνει «για πάντα», και η επιλογή της γλώσσας δίνει στο τραγούδι μια πιο άμεση, προσωπική και ευρωπαϊκή ταυτότητα. Η σύνθεση είναι power ballad, αλλά δεν στηρίζεται στη σακχαρώδη ευκολία, ξεκινά με μελαγχολία, χτίζει σε δραματικό chorus και αφήνει τη φωνή της Doro να μεταφέρει αφοσίωση, απώλεια και ελπίδα. Το τραγούδι παραμένει στα live setlists της Doro, ενώ οι πηγές το αναγνωρίζουν ως ένα από τα δύο τραγούδια-πυλώνες του album μαζί με το “All We Are”. Είναι ο σωστός αντίποδας του opener, από τη συλλογική metal ενότητα οδηγεί σε προσωπική, διαχρονική υπόσχεση.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Traditional Heavy Metal, Melodic Heavy Metal, German Metal, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Arena Metal, Metal Anthem, Melodic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Speed Metal [Fast Traditional Metal, Teutonic Metal, Riff Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Heavy Metal, Melodic Metal, Dark Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Metal, Theatrical Metal, Gothic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Power Ballad, Melodic Hard Rock, Dramatic Metal Ballad]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Melodic Metal, Japan-themed Metal, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Screaming Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Theatrical Metal, Mid-tempo Riff Metal, Melodic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Melodic Heavy Metal, Social Alienation Metal, Dark Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Power Ballad, German-language Metal Ballad, Epic Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Vertigo – 832 804-1 (Europe / Netherlands, 1987, LP, Album). Features GEMA rights society, "Made in Holland" on labels, and "Made in W.-Germany" on the rear cover. Direct Metal Mastering (DMM) cut utilizing Sterling Sound metal parts with custom runout variations.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Triumph And Agony είναι το τέταρτο και τελευταίο studio album των Warlock, κυκλοφόρησε στις 29 Σεπτεμβρίου 1987 και ηχογραφήθηκε στις ΗΠΑ με παραγωγό τον Joey Balin. Είναι ο δίσκος που καθόρισε την κληρονομιά του σχήματος: traditional heavy metal με melodic hard-rock hooks, power-ballad δραματικότητα και καθαρό late-'80s metal sheen, χωρίς να γίνεται πλήρως hair metal. Συνοδεύεται από εσωτερικό φάκελο (OIS) με στίχους. Τυπική DMM κοπή με εξαιρετική διαύγεια στα πρίμα και τα μεσαία.</t>
   </si>
 </sst>
 </file>
@@ -12220,7 +12331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12287,9 +12398,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12610,7 +12718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16046,6 +16154,38 @@
       </c>
       <c r="J107" s="11" t="s">
         <v>3571</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>3641</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>3642</v>
+      </c>
+      <c r="D108" s="6">
+        <v>1987</v>
+      </c>
+      <c r="E108" s="10">
+        <v>3.58</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>3665</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>3677</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>3676</v>
+      </c>
+      <c r="I108" s="11" t="s">
+        <v>3644</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>3643</v>
       </c>
     </row>
   </sheetData>
@@ -16259,6 +16399,8 @@
     <hyperlink ref="J106" r:id="rId207" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
     <hyperlink ref="J107" r:id="rId208" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
     <hyperlink ref="I107" r:id="rId209" xr:uid="{EF8A629E-3733-475B-9310-6FA2999BA7DF}"/>
+    <hyperlink ref="J108" r:id="rId210" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
+    <hyperlink ref="I108" r:id="rId211" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16266,7 +16408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1017"/>
+  <dimension ref="A1:I1027"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -42029,7 +42171,7 @@
       </c>
       <c r="I948" s="6"/>
     </row>
-    <row r="949" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+    <row r="949" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A949" s="6">
         <v>646934</v>
       </c>
@@ -42051,14 +42193,14 @@
       <c r="G949" s="12">
         <v>4</v>
       </c>
-      <c r="H949" s="23" t="s">
+      <c r="H949" s="9" t="s">
         <v>3423</v>
       </c>
       <c r="I949" s="6" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="950" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+    <row r="950" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A950" s="6">
         <v>646934</v>
       </c>
@@ -42080,12 +42222,12 @@
       <c r="G950" s="12">
         <v>3.8</v>
       </c>
-      <c r="H950" s="23" t="s">
+      <c r="H950" s="9" t="s">
         <v>3424</v>
       </c>
       <c r="I950" s="6"/>
     </row>
-    <row r="951" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+    <row r="951" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A951" s="6">
         <v>646934</v>
       </c>
@@ -42107,12 +42249,12 @@
       <c r="G951" s="12">
         <v>4.2</v>
       </c>
-      <c r="H951" s="23" t="s">
+      <c r="H951" s="9" t="s">
         <v>3425</v>
       </c>
       <c r="I951" s="6"/>
     </row>
-    <row r="952" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="952" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A952" s="6">
         <v>646934</v>
       </c>
@@ -42134,12 +42276,12 @@
       <c r="G952" s="12">
         <v>4.5</v>
       </c>
-      <c r="H952" s="23" t="s">
+      <c r="H952" s="9" t="s">
         <v>3426</v>
       </c>
       <c r="I952" s="6"/>
     </row>
-    <row r="953" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+    <row r="953" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A953" s="6">
         <v>646934</v>
       </c>
@@ -42161,12 +42303,12 @@
       <c r="G953" s="12">
         <v>3.9</v>
       </c>
-      <c r="H953" s="23" t="s">
+      <c r="H953" s="9" t="s">
         <v>3427</v>
       </c>
       <c r="I953" s="6"/>
     </row>
-    <row r="954" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+    <row r="954" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A954" s="6">
         <v>646934</v>
       </c>
@@ -42188,12 +42330,12 @@
       <c r="G954" s="12">
         <v>4.3</v>
       </c>
-      <c r="H954" s="23" t="s">
+      <c r="H954" s="9" t="s">
         <v>3428</v>
       </c>
       <c r="I954" s="6"/>
     </row>
-    <row r="955" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+    <row r="955" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A955" s="6">
         <v>646934</v>
       </c>
@@ -42215,12 +42357,12 @@
       <c r="G955" s="12">
         <v>3.7</v>
       </c>
-      <c r="H955" s="23" t="s">
+      <c r="H955" s="9" t="s">
         <v>3422</v>
       </c>
       <c r="I955" s="6"/>
     </row>
-    <row r="956" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+    <row r="956" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A956" s="6">
         <v>646934</v>
       </c>
@@ -42242,12 +42384,12 @@
       <c r="G956" s="12">
         <v>3.8</v>
       </c>
-      <c r="H956" s="23" t="s">
+      <c r="H956" s="9" t="s">
         <v>3421</v>
       </c>
       <c r="I956" s="6"/>
     </row>
-    <row r="957" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+    <row r="957" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A957" s="6">
         <v>646934</v>
       </c>
@@ -42269,12 +42411,12 @@
       <c r="G957" s="12">
         <v>4</v>
       </c>
-      <c r="H957" s="23" t="s">
+      <c r="H957" s="9" t="s">
         <v>3429</v>
       </c>
       <c r="I957" s="6"/>
     </row>
-    <row r="958" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+    <row r="958" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A958" s="6">
         <v>646934</v>
       </c>
@@ -42296,7 +42438,7 @@
       <c r="G958" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H958" s="23" t="s">
+      <c r="H958" s="9" t="s">
         <v>3430</v>
       </c>
       <c r="I958" s="6" t="s">
@@ -42732,7 +42874,7 @@
       <c r="G974" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H974" s="24" t="s">
+      <c r="H974" s="23" t="s">
         <v>3500</v>
       </c>
       <c r="I974" s="6"/>
@@ -42759,7 +42901,7 @@
       <c r="G975" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H975" s="24" t="s">
+      <c r="H975" s="23" t="s">
         <v>3491</v>
       </c>
       <c r="I975" s="6" t="s">
@@ -43359,7 +43501,7 @@
       <c r="G997" s="12">
         <v>4.5</v>
       </c>
-      <c r="H997" s="25" t="s">
+      <c r="H997" s="24" t="s">
         <v>3593</v>
       </c>
       <c r="I997" s="6"/>
@@ -43386,7 +43528,7 @@
       <c r="G998" s="12">
         <v>4.3</v>
       </c>
-      <c r="H998" s="25" t="s">
+      <c r="H998" s="24" t="s">
         <v>3594</v>
       </c>
       <c r="I998" s="6"/>
@@ -43413,7 +43555,7 @@
       <c r="G999" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H999" s="25" t="s">
+      <c r="H999" s="24" t="s">
         <v>3597</v>
       </c>
       <c r="I999" s="6"/>
@@ -43440,7 +43582,7 @@
       <c r="G1000" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1000" s="25" t="s">
+      <c r="H1000" s="24" t="s">
         <v>3598</v>
       </c>
       <c r="I1000" s="6"/>
@@ -43467,7 +43609,7 @@
       <c r="G1001" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1001" s="25" t="s">
+      <c r="H1001" s="24" t="s">
         <v>3599</v>
       </c>
       <c r="I1001" s="6"/>
@@ -43494,7 +43636,7 @@
       <c r="G1002" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1002" s="25" t="s">
+      <c r="H1002" s="24" t="s">
         <v>3595</v>
       </c>
       <c r="I1002" s="6"/>
@@ -43521,7 +43663,7 @@
       <c r="G1003" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H1003" s="25" t="s">
+      <c r="H1003" s="24" t="s">
         <v>3600</v>
       </c>
       <c r="I1003" s="6"/>
@@ -43548,7 +43690,7 @@
       <c r="G1004" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1004" s="25" t="s">
+      <c r="H1004" s="24" t="s">
         <v>3601</v>
       </c>
       <c r="I1004" s="6"/>
@@ -43575,7 +43717,7 @@
       <c r="G1005" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1005" s="25" t="s">
+      <c r="H1005" s="24" t="s">
         <v>3596</v>
       </c>
       <c r="I1005" s="6"/>
@@ -43602,7 +43744,7 @@
       <c r="G1006" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1006" s="25" t="s">
+      <c r="H1006" s="24" t="s">
         <v>3602</v>
       </c>
       <c r="I1006" s="6"/>
@@ -43629,8 +43771,8 @@
       <c r="G1007" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1007" s="26" t="s">
-        <v>3633</v>
+      <c r="H1007" s="25" t="s">
+        <v>3632</v>
       </c>
       <c r="I1007" s="6"/>
     </row>
@@ -43656,8 +43798,8 @@
       <c r="G1008" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1008" s="26" t="s">
-        <v>3634</v>
+      <c r="H1008" s="25" t="s">
+        <v>3633</v>
       </c>
       <c r="I1008" s="6"/>
     </row>
@@ -43683,8 +43825,8 @@
       <c r="G1009" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1009" s="26" t="s">
-        <v>3635</v>
+      <c r="H1009" s="25" t="s">
+        <v>3634</v>
       </c>
       <c r="I1009" s="6"/>
     </row>
@@ -43710,7 +43852,7 @@
       <c r="G1010" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1010" s="26" t="s">
+      <c r="H1010" s="25" t="s">
         <v>3630</v>
       </c>
       <c r="I1010" s="6"/>
@@ -43737,7 +43879,7 @@
       <c r="G1011" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1011" s="26" t="s">
+      <c r="H1011" s="25" t="s">
         <v>3631</v>
       </c>
       <c r="I1011" s="6"/>
@@ -43764,8 +43906,8 @@
       <c r="G1012" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1012" s="26" t="s">
-        <v>3632</v>
+      <c r="H1012" s="24" t="s">
+        <v>3638</v>
       </c>
       <c r="I1012" s="6"/>
     </row>
@@ -43791,8 +43933,8 @@
       <c r="G1013" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H1013" s="26" t="s">
-        <v>3636</v>
+      <c r="H1013" s="25" t="s">
+        <v>3639</v>
       </c>
       <c r="I1013" s="6"/>
     </row>
@@ -43818,8 +43960,8 @@
       <c r="G1014" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1014" s="26" t="s">
-        <v>3637</v>
+      <c r="H1014" s="25" t="s">
+        <v>3635</v>
       </c>
       <c r="I1014" s="6"/>
     </row>
@@ -43845,8 +43987,8 @@
       <c r="G1015" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1015" s="26" t="s">
-        <v>3638</v>
+      <c r="H1015" s="25" t="s">
+        <v>3636</v>
       </c>
       <c r="I1015" s="6"/>
     </row>
@@ -43872,8 +44014,8 @@
       <c r="G1016" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1016" s="26" t="s">
-        <v>3639</v>
+      <c r="H1016" s="25" t="s">
+        <v>3640</v>
       </c>
       <c r="I1016" s="6"/>
     </row>
@@ -43899,10 +44041,282 @@
       <c r="G1017" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1017" s="26" t="s">
-        <v>3640</v>
+      <c r="H1017" s="25" t="s">
+        <v>3637</v>
       </c>
       <c r="I1017" s="6"/>
+    </row>
+    <row r="1018" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1018" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1018" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1018" s="22" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D1018" s="7" t="s">
+        <v>3666</v>
+      </c>
+      <c r="E1018" s="20">
+        <v>4.16</v>
+      </c>
+      <c r="F1018" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1018" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1018" s="9" t="s">
+        <v>3659</v>
+      </c>
+      <c r="I1018" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1019" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1019" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1019" s="22" t="s">
+        <v>3646</v>
+      </c>
+      <c r="D1019" s="7" t="s">
+        <v>3667</v>
+      </c>
+      <c r="E1019" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F1019" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1019" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1019" s="9" t="s">
+        <v>3658</v>
+      </c>
+      <c r="I1019" s="6"/>
+    </row>
+    <row r="1020" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1020" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1020" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1020" s="22" t="s">
+        <v>3647</v>
+      </c>
+      <c r="D1020" s="7" t="s">
+        <v>3668</v>
+      </c>
+      <c r="E1020" s="20">
+        <v>4.16</v>
+      </c>
+      <c r="F1020" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1020" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1020" s="9" t="s">
+        <v>3660</v>
+      </c>
+      <c r="I1020" s="6"/>
+    </row>
+    <row r="1021" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1021" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1021" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1021" s="22" t="s">
+        <v>3648</v>
+      </c>
+      <c r="D1021" s="7" t="s">
+        <v>3669</v>
+      </c>
+      <c r="E1021" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F1021" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1021" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1021" s="9" t="s">
+        <v>3655</v>
+      </c>
+      <c r="I1021" s="6"/>
+    </row>
+    <row r="1022" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1022" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1022" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1022" s="22" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D1022" s="7" t="s">
+        <v>3670</v>
+      </c>
+      <c r="E1022" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F1022" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1022" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1022" s="9" t="s">
+        <v>3656</v>
+      </c>
+      <c r="I1022" s="6"/>
+    </row>
+    <row r="1023" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1023" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1023" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1023" s="22" t="s">
+        <v>3654</v>
+      </c>
+      <c r="D1023" s="7" t="s">
+        <v>3671</v>
+      </c>
+      <c r="E1023" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F1023" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1023" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1023" s="9" t="s">
+        <v>3657</v>
+      </c>
+      <c r="I1023" s="6"/>
+    </row>
+    <row r="1024" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1024" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1024" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1024" s="22" t="s">
+        <v>3653</v>
+      </c>
+      <c r="D1024" s="7" t="s">
+        <v>3672</v>
+      </c>
+      <c r="E1024" s="20">
+        <v>3.77</v>
+      </c>
+      <c r="F1024" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1024" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1024" s="9" t="s">
+        <v>3661</v>
+      </c>
+      <c r="I1024" s="6"/>
+    </row>
+    <row r="1025" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1025" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1025" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1025" s="22" t="s">
+        <v>3652</v>
+      </c>
+      <c r="D1025" s="7" t="s">
+        <v>3673</v>
+      </c>
+      <c r="E1025" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F1025" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1025" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1025" s="9" t="s">
+        <v>3662</v>
+      </c>
+      <c r="I1025" s="6"/>
+    </row>
+    <row r="1026" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1026" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1026" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1026" s="22" t="s">
+        <v>3651</v>
+      </c>
+      <c r="D1026" s="7" t="s">
+        <v>3674</v>
+      </c>
+      <c r="E1026" s="20">
+        <v>3.47</v>
+      </c>
+      <c r="F1026" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1026" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1026" s="9" t="s">
+        <v>3663</v>
+      </c>
+      <c r="I1026" s="6"/>
+    </row>
+    <row r="1027" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1027" s="6">
+        <v>8864393</v>
+      </c>
+      <c r="B1027" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1027" s="22" t="s">
+        <v>3650</v>
+      </c>
+      <c r="D1027" s="7" t="s">
+        <v>3675</v>
+      </c>
+      <c r="E1027" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F1027" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1027" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1027" s="9" t="s">
+        <v>3664</v>
+      </c>
+      <c r="I1027" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55647B5C-C999-4578-A4E3-25F1E57F74E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C089E655-E3F0-4431-A836-3BEE9F748797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="3678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="3711">
   <si>
     <t>No</t>
   </si>
@@ -12169,6 +12169,135 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Triumph And Agony είναι το τέταρτο και τελευταίο studio album των Warlock, κυκλοφόρησε στις 29 Σεπτεμβρίου 1987 και ηχογραφήθηκε στις ΗΠΑ με παραγωγό τον Joey Balin. Είναι ο δίσκος που καθόρισε την κληρονομιά του σχήματος: traditional heavy metal με melodic hard-rock hooks, power-ballad δραματικότητα και καθαρό late-'80s metal sheen, χωρίς να γίνεται πλήρως hair metal. Συνοδεύεται από εσωτερικό φάκελο (OIS) με στίχους. Τυπική DMM κοπή με εξαιρετική διαύγεια στα πρίμα και τα μεσαία.</t>
+  </si>
+  <si>
+    <t>Denim And Leather</t>
+  </si>
+  <si>
+    <t>Saxon</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/385433-Saxon-Denim-And-Leather</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/yys6_5UmEs-djwpsvklDQtcqtHDKFK9ChRy0MOif8DA/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM4NTQz/My0xNDkxOTIxMjQ3/LTM4MzkuanBlZw.jpeg</t>
+  </si>
+  <si>
+    <t>Carrere – 67.811 (France, 1981, LP, Album). Pressed by and printed at SNA, with lacquer cut at Translab (indicated by the joined "TL" symbol).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Denim And Leather είναι το τέταρτο studio album των Saxon, κυκλοφόρησε το 1981 και αποτελεί έναν από τους απόλυτους πυλώνες του New Wave of British Heavy Metal (NWOBHM). Η ηχογράφηση πραγματοποιήθηκε στα Aquarius Studios στη Γενεύη και στα Polar Studios στη Στοκχόλμη, με μικτή παραγωγή από τους Nigel Thomas και Saxon. Ο δίσκος συνδυάζει την ωμή ενέργεια της εργατικής τάξης με anthemic hard rock ρυθμούς, καθορίζοντας την αισθητική ολόκληρης της εποχής. Made in France. Τα runout markings είναι etched, εκτός από το λογότυπο της SNA που είναι stamped.</t>
+  </si>
+  <si>
+    <t>Fire In The Sky</t>
+  </si>
+  <si>
+    <t>Midnight Rider</t>
+  </si>
+  <si>
+    <t>Princess Of The Night</t>
+  </si>
+  <si>
+    <t>Never Surrender</t>
+  </si>
+  <si>
+    <t>And The Bands Played On</t>
+  </si>
+  <si>
+    <t>Rough And Ready</t>
+  </si>
+  <si>
+    <t>Play It Loud</t>
+  </si>
+  <si>
+    <t>Out Of Control</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [British Heavy Metal, Traditional Metal, Rock ’n’ Roll Metal, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [Train Metal, Twin-Guitar Metal, Anthemic Opener]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Defiant Metal Anthem, Melodic NWOBHM, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Traditional Metal, Riff Rock, Road Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Mid-tempo Heavy Rock, Bluesy Metal, Street Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Rock ’n’ Roll Metal, Party Metal, Crowd Chant]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [Festival Anthem, Melodic Metal, Live-Community Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Metal, Road Metal, Dramatic Twin-Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [Fast Metal, Apocalyptic Metal, Riff-Driven Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [Metal Community Anthem, Traditional Metal, Arena Sing-Along]</t>
+  </si>
+  <si>
+    <t>Γρήγορο και ευθύ traditional metal, με τίτλο που δηλώνει απώλεια ελέγχου αλλά και την απελευθέρωση που προσφέρει η ένταση του rock ’n’ roll. Η μπάντα δεν επιχειρεί να δημιουργήσει το επόμενο μεγάλο hit· υπηρετεί την αδρεναλίνη. Τα drums του Pete Gill και το μπάσο του Steve Dawson κρατούν το track σε διαρκή forward motion, ενώ οι κιθάρες δίνουν μικρά μελωδικά περάσματα χωρίς να μειώνουν την ταχύτητα. Είναι πολύ καλό deep cut, όχι όμως στο επίπεδο των κλασικών singles. Η θέση του μετά το “Never Surrender” είναι σωστή, γιατί διατηρεί την A πλευρά γρήγορη και νεανική πριν τη μετάβαση στα πιο mid-tempo cuts.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η μεγάλη festival σύνθεση του δίσκου και, μαζί με το title track, η πιο καθαρή ιστορική καταγραφή της NWOBHM κοινότητας. Το τραγούδι γράφτηκε για το πρώτο </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Monsters of Rock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> festival στο Donington το 1980, όπου οι Saxon έπαιξαν δίπλα σε Rainbow, Judas Priest, Scorpions, April Wine, Riot και Touch. Ο τίτλος δεν αφορά μόνο τις μπάντες· αφορά το κοινό, τον καιρό, τη λάσπη, την ένταση και τη συλλογική εμπειρία μιας σκηνής που καταλάβαινε ότι γεννιόταν κάτι μεγαλύτερο. Η μουσική είναι σύντομη αλλά γεμάτη μελωδία, με chorus που λειτουργεί σαν μνήμη μιας συγκεκριμένης συναυλιακής στιγμής. Είναι μία από τις πιο αγαπητές Saxon συνθέσεις και θεωρείται από πολλούς η ουσιαστική καρδιά του album.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το τέλειο Saxon opener και ένα από τα πιο εμβληματικά NWOBHM τραγούδια. Η “πριγκίπισσα της νύχτας” δεν είναι άνθρωπος αλλά η ατμομηχανή Princess Elizabeth, που μεταφέρει ταχυδρομείο μέσα από χιόνι και σκοτάδι. Αυτό το ασυνήθιστο θέμα , μια ατμομηχανή ως ηρωική φιγούρα , είναι τυπικό Saxon, μηχανές, κίνηση και βρετανική εργατική φαντασία μετατρέπονται σε metal μύθο. Το riff είναι γρήγορο και κοφτό, οι twin guitars των Graham Oliver και Paul Quinn δημιουργούν μελωδική ένταση και ο Biff Byford τραγουδά με την καθαρή, επιτακτική φωνή που κάνει το refrain αμέσως τραγουδήσιμο. Είναι τόσο ισχυρό ως σύνθεση ώστε το AllMusic το χαρακτηρίζει “infectiously anthemic opening statement”.</t>
+  </si>
+  <si>
+    <t>Η φυσική συνέχεια του opener, ένα τραγούδι άρνησης, επιμονής και σκληρής στάσης απέναντι σε ό,τι προσπαθεί να σε λυγίσει. Ο τίτλος λειτουργεί σαν motto για τη metal κοινότητα , δεν παραδίνεσαι, δεν συμβιβάζεσαι και συνεχίζεις να προχωράς. Η μουσική έχει λιγότερη ταχύτητα από το “Princess Of The Night”, αλλά περισσότερο arena-rock chorus και καθαρή sing-along λογική. Η παραγωγή δίνει χώρο στις κιθάρες και στον Biff να οδηγούν το track, χωρίς να το φορτώνει με υπερβολές. Είναι πιο απλό από τα μεγάλα επικά κομμάτια της B πλευράς, όμως η απλότητά του είναι αποτελεσματική, αποτελεί ένα από τα χαρακτηριστικά early-’80s Saxon anthems και βασικό single του album.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Πιο βαριά, mid-tempo και πιο γήινη στιγμή, με τίτλο που περιγράφει τόσο την προσέγγιση της μπάντας όσο και το character του τραγουδιού. Εδώ οι Saxon πατούν περισσότερο σε bluesy hard-rock groove και λιγότερο στο γρήγορο NWOBHM gallop. Η σύνθεση έχει rough bar-band αίσθηση, κιθάρες με μεγαλύτερη έμφαση στο riff, ρυθμός που αφήνει χώρο για headbanging και φωνητικά που διατηρούν το street-level ύφος. Δεν είναι αδύναμο, αλλά η συγκρατημένη ανάπτυξή του το κάνει λιγότερο διακριτό από τα κορυφαία tracks. Είναι χρήσιμο όμως ως αλλαγή ταχύτητας, ώστε η πλευρά να μη γίνει απλώς ακολουθία fast anthems.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεση rock ’n’ roll δήλωση του δίσκου. Το μήνυμα είναι στοιχειώδες , παίξε το δυνατά , και δεν χρειάζεται περισσότερο βάθος για να λειτουργήσει. Οι Saxon το αντιμετωπίζουν ως crowd chant, απλό riff, δυνατή ρυθμική βάση και chorus που καλεί το κοινό να συμμετάσχει. Η αξία του έρχεται από τη λειτουργία του ως live-oriented track και από το πώς συμπυκνώνει την κοινή εμπειρία του heavy metal, ένταση, ένταση ήχου και συλλογική εκτόνωση. Ωστόσο, σε δίσκο με “Princess Of The Night”, “And The Bands Played On” και title track, ακούγεται λιγότερο αναγκαίο και πιο κοντά σε filler. Είναι το ένα κομμάτι που ακόμα και πολύ θετικές κριτικές συχνά θεωρούν πιο αδύναμο.</t>
+  </si>
+  <si>
+    <t>Το πιο εκτεταμένο και δραματικό heavy track της B πλευράς. Ο “midnight rider” είναι φιγούρα δρόμου, νύχτας και φυγής , ένα μοτίβο που οι Saxon μετατρέπουν σε epic metal αφήγηση. Η σύνθεση αφήνει περισσότερο χώρο σε κιθαριστικές μελωδίες, μεταβάσεις και κλιμάκωση απ’ ό,τι τα σύντομα anthems της A πλευράς. Ο Biff Byford κρατά την ένταση με storytelling φωνητική γραμμή, ενώ οι twin guitars δημιουργούν αίσθηση ταξιδιού και κινδύνου. Το AllMusic το χαρακτηρίζει “spectacular”, και σωστά, δεν είναι τόσο άμεσο όσο το “Princess”, αλλά ανταμείβει περισσότερο την προσεκτική ακρόαση και δείχνει ότι οι Saxon μπορούσαν να ξεφύγουν από το τρίλεπτο formula.</t>
+  </si>
+  <si>
+    <t>Γρήγορο και πιο σκοτεινό, με τον τίτλο να δημιουργεί εικόνες καταστροφής, πολέμου ή ανεξέλεγκτης δύναμης. Το riffing επιστρέφει στο πιο κοφτό NWOBHM ύφος, αλλά η μελωδία παραμένει σημαντική, δεν είναι speed metal με τη μεταγενέστερη, ακραία έννοια, αλλά κλασικό British metal που κινείται γρήγορα χωρίς να χάνει το hook. Η θέση του μετά το “Midnight Rider” λειτουργεί ιδανικά ως επιτάχυνση πριν από το μεγάλο κλείσιμο. Είναι ένα από τα tracks που το AllMusic ξεχωρίζει ως “spectacular”, παρότι λιγότερο γνωστό από τα singles.</t>
+  </si>
+  <si>
+    <t>Το ιδανικό finale και ένα από τα μεγάλα τραγούδια-ταυτότητα του heavy metal. Ο τίτλος αναφέρεται στα ρούχα και στα σύμβολα της κουλτούρας , denim jackets, δερμάτινα, patches, συναυλίες, παρέες , όμως η ουσία είναι η αφοσίωση σε ένα κοινό τρόπο ζωής. Το τραγούδι δεν αντιμετωπίζει το metal ως απλή μουσική προτίμηση, αλλά ως κοινότητα που επιβιώνει όταν οι μόδες αλλάζουν. Η σύνθεση χτίζει σταδιακά, με κιθάρες που ανοίγουν τον ήχο και chorus σχεδιασμένο για μεγάλα πλήθη. Δεν είναι τυχαίο ότι εξακολουθεί να αποτελεί live staple, ενώνει γενιές ακροατών επειδή μιλά για την εμπειρία του να ανήκεις σε μια σκηνή. Το AllMusic το αποκαλεί “unqualified classic”, ενώ το Voices From The Darkside το περιγράφει ως anthem που ανεβάζει το αίμα κάθε metalhead.</t>
   </si>
 </sst>
 </file>
@@ -12718,7 +12847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16186,6 +16315,38 @@
       </c>
       <c r="J108" s="11" t="s">
         <v>3643</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>3678</v>
+      </c>
+      <c r="D109" s="6">
+        <v>1981</v>
+      </c>
+      <c r="E109" s="10">
+        <v>3.67</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>3692</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>3683</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>3682</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>3680</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>3681</v>
       </c>
     </row>
   </sheetData>
@@ -16401,6 +16562,8 @@
     <hyperlink ref="I107" r:id="rId209" xr:uid="{EF8A629E-3733-475B-9310-6FA2999BA7DF}"/>
     <hyperlink ref="J108" r:id="rId210" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
     <hyperlink ref="I108" r:id="rId211" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
+    <hyperlink ref="I109" r:id="rId212" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
+    <hyperlink ref="J109" r:id="rId213" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16408,7 +16571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1027"/>
+  <dimension ref="A1:I1036"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
@@ -44318,6 +44481,253 @@
       </c>
       <c r="I1027" s="6"/>
     </row>
+    <row r="1028" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1028" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1028" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1028" s="22" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D1028" s="7" t="s">
+        <v>3693</v>
+      </c>
+      <c r="E1028" s="20">
+        <v>4.26</v>
+      </c>
+      <c r="F1028" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1028" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1028" s="23" t="s">
+        <v>3704</v>
+      </c>
+      <c r="I1028" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1029" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1029" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1029" s="22" t="s">
+        <v>3687</v>
+      </c>
+      <c r="D1029" s="7" t="s">
+        <v>3694</v>
+      </c>
+      <c r="E1029" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F1029" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1029" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1029" s="9" t="s">
+        <v>3705</v>
+      </c>
+      <c r="I1029" s="6"/>
+    </row>
+    <row r="1030" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1030" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1030" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1030" s="22" t="s">
+        <v>3691</v>
+      </c>
+      <c r="D1030" s="7" t="s">
+        <v>3695</v>
+      </c>
+      <c r="E1030" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F1030" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1030" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1030" s="9" t="s">
+        <v>3702</v>
+      </c>
+      <c r="I1030" s="6"/>
+    </row>
+    <row r="1031" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1031" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1031" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1031" s="22" t="s">
+        <v>3689</v>
+      </c>
+      <c r="D1031" s="7" t="s">
+        <v>3696</v>
+      </c>
+      <c r="E1031" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F1031" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1031" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1031" s="9" t="s">
+        <v>3706</v>
+      </c>
+      <c r="I1031" s="6"/>
+    </row>
+    <row r="1032" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1032" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1032" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1032" s="22" t="s">
+        <v>3690</v>
+      </c>
+      <c r="D1032" s="7" t="s">
+        <v>3697</v>
+      </c>
+      <c r="E1032" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F1032" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1032" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1032" s="9" t="s">
+        <v>3707</v>
+      </c>
+      <c r="I1032" s="6"/>
+    </row>
+    <row r="1033" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1033" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1033" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1033" s="22" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D1033" s="7" t="s">
+        <v>3698</v>
+      </c>
+      <c r="E1033" s="20">
+        <v>3.94</v>
+      </c>
+      <c r="F1033" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1033" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1033" s="23" t="s">
+        <v>3703</v>
+      </c>
+      <c r="I1033" s="6"/>
+    </row>
+    <row r="1034" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1034" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1034" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1034" s="22" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D1034" s="7" t="s">
+        <v>3699</v>
+      </c>
+      <c r="E1034" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F1034" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1034" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1034" s="9" t="s">
+        <v>3708</v>
+      </c>
+      <c r="I1034" s="6"/>
+    </row>
+    <row r="1035" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1035" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1035" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1035" s="22" t="s">
+        <v>3684</v>
+      </c>
+      <c r="D1035" s="7" t="s">
+        <v>3700</v>
+      </c>
+      <c r="E1035" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F1035" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1035" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1035" s="9" t="s">
+        <v>3709</v>
+      </c>
+      <c r="I1035" s="6"/>
+    </row>
+    <row r="1036" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1036" s="6">
+        <v>385433</v>
+      </c>
+      <c r="B1036" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1036" s="22" t="s">
+        <v>3678</v>
+      </c>
+      <c r="D1036" s="7" t="s">
+        <v>3701</v>
+      </c>
+      <c r="E1036" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1036" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1036" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1036" s="9" t="s">
+        <v>3710</v>
+      </c>
+      <c r="I1036" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C089E655-E3F0-4431-A836-3BEE9F748797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B674A17-363C-4710-81CE-CA2DFCF0CBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="3711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="3740">
   <si>
     <t>No</t>
   </si>
@@ -12298,6 +12298,93 @@
   </si>
   <si>
     <t>Το ιδανικό finale και ένα από τα μεγάλα τραγούδια-ταυτότητα του heavy metal. Ο τίτλος αναφέρεται στα ρούχα και στα σύμβολα της κουλτούρας , denim jackets, δερμάτινα, patches, συναυλίες, παρέες , όμως η ουσία είναι η αφοσίωση σε ένα κοινό τρόπο ζωής. Το τραγούδι δεν αντιμετωπίζει το metal ως απλή μουσική προτίμηση, αλλά ως κοινότητα που επιβιώνει όταν οι μόδες αλλάζουν. Η σύνθεση χτίζει σταδιακά, με κιθάρες που ανοίγουν τον ήχο και chorus σχεδιασμένο για μεγάλα πλήθη. Δεν είναι τυχαίο ότι εξακολουθεί να αποτελεί live staple, ενώνει γενιές ακροατών επειδή μιλά για την εμπειρία του να ανήκεις σε μια σκηνή. Το AllMusic το αποκαλεί “unqualified classic”, ενώ το Voices From The Darkside το περιγράφει ως anthem που ανεβάζει το αίμα κάθε metalhead.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/6431834-Saxon-Saxon</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/b1GOv6NGewJ2ZrD5ofYLje33X_gmZJ6gcq1bziGKH44/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTY0MzE4/MzQtMTcxMDU0MTk3/OC0yMDk2LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Parlophone – 062-2608811 (Greece, 1986, LP, Album). Pressed at Columbia, Athens (EMI Greece / EMIAL S.A.).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ντεμπούτο album των Saxon κυκλοφόρησε αρχικά το 1979 και ηχογραφήθηκε και μιξαρίστηκε στα Livingston Studios του Λονδίνου με παραγωγό τον John V (John Verity). Αποτελεί έναν από τους θεμελιώδεις λίθους του New Wave of British Heavy Metal (NWOBHM), συνδυάζοντας τα blues-rock θεμέλια των αρχών του '70 με την επιθετικότητα και την ορμή του ανερχόμενου βρετανικού heavy metal κινήματος. Η συγκεκριμένη ελληνική έκδοση κυκλοφόρησε το 1986 από την Parlophone / EMI Greece με αριθμό μήτρας MT 12958 και pressing plant ID A/A 12958 στις ετικέτες. Made and printed in Greece.</t>
+  </si>
+  <si>
+    <t>Rainbow Theme</t>
+  </si>
+  <si>
+    <t>Frozen Rainbow</t>
+  </si>
+  <si>
+    <t>Big Teaser</t>
+  </si>
+  <si>
+    <t>Judgement Day</t>
+  </si>
+  <si>
+    <t>Militia Guard</t>
+  </si>
+  <si>
+    <t>Still Fit To Boogie</t>
+  </si>
+  <si>
+    <t>Backs To The Wall</t>
+  </si>
+  <si>
+    <t>Stallions Of The Highway</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Proto-NWOBHM, British Hard Rock, Progressive Rock elements, Pub Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Metal [Atmospheric Instrumental, Proto-Metal, Keyboard-led Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Rock [Melodic Proto-Metal, Progressive Hard Rock, Atmospheric Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Glam-tinged Hard Rock, Pub Rock, Punky Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Rock, Doom-tinged Proto-Metal, Dramatic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, NWOBHM [Biker Metal, Fast British Metal, Road Anthem]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Working-Class Metal, Street Metal, NWOBHM Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Boogie Rock, Glam Rock residue, Party Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Progressive Rock [Epic Proto-Metal, Dramatic Heavy Rock, Prog-Metal elements]</t>
+  </si>
+  <si>
+    <t>Το πρώτο ουσιαστικό τραγούδι και ένα από τα πιο ενδιαφέροντα της A πλευράς. Ο “παγωμένος ουρανός” λειτουργεί ως εικόνα απομόνωσης, στασιμότητας ή μιας ομορφιάς που είναι ψυχρή και μακρινή. Οι κιθάρες έχουν μελαγχολική, σχεδόν λυρική κίνηση, ενώ η σύνθεση διαθέτει περισσότερη progressive ανάπτυξη από τα τυπικά Saxon rockers. Η ερμηνεία του Biff Byford είναι συγκρατημένη σε σχέση με τον μεταγενέστερο, πιο πολεμικό τρόπο του, αλλά αυτό ταιριάζει στην ατμόσφαιρα. Δεν είναι το πιο αντιπροσωπευτικό NWOBHM τραγούδι, είναι όμως ένα αξιόλογο proto-metal κομμάτι που δείχνει ότι υπήρχε ήδη συνθετική φιλοδοξία.</t>
+  </si>
+  <si>
+    <t>Η πιο σκοτεινή και βαριά κορύφωση της A πλευράς. Η «Ημέρα της Κρίσης» προσφέρει φυσικά υλικό για απειλή, ενοχή και τελική λογοδοσία, και οι Saxon το χειρίζονται με πιο αργό, δραματικό riffing. Εδώ η μπάντα πλησιάζει περισσότερο το βαρύ hard rock και το proto-doom ύφος, ενώ οι κιθάρες αφήνουν χώρο για ένταση αντί για απλή ταχύτητα. Ο Biff χρησιμοποιεί πιο θεατρική φωνητική γραμμή και η σύνθεση αποκτά αίσθηση κλιμάκωσης. Δεν φτάνει τη μεταγενέστερη ακρίβεια των Saxon epics, αλλά είναι ένα από τα καλύτερα τραγούδια του δίσκου γιατί δείχνει πραγματικό βάρος και όχι απλώς υποσχέσεις.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πρώτα μεγάλα Saxon working-class anthems. Η φράση “backs to the wall” σημαίνει ότι έχεις στριμωχτεί και δεν υπάρχει εύκολη διέξοδος , άρα πρέπει να αντισταθείς. Ο Biff Byford χρησιμοποιεί το τραγούδι για να μιλήσει εναντίον εξουσίας και κοινωνικής πίεσης, ενώ η μπάντα απαντά με σφιχτό hard-metal riff και αίσθηση street-level αντίδρασης. Η σύνθεση είναι λιγότερο γρήγορη από το “Stallions…”, αλλά πιο επιβλητική στο chorus και πιο ξεκάθαρη ως δήλωση ταυτότητας. Είναι από τα τραγούδια που όχι μόνο έβαλαν τους Saxon στον χάρτη, αλλά έδειξαν πώς το heavy metal μπορούσε να μιλά τη γλώσσα των νέων εργατικών κοινοτήτων της Βρετανίας.</t>
+  </si>
+  <si>
+    <t>Σύντομη instrumental εισαγωγή, περισσότερο ατμοσφαιρική παρά επιθετική. Τα keyboards και η κιθάρα δημιουργούν μια σχεδόν prog-rock σκιά, σαν να ανήκει ο δίσκος ακόμη στον κόσμο των mid-’70s hard/progressive σχημάτων και όχι πλήρως στη νέα heavy-metal έκρηξη. Η αξία του βρίσκεται στη λειτουργία του ως προοίμιο για το “Frozen Rainbow”, δεν είναι αυτόνομο highlight, αλλά προετοιμάζει το πιο μελαγχολικό και δραματικό mood της αρχής. Δείχνει τις τότε εκκρεμότητες του ήχου των Saxon , ενδιαφέρον για ατμόσφαιρα, αλλά όχι ακόμα η άμεση, σκληρή ταυτότητα των μεταγενέστερων δίσκων</t>
+  </si>
+  <si>
+    <t>Πιο άμεσο, πιο παιχνιδιάρικο και σαφώς επηρεασμένο από glam/pub rock. Ο τίτλος είναι σκόπιμα προκλητικός και το τραγούδι χρησιμοποιεί ρυθμική απλότητα, boogie αίσθηση και attitude αντί για μεγάλη metal δραματικότητα. Μερικές πηγές το βλέπουν ως punky/metal cut, άλλες ως «brickie boogie» που βαραίνει το album. Και οι δύο αναγνώσεις έχουν βάση, έχει ενέργεια και raw charm, αλλά ακούγεται πιο παλιό από το επερχόμενο NWOBHM ύφος. Στο sequence, λειτουργεί σαν αλλαγή μετά το “Frozen Rainbow”, όμως δεν έχει την ίδια διαχρονική αξία με τα tracks της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Στη δεύτερη πλευρά εμφανίζεται επιτέλους το Saxon που θα γίνει καθοριστικό για τη NWOBHM. Τα “stallions” είναι μηχανές, δρόμος, ταχύτητα και ελευθερία , το κλασικό biker-metal μοτίβο που η μπάντα μετατρέπει σε σύντομη, εκρηκτική δήλωση. Το riff είναι γρήγορο και αποφασιστικό, τα drums του Pete Gill σπρώχνουν το κομμάτι και το chorus έχει άμεση live ποιότητα. Δεν χρειάζεται περίπλοκη δομή, δείχνει ότι οι Saxon βρήκαν τη γλώσσα τους όταν άφησαν πίσω τα πιο διστακτικά prog και glam στοιχεία. Η Metal Archives κριτική το θεωρεί το σημείο όπου δηλώνεται καθαρά ότι μια νέα εποχή του metal βρίσκεται προ των πυλών.</t>
+  </si>
+  <si>
+    <t>Η πιο καθαρή επιστροφή στην παλιά hard-rock/boogie καταγωγή της μπάντας. Ο τίτλος , «ακόμη σε φόρμα για boogie» , είναι σχεδόν αυτοσαρκαστικός, οι Saxon ήταν μεγαλύτεροι από αρκετούς NWOBHM συνομηλίκους τους και είχαν ήδη περάσει χρόνια σε clubs. Η μουσική είναι ελαφρύτερη, πιο bar-band και περισσότερο glam-tinged από τα δύο προηγούμενα tracks. Η ενέργεια είναι αυθεντική, αλλά μέσα στον δίσκο η θέση του μετά από “Stallions…” και “Backs…” αποκαλύπτει την αστάθεια ύφους του debut. Είναι διασκεδαστικό, όχι όμως ουσιώδες για τη μεταγενέστερη Saxon ταυτότητα.</t>
+  </si>
+  <si>
+    <t>Το πιο εκτεταμένο και θεατρικό κλείσιμο. Η “militia guard” παραπέμπει σε ένοπλη επιτήρηση, φόβο και εξουσία, και η σύνθεση χρησιμοποιεί αυτό το υλικό για να χτίσει πιο επικό proto-metal τραγούδι. Οι κιθάρες αναπτύσσουν μοτίβα με μεγαλύτερη υπομονή, η φωνή του Biff αποκτά πιο δραματικό χαρακτήρα και η μπάντα συνδέει το prog υπόβαθρο της A πλευράς με την καθαρότερη metal δύναμη της B. Δεν είναι τέλειο , η παραγωγή παραμένει σχετικά αδύναμη , αλλά ως finale λειτουργεί, αφήνει την υπόσχεση ότι οι Saxon μπορούν να γράψουν μεγαλύτερες, πιο φιλόδοξες heavy συνθέσεις. Πηγές το συνδέουν με Queen-like δραματικότητα και το αναφέρουν μαζί με το “Frozen Rainbow” ως prog-flavoured epic που πλαισιώνει το album.</t>
   </si>
 </sst>
 </file>
@@ -12460,7 +12547,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12524,9 +12611,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -12847,7 +12931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16347,6 +16431,38 @@
       </c>
       <c r="J109" s="11" t="s">
         <v>3681</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>3679</v>
+      </c>
+      <c r="D110" s="6">
+        <v>1979</v>
+      </c>
+      <c r="E110" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>3723</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>3714</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>3713</v>
+      </c>
+      <c r="I110" s="11" t="s">
+        <v>3711</v>
+      </c>
+      <c r="J110" s="11" t="s">
+        <v>3712</v>
       </c>
     </row>
   </sheetData>
@@ -16564,6 +16680,8 @@
     <hyperlink ref="I108" r:id="rId211" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
     <hyperlink ref="I109" r:id="rId212" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
     <hyperlink ref="J109" r:id="rId213" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
+    <hyperlink ref="I110" r:id="rId214" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
+    <hyperlink ref="J110" r:id="rId215" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16571,18 +16689,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1036"/>
+  <dimension ref="A1:I1044"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="35.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="4" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" style="4" customWidth="1"/>
     <col min="8" max="8" width="65.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -17101,7 +17217,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>37452171</v>
       </c>
@@ -19173,7 +19289,7 @@
       </c>
       <c r="I95" s="6"/>
     </row>
-    <row r="96" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>24831386</v>
       </c>
@@ -19366,7 +19482,7 @@
       </c>
       <c r="I102" s="6"/>
     </row>
-    <row r="103" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>24831386</v>
       </c>
@@ -19889,7 +20005,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>2138840</v>
       </c>
@@ -20026,7 +20142,7 @@
       </c>
       <c r="I126" s="6"/>
     </row>
-    <row r="127" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>2138840</v>
       </c>
@@ -29018,7 +29134,7 @@
       </c>
       <c r="I458" s="6"/>
     </row>
-    <row r="459" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A459" s="6">
         <v>30630553</v>
       </c>
@@ -29045,7 +29161,7 @@
       </c>
       <c r="I459" s="6"/>
     </row>
-    <row r="460" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A460" s="6">
         <v>30630553</v>
       </c>
@@ -29072,7 +29188,7 @@
       </c>
       <c r="I460" s="6"/>
     </row>
-    <row r="461" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A461" s="6">
         <v>30630553</v>
       </c>
@@ -29261,7 +29377,7 @@
       </c>
       <c r="I467" s="6"/>
     </row>
-    <row r="468" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A468" s="6">
         <v>30630553</v>
       </c>
@@ -29618,7 +29734,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="481" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A481" s="6">
         <v>13795818</v>
       </c>
@@ -29761,7 +29877,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="486" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A486" s="6">
         <v>13795818</v>
       </c>
@@ -29819,7 +29935,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="488" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A488" s="6">
         <v>13795818</v>
       </c>
@@ -29846,7 +29962,7 @@
       </c>
       <c r="I488" s="6"/>
     </row>
-    <row r="489" spans="1:9" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A489" s="6">
         <v>11007106</v>
       </c>
@@ -29873,7 +29989,7 @@
       </c>
       <c r="I489" s="6"/>
     </row>
-    <row r="490" spans="1:9" ht="53.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A490" s="6">
         <v>11007106</v>
       </c>
@@ -29927,7 +30043,7 @@
       </c>
       <c r="I491" s="6"/>
     </row>
-    <row r="492" spans="1:9" ht="408.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" ht="357" x14ac:dyDescent="0.25">
       <c r="A492" s="6">
         <v>11007106</v>
       </c>
@@ -30064,7 +30180,7 @@
       </c>
       <c r="I496" s="6"/>
     </row>
-    <row r="497" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A497" s="6">
         <v>11007106</v>
       </c>
@@ -30091,7 +30207,7 @@
       </c>
       <c r="I497" s="6"/>
     </row>
-    <row r="498" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A498" s="6">
         <v>11007106</v>
       </c>
@@ -30145,7 +30261,7 @@
       </c>
       <c r="I499" s="6"/>
     </row>
-    <row r="500" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A500" s="6">
         <v>22100377</v>
       </c>
@@ -30523,7 +30639,7 @@
       </c>
       <c r="I513" s="6"/>
     </row>
-    <row r="514" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A514" s="6">
         <v>27606564</v>
       </c>
@@ -30577,7 +30693,7 @@
       </c>
       <c r="I515" s="6"/>
     </row>
-    <row r="516" spans="1:9" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A516" s="6">
         <v>26012116</v>
       </c>
@@ -31198,7 +31314,7 @@
       </c>
       <c r="I538" s="6"/>
     </row>
-    <row r="539" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A539" s="6">
         <v>33564954</v>
       </c>
@@ -32475,7 +32591,7 @@
       </c>
       <c r="I585" s="6"/>
     </row>
-    <row r="586" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A586" s="6">
         <v>14186441</v>
       </c>
@@ -32610,7 +32726,7 @@
       </c>
       <c r="I590" s="6"/>
     </row>
-    <row r="591" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A591" s="6">
         <v>33653532</v>
       </c>
@@ -32664,7 +32780,7 @@
       </c>
       <c r="I592" s="6"/>
     </row>
-    <row r="593" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A593" s="6">
         <v>33653532</v>
       </c>
@@ -32691,7 +32807,7 @@
       </c>
       <c r="I593" s="6"/>
     </row>
-    <row r="594" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A594" s="6">
         <v>33653532</v>
       </c>
@@ -32882,7 +32998,7 @@
       </c>
       <c r="I600" s="6"/>
     </row>
-    <row r="601" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A601" s="6">
         <v>32916789</v>
       </c>
@@ -32936,7 +33052,7 @@
       </c>
       <c r="I602" s="6"/>
     </row>
-    <row r="603" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A603" s="6">
         <v>15960193</v>
       </c>
@@ -32963,7 +33079,7 @@
       </c>
       <c r="I603" s="6"/>
     </row>
-    <row r="604" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A604" s="6">
         <v>15960193</v>
       </c>
@@ -33100,7 +33216,7 @@
       </c>
       <c r="I608" s="6"/>
     </row>
-    <row r="609" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A609" s="6">
         <v>15960193</v>
       </c>
@@ -33154,14 +33270,14 @@
       </c>
       <c r="I610" s="6"/>
     </row>
-    <row r="611" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A611" s="6">
         <v>28423156</v>
       </c>
       <c r="B611" s="6">
         <v>1</v>
       </c>
-      <c r="C611" s="22" t="s">
+      <c r="C611" s="7" t="s">
         <v>2074</v>
       </c>
       <c r="D611" s="7" t="s">
@@ -33181,14 +33297,14 @@
       </c>
       <c r="I611" s="6"/>
     </row>
-    <row r="612" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A612" s="6">
         <v>28423156</v>
       </c>
       <c r="B612" s="6">
         <v>2</v>
       </c>
-      <c r="C612" s="22" t="s">
+      <c r="C612" s="7" t="s">
         <v>2075</v>
       </c>
       <c r="D612" s="7" t="s">
@@ -33215,7 +33331,7 @@
       <c r="B613" s="6">
         <v>3</v>
       </c>
-      <c r="C613" s="22" t="s">
+      <c r="C613" s="7" t="s">
         <v>2076</v>
       </c>
       <c r="D613" s="7" t="s">
@@ -33242,7 +33358,7 @@
       <c r="B614" s="6">
         <v>4</v>
       </c>
-      <c r="C614" s="22" t="s">
+      <c r="C614" s="7" t="s">
         <v>2077</v>
       </c>
       <c r="D614" s="7" t="s">
@@ -33269,7 +33385,7 @@
       <c r="B615" s="6">
         <v>5</v>
       </c>
-      <c r="C615" s="22" t="s">
+      <c r="C615" s="7" t="s">
         <v>2078</v>
       </c>
       <c r="D615" s="7" t="s">
@@ -33289,14 +33405,14 @@
       </c>
       <c r="I615" s="6"/>
     </row>
-    <row r="616" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A616" s="6">
         <v>28423156</v>
       </c>
       <c r="B616" s="6">
         <v>6</v>
       </c>
-      <c r="C616" s="22" t="s">
+      <c r="C616" s="7" t="s">
         <v>2079</v>
       </c>
       <c r="D616" s="7" t="s">
@@ -33323,7 +33439,7 @@
       <c r="B617" s="6">
         <v>7</v>
       </c>
-      <c r="C617" s="22" t="s">
+      <c r="C617" s="7" t="s">
         <v>2080</v>
       </c>
       <c r="D617" s="7" t="s">
@@ -33350,7 +33466,7 @@
       <c r="B618" s="6">
         <v>8</v>
       </c>
-      <c r="C618" s="22" t="s">
+      <c r="C618" s="7" t="s">
         <v>2081</v>
       </c>
       <c r="D618" s="7" t="s">
@@ -33377,7 +33493,7 @@
       <c r="B619" s="6">
         <v>9</v>
       </c>
-      <c r="C619" s="22" t="s">
+      <c r="C619" s="7" t="s">
         <v>2082</v>
       </c>
       <c r="D619" s="7" t="s">
@@ -33404,7 +33520,7 @@
       <c r="B620" s="6">
         <v>10</v>
       </c>
-      <c r="C620" s="22" t="s">
+      <c r="C620" s="7" t="s">
         <v>2073</v>
       </c>
       <c r="D620" s="7" t="s">
@@ -33431,7 +33547,7 @@
       <c r="B621" s="6">
         <v>11</v>
       </c>
-      <c r="C621" s="22" t="s">
+      <c r="C621" s="7" t="s">
         <v>2083</v>
       </c>
       <c r="D621" s="7" t="s">
@@ -33458,7 +33574,7 @@
       <c r="B622" s="6">
         <v>12</v>
       </c>
-      <c r="C622" s="22" t="s">
+      <c r="C622" s="7" t="s">
         <v>2084</v>
       </c>
       <c r="D622" s="7" t="s">
@@ -33478,14 +33594,14 @@
       </c>
       <c r="I622" s="6"/>
     </row>
-    <row r="623" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A623" s="6">
         <v>28423156</v>
       </c>
       <c r="B623" s="6">
         <v>13</v>
       </c>
-      <c r="C623" s="22" t="s">
+      <c r="C623" s="7" t="s">
         <v>2085</v>
       </c>
       <c r="D623" s="7" t="s">
@@ -33512,7 +33628,7 @@
       <c r="B624" s="6">
         <v>14</v>
       </c>
-      <c r="C624" s="22" t="s">
+      <c r="C624" s="7" t="s">
         <v>2086</v>
       </c>
       <c r="D624" s="7" t="s">
@@ -33539,7 +33655,7 @@
       <c r="B625" s="6">
         <v>1</v>
       </c>
-      <c r="C625" s="22" t="s">
+      <c r="C625" s="7" t="s">
         <v>2115</v>
       </c>
       <c r="D625" s="7" t="s">
@@ -33566,7 +33682,7 @@
       <c r="B626" s="6">
         <v>2</v>
       </c>
-      <c r="C626" s="22" t="s">
+      <c r="C626" s="7" t="s">
         <v>2116</v>
       </c>
       <c r="D626" s="7" t="s">
@@ -33593,7 +33709,7 @@
       <c r="B627" s="6">
         <v>3</v>
       </c>
-      <c r="C627" s="22" t="s">
+      <c r="C627" s="7" t="s">
         <v>2117</v>
       </c>
       <c r="D627" s="7" t="s">
@@ -33620,7 +33736,7 @@
       <c r="B628" s="6">
         <v>4</v>
       </c>
-      <c r="C628" s="22" t="s">
+      <c r="C628" s="7" t="s">
         <v>2118</v>
       </c>
       <c r="D628" s="7" t="s">
@@ -33647,7 +33763,7 @@
       <c r="B629" s="6">
         <v>5</v>
       </c>
-      <c r="C629" s="22" t="s">
+      <c r="C629" s="7" t="s">
         <v>2119</v>
       </c>
       <c r="D629" s="7" t="s">
@@ -33674,7 +33790,7 @@
       <c r="B630" s="6">
         <v>6</v>
       </c>
-      <c r="C630" s="22" t="s">
+      <c r="C630" s="7" t="s">
         <v>2120</v>
       </c>
       <c r="D630" s="7" t="s">
@@ -33701,7 +33817,7 @@
       <c r="B631" s="6">
         <v>7</v>
       </c>
-      <c r="C631" s="22" t="s">
+      <c r="C631" s="7" t="s">
         <v>2121</v>
       </c>
       <c r="D631" s="7" t="s">
@@ -33728,7 +33844,7 @@
       <c r="B632" s="6">
         <v>8</v>
       </c>
-      <c r="C632" s="22" t="s">
+      <c r="C632" s="7" t="s">
         <v>2122</v>
       </c>
       <c r="D632" s="7" t="s">
@@ -33755,7 +33871,7 @@
       <c r="B633" s="6">
         <v>9</v>
       </c>
-      <c r="C633" s="22" t="s">
+      <c r="C633" s="7" t="s">
         <v>2123</v>
       </c>
       <c r="D633" s="7" t="s">
@@ -33782,7 +33898,7 @@
       <c r="B634" s="6">
         <v>10</v>
       </c>
-      <c r="C634" s="22" t="s">
+      <c r="C634" s="7" t="s">
         <v>2124</v>
       </c>
       <c r="D634" s="7" t="s">
@@ -33809,7 +33925,7 @@
       <c r="B635" s="6">
         <v>1</v>
       </c>
-      <c r="C635" s="22" t="s">
+      <c r="C635" s="7" t="s">
         <v>2153</v>
       </c>
       <c r="D635" s="7" t="s">
@@ -33838,7 +33954,7 @@
       <c r="B636" s="6">
         <v>2</v>
       </c>
-      <c r="C636" s="22" t="s">
+      <c r="C636" s="7" t="s">
         <v>2154</v>
       </c>
       <c r="D636" s="7" t="s">
@@ -33860,14 +33976,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="637" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A637" s="6">
         <v>18001219</v>
       </c>
       <c r="B637" s="6">
         <v>3</v>
       </c>
-      <c r="C637" s="22" t="s">
+      <c r="C637" s="7" t="s">
         <v>2155</v>
       </c>
       <c r="D637" s="7" t="s">
@@ -33887,14 +34003,14 @@
       </c>
       <c r="I637" s="6"/>
     </row>
-    <row r="638" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A638" s="6">
         <v>18001219</v>
       </c>
       <c r="B638" s="6">
         <v>4</v>
       </c>
-      <c r="C638" s="22" t="s">
+      <c r="C638" s="7" t="s">
         <v>2156</v>
       </c>
       <c r="D638" s="7" t="s">
@@ -33921,7 +34037,7 @@
       <c r="B639" s="6">
         <v>5</v>
       </c>
-      <c r="C639" s="22" t="s">
+      <c r="C639" s="7" t="s">
         <v>2157</v>
       </c>
       <c r="D639" s="7" t="s">
@@ -33948,7 +34064,7 @@
       <c r="B640" s="6">
         <v>6</v>
       </c>
-      <c r="C640" s="22" t="s">
+      <c r="C640" s="7" t="s">
         <v>2158</v>
       </c>
       <c r="D640" s="7" t="s">
@@ -33968,14 +34084,14 @@
       </c>
       <c r="I640" s="6"/>
     </row>
-    <row r="641" spans="1:9" ht="96.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A641" s="6">
         <v>18001219</v>
       </c>
       <c r="B641" s="6">
         <v>7</v>
       </c>
-      <c r="C641" s="22" t="s">
+      <c r="C641" s="7" t="s">
         <v>2159</v>
       </c>
       <c r="D641" s="7" t="s">
@@ -34004,7 +34120,7 @@
       <c r="B642" s="6">
         <v>1</v>
       </c>
-      <c r="C642" s="22" t="s">
+      <c r="C642" s="7" t="s">
         <v>283</v>
       </c>
       <c r="D642" s="7" t="s">
@@ -34026,14 +34142,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="643" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A643" s="6">
         <v>15223559</v>
       </c>
       <c r="B643" s="6">
         <v>2</v>
       </c>
-      <c r="C643" s="22" t="s">
+      <c r="C643" s="7" t="s">
         <v>2178</v>
       </c>
       <c r="D643" s="7" t="s">
@@ -34062,7 +34178,7 @@
       <c r="B644" s="6">
         <v>3</v>
       </c>
-      <c r="C644" s="22" t="s">
+      <c r="C644" s="7" t="s">
         <v>2179</v>
       </c>
       <c r="D644" s="7" t="s">
@@ -34084,14 +34200,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A645" s="6">
         <v>15223559</v>
       </c>
       <c r="B645" s="6">
         <v>4</v>
       </c>
-      <c r="C645" s="22" t="s">
+      <c r="C645" s="7" t="s">
         <v>2180</v>
       </c>
       <c r="D645" s="7" t="s">
@@ -34120,7 +34236,7 @@
       <c r="B646" s="6">
         <v>5</v>
       </c>
-      <c r="C646" s="22" t="s">
+      <c r="C646" s="7" t="s">
         <v>2181</v>
       </c>
       <c r="D646" s="7" t="s">
@@ -34149,7 +34265,7 @@
       <c r="B647" s="6">
         <v>6</v>
       </c>
-      <c r="C647" s="22" t="s">
+      <c r="C647" s="7" t="s">
         <v>2182</v>
       </c>
       <c r="D647" s="7" t="s">
@@ -34178,7 +34294,7 @@
       <c r="B648" s="6">
         <v>7</v>
       </c>
-      <c r="C648" s="22" t="s">
+      <c r="C648" s="7" t="s">
         <v>287</v>
       </c>
       <c r="D648" s="7" t="s">
@@ -34207,7 +34323,7 @@
       <c r="B649" s="6">
         <v>8</v>
       </c>
-      <c r="C649" s="22" t="s">
+      <c r="C649" s="7" t="s">
         <v>2183</v>
       </c>
       <c r="D649" s="7" t="s">
@@ -34229,14 +34345,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A650" s="6">
         <v>15223559</v>
       </c>
       <c r="B650" s="6">
         <v>9</v>
       </c>
-      <c r="C650" s="22" t="s">
+      <c r="C650" s="7" t="s">
         <v>2184</v>
       </c>
       <c r="D650" s="7" t="s">
@@ -34258,14 +34374,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A651" s="6">
         <v>15223559</v>
       </c>
       <c r="B651" s="6">
         <v>10</v>
       </c>
-      <c r="C651" s="22" t="s">
+      <c r="C651" s="7" t="s">
         <v>2185</v>
       </c>
       <c r="D651" s="7" t="s">
@@ -34292,7 +34408,7 @@
       <c r="B652" s="6">
         <v>1</v>
       </c>
-      <c r="C652" s="22" t="s">
+      <c r="C652" s="7" t="s">
         <v>2212</v>
       </c>
       <c r="D652" s="7" t="s">
@@ -34319,7 +34435,7 @@
       <c r="B653" s="6">
         <v>2</v>
       </c>
-      <c r="C653" s="22" t="s">
+      <c r="C653" s="7" t="s">
         <v>2213</v>
       </c>
       <c r="D653" s="7" t="s">
@@ -34346,7 +34462,7 @@
       <c r="B654" s="6">
         <v>3</v>
       </c>
-      <c r="C654" s="22" t="s">
+      <c r="C654" s="7" t="s">
         <v>2214</v>
       </c>
       <c r="D654" s="7" t="s">
@@ -34373,7 +34489,7 @@
       <c r="B655" s="6">
         <v>4</v>
       </c>
-      <c r="C655" s="22" t="s">
+      <c r="C655" s="7" t="s">
         <v>1402</v>
       </c>
       <c r="D655" s="7" t="s">
@@ -34400,7 +34516,7 @@
       <c r="B656" s="6">
         <v>5</v>
       </c>
-      <c r="C656" s="22" t="s">
+      <c r="C656" s="7" t="s">
         <v>2215</v>
       </c>
       <c r="D656" s="7" t="s">
@@ -34427,7 +34543,7 @@
       <c r="B657" s="6">
         <v>6</v>
       </c>
-      <c r="C657" s="22" t="s">
+      <c r="C657" s="7" t="s">
         <v>2216</v>
       </c>
       <c r="D657" s="7" t="s">
@@ -34454,7 +34570,7 @@
       <c r="B658" s="6">
         <v>7</v>
       </c>
-      <c r="C658" s="22" t="s">
+      <c r="C658" s="7" t="s">
         <v>2217</v>
       </c>
       <c r="D658" s="7" t="s">
@@ -34481,7 +34597,7 @@
       <c r="B659" s="6">
         <v>8</v>
       </c>
-      <c r="C659" s="22" t="s">
+      <c r="C659" s="7" t="s">
         <v>2218</v>
       </c>
       <c r="D659" s="7" t="s">
@@ -34508,7 +34624,7 @@
       <c r="B660" s="6">
         <v>9</v>
       </c>
-      <c r="C660" s="22" t="s">
+      <c r="C660" s="7" t="s">
         <v>2219</v>
       </c>
       <c r="D660" s="7" t="s">
@@ -34535,7 +34651,7 @@
       <c r="B661" s="6">
         <v>10</v>
       </c>
-      <c r="C661" s="22" t="s">
+      <c r="C661" s="7" t="s">
         <v>2220</v>
       </c>
       <c r="D661" s="7" t="s">
@@ -34562,7 +34678,7 @@
       <c r="B662" s="6">
         <v>1</v>
       </c>
-      <c r="C662" s="22" t="s">
+      <c r="C662" s="7" t="s">
         <v>2238</v>
       </c>
       <c r="D662" s="7" t="s">
@@ -34582,14 +34698,14 @@
       </c>
       <c r="I662" s="6"/>
     </row>
-    <row r="663" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A663" s="6">
         <v>28699510</v>
       </c>
       <c r="B663" s="6">
         <v>2</v>
       </c>
-      <c r="C663" s="22" t="s">
+      <c r="C663" s="7" t="s">
         <v>2239</v>
       </c>
       <c r="D663" s="7" t="s">
@@ -34616,7 +34732,7 @@
       <c r="B664" s="6">
         <v>3</v>
       </c>
-      <c r="C664" s="22" t="s">
+      <c r="C664" s="7" t="s">
         <v>2240</v>
       </c>
       <c r="D664" s="7" t="s">
@@ -34636,14 +34752,14 @@
       </c>
       <c r="I664" s="6"/>
     </row>
-    <row r="665" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A665" s="6">
         <v>28699510</v>
       </c>
       <c r="B665" s="6">
         <v>4</v>
       </c>
-      <c r="C665" s="22" t="s">
+      <c r="C665" s="7" t="s">
         <v>2241</v>
       </c>
       <c r="D665" s="7" t="s">
@@ -34670,7 +34786,7 @@
       <c r="B666" s="6">
         <v>5</v>
       </c>
-      <c r="C666" s="22" t="s">
+      <c r="C666" s="7" t="s">
         <v>325</v>
       </c>
       <c r="D666" s="7" t="s">
@@ -34697,7 +34813,7 @@
       <c r="B667" s="6">
         <v>6</v>
       </c>
-      <c r="C667" s="22" t="s">
+      <c r="C667" s="7" t="s">
         <v>2242</v>
       </c>
       <c r="D667" s="7" t="s">
@@ -34724,7 +34840,7 @@
       <c r="B668" s="6">
         <v>7</v>
       </c>
-      <c r="C668" s="22" t="s">
+      <c r="C668" s="7" t="s">
         <v>2243</v>
       </c>
       <c r="D668" s="7" t="s">
@@ -34751,7 +34867,7 @@
       <c r="B669" s="6">
         <v>8</v>
       </c>
-      <c r="C669" s="22" t="s">
+      <c r="C669" s="7" t="s">
         <v>2244</v>
       </c>
       <c r="D669" s="7" t="s">
@@ -34778,7 +34894,7 @@
       <c r="B670" s="6">
         <v>9</v>
       </c>
-      <c r="C670" s="22" t="s">
+      <c r="C670" s="7" t="s">
         <v>2245</v>
       </c>
       <c r="D670" s="7" t="s">
@@ -34798,14 +34914,14 @@
       </c>
       <c r="I670" s="6"/>
     </row>
-    <row r="671" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A671" s="6">
         <v>28699510</v>
       </c>
       <c r="B671" s="6">
         <v>10</v>
       </c>
-      <c r="C671" s="22" t="s">
+      <c r="C671" s="7" t="s">
         <v>2246</v>
       </c>
       <c r="D671" s="7" t="s">
@@ -34825,14 +34941,14 @@
       </c>
       <c r="I671" s="6"/>
     </row>
-    <row r="672" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A672" s="6">
         <v>11898961</v>
       </c>
       <c r="B672" s="6">
         <v>1</v>
       </c>
-      <c r="C672" s="22" t="s">
+      <c r="C672" s="7" t="s">
         <v>2291</v>
       </c>
       <c r="D672" s="7" t="s">
@@ -34852,14 +34968,14 @@
       </c>
       <c r="I672" s="6"/>
     </row>
-    <row r="673" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A673" s="6">
         <v>11898961</v>
       </c>
       <c r="B673" s="6">
         <v>2</v>
       </c>
-      <c r="C673" s="22" t="s">
+      <c r="C673" s="7" t="s">
         <v>2292</v>
       </c>
       <c r="D673" s="7" t="s">
@@ -34886,7 +35002,7 @@
       <c r="B674" s="6">
         <v>3</v>
       </c>
-      <c r="C674" s="22" t="s">
+      <c r="C674" s="7" t="s">
         <v>2293</v>
       </c>
       <c r="D674" s="7" t="s">
@@ -34915,7 +35031,7 @@
       <c r="B675" s="6">
         <v>4</v>
       </c>
-      <c r="C675" s="22" t="s">
+      <c r="C675" s="7" t="s">
         <v>2294</v>
       </c>
       <c r="D675" s="7" t="s">
@@ -34942,7 +35058,7 @@
       <c r="B676" s="6">
         <v>5</v>
       </c>
-      <c r="C676" s="22" t="s">
+      <c r="C676" s="7" t="s">
         <v>2295</v>
       </c>
       <c r="D676" s="7" t="s">
@@ -34969,7 +35085,7 @@
       <c r="B677" s="6">
         <v>6</v>
       </c>
-      <c r="C677" s="22" t="s">
+      <c r="C677" s="7" t="s">
         <v>2296</v>
       </c>
       <c r="D677" s="7" t="s">
@@ -34996,7 +35112,7 @@
       <c r="B678" s="6">
         <v>7</v>
       </c>
-      <c r="C678" s="22" t="s">
+      <c r="C678" s="7" t="s">
         <v>2297</v>
       </c>
       <c r="D678" s="7" t="s">
@@ -35023,7 +35139,7 @@
       <c r="B679" s="6">
         <v>8</v>
       </c>
-      <c r="C679" s="22" t="s">
+      <c r="C679" s="7" t="s">
         <v>2298</v>
       </c>
       <c r="D679" s="7" t="s">
@@ -35050,7 +35166,7 @@
       <c r="B680" s="6">
         <v>1</v>
       </c>
-      <c r="C680" s="22" t="s">
+      <c r="C680" s="7" t="s">
         <v>2361</v>
       </c>
       <c r="D680" s="7" t="s">
@@ -35077,7 +35193,7 @@
       <c r="B681" s="6">
         <v>2</v>
       </c>
-      <c r="C681" s="22" t="s">
+      <c r="C681" s="7" t="s">
         <v>2362</v>
       </c>
       <c r="D681" s="7" t="s">
@@ -35104,7 +35220,7 @@
       <c r="B682" s="6">
         <v>3</v>
       </c>
-      <c r="C682" s="22" t="s">
+      <c r="C682" s="7" t="s">
         <v>2363</v>
       </c>
       <c r="D682" s="7" t="s">
@@ -35131,7 +35247,7 @@
       <c r="B683" s="6">
         <v>4</v>
       </c>
-      <c r="C683" s="22" t="s">
+      <c r="C683" s="7" t="s">
         <v>2364</v>
       </c>
       <c r="D683" s="7" t="s">
@@ -35151,14 +35267,14 @@
       </c>
       <c r="I683" s="6"/>
     </row>
-    <row r="684" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A684" s="6">
         <v>35389759</v>
       </c>
       <c r="B684" s="6">
         <v>5</v>
       </c>
-      <c r="C684" s="22" t="s">
+      <c r="C684" s="7" t="s">
         <v>2365</v>
       </c>
       <c r="D684" s="7" t="s">
@@ -35185,7 +35301,7 @@
       <c r="B685" s="6">
         <v>6</v>
       </c>
-      <c r="C685" s="22" t="s">
+      <c r="C685" s="7" t="s">
         <v>2366</v>
       </c>
       <c r="D685" s="7" t="s">
@@ -35212,7 +35328,7 @@
       <c r="B686" s="6">
         <v>7</v>
       </c>
-      <c r="C686" s="22" t="s">
+      <c r="C686" s="7" t="s">
         <v>2367</v>
       </c>
       <c r="D686" s="7" t="s">
@@ -35239,7 +35355,7 @@
       <c r="B687" s="6">
         <v>8</v>
       </c>
-      <c r="C687" s="22" t="s">
+      <c r="C687" s="7" t="s">
         <v>2368</v>
       </c>
       <c r="D687" s="7" t="s">
@@ -35266,7 +35382,7 @@
       <c r="B688" s="6">
         <v>9</v>
       </c>
-      <c r="C688" s="22" t="s">
+      <c r="C688" s="7" t="s">
         <v>2369</v>
       </c>
       <c r="D688" s="7" t="s">
@@ -35293,7 +35409,7 @@
       <c r="B689" s="6">
         <v>10</v>
       </c>
-      <c r="C689" s="22" t="s">
+      <c r="C689" s="7" t="s">
         <v>2370</v>
       </c>
       <c r="D689" s="7" t="s">
@@ -35320,7 +35436,7 @@
       <c r="B690" s="6">
         <v>1</v>
       </c>
-      <c r="C690" s="22" t="s">
+      <c r="C690" s="7" t="s">
         <v>2393</v>
       </c>
       <c r="D690" s="7" t="s">
@@ -35347,7 +35463,7 @@
       <c r="B691" s="6">
         <v>2</v>
       </c>
-      <c r="C691" s="22" t="s">
+      <c r="C691" s="7" t="s">
         <v>2398</v>
       </c>
       <c r="D691" s="7" t="s">
@@ -35374,7 +35490,7 @@
       <c r="B692" s="6">
         <v>3</v>
       </c>
-      <c r="C692" s="22" t="s">
+      <c r="C692" s="7" t="s">
         <v>2399</v>
       </c>
       <c r="D692" s="7" t="s">
@@ -35401,7 +35517,7 @@
       <c r="B693" s="6">
         <v>4</v>
       </c>
-      <c r="C693" s="22" t="s">
+      <c r="C693" s="7" t="s">
         <v>2403</v>
       </c>
       <c r="D693" s="7" t="s">
@@ -35428,7 +35544,7 @@
       <c r="B694" s="6">
         <v>5</v>
       </c>
-      <c r="C694" s="22" t="s">
+      <c r="C694" s="7" t="s">
         <v>2400</v>
       </c>
       <c r="D694" s="7" t="s">
@@ -35455,7 +35571,7 @@
       <c r="B695" s="6">
         <v>6</v>
       </c>
-      <c r="C695" s="22" t="s">
+      <c r="C695" s="7" t="s">
         <v>2401</v>
       </c>
       <c r="D695" s="7" t="s">
@@ -35482,7 +35598,7 @@
       <c r="B696" s="6">
         <v>7</v>
       </c>
-      <c r="C696" s="22" t="s">
+      <c r="C696" s="7" t="s">
         <v>2402</v>
       </c>
       <c r="D696" s="7" t="s">
@@ -35509,7 +35625,7 @@
       <c r="B697" s="6">
         <v>8</v>
       </c>
-      <c r="C697" s="22" t="s">
+      <c r="C697" s="7" t="s">
         <v>759</v>
       </c>
       <c r="D697" s="7" t="s">
@@ -35536,7 +35652,7 @@
       <c r="B698" s="6">
         <v>1</v>
       </c>
-      <c r="C698" s="22" t="s">
+      <c r="C698" s="7" t="s">
         <v>2424</v>
       </c>
       <c r="D698" s="7" t="s">
@@ -35563,7 +35679,7 @@
       <c r="B699" s="6">
         <v>2</v>
       </c>
-      <c r="C699" s="22" t="s">
+      <c r="C699" s="7" t="s">
         <v>2425</v>
       </c>
       <c r="D699" s="7" t="s">
@@ -35590,7 +35706,7 @@
       <c r="B700" s="6">
         <v>3</v>
       </c>
-      <c r="C700" s="22" t="s">
+      <c r="C700" s="7" t="s">
         <v>2426</v>
       </c>
       <c r="D700" s="7" t="s">
@@ -35617,7 +35733,7 @@
       <c r="B701" s="6">
         <v>4</v>
       </c>
-      <c r="C701" s="22" t="s">
+      <c r="C701" s="7" t="s">
         <v>2427</v>
       </c>
       <c r="D701" s="7" t="s">
@@ -35644,7 +35760,7 @@
       <c r="B702" s="6">
         <v>5</v>
       </c>
-      <c r="C702" s="22" t="s">
+      <c r="C702" s="7" t="s">
         <v>2428</v>
       </c>
       <c r="D702" s="7" t="s">
@@ -35671,7 +35787,7 @@
       <c r="B703" s="6">
         <v>6</v>
       </c>
-      <c r="C703" s="22" t="s">
+      <c r="C703" s="7" t="s">
         <v>2429</v>
       </c>
       <c r="D703" s="7" t="s">
@@ -35698,7 +35814,7 @@
       <c r="B704" s="6">
         <v>7</v>
       </c>
-      <c r="C704" s="22" t="s">
+      <c r="C704" s="7" t="s">
         <v>2430</v>
       </c>
       <c r="D704" s="7" t="s">
@@ -35725,7 +35841,7 @@
       <c r="B705" s="6">
         <v>8</v>
       </c>
-      <c r="C705" s="22" t="s">
+      <c r="C705" s="7" t="s">
         <v>2431</v>
       </c>
       <c r="D705" s="7" t="s">
@@ -35752,7 +35868,7 @@
       <c r="B706" s="6">
         <v>9</v>
       </c>
-      <c r="C706" s="22" t="s">
+      <c r="C706" s="7" t="s">
         <v>2432</v>
       </c>
       <c r="D706" s="7" t="s">
@@ -35779,7 +35895,7 @@
       <c r="B707" s="6">
         <v>10</v>
       </c>
-      <c r="C707" s="22" t="s">
+      <c r="C707" s="7" t="s">
         <v>2433</v>
       </c>
       <c r="D707" s="7" t="s">
@@ -35806,7 +35922,7 @@
       <c r="B708" s="6">
         <v>1</v>
       </c>
-      <c r="C708" s="22" t="s">
+      <c r="C708" s="7" t="s">
         <v>2457</v>
       </c>
       <c r="D708" s="7" t="s">
@@ -35833,7 +35949,7 @@
       <c r="B709" s="6">
         <v>2</v>
       </c>
-      <c r="C709" s="22" t="s">
+      <c r="C709" s="7" t="s">
         <v>2458</v>
       </c>
       <c r="D709" s="7" t="s">
@@ -35860,7 +35976,7 @@
       <c r="B710" s="6">
         <v>3</v>
       </c>
-      <c r="C710" s="22" t="s">
+      <c r="C710" s="7" t="s">
         <v>2459</v>
       </c>
       <c r="D710" s="7" t="s">
@@ -35887,7 +36003,7 @@
       <c r="B711" s="6">
         <v>4</v>
       </c>
-      <c r="C711" s="22" t="s">
+      <c r="C711" s="7" t="s">
         <v>2460</v>
       </c>
       <c r="D711" s="7" t="s">
@@ -35914,7 +36030,7 @@
       <c r="B712" s="6">
         <v>5</v>
       </c>
-      <c r="C712" s="22" t="s">
+      <c r="C712" s="7" t="s">
         <v>2461</v>
       </c>
       <c r="D712" s="7" t="s">
@@ -35941,7 +36057,7 @@
       <c r="B713" s="6">
         <v>6</v>
       </c>
-      <c r="C713" s="22" t="s">
+      <c r="C713" s="7" t="s">
         <v>2462</v>
       </c>
       <c r="D713" s="7" t="s">
@@ -35968,7 +36084,7 @@
       <c r="B714" s="6">
         <v>7</v>
       </c>
-      <c r="C714" s="22" t="s">
+      <c r="C714" s="7" t="s">
         <v>2463</v>
       </c>
       <c r="D714" s="7" t="s">
@@ -35995,7 +36111,7 @@
       <c r="B715" s="6">
         <v>8</v>
       </c>
-      <c r="C715" s="22" t="s">
+      <c r="C715" s="7" t="s">
         <v>2464</v>
       </c>
       <c r="D715" s="7" t="s">
@@ -36022,7 +36138,7 @@
       <c r="B716" s="6">
         <v>9</v>
       </c>
-      <c r="C716" s="22" t="s">
+      <c r="C716" s="7" t="s">
         <v>2465</v>
       </c>
       <c r="D716" s="7" t="s">
@@ -36049,7 +36165,7 @@
       <c r="B717" s="6">
         <v>10</v>
       </c>
-      <c r="C717" s="22" t="s">
+      <c r="C717" s="7" t="s">
         <v>2466</v>
       </c>
       <c r="D717" s="7" t="s">
@@ -36076,7 +36192,7 @@
       <c r="B718" s="6">
         <v>1</v>
       </c>
-      <c r="C718" s="22" t="s">
+      <c r="C718" s="7" t="s">
         <v>2495</v>
       </c>
       <c r="D718" s="7" t="s">
@@ -36096,14 +36212,14 @@
       </c>
       <c r="I718" s="6"/>
     </row>
-    <row r="719" spans="1:9" ht="303" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" ht="273" x14ac:dyDescent="0.25">
       <c r="A719" s="6">
         <v>2021194</v>
       </c>
       <c r="B719" s="6">
         <v>2</v>
       </c>
-      <c r="C719" s="22" t="s">
+      <c r="C719" s="7" t="s">
         <v>2496</v>
       </c>
       <c r="D719" s="7" t="s">
@@ -36132,7 +36248,7 @@
       <c r="B720" s="6">
         <v>3</v>
       </c>
-      <c r="C720" s="22" t="s">
+      <c r="C720" s="7" t="s">
         <v>2497</v>
       </c>
       <c r="D720" s="7" t="s">
@@ -36159,7 +36275,7 @@
       <c r="B721" s="6">
         <v>4</v>
       </c>
-      <c r="C721" s="22" t="s">
+      <c r="C721" s="7" t="s">
         <v>2498</v>
       </c>
       <c r="D721" s="7" t="s">
@@ -36186,7 +36302,7 @@
       <c r="B722" s="6">
         <v>5</v>
       </c>
-      <c r="C722" s="22" t="s">
+      <c r="C722" s="7" t="s">
         <v>2499</v>
       </c>
       <c r="D722" s="7" t="s">
@@ -36213,7 +36329,7 @@
       <c r="B723" s="6">
         <v>6</v>
       </c>
-      <c r="C723" s="22" t="s">
+      <c r="C723" s="7" t="s">
         <v>2500</v>
       </c>
       <c r="D723" s="7" t="s">
@@ -36240,7 +36356,7 @@
       <c r="B724" s="6">
         <v>7</v>
       </c>
-      <c r="C724" s="22" t="s">
+      <c r="C724" s="7" t="s">
         <v>2501</v>
       </c>
       <c r="D724" s="7" t="s">
@@ -36267,7 +36383,7 @@
       <c r="B725" s="6">
         <v>8</v>
       </c>
-      <c r="C725" s="22" t="s">
+      <c r="C725" s="7" t="s">
         <v>2502</v>
       </c>
       <c r="D725" s="7" t="s">
@@ -36294,7 +36410,7 @@
       <c r="B726" s="6">
         <v>9</v>
       </c>
-      <c r="C726" s="22" t="s">
+      <c r="C726" s="7" t="s">
         <v>2503</v>
       </c>
       <c r="D726" s="7" t="s">
@@ -36321,7 +36437,7 @@
       <c r="B727" s="6">
         <v>10</v>
       </c>
-      <c r="C727" s="22" t="s">
+      <c r="C727" s="7" t="s">
         <v>2504</v>
       </c>
       <c r="D727" s="7" t="s">
@@ -36348,7 +36464,7 @@
       <c r="B728" s="6">
         <v>1</v>
       </c>
-      <c r="C728" s="22" t="s">
+      <c r="C728" s="7" t="s">
         <v>2495</v>
       </c>
       <c r="D728" s="7" t="s">
@@ -36375,7 +36491,7 @@
       <c r="B729" s="6">
         <v>2</v>
       </c>
-      <c r="C729" s="22" t="s">
+      <c r="C729" s="7" t="s">
         <v>2496</v>
       </c>
       <c r="D729" s="7" t="s">
@@ -36404,7 +36520,7 @@
       <c r="B730" s="6">
         <v>3</v>
       </c>
-      <c r="C730" s="22" t="s">
+      <c r="C730" s="7" t="s">
         <v>2497</v>
       </c>
       <c r="D730" s="7" t="s">
@@ -36431,7 +36547,7 @@
       <c r="B731" s="6">
         <v>4</v>
       </c>
-      <c r="C731" s="22" t="s">
+      <c r="C731" s="7" t="s">
         <v>2498</v>
       </c>
       <c r="D731" s="7" t="s">
@@ -36458,7 +36574,7 @@
       <c r="B732" s="6">
         <v>5</v>
       </c>
-      <c r="C732" s="22" t="s">
+      <c r="C732" s="7" t="s">
         <v>2499</v>
       </c>
       <c r="D732" s="7" t="s">
@@ -36485,7 +36601,7 @@
       <c r="B733" s="6">
         <v>6</v>
       </c>
-      <c r="C733" s="22" t="s">
+      <c r="C733" s="7" t="s">
         <v>2500</v>
       </c>
       <c r="D733" s="7" t="s">
@@ -36512,7 +36628,7 @@
       <c r="B734" s="6">
         <v>7</v>
       </c>
-      <c r="C734" s="22" t="s">
+      <c r="C734" s="7" t="s">
         <v>2501</v>
       </c>
       <c r="D734" s="7" t="s">
@@ -36539,7 +36655,7 @@
       <c r="B735" s="6">
         <v>8</v>
       </c>
-      <c r="C735" s="22" t="s">
+      <c r="C735" s="7" t="s">
         <v>2502</v>
       </c>
       <c r="D735" s="7" t="s">
@@ -36566,7 +36682,7 @@
       <c r="B736" s="6">
         <v>9</v>
       </c>
-      <c r="C736" s="22" t="s">
+      <c r="C736" s="7" t="s">
         <v>2503</v>
       </c>
       <c r="D736" s="7" t="s">
@@ -36593,7 +36709,7 @@
       <c r="B737" s="6">
         <v>10</v>
       </c>
-      <c r="C737" s="22" t="s">
+      <c r="C737" s="7" t="s">
         <v>2504</v>
       </c>
       <c r="D737" s="7" t="s">
@@ -36613,14 +36729,14 @@
       </c>
       <c r="I737" s="6"/>
     </row>
-    <row r="738" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A738" s="6">
         <v>12282039</v>
       </c>
       <c r="B738" s="6">
         <v>1</v>
       </c>
-      <c r="C738" s="22" t="s">
+      <c r="C738" s="7" t="s">
         <v>2636</v>
       </c>
       <c r="D738" s="7" t="s">
@@ -36640,14 +36756,14 @@
       </c>
       <c r="I738" s="6"/>
     </row>
-    <row r="739" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A739" s="6">
         <v>12282039</v>
       </c>
       <c r="B739" s="6">
         <v>2</v>
       </c>
-      <c r="C739" s="22" t="s">
+      <c r="C739" s="7" t="s">
         <v>2637</v>
       </c>
       <c r="D739" s="7" t="s">
@@ -36674,7 +36790,7 @@
       <c r="B740" s="6">
         <v>3</v>
       </c>
-      <c r="C740" s="22" t="s">
+      <c r="C740" s="7" t="s">
         <v>2631</v>
       </c>
       <c r="D740" s="7" t="s">
@@ -36699,7 +36815,7 @@
       <c r="B741" s="6">
         <v>4</v>
       </c>
-      <c r="C741" s="22" t="s">
+      <c r="C741" s="7" t="s">
         <v>2638</v>
       </c>
       <c r="D741" s="7" t="s">
@@ -36726,7 +36842,7 @@
       <c r="B742" s="6">
         <v>5</v>
       </c>
-      <c r="C742" s="22" t="s">
+      <c r="C742" s="7" t="s">
         <v>2639</v>
       </c>
       <c r="D742" s="7" t="s">
@@ -36751,7 +36867,7 @@
       <c r="B743" s="6">
         <v>6</v>
       </c>
-      <c r="C743" s="22" t="s">
+      <c r="C743" s="7" t="s">
         <v>2640</v>
       </c>
       <c r="D743" s="7" t="s">
@@ -36780,7 +36896,7 @@
       <c r="B744" s="6">
         <v>7</v>
       </c>
-      <c r="C744" s="22" t="s">
+      <c r="C744" s="7" t="s">
         <v>2641</v>
       </c>
       <c r="D744" s="7" t="s">
@@ -36807,7 +36923,7 @@
       <c r="B745" s="6">
         <v>8</v>
       </c>
-      <c r="C745" s="22" t="s">
+      <c r="C745" s="7" t="s">
         <v>2642</v>
       </c>
       <c r="D745" s="7" t="s">
@@ -36832,7 +36948,7 @@
       <c r="B746" s="6">
         <v>9</v>
       </c>
-      <c r="C746" s="22" t="s">
+      <c r="C746" s="7" t="s">
         <v>2643</v>
       </c>
       <c r="D746" s="7" t="s">
@@ -36852,14 +36968,14 @@
       </c>
       <c r="I746" s="6"/>
     </row>
-    <row r="747" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A747" s="6">
         <v>12282039</v>
       </c>
       <c r="B747" s="6">
         <v>10</v>
       </c>
-      <c r="C747" s="22" t="s">
+      <c r="C747" s="7" t="s">
         <v>2644</v>
       </c>
       <c r="D747" s="7" t="s">
@@ -36884,7 +37000,7 @@
       <c r="B748" s="6">
         <v>1</v>
       </c>
-      <c r="C748" s="22" t="s">
+      <c r="C748" s="7" t="s">
         <v>2672</v>
       </c>
       <c r="D748" s="7" t="s">
@@ -36911,7 +37027,7 @@
       <c r="B749" s="6">
         <v>2</v>
       </c>
-      <c r="C749" s="22" t="s">
+      <c r="C749" s="7" t="s">
         <v>2673</v>
       </c>
       <c r="D749" s="7" t="s">
@@ -36938,7 +37054,7 @@
       <c r="B750" s="6">
         <v>3</v>
       </c>
-      <c r="C750" s="22" t="s">
+      <c r="C750" s="7" t="s">
         <v>2674</v>
       </c>
       <c r="D750" s="7" t="s">
@@ -36965,7 +37081,7 @@
       <c r="B751" s="6">
         <v>4</v>
       </c>
-      <c r="C751" s="22" t="s">
+      <c r="C751" s="7" t="s">
         <v>2675</v>
       </c>
       <c r="D751" s="7" t="s">
@@ -36985,14 +37101,14 @@
       </c>
       <c r="I751" s="6"/>
     </row>
-    <row r="752" spans="1:9" ht="92.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A752" s="6">
         <v>8816501</v>
       </c>
       <c r="B752" s="6">
         <v>5</v>
       </c>
-      <c r="C752" s="22" t="s">
+      <c r="C752" s="7" t="s">
         <v>2676</v>
       </c>
       <c r="D752" s="7" t="s">
@@ -37019,7 +37135,7 @@
       <c r="B753" s="6">
         <v>6</v>
       </c>
-      <c r="C753" s="22" t="s">
+      <c r="C753" s="7" t="s">
         <v>2677</v>
       </c>
       <c r="D753" s="7" t="s">
@@ -37041,14 +37157,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="754" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A754" s="6">
         <v>8816501</v>
       </c>
       <c r="B754" s="6">
         <v>7</v>
       </c>
-      <c r="C754" s="22" t="s">
+      <c r="C754" s="7" t="s">
         <v>2678</v>
       </c>
       <c r="D754" s="7" t="s">
@@ -37068,14 +37184,14 @@
       </c>
       <c r="I754" s="6"/>
     </row>
-    <row r="755" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A755" s="6">
         <v>8816501</v>
       </c>
       <c r="B755" s="6">
         <v>8</v>
       </c>
-      <c r="C755" s="22" t="s">
+      <c r="C755" s="7" t="s">
         <v>2679</v>
       </c>
       <c r="D755" s="7" t="s">
@@ -37095,14 +37211,14 @@
       </c>
       <c r="I755" s="6"/>
     </row>
-    <row r="756" spans="1:9" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A756" s="6">
         <v>8816501</v>
       </c>
       <c r="B756" s="6">
         <v>9</v>
       </c>
-      <c r="C756" s="22" t="s">
+      <c r="C756" s="7" t="s">
         <v>2680</v>
       </c>
       <c r="D756" s="7" t="s">
@@ -37122,14 +37238,14 @@
       </c>
       <c r="I756" s="6"/>
     </row>
-    <row r="757" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A757" s="6">
         <v>22296643</v>
       </c>
       <c r="B757" s="6">
         <v>1</v>
       </c>
-      <c r="C757" s="22" t="s">
+      <c r="C757" s="7" t="s">
         <v>2700</v>
       </c>
       <c r="D757" s="7" t="s">
@@ -37149,14 +37265,14 @@
       </c>
       <c r="I757" s="6"/>
     </row>
-    <row r="758" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A758" s="6">
         <v>22296643</v>
       </c>
       <c r="B758" s="6">
         <v>2</v>
       </c>
-      <c r="C758" s="22" t="s">
+      <c r="C758" s="7" t="s">
         <v>2701</v>
       </c>
       <c r="D758" s="7" t="s">
@@ -37176,14 +37292,14 @@
       </c>
       <c r="I758" s="6"/>
     </row>
-    <row r="759" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A759" s="6">
         <v>22296643</v>
       </c>
       <c r="B759" s="6">
         <v>3</v>
       </c>
-      <c r="C759" s="22" t="s">
+      <c r="C759" s="7" t="s">
         <v>2702</v>
       </c>
       <c r="D759" s="7" t="s">
@@ -37210,7 +37326,7 @@
       <c r="B760" s="6">
         <v>4</v>
       </c>
-      <c r="C760" s="22" t="s">
+      <c r="C760" s="7" t="s">
         <v>2703</v>
       </c>
       <c r="D760" s="7" t="s">
@@ -37237,7 +37353,7 @@
       <c r="B761" s="6">
         <v>5</v>
       </c>
-      <c r="C761" s="22" t="s">
+      <c r="C761" s="7" t="s">
         <v>2704</v>
       </c>
       <c r="D761" s="7" t="s">
@@ -37264,7 +37380,7 @@
       <c r="B762" s="6">
         <v>6</v>
       </c>
-      <c r="C762" s="22" t="s">
+      <c r="C762" s="7" t="s">
         <v>2705</v>
       </c>
       <c r="D762" s="7" t="s">
@@ -37291,7 +37407,7 @@
       <c r="B763" s="6">
         <v>7</v>
       </c>
-      <c r="C763" s="22" t="s">
+      <c r="C763" s="7" t="s">
         <v>2706</v>
       </c>
       <c r="D763" s="7" t="s">
@@ -37318,7 +37434,7 @@
       <c r="B764" s="6">
         <v>8</v>
       </c>
-      <c r="C764" s="22" t="s">
+      <c r="C764" s="7" t="s">
         <v>2707</v>
       </c>
       <c r="D764" s="7" t="s">
@@ -37345,7 +37461,7 @@
       <c r="B765" s="6">
         <v>9</v>
       </c>
-      <c r="C765" s="22">
+      <c r="C765" s="7">
         <v>2121313</v>
       </c>
       <c r="D765" s="7" t="s">
@@ -37372,7 +37488,7 @@
       <c r="B766" s="6">
         <v>10</v>
       </c>
-      <c r="C766" s="22" t="s">
+      <c r="C766" s="7" t="s">
         <v>2708</v>
       </c>
       <c r="D766" s="7" t="s">
@@ -37399,7 +37515,7 @@
       <c r="B767" s="6">
         <v>11</v>
       </c>
-      <c r="C767" s="22" t="s">
+      <c r="C767" s="7" t="s">
         <v>2709</v>
       </c>
       <c r="D767" s="7" t="s">
@@ -37426,7 +37542,7 @@
       <c r="B768" s="6">
         <v>12</v>
       </c>
-      <c r="C768" s="22" t="s">
+      <c r="C768" s="7" t="s">
         <v>2710</v>
       </c>
       <c r="D768" s="7" t="s">
@@ -37453,7 +37569,7 @@
       <c r="B769" s="6">
         <v>13</v>
       </c>
-      <c r="C769" s="22" t="s">
+      <c r="C769" s="7" t="s">
         <v>2711</v>
       </c>
       <c r="D769" s="7" t="s">
@@ -37473,14 +37589,14 @@
       </c>
       <c r="I769" s="6"/>
     </row>
-    <row r="770" spans="1:9" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A770" s="6">
         <v>22296643</v>
       </c>
       <c r="B770" s="6">
         <v>14</v>
       </c>
-      <c r="C770" s="22" t="s">
+      <c r="C770" s="7" t="s">
         <v>2712</v>
       </c>
       <c r="D770" s="7" t="s">
@@ -37507,7 +37623,7 @@
       <c r="B771" s="6">
         <v>15</v>
       </c>
-      <c r="C771" s="22" t="s">
+      <c r="C771" s="7" t="s">
         <v>2713</v>
       </c>
       <c r="D771" s="7" t="s">
@@ -37534,7 +37650,7 @@
       <c r="B772" s="6">
         <v>16</v>
       </c>
-      <c r="C772" s="22" t="s">
+      <c r="C772" s="7" t="s">
         <v>2714</v>
       </c>
       <c r="D772" s="7" t="s">
@@ -37561,7 +37677,7 @@
       <c r="B773" s="6">
         <v>17</v>
       </c>
-      <c r="C773" s="22" t="s">
+      <c r="C773" s="7" t="s">
         <v>2715</v>
       </c>
       <c r="D773" s="7" t="s">
@@ -37581,14 +37697,14 @@
       </c>
       <c r="I773" s="6"/>
     </row>
-    <row r="774" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A774" s="6">
         <v>29667079</v>
       </c>
       <c r="B774" s="6">
         <v>1</v>
       </c>
-      <c r="C774" s="22" t="s">
+      <c r="C774" s="7" t="s">
         <v>2760</v>
       </c>
       <c r="D774" s="7" t="s">
@@ -37610,14 +37726,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="775" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A775" s="6">
         <v>29667079</v>
       </c>
       <c r="B775" s="6">
         <v>2</v>
       </c>
-      <c r="C775" s="22" t="s">
+      <c r="C775" s="7" t="s">
         <v>2761</v>
       </c>
       <c r="D775" s="7" t="s">
@@ -37637,14 +37753,14 @@
       </c>
       <c r="I775" s="6"/>
     </row>
-    <row r="776" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A776" s="6">
         <v>29667079</v>
       </c>
       <c r="B776" s="6">
         <v>3</v>
       </c>
-      <c r="C776" s="22" t="s">
+      <c r="C776" s="7" t="s">
         <v>2762</v>
       </c>
       <c r="D776" s="7" t="s">
@@ -37671,7 +37787,7 @@
       <c r="B777" s="6">
         <v>4</v>
       </c>
-      <c r="C777" s="22" t="s">
+      <c r="C777" s="7" t="s">
         <v>2763</v>
       </c>
       <c r="D777" s="7" t="s">
@@ -37698,7 +37814,7 @@
       <c r="B778" s="6">
         <v>5</v>
       </c>
-      <c r="C778" s="22" t="s">
+      <c r="C778" s="7" t="s">
         <v>2764</v>
       </c>
       <c r="D778" s="7" t="s">
@@ -37718,14 +37834,14 @@
       </c>
       <c r="I778" s="6"/>
     </row>
-    <row r="779" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A779" s="6">
         <v>29667079</v>
       </c>
       <c r="B779" s="6">
         <v>6</v>
       </c>
-      <c r="C779" s="22" t="s">
+      <c r="C779" s="7" t="s">
         <v>2765</v>
       </c>
       <c r="D779" s="7" t="s">
@@ -37752,7 +37868,7 @@
       <c r="B780" s="6">
         <v>1</v>
       </c>
-      <c r="C780" s="22" t="s">
+      <c r="C780" s="7" t="s">
         <v>2787</v>
       </c>
       <c r="D780" s="7" t="s">
@@ -37779,7 +37895,7 @@
       <c r="B781" s="6">
         <v>2</v>
       </c>
-      <c r="C781" s="22" t="s">
+      <c r="C781" s="7" t="s">
         <v>2788</v>
       </c>
       <c r="D781" s="7" t="s">
@@ -37806,7 +37922,7 @@
       <c r="B782" s="6">
         <v>3</v>
       </c>
-      <c r="C782" s="22" t="s">
+      <c r="C782" s="7" t="s">
         <v>2789</v>
       </c>
       <c r="D782" s="7" t="s">
@@ -37833,7 +37949,7 @@
       <c r="B783" s="6">
         <v>4</v>
       </c>
-      <c r="C783" s="22" t="s">
+      <c r="C783" s="7" t="s">
         <v>2790</v>
       </c>
       <c r="D783" s="7" t="s">
@@ -37860,7 +37976,7 @@
       <c r="B784" s="6">
         <v>5</v>
       </c>
-      <c r="C784" s="22" t="s">
+      <c r="C784" s="7" t="s">
         <v>2791</v>
       </c>
       <c r="D784" s="7" t="s">
@@ -37887,7 +38003,7 @@
       <c r="B785" s="6">
         <v>6</v>
       </c>
-      <c r="C785" s="22" t="s">
+      <c r="C785" s="7" t="s">
         <v>2792</v>
       </c>
       <c r="D785" s="7" t="s">
@@ -37914,7 +38030,7 @@
       <c r="B786" s="6">
         <v>7</v>
       </c>
-      <c r="C786" s="22" t="s">
+      <c r="C786" s="7" t="s">
         <v>2793</v>
       </c>
       <c r="D786" s="7" t="s">
@@ -37941,7 +38057,7 @@
       <c r="B787" s="6">
         <v>8</v>
       </c>
-      <c r="C787" s="22" t="s">
+      <c r="C787" s="7" t="s">
         <v>2794</v>
       </c>
       <c r="D787" s="7" t="s">
@@ -37961,14 +38077,14 @@
       </c>
       <c r="I787" s="6"/>
     </row>
-    <row r="788" spans="1:9" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" ht="42" x14ac:dyDescent="0.25">
       <c r="A788" s="6">
         <v>28729798</v>
       </c>
       <c r="B788" s="6">
         <v>9</v>
       </c>
-      <c r="C788" s="22" t="s">
+      <c r="C788" s="7" t="s">
         <v>2795</v>
       </c>
       <c r="D788" s="7" t="s">
@@ -37988,14 +38104,14 @@
       </c>
       <c r="I788" s="6"/>
     </row>
-    <row r="789" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A789" s="6">
         <v>28729798</v>
       </c>
       <c r="B789" s="6">
         <v>10</v>
       </c>
-      <c r="C789" s="22" t="s">
+      <c r="C789" s="7" t="s">
         <v>2796</v>
       </c>
       <c r="D789" s="7" t="s">
@@ -38015,14 +38131,14 @@
       </c>
       <c r="I789" s="6"/>
     </row>
-    <row r="790" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A790" s="6">
         <v>28729798</v>
       </c>
       <c r="B790" s="6">
         <v>11</v>
       </c>
-      <c r="C790" s="22" t="s">
+      <c r="C790" s="7" t="s">
         <v>2797</v>
       </c>
       <c r="D790" s="7" t="s">
@@ -38042,14 +38158,14 @@
       </c>
       <c r="I790" s="6"/>
     </row>
-    <row r="791" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A791" s="6">
         <v>27663855</v>
       </c>
       <c r="B791" s="6">
         <v>1</v>
       </c>
-      <c r="C791" s="22" t="s">
+      <c r="C791" s="7" t="s">
         <v>2822</v>
       </c>
       <c r="D791" s="7" t="s">
@@ -38069,14 +38185,14 @@
       </c>
       <c r="I791" s="6"/>
     </row>
-    <row r="792" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A792" s="6">
         <v>27663855</v>
       </c>
       <c r="B792" s="6">
         <v>2</v>
       </c>
-      <c r="C792" s="22" t="s">
+      <c r="C792" s="7" t="s">
         <v>2827</v>
       </c>
       <c r="D792" s="7" t="s">
@@ -38096,14 +38212,14 @@
       </c>
       <c r="I792" s="6"/>
     </row>
-    <row r="793" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A793" s="6">
         <v>27663855</v>
       </c>
       <c r="B793" s="6">
         <v>3</v>
       </c>
-      <c r="C793" s="22" t="s">
+      <c r="C793" s="7" t="s">
         <v>2828</v>
       </c>
       <c r="D793" s="7" t="s">
@@ -38123,14 +38239,14 @@
       </c>
       <c r="I793" s="6"/>
     </row>
-    <row r="794" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A794" s="6">
         <v>27663855</v>
       </c>
       <c r="B794" s="6">
         <v>4</v>
       </c>
-      <c r="C794" s="22" t="s">
+      <c r="C794" s="7" t="s">
         <v>2829</v>
       </c>
       <c r="D794" s="7" t="s">
@@ -38150,14 +38266,14 @@
       </c>
       <c r="I794" s="6"/>
     </row>
-    <row r="795" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A795" s="6">
         <v>27663855</v>
       </c>
       <c r="B795" s="6">
         <v>5</v>
       </c>
-      <c r="C795" s="22" t="s">
+      <c r="C795" s="7" t="s">
         <v>2830</v>
       </c>
       <c r="D795" s="7" t="s">
@@ -38184,7 +38300,7 @@
       <c r="B796" s="6">
         <v>6</v>
       </c>
-      <c r="C796" s="22" t="s">
+      <c r="C796" s="7" t="s">
         <v>2831</v>
       </c>
       <c r="D796" s="7" t="s">
@@ -38204,14 +38320,14 @@
       </c>
       <c r="I796" s="6"/>
     </row>
-    <row r="797" spans="1:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A797" s="6">
         <v>27663855</v>
       </c>
       <c r="B797" s="6">
         <v>7</v>
       </c>
-      <c r="C797" s="22" t="s">
+      <c r="C797" s="7" t="s">
         <v>2832</v>
       </c>
       <c r="D797" s="7" t="s">
@@ -38238,7 +38354,7 @@
       <c r="B798" s="6">
         <v>1</v>
       </c>
-      <c r="C798" s="22" t="s">
+      <c r="C798" s="7" t="s">
         <v>2854</v>
       </c>
       <c r="D798" s="7" t="s">
@@ -38265,7 +38381,7 @@
       <c r="B799" s="6">
         <v>2</v>
       </c>
-      <c r="C799" s="22" t="s">
+      <c r="C799" s="7" t="s">
         <v>2855</v>
       </c>
       <c r="D799" s="7" t="s">
@@ -38285,14 +38401,14 @@
       </c>
       <c r="I799" s="6"/>
     </row>
-    <row r="800" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A800" s="6">
         <v>23148584</v>
       </c>
       <c r="B800" s="6">
         <v>3</v>
       </c>
-      <c r="C800" s="22" t="s">
+      <c r="C800" s="7" t="s">
         <v>2856</v>
       </c>
       <c r="D800" s="7" t="s">
@@ -38319,7 +38435,7 @@
       <c r="B801" s="6">
         <v>4</v>
       </c>
-      <c r="C801" s="22" t="s">
+      <c r="C801" s="7" t="s">
         <v>2857</v>
       </c>
       <c r="D801" s="7" t="s">
@@ -38346,7 +38462,7 @@
       <c r="B802" s="6">
         <v>5</v>
       </c>
-      <c r="C802" s="22" t="s">
+      <c r="C802" s="7" t="s">
         <v>2858</v>
       </c>
       <c r="D802" s="7" t="s">
@@ -38373,7 +38489,7 @@
       <c r="B803" s="6">
         <v>6</v>
       </c>
-      <c r="C803" s="22" t="s">
+      <c r="C803" s="7" t="s">
         <v>2859</v>
       </c>
       <c r="D803" s="7" t="s">
@@ -38400,7 +38516,7 @@
       <c r="B804" s="6">
         <v>7</v>
       </c>
-      <c r="C804" s="22" t="s">
+      <c r="C804" s="7" t="s">
         <v>2860</v>
       </c>
       <c r="D804" s="7" t="s">
@@ -38420,14 +38536,14 @@
       </c>
       <c r="I804" s="6"/>
     </row>
-    <row r="805" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A805" s="6">
         <v>23148584</v>
       </c>
       <c r="B805" s="6">
         <v>8</v>
       </c>
-      <c r="C805" s="22" t="s">
+      <c r="C805" s="7" t="s">
         <v>2861</v>
       </c>
       <c r="D805" s="7" t="s">
@@ -38447,14 +38563,14 @@
       </c>
       <c r="I805" s="6"/>
     </row>
-    <row r="806" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A806" s="6">
         <v>23148584</v>
       </c>
       <c r="B806" s="6">
         <v>9</v>
       </c>
-      <c r="C806" s="22" t="s">
+      <c r="C806" s="7" t="s">
         <v>2862</v>
       </c>
       <c r="D806" s="7" t="s">
@@ -38481,7 +38597,7 @@
       <c r="B807" s="6">
         <v>10</v>
       </c>
-      <c r="C807" s="22" t="s">
+      <c r="C807" s="7" t="s">
         <v>2863</v>
       </c>
       <c r="D807" s="7" t="s">
@@ -38508,7 +38624,7 @@
       <c r="B808" s="6">
         <v>1</v>
       </c>
-      <c r="C808" s="22" t="s">
+      <c r="C808" s="7" t="s">
         <v>2889</v>
       </c>
       <c r="D808" s="7" t="s">
@@ -38535,7 +38651,7 @@
       <c r="B809" s="6">
         <v>2</v>
       </c>
-      <c r="C809" s="22" t="s">
+      <c r="C809" s="7" t="s">
         <v>2890</v>
       </c>
       <c r="D809" s="7" t="s">
@@ -38562,7 +38678,7 @@
       <c r="B810" s="6">
         <v>3</v>
       </c>
-      <c r="C810" s="22" t="s">
+      <c r="C810" s="7" t="s">
         <v>2891</v>
       </c>
       <c r="D810" s="7" t="s">
@@ -38589,7 +38705,7 @@
       <c r="B811" s="6">
         <v>4</v>
       </c>
-      <c r="C811" s="22" t="s">
+      <c r="C811" s="7" t="s">
         <v>2892</v>
       </c>
       <c r="D811" s="7" t="s">
@@ -38616,7 +38732,7 @@
       <c r="B812" s="6">
         <v>5</v>
       </c>
-      <c r="C812" s="22" t="s">
+      <c r="C812" s="7" t="s">
         <v>2893</v>
       </c>
       <c r="D812" s="7" t="s">
@@ -38643,7 +38759,7 @@
       <c r="B813" s="6">
         <v>6</v>
       </c>
-      <c r="C813" s="22" t="s">
+      <c r="C813" s="7" t="s">
         <v>2894</v>
       </c>
       <c r="D813" s="7" t="s">
@@ -38670,7 +38786,7 @@
       <c r="B814" s="6">
         <v>7</v>
       </c>
-      <c r="C814" s="22" t="s">
+      <c r="C814" s="7" t="s">
         <v>2895</v>
       </c>
       <c r="D814" s="7" t="s">
@@ -38697,7 +38813,7 @@
       <c r="B815" s="6">
         <v>8</v>
       </c>
-      <c r="C815" s="22" t="s">
+      <c r="C815" s="7" t="s">
         <v>2896</v>
       </c>
       <c r="D815" s="7" t="s">
@@ -38717,14 +38833,14 @@
       </c>
       <c r="I815" s="6"/>
     </row>
-    <row r="816" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A816" s="6">
         <v>33527013</v>
       </c>
       <c r="B816" s="6">
         <v>9</v>
       </c>
-      <c r="C816" s="22" t="s">
+      <c r="C816" s="7" t="s">
         <v>2886</v>
       </c>
       <c r="D816" s="7" t="s">
@@ -38751,7 +38867,7 @@
       <c r="B817" s="6">
         <v>10</v>
       </c>
-      <c r="C817" s="22" t="s">
+      <c r="C817" s="7" t="s">
         <v>2897</v>
       </c>
       <c r="D817" s="7" t="s">
@@ -38771,14 +38887,14 @@
       </c>
       <c r="I817" s="6"/>
     </row>
-    <row r="818" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A818" s="6">
         <v>33527013</v>
       </c>
       <c r="B818" s="6">
         <v>11</v>
       </c>
-      <c r="C818" s="22" t="s">
+      <c r="C818" s="7" t="s">
         <v>2898</v>
       </c>
       <c r="D818" s="7" t="s">
@@ -38805,7 +38921,7 @@
       <c r="B819" s="6">
         <v>1</v>
       </c>
-      <c r="C819" s="22" t="s">
+      <c r="C819" s="7" t="s">
         <v>2926</v>
       </c>
       <c r="D819" s="7" t="s">
@@ -38832,7 +38948,7 @@
       <c r="B820" s="6">
         <v>2</v>
       </c>
-      <c r="C820" s="22" t="s">
+      <c r="C820" s="7" t="s">
         <v>2927</v>
       </c>
       <c r="D820" s="7" t="s">
@@ -38859,7 +38975,7 @@
       <c r="B821" s="6">
         <v>3</v>
       </c>
-      <c r="C821" s="22" t="s">
+      <c r="C821" s="7" t="s">
         <v>2928</v>
       </c>
       <c r="D821" s="7" t="s">
@@ -38886,7 +39002,7 @@
       <c r="B822" s="6">
         <v>4</v>
       </c>
-      <c r="C822" s="22" t="s">
+      <c r="C822" s="7" t="s">
         <v>2929</v>
       </c>
       <c r="D822" s="7" t="s">
@@ -38913,7 +39029,7 @@
       <c r="B823" s="6">
         <v>5</v>
       </c>
-      <c r="C823" s="22" t="s">
+      <c r="C823" s="7" t="s">
         <v>2930</v>
       </c>
       <c r="D823" s="7" t="s">
@@ -38940,7 +39056,7 @@
       <c r="B824" s="6">
         <v>6</v>
       </c>
-      <c r="C824" s="22" t="s">
+      <c r="C824" s="7" t="s">
         <v>2931</v>
       </c>
       <c r="D824" s="7" t="s">
@@ -38967,7 +39083,7 @@
       <c r="B825" s="6">
         <v>7</v>
       </c>
-      <c r="C825" s="22" t="s">
+      <c r="C825" s="7" t="s">
         <v>2932</v>
       </c>
       <c r="D825" s="7" t="s">
@@ -38994,7 +39110,7 @@
       <c r="B826" s="6">
         <v>8</v>
       </c>
-      <c r="C826" s="22" t="s">
+      <c r="C826" s="7" t="s">
         <v>2933</v>
       </c>
       <c r="D826" s="7" t="s">
@@ -39014,14 +39130,14 @@
       </c>
       <c r="I826" s="6"/>
     </row>
-    <row r="827" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A827" s="6">
         <v>2598614</v>
       </c>
       <c r="B827" s="6">
         <v>1</v>
       </c>
-      <c r="C827" s="22" t="s">
+      <c r="C827" s="7" t="s">
         <v>2956</v>
       </c>
       <c r="D827" s="7" t="s">
@@ -39048,7 +39164,7 @@
       <c r="B828" s="6">
         <v>2</v>
       </c>
-      <c r="C828" s="22" t="s">
+      <c r="C828" s="7" t="s">
         <v>2957</v>
       </c>
       <c r="D828" s="7" t="s">
@@ -39075,7 +39191,7 @@
       <c r="B829" s="6">
         <v>3</v>
       </c>
-      <c r="C829" s="22" t="s">
+      <c r="C829" s="7" t="s">
         <v>2958</v>
       </c>
       <c r="D829" s="7" t="s">
@@ -39095,14 +39211,14 @@
       </c>
       <c r="I829" s="6"/>
     </row>
-    <row r="830" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A830" s="6">
         <v>2598614</v>
       </c>
       <c r="B830" s="6">
         <v>4</v>
       </c>
-      <c r="C830" s="22" t="s">
+      <c r="C830" s="7" t="s">
         <v>2959</v>
       </c>
       <c r="D830" s="7" t="s">
@@ -39122,14 +39238,14 @@
       </c>
       <c r="I830" s="6"/>
     </row>
-    <row r="831" spans="1:9" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A831" s="6">
         <v>2598614</v>
       </c>
       <c r="B831" s="6">
         <v>5</v>
       </c>
-      <c r="C831" s="22" t="s">
+      <c r="C831" s="7" t="s">
         <v>2960</v>
       </c>
       <c r="D831" s="7" t="s">
@@ -39156,7 +39272,7 @@
       <c r="B832" s="6">
         <v>6</v>
       </c>
-      <c r="C832" s="22" t="s">
+      <c r="C832" s="7" t="s">
         <v>2961</v>
       </c>
       <c r="D832" s="7" t="s">
@@ -39183,7 +39299,7 @@
       <c r="B833" s="6">
         <v>7</v>
       </c>
-      <c r="C833" s="22" t="s">
+      <c r="C833" s="7" t="s">
         <v>2962</v>
       </c>
       <c r="D833" s="7" t="s">
@@ -39210,7 +39326,7 @@
       <c r="B834" s="6">
         <v>8</v>
       </c>
-      <c r="C834" s="22" t="s">
+      <c r="C834" s="7" t="s">
         <v>2963</v>
       </c>
       <c r="D834" s="7" t="s">
@@ -39237,7 +39353,7 @@
       <c r="B835" s="6">
         <v>9</v>
       </c>
-      <c r="C835" s="22" t="s">
+      <c r="C835" s="7" t="s">
         <v>2964</v>
       </c>
       <c r="D835" s="7" t="s">
@@ -39264,7 +39380,7 @@
       <c r="B836" s="6">
         <v>10</v>
       </c>
-      <c r="C836" s="22" t="s">
+      <c r="C836" s="7" t="s">
         <v>2965</v>
       </c>
       <c r="D836" s="7" t="s">
@@ -39291,7 +39407,7 @@
       <c r="B837" s="6">
         <v>1</v>
       </c>
-      <c r="C837" s="22" t="s">
+      <c r="C837" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="D837" s="7" t="s">
@@ -39318,7 +39434,7 @@
       <c r="B838" s="6">
         <v>2</v>
       </c>
-      <c r="C838" s="22" t="s">
+      <c r="C838" s="7" t="s">
         <v>2998</v>
       </c>
       <c r="D838" s="7" t="s">
@@ -39345,7 +39461,7 @@
       <c r="B839" s="6">
         <v>3</v>
       </c>
-      <c r="C839" s="22" t="s">
+      <c r="C839" s="7" t="s">
         <v>2999</v>
       </c>
       <c r="D839" s="7" t="s">
@@ -39372,7 +39488,7 @@
       <c r="B840" s="6">
         <v>4</v>
       </c>
-      <c r="C840" s="22" t="s">
+      <c r="C840" s="7" t="s">
         <v>3000</v>
       </c>
       <c r="D840" s="7" t="s">
@@ -39399,7 +39515,7 @@
       <c r="B841" s="6">
         <v>5</v>
       </c>
-      <c r="C841" s="22" t="s">
+      <c r="C841" s="7" t="s">
         <v>3001</v>
       </c>
       <c r="D841" s="7" t="s">
@@ -39426,7 +39542,7 @@
       <c r="B842" s="6">
         <v>6</v>
       </c>
-      <c r="C842" s="22" t="s">
+      <c r="C842" s="7" t="s">
         <v>3002</v>
       </c>
       <c r="D842" s="7" t="s">
@@ -39453,7 +39569,7 @@
       <c r="B843" s="6">
         <v>7</v>
       </c>
-      <c r="C843" s="22" t="s">
+      <c r="C843" s="7" t="s">
         <v>3003</v>
       </c>
       <c r="D843" s="7" t="s">
@@ -39480,7 +39596,7 @@
       <c r="B844" s="6">
         <v>8</v>
       </c>
-      <c r="C844" s="22" t="s">
+      <c r="C844" s="7" t="s">
         <v>3004</v>
       </c>
       <c r="D844" s="7" t="s">
@@ -39507,7 +39623,7 @@
       <c r="B845" s="6">
         <v>9</v>
       </c>
-      <c r="C845" s="22" t="s">
+      <c r="C845" s="7" t="s">
         <v>3005</v>
       </c>
       <c r="D845" s="7" t="s">
@@ -39534,7 +39650,7 @@
       <c r="B846" s="6">
         <v>10</v>
       </c>
-      <c r="C846" s="22" t="s">
+      <c r="C846" s="7" t="s">
         <v>3006</v>
       </c>
       <c r="D846" s="7" t="s">
@@ -39561,7 +39677,7 @@
       <c r="B847" s="6">
         <v>11</v>
       </c>
-      <c r="C847" s="22" t="s">
+      <c r="C847" s="7" t="s">
         <v>3007</v>
       </c>
       <c r="D847" s="7" t="s">
@@ -39588,7 +39704,7 @@
       <c r="B848" s="6">
         <v>12</v>
       </c>
-      <c r="C848" s="22" t="s">
+      <c r="C848" s="7" t="s">
         <v>3008</v>
       </c>
       <c r="D848" s="7" t="s">
@@ -39608,14 +39724,14 @@
       </c>
       <c r="I848" s="6"/>
     </row>
-    <row r="849" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A849" s="6">
         <v>35187877</v>
       </c>
       <c r="B849" s="6">
         <v>13</v>
       </c>
-      <c r="C849" s="22" t="s">
+      <c r="C849" s="7" t="s">
         <v>3009</v>
       </c>
       <c r="D849" s="7" t="s">
@@ -39642,7 +39758,7 @@
       <c r="B850" s="6">
         <v>1</v>
       </c>
-      <c r="C850" s="22" t="s">
+      <c r="C850" s="7" t="s">
         <v>3043</v>
       </c>
       <c r="D850" s="7" t="s">
@@ -39669,7 +39785,7 @@
       <c r="B851" s="6">
         <v>2</v>
       </c>
-      <c r="C851" s="22" t="s">
+      <c r="C851" s="7" t="s">
         <v>3044</v>
       </c>
       <c r="D851" s="7" t="s">
@@ -39696,7 +39812,7 @@
       <c r="B852" s="6">
         <v>3</v>
       </c>
-      <c r="C852" s="22" t="s">
+      <c r="C852" s="7" t="s">
         <v>3045</v>
       </c>
       <c r="D852" s="7" t="s">
@@ -39723,7 +39839,7 @@
       <c r="B853" s="6">
         <v>4</v>
       </c>
-      <c r="C853" s="22" t="s">
+      <c r="C853" s="7" t="s">
         <v>3046</v>
       </c>
       <c r="D853" s="7" t="s">
@@ -39750,7 +39866,7 @@
       <c r="B854" s="6">
         <v>5</v>
       </c>
-      <c r="C854" s="22" t="s">
+      <c r="C854" s="7" t="s">
         <v>3047</v>
       </c>
       <c r="D854" s="7" t="s">
@@ -39777,7 +39893,7 @@
       <c r="B855" s="6">
         <v>6</v>
       </c>
-      <c r="C855" s="22" t="s">
+      <c r="C855" s="7" t="s">
         <v>3037</v>
       </c>
       <c r="D855" s="7" t="s">
@@ -39804,7 +39920,7 @@
       <c r="B856" s="6">
         <v>7</v>
       </c>
-      <c r="C856" s="22" t="s">
+      <c r="C856" s="7" t="s">
         <v>3048</v>
       </c>
       <c r="D856" s="7" t="s">
@@ -39831,7 +39947,7 @@
       <c r="B857" s="6">
         <v>8</v>
       </c>
-      <c r="C857" s="22" t="s">
+      <c r="C857" s="7" t="s">
         <v>3049</v>
       </c>
       <c r="D857" s="7" t="s">
@@ -39858,7 +39974,7 @@
       <c r="B858" s="6">
         <v>9</v>
       </c>
-      <c r="C858" s="22" t="s">
+      <c r="C858" s="7" t="s">
         <v>3050</v>
       </c>
       <c r="D858" s="7" t="s">
@@ -39885,7 +40001,7 @@
       <c r="B859" s="6">
         <v>10</v>
       </c>
-      <c r="C859" s="22" t="s">
+      <c r="C859" s="7" t="s">
         <v>3051</v>
       </c>
       <c r="D859" s="7" t="s">
@@ -39912,7 +40028,7 @@
       <c r="B860" s="6">
         <v>1</v>
       </c>
-      <c r="C860" s="22" t="s">
+      <c r="C860" s="7" t="s">
         <v>3052</v>
       </c>
       <c r="D860" s="7" t="s">
@@ -39939,7 +40055,7 @@
       <c r="B861" s="6">
         <v>2</v>
       </c>
-      <c r="C861" s="22" t="s">
+      <c r="C861" s="7" t="s">
         <v>3053</v>
       </c>
       <c r="D861" s="7" t="s">
@@ -39966,7 +40082,7 @@
       <c r="B862" s="6">
         <v>3</v>
       </c>
-      <c r="C862" s="22" t="s">
+      <c r="C862" s="7" t="s">
         <v>3054</v>
       </c>
       <c r="D862" s="7" t="s">
@@ -39993,7 +40109,7 @@
       <c r="B863" s="6">
         <v>4</v>
       </c>
-      <c r="C863" s="22" t="s">
+      <c r="C863" s="7" t="s">
         <v>3055</v>
       </c>
       <c r="D863" s="7" t="s">
@@ -40020,7 +40136,7 @@
       <c r="B864" s="6">
         <v>5</v>
       </c>
-      <c r="C864" s="22" t="s">
+      <c r="C864" s="7" t="s">
         <v>3056</v>
       </c>
       <c r="D864" s="7" t="s">
@@ -40047,7 +40163,7 @@
       <c r="B865" s="6">
         <v>6</v>
       </c>
-      <c r="C865" s="22" t="s">
+      <c r="C865" s="7" t="s">
         <v>3057</v>
       </c>
       <c r="D865" s="7" t="s">
@@ -40074,7 +40190,7 @@
       <c r="B866" s="6">
         <v>7</v>
       </c>
-      <c r="C866" s="22" t="s">
+      <c r="C866" s="7" t="s">
         <v>3058</v>
       </c>
       <c r="D866" s="7" t="s">
@@ -40101,7 +40217,7 @@
       <c r="B867" s="6">
         <v>8</v>
       </c>
-      <c r="C867" s="22" t="s">
+      <c r="C867" s="7" t="s">
         <v>3059</v>
       </c>
       <c r="D867" s="7" t="s">
@@ -40128,7 +40244,7 @@
       <c r="B868" s="6">
         <v>9</v>
       </c>
-      <c r="C868" s="22" t="s">
+      <c r="C868" s="7" t="s">
         <v>3060</v>
       </c>
       <c r="D868" s="7" t="s">
@@ -40155,7 +40271,7 @@
       <c r="B869" s="6">
         <v>10</v>
       </c>
-      <c r="C869" s="22" t="s">
+      <c r="C869" s="7" t="s">
         <v>3061</v>
       </c>
       <c r="D869" s="7" t="s">
@@ -40182,7 +40298,7 @@
       <c r="B870" s="6">
         <v>11</v>
       </c>
-      <c r="C870" s="22" t="s">
+      <c r="C870" s="7" t="s">
         <v>3062</v>
       </c>
       <c r="D870" s="7" t="s">
@@ -40209,7 +40325,7 @@
       <c r="B871" s="6">
         <v>12</v>
       </c>
-      <c r="C871" s="22" t="s">
+      <c r="C871" s="7" t="s">
         <v>3063</v>
       </c>
       <c r="D871" s="7" t="s">
@@ -40236,7 +40352,7 @@
       <c r="B872" s="6">
         <v>13</v>
       </c>
-      <c r="C872" s="22" t="s">
+      <c r="C872" s="7" t="s">
         <v>3064</v>
       </c>
       <c r="D872" s="7" t="s">
@@ -40263,7 +40379,7 @@
       <c r="B873" s="6">
         <v>1</v>
       </c>
-      <c r="C873" s="22" t="s">
+      <c r="C873" s="7" t="s">
         <v>3121</v>
       </c>
       <c r="D873" s="7" t="s">
@@ -40290,7 +40406,7 @@
       <c r="B874" s="6">
         <v>2</v>
       </c>
-      <c r="C874" s="22" t="s">
+      <c r="C874" s="7" t="s">
         <v>3122</v>
       </c>
       <c r="D874" s="7" t="s">
@@ -40317,7 +40433,7 @@
       <c r="B875" s="6">
         <v>3</v>
       </c>
-      <c r="C875" s="22" t="s">
+      <c r="C875" s="7" t="s">
         <v>3123</v>
       </c>
       <c r="D875" s="7" t="s">
@@ -40344,7 +40460,7 @@
       <c r="B876" s="6">
         <v>4</v>
       </c>
-      <c r="C876" s="22" t="s">
+      <c r="C876" s="7" t="s">
         <v>3124</v>
       </c>
       <c r="D876" s="7" t="s">
@@ -40371,7 +40487,7 @@
       <c r="B877" s="6">
         <v>5</v>
       </c>
-      <c r="C877" s="22" t="s">
+      <c r="C877" s="7" t="s">
         <v>3125</v>
       </c>
       <c r="D877" s="7" t="s">
@@ -40398,7 +40514,7 @@
       <c r="B878" s="6">
         <v>6</v>
       </c>
-      <c r="C878" s="22" t="s">
+      <c r="C878" s="7" t="s">
         <v>3126</v>
       </c>
       <c r="D878" s="7" t="s">
@@ -40425,7 +40541,7 @@
       <c r="B879" s="6">
         <v>7</v>
       </c>
-      <c r="C879" s="22" t="s">
+      <c r="C879" s="7" t="s">
         <v>3127</v>
       </c>
       <c r="D879" s="7" t="s">
@@ -40452,7 +40568,7 @@
       <c r="B880" s="6">
         <v>8</v>
       </c>
-      <c r="C880" s="22" t="s">
+      <c r="C880" s="7" t="s">
         <v>3128</v>
       </c>
       <c r="D880" s="7" t="s">
@@ -40479,7 +40595,7 @@
       <c r="B881" s="6">
         <v>9</v>
       </c>
-      <c r="C881" s="22" t="s">
+      <c r="C881" s="7" t="s">
         <v>3129</v>
       </c>
       <c r="D881" s="7" t="s">
@@ -40506,7 +40622,7 @@
       <c r="B882" s="6">
         <v>10</v>
       </c>
-      <c r="C882" s="22" t="s">
+      <c r="C882" s="7" t="s">
         <v>3130</v>
       </c>
       <c r="D882" s="7" t="s">
@@ -40533,7 +40649,7 @@
       <c r="B883" s="6">
         <v>1</v>
       </c>
-      <c r="C883" s="22" t="s">
+      <c r="C883" s="7" t="s">
         <v>3156</v>
       </c>
       <c r="D883" s="7" t="s">
@@ -40560,7 +40676,7 @@
       <c r="B884" s="6">
         <v>2</v>
       </c>
-      <c r="C884" s="22" t="s">
+      <c r="C884" s="7" t="s">
         <v>3157</v>
       </c>
       <c r="D884" s="7" t="s">
@@ -40587,7 +40703,7 @@
       <c r="B885" s="6">
         <v>3</v>
       </c>
-      <c r="C885" s="22" t="s">
+      <c r="C885" s="7" t="s">
         <v>3158</v>
       </c>
       <c r="D885" s="7" t="s">
@@ -40614,7 +40730,7 @@
       <c r="B886" s="6">
         <v>4</v>
       </c>
-      <c r="C886" s="22" t="s">
+      <c r="C886" s="7" t="s">
         <v>3159</v>
       </c>
       <c r="D886" s="7" t="s">
@@ -40641,7 +40757,7 @@
       <c r="B887" s="6">
         <v>5</v>
       </c>
-      <c r="C887" s="22" t="s">
+      <c r="C887" s="7" t="s">
         <v>3160</v>
       </c>
       <c r="D887" s="7" t="s">
@@ -40668,7 +40784,7 @@
       <c r="B888" s="6">
         <v>6</v>
       </c>
-      <c r="C888" s="22" t="s">
+      <c r="C888" s="7" t="s">
         <v>3161</v>
       </c>
       <c r="D888" s="7" t="s">
@@ -40695,7 +40811,7 @@
       <c r="B889" s="6">
         <v>7</v>
       </c>
-      <c r="C889" s="22" t="s">
+      <c r="C889" s="7" t="s">
         <v>3162</v>
       </c>
       <c r="D889" s="7" t="s">
@@ -40722,7 +40838,7 @@
       <c r="B890" s="6">
         <v>8</v>
       </c>
-      <c r="C890" s="22" t="s">
+      <c r="C890" s="7" t="s">
         <v>3163</v>
       </c>
       <c r="D890" s="7" t="s">
@@ -40749,7 +40865,7 @@
       <c r="B891" s="6">
         <v>1</v>
       </c>
-      <c r="C891" s="22" t="s">
+      <c r="C891" s="7" t="s">
         <v>3190</v>
       </c>
       <c r="D891" s="7" t="s">
@@ -40776,7 +40892,7 @@
       <c r="B892" s="6">
         <v>2</v>
       </c>
-      <c r="C892" s="22" t="s">
+      <c r="C892" s="7" t="s">
         <v>3191</v>
       </c>
       <c r="D892" s="7" t="s">
@@ -40803,7 +40919,7 @@
       <c r="B893" s="6">
         <v>3</v>
       </c>
-      <c r="C893" s="22" t="s">
+      <c r="C893" s="7" t="s">
         <v>3192</v>
       </c>
       <c r="D893" s="7" t="s">
@@ -40832,7 +40948,7 @@
       <c r="B894" s="6">
         <v>4</v>
       </c>
-      <c r="C894" s="22" t="s">
+      <c r="C894" s="7" t="s">
         <v>3193</v>
       </c>
       <c r="D894" s="7" t="s">
@@ -40859,7 +40975,7 @@
       <c r="B895" s="6">
         <v>5</v>
       </c>
-      <c r="C895" s="22" t="s">
+      <c r="C895" s="7" t="s">
         <v>3194</v>
       </c>
       <c r="D895" s="7" t="s">
@@ -40886,7 +41002,7 @@
       <c r="B896" s="6">
         <v>6</v>
       </c>
-      <c r="C896" s="22" t="s">
+      <c r="C896" s="7" t="s">
         <v>3195</v>
       </c>
       <c r="D896" s="7" t="s">
@@ -40913,7 +41029,7 @@
       <c r="B897" s="6">
         <v>7</v>
       </c>
-      <c r="C897" s="22" t="s">
+      <c r="C897" s="7" t="s">
         <v>3196</v>
       </c>
       <c r="D897" s="7" t="s">
@@ -40940,7 +41056,7 @@
       <c r="B898" s="6">
         <v>8</v>
       </c>
-      <c r="C898" s="22" t="s">
+      <c r="C898" s="7" t="s">
         <v>3197</v>
       </c>
       <c r="D898" s="7" t="s">
@@ -40967,7 +41083,7 @@
       <c r="B899" s="6">
         <v>9</v>
       </c>
-      <c r="C899" s="22" t="s">
+      <c r="C899" s="7" t="s">
         <v>3198</v>
       </c>
       <c r="D899" s="7" t="s">
@@ -40996,7 +41112,7 @@
       <c r="B900" s="6">
         <v>10</v>
       </c>
-      <c r="C900" s="22" t="s">
+      <c r="C900" s="7" t="s">
         <v>3199</v>
       </c>
       <c r="D900" s="7" t="s">
@@ -41023,7 +41139,7 @@
       <c r="B901" s="6">
         <v>1</v>
       </c>
-      <c r="C901" s="22" t="s">
+      <c r="C901" s="7" t="s">
         <v>3226</v>
       </c>
       <c r="D901" s="7" t="s">
@@ -41050,7 +41166,7 @@
       <c r="B902" s="6">
         <v>2</v>
       </c>
-      <c r="C902" s="22" t="s">
+      <c r="C902" s="7" t="s">
         <v>3227</v>
       </c>
       <c r="D902" s="7" t="s">
@@ -41079,7 +41195,7 @@
       <c r="B903" s="6">
         <v>3</v>
       </c>
-      <c r="C903" s="22" t="s">
+      <c r="C903" s="7" t="s">
         <v>3228</v>
       </c>
       <c r="D903" s="7" t="s">
@@ -41106,7 +41222,7 @@
       <c r="B904" s="6">
         <v>4</v>
       </c>
-      <c r="C904" s="22" t="s">
+      <c r="C904" s="7" t="s">
         <v>3229</v>
       </c>
       <c r="D904" s="7" t="s">
@@ -41135,7 +41251,7 @@
       <c r="B905" s="6">
         <v>5</v>
       </c>
-      <c r="C905" s="22" t="s">
+      <c r="C905" s="7" t="s">
         <v>3230</v>
       </c>
       <c r="D905" s="7" t="s">
@@ -41162,7 +41278,7 @@
       <c r="B906" s="6">
         <v>6</v>
       </c>
-      <c r="C906" s="22" t="s">
+      <c r="C906" s="7" t="s">
         <v>3231</v>
       </c>
       <c r="D906" s="7" t="s">
@@ -41189,7 +41305,7 @@
       <c r="B907" s="6">
         <v>7</v>
       </c>
-      <c r="C907" s="22" t="s">
+      <c r="C907" s="7" t="s">
         <v>3232</v>
       </c>
       <c r="D907" s="7" t="s">
@@ -41216,7 +41332,7 @@
       <c r="B908" s="6">
         <v>8</v>
       </c>
-      <c r="C908" s="22" t="s">
+      <c r="C908" s="7" t="s">
         <v>3234</v>
       </c>
       <c r="D908" s="7" t="s">
@@ -41243,7 +41359,7 @@
       <c r="B909" s="6">
         <v>9</v>
       </c>
-      <c r="C909" s="22" t="s">
+      <c r="C909" s="7" t="s">
         <v>3233</v>
       </c>
       <c r="D909" s="7" t="s">
@@ -41270,7 +41386,7 @@
       <c r="B910" s="6">
         <v>1</v>
       </c>
-      <c r="C910" s="22" t="s">
+      <c r="C910" s="7" t="s">
         <v>3260</v>
       </c>
       <c r="D910" s="7" t="s">
@@ -41297,7 +41413,7 @@
       <c r="B911" s="6">
         <v>2</v>
       </c>
-      <c r="C911" s="22" t="s">
+      <c r="C911" s="7" t="s">
         <v>3261</v>
       </c>
       <c r="D911" s="7" t="s">
@@ -41324,7 +41440,7 @@
       <c r="B912" s="6">
         <v>3</v>
       </c>
-      <c r="C912" s="22" t="s">
+      <c r="C912" s="7" t="s">
         <v>3267</v>
       </c>
       <c r="D912" s="7" t="s">
@@ -41351,7 +41467,7 @@
       <c r="B913" s="6">
         <v>4</v>
       </c>
-      <c r="C913" s="22" t="s">
+      <c r="C913" s="7" t="s">
         <v>3266</v>
       </c>
       <c r="D913" s="7" t="s">
@@ -41378,7 +41494,7 @@
       <c r="B914" s="6">
         <v>5</v>
       </c>
-      <c r="C914" s="22" t="s">
+      <c r="C914" s="7" t="s">
         <v>3264</v>
       </c>
       <c r="D914" s="7" t="s">
@@ -41407,7 +41523,7 @@
       <c r="B915" s="6">
         <v>6</v>
       </c>
-      <c r="C915" s="22" t="s">
+      <c r="C915" s="7" t="s">
         <v>3254</v>
       </c>
       <c r="D915" s="7" t="s">
@@ -41434,7 +41550,7 @@
       <c r="B916" s="6">
         <v>7</v>
       </c>
-      <c r="C916" s="22" t="s">
+      <c r="C916" s="7" t="s">
         <v>3265</v>
       </c>
       <c r="D916" s="7" t="s">
@@ -41461,7 +41577,7 @@
       <c r="B917" s="6">
         <v>8</v>
       </c>
-      <c r="C917" s="22" t="s">
+      <c r="C917" s="7" t="s">
         <v>3263</v>
       </c>
       <c r="D917" s="7" t="s">
@@ -41488,7 +41604,7 @@
       <c r="B918" s="6">
         <v>9</v>
       </c>
-      <c r="C918" s="22" t="s">
+      <c r="C918" s="7" t="s">
         <v>3262</v>
       </c>
       <c r="D918" s="7" t="s">
@@ -41515,7 +41631,7 @@
       <c r="B919" s="6">
         <v>1</v>
       </c>
-      <c r="C919" s="22" t="s">
+      <c r="C919" s="7" t="s">
         <v>3288</v>
       </c>
       <c r="D919" s="7" t="s">
@@ -41542,7 +41658,7 @@
       <c r="B920" s="6">
         <v>2</v>
       </c>
-      <c r="C920" s="22" t="s">
+      <c r="C920" s="7" t="s">
         <v>3289</v>
       </c>
       <c r="D920" s="7" t="s">
@@ -41569,7 +41685,7 @@
       <c r="B921" s="6">
         <v>3</v>
       </c>
-      <c r="C921" s="22" t="s">
+      <c r="C921" s="7" t="s">
         <v>3290</v>
       </c>
       <c r="D921" s="7" t="s">
@@ -41596,7 +41712,7 @@
       <c r="B922" s="6">
         <v>4</v>
       </c>
-      <c r="C922" s="22" t="s">
+      <c r="C922" s="7" t="s">
         <v>3291</v>
       </c>
       <c r="D922" s="7" t="s">
@@ -41623,7 +41739,7 @@
       <c r="B923" s="6">
         <v>5</v>
       </c>
-      <c r="C923" s="22" t="s">
+      <c r="C923" s="7" t="s">
         <v>3292</v>
       </c>
       <c r="D923" s="7" t="s">
@@ -41650,7 +41766,7 @@
       <c r="B924" s="6">
         <v>6</v>
       </c>
-      <c r="C924" s="22" t="s">
+      <c r="C924" s="7" t="s">
         <v>3293</v>
       </c>
       <c r="D924" s="7" t="s">
@@ -41677,7 +41793,7 @@
       <c r="B925" s="6">
         <v>7</v>
       </c>
-      <c r="C925" s="22" t="s">
+      <c r="C925" s="7" t="s">
         <v>3294</v>
       </c>
       <c r="D925" s="7" t="s">
@@ -41704,7 +41820,7 @@
       <c r="B926" s="6">
         <v>8</v>
       </c>
-      <c r="C926" s="22" t="s">
+      <c r="C926" s="7" t="s">
         <v>3295</v>
       </c>
       <c r="D926" s="7" t="s">
@@ -41731,7 +41847,7 @@
       <c r="B927" s="6">
         <v>9</v>
       </c>
-      <c r="C927" s="22" t="s">
+      <c r="C927" s="7" t="s">
         <v>3296</v>
       </c>
       <c r="D927" s="7" t="s">
@@ -41758,7 +41874,7 @@
       <c r="B928" s="6">
         <v>10</v>
       </c>
-      <c r="C928" s="22" t="s">
+      <c r="C928" s="7" t="s">
         <v>3297</v>
       </c>
       <c r="D928" s="7" t="s">
@@ -41785,7 +41901,7 @@
       <c r="B929" s="6">
         <v>11</v>
       </c>
-      <c r="C929" s="22" t="s">
+      <c r="C929" s="7" t="s">
         <v>3298</v>
       </c>
       <c r="D929" s="7" t="s">
@@ -41812,7 +41928,7 @@
       <c r="B930" s="6">
         <v>1</v>
       </c>
-      <c r="C930" s="22" t="s">
+      <c r="C930" s="7" t="s">
         <v>3329</v>
       </c>
       <c r="D930" s="7" t="s">
@@ -41841,7 +41957,7 @@
       <c r="B931" s="6">
         <v>2</v>
       </c>
-      <c r="C931" s="22" t="s">
+      <c r="C931" s="7" t="s">
         <v>3330</v>
       </c>
       <c r="D931" s="7" t="s">
@@ -41868,7 +41984,7 @@
       <c r="B932" s="6">
         <v>3</v>
       </c>
-      <c r="C932" s="22" t="s">
+      <c r="C932" s="7" t="s">
         <v>3331</v>
       </c>
       <c r="D932" s="7" t="s">
@@ -41895,7 +42011,7 @@
       <c r="B933" s="6">
         <v>4</v>
       </c>
-      <c r="C933" s="22" t="s">
+      <c r="C933" s="7" t="s">
         <v>3332</v>
       </c>
       <c r="D933" s="7" t="s">
@@ -41922,7 +42038,7 @@
       <c r="B934" s="6">
         <v>5</v>
       </c>
-      <c r="C934" s="22" t="s">
+      <c r="C934" s="7" t="s">
         <v>3333</v>
       </c>
       <c r="D934" s="7" t="s">
@@ -41949,7 +42065,7 @@
       <c r="B935" s="6">
         <v>6</v>
       </c>
-      <c r="C935" s="22" t="s">
+      <c r="C935" s="7" t="s">
         <v>3334</v>
       </c>
       <c r="D935" s="7" t="s">
@@ -41978,7 +42094,7 @@
       <c r="B936" s="6">
         <v>7</v>
       </c>
-      <c r="C936" s="22" t="s">
+      <c r="C936" s="7" t="s">
         <v>3335</v>
       </c>
       <c r="D936" s="7" t="s">
@@ -42007,7 +42123,7 @@
       <c r="B937" s="6">
         <v>8</v>
       </c>
-      <c r="C937" s="22" t="s">
+      <c r="C937" s="7" t="s">
         <v>3336</v>
       </c>
       <c r="D937" s="7" t="s">
@@ -42034,7 +42150,7 @@
       <c r="B938" s="6">
         <v>9</v>
       </c>
-      <c r="C938" s="22" t="s">
+      <c r="C938" s="7" t="s">
         <v>3337</v>
       </c>
       <c r="D938" s="7" t="s">
@@ -42061,7 +42177,7 @@
       <c r="B939" s="6">
         <v>10</v>
       </c>
-      <c r="C939" s="22" t="s">
+      <c r="C939" s="7" t="s">
         <v>3338</v>
       </c>
       <c r="D939" s="7" t="s">
@@ -42088,7 +42204,7 @@
       <c r="B940" s="6">
         <v>1</v>
       </c>
-      <c r="C940" s="22" t="s">
+      <c r="C940" s="7" t="s">
         <v>3362</v>
       </c>
       <c r="D940" s="7" t="s">
@@ -42117,7 +42233,7 @@
       <c r="B941" s="6">
         <v>2</v>
       </c>
-      <c r="C941" s="22" t="s">
+      <c r="C941" s="7" t="s">
         <v>3363</v>
       </c>
       <c r="D941" s="7" t="s">
@@ -42146,7 +42262,7 @@
       <c r="B942" s="6">
         <v>3</v>
       </c>
-      <c r="C942" s="22" t="s">
+      <c r="C942" s="7" t="s">
         <v>3364</v>
       </c>
       <c r="D942" s="7" t="s">
@@ -42200,7 +42316,7 @@
       <c r="B944" s="6">
         <v>5</v>
       </c>
-      <c r="C944" s="22" t="s">
+      <c r="C944" s="7" t="s">
         <v>3366</v>
       </c>
       <c r="D944" s="7" t="s">
@@ -42229,7 +42345,7 @@
       <c r="B945" s="6">
         <v>6</v>
       </c>
-      <c r="C945" s="22" t="s">
+      <c r="C945" s="7" t="s">
         <v>3367</v>
       </c>
       <c r="D945" s="7" t="s">
@@ -42258,7 +42374,7 @@
       <c r="B946" s="6">
         <v>7</v>
       </c>
-      <c r="C946" s="22" t="s">
+      <c r="C946" s="7" t="s">
         <v>3368</v>
       </c>
       <c r="D946" s="7" t="s">
@@ -42287,7 +42403,7 @@
       <c r="B947" s="6">
         <v>8</v>
       </c>
-      <c r="C947" s="22" t="s">
+      <c r="C947" s="7" t="s">
         <v>3369</v>
       </c>
       <c r="D947" s="7" t="s">
@@ -42314,7 +42430,7 @@
       <c r="B948" s="6">
         <v>9</v>
       </c>
-      <c r="C948" s="22" t="s">
+      <c r="C948" s="7" t="s">
         <v>3370</v>
       </c>
       <c r="D948" s="7" t="s">
@@ -42341,7 +42457,7 @@
       <c r="B949" s="6">
         <v>1</v>
       </c>
-      <c r="C949" s="22" t="s">
+      <c r="C949" s="7" t="s">
         <v>3401</v>
       </c>
       <c r="D949" s="7" t="s">
@@ -42370,7 +42486,7 @@
       <c r="B950" s="6">
         <v>2</v>
       </c>
-      <c r="C950" s="22" t="s">
+      <c r="C950" s="7" t="s">
         <v>3402</v>
       </c>
       <c r="D950" s="7" t="s">
@@ -42397,7 +42513,7 @@
       <c r="B951" s="6">
         <v>3</v>
       </c>
-      <c r="C951" s="22" t="s">
+      <c r="C951" s="7" t="s">
         <v>3403</v>
       </c>
       <c r="D951" s="7" t="s">
@@ -42424,7 +42540,7 @@
       <c r="B952" s="6">
         <v>4</v>
       </c>
-      <c r="C952" s="22" t="s">
+      <c r="C952" s="7" t="s">
         <v>3404</v>
       </c>
       <c r="D952" s="7" t="s">
@@ -42451,7 +42567,7 @@
       <c r="B953" s="6">
         <v>5</v>
       </c>
-      <c r="C953" s="22" t="s">
+      <c r="C953" s="7" t="s">
         <v>3405</v>
       </c>
       <c r="D953" s="7" t="s">
@@ -42478,7 +42594,7 @@
       <c r="B954" s="6">
         <v>6</v>
       </c>
-      <c r="C954" s="22" t="s">
+      <c r="C954" s="7" t="s">
         <v>3406</v>
       </c>
       <c r="D954" s="7" t="s">
@@ -42505,7 +42621,7 @@
       <c r="B955" s="6">
         <v>7</v>
       </c>
-      <c r="C955" s="22" t="s">
+      <c r="C955" s="7" t="s">
         <v>3410</v>
       </c>
       <c r="D955" s="7" t="s">
@@ -42532,7 +42648,7 @@
       <c r="B956" s="6">
         <v>8</v>
       </c>
-      <c r="C956" s="22" t="s">
+      <c r="C956" s="7" t="s">
         <v>3409</v>
       </c>
       <c r="D956" s="7" t="s">
@@ -42559,7 +42675,7 @@
       <c r="B957" s="6">
         <v>9</v>
       </c>
-      <c r="C957" s="22" t="s">
+      <c r="C957" s="7" t="s">
         <v>3408</v>
       </c>
       <c r="D957" s="7" t="s">
@@ -42586,7 +42702,7 @@
       <c r="B958" s="6">
         <v>10</v>
       </c>
-      <c r="C958" s="22" t="s">
+      <c r="C958" s="7" t="s">
         <v>3407</v>
       </c>
       <c r="D958" s="7" t="s">
@@ -42615,7 +42731,7 @@
       <c r="B959" s="6">
         <v>1</v>
       </c>
-      <c r="C959" s="22" t="s">
+      <c r="C959" s="7" t="s">
         <v>3437</v>
       </c>
       <c r="D959" s="7" t="s">
@@ -42642,7 +42758,7 @@
       <c r="B960" s="6">
         <v>2</v>
       </c>
-      <c r="C960" s="22" t="s">
+      <c r="C960" s="7" t="s">
         <v>3438</v>
       </c>
       <c r="D960" s="7" t="s">
@@ -42669,7 +42785,7 @@
       <c r="B961" s="6">
         <v>3</v>
       </c>
-      <c r="C961" s="22" t="s">
+      <c r="C961" s="7" t="s">
         <v>3431</v>
       </c>
       <c r="D961" s="7" t="s">
@@ -42696,7 +42812,7 @@
       <c r="B962" s="6">
         <v>4</v>
       </c>
-      <c r="C962" s="22" t="s">
+      <c r="C962" s="7" t="s">
         <v>3439</v>
       </c>
       <c r="D962" s="7" t="s">
@@ -42723,7 +42839,7 @@
       <c r="B963" s="6">
         <v>5</v>
       </c>
-      <c r="C963" s="22" t="s">
+      <c r="C963" s="7" t="s">
         <v>3440</v>
       </c>
       <c r="D963" s="7" t="s">
@@ -42750,7 +42866,7 @@
       <c r="B964" s="6">
         <v>6</v>
       </c>
-      <c r="C964" s="22" t="s">
+      <c r="C964" s="7" t="s">
         <v>3442</v>
       </c>
       <c r="D964" s="7" t="s">
@@ -42777,7 +42893,7 @@
       <c r="B965" s="6">
         <v>7</v>
       </c>
-      <c r="C965" s="22" t="s">
+      <c r="C965" s="7" t="s">
         <v>3441</v>
       </c>
       <c r="D965" s="7" t="s">
@@ -42804,7 +42920,7 @@
       <c r="B966" s="6">
         <v>8</v>
       </c>
-      <c r="C966" s="22" t="s">
+      <c r="C966" s="7" t="s">
         <v>3445</v>
       </c>
       <c r="D966" s="7" t="s">
@@ -42831,7 +42947,7 @@
       <c r="B967" s="6">
         <v>9</v>
       </c>
-      <c r="C967" s="22" t="s">
+      <c r="C967" s="7" t="s">
         <v>3444</v>
       </c>
       <c r="D967" s="7" t="s">
@@ -42858,7 +42974,7 @@
       <c r="B968" s="6">
         <v>10</v>
       </c>
-      <c r="C968" s="22" t="s">
+      <c r="C968" s="7" t="s">
         <v>3443</v>
       </c>
       <c r="D968" s="7" t="s">
@@ -42885,7 +43001,7 @@
       <c r="B969" s="6">
         <v>1</v>
       </c>
-      <c r="C969" s="22" t="s">
+      <c r="C969" s="7" t="s">
         <v>3468</v>
       </c>
       <c r="D969" s="7" t="s">
@@ -42912,7 +43028,7 @@
       <c r="B970" s="6">
         <v>2</v>
       </c>
-      <c r="C970" s="22" t="s">
+      <c r="C970" s="7" t="s">
         <v>3469</v>
       </c>
       <c r="D970" s="7" t="s">
@@ -42939,7 +43055,7 @@
       <c r="B971" s="6">
         <v>3</v>
       </c>
-      <c r="C971" s="22" t="s">
+      <c r="C971" s="7" t="s">
         <v>3470</v>
       </c>
       <c r="D971" s="7" t="s">
@@ -42966,7 +43082,7 @@
       <c r="B972" s="6">
         <v>4</v>
       </c>
-      <c r="C972" s="22" t="s">
+      <c r="C972" s="7" t="s">
         <v>3471</v>
       </c>
       <c r="D972" s="7" t="s">
@@ -42993,7 +43109,7 @@
       <c r="B973" s="6">
         <v>5</v>
       </c>
-      <c r="C973" s="22" t="s">
+      <c r="C973" s="7" t="s">
         <v>3472</v>
       </c>
       <c r="D973" s="7" t="s">
@@ -43022,7 +43138,7 @@
       <c r="B974" s="6">
         <v>6</v>
       </c>
-      <c r="C974" s="22" t="s">
+      <c r="C974" s="7" t="s">
         <v>3473</v>
       </c>
       <c r="D974" s="7" t="s">
@@ -43037,7 +43153,7 @@
       <c r="G974" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H974" s="23" t="s">
+      <c r="H974" s="22" t="s">
         <v>3500</v>
       </c>
       <c r="I974" s="6"/>
@@ -43049,7 +43165,7 @@
       <c r="B975" s="6">
         <v>7</v>
       </c>
-      <c r="C975" s="22" t="s">
+      <c r="C975" s="7" t="s">
         <v>3474</v>
       </c>
       <c r="D975" s="7" t="s">
@@ -43064,7 +43180,7 @@
       <c r="G975" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H975" s="23" t="s">
+      <c r="H975" s="22" t="s">
         <v>3491</v>
       </c>
       <c r="I975" s="6" t="s">
@@ -43078,7 +43194,7 @@
       <c r="B976" s="6">
         <v>8</v>
       </c>
-      <c r="C976" s="22" t="s">
+      <c r="C976" s="7" t="s">
         <v>3475</v>
       </c>
       <c r="D976" s="7" t="s">
@@ -43105,7 +43221,7 @@
       <c r="B977" s="6">
         <v>9</v>
       </c>
-      <c r="C977" s="22" t="s">
+      <c r="C977" s="7" t="s">
         <v>3476</v>
       </c>
       <c r="D977" s="7" t="s">
@@ -43132,7 +43248,7 @@
       <c r="B978" s="6">
         <v>10</v>
       </c>
-      <c r="C978" s="22" t="s">
+      <c r="C978" s="7" t="s">
         <v>3477</v>
       </c>
       <c r="D978" s="7" t="s">
@@ -43159,7 +43275,7 @@
       <c r="B979" s="6">
         <v>1</v>
       </c>
-      <c r="C979" s="22" t="s">
+      <c r="C979" s="7" t="s">
         <v>1178</v>
       </c>
       <c r="D979" s="7" t="s">
@@ -43186,7 +43302,7 @@
       <c r="B980" s="6">
         <v>2</v>
       </c>
-      <c r="C980" s="22" t="s">
+      <c r="C980" s="7" t="s">
         <v>3507</v>
       </c>
       <c r="D980" s="7" t="s">
@@ -43213,7 +43329,7 @@
       <c r="B981" s="6">
         <v>3</v>
       </c>
-      <c r="C981" s="22" t="s">
+      <c r="C981" s="7" t="s">
         <v>3508</v>
       </c>
       <c r="D981" s="7" t="s">
@@ -43240,7 +43356,7 @@
       <c r="B982" s="6">
         <v>4</v>
       </c>
-      <c r="C982" s="22" t="s">
+      <c r="C982" s="7" t="s">
         <v>3509</v>
       </c>
       <c r="D982" s="7" t="s">
@@ -43267,7 +43383,7 @@
       <c r="B983" s="6">
         <v>5</v>
       </c>
-      <c r="C983" s="22" t="s">
+      <c r="C983" s="7" t="s">
         <v>3502</v>
       </c>
       <c r="D983" s="7" t="s">
@@ -43294,7 +43410,7 @@
       <c r="B984" s="6">
         <v>6</v>
       </c>
-      <c r="C984" s="22" t="s">
+      <c r="C984" s="7" t="s">
         <v>3510</v>
       </c>
       <c r="D984" s="7" t="s">
@@ -43321,7 +43437,7 @@
       <c r="B985" s="6">
         <v>7</v>
       </c>
-      <c r="C985" s="22" t="s">
+      <c r="C985" s="7" t="s">
         <v>3511</v>
       </c>
       <c r="D985" s="7" t="s">
@@ -43348,7 +43464,7 @@
       <c r="B986" s="6">
         <v>8</v>
       </c>
-      <c r="C986" s="22" t="s">
+      <c r="C986" s="7" t="s">
         <v>3512</v>
       </c>
       <c r="D986" s="7" t="s">
@@ -43375,7 +43491,7 @@
       <c r="B987" s="6">
         <v>1</v>
       </c>
-      <c r="C987" s="22" t="s">
+      <c r="C987" s="7" t="s">
         <v>3536</v>
       </c>
       <c r="D987" s="7" t="s">
@@ -43404,7 +43520,7 @@
       <c r="B988" s="6">
         <v>2</v>
       </c>
-      <c r="C988" s="22" t="s">
+      <c r="C988" s="7" t="s">
         <v>3538</v>
       </c>
       <c r="D988" s="7" t="s">
@@ -43431,7 +43547,7 @@
       <c r="B989" s="6">
         <v>3</v>
       </c>
-      <c r="C989" s="22" t="s">
+      <c r="C989" s="7" t="s">
         <v>3537</v>
       </c>
       <c r="D989" s="7" t="s">
@@ -43460,7 +43576,7 @@
       <c r="B990" s="6">
         <v>4</v>
       </c>
-      <c r="C990" s="22" t="s">
+      <c r="C990" s="7" t="s">
         <v>3545</v>
       </c>
       <c r="D990" s="7" t="s">
@@ -43487,7 +43603,7 @@
       <c r="B991" s="6">
         <v>5</v>
       </c>
-      <c r="C991" s="22" t="s">
+      <c r="C991" s="7" t="s">
         <v>3544</v>
       </c>
       <c r="D991" s="7" t="s">
@@ -43514,7 +43630,7 @@
       <c r="B992" s="6">
         <v>6</v>
       </c>
-      <c r="C992" s="22" t="s">
+      <c r="C992" s="7" t="s">
         <v>3539</v>
       </c>
       <c r="D992" s="7" t="s">
@@ -43541,7 +43657,7 @@
       <c r="B993" s="6">
         <v>7</v>
       </c>
-      <c r="C993" s="22" t="s">
+      <c r="C993" s="7" t="s">
         <v>3543</v>
       </c>
       <c r="D993" s="7" t="s">
@@ -43568,7 +43684,7 @@
       <c r="B994" s="6">
         <v>8</v>
       </c>
-      <c r="C994" s="22" t="s">
+      <c r="C994" s="7" t="s">
         <v>3542</v>
       </c>
       <c r="D994" s="7" t="s">
@@ -43595,7 +43711,7 @@
       <c r="B995" s="6">
         <v>9</v>
       </c>
-      <c r="C995" s="22" t="s">
+      <c r="C995" s="7" t="s">
         <v>3541</v>
       </c>
       <c r="D995" s="7" t="s">
@@ -43622,7 +43738,7 @@
       <c r="B996" s="6">
         <v>10</v>
       </c>
-      <c r="C996" s="22" t="s">
+      <c r="C996" s="7" t="s">
         <v>3540</v>
       </c>
       <c r="D996" s="7" t="s">
@@ -43649,7 +43765,7 @@
       <c r="B997" s="6">
         <v>1</v>
       </c>
-      <c r="C997" s="22" t="s">
+      <c r="C997" s="7" t="s">
         <v>3573</v>
       </c>
       <c r="D997" s="7" t="s">
@@ -43664,7 +43780,7 @@
       <c r="G997" s="12">
         <v>4.5</v>
       </c>
-      <c r="H997" s="24" t="s">
+      <c r="H997" s="23" t="s">
         <v>3593</v>
       </c>
       <c r="I997" s="6"/>
@@ -43676,7 +43792,7 @@
       <c r="B998" s="6">
         <v>2</v>
       </c>
-      <c r="C998" s="22" t="s">
+      <c r="C998" s="7" t="s">
         <v>3574</v>
       </c>
       <c r="D998" s="7" t="s">
@@ -43691,7 +43807,7 @@
       <c r="G998" s="12">
         <v>4.3</v>
       </c>
-      <c r="H998" s="24" t="s">
+      <c r="H998" s="23" t="s">
         <v>3594</v>
       </c>
       <c r="I998" s="6"/>
@@ -43703,7 +43819,7 @@
       <c r="B999" s="6">
         <v>3</v>
       </c>
-      <c r="C999" s="22" t="s">
+      <c r="C999" s="7" t="s">
         <v>3567</v>
       </c>
       <c r="D999" s="7" t="s">
@@ -43718,7 +43834,7 @@
       <c r="G999" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H999" s="24" t="s">
+      <c r="H999" s="23" t="s">
         <v>3597</v>
       </c>
       <c r="I999" s="6"/>
@@ -43730,7 +43846,7 @@
       <c r="B1000" s="6">
         <v>4</v>
       </c>
-      <c r="C1000" s="22" t="s">
+      <c r="C1000" s="7" t="s">
         <v>3575</v>
       </c>
       <c r="D1000" s="7" t="s">
@@ -43745,7 +43861,7 @@
       <c r="G1000" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1000" s="24" t="s">
+      <c r="H1000" s="23" t="s">
         <v>3598</v>
       </c>
       <c r="I1000" s="6"/>
@@ -43757,7 +43873,7 @@
       <c r="B1001" s="6">
         <v>5</v>
       </c>
-      <c r="C1001" s="22" t="s">
+      <c r="C1001" s="7" t="s">
         <v>3579</v>
       </c>
       <c r="D1001" s="7" t="s">
@@ -43772,7 +43888,7 @@
       <c r="G1001" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1001" s="24" t="s">
+      <c r="H1001" s="23" t="s">
         <v>3599</v>
       </c>
       <c r="I1001" s="6"/>
@@ -43784,7 +43900,7 @@
       <c r="B1002" s="6">
         <v>6</v>
       </c>
-      <c r="C1002" s="22" t="s">
+      <c r="C1002" s="7" t="s">
         <v>3580</v>
       </c>
       <c r="D1002" s="7" t="s">
@@ -43799,7 +43915,7 @@
       <c r="G1002" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1002" s="24" t="s">
+      <c r="H1002" s="23" t="s">
         <v>3595</v>
       </c>
       <c r="I1002" s="6"/>
@@ -43811,7 +43927,7 @@
       <c r="B1003" s="6">
         <v>7</v>
       </c>
-      <c r="C1003" s="22" t="s">
+      <c r="C1003" s="7" t="s">
         <v>3581</v>
       </c>
       <c r="D1003" s="7" t="s">
@@ -43826,7 +43942,7 @@
       <c r="G1003" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H1003" s="24" t="s">
+      <c r="H1003" s="23" t="s">
         <v>3600</v>
       </c>
       <c r="I1003" s="6"/>
@@ -43838,7 +43954,7 @@
       <c r="B1004" s="6">
         <v>8</v>
       </c>
-      <c r="C1004" s="22" t="s">
+      <c r="C1004" s="7" t="s">
         <v>3577</v>
       </c>
       <c r="D1004" s="7" t="s">
@@ -43853,7 +43969,7 @@
       <c r="G1004" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1004" s="24" t="s">
+      <c r="H1004" s="23" t="s">
         <v>3601</v>
       </c>
       <c r="I1004" s="6"/>
@@ -43865,7 +43981,7 @@
       <c r="B1005" s="6">
         <v>9</v>
       </c>
-      <c r="C1005" s="22" t="s">
+      <c r="C1005" s="7" t="s">
         <v>3578</v>
       </c>
       <c r="D1005" s="7" t="s">
@@ -43880,7 +43996,7 @@
       <c r="G1005" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1005" s="24" t="s">
+      <c r="H1005" s="23" t="s">
         <v>3596</v>
       </c>
       <c r="I1005" s="6"/>
@@ -43892,7 +44008,7 @@
       <c r="B1006" s="6">
         <v>10</v>
       </c>
-      <c r="C1006" s="22" t="s">
+      <c r="C1006" s="7" t="s">
         <v>3576</v>
       </c>
       <c r="D1006" s="7" t="s">
@@ -43907,7 +44023,7 @@
       <c r="G1006" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1006" s="24" t="s">
+      <c r="H1006" s="23" t="s">
         <v>3602</v>
       </c>
       <c r="I1006" s="6"/>
@@ -43919,7 +44035,7 @@
       <c r="B1007" s="6">
         <v>1</v>
       </c>
-      <c r="C1007" s="22" t="s">
+      <c r="C1007" s="7" t="s">
         <v>3607</v>
       </c>
       <c r="D1007" s="7" t="s">
@@ -43934,7 +44050,7 @@
       <c r="G1007" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1007" s="25" t="s">
+      <c r="H1007" s="24" t="s">
         <v>3632</v>
       </c>
       <c r="I1007" s="6"/>
@@ -43946,7 +44062,7 @@
       <c r="B1008" s="6">
         <v>2</v>
       </c>
-      <c r="C1008" s="22" t="s">
+      <c r="C1008" s="7" t="s">
         <v>3608</v>
       </c>
       <c r="D1008" s="7" t="s">
@@ -43961,7 +44077,7 @@
       <c r="G1008" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1008" s="25" t="s">
+      <c r="H1008" s="24" t="s">
         <v>3633</v>
       </c>
       <c r="I1008" s="6"/>
@@ -43973,7 +44089,7 @@
       <c r="B1009" s="6">
         <v>3</v>
       </c>
-      <c r="C1009" s="22" t="s">
+      <c r="C1009" s="7" t="s">
         <v>3609</v>
       </c>
       <c r="D1009" s="7" t="s">
@@ -43988,7 +44104,7 @@
       <c r="G1009" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1009" s="25" t="s">
+      <c r="H1009" s="24" t="s">
         <v>3634</v>
       </c>
       <c r="I1009" s="6"/>
@@ -44000,7 +44116,7 @@
       <c r="B1010" s="6">
         <v>4</v>
       </c>
-      <c r="C1010" s="22" t="s">
+      <c r="C1010" s="7" t="s">
         <v>3610</v>
       </c>
       <c r="D1010" s="7" t="s">
@@ -44015,7 +44131,7 @@
       <c r="G1010" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1010" s="25" t="s">
+      <c r="H1010" s="24" t="s">
         <v>3630</v>
       </c>
       <c r="I1010" s="6"/>
@@ -44027,7 +44143,7 @@
       <c r="B1011" s="6">
         <v>5</v>
       </c>
-      <c r="C1011" s="22" t="s">
+      <c r="C1011" s="7" t="s">
         <v>3611</v>
       </c>
       <c r="D1011" s="7" t="s">
@@ -44042,7 +44158,7 @@
       <c r="G1011" s="12">
         <v>4.2</v>
       </c>
-      <c r="H1011" s="25" t="s">
+      <c r="H1011" s="24" t="s">
         <v>3631</v>
       </c>
       <c r="I1011" s="6"/>
@@ -44054,7 +44170,7 @@
       <c r="B1012" s="6">
         <v>6</v>
       </c>
-      <c r="C1012" s="22" t="s">
+      <c r="C1012" s="7" t="s">
         <v>3616</v>
       </c>
       <c r="D1012" s="7" t="s">
@@ -44069,7 +44185,7 @@
       <c r="G1012" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1012" s="24" t="s">
+      <c r="H1012" s="23" t="s">
         <v>3638</v>
       </c>
       <c r="I1012" s="6"/>
@@ -44081,7 +44197,7 @@
       <c r="B1013" s="6">
         <v>7</v>
       </c>
-      <c r="C1013" s="22" t="s">
+      <c r="C1013" s="7" t="s">
         <v>3615</v>
       </c>
       <c r="D1013" s="7" t="s">
@@ -44096,7 +44212,7 @@
       <c r="G1013" s="12">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H1013" s="25" t="s">
+      <c r="H1013" s="24" t="s">
         <v>3639</v>
       </c>
       <c r="I1013" s="6"/>
@@ -44108,7 +44224,7 @@
       <c r="B1014" s="6">
         <v>8</v>
       </c>
-      <c r="C1014" s="22" t="s">
+      <c r="C1014" s="7" t="s">
         <v>3614</v>
       </c>
       <c r="D1014" s="7" t="s">
@@ -44123,7 +44239,7 @@
       <c r="G1014" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H1014" s="25" t="s">
+      <c r="H1014" s="24" t="s">
         <v>3635</v>
       </c>
       <c r="I1014" s="6"/>
@@ -44135,7 +44251,7 @@
       <c r="B1015" s="6">
         <v>9</v>
       </c>
-      <c r="C1015" s="22" t="s">
+      <c r="C1015" s="7" t="s">
         <v>3629</v>
       </c>
       <c r="D1015" s="7" t="s">
@@ -44150,7 +44266,7 @@
       <c r="G1015" s="12">
         <v>4.3</v>
       </c>
-      <c r="H1015" s="25" t="s">
+      <c r="H1015" s="24" t="s">
         <v>3636</v>
       </c>
       <c r="I1015" s="6"/>
@@ -44162,7 +44278,7 @@
       <c r="B1016" s="6">
         <v>10</v>
       </c>
-      <c r="C1016" s="22" t="s">
+      <c r="C1016" s="7" t="s">
         <v>3613</v>
       </c>
       <c r="D1016" s="7" t="s">
@@ -44177,7 +44293,7 @@
       <c r="G1016" s="12">
         <v>4.5</v>
       </c>
-      <c r="H1016" s="25" t="s">
+      <c r="H1016" s="24" t="s">
         <v>3640</v>
       </c>
       <c r="I1016" s="6"/>
@@ -44189,7 +44305,7 @@
       <c r="B1017" s="6">
         <v>11</v>
       </c>
-      <c r="C1017" s="22" t="s">
+      <c r="C1017" s="7" t="s">
         <v>3612</v>
       </c>
       <c r="D1017" s="7" t="s">
@@ -44204,7 +44320,7 @@
       <c r="G1017" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H1017" s="25" t="s">
+      <c r="H1017" s="24" t="s">
         <v>3637</v>
       </c>
       <c r="I1017" s="6"/>
@@ -44216,7 +44332,7 @@
       <c r="B1018" s="6">
         <v>1</v>
       </c>
-      <c r="C1018" s="22" t="s">
+      <c r="C1018" s="7" t="s">
         <v>3645</v>
       </c>
       <c r="D1018" s="7" t="s">
@@ -44245,7 +44361,7 @@
       <c r="B1019" s="6">
         <v>2</v>
       </c>
-      <c r="C1019" s="22" t="s">
+      <c r="C1019" s="7" t="s">
         <v>3646</v>
       </c>
       <c r="D1019" s="7" t="s">
@@ -44272,7 +44388,7 @@
       <c r="B1020" s="6">
         <v>3</v>
       </c>
-      <c r="C1020" s="22" t="s">
+      <c r="C1020" s="7" t="s">
         <v>3647</v>
       </c>
       <c r="D1020" s="7" t="s">
@@ -44299,7 +44415,7 @@
       <c r="B1021" s="6">
         <v>4</v>
       </c>
-      <c r="C1021" s="22" t="s">
+      <c r="C1021" s="7" t="s">
         <v>3648</v>
       </c>
       <c r="D1021" s="7" t="s">
@@ -44326,7 +44442,7 @@
       <c r="B1022" s="6">
         <v>5</v>
       </c>
-      <c r="C1022" s="22" t="s">
+      <c r="C1022" s="7" t="s">
         <v>3649</v>
       </c>
       <c r="D1022" s="7" t="s">
@@ -44353,7 +44469,7 @@
       <c r="B1023" s="6">
         <v>6</v>
       </c>
-      <c r="C1023" s="22" t="s">
+      <c r="C1023" s="7" t="s">
         <v>3654</v>
       </c>
       <c r="D1023" s="7" t="s">
@@ -44380,7 +44496,7 @@
       <c r="B1024" s="6">
         <v>7</v>
       </c>
-      <c r="C1024" s="22" t="s">
+      <c r="C1024" s="7" t="s">
         <v>3653</v>
       </c>
       <c r="D1024" s="7" t="s">
@@ -44407,7 +44523,7 @@
       <c r="B1025" s="6">
         <v>8</v>
       </c>
-      <c r="C1025" s="22" t="s">
+      <c r="C1025" s="7" t="s">
         <v>3652</v>
       </c>
       <c r="D1025" s="7" t="s">
@@ -44434,7 +44550,7 @@
       <c r="B1026" s="6">
         <v>9</v>
       </c>
-      <c r="C1026" s="22" t="s">
+      <c r="C1026" s="7" t="s">
         <v>3651</v>
       </c>
       <c r="D1026" s="7" t="s">
@@ -44461,7 +44577,7 @@
       <c r="B1027" s="6">
         <v>10</v>
       </c>
-      <c r="C1027" s="22" t="s">
+      <c r="C1027" s="7" t="s">
         <v>3650</v>
       </c>
       <c r="D1027" s="7" t="s">
@@ -44488,7 +44604,7 @@
       <c r="B1028" s="6">
         <v>1</v>
       </c>
-      <c r="C1028" s="22" t="s">
+      <c r="C1028" s="7" t="s">
         <v>3686</v>
       </c>
       <c r="D1028" s="7" t="s">
@@ -44503,7 +44619,7 @@
       <c r="G1028" s="12">
         <v>4.8</v>
       </c>
-      <c r="H1028" s="23" t="s">
+      <c r="H1028" s="22" t="s">
         <v>3704</v>
       </c>
       <c r="I1028" s="6" t="s">
@@ -44517,7 +44633,7 @@
       <c r="B1029" s="6">
         <v>2</v>
       </c>
-      <c r="C1029" s="22" t="s">
+      <c r="C1029" s="7" t="s">
         <v>3687</v>
       </c>
       <c r="D1029" s="7" t="s">
@@ -44544,7 +44660,7 @@
       <c r="B1030" s="6">
         <v>3</v>
       </c>
-      <c r="C1030" s="22" t="s">
+      <c r="C1030" s="7" t="s">
         <v>3691</v>
       </c>
       <c r="D1030" s="7" t="s">
@@ -44571,7 +44687,7 @@
       <c r="B1031" s="6">
         <v>4</v>
       </c>
-      <c r="C1031" s="22" t="s">
+      <c r="C1031" s="7" t="s">
         <v>3689</v>
       </c>
       <c r="D1031" s="7" t="s">
@@ -44598,7 +44714,7 @@
       <c r="B1032" s="6">
         <v>5</v>
       </c>
-      <c r="C1032" s="22" t="s">
+      <c r="C1032" s="7" t="s">
         <v>3690</v>
       </c>
       <c r="D1032" s="7" t="s">
@@ -44625,7 +44741,7 @@
       <c r="B1033" s="6">
         <v>6</v>
       </c>
-      <c r="C1033" s="22" t="s">
+      <c r="C1033" s="7" t="s">
         <v>3688</v>
       </c>
       <c r="D1033" s="7" t="s">
@@ -44640,7 +44756,7 @@
       <c r="G1033" s="12">
         <v>4.7</v>
       </c>
-      <c r="H1033" s="23" t="s">
+      <c r="H1033" s="22" t="s">
         <v>3703</v>
       </c>
       <c r="I1033" s="6"/>
@@ -44652,7 +44768,7 @@
       <c r="B1034" s="6">
         <v>7</v>
       </c>
-      <c r="C1034" s="22" t="s">
+      <c r="C1034" s="7" t="s">
         <v>3685</v>
       </c>
       <c r="D1034" s="7" t="s">
@@ -44679,7 +44795,7 @@
       <c r="B1035" s="6">
         <v>8</v>
       </c>
-      <c r="C1035" s="22" t="s">
+      <c r="C1035" s="7" t="s">
         <v>3684</v>
       </c>
       <c r="D1035" s="7" t="s">
@@ -44706,7 +44822,7 @@
       <c r="B1036" s="6">
         <v>9</v>
       </c>
-      <c r="C1036" s="22" t="s">
+      <c r="C1036" s="7" t="s">
         <v>3678</v>
       </c>
       <c r="D1036" s="7" t="s">
@@ -44727,6 +44843,222 @@
       <c r="I1036" s="6" t="s">
         <v>240</v>
       </c>
+    </row>
+    <row r="1037" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1037" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1037" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1037" s="7" t="s">
+        <v>3715</v>
+      </c>
+      <c r="D1037" s="7" t="s">
+        <v>3724</v>
+      </c>
+      <c r="E1037" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F1037" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G1037" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H1037" s="9" t="s">
+        <v>3735</v>
+      </c>
+      <c r="I1037" s="6"/>
+    </row>
+    <row r="1038" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1038" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1038" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1038" s="7" t="s">
+        <v>3716</v>
+      </c>
+      <c r="D1038" s="7" t="s">
+        <v>3725</v>
+      </c>
+      <c r="E1038" s="20">
+        <v>3.69</v>
+      </c>
+      <c r="F1038" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1038" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1038" s="9" t="s">
+        <v>3732</v>
+      </c>
+      <c r="I1038" s="6"/>
+    </row>
+    <row r="1039" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1039" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1039" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1039" s="7" t="s">
+        <v>3717</v>
+      </c>
+      <c r="D1039" s="7" t="s">
+        <v>3726</v>
+      </c>
+      <c r="E1039" s="20">
+        <v>3.17</v>
+      </c>
+      <c r="F1039" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G1039" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1039" s="9" t="s">
+        <v>3736</v>
+      </c>
+      <c r="I1039" s="6"/>
+    </row>
+    <row r="1040" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1040" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1040" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1040" s="7" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1040" s="7" t="s">
+        <v>3727</v>
+      </c>
+      <c r="E1040" s="20">
+        <v>3.37</v>
+      </c>
+      <c r="F1040" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1040" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1040" s="9" t="s">
+        <v>3733</v>
+      </c>
+      <c r="I1040" s="6"/>
+    </row>
+    <row r="1041" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1041" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1041" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1041" s="7" t="s">
+        <v>3722</v>
+      </c>
+      <c r="D1041" s="7" t="s">
+        <v>3728</v>
+      </c>
+      <c r="E1041" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F1041" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1041" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1041" s="9" t="s">
+        <v>3737</v>
+      </c>
+      <c r="I1041" s="6"/>
+    </row>
+    <row r="1042" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1042" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1042" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1042" s="7" t="s">
+        <v>3721</v>
+      </c>
+      <c r="D1042" s="7" t="s">
+        <v>3729</v>
+      </c>
+      <c r="E1042" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F1042" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1042" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1042" s="9" t="s">
+        <v>3734</v>
+      </c>
+      <c r="I1042" s="6"/>
+    </row>
+    <row r="1043" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1043" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1043" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1043" s="7" t="s">
+        <v>3720</v>
+      </c>
+      <c r="D1043" s="7" t="s">
+        <v>3730</v>
+      </c>
+      <c r="E1043" s="20">
+        <v>3.13</v>
+      </c>
+      <c r="F1043" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G1043" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1043" s="9" t="s">
+        <v>3738</v>
+      </c>
+      <c r="I1043" s="6"/>
+    </row>
+    <row r="1044" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1044" s="6">
+        <v>6431834</v>
+      </c>
+      <c r="B1044" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1044" s="7" t="s">
+        <v>3719</v>
+      </c>
+      <c r="D1044" s="7" t="s">
+        <v>3731</v>
+      </c>
+      <c r="E1044" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F1044" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1044" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1044" s="9" t="s">
+        <v>3739</v>
+      </c>
+      <c r="I1044" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B674A17-363C-4710-81CE-CA2DFCF0CBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6896533F-281C-4ACB-B536-D12C1D2C8C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="3740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="3773">
   <si>
     <t>No</t>
   </si>
@@ -12385,6 +12385,156 @@
   </si>
   <si>
     <t>Το πιο εκτεταμένο και θεατρικό κλείσιμο. Η “militia guard” παραπέμπει σε ένοπλη επιτήρηση, φόβο και εξουσία, και η σύνθεση χρησιμοποιεί αυτό το υλικό για να χτίσει πιο επικό proto-metal τραγούδι. Οι κιθάρες αναπτύσσουν μοτίβα με μεγαλύτερη υπομονή, η φωνή του Biff αποκτά πιο δραματικό χαρακτήρα και η μπάντα συνδέει το prog υπόβαθρο της A πλευράς με την καθαρότερη metal δύναμη της B. Δεν είναι τέλειο , η παραγωγή παραμένει σχετικά αδύναμη , αλλά ως finale λειτουργεί, αφήνει την υπόσχεση ότι οι Saxon μπορούν να γράψουν μεγαλύτερες, πιο φιλόδοξες heavy συνθέσεις. Πηγές το συνδέουν με Queen-like δραματικότητα και το αναφέρουν μαζί με το “Frozen Rainbow” ως prog-flavoured epic που πλαισιώνει το album.</t>
+  </si>
+  <si>
+    <t>Rock The Nations</t>
+  </si>
+  <si>
+    <t>EMI – 062-2406231 (Greece, 1986, LP, Album). Pressed at Columbia, Athens (EMIAL S.A.) με αύξοντα αριθμό μήτρας MT 13358 και A/A 13358.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** ο Rock The Nations είναι το όγδοο studio album των Saxon, κυκλοφόρησε το 1986 και ηχογραφήθηκε στα Wisseloord Studios στην Ολλανδία με παραγωγό τον Gary Lyons. Αποτελεί μια καθοριστική στροφή του σχήματος προς πιο εμπορικά, arena-rock και melodic metal μονοπάτια, αξιοποιώντας έντονα τα πλήκτρα και διαθέτοντας μάλιστα τη συμμετοχή του Elton John στο πιάνο στα κομμάτια "Party Til You Puke" και "Northern Lady". Η ελληνική έκδοση ξεχωρίζει για τα ελληνικά γράμματα (ελληνική ονοματοδοσία) στο οπισθόφυλλο και τις ετικέτες ("Ροκ Δε Νέισονς"). Made and printed in Greece by EMI.</t>
+  </si>
+  <si>
+    <t>Rock The Nations (Ροκ Δε Νέϊσονς)</t>
+  </si>
+  <si>
+    <t>Battle Cry (Μπαττλ Κράϊ)</t>
+  </si>
+  <si>
+    <t>Waiting For The Night (Γουέϊτινγκ Φορ Δε Νάϊτ)</t>
+  </si>
+  <si>
+    <t>We Came Here To Rock (Γουή Κέϊμ Χήαρ Του Ροκ)</t>
+  </si>
+  <si>
+    <t>You Ain’t No Angel (Γιου Έϊν'τ Νο Έϊντζελ)</t>
+  </si>
+  <si>
+    <t>Running Hot (Ράννινγκ Χοτ)</t>
+  </si>
+  <si>
+    <t>Empty Promises (Έμπτυ Πρόμισις)</t>
+  </si>
+  <si>
+    <t>Party ’Til You Puke [Piano – Elton John] (Πάρτυ Τιλ Γιου Πιούκ)</t>
+  </si>
+  <si>
+    <t>Northern Lady [Piano – Elton John] (Νόρθερν Λέϊντυ)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/5815845-Saxon-%CE%A3%CE%AC%CE%BE%CE%BF%CE%BD-Rock-The-Nations-%CE%A1%CE%BF%CE%BA-%CE%94%CE%B5-%CE%9D%CE%AD%CF%8A%CF%83%CE%BF%CE%BD%CF%82</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/DQ6Y_nhzYP4qmy8boc7KzsNia9qLHpdM9yAO_vb2jZc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTU4MTU4/NDUtMTQwMzQ2MzQ0/OC0xODEzLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [NWOBHM roots, Glam Metal influence, Pop Metal, Melodic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Metal Anthem, Traditional Heavy Metal, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Heavy Metal, War Metal, Dramatic Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Metal [Melodic Hard Rock, Radio Metal, AOR-adjacent]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Rock ’n’ Roll Anthem, Arena Hard Rock, Party Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Dark Melodic Metal, Glam-Metal edge, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fast Hard Rock, Driving Metal, Road Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Party Rock, Pop Metal, Boogie Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Melodic Rock, AOR, Power-Ballad edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Melodic Hard Rock, Piano Rock, AOR Ballad]</t>
+  </si>
+  <si>
+    <t>Γρήγορο, driving hard-rock τραγούδι που επιστρέφει σε road-metal θεματολογία. Η εικόνα του να «τρέχεις καυτός» δηλώνει ταχύτητα, ένταση και άρνηση να πατήσεις φρένο. Το riff είναι αρκετά δυνατό, η μπάντα παίζει με σωστή εμπειρία και ο Byford διατηρεί το πιο τραχύ του delivery. Παρ’ όλα αυτά, το track μοιάζει περισσότερο με λειτουργικό filler παρά με τραγούδι που θα μπορούσε να σταθεί δίπλα στα κλασικά τους. Η διάρκεια του και το straight-ahead drive βοηθούν να κινηθεί η B πλευρά, αλλά δεν αφήνει πολύ ισχυρή προσωπική ταυτότητα.</t>
+  </si>
+  <si>
+    <t>Το χαμηλότερο σημείο του δίσκου. Η party-rock ιδέα είναι σκόπιμα υπερβολική , διασκέδαση μέχρι εμετού , αλλά δεν μετατρέπεται σε πειστική ή ιδιαίτερα ευρηματική rock σύνθεση. Η μπάντα φαίνεται να ακολουθεί το glamour/party-metal κλίμα της εποχής, με απλό boogie riff και στίχους που μοιάζουν πιο επιφανειακοί από τη συνηθισμένη Saxon εικόνα. Δεν είναι ότι ένα heavy-metal album δεν μπορεί να έχει χιούμορ ή fun· οι Saxon το έκαναν συχνά. Εδώ, όμως, το τραγούδι δεν έχει ούτε την αμεσότητα του “Play It Loud” ούτε την επιθετικότητα του “Party Till You Puke” που θα απαιτούσε ο τίτλος. Οι αρνητικές αναδρομικές κριτικές το αναφέρουν συχνά ως ένδειξη της δημιουργικής πτώσης του album.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Το album κλείνει με το πιο ασυνήθιστο και πιο μελωδικό track του, μια rock ballad με πιάνο από τον </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Elton John</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">, ο οποίος δεν πιστώνεται στο αρχικό sleeve λόγω συμβατικών περιορισμών. Η “Northern Lady” είναι αφιέρωση σε μια γυναικεία φιγούρα του Βορρά, νοσταλγική, ρομαντική και πιο προσωπική από τα community anthems του δίσκου. Το πιάνο προσθέτει υφή που δεν συναντάς συνήθως στους Saxon και δίνει στο track πιο AOR/pop-rock χαρακτήρα. Δεν είναι κακή επιλογή κλεισίματος, έχει αξιοπρέπεια, μελωδία και διαφορετικό χρώμα. Ωστόσο, ως finale για ένα album που λέγεται </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Rock The Nations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, αφήνει πιο ήπια και λιγότερο θριαμβευτική εντύπωση από ό,τι θα περίμενε κανείς. Η συμμετοχή του Elton John αποτελεί επιβεβαιωμένο και κεντρικό στοιχείο των πηγών για το album.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τον δίσκο με την αναμενόμενη Saxon συνταγή, εθνική/διεθνής metal ενότητα, μεγάλα drums, κιθάρες που κινούνται με σταθερό mid-tempo βάρος και chorus σχεδιασμένο για κοινό. Το “rock the nations” δεν είναι απλώς δήλωση εμπορικής εξάπλωσης· μέσα στην παραδοσιακή metal γλώσσα των Saxon είναι κάλεσμα για μια διεθνή κοινότητα που ενώνεται μέσα από τη μουσική. Η σύνθεση είναι επαγγελματική και αρκετά δυνατή ως opener, αλλά δεν διαθέτει το ξεχωριστό riff ή τη φρεσκάδα που είχαν τα “Denim And Leather” και “Power And The Glory”. Ακούγεται σαν μια μπάντα που γνωρίζει τέλεια το formula της, χωρίς να το ανανεώνει αποφασιστικά.</t>
+  </si>
+  <si>
+    <t>Η πιο δυνατή και πιο καθαρά heavy-metal στιγμή της A πλευράς. Ο τίτλος καλεί σε μάχη, αλλά η μουσική αποφεύγει τη σκέτη speed-metal επιθετικότητα, χτίζει δραματικά με mid-tempo riffing, πολεμικό refrain και αίσθηση επικείμενης σύγκρουσης. Ο Biff Byford τραγουδά με την απαραίτητη αυστηρότητα, ενώ οι κιθάρες των Paul Quinn και Graham Oliver προσφέρουν αρκετό βάρος ώστε το track να μη χαθεί μέσα στον πιο pop-metal χαρακτήρα του δίσκου. Είναι το κομμάτι που φέρνει πιο κοντά το Rock The Nations στην παλιότερη, αξιόπιστη Saxon ταυτότητα , απλό, αλλά στιβαρό traditional heavy metal.</t>
+  </si>
+  <si>
+    <t>Το πρώτο εμφανές βήμα προς πιο μελωδική και ραδιοφωνική κατεύθυνση. Η νύχτα γίνεται σύμβολο προσμονής, επιθυμίας και υπόσχεσης για κάτι που θα συμβεί όταν αλλάξει η καθημερινή πραγματικότητα. Η μουσική έχει πιο καθαρό AOR/melodic hard-rock chorus, με λιγότερο σκληρό riffing και μεγαλύτερη έμφαση στην ευκολία της μελωδίας. Δεν είναι κακό τραγούδι , αρκετές κριτικές το ξεχωρίζουν ως ένα από τα καλύτερα του δίσκου , αλλά η θέση του αποκαλύπτει τη στρατηγική αλλαγή, οι Saxon προσπαθούν να παραμείνουν metal ενώ χρησιμοποιούν πιο commercial hooks.</t>
+  </si>
+  <si>
+    <t>Αυτοαναφορικό hard-rock anthem, η μπάντα και το κοινό ήρθαν για έναν λόγο, να παίξουν και να ακούσουν rock. Η θεματική είναι εξαιρετικά γνώριμη στη δισκογραφία των Saxon, όμως το τραγούδι έχει ενέργεια, καθαρή ρυθμική βάση και chorus που δουλεύει σε live πλαίσιο. Είναι πιο party-oriented από το “Battle Cry”, αλλά πιο πειστικό από το “Party ’Til You Puke” επειδή δεν προσπαθεί υπερβολικά να αντιγράψει τη mid-’80s glam-metal ευκολία. Μοιάζει με τραγούδι που θα μπορούσε να σταθεί σε συναυλία, έστω και αν δεν φτάνει το status των κλασικών community anthems τους. Η κριτική του Lightning’s Limbo το αναφέρει μαζί με το “Waiting For The Night” ως ένα από τα βασικά «no-nonsense» τραγούδια της πρώτης πλευράς.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ξεκινά σε πιο σκοτεινό melodic hard-rock πεδίο. Ο τίτλος υπονοεί ότι μια ερωτική ή συμβολική φιγούρα δεν είναι τόσο αγνή όσο φαίνεται, και το τραγούδι αξιοποιεί αυτή την αμφισημία με βαρύτερο ρυθμό και πιο μελωδικό refrain. Η σύνθεση έχει glam-metal άκρη, όχι ως εικόνα αλλά ως κατασκευή, polished κιθάρες, ήπια radio-friendly φωνητικά και δομή που αναζητά hook. Έχει ένα καλό σκοτεινό χρώμα, αλλά δεν αναπτύσσει αρκετά την ιδέα του ώστε να γίνει standout. Είναι αξιοπρεπές mid-album cut και όχι κάτι που ορίζει τον δίσκο.</t>
+  </si>
+  <si>
+    <t>Πιο ήρεμο και μελωδικό, με θέμα τη διάψευση προσδοκιών και τις υποσχέσεις που δεν τηρήθηκαν. Εδώ η μπάντα αφήνει περισσότερο χώρο στο melodic hard rock και στις AOR κινήσεις, με το chorus να προσπαθεί να μεταφέρει απογοήτευση χωρίς να μετατρέπεται σε βαριά power ballad. Ο τίτλος έχει μεγαλύτερη συναισθηματική δυνατότητα από το τελικό αποτέλεσμα, η ερμηνεία και οι κιθάρες είναι καλές, αλλά η σύνθεση ακολουθεί αρκετά προβλέψιμη late-’80s radio-rock διαδρομή. Λειτουργεί ως άκουσμα, όχι όμως ως εντυπωσιακή έκφραση του θέματος. Η RYM σημειώνει ακριβώς την radio-friendly pop-metal κατεύθυνση του “Empty Promises”.</t>
   </si>
 </sst>
 </file>
@@ -12931,7 +13081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16463,6 +16613,38 @@
       </c>
       <c r="J110" s="11" t="s">
         <v>3712</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>3740</v>
+      </c>
+      <c r="D111" s="6">
+        <v>1986</v>
+      </c>
+      <c r="E111" s="10">
+        <v>2.82</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>3754</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>3742</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>3741</v>
+      </c>
+      <c r="I111" s="11" t="s">
+        <v>3752</v>
+      </c>
+      <c r="J111" s="11" t="s">
+        <v>3753</v>
       </c>
     </row>
   </sheetData>
@@ -16682,6 +16864,8 @@
     <hyperlink ref="J109" r:id="rId213" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
     <hyperlink ref="I110" r:id="rId214" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
     <hyperlink ref="J110" r:id="rId215" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
+    <hyperlink ref="I111" r:id="rId216" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
+    <hyperlink ref="J111" r:id="rId217" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16689,7 +16873,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1044"/>
+  <dimension ref="A1:I1053"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -44869,7 +45053,9 @@
       <c r="H1037" s="9" t="s">
         <v>3735</v>
       </c>
-      <c r="I1037" s="6"/>
+      <c r="I1037" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="1038" spans="1:9" ht="84" x14ac:dyDescent="0.25">
       <c r="A1038" s="6">
@@ -45059,6 +45245,249 @@
         <v>3739</v>
       </c>
       <c r="I1044" s="6"/>
+    </row>
+    <row r="1045" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1045" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1045" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1045" s="7" t="s">
+        <v>3743</v>
+      </c>
+      <c r="D1045" s="7" t="s">
+        <v>3755</v>
+      </c>
+      <c r="E1045" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="F1045" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1045" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1045" s="9" t="s">
+        <v>3767</v>
+      </c>
+      <c r="I1045" s="6"/>
+    </row>
+    <row r="1046" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1046" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1046" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1046" s="7" t="s">
+        <v>3744</v>
+      </c>
+      <c r="D1046" s="7" t="s">
+        <v>3756</v>
+      </c>
+      <c r="E1046" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F1046" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1046" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H1046" s="9" t="s">
+        <v>3768</v>
+      </c>
+      <c r="I1046" s="6"/>
+    </row>
+    <row r="1047" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1047" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1047" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1047" s="7" t="s">
+        <v>3745</v>
+      </c>
+      <c r="D1047" s="7" t="s">
+        <v>3757</v>
+      </c>
+      <c r="E1047" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F1047" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1047" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1047" s="9" t="s">
+        <v>3769</v>
+      </c>
+      <c r="I1047" s="6"/>
+    </row>
+    <row r="1048" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1048" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1048" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1048" s="7" t="s">
+        <v>3746</v>
+      </c>
+      <c r="D1048" s="7" t="s">
+        <v>3758</v>
+      </c>
+      <c r="E1048" s="20">
+        <v>3.29</v>
+      </c>
+      <c r="F1048" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1048" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H1048" s="9" t="s">
+        <v>3770</v>
+      </c>
+      <c r="I1048" s="6"/>
+    </row>
+    <row r="1049" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1049" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1049" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1049" s="7" t="s">
+        <v>3747</v>
+      </c>
+      <c r="D1049" s="7" t="s">
+        <v>3759</v>
+      </c>
+      <c r="E1049" s="20">
+        <v>2.94</v>
+      </c>
+      <c r="F1049" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1049" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="H1049" s="9" t="s">
+        <v>3771</v>
+      </c>
+      <c r="I1049" s="6"/>
+    </row>
+    <row r="1050" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1050" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1050" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1050" s="7" t="s">
+        <v>3748</v>
+      </c>
+      <c r="D1050" s="7" t="s">
+        <v>3760</v>
+      </c>
+      <c r="E1050" s="20">
+        <v>3.14</v>
+      </c>
+      <c r="F1050" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G1050" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="H1050" s="9" t="s">
+        <v>3764</v>
+      </c>
+      <c r="I1050" s="6"/>
+    </row>
+    <row r="1051" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1051" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1051" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1051" s="7" t="s">
+        <v>3750</v>
+      </c>
+      <c r="D1051" s="7" t="s">
+        <v>3761</v>
+      </c>
+      <c r="E1051" s="20">
+        <v>2.72</v>
+      </c>
+      <c r="F1051" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="G1051" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H1051" s="9" t="s">
+        <v>3765</v>
+      </c>
+      <c r="I1051" s="6"/>
+    </row>
+    <row r="1052" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1052" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1052" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1052" s="7" t="s">
+        <v>3749</v>
+      </c>
+      <c r="D1052" s="7" t="s">
+        <v>3762</v>
+      </c>
+      <c r="E1052" s="20">
+        <v>3.11</v>
+      </c>
+      <c r="F1052" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G1052" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="H1052" s="9" t="s">
+        <v>3772</v>
+      </c>
+      <c r="I1052" s="6"/>
+    </row>
+    <row r="1053" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1053" s="6">
+        <v>5815845</v>
+      </c>
+      <c r="B1053" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1053" s="7" t="s">
+        <v>3751</v>
+      </c>
+      <c r="D1053" s="7" t="s">
+        <v>3763</v>
+      </c>
+      <c r="E1053" s="20">
+        <v>3.04</v>
+      </c>
+      <c r="F1053" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1053" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1053" s="22" t="s">
+        <v>3766</v>
+      </c>
+      <c r="I1053" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6896533F-281C-4ACB-B536-D12C1D2C8C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAE4FB0-062B-4F1A-9887-644B8B38DDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="3773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4119" uniqueCount="3809">
   <si>
     <t>No</t>
   </si>
@@ -12393,9 +12393,6 @@
     <t>EMI – 062-2406231 (Greece, 1986, LP, Album). Pressed at Columbia, Athens (EMIAL S.A.) με αύξοντα αριθμό μήτρας MT 13358 και A/A 13358.</t>
   </si>
   <si>
-    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** ο Rock The Nations είναι το όγδοο studio album των Saxon, κυκλοφόρησε το 1986 και ηχογραφήθηκε στα Wisseloord Studios στην Ολλανδία με παραγωγό τον Gary Lyons. Αποτελεί μια καθοριστική στροφή του σχήματος προς πιο εμπορικά, arena-rock και melodic metal μονοπάτια, αξιοποιώντας έντονα τα πλήκτρα και διαθέτοντας μάλιστα τη συμμετοχή του Elton John στο πιάνο στα κομμάτια "Party Til You Puke" και "Northern Lady". Η ελληνική έκδοση ξεχωρίζει για τα ελληνικά γράμματα (ελληνική ονοματοδοσία) στο οπισθόφυλλο και τις ετικέτες ("Ροκ Δε Νέισονς"). Made and printed in Greece by EMI.</t>
-  </si>
-  <si>
     <t>Rock The Nations (Ροκ Δε Νέϊσονς)</t>
   </si>
   <si>
@@ -12535,6 +12532,117 @@
   </si>
   <si>
     <t>Πιο ήρεμο και μελωδικό, με θέμα τη διάψευση προσδοκιών και τις υποσχέσεις που δεν τηρήθηκαν. Εδώ η μπάντα αφήνει περισσότερο χώρο στο melodic hard rock και στις AOR κινήσεις, με το chorus να προσπαθεί να μεταφέρει απογοήτευση χωρίς να μετατρέπεται σε βαριά power ballad. Ο τίτλος έχει μεγαλύτερη συναισθηματική δυνατότητα από το τελικό αποτέλεσμα, η ερμηνεία και οι κιθάρες είναι καλές, αλλά η σύνθεση ακολουθεί αρκετά προβλέψιμη late-’80s radio-rock διαδρομή. Λειτουργεί ως άκουσμα, όχι όμως ως εντυπωσιακή έκφραση του θέματος. Η RYM σημειώνει ακριβώς την radio-friendly pop-metal κατεύθυνση του “Empty Promises”.</t>
+  </si>
+  <si>
+    <t>Night Songs</t>
+  </si>
+  <si>
+    <t>Shake Me</t>
+  </si>
+  <si>
+    <t>Back Home Again</t>
+  </si>
+  <si>
+    <t>Push, Push</t>
+  </si>
+  <si>
+    <t>In From The Outside</t>
+  </si>
+  <si>
+    <t>Nobody’s Fool</t>
+  </si>
+  <si>
+    <t>Nothin’ For Nothin’</t>
+  </si>
+  <si>
+    <t>Once Around The Ride</t>
+  </si>
+  <si>
+    <t>Hell On Wheels</t>
+  </si>
+  <si>
+    <t>Somebody Save Me</t>
+  </si>
+  <si>
+    <t>Mercury – 830 076-1, Mercury – 830076-1 (Greece, 1986, LP, Album, Mispress). Manufactured by G.P.I. S.A. και printed by Δ. Πιτσιλός.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2460844-Cinderella-Night-Songs</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/OM39jRa-oaPSntscLBNzVKo5X99vQLCTZ-o60le3v44/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI0NjA4/NDQtMTQwNTg2OTA0/MC02MDEyLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Rock The Nations είναι το όγδοο studio album των Saxon, κυκλοφόρησε το 1986 και ηχογραφήθηκε στα Wisseloord Studios στην Ολλανδία με παραγωγό τον Gary Lyons. Αποτελεί μια καθοριστική στροφή του σχήματος προς πιο εμπορικά, arena-rock και melodic metal μονοπάτια, αξιοποιώντας έντονα τα πλήκτρα και διαθέτοντας μάλιστα τη συμμετοχή του Elton John στο πιάνο στα κομμάτια "Party Til You Puke" και "Northern Lady". Η ελληνική έκδοση ξεχωρίζει για τα ελληνικά γράμματα (ελληνική ονοματοδοσία) στο οπισθόφυλλο και τις ετικέτες ("Ροκ Δε Νέισονς"). Made and printed in Greece by EMI.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Night Songs είναι το ντεμπούτο album των Cinderella, κυκλοφόρησε το 1986 από τη Mercury και έφτασε μέχρι το Νο. 3 του US Billboard 200, γινόμενο τρεις φορές πλατινένιο. Η παραγωγή έγινε από τον θρυλικό Andy Johns (Led Zeppelin, Rolling Stones), χαρίζοντας στον δίσκο έναν τεράστιο, γυαλισμένο αλλά ταυτόχρονα αληθινό hard rock/glam metal ήχο. Στις ηχογραφήσεις συμμετείχαν κορυφαίοι μουσικοί, όπως ο Jon Bon Jovi στα backing vocals (στα "Nothin' For Nothin'" και "In From The Outside") και ο Jeff Paris στα πλήκτρα. Η συγκεκριμένη ελληνική κοπή αποτελεί χαρακτηριστικό mispress (όπως αναφέρεται και στα notes της έκδοσης), καθώς η πλευρά 1 περιέχει (και εμφανίζει στην ετικέτα) τα τραγούδια της πλευράς 2 και το αντίστροφο.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Hair Metal, Bluesy Hard Rock, Sleaze Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Cinderella</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Dark Glam Metal, Sleaze Rock, Heavy Album Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Hair-Metal Anthem, Bluesy Hard Rock, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Blues-Rock Ballad, Melodic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Rock, Bluesy Riff Rock, Party Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Dark Hard Rock, Dramatic Glam Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Fast Sleaze Rock, Boogie Metal, Road Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Arena Rock, Melodic Hard Rock, Party Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Bluesy Heavy Rock, Street Rock, Dark Glam Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Rock, Boogie Hard Rock, Sexualized Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Southern-tinged Hard Rock, Album Closer, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Η μεγάλη power ballad και το πιο διαχρονικό melodic τραγούδι του δίσκου. Ο αφηγητής αρνείται να παραμείνει «ο ανόητος» μιας σχέσης που τον υποτιμά ή τον χειραγωγεί. Η σύνθεση ξεκινά πιο συγκρατημένα και αναπτύσσεται σε μεγάλο hard-rock refrain, με την κιθάρα να λειτουργεί ως συναισθηματικό αντίβαρο στη φωνητική ερμηνεία. Ο Keifer δεν τραγουδά με το καθαρό, γυαλισμένο ύφος ενός AOR τραγουδιστή· η βραχνή φωνή του δίνει στο κομμάτι αληθινή πληγή και blues-rock βάρος. Αυτή η ισορροπία ανάμεσα σε ευάλωτη μπαλάντα και δυνατή rock κορύφωση εξηγεί γιατί το τραγούδι έγινε η πρώτη μεγάλη επιτυχία τους.</t>
+  </si>
+  <si>
+    <t>Η πιο απλή και πιο στερεοτυπική party/sleaze-rock στιγμή του δίσκου. Ο τίτλος είναι σκόπιμα διφορούμενος και το τραγούδι στηρίζεται σε boogie groove, μικρά κιθαριστικά hooks και φωνητικά με sex-and-party attitude. Η μπάντα το παίζει με ενέργεια, αλλά το lyric concept και η δομή είναι πιο προβλέψιμα από τις δυνατές στιγμές του album. Λειτουργεί μέσα στο ύφος του 1986, όπου τέτοια κομμάτια ήταν σχεδόν υποχρεωτικά για glam-metal LPs, αλλά δεν προσθέτει κάτι ουσιαστικό στην ταυτότητα των Cinderella.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στο πιο απλό, riff-driven sleaze rock. Ο τίτλος δηλώνει ότι τίποτα δεν δίνεται δωρεάν , μια μάλλον κυνική, street-level στάση που ταιριάζει με το bluesy hard-rock πλαίσιο της μπάντας. Η σύνθεση έχει ενέργεια, boogie κίνηση και αρκετό attitude, αλλά δεν αναπτύσσει την προσωπικότητα των προηγούμενων τραγουδιών. Είναι ένα λειτουργικό album cut, χρήσιμο για να απομακρύνει τον δίσκο από τη μπαλάντα και να επαναφέρει την ένταση, όμως δεν έχει ιδιαίτερα ισχυρό refrain ή αφηγηματικό βάρος.</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και πιο δραματικό, με τίτλο που παραπέμπει σε μια μοναδική διαδρομή , πιθανώς μια ερωτική ή επικίνδυνη εμπειρία από την οποία δεν βγαίνεις αλώβητος. Η μπάντα επιλέγει πιο βαριά κιθάρα και λιγότερη party διάθεση, ενώ ο Keifer δίνει στην ερμηνεία μια αίσθηση έντασης που ταιριάζει με την ιδέα της «βόλτας» ως ρίσκου. Δεν είναι από τα πιο γνωστά tracks, αλλά έχει περισσότερο χαρακτήρα από αρκετά hair-metal filler της εποχής. Ως κλείσιμο της A πλευράς, κρατά το album σε πιο βαριά και σκοτεινή τροχιά αντί να το αφήνει να καταλήξει σε απλή glam-rock διασκέδαση.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο υποτιμημένα τραγούδια του album. Ο τίτλος μιλά για την εμπειρία του outsider , κάποιου που παρατηρεί ή προσπαθεί να εισέλθει σε έναν κόσμο που τον κρατά απ’ έξω. Η μουσική έχει πιο bluesy και βαριά χροιά, με riffing που φέρνει τη μπάντα πιο κοντά σε traditional hard rock παρά σε bubblegum glam. Ο Keifer τραγουδά με περισσότερη ένταση και λιγότερη ερωτική πόζα, ενώ το arrangement δίνει χώρο για μια πιο σκοτεινή αίσθηση. Δεν έγινε single, αλλά αρκετές αναδρομικές κριτικές το αναφέρουν μαζί με το “Shake Me” ως ιδιαίτερα ισχυρό hard-rock κομμάτι.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τον δίσκο με πιο σκοτεινή και απειλητική ατμόσφαιρα από ό,τι υποδηλώνει η αργότερα πιο pop-metal φήμη της μπάντας. Οι «νυχτερινές ιστορίες» δεν είναι απλή party εικόνα, το κομμάτι χρησιμοποιεί τη νύχτα ως χώρο επιθυμίας, κινδύνου και απομόνωσης. Η κιθάρα έχει σχετικά βαρύ riff, ενώ η βραχνή, bluesy φωνή του Tom Keifer εμποδίζει το τραγούδι να γίνει τυπικό glossy glam opener. Είναι αποτελεσματικό ως εισαγωγή στην πιο sleazy και σκοτεινή πλευρά του album, χωρίς να έχει το τεράστιο hook των δύο singles που ακολουθούν.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, άμεσο hard-rock hit του album. Το “Shake Me” χτίζεται πάνω σε riff που μπαίνει αμέσως, σε driving ρυθμό και σε chorus σχεδιασμένο για fist-pumping συμμετοχή. Ο τίτλος και οι στίχοι έχουν τη σωματική, ερωτική υπερβολή του mid-’80s hair metal, αλλά η ερμηνεία του Keifer προσθέτει bluesy αγριάδα και κάνει το τραγούδι να ακούγεται λιγότερο αποστειρωμένο από αρκετούς συγχρόνους του. Ήταν το πρώτο single των Cinderella, δεν μπήκε στα charts, αλλά άνοιξε τον δρόμο για την επιτυχία που ακολούθησε με το “Nobody’s Fool”. Είναι από τις χαρακτηριστικές hair-metal anthems της εποχής, όχι επειδή είναι καινοτόμο, αλλά επειδή εκτελεί τέλεια τη φόρμα του.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, σύντομο και βασισμένο στο road-rock μοτίβο. Η «κόλαση πάνω σε ρόδες» είναι εικόνα ταχύτητας, μηχανής, σεξουαλικότητας και ανεξέλεγκτης κίνησης , ένα απολύτως γνώριμο late-’80s hard-rock θέμα. Το riff είναι άμεσο και ο ρυθμός δεν αφήνει χώρο για μεγάλη ανάπτυξη. Αυτό λειτουργεί υπέρ του τραγουδιού ως energizer, αλλά περιορίζει τη διακριτή του ταυτότητα. Είναι καθαρά deep cut, διασκεδαστικό, σωστά παιγμένο και κατάλληλο για να ανοίγει τη B πλευρά, χωρίς όμως να πλησιάζει τα μεγάλα singles.</t>
+  </si>
+  <si>
+    <t>Από τα καλύτερα και πιο καθαρά arena-rock τραγούδια του δίσκου. Η φράση του τίτλου είναι κραυγή διαφυγής, ο αφηγητής παγιδεύεται σε πίεση, σχέση ή τρόπο ζωής και ζητά λύτρωση. Οι κιθάρες έχουν μεγαλύτερη μελωδική κίνηση, το chorus είναι άμεσο και η ερμηνεία του Keifer διατηρεί τη σωστή αναλογία ανάμεσα σε hook και τραχύτητα. Δεν είναι τόσο συναισθηματικά λεπτοδουλεμένο όσο το “Nobody’s Fool”, αλλά είναι πιο γρήγορο και εξίσου αποτελεσματικό ως hard-rock single. Μαζί με τα “Shake Me” και “Nobody’s Fool”, αποτελεί την τριάδα που περισσότεροι αναδρομικοί σχολιαστές ξεχωρίζουν από το album.</t>
+  </si>
+  <si>
+    <t>Το closing track επιλέγει πιο μελωδικό, ελαφρά Southern/blues-rock τόνο. Η επιστροφή «πίσω στο σπίτι» δεν ακούγεται σαν θριαμβευτικό τέλος, αλλά σαν αναζήτηση σταθερότητας μετά από ένταση, περιπλάνηση και νυχτερινή υπερβολή. Το τραγούδι έχει πιο ανθρώπινη αίσθηση από το προηγούμενο party material, με τις κιθάρες να υπηρετούν τη μελωδία και τον Keifer να αφήνει τη φωνή του να ακουστεί πιο κουρασμένη και ειλικρινής. Δεν είναι ένα τεράστιο finale, αλλά λειτουργεί σωστά, υπογραμμίζει τη bluesy πλευρά της μπάντας και δείχνει προς τη βαθύτερη roots-rock κατεύθυνση που οι Cinderella θα ανέπτυσσαν στους επόμενους δίσκους.</t>
   </si>
 </sst>
 </file>
@@ -13081,7 +13189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16632,19 +16740,51 @@
         <v>2.82</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>3742</v>
+        <v>3785</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>3741</v>
       </c>
       <c r="I111" s="11" t="s">
+        <v>3751</v>
+      </c>
+      <c r="J111" s="11" t="s">
         <v>3752</v>
       </c>
-      <c r="J111" s="11" t="s">
-        <v>3753</v>
+    </row>
+    <row r="112" spans="1:10" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>3772</v>
+      </c>
+      <c r="D112" s="6">
+        <v>1986</v>
+      </c>
+      <c r="E112" s="10">
+        <v>3.45</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>3787</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>3786</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>3782</v>
+      </c>
+      <c r="I112" s="11" t="s">
+        <v>3783</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>3784</v>
       </c>
     </row>
   </sheetData>
@@ -16866,6 +17006,8 @@
     <hyperlink ref="J110" r:id="rId215" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
     <hyperlink ref="I111" r:id="rId216" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
     <hyperlink ref="J111" r:id="rId217" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
+    <hyperlink ref="I112" r:id="rId218" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
+    <hyperlink ref="J112" r:id="rId219" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16873,7 +17015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1053"/>
+  <dimension ref="A1:I1063"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -45254,10 +45396,10 @@
         <v>1</v>
       </c>
       <c r="C1045" s="7" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="D1045" s="7" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="E1045" s="20">
         <v>3.6</v>
@@ -45269,7 +45411,7 @@
         <v>3.8</v>
       </c>
       <c r="H1045" s="9" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="I1045" s="6"/>
     </row>
@@ -45281,10 +45423,10 @@
         <v>2</v>
       </c>
       <c r="C1046" s="7" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="D1046" s="7" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="E1046" s="20">
         <v>3.68</v>
@@ -45296,7 +45438,7 @@
         <v>3.6</v>
       </c>
       <c r="H1046" s="9" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="I1046" s="6"/>
     </row>
@@ -45308,10 +45450,10 @@
         <v>3</v>
       </c>
       <c r="C1047" s="7" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="D1047" s="7" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="E1047" s="20">
         <v>3.35</v>
@@ -45323,7 +45465,7 @@
         <v>3.9</v>
       </c>
       <c r="H1047" s="9" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="I1047" s="6"/>
     </row>
@@ -45335,10 +45477,10 @@
         <v>4</v>
       </c>
       <c r="C1048" s="7" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="D1048" s="7" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="E1048" s="20">
         <v>3.29</v>
@@ -45350,7 +45492,7 @@
         <v>3.4</v>
       </c>
       <c r="H1048" s="9" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="I1048" s="6"/>
     </row>
@@ -45362,10 +45504,10 @@
         <v>5</v>
       </c>
       <c r="C1049" s="7" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="D1049" s="7" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="E1049" s="20">
         <v>2.94</v>
@@ -45377,7 +45519,7 @@
         <v>3.3</v>
       </c>
       <c r="H1049" s="9" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="I1049" s="6"/>
     </row>
@@ -45389,10 +45531,10 @@
         <v>6</v>
       </c>
       <c r="C1050" s="7" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="D1050" s="7" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="E1050" s="20">
         <v>3.14</v>
@@ -45404,7 +45546,7 @@
         <v>3.2</v>
       </c>
       <c r="H1050" s="9" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="I1050" s="6"/>
     </row>
@@ -45416,10 +45558,10 @@
         <v>7</v>
       </c>
       <c r="C1051" s="7" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="D1051" s="7" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="E1051" s="20">
         <v>2.72</v>
@@ -45431,7 +45573,7 @@
         <v>2.5</v>
       </c>
       <c r="H1051" s="9" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="I1051" s="6"/>
     </row>
@@ -45443,10 +45585,10 @@
         <v>8</v>
       </c>
       <c r="C1052" s="7" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="D1052" s="7" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="E1052" s="20">
         <v>3.11</v>
@@ -45458,7 +45600,7 @@
         <v>3.1</v>
       </c>
       <c r="H1052" s="9" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="I1052" s="6"/>
     </row>
@@ -45470,10 +45612,10 @@
         <v>9</v>
       </c>
       <c r="C1053" s="7" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="D1053" s="7" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="E1053" s="20">
         <v>3.04</v>
@@ -45485,9 +45627,281 @@
         <v>4</v>
       </c>
       <c r="H1053" s="22" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="I1053" s="6"/>
+    </row>
+    <row r="1054" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1054" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1054" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1054" s="7" t="s">
+        <v>3772</v>
+      </c>
+      <c r="D1054" s="7" t="s">
+        <v>3789</v>
+      </c>
+      <c r="E1054" s="20">
+        <v>3.75</v>
+      </c>
+      <c r="F1054" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1054" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1054" s="9" t="s">
+        <v>3804</v>
+      </c>
+      <c r="I1054" s="6"/>
+    </row>
+    <row r="1055" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1055" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1055" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1055" s="7" t="s">
+        <v>3773</v>
+      </c>
+      <c r="D1055" s="7" t="s">
+        <v>3790</v>
+      </c>
+      <c r="E1055" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F1055" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1055" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1055" s="9" t="s">
+        <v>3805</v>
+      </c>
+      <c r="I1055" s="6"/>
+    </row>
+    <row r="1056" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1056" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1056" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1056" s="7" t="s">
+        <v>3777</v>
+      </c>
+      <c r="D1056" s="7" t="s">
+        <v>3791</v>
+      </c>
+      <c r="E1056" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1056" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1056" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1056" s="9" t="s">
+        <v>3799</v>
+      </c>
+      <c r="I1056" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1057" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1057" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1057" s="7" t="s">
+        <v>3778</v>
+      </c>
+      <c r="D1057" s="7" t="s">
+        <v>3792</v>
+      </c>
+      <c r="E1057" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F1057" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1057" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H1057" s="9" t="s">
+        <v>3801</v>
+      </c>
+      <c r="I1057" s="6"/>
+    </row>
+    <row r="1058" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1058" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1058" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1058" s="7" t="s">
+        <v>3779</v>
+      </c>
+      <c r="D1058" s="7" t="s">
+        <v>3793</v>
+      </c>
+      <c r="E1058" s="20">
+        <v>3.38</v>
+      </c>
+      <c r="F1058" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1058" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1058" s="9" t="s">
+        <v>3802</v>
+      </c>
+      <c r="I1058" s="6"/>
+    </row>
+    <row r="1059" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1059" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1059" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1059" s="7" t="s">
+        <v>3780</v>
+      </c>
+      <c r="D1059" s="7" t="s">
+        <v>3794</v>
+      </c>
+      <c r="E1059" s="20">
+        <v>3.46</v>
+      </c>
+      <c r="F1059" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1059" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="H1059" s="9" t="s">
+        <v>3806</v>
+      </c>
+      <c r="I1059" s="6"/>
+    </row>
+    <row r="1060" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1060" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1060" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1060" s="7" t="s">
+        <v>3781</v>
+      </c>
+      <c r="D1060" s="7" t="s">
+        <v>3795</v>
+      </c>
+      <c r="E1060" s="20">
+        <v>3.83</v>
+      </c>
+      <c r="F1060" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1060" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1060" s="9" t="s">
+        <v>3807</v>
+      </c>
+      <c r="I1060" s="6"/>
+    </row>
+    <row r="1061" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1061" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1061" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1061" s="7" t="s">
+        <v>3776</v>
+      </c>
+      <c r="D1061" s="7" t="s">
+        <v>3796</v>
+      </c>
+      <c r="E1061" s="20">
+        <v>3.34</v>
+      </c>
+      <c r="F1061" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1061" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1061" s="9" t="s">
+        <v>3803</v>
+      </c>
+      <c r="I1061" s="6"/>
+    </row>
+    <row r="1062" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1062" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1062" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1062" s="7" t="s">
+        <v>3775</v>
+      </c>
+      <c r="D1062" s="7" t="s">
+        <v>3797</v>
+      </c>
+      <c r="E1062" s="20">
+        <v>3.26</v>
+      </c>
+      <c r="F1062" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G1062" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="H1062" s="9" t="s">
+        <v>3800</v>
+      </c>
+      <c r="I1062" s="6"/>
+    </row>
+    <row r="1063" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1063" s="6">
+        <v>2460844</v>
+      </c>
+      <c r="B1063" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1063" s="7" t="s">
+        <v>3774</v>
+      </c>
+      <c r="D1063" s="7" t="s">
+        <v>3798</v>
+      </c>
+      <c r="E1063" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F1063" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1063" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1063" s="9" t="s">
+        <v>3808</v>
+      </c>
+      <c r="I1063" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAE4FB0-062B-4F1A-9887-644B8B38DDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193844B-A0D0-49F1-BE4A-96D2EA140234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4119" uniqueCount="3809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="3844">
   <si>
     <t>No</t>
   </si>
@@ -12643,6 +12643,111 @@
   </si>
   <si>
     <t>Το closing track επιλέγει πιο μελωδικό, ελαφρά Southern/blues-rock τόνο. Η επιστροφή «πίσω στο σπίτι» δεν ακούγεται σαν θριαμβευτικό τέλος, αλλά σαν αναζήτηση σταθερότητας μετά από ένταση, περιπλάνηση και νυχτερινή υπερβολή. Το τραγούδι έχει πιο ανθρώπινη αίσθηση από το προηγούμενο party material, με τις κιθάρες να υπηρετούν τη μελωδία και τον Keifer να αφήνει τη φωνή του να ακουστεί πιο κουρασμένη και ειλικρινής. Δεν είναι ένα τεράστιο finale, αλλά λειτουργεί σωστά, υπογραμμίζει τη bluesy πλευρά της μπάντας και δείχνει προς τη βαθύτερη roots-rock κατεύθυνση που οι Cinderella θα ανέπτυσσαν στους επόμενους δίσκους.</t>
+  </si>
+  <si>
+    <t>Long Cold Winter</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/3403683-Cinderella-Long-Cold-Winter</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/X0Fi-vD8AlQUJtLaNrxLMUvSCvQr_aLozcLXzGUKdAg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0MDM2/ODMtMTMyOTA1ODMx/OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Mercury – 834 612-1 (Greece, 1988, LP, Album, Stereo). Manufactured and pressed by G.P.I. S.A., με lacquer cut από G.P.I. S.A. (2784) και printed by Φώτο Όφσετ ΕΠΕ.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Long Cold Winter κυκλοφόρησε τον Ιούνιο του 1988 και σηματοδότησε μια τεράστια καλλιτεχνική και στιλιστική στροφή για τους Cinderella. Το συγκρότημα απομακρύνθηκε από το καθαρόαιμο, γυαλισμένο glam metal του ντεμπούτου και στράφηκε συνειδητά προς ένα βαρύτερο, blues-infused hard rock / blues-metal ήχο, επηρεασμένο έντονα από τους Led Zeppelin, AC/DC και τους κλασικούς bluesmen. Την παραγωγή ανέλαβε ο Tom Keifer μαζί με τους Andy Johns και Eric Brittingham. Στις ηχογραφήσεις συμμετείχαν κορυφαίοι session μουσικοί, όπως οι θρυλικοί ντράμερ Cozy Powell και Denny Carmassl σε επιλεγμένα μέρη, ο Paulinho Da Costa στα κρουστά και ο Rick Criniti στα πλήκτρα. Η ελληνική έκδοση κυκλοφόρησε σε γυαλιστερό εξώφυλλο με δίγλωσσο εσωτερικό ένθετο (insert) στίχων και φωτογραφιών.</t>
+  </si>
+  <si>
+    <t>Bad Seamstress Blues / Fallin’ Apart At The Seams</t>
+  </si>
+  <si>
+    <t>Gypsy Road</t>
+  </si>
+  <si>
+    <t>Don’t Know What You Got (Till It’s Gone)</t>
+  </si>
+  <si>
+    <t>The Last Mile</t>
+  </si>
+  <si>
+    <t>Second Wind</t>
+  </si>
+  <si>
+    <t>If You Don’t Like It</t>
+  </si>
+  <si>
+    <t>Coming Home</t>
+  </si>
+  <si>
+    <t>Fire And Ice</t>
+  </si>
+  <si>
+    <t>Take Me Back</t>
+  </si>
+  <si>
+    <t>Η μεγάλη hard-rock διαδρομή του album και μία από τις χαρακτηριστικές Cinderella συνθέσεις. Ο “gypsy road” είναι δρόμος περιπλάνησης, ελευθερίας και άρνησης να δεχτείς μια ασφαλή, προβλέψιμη ζωή. Το τραγούδι έχει άμεσο riff, Southern/bluesy κίνηση και μεγάλο chorus, αλλά η βασική του δύναμη είναι ότι δεν ακούγεται σαν τυπικό MTV hair-metal single. Ο Keifer τραγουδά με την αίσθηση κάποιου που πραγματικά θέλει να φύγει, όχι απλώς να παίξει τον rock-star χαρακτήρα. Οι κιθάρες έχουν αρκετή βρωμιά και το rhythm section αρκετή κίνηση ώστε να ενώνουν Stones/Aerosmith DNA με late-’80s arena rock. Αρκετές αναδρομικές πηγές το θεωρούν από τα καλύτερα glam/hard-rock τραγούδια της εποχής.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στην κίνηση, με road-rock θεματική και γήινο Southern hard-rock groove. Η «τελευταία μίλια» είναι η τελική προσπάθεια πριν από τον προορισμό , είτε πρόκειται για σχέση, είτε για προσωπική επιβίωση, είτε για τη ζωή ενός μουσικού στον δρόμο. Οι κιθάρες έχουν σκληρότερη, πιο rootsy αίσθηση και η μπάντα παίζει με περισσότερο swing απ’ ό,τι στο βασικό glam metal της περιόδου. Δεν έχει το άμεσο hit power του “Gypsy Road”, αλλά είναι ουσιώδες επειδή κρατά ζωντανό το album’s road-and-blues χαρακτήρα. Οι κριτικές το αναφέρουν συχνά μαζί με το “Gypsy Road” ως πολύ καλά πετυχημένο cock-rock / hard-rock track.</t>
+  </si>
+  <si>
+    <t>Πιο ανοιχτό, μελαγχολικό και Southern-tinged, με θέμα την επιστροφή , σε έναν τόπο, σε έναν άνθρωπο ή σε μια πιο αληθινή εκδοχή του εαυτού σου. Οι ακουστικές/rootsy αποχρώσεις και η ήρεμη αρχική ανάπτυξη δημιουργούν χώρο, ενώ η φωνή του Keifer ακούγεται πιο προσωπική από ό,τι στα party/hard-rock tracks. Το τραγούδι συνδέεται με την αμερικανική rock παράδοση δρόμου και επιστροφής, αλλά οι Cinderella το κρατούν μέσα στο δικό τους melodic hard-rock πλαίσιο. Δεν είναι ένα τεράστιο single, όμως είναι από τις πιο ώριμες και συνεκτικές συνθέσεις του δίσκου.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με φυσαρμόνικα, κάτι που δηλώνει αμέσως ότι οι Cinderella δεν θέλουν να επαναλάβουν απλώς τη glam-metal φόρμα του Night Songs. Το “Bad Seamstress Blues” λειτουργεί ως σύντομο bluesy προοίμιο, με τίτλο που παίζει με την εικόνα μιας σχέσης ή ζωής που «ράβεται» πρόχειρα και αρχίζει να ξηλώνεται. Το “Fallin’ Apart at the Seams” μπαίνει σαν φυσική έκρηξη, σκληρό riff, dirty groove και η βραχνή φωνή του Tom Keifer να μεταφέρει τη διάλυση όχι ως polished heartbreak αλλά ως πραγματική φθορά. Η σύνδεση των δύο μερών είναι ουσιαστική, πρώτα το blues mood, μετά το hard-rock ξέσπασμα. Είναι η πιο σαφής δήλωση του νέου ήχου του δίσκου.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη power ballad του δίσκου και πιθανότατα η πιο αναγνωρίσιμη Cinderella σύνθεση. Το θέμα είναι διαχρονικό, καταλαβαίνεις την αξία ενός ανθρώπου μόνο όταν τον έχεις χάσει. Αυτό που ξεχωρίζει το τραγούδι από άπειρες 1980s μπαλάντες είναι η ερμηνεία του Keifer, βραχνή, ευάλωτη και με blues αίσθηση, όχι απλώς γυαλισμένη arena-φωνή. Η σύνθεση ανεβαίνει σταδιακά από τη θλίψη σε μεγάλη κιθαριστική/φωνητική κορύφωση, ενώ το solo κρατά τη μελωδική δραματικότητα χωρίς υπερβολική επίδειξη. Έγινε το μεγαλύτερο hit του album και παραμένει ένα από τα πιο αποτελεσματικά παραδείγματα power-ballad songwriting της δεκαετίας.</t>
+  </si>
+  <si>
+    <t>Ένα up-tempo τραγούδι ανανέωσης και επιμονής. Ο “δεύτερος άνεμος” είναι η ενέργεια που εμφανίζεται όταν νομίζεις ότι έχεις εξαντληθεί, και η μουσική το αποδίδει με σταθερό drive, καθαρό chorus και πιο προσιτό arena-rock σχήμα. Είναι πιο κοντά στο melodic hard rock του Night Songs από τα bluesier tracks της A πλευράς, αλλά δεν διαταράσσει τη συνοχή, λειτουργεί ως γρήγορη ανάσα μετά τη συναισθηματική κορύφωση του “Don’t Know What You Got” και την road-rock αίσθηση του “The Last Mile”. Δεν διαθέτει ιδιαίτερα μοναδικό hook, γι’ αυτό και μένει λίγο κάτω από τα βασικά highlights, αλλά παραμένει καλοπαιγμένο και αποτελεσματικό.</t>
+  </si>
+  <si>
+    <t>Το title track κατεβάζει την ταχύτητα και μεταφέρει τον δίσκο σε πιο μελαγχολικό, blues-rock πεδίο. Ο «μακρύς κρύος χειμώνας» είναι μεταφορά για μια περίοδο συναισθηματικής απομόνωσης, απώλειας ή πίκρας. Η μπάντα αφήνει χώρο στη φωνή του Keifer, στη χροιά της κιθάρας και στη σταδιακή κλιμάκωση, αντί να κυνηγήσει άλλο ένα μεγάλο chorus. Είναι από τα tracks που αποδεικνύουν ότι το album έχει ουσία και έξω από τα singles, οι Cinderella χρησιμοποιούν τη blues γλώσσα για να δημιουργήσουν βάρος, χωρίς να αντιγράφουν απλώς παλιό blues-rock. Η θέση του στην αρχή της B πλευράς λειτουργεί σαν σκοτεινή επανεκκίνηση μετά τη δυναμική πρώτη πλευρά.</t>
+  </si>
+  <si>
+    <t>Το πιο επιθετικό, νευρικό σημείο της B πλευράς. Ο τίτλος είναι απλή και σαφής πρόκληση, αν δεν σου αρέσει, δεν χρειάζεται να μείνεις. Η μουσική ανταποκρίνεται με κοφτό riffing, πιο έντονο rhythm section και φωνητικά που έχουν rock ’n’ roll περιφρόνηση. Δεν έχει το δραματικό βάθος του title track ούτε το μελωδικό μεγαλείο του “Don’t Know What You Got”, όμως προσφέρει την απαραίτητη σκληρή αντίθεση. Είναι πιο κοντά σε αυθεντικό bar-band hard rock απ’ ό,τι σε γυαλισμένο pop metal, και αυτό ενισχύει τη συνοχή της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Γρήγορο hard rock με κλασική αντιθετική εικόνα, πάθος και ψυχρότητα, έλξη και απόρριψη. Η μπάντα ανεβάζει ξανά τον ρυθμό με straightforward riff, έντονα drums και φωνητική ερμηνεία που ισορροπεί ανάμεσα σε grit και chorus-friendly μελωδία. Λειτουργεί σαν late-album energizer, λίγο πιο κοντά στο glam-hard-rock λεξιλόγιο του debut, χωρίς όμως να χάνει πλήρως τη bluesy χροιά του Keifer. Δεν είναι από τα πιο ιδιαίτερα τραγούδια, αλλά η σύντομη διάρκεια και η άμεση εκτέλεση το κάνουν χρήσιμο πριν από το closing track.</t>
+  </si>
+  <si>
+    <t>Το album κλείνει με retro hard-rock/boogie διάθεση και τίτλο που συνδυάζει επιστροφή, νοσταλγία και ερωτική παράκληση. Μετά τη μελαγχολία του title track και το rootsy “Coming Home”, η επιλογή ενός πιο άμεσου rocker ως finale δίνει αίσθηση ότι η μπάντα δεν θέλει να φύγει σε απόλυτη θλίψη. Οι κιθάρες και η ρυθμική βάση παραπέμπουν στην παλιότερη rock ’n’ roll παράδοση που οι Cinderella προσπαθούν να αναβιώσουν σε όλο τον δίσκο. Δεν είναι κορυφαίο song, αλλά είναι σωστό closing cut, διατηρεί την ανθρώπινη, bluesy hard-rock θερμοκρασία του album και δείχνει προς το ακόμη πιο roots-oriented μονοπάτι που η μπάντα θα ακολουθούσε αργότερα.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Glam Metal, Bluesy Hard Rock, Southern Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Harmonica Blues Rock, Gritty Glam Metal, Album Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Bluesy Arena Rock, Southern Hard Rock, Glam Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Blues-Rock Ballad, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Road Rock, Southern Hard Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Melodic Hard Rock, Arena Rock, Up-tempo Rocker]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Slow Blues Rock, Melancholic Rock, Soulful Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Defiant Hard Rock, Bluesy Riff Rock, Arena Metal edge]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Southern Rock, Acoustic-tinged Hard Rock, Road Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Fast Hard Rock, Melodic Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Retro Hard Rock, Bluesy Rock ’n’ Roll, Album Closer]</t>
   </si>
 </sst>
 </file>
@@ -13189,7 +13294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16785,6 +16890,38 @@
       </c>
       <c r="J112" s="11" t="s">
         <v>3784</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D113" s="6">
+        <v>1988</v>
+      </c>
+      <c r="E113" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>3833</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>3813</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>3812</v>
+      </c>
+      <c r="I113" s="11" t="s">
+        <v>3810</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>3811</v>
       </c>
     </row>
   </sheetData>
@@ -17008,6 +17145,8 @@
     <hyperlink ref="J111" r:id="rId217" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
     <hyperlink ref="I112" r:id="rId218" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
     <hyperlink ref="J112" r:id="rId219" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
+    <hyperlink ref="I113" r:id="rId220" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
+    <hyperlink ref="J113" r:id="rId221" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17015,7 +17154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1063"/>
+  <dimension ref="A1:I1073"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -45903,6 +46042,276 @@
       </c>
       <c r="I1063" s="6"/>
     </row>
+    <row r="1064" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1064" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1064" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1064" s="7" t="s">
+        <v>3814</v>
+      </c>
+      <c r="D1064" s="7" t="s">
+        <v>3834</v>
+      </c>
+      <c r="E1064" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F1064" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1064" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1064" s="9" t="s">
+        <v>3826</v>
+      </c>
+      <c r="I1064" s="6"/>
+    </row>
+    <row r="1065" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1065" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1065" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1065" s="7" t="s">
+        <v>3815</v>
+      </c>
+      <c r="D1065" s="7" t="s">
+        <v>3835</v>
+      </c>
+      <c r="E1065" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F1065" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1065" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1065" s="9" t="s">
+        <v>3823</v>
+      </c>
+      <c r="I1065" s="6"/>
+    </row>
+    <row r="1066" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1066" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1066" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1066" s="7" t="s">
+        <v>3816</v>
+      </c>
+      <c r="D1066" s="7" t="s">
+        <v>3836</v>
+      </c>
+      <c r="E1066" s="20">
+        <v>4</v>
+      </c>
+      <c r="F1066" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1066" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1066" s="9" t="s">
+        <v>3827</v>
+      </c>
+      <c r="I1066" s="6"/>
+    </row>
+    <row r="1067" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1067" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1067" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1067" s="7" t="s">
+        <v>3817</v>
+      </c>
+      <c r="D1067" s="7" t="s">
+        <v>3837</v>
+      </c>
+      <c r="E1067" s="20">
+        <v>3.62</v>
+      </c>
+      <c r="F1067" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1067" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1067" s="9" t="s">
+        <v>3824</v>
+      </c>
+      <c r="I1067" s="6"/>
+    </row>
+    <row r="1068" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1068" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1068" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1068" s="7" t="s">
+        <v>3818</v>
+      </c>
+      <c r="D1068" s="7" t="s">
+        <v>3838</v>
+      </c>
+      <c r="E1068" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F1068" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1068" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1068" s="9" t="s">
+        <v>3828</v>
+      </c>
+      <c r="I1068" s="6"/>
+    </row>
+    <row r="1069" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1069" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1069" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1069" s="7" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D1069" s="7" t="s">
+        <v>3839</v>
+      </c>
+      <c r="E1069" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F1069" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1069" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1069" s="9" t="s">
+        <v>3829</v>
+      </c>
+      <c r="I1069" s="6"/>
+    </row>
+    <row r="1070" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1070" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1070" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1070" s="7" t="s">
+        <v>3819</v>
+      </c>
+      <c r="D1070" s="7" t="s">
+        <v>3840</v>
+      </c>
+      <c r="E1070" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F1070" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1070" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1070" s="9" t="s">
+        <v>3830</v>
+      </c>
+      <c r="I1070" s="6"/>
+    </row>
+    <row r="1071" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1071" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1071" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1071" s="7" t="s">
+        <v>3820</v>
+      </c>
+      <c r="D1071" s="7" t="s">
+        <v>3841</v>
+      </c>
+      <c r="E1071" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F1071" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1071" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1071" s="9" t="s">
+        <v>3825</v>
+      </c>
+      <c r="I1071" s="6"/>
+    </row>
+    <row r="1072" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1072" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1072" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1072" s="7" t="s">
+        <v>3821</v>
+      </c>
+      <c r="D1072" s="7" t="s">
+        <v>3842</v>
+      </c>
+      <c r="E1072" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F1072" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1072" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1072" s="9" t="s">
+        <v>3831</v>
+      </c>
+      <c r="I1072" s="6"/>
+    </row>
+    <row r="1073" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1073" s="6">
+        <v>3403683</v>
+      </c>
+      <c r="B1073" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1073" s="7" t="s">
+        <v>3822</v>
+      </c>
+      <c r="D1073" s="7" t="s">
+        <v>3843</v>
+      </c>
+      <c r="E1073" s="20">
+        <v>3.44</v>
+      </c>
+      <c r="F1073" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1073" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1073" s="9" t="s">
+        <v>3832</v>
+      </c>
+      <c r="I1073" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193844B-A0D0-49F1-BE4A-96D2EA140234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA71141-BB39-47B3-99AC-CED529071A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="3844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4193" uniqueCount="3877">
   <si>
     <t>No</t>
   </si>
@@ -12748,6 +12748,135 @@
   </si>
   <si>
     <t>Blues Rock, Hard Rock [Retro Hard Rock, Bluesy Rock ’n’ Roll, Album Closer]</t>
+  </si>
+  <si>
+    <t>Manowar</t>
+  </si>
+  <si>
+    <t>Fighting The World</t>
+  </si>
+  <si>
+    <t>ATCO Records – 790563-1 (Greece, May 1987, LP, Album, Stereo). Manufactured by G.P.I. S.A. (MT410), manufactured for και distributed by WEA Records S.A. (W609), με lacquer cut από G.P.I. S.A. και printed by Ορφανός - Σκαλτσάς.</t>
+  </si>
+  <si>
+    <t>Το Fighting The World κυκλοφόρησε τον Μάιο του 1987 και αποτελεί το πέμπτο studio album των Manowar. Είναι πρωτοποριακό στην ιστορία του heavy metal καθώς υπήρξε από τα πρώτα metal άλμπουμ που ηχογραφήθηκαν και μιξαρίστηκαν εξ ολοκλήρου ψηφιακά (χρησιμοποιώντας το σύστημα Synclavier). Την παραγωγή υπογράφουν οι ίδιοι οι Manowar, με τον Howie Weinberg στο mastering (Masterdisk) και τον Richard Breen στον ψηφιακό προγραμματισμό και τη μίξη. Το άλμπουμ περιλαμβάνει ιστορικές στιγμές, όπως η αφηγηναστική συμμετοχή του θρυλικού Orson Welles στο κομμάτι "Defender", συνοδευόμενου από τη General VanClibreen Philharmonic. Η ελληνική έκδοση της WEA/ATCO κυκλοφόρησε με εσωτερικό μονόφυλλο sleeve και stamped runouts.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/12991988-Manowar-Fighting-The-World</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/vwwdD-t7JRtFPTOsKnJuAAmjJLNsM-vFSXZVcaX7FIM/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEyOTkx/OTg4LTE1NDYwNDI0/OTItMTk2OC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Blow Your Speakers</t>
+  </si>
+  <si>
+    <t>Carry On</t>
+  </si>
+  <si>
+    <t>Violence And Bloodshed</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Drums Of Doom</t>
+  </si>
+  <si>
+    <t>Holy War</t>
+  </si>
+  <si>
+    <t>Master Of Revenge</t>
+  </si>
+  <si>
+    <t>Black Wind, Fire And Steel</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Power Metal [Epic Heavy Metal, US Power Metal, Arena Metal, Digital Metal Production]</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τον δίσκο σαν δήλωση αποστολής. Η «μάχη με τον κόσμο» δεν παρουσιάζεται ως προσωπική αυτολύπηση, αλλά ως metal-community στάση: αντίσταση στην αδιαφορία, στην υποτίμηση και στην πίεση να προσαρμοστείς. Η μουσική είναι πιο απλή και πιο άμεση από τα μεγάλα epics των πρώτων Manowar albums: σταθερό ρυθμικό βάρος, chorus που λειτουργεί σαν crowd chant και φωνή του Eric Adams που μετατρέπει μια βασική φράση σε τελετουργική διακήρυξη. Η παραγωγή είναι πολύ καθαρή, με τα drums και το μπάσο μπροστά, και έτσι το track ακούγεται σαν γέφυρα από το traditional metal προς το πιο glossy 1987 arena metal. Δεν είναι η πιο σύνθετη Manowar σύνθεση, αλλά λειτουργεί σωστά ως opener και ως σύνθημα ταυτότητας.</t>
+  </si>
+  <si>
+    <t>Το πιο rock ’n’ roll και πιο προκλητικό τραγούδι της A πλευράς. Ο τίτλος προτρέπει να «σπάσεις τα ηχεία», δηλαδή να ακούσεις metal τόσο δυνατά ώστε να ξεπεράσεις τους περιορισμούς του χώρου, του γούστου ή του mainstream. Οι στίχοι συνδέθηκαν συχνά με anti-MTV στάση — μια μπάντα που υποστήριζε την ιδέα του “true metal” και αντιδρούσε στην πιο pop/visual διάσταση του rock. Το riff είναι γρήγορο και απλό, η φωνή του Adams υπερβολική με τον σωστό τρόπο και το τραγούδι λειτουργεί σαν σύντομη έκρηξη. Δεν έχει την επική βαρύτητα των B-side tracks, αλλά κρατά καλά την A πλευρά σε ένταση και αποκαλύπτει τη πιο άμεση hard-rock όψη του album.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Από τις πιο μελωδικές και πιο αγαπητές στιγμές του δίσκου. Το “carry on” είναι μήνυμα αντοχής: συνέχισε, ακόμα και όταν η απογοήτευση, η πίεση ή η απώλεια σε κάνουν να θέλεις να σταματήσεις. Το τραγούδι έχει σχετικά απλή δομή, αλλά η μελωδία και η ερμηνεία του Eric Adams το ανεβάζουν πολύ πάνω από το επίπεδο ενός τυπικού motivational hard-rock κομματιού. Η αίσθηση είναι σχεδόν Queen-like στον τρόπο που η φωνή ξεδιπλώνεται πάνω από τις κιθάρες και το rhythm section, χωρίς η μπάντα να χάνει τον heavy-metal χαρακτήρα της. Είναι το κομμάτι που αποδεικνύει καλύτερα γιατί η πιο προσβάσιμη πλευρά του </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Fighting The World</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> δεν ήταν απαραίτητα καλλιτεχνικός συμβιβασμός.</t>
+    </r>
+  </si>
+  <si>
+    <t>Η σκληρότερη και πιο ταχεία στιγμή της A πλευράς. Ο τίτλος δείχνει αμέσως ότι η μπάντα επιστρέφει σε battle-metal θεματολογία, με εικόνες σύγκρουσης, επιβίωσης και τιμής. Η μουσική δεν αναζητά μεγάλες μελωδικές ανάσες: τα drums κινούνται γρήγορα, το riffing είναι κοφτό και το μπάσο του Joey DeMaio οδηγεί την επίθεση. Η ψηφιακή παραγωγή εδώ λειτουργεί διπλά: δίνει καθαρότητα και ταχύτητα, αλλά κάνει ορισμένα σημεία να ακούγονται πιο μηχανικά από το ζωντανό βάρος των παλαιότερων δίσκων. Παρόλα αυτά, είναι αποτελεσματικό fast-metal track και προετοιμάζει την αλλαγή προς την επική B πλευρά.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο κλείσιμο και ένα από τα βασικά Manowar classics. Ο τίτλος συσσωρεύει τέσσερις elemental/battle εικόνες — άνεμος, φωτιά, ατσάλι — και η μουσική αντιστοιχεί με fast riffing, κυρίαρχο μπάσο, δυνατά drums και φωνητικά που ανεβαίνουν από πολεμικό κάλεσμα σε σχεδόν θριαμβευτική κορύφωση. Ο Eric Adams είναι εδώ σε εξαιρετική φόρμα: η φωνή του δίνει στο τραγούδι την αίσθηση ότι το metal δεν είναι απλώς είδος, αλλά τελετουργική μάχη. Η σύνθεση έχει σαφή speed-metal drive, αλλά παραμένει μελωδική και anthem-oriented, αποφεύγοντας την απλή τεχνική επίδειξη. Οι κριτικές το ξεχωρίζουν σταθερά ως το κορυφαίο ή ένα από τα κορυφαία tracks του δίσκου, και δικαίως παίρνει την υψηλότερη βαθμολογία του πίνακα.</t>
+  </si>
+  <si>
+    <t>Δεύτερο σύντομο interlude, αυτή τη φορά με πιο σκοτεινή και horror-like λειτουργία. Ο τίτλος προετοιμάζει τη μετάβαση προς την τελική εκδίκηση/σύγκρουση του “Black Wind, Fire And Steel”. Δεν έχει αρκετή μουσική ανάπτυξη για να αξιολογηθεί ως πλήρες τραγούδι, αλλά το placement του είναι σωστό: προσθέτει μικρή παύση, υποβλητική ατμόσφαιρα και έναν θεατρικό προθάλαμο πριν από το πιο μεγάλο finale. Η χαμηλότερη βαθμολογία αφορά μόνο την αυτονομία του, όχι τη χρησιμότητά του στη δραματουργία της πλευράς.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στην πλήρη ταχύτητα και στο epic battle-metal ύφος. Η «ιερή μάχη» δεν αντιμετωπίζεται με ιστορική ακρίβεια ή θρησκευτική ανάλυση· λειτουργεί ως Manowar mythic language για πίστη, σύγκρουση και πολεμική αφοσίωση. Η μουσική είναι γρήγορη, με riffs που θυμίζουν κλασικό US/European power metal και φωνητική ερμηνεία που ανεβαίνει σε μεγάλα, πολεμικά refrains. Το track έχει περισσότερο βάρος από το “Violence And Bloodshed” επειδή ενώνει την ταχύτητα με ισχυρότερη μελωδική κλιμάκωση. Κριτικές το τοποθετούν στα πιο δυνατά κομμάτια της B πλευράς, μαζί με το finale.</t>
+  </si>
+  <si>
+    <t>Σύντομο drum interlude, με τον Scott Columbus και πρόσθετα percussion από τον Vincent Gutman. Δεν είναι πλήρης σύνθεση με verse, refrain ή θεματική ανάπτυξη, αλλά λειτουργεί ως τελετουργικό πέρασμα: μετά το κινηματογραφικό “Defender”, αφήνει τα κρουστά να δημιουργήσουν αίσθηση πορείας προς τη μάχη. Η αξία του είναι κυρίως sequencing και live-ritual ατμόσφαιρα. Ως αυτόνομο track δεν δικαιολογεί υψηλή βαθμολογία, όμως μέσα στη B πλευρά χτίζει σωστά την ένταση πριν από το “Holy War”.</t>
+  </si>
+  <si>
+    <t>Η επική καρδιά του album. Το “Defender” είχε ήδη γραφτεί σε παλιότερη μορφή και η συγκεκριμένη εκδοχή αξιοποιεί την αφήγηση του Orson Welles — η οποία είχε ηχογραφηθεί για το demo της πρώτης περιόδου και χρησιμοποιήθηκε εδώ μετά θάνατον. Η φωνή του Welles δίνει στο τραγούδι κινηματογραφική κλίμακα, σαν προφητεία σε κόσμο ερειπίων και πολέμου. Όταν μπαίνει το πλήρες band, οι Manowar χτίζουν classic sword-and-sorcery metal: αργή αρχική ανάπτυξη, δραματικά keyboards/strings, μεγάλες φωνητικές κορυφώσεις και κιθάρες που δημιουργούν αίσθηση ηρωικού πεπρωμένου. Κάποιοι κριτικοί θεωρούν ότι η ατμόσφαιρα και η αφήγηση κάνουν περισσότερη δουλειά από τη σύνθεση, αλλά ακριβώς αυτή η θεατρικότητα είναι που κάνει το track μοναδικό στον κατάλογό τους.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Power Metal [Metal Anthem, Arena Metal, Traditional Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Heavy Rock, Anti-MTV Metal, Arena Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Metal Anthem, Hard ’n’ Heavy, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Speed Metal [Fast Metal, Battle Metal, Aggressive Riff Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Power Metal [Epic Metal, Sword-and-Sorcery, Spoken-Word Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Metal [Drum Interlude, Percussion Showcase]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Power Metal [Epic Battle Metal, Fast Traditional Metal, War Anthem]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Metal [Horror Interlude, Atmospheric Metal, Narrative Bridge]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Speed Metal [Epic Speed Metal, Power Metal, Grand Finale]</t>
   </si>
 </sst>
 </file>
@@ -13294,7 +13423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16922,6 +17051,38 @@
       </c>
       <c r="J113" s="11" t="s">
         <v>3811</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>3844</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D114" s="6">
+        <v>1987</v>
+      </c>
+      <c r="E114" s="10">
+        <v>3.29</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>3858</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>3847</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>3846</v>
+      </c>
+      <c r="I114" s="11" t="s">
+        <v>3848</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>3849</v>
       </c>
     </row>
   </sheetData>
@@ -17147,6 +17308,8 @@
     <hyperlink ref="J112" r:id="rId219" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
     <hyperlink ref="I113" r:id="rId220" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
     <hyperlink ref="J113" r:id="rId221" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
+    <hyperlink ref="I114" r:id="rId222" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
+    <hyperlink ref="J114" r:id="rId223" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17154,7 +17317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1073"/>
+  <dimension ref="A1:I1082"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -46312,6 +46475,255 @@
       </c>
       <c r="I1073" s="6"/>
     </row>
+    <row r="1074" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1074" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1074" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1074" s="7" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1074" s="7" t="s">
+        <v>3868</v>
+      </c>
+      <c r="E1074" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F1074" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1074" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1074" s="9" t="s">
+        <v>3859</v>
+      </c>
+      <c r="I1074" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1075" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1075" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1075" s="7" t="s">
+        <v>3850</v>
+      </c>
+      <c r="D1075" s="7" t="s">
+        <v>3869</v>
+      </c>
+      <c r="E1075" s="20">
+        <v>3.28</v>
+      </c>
+      <c r="F1075" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1075" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1075" s="9" t="s">
+        <v>3860</v>
+      </c>
+      <c r="I1075" s="6"/>
+    </row>
+    <row r="1076" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1076" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1076" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1076" s="7" t="s">
+        <v>3851</v>
+      </c>
+      <c r="D1076" s="7" t="s">
+        <v>3870</v>
+      </c>
+      <c r="E1076" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F1076" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1076" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1076" s="9" t="s">
+        <v>3861</v>
+      </c>
+      <c r="I1076" s="6"/>
+    </row>
+    <row r="1077" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1077" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1077" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1077" s="7" t="s">
+        <v>3852</v>
+      </c>
+      <c r="D1077" s="7" t="s">
+        <v>3871</v>
+      </c>
+      <c r="E1077" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F1077" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1077" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1077" s="9" t="s">
+        <v>3862</v>
+      </c>
+      <c r="I1077" s="6"/>
+    </row>
+    <row r="1078" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1078" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1078" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1078" s="7" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1078" s="7" t="s">
+        <v>3872</v>
+      </c>
+      <c r="E1078" s="20">
+        <v>3.76</v>
+      </c>
+      <c r="F1078" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1078" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1078" s="9" t="s">
+        <v>3867</v>
+      </c>
+      <c r="I1078" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1079" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1079" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1079" s="7" t="s">
+        <v>3854</v>
+      </c>
+      <c r="D1079" s="7" t="s">
+        <v>3873</v>
+      </c>
+      <c r="E1079" s="20">
+        <v>2.77</v>
+      </c>
+      <c r="F1079" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="G1079" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1079" s="9" t="s">
+        <v>3866</v>
+      </c>
+      <c r="I1079" s="6"/>
+    </row>
+    <row r="1080" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1080" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1080" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1080" s="7" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1080" s="7" t="s">
+        <v>3874</v>
+      </c>
+      <c r="E1080" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F1080" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1080" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1080" s="9" t="s">
+        <v>3865</v>
+      </c>
+      <c r="I1080" s="6"/>
+    </row>
+    <row r="1081" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1081" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1081" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1081" s="7" t="s">
+        <v>3856</v>
+      </c>
+      <c r="D1081" s="7" t="s">
+        <v>3875</v>
+      </c>
+      <c r="E1081" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="F1081" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="G1081" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1081" s="9" t="s">
+        <v>3864</v>
+      </c>
+      <c r="I1081" s="6"/>
+    </row>
+    <row r="1082" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1082" s="6">
+        <v>12991988</v>
+      </c>
+      <c r="B1082" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1082" s="7" t="s">
+        <v>3857</v>
+      </c>
+      <c r="D1082" s="7" t="s">
+        <v>3876</v>
+      </c>
+      <c r="E1082" s="20">
+        <v>4.13</v>
+      </c>
+      <c r="F1082" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1082" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1082" s="9" t="s">
+        <v>3863</v>
+      </c>
+      <c r="I1082" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA71141-BB39-47B3-99AC-CED529071A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429E1795-3E54-4977-93F2-0C2278523C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4193" uniqueCount="3877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="3916">
   <si>
     <t>No</t>
   </si>
@@ -12878,12 +12878,129 @@
   <si>
     <t>Heavy Metal, Speed Metal [Epic Speed Metal, Power Metal, Grand Finale]</t>
   </si>
+  <si>
+    <t>Mötley Crüe</t>
+  </si>
+  <si>
+    <t>Shout At The Devil</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/PzmUawLQg_s1O9JfWA6pe-XysLhHZ7Hk8mcYodx4_LU/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTEwODI0/OTMwLTE3NDU3NDQ3/NDAtMzYxOS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/10824930-M%C3%B6tley-Cr%C3%BCe-Shout-At-The-Devil</t>
+  </si>
+  <si>
+    <t>Elektra – 96-0289-1, Elektra – 960 289-1 (Europe, 1983, LP, Album, Reissue). Manufactured by Record Service GmbH και pressed by Record Service Alsdorf στη Γερμανία, με Mastering από τον George Marino στη Sterling Sound.</t>
+  </si>
+  <si>
+    <t>Το Shout At The Devil είναι το δεύτερο studio album των Mötley Crüe, κυκλοφόρησε αρχικά το 1983 και καθιέρωσε παγκοσμίως το συγκρότημα ως ηγέτη της 80s glam/heavy metal σκηνής. Η παραγωγή έγινε από τον Tom Werman στα Cherokee Studios στο Λος Άντζελες, συνδυάζοντας την ωμή επιθετικότητα του heavy metal με τεράστια, ραδιοφωνικά hooks. Η αισθητική του δίσκου (με το εμβληματικό πεντάγραμμο/pentagram εξώφυλλο) και κομμάτια-ορόσημα όπως η διασκευή στο "Helter Skelter" των Beatles άφησαν εποχή. Η συγκεκριμένη ευρωπαϊκή κοπή της Record Service Alsdorf διαθέτει κόκκινες ετικέτες (red labels), non-gatefold εξώφυλλο και περιλαμβάνει το τυπωμένο εσωτερικό ένθετο (printed inner-sleeve).</t>
+  </si>
+  <si>
+    <t>In The Beginning</t>
+  </si>
+  <si>
+    <t>Looks That Kill</t>
+  </si>
+  <si>
+    <t>Bastard</t>
+  </si>
+  <si>
+    <t>Danger</t>
+  </si>
+  <si>
+    <t>Ten Seconds To Love</t>
+  </si>
+  <si>
+    <t>Knock ’Em Dead, Kid</t>
+  </si>
+  <si>
+    <t>Too Young To Fall In Love</t>
+  </si>
+  <si>
+    <t>Red Hot</t>
+  </si>
+  <si>
+    <t>Helter Skelter</t>
+  </si>
+  <si>
+    <t>God Bless The Children Of The Beast</t>
+  </si>
+  <si>
+    <t>Glam Metal, Heavy Metal [Sleaze Metal, Hard Rock, Shock Rock, Sunset Strip Metal]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η κεντρική δήλωση του δίσκου και ένα από τα καθοριστικά songs του early glam metal. Το «shout at the devil» δεν είναι απαραίτητα πρόσκληση στο κακό· στον κόσμο του τραγουδιού λειτουργεί ως πρόκληση προς τον φόβο, την αυθεντία και την υποκρισία που θέλει να ελέγξει την rock κουλτούρα. Το riff του Mick Mars είναι βαρύ, απλό και αμέσως αναγνωρίσιμο, ενώ τα drums του Tommy Lee δίνουν marching, σχεδόν στρατιωτική ώθηση. Ο Vince Neil τραγουδά με καθαρό sleaze-metal swagger, όμως η μπάντα έχει αρκετό πραγματικό βάρος ώστε να μην ακούγεται σαν cartoon. Η μετάβαση από το “In The Beginning” στο βασικό riff είναι μία από τις καλύτερες εισόδους σε ’80s metal album. </t>
+  </si>
+  <si>
+    <t>Πιο γρήγορο, πιο ωμό και λιγότερο «MTV-polished», το “Bastard” στρέφει την ένταση του δίσκου προς μια πιο επιθετική street-metal κατεύθυνση. Ο τίτλος χρησιμοποιείται σαν κατηγορία και κραυγή οργής· η μουσική απαντά με σύντομο, σκληρό riffing, κοφτή ρυθμική βάση και φωνητικά που δεν προσπαθούν να είναι κομψά. Είναι από τα tracks που αποδεικνύουν ότι το album δεν είναι μόνο για image και singles. Δεν έχει το ίδιο τεράστιο hook με το “Looks That Kill”, αλλά είναι πιο κοντά σε καθαρή hard/heavy-metal εκτόνωση και λειτουργεί πολύ σωστά ως αντίθεση μετά το βαρύ mid-tempo προηγούμενο τραγούδι.</t>
+  </si>
+  <si>
+    <t>Σύντομο, σκοτεινό προοίμιο με spoken-word/horror αίσθηση, όχι πλήρες τραγούδι. Η λειτουργία του είναι να χτίσει το «σατανικό» και θεατρικό πλαίσιο του album πριν μπει το title track. Οι Mötley Crüe αξιοποιούν τη γλώσσα της απαγορευμένης τελετής και του occult χωρίς να επιχειρούν θρησκευτική ή φιλοσοφική ανάλυση, είναι shock-rock σκηνογραφία, φτιαγμένη να προκαλέσει την ηθική υστερία της εποχής και να δώσει μεγαλύτερη δραματικότητα στην είσοδο της μπάντας. Ως σύνθεση είναι περιορισμένο, αλλά ως εισαγωγή λειτουργεί άψογα , το album δεν ξεκινά απλώς, «ανοίγει η αυλαία».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το πιο εμβληματικό riff track του δίσκου και η σύνθεση που κάνει σαφές γιατί οι Mötley Crüe ξεχώρισαν στη Sunset Strip σκηνή. Η “looks that kill” γυναίκα είναι μια φιγούρα θανατηφόρας έλξης, γοητευτική, επικίνδυνη και σχεδόν υπερφυσική. Η θεματική είναι κλασικό sleaze-metal υλικό, αλλά η μουσική είναι πολύ πιο αυστηρή από ένα απλό sex-and-party τραγούδι. Ο Mars χτίζει με κιθάρα που έχει πραγματική απειλή, η μπάντα παίζει σε βαριά mid-tempo κίνηση και το chorus είναι σύντομο, ακαριαίο και σχεδιασμένο για να μείνει. Ήταν το lead single του album και έγινε θεμέλιο του Crüe ήχου, glam εμφάνιση, heavy riffs και μόνιμη αίσθηση κινδύνου. </t>
+  </si>
+  <si>
+    <t>Σύντομο ακουστικό κιθαριστικό interlude από τον Mick Mars, που χαμηλώνει δραστικά την ένταση μετά το “Bastard”. Ο τίτλος κρατά τη σκοτεινή, σχεδόν βλάσφημη γλώσσα του δίσκου, αλλά η μουσική είναι μελωδική και εύθραυστη, όχι επιθετική. Η λειτουργία του είναι sequencing, δίνει χώρο στην A πλευρά και προετοιμάζει το έδαφος για την πιο θεατρική διασκευή του “Helter Skelter”. Ως αυτοτελές κομμάτι έχει περιορισμένο βάρος, όμως δείχνει ότι ο Mars μπορούσε να προσθέσει μελωδία και ατμόσφαιρα πέρα από τα μεγάλα riffs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η διασκευή στους Beatles μετατρέπει το πρωτότυπο σε σκοτεινότερο, πιο επιθετικό hard-rock κομμάτι. Οι Mötley Crüe ακολουθούν το chaotic, σχεδόν απειλητικό στοιχείο που ήδη υπάρχει στο τραγούδι των Beatles, αλλά το ντύνουν με heavy κιθάρες, μεγαλύτερο drum impact και sleaze-metal φωνητικά. Η επιλογή ταιριάζει απόλυτα στο Shout At The Devil, “helter skelter” σημαίνει χάος, σύγχυση και ανεξέλεγκτη κίνηση , ακριβώς το κλίμα που επιδιώκει η μπάντα. Δεν ξεπερνά το original σε σύνθεση, αλλά ως διασκευή έχει νόημα και δίνει στον δίσκο μια ακόμη layer classic-rock συνείδησης. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η B πλευρά ανοίγει με από τις πιο γρήγορες και έντονες στιγμές του album. Ο τίτλος είναι διφορούμενος , θερμότητα, πάθος, κίνδυνος , και η μουσική επιλέγει αδιάκοπο momentum, speedier riffing, driving drums και κιθαριστικό solo που δίνει στον Mick Mars χώρο να γίνει περισσότερο τεχνικός. Το “Red Hot” είναι ένα από τα tracks που αναδεικνύουν την heavy-metal πλευρά της μπάντας, όχι απλώς το glam image. Η εξωτερική αποτίμηση το καταγράφει συχνά ανάμεσα στα σημαντικά deep cuts του δίσκου, ενώ η RYM το αναφέρει μαζί με τα “Looks That Kill” και “Shout At The Devil” ως από τα greatest songs του album. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Από τα πιο τέλεια δομημένα Crüe τραγούδια. Η ιδέα της ηλικίας και του έρωτα γίνεται εδώ σχεδόν αντίστροφη από μια ρομαντική μπαλάντα, ο αφηγητής δηλώνει ότι είναι πολύ νέος για να παγιδευτεί συναισθηματικά. Το riff έχει ακαριαία κίνηση, η παραγωγή δίνει χώρο σε κάθε μέρος της μπάντας και το chorus είναι σχεδιασμένο για arena response. Παρότι είναι μελωδικότερο και πιο «εμπορικό» από το “Bastard”, δεν χάνει την ένταση ούτε τη streetwise αυτοπεποίθηση. Ήταν το τρίτο μεγάλο single του album και έφτασε στο Νο. 90 του Billboard Hot 100, ενώ οι user track ratings το κατατάσσουν σταθερά στα δύο/τρία κορυφαία songs του LP. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggressive street-metal track με τίτλο που λειτουργεί σαν προτροπή προς κάποιον νεότερο να μπει στη ζωή/σκηνή και να επιβληθεί. Το riffing είναι κοφτό, τα drums επιτακτικά και η φωνή του Neil έχει περισσότερο attitude παρά μελωδική λεπτότητα. Δεν είναι τόσο γνωστό όσο τα singles, όμως είναι από τα πιο καθαρά παραδείγματα της ικανότητας του album να διατηρεί ένταση και μετά τα hits. Οι εξωτερικές track βαθμολογίες το δείχνουν ως ισχυρό deep cut, περίπου 91,7/100 στο Metal Kingdom και 90/100 στο Album of the Year user data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleaze-rock κομμάτι που παίζει με την ιδέα της γρήγορης ερωτικής κατάκτησης. Οι στίχοι και η εικόνα είναι τυπικά Mötley Crüe , υπερβολικοί, σεξουαλικοί και καθόλου λεπτοί , όμως το τραγούδι σώζεται από το groove, η κιθάρα έχει bluesy/dirty χροιά, τα drums κινούνται με swagger και το refrain μένει. Δεν είναι το πιο σύνθετο ή ουσιαστικό σημείο του album, αλλά είναι πολύ αποτελεσματικό ως late-night Sunset Strip hard rock. Οι δημόσιες track ratings το τοποθετούν μάλιστα υψηλότερα από αρκετά πιο διάσημα tracks, κάτι που υποδεικνύει τη διαχρονική εκτίμηση των fans για τη sleazy πλευρά του δίσκου. </t>
+  </si>
+  <si>
+    <t>Το κλείσιμο επιλέγει σκοτεινότερο και πιο ατμοσφαιρικό ύφος αντί για άλλο γρήγορο party rocker. Η “danger” είναι μια γυναικεία ή συμβολική φιγούρα απειλής, αλλά η μουσική αφήνει την εικόνα πιο ανοιχτή, mid-tempo ένταση, πιο μελωδική φωνητική γραμμή και κιθάρα που χτίζει αίσθηση νυχτερινής αστάθειας. Ως finale λειτουργεί πολύ καλύτερα από ένα απλό chant track, επειδή δείχνει ότι η μπάντα μπορούσε να χειριστεί και πιο σκοτεινό mood. Δεν είναι full power ballad, αλλά έχει στοιχεία δραματικής hard-rock μπαλάντας και αφήνει το album να τελειώσει με αίσθηση απειλής αντί με εύκολη θριαμβευτική λύση.</t>
+  </si>
+  <si>
+    <t>Dark Ambient, Heavy Metal [Horror Intro, Spoken-word Interlude, Theatrical Shock Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Glam Metal [Anthemic Heavy Metal, Shock Rock, Sleaze Metal]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Heavy Metal [Sleaze Metal, Arena Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Heavy Rock, Aggressive Metal, Street Metal]</t>
+  </si>
+  <si>
+    <t>Instrumental Rock, Hard Rock [Acoustic Guitar Interlude, Melodic Guitar Piece]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Beatles Cover, Dark Hard Rock, Shock Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Glam Metal [Fast Metal, Sleaze Rock, Arena Riff Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Heavy Metal [Melodic Metal, Arena Rock, Power-Hook Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Street Metal, Aggressive Riff Rock, Sleaze Metal]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Sleaze Rock, Sexualized Hard Rock, Bluesy Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Atmospheric Album Closer, Power Ballad elements]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12981,8 +13098,22 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12992,6 +13123,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F4F4F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13039,7 +13176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -13112,6 +13249,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13423,7 +13566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -17083,6 +17226,38 @@
       </c>
       <c r="J114" s="11" t="s">
         <v>3849</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>3877</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>3878</v>
+      </c>
+      <c r="D115" s="6">
+        <v>1983</v>
+      </c>
+      <c r="E115" s="10">
+        <v>3.42</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>3893</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>3882</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>3881</v>
+      </c>
+      <c r="I115" s="11" t="s">
+        <v>3880</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>3879</v>
       </c>
     </row>
   </sheetData>
@@ -17310,6 +17485,8 @@
     <hyperlink ref="J113" r:id="rId221" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
     <hyperlink ref="I114" r:id="rId222" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
     <hyperlink ref="J114" r:id="rId223" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
+    <hyperlink ref="J115" r:id="rId224" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
+    <hyperlink ref="I115" r:id="rId225" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17317,7 +17494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1082"/>
+  <dimension ref="A1:I1093"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -46724,6 +46901,309 @@
         <v>240</v>
       </c>
     </row>
+    <row r="1083" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1083" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1083" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1083" s="7" t="s">
+        <v>3883</v>
+      </c>
+      <c r="D1083" s="26" t="s">
+        <v>3905</v>
+      </c>
+      <c r="E1083" s="20">
+        <v>2.98</v>
+      </c>
+      <c r="F1083" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1083" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1083" s="25" t="s">
+        <v>3896</v>
+      </c>
+      <c r="I1083" s="6"/>
+    </row>
+    <row r="1084" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1084" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1084" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1084" s="7" t="s">
+        <v>3878</v>
+      </c>
+      <c r="D1084" s="26" t="s">
+        <v>3906</v>
+      </c>
+      <c r="E1084" s="20">
+        <v>4.04</v>
+      </c>
+      <c r="F1084" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1084" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1084" s="25" t="s">
+        <v>3894</v>
+      </c>
+      <c r="I1084" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1085" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1085" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1085" s="7" t="s">
+        <v>3884</v>
+      </c>
+      <c r="D1085" s="26" t="s">
+        <v>3907</v>
+      </c>
+      <c r="E1085" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1085" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1085" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1085" s="25" t="s">
+        <v>3897</v>
+      </c>
+      <c r="I1085" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1086" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1086" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1086" s="7" t="s">
+        <v>3885</v>
+      </c>
+      <c r="D1086" s="26" t="s">
+        <v>3908</v>
+      </c>
+      <c r="E1086" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F1086" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1086" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1086" s="25" t="s">
+        <v>3895</v>
+      </c>
+      <c r="I1086" s="6"/>
+    </row>
+    <row r="1087" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1087" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1087" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1087" s="7" t="s">
+        <v>3892</v>
+      </c>
+      <c r="D1087" s="26" t="s">
+        <v>3909</v>
+      </c>
+      <c r="E1087" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F1087" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1087" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1087" s="25" t="s">
+        <v>3898</v>
+      </c>
+      <c r="I1087" s="6"/>
+    </row>
+    <row r="1088" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1088" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1088" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1088" s="7" t="s">
+        <v>3891</v>
+      </c>
+      <c r="D1088" s="26" t="s">
+        <v>3910</v>
+      </c>
+      <c r="E1088" s="20">
+        <v>3.4</v>
+      </c>
+      <c r="F1088" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1088" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1088" s="25" t="s">
+        <v>3899</v>
+      </c>
+      <c r="I1088" s="6"/>
+    </row>
+    <row r="1089" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1089" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1089" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1089" s="7" t="s">
+        <v>3890</v>
+      </c>
+      <c r="D1089" s="26" t="s">
+        <v>3911</v>
+      </c>
+      <c r="E1089" s="20">
+        <v>3.58</v>
+      </c>
+      <c r="F1089" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1089" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1089" s="25" t="s">
+        <v>3900</v>
+      </c>
+      <c r="I1089" s="6"/>
+    </row>
+    <row r="1090" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1090" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1090" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1090" s="7" t="s">
+        <v>3889</v>
+      </c>
+      <c r="D1090" s="26" t="s">
+        <v>3912</v>
+      </c>
+      <c r="E1090" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F1090" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1090" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1090" s="25" t="s">
+        <v>3901</v>
+      </c>
+      <c r="I1090" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1091" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1091" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1091" s="7" t="s">
+        <v>3888</v>
+      </c>
+      <c r="D1091" s="26" t="s">
+        <v>3913</v>
+      </c>
+      <c r="E1091" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F1091" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1091" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1091" s="25" t="s">
+        <v>3902</v>
+      </c>
+      <c r="I1091" s="6"/>
+    </row>
+    <row r="1092" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1092" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1092" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1092" s="7" t="s">
+        <v>3887</v>
+      </c>
+      <c r="D1092" s="26" t="s">
+        <v>3914</v>
+      </c>
+      <c r="E1092" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F1092" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1092" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1092" s="25" t="s">
+        <v>3903</v>
+      </c>
+      <c r="I1092" s="6"/>
+    </row>
+    <row r="1093" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1093" s="6">
+        <v>10824930</v>
+      </c>
+      <c r="B1093" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1093" s="7" t="s">
+        <v>3886</v>
+      </c>
+      <c r="D1093" s="26" t="s">
+        <v>3915</v>
+      </c>
+      <c r="E1093" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F1093" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1093" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1093" s="25" t="s">
+        <v>3904</v>
+      </c>
+      <c r="I1093" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429E1795-3E54-4977-93F2-0C2278523C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C80D6F-0157-4D84-A8C3-DCACB2F65041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="3916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4276" uniqueCount="3952">
   <si>
     <t>No</t>
   </si>
@@ -12759,9 +12759,6 @@
     <t>ATCO Records – 790563-1 (Greece, May 1987, LP, Album, Stereo). Manufactured by G.P.I. S.A. (MT410), manufactured for και distributed by WEA Records S.A. (W609), με lacquer cut από G.P.I. S.A. και printed by Ορφανός - Σκαλτσάς.</t>
   </si>
   <si>
-    <t>Το Fighting The World κυκλοφόρησε τον Μάιο του 1987 και αποτελεί το πέμπτο studio album των Manowar. Είναι πρωτοποριακό στην ιστορία του heavy metal καθώς υπήρξε από τα πρώτα metal άλμπουμ που ηχογραφήθηκαν και μιξαρίστηκαν εξ ολοκλήρου ψηφιακά (χρησιμοποιώντας το σύστημα Synclavier). Την παραγωγή υπογράφουν οι ίδιοι οι Manowar, με τον Howie Weinberg στο mastering (Masterdisk) και τον Richard Breen στον ψηφιακό προγραμματισμό και τη μίξη. Το άλμπουμ περιλαμβάνει ιστορικές στιγμές, όπως η αφηγηναστική συμμετοχή του θρυλικού Orson Welles στο κομμάτι "Defender", συνοδευόμενου από τη General VanClibreen Philharmonic. Η ελληνική έκδοση της WEA/ATCO κυκλοφόρησε με εσωτερικό μονόφυλλο sleeve και stamped runouts.</t>
-  </si>
-  <si>
     <t>https://www.discogs.com/release/12991988-Manowar-Fighting-The-World</t>
   </si>
   <si>
@@ -12894,9 +12891,6 @@
     <t>Elektra – 96-0289-1, Elektra – 960 289-1 (Europe, 1983, LP, Album, Reissue). Manufactured by Record Service GmbH και pressed by Record Service Alsdorf στη Γερμανία, με Mastering από τον George Marino στη Sterling Sound.</t>
   </si>
   <si>
-    <t>Το Shout At The Devil είναι το δεύτερο studio album των Mötley Crüe, κυκλοφόρησε αρχικά το 1983 και καθιέρωσε παγκοσμίως το συγκρότημα ως ηγέτη της 80s glam/heavy metal σκηνής. Η παραγωγή έγινε από τον Tom Werman στα Cherokee Studios στο Λος Άντζελες, συνδυάζοντας την ωμή επιθετικότητα του heavy metal με τεράστια, ραδιοφωνικά hooks. Η αισθητική του δίσκου (με το εμβληματικό πεντάγραμμο/pentagram εξώφυλλο) και κομμάτια-ορόσημα όπως η διασκευή στο "Helter Skelter" των Beatles άφησαν εποχή. Η συγκεκριμένη ευρωπαϊκή κοπή της Record Service Alsdorf διαθέτει κόκκινες ετικέτες (red labels), non-gatefold εξώφυλλο και περιλαμβάνει το τυπωμένο εσωτερικό ένθετο (printed inner-sleeve).</t>
-  </si>
-  <si>
     <t>In The Beginning</t>
   </si>
   <si>
@@ -12994,13 +12988,127 @@
   </si>
   <si>
     <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Atmospheric Album Closer, Power Ballad elements]</t>
+  </si>
+  <si>
+    <t>Dr. Feelgood</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Fighting The World κυκλοφόρησε τον Μάιο του 1987 και αποτελεί το πέμπτο studio album των Manowar. Είναι πρωτοποριακό στην ιστορία του heavy metal καθώς υπήρξε από τα πρώτα metal άλμπουμ που ηχογραφήθηκαν και μιξαρίστηκαν εξ ολοκλήρου ψηφιακά (χρησιμοποιώντας το σύστημα Synclavier). Την παραγωγή υπογράφουν οι ίδιοι οι Manowar, με τον Howie Weinberg στο mastering (Masterdisk) και τον Richard Breen στον ψηφιακό προγραμματισμό και τη μίξη. Το άλμπουμ περιλαμβάνει ιστορικές στιγμές, όπως η αφηγηναστική συμμετοχή του θρυλικού Orson Welles στο κομμάτι "Defender", συνοδευόμενου από τη General VanClibreen Philharmonic. Η ελληνική έκδοση της WEA/ATCO κυκλοφόρησε με εσωτερικό μονόφυλλο sleeve και stamped runouts.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Shout At The Devil είναι το δεύτερο studio album των Mötley Crüe, κυκλοφόρησε αρχικά το 1983 και καθιέρωσε παγκοσμίως το συγκρότημα ως ηγέτη της 80s glam/heavy metal σκηνής. Η παραγωγή έγινε από τον Tom Werman στα Cherokee Studios στο Λος Άντζελες, συνδυάζοντας την ωμή επιθετικότητα του heavy metal με τεράστια, ραδιοφωνικά hooks. Η αισθητική του δίσκου (με το εμβληματικό πεντάγραμμο/pentagram εξώφυλλο) και κομμάτια-ορόσημα όπως η διασκευή στο "Helter Skelter" των Beatles άφησαν εποχή. Η συγκεκριμένη ευρωπαϊκή κοπή της Record Service Alsdorf διαθέτει κόκκινες ετικέτες (red labels), non-gatefold εξώφυλλο και περιλαμβάνει το τυπωμένο εσωτερικό ένθετο (printed inner-sleeve).</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2589429-M%C3%B6tley-Cr%C3%BCe-Dr-Feelgood</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/hop80y3_vtHkYWvFLKm9VPk5w9FXLsxEF6ZsU7nlue8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI1ODk0/MjktMTQ2NDE2Mzgw/Mi0xNDM3LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>T.n.T. (Terror ’n Tinseltown)</t>
+  </si>
+  <si>
+    <t>Slice Of Your Pie</t>
+  </si>
+  <si>
+    <t>Kickstart My Heart</t>
+  </si>
+  <si>
+    <t>Without You</t>
+  </si>
+  <si>
+    <t>Same Ol’ Situation (S.O.S.)</t>
+  </si>
+  <si>
+    <t>Sticky Sweet</t>
+  </si>
+  <si>
+    <t>She Goes Down</t>
+  </si>
+  <si>
+    <t>Don’t Go Away Mad (Just Go Away)</t>
+  </si>
+  <si>
+    <t>Time For Change</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Heavy Glam Metal, Arena Rock, Sleaze Metal, Bluesy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Dark Ambient, Hard Rock [Spoken-word Intro, Horror Atmosphere, Theatrical Shock Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Heavy Glam Metal, Bluesy Riff Rock, Sleaze Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Rock, Bluesy Hard Rock, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Boogie Rock, Horn-Driven Hard Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Arena Metal, Speedy Glam Metal, Adrenaline Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Pop Metal, Arena Rock, Melodic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Rock, Bluesy Riff Rock, Sexualized Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Sleaze Metal, Blues-Rock groove, Dark Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Pop Rock [Melodic Hard Rock, Power-Pop Metal, Breakup Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Reflective Power Ballad, Piano Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Elektra – 960829-1 (Greece, 1989, LP, Album, Stereo). Manufactured by G.P.I. S.A., με ελληνική ετικέτα και εσωτερικό ένθετο με στίχους, credits και φωτογραφίες.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Dr. Feelgood κυκλοφόρησε τον Σεπτέμβριο του 1989 και αποτελεί το εμπορικότερο και πιο καλοδουλεμένο άλμπουμ στην καριέρα των Mötley Crüe, φτάνοντας στο #1 του Billboard 200. Την παραγωγή ανέλαβε ο Bob Rock στα Little Mountain Sound Studios στο Βανκούβερ, εισάγοντας έναν τεράστιο, γυαλισμένο, ογκώδη ήχο που επανακαθόρισε τα δεδομένα του arena rock και του heavy metal στις αρχές της δεκαετίας του '90. Το mastering έγινε από τον George Marino στη Sterling Sound. Η ελληνική έκδοση ξεχωρίζει για τη χρήση κοπής Direct Metal Mastering (DMM), η οποία προσφέρει εξαιρετική διαύγεια στα πρίμα και σφιχτό, ελεγχόμενο χαμηλό φάσμα.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleaze-rock τραγούδι που συνδέει την ερωτική επιθυμία με την ανάγκη να «πάρεις το κομμάτι σου» από τη ζωή. Η φράση είναι ταυτόχρονα υλική, ερωτική και ανταγωνιστική· ταιριάζει απόλυτα στη χαρακτηριστική Crüe υπερβολή. Το riffing είναι bluesy και βαρύ, με τον Bob Rock να κρατά το low end συμπαγές και τις κιθάρες του Mars να κινούνται ανάμεσα σε groove και metal bite. Ο Vince Neil παίζει φυσαρμόνικα, μικρή λεπτομέρεια που δίνει στο τραγούδι dirty bar-rock χρώμα. Δεν έχει το μοναδικό impact του title track, αλλά είναι πολύ δυνατό deep cut και δείχνει καλά την πιο blues-influenced πλευρά του album. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το πιο boogie, bar-room και rhythm-driven κομμάτι της A πλευράς. Ο τίτλος χρησιμοποιεί τη «κροταλία» ως εικόνα κινδύνου και σωματικής κίνησης, αλλά το τραγούδι παίζει περισσότερο σαν party-rock groove παρά σαν σκοτεινή απειλή. Τα πνευστά, το honky-tonk πιάνο και η πιο loose ρυθμική αίσθηση το ξεχωρίζουν από τα τυπικά glam-metal tracks του δίσκου. Ουσιαστικά είναι μια απόπειρα των Crüe να φέρουν classic rock ’n’ roll/boogie χρώμα μέσα στην polished Bob Rock παραγωγή. Δεν είναι κεντρικό κομμάτι του album, αλλά προσφέρει χρήσιμη αλλαγή υφής και δείχνει ότι η μπάντα δεν λειτουργεί μόνο με μεγάλα metal riffs. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η μεγάλη power ballad της A πλευράς και μία από τις πιο συναισθηματικά άμεσες ερμηνείες του Vince Neil. Μετά την υπερβολή του “Kickstart My Heart”, το τραγούδι χαμηλώνει τον τόνο και μιλά για απώλεια, ανάγκη και αδυναμία να σταθείς χωρίς ένα συγκεκριμένο πρόσωπο. Η σύνθεση κινείται από πιο συγκρατημένα verse σε μεγάλο arena refrain, χωρίς να αποβάλλει το hard-rock σώμα της. Η κιθάρα του Mars προσθέτει μελωδική ένταση αντί για απλό γυαλισμένο slow-dance solo. Είναι χαρακτηριστικό power ballad της εποχής, αλλά η παραγωγή και το φωνητικό συναίσθημα το κρατούν πάνω από το μέσο επίπεδο του είδους. </t>
+  </si>
+  <si>
+    <t>Σύντομο, κινηματογραφικό intro που μεταφέρει αμέσως τον ακροατή σε έναν κόσμο Los Angeles παρακμής, βίας, νυχτερινής υπερβολής και φαντασιακού τρόμου. Το “Terror ’n Tinseltown” παίζει με την αντίθεση ανάμεσα στη λάμψη του Hollywood και στην σκοτεινή πλευρά του , ναρκωτικά, εγκληματικότητα, εξάρτηση και ηθική φθορά. Δεν είναι πλήρες τραγούδι, αλλά το spoken-word/horror πλαίσιο λειτουργεί σωστά ως προθάλαμος, προετοιμάζει το “Dr. Feelgood”, όπου ο υπόκοσμος του L.A. αποκτά συγκεκριμένο πρόσωπο.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η μεγάλη, βαριά κορύφωση του album και ένα από τα πιο αποτελεσματικά Mötley Crüe riffs. Ο Dr. Feelgood είναι η φιγούρα του dealer , ένας άνθρωπος που πουλά ευφορία, εξάρτηση και καταστροφή κάτω από την υπόσχεση της ευχαρίστησης. Η μπάντα μετατρέπει αυτή την εικόνα σε slow, menacing heavy-glam groove, το riff του Mick Mars είναι κοφτό και απειλητικό, ο Tommy Lee παίζει με τεράστιο drum impact και ο Vince Neil δίνει στον χαρακτήρα snake-oil swagger. Η παραγωγή του Bob Rock κάνει τον ήχο πιο βαρύ και πιο τρισδιάστατο από τους προηγούμενους δίσκους, ενώ η «δαιμονική» φωνή του Mars προσθέτει horror στοιχείο. Είναι ακριβώς το τραγούδι όπου οι Mötley Crüe ακούγονται σαν μεγαλύτερη και πιο πειθαρχημένη μπάντα, χωρίς να χάνουν τη βρομιά τους. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η απόλυτη αδρεναλινική στιγμή του δίσκου και ένα από τα πιο αναγνωρίσιμα late-’80s hard-rock τραγούδια. Η σύνθεση είναι εμπνευσμένη από την εμπειρία του Nikki Sixx όταν επανήλθε στη ζωή μετά από overdose, οπότε το “kickstart” δεν είναι απλώς εικόνα ταχύτητας, μιλά κυριολεκτικά για καρδιά που ξαναρχίζει να χτυπά. Η μουσική ακολουθεί την ιστορία με γρήγορο, ασταμάτητο momentum, propulsive beat από τον Tommy Lee, κοφτό riffing και chorus που λειτουργεί σαν έκρηξη. Η παραγωγή του Bob Rock εδώ είναι υποδειγματική για το είδος, κάθε κιθάρα, drum hit και φωνητικό layer έχουν καθαρότητα, αλλά ο ήχος παραμένει επιθετικός. Το BBC ξεχωρίζει ακριβώς το drum drive και την αδρεναλινική ώθηση του track, ενώ οι περισσότερες αναδρομικές κριτικές το αντιμετωπίζουν ως αναμφισβήτητο Crüe classic. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ένα από τα πιο άμεσα και πιο «πιασάρικα» τραγούδια του δίσκου. Ο τίτλος μιλά για επανάληψη ενός καταστροφικού μοτίβου , άλλη μία σχέση, άλλη μία νύχτα, το ίδιο μπλέξιμο , και η μουσική το μετατρέπει σε φωτεινό, επιθετικό pop-metal chorus. Ο Tommy Lee και ο Vince Neil συνυπογράφουν, κάτι που εξηγεί ίσως την πιο straight-ahead, μελωδική δομή του. Το riff δεν έχει τη σκοτεινή βαρύτητα του “Dr. Feelgood”, αλλά το track λειτουργεί άψογα ως arena-rock single, σφιχτή διάρκεια, άμεσο hook, φωνητικά που μένουν και παραγωγή που δεν αφήνει κενό χώρο. Το BBC αναφέρει ειδικά το addictive hook του ως δείγμα της δύναμης του δίσκου. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Επιστροφή στη sleaze/bluesy πλευρά, με τίτλο που συνδυάζει γλύκα και κολλητική, επικίνδυνη επιθυμία. Το τραγούδι δεν επιδιώκει κοινωνικό σχόλιο ή συναισθηματική λεπτότητα· είναι groove-led hard rock, με τον Mars να δίνει dirty riff texture και τον Neil να τραγουδά με το γνώριμο swagger. Ο shaker του Neil προσθέτει μικρή ρυθμική λεπτομέρεια, αλλά η βασική αρετή είναι η οικονομία, το κομμάτι δεν προσπαθεί να γίνει μεγαλύτερο από όσο χρειάζεται. Δεν έχει το σπουδαίο hook των singles, γι’ αυτό η βαθμολογία του είναι λίγο χαμηλότερη, όμως διατηρεί σωστά την ατμόσφαιρα της B πλευράς. </t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο βρώμικα και πιο βαριά groove tracks του album. Ο τίτλος παραπέμπει σε ερωτική υπερβολή, αλλά μουσικά το τραγούδι έχει πιο υποβλητικό, σχεδόν απειλητικό χαρακτήρα από ένα απλό party number. Το riff είναι slow-burn και ο ήχος του Bob Rock το κάνει να μοιάζει βαρύτερο από την glam-metal επιφάνειά του. Η μπάντα ακούγεται άνετη μέσα στο groove, χωρίς να χρειάζεται τεράστιο chorus. Είναι χαρακτηριστικό deep cut, όχι το πιο εύκολο ή πιο ραδιοφωνικό, αλλά δείχνει την ικανότητα των Crüe να δημιουργούν sexy, dangerous hard rock με βάρος και όχι μόνο με image.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η πιο φωτεινή και πιο pop-rock στιγμή της B πλευράς. Ο τίτλος ανατρέπει την κλασική breakup φράση, δεν ζητά από τον/την άλλο/η να φύγει θυμωμένος/η, ζητά απλώς να φύγει. Το τραγούδι έχει μελωδία που θα μπορούσε να λειτουργήσει σε mainstream rock radio, αλλά η μπάντα την κρατά μέσα στο hard-rock πλαίσιο με guitar crunch και δυναμικά backing vocals. Είναι λιγότερο βαρύ από το title track και λιγότερο αδρεναλινικό από το “Kickstart My Heart”, όμως ως single λειτουργεί εξαιρετικά, έχει άμεσο chorus, χιούμορ και αρκετή ενέργεια ώστε να μη γίνει απλή pop μπαλάντα. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το πιο αναστοχαστικό και ασυνήθιστα ώριμο κλείσιμο ενός Mötley Crüe album. Με πιάνο/όργανο από τον Nikki Sixx και bass από τον Bob Rock, το τραγούδι αφήνει προσωρινά το sex-and-sleaze persona και κοιτά πίσω στα χρόνια αυτοκαταστροφής της μπάντας. Η «ώρα για αλλαγή» έχει πραγματικό βάρος επειδή το Dr. Feelgood γράφτηκε μετά την περίοδο νηφαλιότητας τους, δεν είναι απλώς generic motivational ballad, αλλά απολογισμός μιας μπάντας που επέζησε από την ίδια της την εικόνα. Η μελωδία είναι πιο ήρεμη, η ερμηνεία πιο συγκρατημένη και η παραγωγή δίνει χώρο στο μήνυμα αντί για riff. Ως τέλος, είναι ιδανικό, μετά το decadence, την εξάρτηση, την ταχύτητα και την ερωτική υπερβολή των προηγούμενων tracks, το album καταλήγει σε αναγνώριση ότι η επιβίωση απαιτεί μεταμόρφωση. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13112,6 +13220,13 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -13176,7 +13291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -13255,6 +13370,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13566,7 +13684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -17213,19 +17331,19 @@
         <v>3.29</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>3847</v>
+        <v>3915</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>3846</v>
       </c>
       <c r="I114" s="11" t="s">
+        <v>3847</v>
+      </c>
+      <c r="J114" s="11" t="s">
         <v>3848</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>3849</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -17233,10 +17351,10 @@
         <v>10824930</v>
       </c>
       <c r="B115" s="7" t="s">
+        <v>3876</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>3877</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>3878</v>
       </c>
       <c r="D115" s="6">
         <v>1983</v>
@@ -17245,19 +17363,51 @@
         <v>3.42</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>3882</v>
+        <v>3916</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>3879</v>
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>3876</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D116" s="6">
+        <v>1989</v>
+      </c>
+      <c r="E116" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>3928</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>3940</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>3939</v>
+      </c>
+      <c r="I116" s="11" t="s">
+        <v>3917</v>
+      </c>
+      <c r="J116" s="11" t="s">
+        <v>3918</v>
       </c>
     </row>
   </sheetData>
@@ -17487,6 +17637,8 @@
     <hyperlink ref="J114" r:id="rId223" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
     <hyperlink ref="J115" r:id="rId224" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
     <hyperlink ref="I115" r:id="rId225" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
+    <hyperlink ref="I116" r:id="rId226" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
+    <hyperlink ref="J116" r:id="rId227" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17494,7 +17646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1093"/>
+  <dimension ref="A1:I1104"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -46663,7 +46815,7 @@
         <v>3845</v>
       </c>
       <c r="D1074" s="7" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="E1074" s="20">
         <v>3.93</v>
@@ -46675,7 +46827,7 @@
         <v>4.2</v>
       </c>
       <c r="H1074" s="9" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="I1074" s="6" t="s">
         <v>240</v>
@@ -46689,10 +46841,10 @@
         <v>2</v>
       </c>
       <c r="C1075" s="7" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="D1075" s="7" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="E1075" s="20">
         <v>3.28</v>
@@ -46704,7 +46856,7 @@
         <v>4</v>
       </c>
       <c r="H1075" s="9" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="I1075" s="6"/>
     </row>
@@ -46716,10 +46868,10 @@
         <v>3</v>
       </c>
       <c r="C1076" s="7" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="D1076" s="7" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="E1076" s="20">
         <v>3.53</v>
@@ -46731,7 +46883,7 @@
         <v>4.5</v>
       </c>
       <c r="H1076" s="9" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="I1076" s="6"/>
     </row>
@@ -46743,10 +46895,10 @@
         <v>4</v>
       </c>
       <c r="C1077" s="7" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="D1077" s="7" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="E1077" s="20">
         <v>3.43</v>
@@ -46758,7 +46910,7 @@
         <v>3.9</v>
       </c>
       <c r="H1077" s="9" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="I1077" s="6"/>
     </row>
@@ -46770,10 +46922,10 @@
         <v>5</v>
       </c>
       <c r="C1078" s="7" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="D1078" s="7" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="E1078" s="20">
         <v>3.76</v>
@@ -46785,7 +46937,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1078" s="9" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="I1078" s="6" t="s">
         <v>240</v>
@@ -46799,10 +46951,10 @@
         <v>6</v>
       </c>
       <c r="C1079" s="7" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="D1079" s="7" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="E1079" s="20">
         <v>2.77</v>
@@ -46814,7 +46966,7 @@
         <v>3.8</v>
       </c>
       <c r="H1079" s="9" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="I1079" s="6"/>
     </row>
@@ -46826,10 +46978,10 @@
         <v>7</v>
       </c>
       <c r="C1080" s="7" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="D1080" s="7" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="E1080" s="20">
         <v>3.64</v>
@@ -46841,7 +46993,7 @@
         <v>4.3</v>
       </c>
       <c r="H1080" s="9" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="I1080" s="6"/>
     </row>
@@ -46853,10 +47005,10 @@
         <v>8</v>
       </c>
       <c r="C1081" s="7" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="D1081" s="7" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="E1081" s="20">
         <v>2.9</v>
@@ -46868,7 +47020,7 @@
         <v>3.7</v>
       </c>
       <c r="H1081" s="9" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="I1081" s="6"/>
     </row>
@@ -46880,10 +47032,10 @@
         <v>9</v>
       </c>
       <c r="C1082" s="7" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="D1082" s="7" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="E1082" s="20">
         <v>4.13</v>
@@ -46895,7 +47047,7 @@
         <v>4.7</v>
       </c>
       <c r="H1082" s="9" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="I1082" s="6" t="s">
         <v>240</v>
@@ -46909,10 +47061,10 @@
         <v>1</v>
       </c>
       <c r="C1083" s="7" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
       <c r="D1083" s="26" t="s">
-        <v>3905</v>
+        <v>3903</v>
       </c>
       <c r="E1083" s="20">
         <v>2.98</v>
@@ -46924,7 +47076,7 @@
         <v>3.9</v>
       </c>
       <c r="H1083" s="25" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
       <c r="I1083" s="6"/>
     </row>
@@ -46936,10 +47088,10 @@
         <v>2</v>
       </c>
       <c r="C1084" s="7" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="D1084" s="26" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
       <c r="E1084" s="20">
         <v>4.04</v>
@@ -46951,7 +47103,7 @@
         <v>4.7</v>
       </c>
       <c r="H1084" s="25" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
       <c r="I1084" s="6" t="s">
         <v>240</v>
@@ -46965,10 +47117,10 @@
         <v>3</v>
       </c>
       <c r="C1085" s="7" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
       <c r="D1085" s="26" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
       <c r="E1085" s="20">
         <v>4.03</v>
@@ -46980,7 +47132,7 @@
         <v>4.8</v>
       </c>
       <c r="H1085" s="25" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
       <c r="I1085" s="6" t="s">
         <v>240</v>
@@ -46994,10 +47146,10 @@
         <v>4</v>
       </c>
       <c r="C1086" s="7" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
       <c r="D1086" s="26" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
       <c r="E1086" s="20">
         <v>3.61</v>
@@ -47009,7 +47161,7 @@
         <v>4.2</v>
       </c>
       <c r="H1086" s="25" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
       <c r="I1086" s="6"/>
     </row>
@@ -47021,10 +47173,10 @@
         <v>5</v>
       </c>
       <c r="C1087" s="7" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
       <c r="D1087" s="26" t="s">
-        <v>3909</v>
+        <v>3907</v>
       </c>
       <c r="E1087" s="20">
         <v>3.15</v>
@@ -47036,7 +47188,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1087" s="25" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
       <c r="I1087" s="6"/>
     </row>
@@ -47048,10 +47200,10 @@
         <v>6</v>
       </c>
       <c r="C1088" s="7" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
       <c r="D1088" s="26" t="s">
-        <v>3910</v>
+        <v>3908</v>
       </c>
       <c r="E1088" s="20">
         <v>3.4</v>
@@ -47063,7 +47215,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1088" s="25" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
       <c r="I1088" s="6"/>
     </row>
@@ -47075,10 +47227,10 @@
         <v>7</v>
       </c>
       <c r="C1089" s="7" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
       <c r="D1089" s="26" t="s">
-        <v>3911</v>
+        <v>3909</v>
       </c>
       <c r="E1089" s="20">
         <v>3.58</v>
@@ -47090,7 +47242,7 @@
         <v>4.3</v>
       </c>
       <c r="H1089" s="25" t="s">
-        <v>3900</v>
+        <v>3898</v>
       </c>
       <c r="I1089" s="6"/>
     </row>
@@ -47102,10 +47254,10 @@
         <v>8</v>
       </c>
       <c r="C1090" s="7" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
       <c r="D1090" s="26" t="s">
-        <v>3912</v>
+        <v>3910</v>
       </c>
       <c r="E1090" s="20">
         <v>3.9</v>
@@ -47117,7 +47269,7 @@
         <v>4.7</v>
       </c>
       <c r="H1090" s="25" t="s">
-        <v>3901</v>
+        <v>3899</v>
       </c>
       <c r="I1090" s="6" t="s">
         <v>240</v>
@@ -47131,10 +47283,10 @@
         <v>9</v>
       </c>
       <c r="C1091" s="7" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
       <c r="D1091" s="26" t="s">
-        <v>3913</v>
+        <v>3911</v>
       </c>
       <c r="E1091" s="20">
         <v>3.51</v>
@@ -47146,7 +47298,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1091" s="25" t="s">
-        <v>3902</v>
+        <v>3900</v>
       </c>
       <c r="I1091" s="6"/>
     </row>
@@ -47158,10 +47310,10 @@
         <v>10</v>
       </c>
       <c r="C1092" s="7" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
       <c r="D1092" s="26" t="s">
-        <v>3914</v>
+        <v>3912</v>
       </c>
       <c r="E1092" s="20">
         <v>3.43</v>
@@ -47173,7 +47325,7 @@
         <v>4.3</v>
       </c>
       <c r="H1092" s="25" t="s">
-        <v>3903</v>
+        <v>3901</v>
       </c>
       <c r="I1092" s="6"/>
     </row>
@@ -47185,10 +47337,10 @@
         <v>11</v>
       </c>
       <c r="C1093" s="7" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
       <c r="D1093" s="26" t="s">
-        <v>3915</v>
+        <v>3913</v>
       </c>
       <c r="E1093" s="20">
         <v>3.48</v>
@@ -47200,9 +47352,306 @@
         <v>4.5</v>
       </c>
       <c r="H1093" s="25" t="s">
-        <v>3904</v>
+        <v>3902</v>
       </c>
       <c r="I1093" s="6"/>
+    </row>
+    <row r="1094" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1094" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1094" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1094" s="7" t="s">
+        <v>3919</v>
+      </c>
+      <c r="D1094" s="7" t="s">
+        <v>3929</v>
+      </c>
+      <c r="E1094" s="20">
+        <v>2.93</v>
+      </c>
+      <c r="F1094" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="G1094" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="H1094" s="27" t="s">
+        <v>3944</v>
+      </c>
+      <c r="I1094" s="6"/>
+    </row>
+    <row r="1095" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1095" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1095" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1095" s="7" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D1095" s="7" t="s">
+        <v>3930</v>
+      </c>
+      <c r="E1095" s="20">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F1095" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1095" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1095" s="27" t="s">
+        <v>3945</v>
+      </c>
+      <c r="I1095" s="6"/>
+    </row>
+    <row r="1096" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1096" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1096" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1096" s="7" t="s">
+        <v>3920</v>
+      </c>
+      <c r="D1096" s="7" t="s">
+        <v>3931</v>
+      </c>
+      <c r="E1096" s="20">
+        <v>3.22</v>
+      </c>
+      <c r="F1096" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1096" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1096" s="27" t="s">
+        <v>3941</v>
+      </c>
+      <c r="I1096" s="6"/>
+    </row>
+    <row r="1097" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1097" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1097" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1097" s="7" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D1097" s="7" t="s">
+        <v>3932</v>
+      </c>
+      <c r="E1097" s="20">
+        <v>3.32</v>
+      </c>
+      <c r="F1097" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1097" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1097" s="27" t="s">
+        <v>3942</v>
+      </c>
+      <c r="I1097" s="6"/>
+    </row>
+    <row r="1098" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1098" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1098" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1098" s="7" t="s">
+        <v>3921</v>
+      </c>
+      <c r="D1098" s="7" t="s">
+        <v>3933</v>
+      </c>
+      <c r="E1098" s="20">
+        <v>4.18</v>
+      </c>
+      <c r="F1098" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G1098" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1098" s="27" t="s">
+        <v>3946</v>
+      </c>
+      <c r="I1098" s="6"/>
+    </row>
+    <row r="1099" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1099" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1099" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1099" s="7" t="s">
+        <v>3922</v>
+      </c>
+      <c r="D1099" s="7" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E1099" s="20">
+        <v>3.29</v>
+      </c>
+      <c r="F1099" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1099" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1099" s="27" t="s">
+        <v>3943</v>
+      </c>
+      <c r="I1099" s="6"/>
+    </row>
+    <row r="1100" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1100" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1100" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1100" s="7" t="s">
+        <v>3923</v>
+      </c>
+      <c r="D1100" s="7" t="s">
+        <v>3934</v>
+      </c>
+      <c r="E1100" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F1100" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1100" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1100" s="27" t="s">
+        <v>3947</v>
+      </c>
+      <c r="I1100" s="6"/>
+    </row>
+    <row r="1101" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1101" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1101" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1101" s="7" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D1101" s="7" t="s">
+        <v>3935</v>
+      </c>
+      <c r="E1101" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F1101" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1101" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1101" s="27" t="s">
+        <v>3948</v>
+      </c>
+      <c r="I1101" s="6"/>
+    </row>
+    <row r="1102" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1102" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1102" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1102" s="7" t="s">
+        <v>3925</v>
+      </c>
+      <c r="D1102" s="7" t="s">
+        <v>3936</v>
+      </c>
+      <c r="E1102" s="20">
+        <v>3.17</v>
+      </c>
+      <c r="F1102" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1102" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1102" s="27" t="s">
+        <v>3949</v>
+      </c>
+      <c r="I1102" s="6"/>
+    </row>
+    <row r="1103" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1103" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1103" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1103" s="7" t="s">
+        <v>3926</v>
+      </c>
+      <c r="D1103" s="7" t="s">
+        <v>3937</v>
+      </c>
+      <c r="E1103" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F1103" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1103" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1103" s="27" t="s">
+        <v>3950</v>
+      </c>
+      <c r="I1103" s="6"/>
+    </row>
+    <row r="1104" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1104" s="6">
+        <v>2589429</v>
+      </c>
+      <c r="B1104" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1104" s="7" t="s">
+        <v>3927</v>
+      </c>
+      <c r="D1104" s="7" t="s">
+        <v>3938</v>
+      </c>
+      <c r="E1104" s="20">
+        <v>3.12</v>
+      </c>
+      <c r="F1104" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1104" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1104" s="27" t="s">
+        <v>3951</v>
+      </c>
+      <c r="I1104" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C80D6F-0157-4D84-A8C3-DCACB2F65041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999BF74B-5E87-4C24-8A98-93DB417D3E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4276" uniqueCount="3952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4313" uniqueCount="3989">
   <si>
     <t>No</t>
   </si>
@@ -13102,6 +13102,117 @@
   </si>
   <si>
     <t xml:space="preserve">Το πιο αναστοχαστικό και ασυνήθιστα ώριμο κλείσιμο ενός Mötley Crüe album. Με πιάνο/όργανο από τον Nikki Sixx και bass από τον Bob Rock, το τραγούδι αφήνει προσωρινά το sex-and-sleaze persona και κοιτά πίσω στα χρόνια αυτοκαταστροφής της μπάντας. Η «ώρα για αλλαγή» έχει πραγματικό βάρος επειδή το Dr. Feelgood γράφτηκε μετά την περίοδο νηφαλιότητας τους, δεν είναι απλώς generic motivational ballad, αλλά απολογισμός μιας μπάντας που επέζησε από την ίδια της την εικόνα. Η μελωδία είναι πιο ήρεμη, η ερμηνεία πιο συγκρατημένη και η παραγωγή δίνει χώρο στο μήνυμα αντί για riff. Ως τέλος, είναι ιδανικό, μετά το decadence, την εξάρτηση, την ταχύτητα και την ερωτική υπερβολή των προηγούμενων tracks, το album καταλήγει σε αναγνώριση ότι η επιβίωση απαιτεί μεταμόρφωση. </t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Capitol Records – 14C 062-7484931, Capitol Records – 7484931, Enigma (4) – 14C 062-7484931, Enigma (4) – 7484931 (Greece, 1988, LP, Album). Ελληνική πρώτη κοπή (Greek first press) χωρίς barcode στο οπισθόφυλλο, με πολλαπλούς κωδικούς καταλόγου (πρώτος κωδικός στη ράχη, δεύτερος στο οπισθόφυλλο και τρίτος στην ετικέτα). Η κατασκευή έγινε από την EMI Greece και η εκτύπωση από την EMI Greece, με κοπή/pressing plant ID στη Columbia, Athens.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Κυκλοφόρησε τον Μάιο του 1988 και έγινε τεράστια εμπορική επιτυχία (πλατινένιο πολλές φορές), εδραιώνοντας τους Poison στην κορυφή του 80s glam metal κινήματος. Η παραγωγή έγινε από τον Tom Werman (ο οποίος υπέγραψε και το Dr. Feelgood των Mötley Crüe την επόμενη χρονιά), προσφέροντας κολλητικά, πολυπλατινένια hard rock anthems. Το mastering έγινε στη Bernie Grundman Mastering από τον Chris Bellman. Η ελληνική κοπή της EMI / Columbia αποτελεί μια κλασική εγχώρια έκδοση της εποχής.</t>
+  </si>
+  <si>
+    <t>Love On The Rocks</t>
+  </si>
+  <si>
+    <t>Nothin’ But A Good Time</t>
+  </si>
+  <si>
+    <t>Back To The Rocking Horse</t>
+  </si>
+  <si>
+    <t>Good Love</t>
+  </si>
+  <si>
+    <t>Tearin’ Down The Walls</t>
+  </si>
+  <si>
+    <t>Look But You Can’t Touch</t>
+  </si>
+  <si>
+    <t>Fallen Angel</t>
+  </si>
+  <si>
+    <t>Every Rose Has Its Thorn</t>
+  </si>
+  <si>
+    <t>Your Mama Don’t Dance</t>
+  </si>
+  <si>
+    <t>Bad To Be Good</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/UO7AHcpu6NdzDznB6d0MmU-CAJqpF6AvrXCPJ7vfF-E/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ3Nzg3/NzQtMTU3MTgxMTQ3/NC04NDA0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4778774-Poison-Open-Up-And-Say-Ahh</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Hair Metal, Pop Metal, Party Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Bluesy Hard Rock, Sleaze Rock, Dark Party Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Party Metal, Pop Metal, Arena Rock Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Melodic Hard Rock, Cowbell Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Rock ’n’ Roll, Sleaze Rock, Up-tempo Party Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Metal, Arena Hard Rock, Defiant Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Sleaze Metal, Bluesy Hard Rock, Sexualized Party Rock]</t>
+  </si>
+  <si>
+    <t>Glam Metal, Hard Rock [Melodic Pop Metal, Arena Rock, Sunset Strip Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Soft Rock [Power Ballad, Acoustic Rock, Country-tinged Glam Ballad]</t>
+  </si>
+  <si>
+    <t>Rock ’n’ Roll, Glam Metal [Classic-Rock Cover, Party Rock, Pop Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Metal [Bluesy Sleaze Rock, Late-night Hard Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Open Up And Say ...Ahh!</t>
+  </si>
+  <si>
+    <t>Η πιο αποφασιστική στιγμή της A πλευράς πέρα από τα singles. Το «γκρέμισμα των τοίχων» λειτουργεί ως εικόνα υπέρβασης εμποδίων, συναισθηματικών φραγμών ή κοινωνικών περιορισμών. Η μουσική είναι πιο βαριά και πιο arena-oriented, με κιθάρες που δίνουν metal bite και chorus που επιδιώκει συλλογική συμμετοχή. Δεν έχει την καθαρή pop ακαριαία επιτυχία του “Nothin’ But A Good Time”, όμως δίνει στον δίσκο μια μικρή δόση σοβαρότερης hard-rock έντασης. Ως closing track της A πλευράς κρατά τη ροή ψηλά και δημιουργεί καλή μετάβαση προς το πιο μελωδικό, hit-driven B-side.</t>
+  </si>
+  <si>
+    <t>Up-tempo, riff-led hard rock με κλασική θεματική έρωτα, επιθυμίας και άμεσης ικανοποίησης. Οι Poison εδώ βασίζονται στην απλή σχέση κιθάρας-ρυθμού-chorus, με τον DeVille να προσθέτει catchy φράσεις και τον Michaels να δίνει pop-metal φωνητικά. Η σύνθεση δεν είναι ιδιαίτερα πρωτότυπη , θα μπορούσε να βρίσκεται σε πολλά 1988 hair-metal albums , αλλά είναι σωστά εκτελεσμένη και έχει τη θετική ενέργεια που ζητά το album. Η τοποθέτησή της μετά το “Back To The Rocking Horse” κάνει την A πλευρά να μοιάζει με συνεχόμενο party set, πριν το “Tearin’ Down The Walls” αλλάξει ελαφρά το θεματικό βάρος.</t>
+  </si>
+  <si>
+    <t>Η διασκευή του τραγουδιού των Loggins &amp; Messina μετατρέπει 1970s soft-rock/rock ’n’ roll υλικό σε glam-metal party rocker. Η βασική ιδέα , γονείς που κρίνουν τον χορό, τη νυχτερινή διασκέδαση και τη νεανική συμπεριφορά , ταιριάζει απόλυτα με τη lighthearted rebel εικόνα των Poison. Η μπάντα δεν προσπαθεί να προσθέσει ιδιαίτερο βάθος· παίρνει μια αναγνωρίσιμη μελωδία, την κάνει πιο δυνατή, πιο γρήγορη και πιο MTV-friendly. Η ερμηνεία λειτουργεί επειδή οι Poison είναι, στην ουσία, καλοί στο να κάνουν το rock ’n’ roll να ακούγεται σαν ανοιχτή πρόσκληση για πάρτι. Ήταν ένα από τα τέσσερα hit singles του δίσκου και διατηρεί τη διασκεδαστική του αξία.</t>
+  </si>
+  <si>
+    <t>Ο δίσκος ανοίγει πιο σκληρά και πιο bluesy από ό,τι θα περίμενε κανείς από τους Poison. Η «αγάπη στα βράχια» είναι σχέση σε κρίση , όχι γιορτή, αλλά ένταση, απογοήτευση και μια αίσθηση ότι η κατάρρευση είναι ήδη σε εξέλιξη. Η κιθάρα του C.C. DeVille δίνει dirty, riff-based χαρακτήρα, ενώ ο Bret Michaels τραγουδά με περισσότερη νευρικότητα απ’ ό,τι στα καθαρά party tracks. Δεν είναι album-defining classic, όμως ως opener λειτουργεί σωστά, παρουσιάζει ένα ελαφρώς πιο σκοτεινό hard-rock πρόσωπο πριν το album περάσει στη χαρά και στη λάμψη του “Nothin’ But A Good Time”.</t>
+  </si>
+  <si>
+    <t>Η απόλυτη Poison δήλωση και ένα από τα πιο αναγνωρίσιμα party-metal anthems της δεκαετίας. Ο τίτλος δεν είναι σύνθετος, μετά από δουλειά, πίεση, οικονομικά και καθημερινή κούραση, ο αφηγητής ζητά μια καλή βραδιά. Η μουσική μεταφέρει ακριβώς αυτή την ανάγκη με εκρηκτικό chorus, upbeat ρυθμό και κιθάρα που συνδυάζει pop ακρίβεια με hard-rock κίνηση. Η δύναμη του τραγουδιού βρίσκεται στην καθολικότητα της απλότητάς του, δεν χρειάζεται να είσαι μέρος της Sunset Strip σκηνής για να καταλάβεις την επιθυμία να αφήσεις πίσω τη ρουτίνα. Ήταν το lead single, έφτασε στο Νο. 6 του Billboard Hot 100 και καθιέρωσε τους Poison ως βασική mainstream glam-metal μπάντα.</t>
+  </si>
+  <si>
+    <t>Ένα πιο παιχνιδιάρικο, mid-tempo party track με cowbell, ρυθμικό bounce και πιο «σκανταλιάρικη» γλώσσα. Ο τίτλος χρησιμοποιεί το rocking horse ως ερωτικό/νοσταλγικό διπλό νόημα, κάτι τυπικό για τη μη ιδιαίτερα λεπτή αλλά χαρούμενη στιχουργική των Poison. Το κομμάτι δεν φτάνει τη συνθετική αμεσότητα του προηγούμενου track, αλλά διατηρεί τη ροή της A πλευράς με καθαρό chorus και αρκετή κιθαριστική κίνηση. Η αξία του είναι η αβίαστη fun διάθεση, δεν προσποιείται ότι έχει μεγάλο βάθος, λειτουργεί ως soundtrack για μια μπάντα που θέλει να κρατήσει το πάρτι σε κίνηση.</t>
+  </si>
+  <si>
+    <t>Το B-side ανοίγει με τη sleaze-rock πλευρά των Poison. Ο τίτλος χτίζει πάνω στην απαγόρευση και στην πρόκληση, μπορείς να κοιτάς, αλλά δεν έχεις δικαίωμα να πλησιάσεις. Η μουσική έχει bluesier groove και λιγότερο γυαλισμένο chorus, με τον DeVille να δίνει κιθαριστικές κινήσεις που θυμίζουν πιο dirty Sunset Strip rock. Οι στίχοι είναι τυπικά late-’80s glam, με υπαινιγμούς και παιχνίδι εξουσίας, όμως το track δεν απογειώνεται σε επίπεδο μεγάλου anthem. Είναι όμως σωστό deep cut και διατηρεί το άλμπουμ σε αναγνωρίσιμο Poison ύφος πριν έρθουν οι δύο μεγαλύτερες στιγμές της πλευράς.</t>
+  </si>
+  <si>
+    <t>Ένα από τα καλύτερα και πιο μελωδικά Poison τραγούδια, με πιο σκοτεινό narrative από το συνηθισμένο party mood. Η “fallen angel” είναι μια νεαρή γυναίκα που φεύγει για Hollywood/Los Angeles κυνηγώντας φήμη και όνειρα, μόνο για να βρεθεί αντιμέτωπη με εκμετάλλευση, απομόνωση και απογοήτευση. Η μουσική διατηρεί το uplifting pop-metal chorus, όμως η θεματική δίνει στο τραγούδι βάρος, πίσω από το γυαλιστερό Sunset Strip βρίσκεται και η σκοτεινή πλευρά της βιομηχανίας του θεάματος. Ο Michaels τραγουδά με περισσότερη αφηγηματική ευαισθησία, ενώ το riff και οι κιθάρες κρατούν το track αρκετά δυνατό. Έγινε Top 20 single στις ΗΠΑ και παραμένει σαφές highlight του album.</t>
+  </si>
+  <si>
+    <t>Η power ballad που ξεπέρασε το είδος και έγινε το μοναδικό No. 1 των Poison. Ο τίτλος χρησιμοποιεί την ιδέα ότι κάθε όμορφο πράγμα , κάθε τριαντάφυλλο , έχει και το αγκάθι του, ο έρωτας εμπεριέχει πόνο, χωρισμό και πληγές. Το τραγούδι είναι πιο ακουστικό και πιο country-tinged από το υπόλοιπο album, κάτι που δίνει χώρο στη μελωδία και στην πιο εύθραυστη φωνητική ερμηνεία του Michaels. Η εσωτερική του δύναμη δεν βασίζεται στην τεχνική πολυπλοκότητα, αλλά στην απλότητα και στην καθαρή συναισθηματική αφήγηση. Γράφτηκε μέσα από προσωπική heartbreak εμπειρία του Michaels, και ακριβώς αυτή η αίσθηση βιωμένης απώλειας το έκανε να λειτουργήσει πολύ πέρα από το hair-metal κοινό.</t>
+  </si>
+  <si>
+    <t>Το album κλείνει με bluesy, sleaze-rock διάθεση και τίτλο που συνοψίζει τη βασική Poison αντίφαση, η «κακία» εδώ δεν είναι πραγματική σκοτεινιά, αλλά η ελευθερία να είσαι άτακτος, να διασκεδάζεις και να μη δίνεις λογαριασμό. Η μουσική επιστρέφει σε πιο χαλαρό groove μετά το acoustic βάρος του “Every Rose…” και την cover χαρά του “Your Mama Don’t Dance”. Δεν είναι κορυφαίο track, αλλά το χαμηλότερο tempo και η dirty κιθαριστική υφή το κάνουν σωστό closer, δεν προσπαθεί να ανταγωνιστεί τα singles, απλώς αφήνει τον δίσκο να κλείσει με την bar-band αίσθηση που βρίσκεται στον πυρήνα των Poison.</t>
   </si>
 </sst>
 </file>
@@ -13291,7 +13402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -13373,6 +13484,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13684,7 +13798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -17408,6 +17522,38 @@
       </c>
       <c r="J116" s="11" t="s">
         <v>3918</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="168" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>3952</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>3978</v>
+      </c>
+      <c r="D117" s="6">
+        <v>1988</v>
+      </c>
+      <c r="E117" s="10">
+        <v>2.84</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>3967</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>3954</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>3953</v>
+      </c>
+      <c r="I117" s="11" t="s">
+        <v>3966</v>
+      </c>
+      <c r="J117" s="11" t="s">
+        <v>3965</v>
       </c>
     </row>
   </sheetData>
@@ -17639,6 +17785,8 @@
     <hyperlink ref="I115" r:id="rId225" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
     <hyperlink ref="I116" r:id="rId226" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
     <hyperlink ref="J116" r:id="rId227" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
+    <hyperlink ref="J117" r:id="rId228" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
+    <hyperlink ref="I117" r:id="rId229" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17646,7 +17794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1104"/>
+  <dimension ref="A1:I1114"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -47653,6 +47801,276 @@
       </c>
       <c r="I1104" s="6"/>
     </row>
+    <row r="1105" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1105" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1105" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1105" s="7" t="s">
+        <v>3955</v>
+      </c>
+      <c r="D1105" s="7" t="s">
+        <v>3968</v>
+      </c>
+      <c r="E1105" s="20">
+        <v>3.16</v>
+      </c>
+      <c r="F1105" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1105" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1105" s="28" t="s">
+        <v>3982</v>
+      </c>
+      <c r="I1105" s="6"/>
+    </row>
+    <row r="1106" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1106" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1106" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1106" s="7" t="s">
+        <v>3956</v>
+      </c>
+      <c r="D1106" s="7" t="s">
+        <v>3969</v>
+      </c>
+      <c r="E1106" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F1106" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1106" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1106" s="28" t="s">
+        <v>3983</v>
+      </c>
+      <c r="I1106" s="6"/>
+    </row>
+    <row r="1107" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1107" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1107" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1107" s="7" t="s">
+        <v>3957</v>
+      </c>
+      <c r="D1107" s="7" t="s">
+        <v>3970</v>
+      </c>
+      <c r="E1107" s="20">
+        <v>3.18</v>
+      </c>
+      <c r="F1107" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1107" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1107" s="28" t="s">
+        <v>3984</v>
+      </c>
+      <c r="I1107" s="6"/>
+    </row>
+    <row r="1108" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1108" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1108" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1108" s="7" t="s">
+        <v>3958</v>
+      </c>
+      <c r="D1108" s="7" t="s">
+        <v>3971</v>
+      </c>
+      <c r="E1108" s="20">
+        <v>3</v>
+      </c>
+      <c r="F1108" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1108" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1108" s="9" t="s">
+        <v>3980</v>
+      </c>
+      <c r="I1108" s="6"/>
+    </row>
+    <row r="1109" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1109" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1109" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1109" s="7" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D1109" s="7" t="s">
+        <v>3972</v>
+      </c>
+      <c r="E1109" s="20">
+        <v>2.96</v>
+      </c>
+      <c r="F1109" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1109" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1109" s="28" t="s">
+        <v>3979</v>
+      </c>
+      <c r="I1109" s="6"/>
+    </row>
+    <row r="1110" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1110" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1110" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1110" s="7" t="s">
+        <v>3960</v>
+      </c>
+      <c r="D1110" s="7" t="s">
+        <v>3973</v>
+      </c>
+      <c r="E1110" s="20">
+        <v>3.03</v>
+      </c>
+      <c r="F1110" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1110" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1110" s="28" t="s">
+        <v>3985</v>
+      </c>
+      <c r="I1110" s="6"/>
+    </row>
+    <row r="1111" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1111" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1111" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1111" s="7" t="s">
+        <v>3961</v>
+      </c>
+      <c r="D1111" s="7" t="s">
+        <v>3974</v>
+      </c>
+      <c r="E1111" s="20">
+        <v>3.71</v>
+      </c>
+      <c r="F1111" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1111" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1111" s="28" t="s">
+        <v>3986</v>
+      </c>
+      <c r="I1111" s="6"/>
+    </row>
+    <row r="1112" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1112" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1112" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1112" s="7" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D1112" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="E1112" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F1112" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1112" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1112" s="28" t="s">
+        <v>3987</v>
+      </c>
+      <c r="I1112" s="6"/>
+    </row>
+    <row r="1113" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1113" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1113" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1113" s="7" t="s">
+        <v>3963</v>
+      </c>
+      <c r="D1113" s="7" t="s">
+        <v>3976</v>
+      </c>
+      <c r="E1113" s="20">
+        <v>2.94</v>
+      </c>
+      <c r="F1113" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1113" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1113" s="28" t="s">
+        <v>3981</v>
+      </c>
+      <c r="I1113" s="6"/>
+    </row>
+    <row r="1114" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1114" s="6">
+        <v>4778774</v>
+      </c>
+      <c r="B1114" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1114" s="7" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D1114" s="7" t="s">
+        <v>3977</v>
+      </c>
+      <c r="E1114" s="20">
+        <v>2.98</v>
+      </c>
+      <c r="F1114" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1114" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1114" s="28" t="s">
+        <v>3988</v>
+      </c>
+      <c r="I1114" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999BF74B-5E87-4C24-8A98-93DB417D3E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483EAB11-A70C-484C-9F8D-221DB9FEE017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4313" uniqueCount="3989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="4019">
   <si>
     <t>No</t>
   </si>
@@ -13213,6 +13213,96 @@
   </si>
   <si>
     <t>Το album κλείνει με bluesy, sleaze-rock διάθεση και τίτλο που συνοψίζει τη βασική Poison αντίφαση, η «κακία» εδώ δεν είναι πραγματική σκοτεινιά, αλλά η ελευθερία να είσαι άτακτος, να διασκεδάζεις και να μη δίνεις λογαριασμό. Η μουσική επιστρέφει σε πιο χαλαρό groove μετά το acoustic βάρος του “Every Rose…” και την cover χαρά του “Your Mama Don’t Dance”. Δεν είναι κορυφαίο track, αλλά το χαμηλότερο tempo και η dirty κιθαριστική υφή το κάνουν σωστό closer, δεν προσπαθεί να ανταγωνιστεί τα singles, απλώς αφήνει τον δίσκο να κλείσει με την bar-band αίσθηση που βρίσκεται στον πυρήνα των Poison.</t>
+  </si>
+  <si>
+    <t>Hellbound</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/zyZ2IO8mEwam3FmVKRIludV5wYBMmYrCTJeNtvIYkLw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTc4MzA2/MDktMTQ1MzAzMzY5/Ny0yMzU4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/7830609-Warlock-Hellbound</t>
+  </si>
+  <si>
+    <t>Vertigo – 824 660-1Q (West Germany, 1985, LP, Album, Stereo). Κλασική δυτικογερμανική κοπή με τις κίτρινες ετικέτες της Vertigo, χωρίς αφίσα (without poster), κατασκευασμένη και τυπωμένη στη Δυτική Γερμανία.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Hellbound κυκλοφόρησε τον Μαΐο του 1985 και αποτελεί το δεύτερο στούντιο άλμπουμ των Γερμανών heavy metallers Warlock, εδραιώνοντας τη θέση τους στην ευρωπαϊκή σκηνή. Την παραγωγή υπέγραψε ο Henry Staroste στα Dierks Studios, προσδίδοντας έναν ωμό, επιθετικό αλλά ταυτόχρονα συμπαγή και ευρωπαϊκού χαρακτήρα heavy metal ήχο. Η ερμηνεία της Doro Pesch ξεχωρίζει για την τραχιά ενέργεια και τη μελωδικότητά της, καθιστώντας το άλμπουμ σημείο αναφοράς για το κίνημα του κλασικού heavy/speed metal της εποχής.</t>
+  </si>
+  <si>
+    <t>All Night</t>
+  </si>
+  <si>
+    <t>Earthshaker Rock</t>
+  </si>
+  <si>
+    <t>Wrathchild</t>
+  </si>
+  <si>
+    <t>Catch My Heart</t>
+  </si>
+  <si>
+    <t>Shout It Out</t>
+  </si>
+  <si>
+    <t>Time To Die</t>
+  </si>
+  <si>
+    <t>Down And Out</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [German Heavy Metal, Traditional Metal, Speed Metal touches, Melodic Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο σκοτεινή και θεατρική γλώσσα. Ο τίτλος φέρνει αμέσως αναπόφευκτη απειλή και τελικότητα, ενώ η μουσική χτίζει με βαριά riffs και συγκρατημένη ένταση. Το τραγούδι δεν κινείται με την ίδια ταχύτητα του “Out Of Control”, αλλά χρησιμοποιεί mid-tempo βάρος και δραματική φωνητική ερμηνεία για να δημιουργήσει ατμόσφαιρα. Η Doro αφήνει τις φράσεις να αποκτήσουν μεγαλύτερο βάρος, χωρίς να χάνει τη metal αποφασιστικότητα. Είναι ένα από τα tracks που προσθέτουν ποικιλία στον δίσκο, αν και δεν έχει τόσο άμεσο hook όσο τα βασικά highlights.</t>
+  </si>
+  <si>
+    <t>Το ιδανικό κλείσιμο και η πιο συναισθηματικά ανοιχτή σύνθεση του album. Η φράση «πιάσε την καρδιά μου» δηλώνει ευαλωτότητα και ανάγκη για εμπιστοσύνη, ενώ η μουσική ξεκινά σαν melodic hard-rock ballad και αναπτύσσεται σε μεγάλη heavy-rock κορύφωση. Η Doro τραγουδά με καθαρή, ισχυρή μελωδία, χωρίς να χάνει την τραχύτητα που κάνει τη φωνή της ξεχωριστή. Το τραγούδι δεν είναι απλώς «η μπαλάντα που πρέπει να έχει ένα metal LP»· η δομή και η ερμηνεία του δίνουν πραγματική δραματική αξία. Είναι το πρώτο τραγούδι των Warlock που έδειξε καθαρά τη δυνατότητα της Doro για power-ballad ερμηνεία και προετοιμάζει φυσικά τη μεταγενέστερη “Für Immer”.</t>
+  </si>
+  <si>
+    <t>Πιο αργό, σκοτεινό και δραματικό κλείσιμο της A πλευράς. Ο τίτλος περιγράφει κάποιον που έχει φτάσει στο χαμηλότερο σημείο , οικονομικά, κοινωνικά ή ψυχολογικά , και η μουσική χρησιμοποιεί mid-tempo βάρος αντί για την ταχύτητα των προηγούμενων tracks. Η φωνή της Doro έχει εδώ περισσότερο συναίσθημα και λιγότερη καθαρή επιθετικότητα, ενώ οι κιθάρες προσθέτουν μελωδικές γραμμές που ενισχύουν την αίσθηση απομόνωσης. Δεν είναι power ballad, αλλά έχει παρόμοια ανάγκη για έκφραση και κλιμάκωση. Είναι επιτυχημένο side closer επειδή δίνει στην A πλευρά πιο σκοτεινή έξοδο.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με τον σωστό τρόπο, γρήγορο riffing, επιθετικά drums και τη Doro Pesch να μπαίνει σαν να βρίσκεται ήδη πάνω στη σκηνή. Ο τίτλος , «δεμένος για την κόλαση» , χρησιμοποιεί κλασική heavy-metal εικόνα καταδίκης, κινδύνου και αδυναμίας διαφυγής. Η μπάντα όμως δεν το κάνει doom track· το μετατρέπει σε fast traditional metal, με ρυθμό που σπρώχνει συνεχώς προς τα εμπρός. Οι κιθάρες έχουν καθαρό Teutonic χαρακτήρα και η φωνή της Doro ισορροπεί ανάμεσα σε μελωδία και κραυγή. Είναι αποτελεσματικό opener επειδή δηλώνει αμέσως ότι οι Warlock κινούνται σε πιο στιβαρό, άμεσο metal από το πιο ανομοιογενές debut τους.</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό και πιο accessible, με τίτλο που παραπέμπει σε νυχτερινή ενέργεια, απόδραση και rock ’n’ roll διασκέδαση. Η μπάντα κατεβάζει ελαφρώς την ταχύτητα και δίνει περισσότερο χώρο σε chorus και σε melodic hard-rock υφή. Η Doro διατηρεί τη δύναμη της φωνής της, αλλά το τραγούδι δεν απαιτεί συνεχείς κορυφώσεις· επιλέγει περισσότερο groove και sing-along λειτουργία. Δεν έχει το βάρος του “Hellbound” ή του “Wrathchild”, όμως είναι σημαντικό για την ισορροπία της A πλευράς, αποδεικνύει ότι οι Warlock μπορούν να είναι μελωδικοί χωρίς να γίνονται pop-metal.</t>
+  </si>
+  <si>
+    <t>Ένα self-referential metal anthem, όπου η μουσική παρουσιάζεται σαν δύναμη που κουνά τη γη. Ο τίτλος είναι σκόπιμα απλός και η μπάντα το χειρίζεται ως crowd chant, riff, σταθερά drums και refrain που ζητά συμμετοχή. Υπάρχει rock ’n’ roll αμεσότητα και party-metal διάθεση, αλλά η κιθαριστική ένταση και η φωνή της Doro το κρατούν σε traditional heavy-metal πλαίσιο. Δεν είναι από τις πιο σύνθετες συνθέσεις του album, όμως λειτουργεί καλά ως live-friendly κομμάτι και ως ανάσα πριν την πιο επιθετική έκρηξη του “Wrathchild”.</t>
+  </si>
+  <si>
+    <t>Από τα γρηγορότερα και πιο σκληρά tracks του δίσκου. Ο “wrathchild” είναι φιγούρα οργής και βίας, και το τραγούδι ανταποκρίνεται με speed-metal νεύρο, κοφτά riffs και φωνητικά που έχουν μεγαλύτερη αγριάδα. Η Doro δεν απλώς τραγουδά δυνατά, επιβάλλεται πάνω στα riffs και μετατρέπει τη φράση του τίτλου σε απειλητικό refrain. Οι κιθάρες προσθέτουν γερμανικό traditional-metal βάρος, με ένταση που φέρνει τους Warlock πιο κοντά σε Accept/Judas Priest λογική απ’ ό,τι σε glam metal. Είναι ένα από τα highlights της A πλευράς και βασικός λόγος που ο δίσκος διατηρεί την ακατέργαστη metal αξία του.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά επιστρέφει αμέσως σε γρήγορη, μελωδική heavy-metal ένταση. Το “out of control” είναι κατάσταση απώλειας ορίων, αλλά η μπάντα το αξιοποιεί ως αδρεναλινικό κάλεσμα και όχι ως εσωστρεφή κρίση. Το rhythm section κινείται με συνεχή ώθηση, τα riffs είναι καθαρά και η φωνή της Doro περνά από δυνατές γραμμές σε πιο μελωδικό refrain. Είναι από τις καλύτερα ισορροπημένες συνθέσεις του album, αρκετά γρήγορη για metal fans, αρκετά μελωδική για να μείνει, και αρκετά καλοδουλεμένη ώστε να μη μοιάζει με απλό filler.</t>
+  </si>
+  <si>
+    <t>Κλασικό community metal anthem. Ο τίτλος είναι εντολή , φώναξέ το , και η σύνθεση σχεδιάζεται για να απαντά το κοινό, ανοιχτό refrain, απλή ρυθμική κίνηση και κιθάρες που υπηρετούν το sing-along. Στην ουσία, είναι πιο μελωδικό sibling του “Earthshaker Rock”. Δεν έχει την ταχύτητα του “Wrathchild” ούτε τη θεατρική σκοτεινιά του “Time To Die”, αλλά λειτουργεί ως συναυλιακό κομμάτι που θυμίζει ότι οι Warlock είχαν στόχο να χτίσουν επαφή με audience, όχι μόνο να γράψουν μουσικά περίπλοκο metal.</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Melodic Heavy Metal, Arena Metal, Party Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Rock ’n’ Roll Metal, Anthemic Heavy Rock, Crowd Chant]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Speed Metal [Fast Metal, Aggressive Teutonic Metal, Riff Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Mid-tempo Heavy Rock, Dramatic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Melodic Metal, Arena Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Metal, Theatrical Metal, Dramatic Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Metal Anthem, Crowd Chant, Melodic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Power Ballad, Melodic Heavy Rock, German Metal Ballad]</t>
   </si>
 </sst>
 </file>
@@ -13798,7 +13888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -17524,7 +17614,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="168" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>4778774</v>
       </c>
@@ -17554,6 +17644,38 @@
       </c>
       <c r="J117" s="11" t="s">
         <v>3965</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>3641</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D118" s="6">
+        <v>1985</v>
+      </c>
+      <c r="E118" s="10">
+        <v>3.38</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>4001</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>3993</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>3992</v>
+      </c>
+      <c r="I118" s="11" t="s">
+        <v>3991</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>3990</v>
       </c>
     </row>
   </sheetData>
@@ -17787,6 +17909,8 @@
     <hyperlink ref="J116" r:id="rId227" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
     <hyperlink ref="J117" r:id="rId228" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
     <hyperlink ref="I117" r:id="rId229" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
+    <hyperlink ref="J118" r:id="rId230" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
+    <hyperlink ref="I118" r:id="rId231" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17794,7 +17918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1114"/>
+  <dimension ref="A1:I1123"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -48071,6 +48195,251 @@
       </c>
       <c r="I1114" s="6"/>
     </row>
+    <row r="1115" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1115" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1115" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1115" s="7" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D1115" s="7" t="s">
+        <v>3667</v>
+      </c>
+      <c r="E1115" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F1115" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1115" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1115" s="28" t="s">
+        <v>4005</v>
+      </c>
+      <c r="I1115" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1116" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1116" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1116" s="7" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D1116" s="7" t="s">
+        <v>4011</v>
+      </c>
+      <c r="E1116" s="20">
+        <v>3.48</v>
+      </c>
+      <c r="F1116" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1116" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1116" s="28" t="s">
+        <v>4006</v>
+      </c>
+      <c r="I1116" s="6"/>
+    </row>
+    <row r="1117" spans="1:9" ht="63" x14ac:dyDescent="0.15">
+      <c r="A1117" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1117" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1117" s="7" t="s">
+        <v>3995</v>
+      </c>
+      <c r="D1117" s="7" t="s">
+        <v>4012</v>
+      </c>
+      <c r="E1117" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="F1117" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1117" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1117" s="28" t="s">
+        <v>4007</v>
+      </c>
+      <c r="I1117" s="6"/>
+    </row>
+    <row r="1118" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1118" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1118" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1118" s="7" t="s">
+        <v>3996</v>
+      </c>
+      <c r="D1118" s="7" t="s">
+        <v>4013</v>
+      </c>
+      <c r="E1118" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F1118" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1118" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1118" s="28" t="s">
+        <v>4008</v>
+      </c>
+      <c r="I1118" s="6"/>
+    </row>
+    <row r="1119" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1119" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1119" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1119" s="7" t="s">
+        <v>4000</v>
+      </c>
+      <c r="D1119" s="7" t="s">
+        <v>4014</v>
+      </c>
+      <c r="E1119" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F1119" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1119" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1119" s="28" t="s">
+        <v>4004</v>
+      </c>
+      <c r="I1119" s="6"/>
+    </row>
+    <row r="1120" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1120" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1120" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1120" s="7" t="s">
+        <v>3691</v>
+      </c>
+      <c r="D1120" s="7" t="s">
+        <v>4015</v>
+      </c>
+      <c r="E1120" s="20">
+        <v>3.73</v>
+      </c>
+      <c r="F1120" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1120" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1120" s="9" t="s">
+        <v>4009</v>
+      </c>
+      <c r="I1120" s="6"/>
+    </row>
+    <row r="1121" spans="1:9" ht="73.5" x14ac:dyDescent="0.15">
+      <c r="A1121" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1121" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1121" s="7" t="s">
+        <v>3999</v>
+      </c>
+      <c r="D1121" s="7" t="s">
+        <v>4016</v>
+      </c>
+      <c r="E1121" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F1121" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1121" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1121" s="28" t="s">
+        <v>4002</v>
+      </c>
+      <c r="I1121" s="6"/>
+    </row>
+    <row r="1122" spans="1:9" ht="63" x14ac:dyDescent="0.15">
+      <c r="A1122" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1122" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1122" s="7" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D1122" s="7" t="s">
+        <v>4017</v>
+      </c>
+      <c r="E1122" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F1122" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1122" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1122" s="28" t="s">
+        <v>4010</v>
+      </c>
+      <c r="I1122" s="6"/>
+    </row>
+    <row r="1123" spans="1:9" ht="84" x14ac:dyDescent="0.15">
+      <c r="A1123" s="6">
+        <v>7830609</v>
+      </c>
+      <c r="B1123" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1123" s="7" t="s">
+        <v>3997</v>
+      </c>
+      <c r="D1123" s="7" t="s">
+        <v>4018</v>
+      </c>
+      <c r="E1123" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F1123" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1123" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1123" s="28" t="s">
+        <v>4003</v>
+      </c>
+      <c r="I1123" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483EAB11-A70C-484C-9F8D-221DB9FEE017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BA5AF0-0B79-4595-A970-595F957F4B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4348" uniqueCount="4019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4387" uniqueCount="4054">
   <si>
     <t>No</t>
   </si>
@@ -13303,6 +13303,141 @@
   </si>
   <si>
     <t>Hard Rock, Heavy Metal [Power Ballad, Melodic Heavy Rock, German Metal Ballad]</t>
+  </si>
+  <si>
+    <t>Metal Rendez-vous</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/4684547-Krokus-Metal-Rendez-vous</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/uFVscvr5qDUKLHxJPjPHZ2xIFl9XEVQkPdxWW_4veFM/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTQ2ODQ1/NDctMTQ0Njc5Mzcz/OC05MDE4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Back-Seat Rock ’n’ Roll</t>
+  </si>
+  <si>
+    <t>Heatstrokes</t>
+  </si>
+  <si>
+    <t>Bedside Radio</t>
+  </si>
+  <si>
+    <t>Come On</t>
+  </si>
+  <si>
+    <t>Streamer</t>
+  </si>
+  <si>
+    <t>No Way</t>
+  </si>
+  <si>
+    <t>Tokyo Nights</t>
+  </si>
+  <si>
+    <t>Lady Double Dealer</t>
+  </si>
+  <si>
+    <t>Shy Kid</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Swiss Hard Rock, AC/DC-influenced Boogie Rock, Early ’80s Metal, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Ariola – 6483233 (Greece, 1980, LP, Album, Stereo). Ελληνική πρώτη/κλασική κοπή, κατασκευασμένη από τη G.P.I. S.A. και τυπωμένη από τον Μιχάλη Ορφανό. Φέρει etched lacquers από τη G.P.I. S.A. (973). Στα notes της έκδοσης αναφέρεται χαρακτηριστικά τυπογραφικό λάθος (misprint) στην ετικέτα της Πλευράς 1 ("KROKOUS" αντί για "KROKUS"), με διαφορετικό κωδικό καταλόγου στο εξώφυλλο και τις ετικέτες</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Metal Rendez-vous κυκλοφόρησε το 1980 και αποτελεί το ορόσημο-καμπή για τους Ελβετούς Krokus, καθώς είναι το πρώτο άλμπουμ με τον Marc Storace στα φωνητικά και σηματοδοτεί τη στροφή τους από το progressive rock στον σκληρό hard rock / heavy metal ήχο (επηρεασμένο έντονα από το ύφος των AC/DC). Η παραγωγή έγινε από τους ίδιους τους Krokus σε συνεργασία με τον Martin Pearson. Η ελληνική κοπή της Ariola / G.P.I. S.A. αποτελεί μια ιδιαίτερη και περιζήτητη εγχώρια έκδοση της εποχής.</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Boogie Hard Rock, AC/DC-style Riff Rock, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Radio Rock, Boogie Rock, Catchy Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Straight-ahead Heavy Rock, Early Metal, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Extended Hard Rock, Guitar-led Metal, Epic Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Short Rocker, Boogie Rock, Party Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Hard Rock, Scorpions-influenced Rock, Night Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Bluesy Hard Rock, Sleaze Rock precursor, Riff Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Epic Heavy Metal, Dark Hard Rock, Extended Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fast Hard Rock, Driving Metal, Defiant Rock]</t>
+  </si>
+  <si>
+    <t>Rock ’n’ Roll, Hard Rock [Boogie Rock, Party Rock, AC/DC-influenced Hard Rock]</t>
+  </si>
+  <si>
+    <t>Το κομμάτι που καθιέρωσε τους Krokus εκτός Ελβετίας και το σωστό άνοιγμα για το album. Το riff είναι καθαρό, βαρύ και άμεσο, με προφανή AC/DC αισθητική: boogie ρυθμός, κιθάρες που χτυπούν στο σωστό σημείο και φωνή που λειτουργεί σαν καθαρή rock ’n’ roll πρόκληση. Ο τίτλος παραπέμπει σε θερμότητα, ένταση και σωματική διέγερση, όμως η πραγματική δύναμη βρίσκεται στο παιχνίδι του riff και στο driving rhythm section. Ο Marc Storace έχει τη βραχνή, υψηλή φωνή που κάνει το τραγούδι να ακούγεται μεγαλύτερο από μια απλή AC/DC μίμηση. Το “Heatstrokes” έφτασε στο Νο. 1 των UK Heavy Metal Charts και παραμένει το βασικό Krokus anthem της περιόδου.</t>
+  </si>
+  <si>
+    <t>Πιο ανάλαφρο και πιο ραδιοφωνικό, χωρίς να εγκαταλείπει το hard-rock βάρος. Ο τίτλος παίζει με την ιδέα του ραδιοφώνου δίπλα στο κρεβάτι ως χώρου νυχτερινής φαντασίας, απομόνωσης ή ερωτικής προσμονής. Το chorus είναι πιο άμεσο και πιο sing-along από το “Heatstrokes”, ενώ η κιθάρα έχει ρυθμική boogie λειτουργία αντί για καθαρά μεταλλική επίθεση. Η μπάντα δείχνει ότι μπορεί να γράψει τραγούδι για radio airplay χωρίς να γίνει soft rock. Το “Bedside Radio” έγινε διεθνές live staple και έφτασε στο Νο. 20 των UK Heavy Metal Charts.</t>
+  </si>
+  <si>
+    <t>Η πιο ευθύγραμμη heavy-rock στιγμή της A πλευράς. Ο τίτλος είναι καθαρό κάλεσμα: έλα, προχώρα, μπες στην ένταση. Η σύνθεση βασίζεται σε πιο σταθερό metal riff, λιγότερο boogie από τα δύο πρώτα tracks και με περισσότερη έμφαση στην κιθαριστική πίεση. Η φωνή του Storace παραμένει μελωδική, αλλά οι κιθάρες δίνουν στον δίσκο την απαραίτητη heavy-metal διάσταση που τον ξεχωρίζει από απλό 1970s hard rock. Το τραγούδι έγινε επίσης UK Heavy Metal Chart hit, φτάνοντας στο Νο. 12, κάτι που δείχνει πόσο ισχυρή ήταν η αρχική λήψη του δίσκου στη βρετανική metal σκηνή.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η πιο εκτεταμένη σύνθεση της A πλευράς και μία από τις πιο κιθαριστικές. Το “Streamer” δεν στηρίζεται μόνο σε ένα γρήγορο hook: αφήνει χώρο για μεγαλύτερη riff ανάπτυξη, solos και αλλαγές έντασης. Η μπάντα δεν γίνεται progressive metal, αλλά δείχνει ότι έχει μεγαλύτερη συνθετική φιλοδοξία από την απλή arena-rock φόρμα. Οι κιθάρες των Fernando von Arb και Tommy Kiefer κινούνται σαν βασικός αφηγητής, με τον Storace να λειτουργεί περισσότερο ως φωνή πάνω σε μια διαρκή hard-rock κίνηση. Είναι από τα tracks που αποδεικνύουν ότι το </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Metal Rendez-vous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> έχει βάθος πέρα από τα τρία singles.</t>
+    </r>
+  </si>
+  <si>
+    <t>Σύντομο και περισσότερο βασισμένο σε rock ’n’ roll ενέργεια. Ο «ντροπαλός νεαρός» του τίτλου είναι μια φιγούρα που έρχεται σε αντίθεση με το bragging, macho ύφος του υπόλοιπου album, αλλά η μουσική δεν γίνεται ιδιαίτερα εσωστρεφής· παραμένει upbeat και boogie-driven. Η διάρκεια του το κάνει περισσότερο transitional cut παρά πλήρη μεγάλη σύνθεση. Έχει σωστό drive και fun διάθεση, αλλά δεν διαθέτει το ιδιαίτερο riff ή την ατμόσφαιρα των καλύτερων tracks. Ως κλείσιμο της A πλευράς, αφήνει μια ελαφρύτερη, πιο χαλαρή εντύπωση πριν από τη νυχτερινή B πλευρά.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με ένα από τα πιο μελωδικά και ατμοσφαιρικά tracks. Οι «νύχτες στο Τόκιο» είναι εικόνα ταξιδιού, ξένης πόλης, νυχτερινής επιθυμίας και περιπλάνησης. Η μουσική έχει πιο Scorpions-like χρώμα, με κιθάρες που κρατούν hard-rock βάρος αλλά αφήνουν χώρο σε μεγαλύτερη μελωδική δραματικότητα. Ο Storace τραγουδά πιο θεατρικά και η σύνθεση έχει αίσθηση ταξιδιού, όχι απλώς party. Οι στίχοι σήμερα ακούγονται dated στον τρόπο που αντιμετωπίζουν την ιαπωνική εικόνα, όμως μουσικά παραμένει ένα από τα πιο ολοκληρωμένα deep cuts του δίσκου.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο bluesy και riff-driven hard rock. Η “double dealer” είναι γυναίκα που παίζει διπλό παιχνίδι, άρα το τραγούδι κινείται σε κλασική rock ’n’ roll θεματική προδοσίας, ερωτικής επικινδυνότητας και swagger. Οι κιθάρες έχουν dirty groove και η φωνή του Storace κρατά την κατάλληλη υπερβολή, αλλά η σύνθεση δεν αναπτύσσει πολύ πέρα από τη βασική ιδέα. Δεν είναι filler, όμως στέκεται λίγο κάτω από τις πιο χαρακτηριστικές στιγμές του album. Λειτουργεί καλύτερα ως ένα σφιχτό, συμπαγές hard-rock cut που κρατά τη B πλευρά σε κίνηση.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη epic heavy-metal στιγμή του δίσκου. Με διάρκεια πάνω από έξι λεπτά, το “Fire” αφήνει την μπάντα να χτίσει πιο σκοτεινή ατμόσφαιρα, βαριά riffs και μεγαλύτερες κιθαριστικές αναπτύξεις. Η φωτιά είναι ταυτόχρονα καταστροφή, πάθος και ανεξέλεγκτη δύναμη· η μουσική της δίνει βάρος αντί να την αντιμετωπίζει σαν απλό party metaphor. Ο Storace τραγουδά με μεγαλύτερη ένταση, οι κιθάρες ανοίγουν σε solos και το rhythm section κρατά αργό, επιβλητικό groove. Η RYM το καταγράφει μαζί με τα “Heatstrokes”, “Bedside Radio” και “No Way” ως ένα από τα standout tracks. 1941</t>
+  </si>
+  <si>
+    <t>Γρήγορο, αποφασιστικό hard-rock τραγούδι με τίτλο άρνησης: «καμία περίπτωση». Η σύνθεση επιστρέφει σε πιο σύντομη και άμεση μορφή μετά το “Fire”, με κοφτό riffing, δυναμικό rhythm section και refrain που λειτουργεί σαν αντίδραση απέναντι σε πίεση ή έλεγχο. Δεν έχει το μνημονικό status των singles, όμως είναι αποτελεσματικό γιατί δεν προσπαθεί να γίνει κάτι που δεν είναι: fast, direct, guitar-led hard rock. Η RYM το ξεχωρίζει ανάμεσα στα πιο δυνατά non-single tracks.</t>
+  </si>
+  <si>
+    <t>Το album κλείνει με το πιο απροκάλυπτα party-rock τραγούδι. Ο τίτλος φέρνει τις κλασικές εικόνες αυτοκινήτου, νεανικής ερωτικής περιπέτειας και rock ’n’ roll ελευθερίας. Η μουσική έχει έντονο AC/DC homage χαρακτήρα: απλό boogie riff, rhythm-first προσέγγιση και προσιτό chorus. Δεν στοχεύει σε δραματικό φινάλε ούτε σε metal epic· προτιμά να τελειώσει το album με χαρά, θόρυβο και την αίσθηση μιας μπάντας που παίζει για να διασκεδάσει. Αυτό είναι περιορισμός αλλά και αρετή: οι Krokus δεν κρύβουν ποτέ ότι στο συγκεκριμένο album η απλότητα του riff είναι συχνά το βασικό τους όπλο.</t>
   </si>
 </sst>
 </file>
@@ -13888,7 +14023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -13898,7 +14033,7 @@
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -17676,6 +17811,38 @@
       </c>
       <c r="J118" s="11" t="s">
         <v>3990</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>4019</v>
+      </c>
+      <c r="D119" s="6">
+        <v>1980</v>
+      </c>
+      <c r="E119" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>4031</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>4033</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>4032</v>
+      </c>
+      <c r="I119" s="11" t="s">
+        <v>4020</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>4021</v>
       </c>
     </row>
   </sheetData>
@@ -17911,6 +18078,8 @@
     <hyperlink ref="I117" r:id="rId229" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
     <hyperlink ref="J118" r:id="rId230" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
     <hyperlink ref="I118" r:id="rId231" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
+    <hyperlink ref="I119" r:id="rId232" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
+    <hyperlink ref="J119" r:id="rId233" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17918,7 +18087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1123"/>
+  <dimension ref="A1:I1133"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -48440,6 +48609,280 @@
       </c>
       <c r="I1123" s="6"/>
     </row>
+    <row r="1124" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1124" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1124" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1124" s="7" t="s">
+        <v>4023</v>
+      </c>
+      <c r="D1124" s="7" t="s">
+        <v>4034</v>
+      </c>
+      <c r="E1124" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F1124" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1124" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1124" s="9" t="s">
+        <v>4044</v>
+      </c>
+      <c r="I1124" s="6"/>
+    </row>
+    <row r="1125" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1125" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1125" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1125" s="7" t="s">
+        <v>4024</v>
+      </c>
+      <c r="D1125" s="7" t="s">
+        <v>4035</v>
+      </c>
+      <c r="E1125" s="20">
+        <v>3.85</v>
+      </c>
+      <c r="F1125" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1125" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1125" s="9" t="s">
+        <v>4045</v>
+      </c>
+      <c r="I1125" s="6"/>
+    </row>
+    <row r="1126" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1126" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1126" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1126" s="7" t="s">
+        <v>4025</v>
+      </c>
+      <c r="D1126" s="7" t="s">
+        <v>4036</v>
+      </c>
+      <c r="E1126" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F1126" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1126" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1126" s="9" t="s">
+        <v>4046</v>
+      </c>
+      <c r="I1126" s="6"/>
+    </row>
+    <row r="1127" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1127" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1127" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1127" s="7" t="s">
+        <v>4026</v>
+      </c>
+      <c r="D1127" s="7" t="s">
+        <v>4037</v>
+      </c>
+      <c r="E1127" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F1127" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1127" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1127" s="9" t="s">
+        <v>4047</v>
+      </c>
+      <c r="I1127" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1128" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1128" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1128" s="7" t="s">
+        <v>4030</v>
+      </c>
+      <c r="D1128" s="7" t="s">
+        <v>4038</v>
+      </c>
+      <c r="E1128" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F1128" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1128" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="H1128" s="9" t="s">
+        <v>4048</v>
+      </c>
+      <c r="I1128" s="6"/>
+    </row>
+    <row r="1129" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1129" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1129" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1129" s="7" t="s">
+        <v>4028</v>
+      </c>
+      <c r="D1129" s="7" t="s">
+        <v>4039</v>
+      </c>
+      <c r="E1129" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F1129" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1129" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1129" s="9" t="s">
+        <v>4049</v>
+      </c>
+      <c r="I1129" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1130" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1130" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1130" s="7" t="s">
+        <v>4029</v>
+      </c>
+      <c r="D1130" s="7" t="s">
+        <v>4040</v>
+      </c>
+      <c r="E1130" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F1130" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1130" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="H1130" s="9" t="s">
+        <v>4050</v>
+      </c>
+      <c r="I1130" s="6"/>
+    </row>
+    <row r="1131" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1131" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1131" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1131" s="7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D1131" s="7" t="s">
+        <v>4041</v>
+      </c>
+      <c r="E1131" s="20">
+        <v>4</v>
+      </c>
+      <c r="F1131" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1131" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1131" s="9" t="s">
+        <v>4051</v>
+      </c>
+      <c r="I1131" s="6"/>
+    </row>
+    <row r="1132" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1132" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1132" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1132" s="7" t="s">
+        <v>4027</v>
+      </c>
+      <c r="D1132" s="7" t="s">
+        <v>4042</v>
+      </c>
+      <c r="E1132" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F1132" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1132" s="12">
+        <v>3.75</v>
+      </c>
+      <c r="H1132" s="9" t="s">
+        <v>4052</v>
+      </c>
+      <c r="I1132" s="6"/>
+    </row>
+    <row r="1133" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1133" s="6">
+        <v>4684547</v>
+      </c>
+      <c r="B1133" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1133" s="7" t="s">
+        <v>4022</v>
+      </c>
+      <c r="D1133" s="7" t="s">
+        <v>4043</v>
+      </c>
+      <c r="E1133" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F1133" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1133" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1133" s="9" t="s">
+        <v>4053</v>
+      </c>
+      <c r="I1133" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BA5AF0-0B79-4595-A970-595F957F4B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF477930-DF91-457F-A5A4-14ABE5617FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4387" uniqueCount="4054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="4088">
   <si>
     <t>No</t>
   </si>
@@ -13438,6 +13438,108 @@
   </si>
   <si>
     <t>Το album κλείνει με το πιο απροκάλυπτα party-rock τραγούδι. Ο τίτλος φέρνει τις κλασικές εικόνες αυτοκινήτου, νεανικής ερωτικής περιπέτειας και rock ’n’ roll ελευθερίας. Η μουσική έχει έντονο AC/DC homage χαρακτήρα: απλό boogie riff, rhythm-first προσέγγιση και προσιτό chorus. Δεν στοχεύει σε δραματικό φινάλε ούτε σε metal epic· προτιμά να τελειώσει το album με χαρά, θόρυβο και την αίσθηση μιας μπάντας που παίζει για να διασκεδάσει. Αυτό είναι περιορισμός αλλά και αρετή: οι Krokus δεν κρύβουν ποτέ ότι στο συγκεκριμένο album η απλότητα του riff είναι συχνά το βασικό τους όπλο.</t>
+  </si>
+  <si>
+    <t>Keeper Of The Seven Keys (Part II)</t>
+  </si>
+  <si>
+    <t>Helloween</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/8415848-Helloween-Keeper-Of-The-Seven-Keys-Part-II</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/gJ1CHuzaE_csnCxu2Rbl5GQoySzQnNIU0d_hY_4e0aw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTg0MTU4/NDgtMTc2OTE4MDUw/OS03MDQ0LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Noise International – N 0117-1 (Germany, 1988, LP, Album, Misprint, Gatefold). Γερμανική πρώτη/κλασική έκδοση σε gatefold εξώφυλλο, διανεμημένη από τη SPV (08-449). Φέρει το γνωστό misprint στην ετικέτα (γράφει λανθασμένα το "Save Us" αντί για το πραγματικό tracklist της Πλευράς Β). Η συγκεκριμένη κόπια είναι χωρίς το εσωτερικό τυπωμένο ένθετο (no inner sleeve). Mastered στο Studio-Nord-Bremen (SNB etched στα runouts).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Keeper Of The Seven Keys (Part II) κυκλοφόρησε τον Αύγουστο του 1988 και θεωρείται ευρέως το άλμπουμ-ορόσημο που καθόρισε και γέννησε το ευρωπαϊκό power metal κίνημα. Η παραγωγή έγινε από τον Tommy Newton και τους Helloween στα Horus Sound Studio του Hannover, ενώ η μίξη έγινε επίσης στα Horus Sound Studio. Ηχητικά διαθέτει τεράστιο δυναμικό εύρος, απίστευτη μελωδική διαύγεια στις διπλές κιθάρες των Michael Weikath και Kai Hansen, και τα εμβληματικά φωνητικά του Michael Kiske. Η γερμανική κοπή της Noise International αποδίδει υποδειγματικά την ταχύτητα και τον όγκο της παραγωγής.</t>
+  </si>
+  <si>
+    <t>Invitation</t>
+  </si>
+  <si>
+    <t>Eagle Fly Free</t>
+  </si>
+  <si>
+    <t>You Always Walk Alone</t>
+  </si>
+  <si>
+    <t>Rise And Fall</t>
+  </si>
+  <si>
+    <t>Dr. Stein</t>
+  </si>
+  <si>
+    <t>We Got The Right</t>
+  </si>
+  <si>
+    <t>March Of Time</t>
+  </si>
+  <si>
+    <t>I Want Out</t>
+  </si>
+  <si>
+    <t>Keeper Of The Seven Keys</t>
+  </si>
+  <si>
+    <t>Power Metal, Heavy Metal [European Power Metal, Speed Metal, Melodic Metal, Epic Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Instrumental Metal [Epic Intro, Keyboard-Orchestral Metal, Fantasy Prelude]</t>
+  </si>
+  <si>
+    <t>Power Metal, Speed Metal [Uplifting Power Metal, Double-Kick Metal, Anthemic Speed Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Heavy Metal [Melodic Power Metal, Emotional Metal, Kiske-style Vocal Anthem]</t>
+  </si>
+  <si>
+    <t>Power Metal, Speed Metal [Fast Melodic Metal, Humorous Power Metal, Euro Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Heavy Metal [Theatrical Metal, Catchy Power Metal, Horror-Fantasy Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Heavy Metal [Epic Power Ballad, Arena Metal, Melodic Heavy Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Speed Metal [Technical Speed Metal, Progressive Power Metal, Urgent Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Heavy Metal [Freedom Anthem, Melodic Metal, Arena Power Metal]</t>
+  </si>
+  <si>
+    <t>Power Metal, Progressive Metal [Epic Power Metal, Fantasy Metal, Long-form Concept Suite]</t>
+  </si>
+  <si>
+    <t>Από τις πιο μουσικά πλούσιες και επείγουσες συνθέσεις των Helloween. Ο χρόνος «παρελαύνει» και δεν περιμένει κανέναν· το τραγούδι μιλά για τις επιλογές, τις συνέπειες και τη συνειδητοποίηση ότι δεν υπάρχει ανεξάντλητος χρόνος. Η μουσική μεταφράζει αυτή την πίεση με γρήγορα, σχεδόν progressive περάσματα, γερές διπλές κάσες και αλλαγές που δεν μοιάζουν ποτέ επιτηδευμένες. Η κιθαριστική εργασία των Kai Hansen και Michael Weikath συνδυάζει ταχύτητα με μελωδική λογική, ενώ η φωνή του Kiske παραμένει στο κέντρο. Είναι λιγότερο άμεσα poppy από το “Dr. Stein”, αλλά βαθύτερο σε δομή και από τα βασικά album peaks. Τα public ratings το κατατάσσουν δίκαια κοντά στην κορυφή του δίσκου.</t>
+  </si>
+  <si>
+    <t>Σύντομη, κινηματογραφική εισαγωγή που χτίζει το fantasy/epic περιβάλλον του δίσκου. Δεν είναι τραγούδι με κανονική verse-chorus δομή· λειτουργεί ως τελετουργικό άνοιγμα, με keyboard/orchestral υφή που δημιουργεί την αίσθηση ότι μια ιστορία πρόκειται να ξεκινήσει. Η “πρόσκληση” του τίτλου καλεί τον ακροατή να περάσει σε έναν κόσμο όπου η μοίρα, η ελευθερία, το καλό και το κακό παρουσιάζονται με μεγάλους power-metal όρους. Η χαμηλότερη βαθμολογία δεν είναι κριτική ποιότητας, αφορά τη λειτουργία του ως intro. Η αξία του φαίνεται ακριβώς στη μετάβαση προς το “Eagle Fly Free”.</t>
+  </si>
+  <si>
+    <t>Η απόλυτη power-metal σύνθεση των Helloween και ένα από τα τραγούδια που καθόρισαν ολόκληρο το είδος. Το opening riff, το double-kick drive, οι δίδυμες κιθάρες και η υψηλή, καθαρή φωνή του Michael Kiske λειτουργούν σαν ιδανικός συνδυασμός ταχύτητας και μελωδίας. Ο αετός του τίτλου είναι εικόνα ελευθερίας και αυτοδιάθεσης, μην αφήνεις κανέναν να σε περιορίσει, πέτα πάνω από τους φόβους σου και διάλεξε τη δική σου πορεία. Η σύνθεση δεν είναι απλώς γρήγορη· έχει εξαιρετικά οργανωμένα transitions, μεγάλο chorus και κιθαριστικές μελωδίες που συνεχίζουν να λειτουργούν σαν hook ακόμη και χωρίς φωνητικά. Το Metal Crypt το περιγράφει ως πιθανότατα το καλύτερο Helloween τραγούδι της Kiske εποχής, και τα δημόσια track ratings το επιβεβαιώνουν ως κορυφαίο σημείο του album.</t>
+  </si>
+  <si>
+    <t>Μετά την ακραία εξωστρέφεια του “Eagle Fly Free”, το album εισέρχεται σε πιο συναισθηματικό πεδίο. Ο τίτλος μοιάζει με σκληρή παραδοχή, τελικά περπατάς μόνος, ακόμη και όταν είσαι surrounded by people. Η μουσική παραμένει γρήγορη και μελωδική, αλλά το chorus έχει μεγαλύτερη δραματική/μελαγχολική χροιά. Η σύνθεση του Kiske επιτρέπει στη φωνή του να γίνει πιο ανθρώπινη, όχι μόνο ηρωική, οι ψηλές νότες δεν χρησιμοποιούνται για επίδειξη, αλλά για να μεταφέρουν ευαλωτότητα. Δεν είναι τόσο τεράστιο anthem όσο το προηγούμενο track, όμως αποτελεί ουσιαστικό μέρος της ισορροπίας του δίσκου, δείχνοντας ότι το power metal του συγκροτήματος μπορούσε να εκφράσει και μοναξιά.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, πιο παιχνιδιάρικο και με εσκεμμένη δόση χιούμορ. Ο τίτλος αφορά τον κύκλο ανόδου και πτώσης στη ζωή, αλλά οι Helloween δεν τον αντιμετωπίζουν ως βαρύ φιλοσοφικό θέμα. Η μπάντα χρησιμοποιεί γρήγορες αλλαγές, animated φωνητικά και κιθαριστικά περάσματα που προσθέτουν σχεδόν cartoonish ενέργεια. Αυτή η ελαφρότητα είναι ουσιώδης στην Helloween ταυτότητα, το συγκρότημα δεν χρειαζόταν να είναι μόνιμα σκοτεινό ή υπερ-σοβαρό για να ακούγεται metal. Το track δεν έχει το διαχρονικό βάρος του “Eagle Fly Free” ή του “I Want Out”, αλλά είναι γεμάτο ιδέες και κρατά τον δίσκο ζωντανό.</t>
+  </si>
+  <si>
+    <t>Η πιο θεατρική και πιασάρικη στιγμή της A πλευράς. Ο Dr. Stein είναι ένας mad-scientist χαρακτήρας, μια φιγούρα που δημιουργεί ή χειραγωγεί ζωή σαν να είναι παιχνίδι. Η μουσική μετατρέπει αυτή την horror/fantasy εικόνα σε playful power metal, κύριο riff που μένει αμέσως, επιτακτικό chorus, γρήγορη κιθαριστική δουλειά και φωνητικές γραμμές που δίνουν στον Kiske χώρο να είναι και dramatic και fun. Το τραγούδι λειτουργεί σαν heavy-metal comic strip, αλλά η σύνθεση είναι πολύ πιο αυστηρή και αποτελεσματική από ένα novelty track. Είναι από τα καλύτερα παραδείγματα της Helloween ικανότητας να συνδυάζει τεχνική, χιούμορ και pop-like hook χωρίς να χάνει μεταλλικό βάρος.</t>
+  </si>
+  <si>
+    <t>Η πιο ώριμη και πιο αργή melodic-metal στιγμή του δίσκου. Ο τίτλος είναι δήλωση συλλογικού δικαιώματος, η ελευθερία και η επιλογή της δικής μας ζωής δεν είναι προνόμιο που παραχωρεί κάποιος άλλος. Η μουσική δεν είναι αυστηρή μπαλάντα, αλλά μια mid-tempo epic power-metal σύνθεση με μεγάλο, συναισθηματικό refrain. Ο Kiske τραγουδά με ευρύτητα και καθαρότητα, ενώ οι κιθάρες κρατούν το τραγούδι σε metal πλαίσιο αντί να το αφήσουν να γίνει AOR. Η θέση του στην αρχή της B πλευράς είναι σωστή, δίνει χρόνο μετά το υπερκινητικό πρώτο μισό, πριν το album επιστρέψει στη μεγάλη ταχύτητα του “March Of Time”.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη freedom anthem σύνθεση του Kai Hansen και ίσως το πιο καθολικό Helloween τραγούδι. Το “I Want Out” είναι η επιθυμία διαφυγής από καταπίεση, ρουτίνα, κοινωνικό έλεγχο ή οποιοδήποτε σύστημα καθορίζει τη ζωή σου. Η μουσική είναι σχεδόν τέλεια power-metal pop, σύντομη, δυναμική, γεμάτη twin-guitar μελωδίες, με chorus που μπορεί να τραγουδηθεί από metal audience αλλά και από οποιονδήποτε ακούει melodic rock. Είναι σημαντικό ότι η αμεσότητά του δεν σημαίνει απλοποίηση, το arrangement, τα guitar harmonies και η Kiske ερμηνεία είναι εξαιρετικά προσεγμένα. Το τραγούδι έγινε η τελευταία μεγάλη σύνθεση του Hansen με τους Helloween πριν φύγει για να ιδρύσει τους Gamma Ray, κάτι που του δίνει επιπλέον αίσθηση αποχαιρετισμού. Τα δημόσια track ratings το τοποθετούν σχεδόν ισότιμα με το “Eagle Fly Free”.</t>
+  </si>
+  <si>
+    <t>Το δεκατριάλεπτο title track κλείνει το album με πλήρη epic-power-metal κλίμακα. Ο Keeper είναι μυθική φιγούρα που κρατά τα επτά κλειδιά, άρα τη δύναμη να διατηρήσει ή να απελευθερώσει την ισορροπία του κόσμου. Η σύνθεση αναπτύσσεται σε διαδοχικές ενότητες, ατμοσφαιρικό ξεκίνημα, πιο βαριά riffs, γρήγορα speed-metal περάσματα, instrumental ανάπτυξη, δραματικά vocal sections και τελική κορύφωση. Δεν είναι απλώς ένα μεγάλο τραγούδι επειδή διαρκεί πολύ· κάθε μέρος υπηρετεί την αίσθηση μιας ιστορίας που περνά από δοκιμασία σε σύγκρουση και τελικά σε λύτρωση. Ο Kiske έχει χώρο να λειτουργήσει σαν αφηγητής, οι κιθάρες να δώσουν διαφορετικά μοτίβα και η μπάντα να δείξει ότι το power metal μπορεί να είναι και σύνθετο και συναρπαστικό. Είναι μαζί με “Eagle Fly Free” και “I Want Out” ο θεμέλιος λίθος του δίσκου.</t>
   </si>
 </sst>
 </file>
@@ -14023,7 +14125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14935,7 +15037,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>31700342</v>
       </c>
@@ -15063,7 +15165,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33253932</v>
       </c>
@@ -15703,7 +15805,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>30630553</v>
       </c>
@@ -15863,7 +15965,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>26012116</v>
       </c>
@@ -16023,7 +16125,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="63" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>14186441</v>
       </c>
@@ -16055,7 +16157,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>33653532</v>
       </c>
@@ -16149,7 +16251,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>28423156</v>
       </c>
@@ -16245,7 +16347,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>15223559</v>
       </c>
@@ -16661,7 +16763,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>29667079</v>
       </c>
@@ -16693,7 +16795,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>28729798</v>
       </c>
@@ -16789,7 +16891,7 @@
         <v>2851</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>33527013</v>
       </c>
@@ -16853,7 +16955,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>2598614</v>
       </c>
@@ -16917,7 +17019,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>34750368</v>
       </c>
@@ -17109,7 +17211,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>12520978</v>
       </c>
@@ -17141,7 +17243,7 @@
         <v>3258</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>2782114</v>
       </c>
@@ -17205,7 +17307,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>1382323</v>
       </c>
@@ -17237,7 +17339,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>646934</v>
       </c>
@@ -17269,7 +17371,7 @@
         <v>3398</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>4116216</v>
       </c>
@@ -17333,7 +17435,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>2661964</v>
       </c>
@@ -17397,7 +17499,7 @@
         <v>3533</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>2903507</v>
       </c>
@@ -17461,7 +17563,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>8864393</v>
       </c>
@@ -17653,7 +17755,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>12991988</v>
       </c>
@@ -17843,6 +17945,38 @@
       </c>
       <c r="J119" s="11" t="s">
         <v>4021</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>4055</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>4054</v>
+      </c>
+      <c r="D120" s="6">
+        <v>1988</v>
+      </c>
+      <c r="E120" s="10">
+        <v>3.84</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>4069</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>4059</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>4058</v>
+      </c>
+      <c r="I120" s="11" t="s">
+        <v>4056</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>4057</v>
       </c>
     </row>
   </sheetData>
@@ -18080,6 +18214,8 @@
     <hyperlink ref="I118" r:id="rId231" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
     <hyperlink ref="I119" r:id="rId232" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
     <hyperlink ref="J119" r:id="rId233" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
+    <hyperlink ref="I120" r:id="rId234" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
+    <hyperlink ref="J120" r:id="rId235" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18087,7 +18223,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1133"/>
+  <dimension ref="A1:I1142"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -48883,6 +49019,251 @@
       </c>
       <c r="I1133" s="6"/>
     </row>
+    <row r="1134" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1134" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1134" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1134" s="7" t="s">
+        <v>4060</v>
+      </c>
+      <c r="D1134" s="7" t="s">
+        <v>4070</v>
+      </c>
+      <c r="E1134" s="20">
+        <v>3.43</v>
+      </c>
+      <c r="F1134" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1134" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1134" s="9" t="s">
+        <v>4080</v>
+      </c>
+      <c r="I1134" s="6"/>
+    </row>
+    <row r="1135" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1135" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1135" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1135" s="7" t="s">
+        <v>4061</v>
+      </c>
+      <c r="D1135" s="7" t="s">
+        <v>4071</v>
+      </c>
+      <c r="E1135" s="20">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F1135" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1135" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1135" s="9" t="s">
+        <v>4081</v>
+      </c>
+      <c r="I1135" s="6"/>
+    </row>
+    <row r="1136" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1136" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1136" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1136" s="7" t="s">
+        <v>4062</v>
+      </c>
+      <c r="D1136" s="7" t="s">
+        <v>4072</v>
+      </c>
+      <c r="E1136" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="F1136" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1136" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1136" s="9" t="s">
+        <v>4082</v>
+      </c>
+      <c r="I1136" s="6"/>
+    </row>
+    <row r="1137" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1137" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1137" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1137" s="7" t="s">
+        <v>4063</v>
+      </c>
+      <c r="D1137" s="7" t="s">
+        <v>4073</v>
+      </c>
+      <c r="E1137" s="20">
+        <v>3.63</v>
+      </c>
+      <c r="F1137" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1137" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H1137" s="9" t="s">
+        <v>4083</v>
+      </c>
+      <c r="I1137" s="6"/>
+    </row>
+    <row r="1138" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1138" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1138" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1138" s="7" t="s">
+        <v>4064</v>
+      </c>
+      <c r="D1138" s="7" t="s">
+        <v>4074</v>
+      </c>
+      <c r="E1138" s="20">
+        <v>4.01</v>
+      </c>
+      <c r="F1138" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1138" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1138" s="9" t="s">
+        <v>4084</v>
+      </c>
+      <c r="I1138" s="6"/>
+    </row>
+    <row r="1139" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1139" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1139" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1139" s="7" t="s">
+        <v>4065</v>
+      </c>
+      <c r="D1139" s="7" t="s">
+        <v>4075</v>
+      </c>
+      <c r="E1139" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F1139" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1139" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1139" s="9" t="s">
+        <v>4085</v>
+      </c>
+      <c r="I1139" s="6"/>
+    </row>
+    <row r="1140" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1140" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1140" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1140" s="7" t="s">
+        <v>4066</v>
+      </c>
+      <c r="D1140" s="7" t="s">
+        <v>4076</v>
+      </c>
+      <c r="E1140" s="20">
+        <v>4.18</v>
+      </c>
+      <c r="F1140" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1140" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1140" s="9" t="s">
+        <v>4079</v>
+      </c>
+      <c r="I1140" s="6"/>
+    </row>
+    <row r="1141" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1141" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1141" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1141" s="7" t="s">
+        <v>4067</v>
+      </c>
+      <c r="D1141" s="7" t="s">
+        <v>4077</v>
+      </c>
+      <c r="E1141" s="20">
+        <v>4.33</v>
+      </c>
+      <c r="F1141" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1141" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H1141" s="9" t="s">
+        <v>4086</v>
+      </c>
+      <c r="I1141" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A1142" s="6">
+        <v>8415848</v>
+      </c>
+      <c r="B1142" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1142" s="7" t="s">
+        <v>4068</v>
+      </c>
+      <c r="D1142" s="7" t="s">
+        <v>4078</v>
+      </c>
+      <c r="E1142" s="20">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F1142" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="G1142" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1142" s="9" t="s">
+        <v>4087</v>
+      </c>
+      <c r="I1142" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF477930-DF91-457F-A5A4-14ABE5617FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C3287C-D1C8-49AC-97C5-07D5BE6F753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="4088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="4126">
   <si>
     <t>No</t>
   </si>
@@ -13540,6 +13540,120 @@
   </si>
   <si>
     <t>Το δεκατριάλεπτο title track κλείνει το album με πλήρη epic-power-metal κλίμακα. Ο Keeper είναι μυθική φιγούρα που κρατά τα επτά κλειδιά, άρα τη δύναμη να διατηρήσει ή να απελευθερώσει την ισορροπία του κόσμου. Η σύνθεση αναπτύσσεται σε διαδοχικές ενότητες, ατμοσφαιρικό ξεκίνημα, πιο βαριά riffs, γρήγορα speed-metal περάσματα, instrumental ανάπτυξη, δραματικά vocal sections και τελική κορύφωση. Δεν είναι απλώς ένα μεγάλο τραγούδι επειδή διαρκεί πολύ· κάθε μέρος υπηρετεί την αίσθηση μιας ιστορίας που περνά από δοκιμασία σε σύγκρουση και τελικά σε λύτρωση. Ο Kiske έχει χώρο να λειτουργήσει σαν αφηγητής, οι κιθάρες να δώσουν διαφορετικά μοτίβα και η μπάντα να δείξει ότι το power metal μπορεί να είναι και σύνθετο και συναρπαστικό. Είναι μαζί με “Eagle Fly Free” και “I Want Out” ο θεμέλιος λίθος του δίσκου.</t>
+  </si>
+  <si>
+    <t>Emeralds</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/e6sDWr6q6kVKLSgJ5D6NigyrmDTYOoTegIDXKWZ2dq0/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3MDA1/MzAzLTE3NzU2MDc3/NjMtODQ5MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/37005303-Parlor-Greens-Emeralds</t>
+  </si>
+  <si>
+    <t>Colemine Records – CLMN 12072 (US, 2026, LP, Album, Limited Edition, Stereo, Gold). Αμερικανική περιορισμένη έκδοση σε χρυσό βινύλιο, ηχογραφημένη τον Ιανουάριο του 2025 στο Portage Lounge. Το lacquer cut έγινε από τη Well Made Music (με χαραγμένα τα αρχικά dP στα runouts) από τον Doug Krebs, ενώ η φυσική κατασκευή/pressing έγινε στη GZ Media (με κωδικό 309074E). Φέρει αυτοκόλλητο "Made in Czech Republic" στο εξωτερικό ζελατινέ ζωνάρι (shrink wrap) και πολλαπλούς κωδικούς (πρώτος καταλόγου στο εξώφυλλο/ράχη, δεύτερος σε αυτοκόλλητο και ετικέτες).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Οι Parlor Greens είναι ένα δυναμικό οργάνικο τρίο αποτελούμενο από τους Adam Scone (hammond organ), Jimmy James (κιθάρα) και Tim Carman (τύμπανα), με παραγωγό τον Leroi Conroy. Το Emeralds κυκλοφόρησε τον Απρίλιο του 2026 από την Colemine Records και αποτελεί σημείο αναφοράς για τη σύγχρονη deep funk, soul-jazz και instrumental σκηνή. Ο ήχος χαρακτηρίζεται από ωμή αναλογική ζεστασιά, groove αισθητική 60s/70s, υποδειγματικό διαχωρισμό οργάνων και το χαρακτηριστικό βαρύ, οργανικό μπάσο του Hammond B3 σε συνδυασμό με κοφτερά κιθαριστικά licks και στιβαρά τύμπανα.</t>
+  </si>
+  <si>
+    <t>Eat Your Greens</t>
+  </si>
+  <si>
+    <t>Mustard Sauce</t>
+  </si>
+  <si>
+    <t>Drop Top</t>
+  </si>
+  <si>
+    <t>Parlor Change</t>
+  </si>
+  <si>
+    <t>Letter To Brother Ben</t>
+  </si>
+  <si>
+    <t>Francisco Smack</t>
+  </si>
+  <si>
+    <t>Jolene</t>
+  </si>
+  <si>
+    <t>Lion’s Mane</t>
+  </si>
+  <si>
+    <t>Red Dog</t>
+  </si>
+  <si>
+    <t>Queen Of My Heart</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul-Jazz [Instrumental Funk, Organ Trio, Deep Funk, Hammond Groove, Retro Soul]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η διασκευή του Dolly Parton είναι έξυπνη, επειδή δεν προσπαθεί να ανταγωνιστεί την αφηγηματική δύναμη και τους στίχους του πρωτοτύπου. Οι Parlor Greens απομονώνουν τη μελωδική ένταση της σύνθεσης και τη μετατρέπουν σε organ-soul instrumental. Χωρίς φωνή, η «Jolene» γίνεται λιγότερο ιστορία ζήλιας και περισσότερο μελαγχολικό θέμα, όπου το Hammond κρατά την απειλή και η κιθάρα προσθέτει λεπτές country/soul αποχρώσεις. Η Bandcamp Daily ξεχωρίζει τη διασκευή ως παράδειγμα της ικανότητας του συγκροτήματος να βάζει προσωπική σφραγίδα στην παράδοση. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το ιδανικό άνοιγμα, επειδή δεν χρειάζεται φωνές ή περίπλοκο concept για να δηλώσει την ταυτότητα του δίσκου. Το track μπαίνει με four-on-the-floor ρυθμό, Hammond όργανο και κιθάρα που κινούνται σαν ατμομηχανή. Η αναφορά στον Charles Earland δεν είναι επιφανειακή, η σύνθεση αξιοποιεί τη λογική του organ groove ως φυσικής, σχεδόν σωματικής κίνησης. Το “Eat Your Greens” ακούγεται παιχνιδιάρικο και ευχάριστο, όμως η εκτέλεση έχει ακρίβεια , ο Scone οργανώνει το groove, ο James δίνει καθαρές guitar γραμμές και ο Carman κρατά το beat ασταμάτητο. Είναι μουσική που σε κάνει να κινείσαι πριν καν προλάβεις να τη «αναλύσεις». </t>
+  </si>
+  <si>
+    <t>Τίτλος με χιουμοριστικό, καθημερινό χαρακτήρα, αλλά η μουσική είναι πυκνή και καλοδουλεμένη. Το “Mustard Sauce” συνεχίζει τη deep-funk βάση του opener, με Hammond stabs, κιθαριστικές φράσεις και rhythm section που προτιμά το pocket από την επίδειξη. Η «σάλτσα» του τίτλου μπορεί να ιδωθεί ως το seasoning, το στοιχείο που προσθέτει πικάντικη, λίγο τραχιά γεύση σε μια ήδη σφιχτή soul-jazz βάση. Δεν διεκδικεί το μεγάλο anthem status του “Eat Your Greens”, αλλά λειτουργεί ως οργανικό jam με σωστή οικονομία. Είναι από τα tracks που αποκαλύπτουν πόσο πολύ η μπάντα καταλαβαίνει ότι το funk πρέπει πρώτα να υπηρετεί τον ρυθμό.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πιο ανοιχτό και πιο cruising-oriented, το “Drop Top” αφήνει τη μουσική να αποκτήσει αίσθηση δρόμου, αέρα και αργής κίνησης. Η κιθάρα του Jimmy James αναφέρεται από τους κριτικούς ως έχουσα την ίδια μελαγχολική cadence με το “I Forgot To Be Your Lover” του William Bell, κάτι που εξηγεί γιατί το κομμάτι ακούγεται πιο soulful και λιγότερο party-driven. Το όργανο δεν προσπαθεί να γεμίσει κάθε κενό· αφήνει χώρο στην κιθάρα να αναπνεύσει. Η αξία του είναι η ατμόσφαιρα, δεν είναι απλώς deep-funk workout, αλλά μικρό instrumental R&amp;B τοπίο. </t>
+  </si>
+  <si>
+    <t>Το τραγούδι παίζει με το όνομα του συγκροτήματος και τη λογική της «αλλαγής» ως διακριτικής μετατόπισης μέσα στο groove. Δεν αλλάζει ριζικά την αισθητική του δίσκου· αντίθετα, δουλεύει σαν κομμάτι που δείχνει πόσες παραλλαγές μπορεί να πάρει ένα organ-trio pocket. Τα drums κρατούν αυστηρή βάση, η κιθάρα παρεμβαίνει με σύντομες, κοφτές απαντήσεις και το Hammond χτίζει αρμονική κίνηση χωρίς υπερβολικό soloing. Είναι πιο λειτουργικό από το να γίνει αυθύπαρκτο highlight, αλλά αυτή η λειτουργικότητα είναι αρετή, κρατά την πρώτη πλευρά συνεκτική και δίνει χώρο στο title track να έρθει με μεγαλύτερη μελωδική παρουσία.</t>
+  </si>
+  <si>
+    <t>Το title track λειτουργεί σαν το χρωματικό κέντρο του album. Τα «σμαράγδια» υποδηλώνουν κάτι λαμπερό, πολύτιμο και βαθύχρωμο, και η μουσική επιλέγει mid-tempo soul-jazz κίνηση αντί για καθαρή ταχύτητα. Το Hammond του Scone παίρνει πιο μελωδικό ρόλο, η κιθάρα απαντά με ζεστές γραμμές και το rhythm section κρατά το κομμάτι σε γήινο funk έδαφος. Δεν χρειάζεται τεράστιες κορυφώσεις, η δύναμη έρχεται από το χρώμα και από την αίσθηση ότι οι τρεις μουσικοί ακούν πραγματικά ο ένας τον άλλον. Είναι αντιπροσωπευτικό του πώς το album τιμά την παλιά organ-soul παράδοση χωρίς να περιορίζεται σε αναβίωση.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με gospel-tinged shuffle και πιο προσωπικό τόνο. Ο “αδελφός Ben” μπορεί να διαβαστεί ως συγκεκριμένη αφιέρωση ή ως συμβολικός συνομιλητής, αλλά μουσικά το track λειτουργεί σαν επιστολή μέσα από ρυθμό, ζεστό Hammond, shuffle drums και κιθάρα που συνομιλεί αντί να ανταγωνίζεται. Οι πηγές ξεχωρίζουν ακριβώς το shuffle του Tim Carman και το gospel χρώμα του κομματιού. Η μπάντα δείχνει ότι η ένταση δεν χρειάζεται πάντα να έρχεται από γρήγορο funk , μπορεί να έρθει από το swing, τη συναισθηματική αμεσότητα και το σωστό κενό ανάμεσα στις νότες.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο ωμό, ξερό instrumental funk. Ο τίτλος έχει το αίσθημα μιας απότομης, σχεδόν κωμικής γροθιάς , και η σύνθεση ανταποκρίνεται με κοφτές φράσεις, δυναμικά accents και άμεση οργανική αντιπαράθεση. Το Hammond και η κιθάρα εναλλάσσονται σαν call-and-response, ενώ το rhythm section κρατά το track γρήγορο και νευρικό. Δεν έχει την τρυφερότητα του “Letter To Brother Ben”, αλλά ακριβώς γι’ αυτό λειτουργεί σωστά στη σειρά, επαναφέρει το gritty, physical funk στοιχείο και προετοιμάζει την απρόσμενη διασκευή που ακολουθεί.</t>
+  </si>
+  <si>
+    <t>Από τις πιο sophisticated στιγμές του δίσκου. Η αναφορά στον Dr. Lonnie Smith έχει ουσία, το track δεν βασίζεται αποκλειστικά στο instant hook, αλλά σε πιο σύνθετο soul-jazz χτίσιμο, με Hammond αρμονίες, πιο αργές μετατοπίσεις και διακριτική modal αίσθηση. Ο τίτλος παραπέμπει σε δύναμη και φυσική ανάπτυξη, και η σύνθεση το αποδίδει χωρίς βιασύνη, αφήνει τα όργανα να εξελιχθούν μέσα στον χρόνο. Είναι το track που δείχνει καλύτερα ότι οι Parlor Greens δεν είναι μόνο heavy instrumental funk band αλλά και organ-jazz ensemble με ερμηνευτικό εύρος.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το πιο βαρύ και πιο R&amp;B-φορτισμένο groove του album. Οι πηγές το περιγράφουν ως την «heaviest shade of early R&amp;B», με crunchy κιθάρα και καυτά solos από James και Scone. Ο τίτλος δεν χρειάζεται να αποκτήσει αφηγηματική εξήγηση, η μουσική λειτουργεί σαν χαρακτήρας , τραχύς, ζεστός, χαμηλά στο έδαφος και επίμονος. Η κιθάρα δίνει bite, το Hammond απαντά με ισχύ και τα drums κρατούν τόσο σταθερό pocket ώστε ακόμη και τα solos δεν σπάνε ποτέ τη συνοχή. Είναι ένα από τα μεγάλα groove peaks του δίσκου. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το σωστό κλείσιμο, γιατί απομακρύνεται από την άμεση fun διάθεση και επιλέγει συναισθηματικό βάρος. Ο Jimmy James έγραψε το τραγούδι για τη μητέρα του λίγο μετά τον θάνατό της, κάτι που εξηγεί τον χαρακτήρα του ως memorial instrumental και όχι ως απλή slow ballad. Το Hammond είναι ζεστό και συγκρατημένο, η κιθάρα αποφεύγει τη φλυαρία, και τα drums κρατούν διακριτικά τη σύνθεση ενωμένη. Το αποτέλεσμα δείχνει την ωριμότητα της μπάντας, ένα organ trio μπορεί να κάνει το κοινό να χορέψει, αλλά μπορεί και να εκφράσει απώλεια χωρίς στίχους. Είναι η πιο συναισθηματικά πλήρης στιγμή του album και δικαίως η υψηλότερα βαθμολογημένη στον πίνακα. </t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Soul-Jazz [Hammond Funk, Charles Earland-style Groove, Four-on-the-Floor Instrumental]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Funk [Deep Funk, Organ Groove, Guitar-led Instrumental Soul]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Jazz-Funk [Slow-Burn Organ Soul, Guitar-Soul, Instrumental R&amp;B]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Funk [Organ Trio Funk, Rhythmic Soul-Jazz, Groove Instrumental]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Jazz-Funk [Melodic Organ Funk, Mid-tempo Instrumental Soul]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Gospel [Gospel Shuffle, Hammond Soul, Deep Groove Jazz]</t>
+  </si>
+  <si>
+    <t>Jazz-Funk, Funk [Raw Instrumental Funk, Organ-Guitar Dialogue, R&amp;B Groove]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Country Soul [Dolly Parton Cover, Organ-Soul Reworking, Instrumental Americana]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Jazz-Funk [Dr. Lonnie Smith-style Organ Jazz, Sophisticated Groove, Modal Soul-Jazz]</t>
+  </si>
+  <si>
+    <t>Funk, Soul-Jazz [Heavy Early R&amp;B, Crunchy Guitar Funk, Organ Trio Workout]</t>
+  </si>
+  <si>
+    <t>Soul-Jazz, Instrumental Soul [Sentimental Organ Ballad, Memorial Piece, Soul-Jazz Closer]</t>
   </si>
 </sst>
 </file>
@@ -14125,7 +14239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -14135,7 +14249,7 @@
     <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="96.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="40.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
@@ -17947,7 +18061,7 @@
         <v>4021</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>8415848</v>
       </c>
@@ -17977,6 +18091,38 @@
       </c>
       <c r="J120" s="11" t="s">
         <v>4057</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>4088</v>
+      </c>
+      <c r="D121" s="6">
+        <v>2026</v>
+      </c>
+      <c r="E121" s="10">
+        <v>3.29</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>4103</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>4092</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>4091</v>
+      </c>
+      <c r="I121" s="11" t="s">
+        <v>4090</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>4089</v>
       </c>
     </row>
   </sheetData>
@@ -18216,6 +18362,8 @@
     <hyperlink ref="J119" r:id="rId233" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
     <hyperlink ref="I120" r:id="rId234" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
     <hyperlink ref="J120" r:id="rId235" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
+    <hyperlink ref="J121" r:id="rId236" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
+    <hyperlink ref="I121" r:id="rId237" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18223,7 +18371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1142"/>
+  <dimension ref="A1:I1153"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -49264,6 +49412,303 @@
       </c>
       <c r="I1142" s="6"/>
     </row>
+    <row r="1143" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1143" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1143" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1143" s="7" t="s">
+        <v>4093</v>
+      </c>
+      <c r="D1143" s="7" t="s">
+        <v>4115</v>
+      </c>
+      <c r="E1143" s="20">
+        <v>4.34</v>
+      </c>
+      <c r="F1143" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1143" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1143" s="9" t="s">
+        <v>4105</v>
+      </c>
+      <c r="I1143" s="6"/>
+    </row>
+    <row r="1144" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1144" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1144" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1144" s="7" t="s">
+        <v>4094</v>
+      </c>
+      <c r="D1144" s="7" t="s">
+        <v>4116</v>
+      </c>
+      <c r="E1144" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F1144" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1144" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1144" s="9" t="s">
+        <v>4106</v>
+      </c>
+      <c r="I1144" s="6"/>
+    </row>
+    <row r="1145" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1145" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1145" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1145" s="7" t="s">
+        <v>4095</v>
+      </c>
+      <c r="D1145" s="7" t="s">
+        <v>4117</v>
+      </c>
+      <c r="E1145" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F1145" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1145" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1145" s="9" t="s">
+        <v>4107</v>
+      </c>
+      <c r="I1145" s="6"/>
+    </row>
+    <row r="1146" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1146" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1146" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1146" s="7" t="s">
+        <v>4096</v>
+      </c>
+      <c r="D1146" s="7" t="s">
+        <v>4118</v>
+      </c>
+      <c r="E1146" s="20">
+        <v>4</v>
+      </c>
+      <c r="F1146" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1146" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1146" s="9" t="s">
+        <v>4108</v>
+      </c>
+      <c r="I1146" s="6"/>
+    </row>
+    <row r="1147" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1147" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1147" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1147" s="7" t="s">
+        <v>4088</v>
+      </c>
+      <c r="D1147" s="7" t="s">
+        <v>4119</v>
+      </c>
+      <c r="E1147" s="20">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F1147" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1147" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1147" s="9" t="s">
+        <v>4109</v>
+      </c>
+      <c r="I1147" s="6"/>
+    </row>
+    <row r="1148" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1148" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1148" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1148" s="7" t="s">
+        <v>4097</v>
+      </c>
+      <c r="D1148" s="7" t="s">
+        <v>4120</v>
+      </c>
+      <c r="E1148" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1148" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1148" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H1148" s="9" t="s">
+        <v>4110</v>
+      </c>
+      <c r="I1148" s="6"/>
+    </row>
+    <row r="1149" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1149" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1149" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1149" s="7" t="s">
+        <v>4098</v>
+      </c>
+      <c r="D1149" s="7" t="s">
+        <v>4121</v>
+      </c>
+      <c r="E1149" s="20">
+        <v>4.08</v>
+      </c>
+      <c r="F1149" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1149" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H1149" s="9" t="s">
+        <v>4111</v>
+      </c>
+      <c r="I1149" s="6"/>
+    </row>
+    <row r="1150" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1150" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1150" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1150" s="7" t="s">
+        <v>4099</v>
+      </c>
+      <c r="D1150" s="7" t="s">
+        <v>4122</v>
+      </c>
+      <c r="E1150" s="20">
+        <v>3.66</v>
+      </c>
+      <c r="F1150" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1150" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1150" s="9" t="s">
+        <v>4104</v>
+      </c>
+      <c r="I1150" s="6"/>
+    </row>
+    <row r="1151" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1151" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1151" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1151" s="7" t="s">
+        <v>4100</v>
+      </c>
+      <c r="D1151" s="7" t="s">
+        <v>4123</v>
+      </c>
+      <c r="E1151" s="20">
+        <v>3.84</v>
+      </c>
+      <c r="F1151" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1151" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1151" s="9" t="s">
+        <v>4112</v>
+      </c>
+      <c r="I1151" s="6"/>
+    </row>
+    <row r="1152" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1152" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1152" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1152" s="7" t="s">
+        <v>4101</v>
+      </c>
+      <c r="D1152" s="7" t="s">
+        <v>4124</v>
+      </c>
+      <c r="E1152" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F1152" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1152" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1152" s="9" t="s">
+        <v>4113</v>
+      </c>
+      <c r="I1152" s="6"/>
+    </row>
+    <row r="1153" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1153" s="6">
+        <v>37005303</v>
+      </c>
+      <c r="B1153" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1153" s="7" t="s">
+        <v>4102</v>
+      </c>
+      <c r="D1153" s="7" t="s">
+        <v>4125</v>
+      </c>
+      <c r="E1153" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1153" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1153" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1153" s="9" t="s">
+        <v>4114</v>
+      </c>
+      <c r="I1153" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C3287C-D1C8-49AC-97C5-07D5BE6F753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3C9204-3D24-4189-8889-1554DC647E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="4126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4501" uniqueCount="4164">
   <si>
     <t>No</t>
   </si>
@@ -13655,12 +13655,126 @@
   <si>
     <t>Soul-Jazz, Instrumental Soul [Sentimental Organ Ballad, Memorial Piece, Soul-Jazz Closer]</t>
   </si>
+  <si>
+    <t>3D Country</t>
+  </si>
+  <si>
+    <t>Cowboy Nudes</t>
+  </si>
+  <si>
+    <t>I See Myself</t>
+  </si>
+  <si>
+    <t>Undoer</t>
+  </si>
+  <si>
+    <t>Crusades</t>
+  </si>
+  <si>
+    <t>Gravity Blues</t>
+  </si>
+  <si>
+    <t>Mysterious Love</t>
+  </si>
+  <si>
+    <t>Domoto</t>
+  </si>
+  <si>
+    <t>Tomorrow’s Crusades</t>
+  </si>
+  <si>
+    <t>St. Elmo</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Art Punk, Alternative Country, Blues Rock, Post-Punk, Experimental Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Post-Punk [Nervy Art Rock, Jagged Guitar Rock, Alternative Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Alternative Country [Art Punk, Country-Rock Deconstruction, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Art Punk, Blues Rock [Raw Garage Rock, Country-Punk, Distorted Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Angular Rock, Theatrical Indie, Melodic Post-Punk]</t>
+  </si>
+  <si>
+    <t>Art Rock, Post-Punk [Slow-Burn Experimental Rock, Noise Rock, Bluesy Art Rock]</t>
+  </si>
+  <si>
+    <t>Art Punk, Indie Rock [Short-form Post-Punk, Jagged Rock, Nervous Art Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Indie Rock [Psychedelic Blues Rock, Art Rock, Heavy Slow-Burn]</t>
+  </si>
+  <si>
+    <t>Art Rock, Indie Rock [Theatrical Ballad, Experimental Rock, Crooning Art Rock]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Indie Rock [Angular Art Punk, Rhythmic Indie Rock, Nervous Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Alternative Country [Epic Indie Rock, Country-Rock Surrealism, Post-Punk]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Art Rock [Melodic Experimental Rock, Reflective Indie Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Geese</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/27342894-Geese-3D-Country</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/qy2cFhlh-I_iC-opExAfDi9mm9KgQBVO34WtrHTynLY/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3MzQy/ODk0LTE2ODc4MDI1/NjktMjAxNC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Partisan Records – PTPS10LP, Play It Again Sam – PTPS10LP (USA &amp; Europe, 2023, LP, Album, Stereo). Έκδοση με συνοδευτικό obi strip και hype sticker. Η κοπή του lacquer (Mastering) έγινε από τον Matt Colton στα Metropolis Studios (= MATT @ METROPOLIS), ενώ η φυσική κατασκευή (pressing) έγινε στη Optimal Media GmbH (με κωδικό BM82688, όπου τα 1= και 1Τ στα runouts δηλώνουν τα mirrored geometric stamps της εταιρείας)</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 3D Country κυκλοφόρησε τον Ιούνιο του 2023 από την Partisan Records και αποτελεί το δεύτερο στούντιο άλμπουμ του Brooklyn indie rock συγκροτήματος Geese, σε παραγωγή των Geese και του James Ford. Η μουσική τους ταυτότητα σε αυτόν τον δίσκο συνδυάζει στοιχεία από post-punk, experimental rock, southern rock και americana/folk rock, με έντονες δυναμικές εναλλαγές, εκρηκτικά κιθαριστικά ξεσπάσματα και τα ιδιαίτερα, theatric φωνητικά του Cameron Winter. Ο ήχος χαρακτηρίζεται από εξαιρετικό εύρος και διαύγεια χάρη στο mastering του Metropolis.</t>
+  </si>
+  <si>
+    <t>Σύντομο, κοφτό και επιθετικό, με τίτλο που φέρνει εικόνες ιδεολογικής βίας, ιερού πολέμου και εμμονικής σύγκρουσης. Οι Geese δεν χτίζουν εδώ μεγάλη ιστορική αφήγηση· χρησιμοποιούν το “crusades” σαν λέξη-σκανδάλη για νευρική post-punk ένταση. Το riffing είναι κοφτό, τα drums σπρώχνουν και η φωνή έχει μια ειρωνική, σχεδόν αποστασιοποιημένη ένταση. Λειτουργεί περισσότερο ως έκρηξη μέσα στη sequence παρά ως αυτόνομο peak, αλλά είναι χρήσιμο επειδή σπάει το πιο εκτεταμένο mood του “Undoer” και οδηγεί στη βαριά B πλευρά.</t>
+  </si>
+  <si>
+    <t>Από τις πιο θεατρικές και πιο παράξενες συνθέσεις του album. Ο τίτλος θα μπορούσε να υποσχεθεί μια παραδοσιακή ερωτική μπαλάντα, όμως οι Geese παρουσιάζουν την αγάπη ως κάτι ακατάληπτο, απειλητικό και διαρκώς μεταβαλλόμενο. Η φωνή του Winter είναι πιο crooning, σχεδόν lounge-like σε σημεία, αλλά η μπάντα δεν αφήνει ποτέ τη σύνθεση να γίνει καθαρή ballad. Οι αρμονίες και η κιθαριστική ένταση δημιουργούν ένα αίσθημα αλλόκοτης οικειότητας. Είναι ένα από τα πιο εντυπωσιακά tracks του δίσκου, επειδή ενώνει μελωδική προσβασιμότητα και experimental αστάθεια χωρίς να χάνει τον χαρακτήρα του.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με νευρική, κοφτή και ακανόνιστη rock ενέργεια. Το “2122” δεν χτίζει έναν παραδοσιακό κόσμο country ή Americana· από την πρώτη στιγμή εισάγει μια παραμορφωμένη εκδοχή του, όπου οι κιθάρες είναι jagged, το rhythm section ασταθές με ελεγχόμενο τρόπο και η φωνή του Cameron Winter κινείται ανάμεσα σε ειρωνεία, ένταση και σχεδόν θεατρική απειλή. Ο αριθμητικός τίτλος δημιουργεί μια αίσθηση δυστοπικού μέλλοντος ή κωδικοποιημένου τόπου, κάτι που ταιριάζει με το album, «country» όχι ως γεωγραφία, αλλά ως παραμορφωμένη φαντασίωση. Είναι αποτελεσματικό opener επειδή σε βάζει αμέσως σε έναν κόσμο όπου τα τραγούδια δεν θα συμπεριφέρονται προβλέψιμα.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η κεντρική δήλωση του δίσκου και ένα από τα πιο ιδιόρρυθμα contemporary rock τραγούδια της περιόδου. Ο τίτλος προσθέτει μια τρίτη διάσταση στο “country”, όχι country μουσική με τη συμβατική έννοια, αλλά έναν αλλόκοτο, υπερπραγματικό χώρο γεμάτο βία, χιούμορ, φαντασιακές εικόνες και παραμορφωμένο rock ’n’ roll. Η σύνθεση μετακινείται από country/blues gesture σε art-punk εκρήξεις, με τον Winter να τραγουδά σαν κάποιος που ταυτόχρονα διηγείται ιστορία, σατιρίζει τον εαυτό του και προσπαθεί να δραπετεύσει από τον ρόλο του. Η Paste το αντιμετωπίζει ως μέρος μιας «brilliant, miraculous assemblage» rock ’n’ roll, ενώ πολλές fan αξιολογήσεις το τοποθετούν ανάμεσα στα highlights του δίσκου. </t>
+  </si>
+  <si>
+    <t>Σύντομο, ωμό και γεμάτο αλλόκοτη εικόνα. Ο τίτλος συνδυάζει δύο στοιχεία που φαίνονται να ανήκουν σε διαφορετικούς κόσμους , τον καουμπόη ως αμερικανικό μύθο και τη γυμνότητα ως έκθεση ή γελοιοποίηση , και η μουσική ακολουθεί με distorted garage-rock ένταση. Οι Geese δεν ενδιαφέρονται να αναπαραστήσουν ρεαλιστικά την Americana· τη διαλύουν, τη μετατρέπουν σε absurdist punk εικόνα και την τρέχουν μέσα από riff που έχει περισσότερο νεύρο παρά polish. Είναι μικρό σε διάρκεια, αλλά πολύ σημαντικό για την ταυτότητα του album, συνδέει το country imagery με art-punk αστάθεια.</t>
+  </si>
+  <si>
+    <t>Πιο μελωδικό στην επιφάνεια, αλλά γεμάτο εσωτερική αμφιβολία. Ο τίτλος υποδηλώνει αυτοπαρατήρηση , βλέπω τον εαυτό μου , όμως στους Geese η αυτογνωσία δεν προσφέρει καθαρότητα, γίνεται άλλη μια παράξενη, θεατρική σκηνή. Οι κιθάρες έχουν angular post-punk κίνηση και η φωνή του Winter μεταβάλλεται ανάμεσα σε σχεδόν crooning γραμμές και εκρήξεις. Το τραγούδι λειτουργεί ως μικρή ανάσα μετά την ωμή ένταση του “Cowboy Nudes”, αλλά δεν γίνεται ποτέ συμβατικό indie-rock κομμάτι. Κρατά τη μελωδία σε μόνιμη ένταση, σαν κάτι που μπορεί ανά πάσα στιγμή να διαλυθεί.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο εκτεταμένα και πιο ατμοσφαιρικά tracks του album. Η έννοια του “undoer” , εκείνος που αναιρεί, ξετυλίγει ή καταστρέφει ό,τι έχει δημιουργηθεί , ταιριάζει στη slow-burn δομή του τραγουδιού. Η μπάντα δεν επιδιώκει γρήγορη λύση, αφήνει θορύβους, riffs, φωνητικές παραμορφώσεις και ρυθμικές αλλαγές να χτίσουν ένα βαρύ, almost psychedelic art-rock τοπίο. Ο Winter ακούγεται σαν να παλεύει με τη γλώσσα του τραγουδιού αντί να την ελέγχει απόλυτα, και αυτή η αβεβαιότητα γίνεται η δύναμή του. Δεν είναι το πιο άμεσο track, αλλά η έκτασή του δίνει στο album βάθος και αποδεικνύει ότι οι Geese μπορούν να λειτουργήσουν και πέρα από τα σύντομα, πανκ κομμάτια.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με blues που δεν είναι παραδοσιακό blues, είναι βαρύ, ψυχεδελικό, παραμορφωμένο και γεμάτο αίσθηση βαρύτητας. Η “gravity” του τίτλου είναι φυσική δύναμη, αλλά και μεταφορά για κατάθλιψη, αδράνεια ή τη συναισθηματική δύναμη που σε τραβά προς τα κάτω. Οι κιθάρες κινούνται αργά, με περισσότερο βάρος και space, ενώ το rhythm section επιτρέπει στο τραγούδι να γίνει σχεδόν υπνωτικό. Είναι από τα πιο πειστικά σημεία όπου οι blues-rock επιρροές του album ακούγονται οργανικές και όχι απλώς αισθητικό δάνειο.</t>
+  </si>
+  <si>
+    <t>Γρήγορο και angular, με έμφαση στο rhythm και στην ανταλλαγή μικρών, αιχμηρών μουσικών φράσεων. Ο αινιγματικός τίτλος δεν χρειάζεται να αποκτήσει συγκεκριμένη ερμηνεία για να λειτουργήσει το τραγούδι, η μουσική μοιάζει με χαρακτήρα που κινείται νευρικά, κάνει ξαφνικές στροφές και αρνείται να σταθεροποιηθεί. Είναι ένα post-punk/art-punk cut που επαναφέρει την ένταση μετά το πιο ανοιχτό “Mysterious Love”. Δεν έχει το μεγάλο δραματικό βάρος των κύριων highlights, αλλά ενισχύει τη συνολική αίσθηση ότι το album είναι διαρκώς απρόβλεπτο.</t>
+  </si>
+  <si>
+    <t>Το album επιστρέφει στην ιδέα των “Crusades”, αλλά το “tomorrow’s” μεταφέρει τη σύγκρουση σε ένα αβέβαιο μέλλον. Η σύνθεση είναι πιο εκτεταμένη και πιο cinematic από το σύντομο A-side track, country-rock σκιές, distorted κιθάρες και ερμηνεία που μοιάζει να περνά από σαρκασμό σε πραγματική ανησυχία. Το τραγούδι δεν δίνει καθαρή λύση ούτε καθαρό πολιτικό μήνυμα· αφήνει την αίσθηση ότι οι ίδιες εμμονές και βίαιοι κύκλοι απλώς μεταφέρονται στην επόμενη ημέρα. Είναι από τα πιο φιλόδοξα tracks της δεύτερης πλευράς και λειτουργεί ως προτελευταία δραματική κορύφωση.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο είναι πιο μελωδικό και στοχαστικό, αλλά όχι πραγματικά ήσυχο. Η αναφορά στον St. Elmo μπορεί να παραπέμπει στο St. Elmo’s fire , ηλεκτρικό, μυστηριώδες φαινόμενο που εμφανίζεται γύρω από αντικείμενα σε φορτισμένη ατμόσφαιρα , και ταιριάζει με το album ως κάτι που λάμπει στιγμιαία μέσα σε αβεβαιότητα. Η μπάντα κρατά τη rock ένταση, όμως η φωνή και η μελωδία προσφέρουν μια πιο ανθρώπινη, λιγότερο σατιρική έξοδο. Δεν είναι το πιο άμεσο τραγούδι του δίσκου, αλλά ως finale επιτρέπει στο 3D Country να τελειώσει χωρίς εύκολη θριαμβευτική λύση, με μια αίσθηση παράξενης, ηλεκτρισμένης επιβίωσης.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13779,6 +13893,13 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -13843,7 +13964,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -13928,6 +14049,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14239,7 +14363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -16239,7 +16363,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>14186441</v>
       </c>
@@ -16877,7 +17001,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>29667079</v>
       </c>
@@ -16909,7 +17033,7 @@
         <v>2759</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>28729798</v>
       </c>
@@ -17069,7 +17193,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>2598614</v>
       </c>
@@ -17133,7 +17257,7 @@
         <v>2995</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>34750368</v>
       </c>
@@ -17165,7 +17289,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>34571488</v>
       </c>
@@ -17325,7 +17449,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>12520978</v>
       </c>
@@ -17357,7 +17481,7 @@
         <v>3258</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>2782114</v>
       </c>
@@ -17421,7 +17545,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>1382323</v>
       </c>
@@ -17453,7 +17577,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>646934</v>
       </c>
@@ -17485,7 +17609,7 @@
         <v>3398</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>4116216</v>
       </c>
@@ -17549,7 +17673,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>2661964</v>
       </c>
@@ -17581,7 +17705,7 @@
         <v>3504</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="42" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>4428247</v>
       </c>
@@ -17613,7 +17737,7 @@
         <v>3533</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="42" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>2903507</v>
       </c>
@@ -17677,7 +17801,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>8864393</v>
       </c>
@@ -18123,6 +18247,38 @@
       </c>
       <c r="J121" s="11" t="s">
         <v>4089</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="101.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>4148</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>4126</v>
+      </c>
+      <c r="D122" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E122" s="10">
+        <v>3.85</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>4136</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>4152</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>4151</v>
+      </c>
+      <c r="I122" s="11" t="s">
+        <v>4149</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>4150</v>
       </c>
     </row>
   </sheetData>
@@ -18364,6 +18520,8 @@
     <hyperlink ref="J120" r:id="rId235" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
     <hyperlink ref="J121" r:id="rId236" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
     <hyperlink ref="I121" r:id="rId237" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
+    <hyperlink ref="I122" r:id="rId238" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
+    <hyperlink ref="J122" r:id="rId239" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18371,7 +18529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1153"/>
+  <dimension ref="A1:I1164"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -49709,6 +49867,303 @@
       </c>
       <c r="I1153" s="6"/>
     </row>
+    <row r="1154" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1154" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1154" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1154" s="7">
+        <v>2122</v>
+      </c>
+      <c r="D1154" s="7" t="s">
+        <v>4137</v>
+      </c>
+      <c r="E1154" s="20">
+        <v>4.38</v>
+      </c>
+      <c r="F1154" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1154" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1154" s="29" t="s">
+        <v>4155</v>
+      </c>
+      <c r="I1154" s="6"/>
+    </row>
+    <row r="1155" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1155" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1155" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1155" s="7" t="s">
+        <v>4126</v>
+      </c>
+      <c r="D1155" s="7" t="s">
+        <v>4138</v>
+      </c>
+      <c r="E1155" s="20">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="F1155" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1155" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H1155" s="29" t="s">
+        <v>4156</v>
+      </c>
+      <c r="I1155" s="6"/>
+    </row>
+    <row r="1156" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1156" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1156" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1156" s="7" t="s">
+        <v>4127</v>
+      </c>
+      <c r="D1156" s="7" t="s">
+        <v>4139</v>
+      </c>
+      <c r="E1156" s="20">
+        <v>4.34</v>
+      </c>
+      <c r="F1156" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1156" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1156" s="29" t="s">
+        <v>4157</v>
+      </c>
+      <c r="I1156" s="6"/>
+    </row>
+    <row r="1157" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1157" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1157" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1157" s="7" t="s">
+        <v>4128</v>
+      </c>
+      <c r="D1157" s="7" t="s">
+        <v>4140</v>
+      </c>
+      <c r="E1157" s="20">
+        <v>4.25</v>
+      </c>
+      <c r="F1157" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1157" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1157" s="29" t="s">
+        <v>4158</v>
+      </c>
+      <c r="I1157" s="6"/>
+    </row>
+    <row r="1158" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1158" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1158" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1158" s="7" t="s">
+        <v>4129</v>
+      </c>
+      <c r="D1158" s="7" t="s">
+        <v>4141</v>
+      </c>
+      <c r="E1158" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F1158" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1158" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1158" s="29" t="s">
+        <v>4159</v>
+      </c>
+      <c r="I1158" s="6"/>
+    </row>
+    <row r="1159" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1159" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1159" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1159" s="7" t="s">
+        <v>4130</v>
+      </c>
+      <c r="D1159" s="7" t="s">
+        <v>4142</v>
+      </c>
+      <c r="E1159" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F1159" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1159" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1159" s="29" t="s">
+        <v>4153</v>
+      </c>
+      <c r="I1159" s="6"/>
+    </row>
+    <row r="1160" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1160" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1160" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1160" s="7" t="s">
+        <v>4131</v>
+      </c>
+      <c r="D1160" s="7" t="s">
+        <v>4143</v>
+      </c>
+      <c r="E1160" s="20">
+        <v>4.07</v>
+      </c>
+      <c r="F1160" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1160" s="12">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1160" s="29" t="s">
+        <v>4160</v>
+      </c>
+      <c r="I1160" s="6"/>
+    </row>
+    <row r="1161" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1161" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1161" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1161" s="7" t="s">
+        <v>4132</v>
+      </c>
+      <c r="D1161" s="7" t="s">
+        <v>4144</v>
+      </c>
+      <c r="E1161" s="20">
+        <v>4.24</v>
+      </c>
+      <c r="F1161" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1161" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1161" s="29" t="s">
+        <v>4154</v>
+      </c>
+      <c r="I1161" s="6"/>
+    </row>
+    <row r="1162" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1162" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1162" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1162" s="7" t="s">
+        <v>4133</v>
+      </c>
+      <c r="D1162" s="7" t="s">
+        <v>4145</v>
+      </c>
+      <c r="E1162" s="20">
+        <v>4.04</v>
+      </c>
+      <c r="F1162" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1162" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1162" s="29" t="s">
+        <v>4161</v>
+      </c>
+      <c r="I1162" s="6"/>
+    </row>
+    <row r="1163" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1163" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1163" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1163" s="7" t="s">
+        <v>4134</v>
+      </c>
+      <c r="D1163" s="7" t="s">
+        <v>4146</v>
+      </c>
+      <c r="E1163" s="20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F1163" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1163" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1163" s="29" t="s">
+        <v>4162</v>
+      </c>
+      <c r="I1163" s="6"/>
+    </row>
+    <row r="1164" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1164" s="6">
+        <v>27342894</v>
+      </c>
+      <c r="B1164" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1164" s="7" t="s">
+        <v>4135</v>
+      </c>
+      <c r="D1164" s="7" t="s">
+        <v>4147</v>
+      </c>
+      <c r="E1164" s="20">
+        <v>3.87</v>
+      </c>
+      <c r="F1164" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1164" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H1164" s="29" t="s">
+        <v>4163</v>
+      </c>
+      <c r="I1164" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3C9204-3D24-4189-8889-1554DC647E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F12E01-E7F0-4B01-8A33-871BDE044089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4501" uniqueCount="4164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4541" uniqueCount="4202">
   <si>
     <t>No</t>
   </si>
@@ -13769,12 +13769,126 @@
   <si>
     <t>Το κλείσιμο είναι πιο μελωδικό και στοχαστικό, αλλά όχι πραγματικά ήσυχο. Η αναφορά στον St. Elmo μπορεί να παραπέμπει στο St. Elmo’s fire , ηλεκτρικό, μυστηριώδες φαινόμενο που εμφανίζεται γύρω από αντικείμενα σε φορτισμένη ατμόσφαιρα , και ταιριάζει με το album ως κάτι που λάμπει στιγμιαία μέσα σε αβεβαιότητα. Η μπάντα κρατά τη rock ένταση, όμως η φωνή και η μελωδία προσφέρουν μια πιο ανθρώπινη, λιγότερο σατιρική έξοδο. Δεν είναι το πιο άμεσο τραγούδι του δίσκου, αλλά ως finale επιτρέπει στο 3D Country να τελειώσει χωρίς εύκολη θριαμβευτική λύση, με μια αίσθηση παράξενης, ηλεκτρισμένης επιβίωσης.</t>
   </si>
+  <si>
+    <t>Partisan Records – PTPS60LPX2, Partisan Records – PTPS60LP, Play It Again Sam – PTPS60LP. Αμερικανική και ευρωπαϊκή έκδοση (USA &amp; Europe) σε περιορισμένη έκδοση μπλε ημιδιαφανούς βινυλίου (Blue Translucent). Το άλμπουμ κυκλοφόρησε στις 26 Σεπτεμβρίου 2025. Το mastering έγινε από τον Felix Davis, ενώ τα Matrix/Runouts (301493E1 και 301493E2) υποδεικνύουν την κατασκευή/plating της μήτρας.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Getting Killed κυκλοφόρησε τον Σεπτέμβριο του 2025 από την Partisan Records και αποτελεί τη συνέχεια της επιτυχημένης πορείας του brooklynιτικού indie rock συγκροτήματος Geese. Την παραγωγή υπογράφουν οι Geese μαζί με τον Kenneth Blume, ενώ το mastering έγινε από τον Felix Davis. Ο ήχος χαρακτηρίζεται από έντονες πειραματικές ροκ δομές, post-punk ενέργεια, πολυεπίπεδα κιθαριστικά μέρη και τα χαρακτηριστικά θεατρικά φωνητικά του Cameron Winter.</t>
+  </si>
+  <si>
+    <t>Getting Killed</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35210866-Geese-Getting-Killed</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Tccfv5z3hikp_-HUos1gDS2KSpGYJfN-ZAedfWUux9U/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1MjEw/ODY2LTE3NjIzNTgy/NTItNDA2MS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Trinidad</t>
+  </si>
+  <si>
+    <t>Cobra</t>
+  </si>
+  <si>
+    <t>Husbands</t>
+  </si>
+  <si>
+    <t>Islands Of Men</t>
+  </si>
+  <si>
+    <t>100 Horses</t>
+  </si>
+  <si>
+    <t>Half Real</t>
+  </si>
+  <si>
+    <t>Au Pays Du Cocaine</t>
+  </si>
+  <si>
+    <t>Bow Down</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Long Island City Here I Come</t>
+  </si>
+  <si>
+    <t>Art Rock, Experimental Rock [Art Punk, Post-Punk, No Wave, Indie Rock, Jazz-Funk elements, Alternative Country]</t>
+  </si>
+  <si>
+    <t>Art Punk, Post-Punk [No Wave, Jagged Art Rock, Chaotic Indie Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Post-Punk [Nervy Art Punk, Funk-Rock pulse, Angular Indie Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Indie Rock [Theatrical Rock, Crooning Art Rock, Emotional Post-Punk]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Art Punk [No Wave, Fractured Rock, Theatrical Noise Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Experimental Rock [Long-form Art Rock, Jazz-Rock tension, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Indie Rock, Alternative Country [Country-tinged Art Rock, Melodic Experimental Rock]</t>
+  </si>
+  <si>
+    <t>Art Punk, Post-Punk [Nervy Art Rock, Fragmented Indie Rock, No Wave edge]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Art Rock [Surreal Art Rock, Latin-tinged Groove, Avant-Indie]</t>
+  </si>
+  <si>
+    <t>Art Punk, Experimental Rock [Aggressive No Wave, Rhythmic Noise Rock, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Art Rock [Tense Art Punk, No-Wave Rock, Funk-leaning Indie Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Experimental Rock [Epic Art Rock, Free-form Indie Rock, Cinematic Album Closer]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πιο σύντομο και πιο ερπετικό, το “Cobra” λειτουργεί με άξονα την ένταση που συσσωρεύεται πριν από την επίθεση. Η κόμπρα του τίτλου δεν είναι αναγκαστικά κυριολεκτικό ζώο· γίνεται εικόνα κινδύνου, υπνωτισμού και απρόβλεπτης κίνησης. Το groove έχει funk-rock νεύρο, αλλά οι Geese το διακόπτουν με angular κιθαριστικές παρεμβάσεις και φωνητικά που δεν επιτρέπουν ποτέ στο τραγούδι να σταθεροποιηθεί ως συμβατικό rock single. Είναι πιο compact από το “Trinidad”, αλλά όχι λιγότερο έντονο. Μετατρέπει το riff σε μηχανισμό απειλής και δείχνει την ικανότητα της μπάντας να φτιάχνει hooks μέσα από ασυμμετρία και θόρυβο. Το “Cobra” αναφέρεται συχνά μαζί με το “Taxes” ως βασικό highlight της κριτικής υποδοχής. </t>
+  </si>
+  <si>
+    <t>Από τις πιο επιθετικές στιγμές της B πλευράς. Η εντολή “bow down” μιλά για υποταγή, λατρεία, εξουσία ή ειρωνεία απέναντι στις κοινωνικές ιεραρχίες. Η μουσική δεν είναι τελετουργική με κλασική έννοια· είναι κοφτή, θορυβώδης και ρυθμικά φορτισμένη, με no-wave χαρακτήρα. Ο Winter χειρίζεται τη φωνή του σαν όπλο και σαν performance μαζί, περνώντας από σχεδόν ειρωνική εκφορά σε ένταση που μοιάζει πραγματική. Το τραγούδι λειτουργεί ως ξεκάθαρη υπενθύμιση ότι, παρά τα πιο ανοιχτά και μελωδικά σημεία, οι Geese παραμένουν μπάντα που ενδιαφέρεται για friction και όχι για ομαλή ροή.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το album ξεκινά με άμεση αποσταθεροποίηση. Το “Trinidad” δεν εισάγει τον ακροατή ομαλά· τον βάζει κατευθείαν σε νευρικό, κοφτό art-punk χώρο όπου το rhythm section και οι κιθάρες μοιάζουν να τραβούν προς διαφορετικές κατευθύνσεις. Ο τίτλος λειτουργεί ως εξωτικός ή γεωγραφικός υπαινιγμός, αλλά η μουσική δεν επιχειρεί να αναπαραστήσει έναν τόπο· χτίζει ένα ψυχολογικό τοπίο έντασης και αστάθειας. Η φωνή του Cameron Winter κινείται ανάμεσα σε παραληρηματική αφήγηση και κρυφή μελωδία. Είναι σωστό opener επειδή δηλώνει αμέσως ότι το Getting Killed δεν θα βασιστεί στην ασφαλή indie-rock φόρμα, ο ήχος του είναι κοφτερός, άβολος και απολύτως ζωντανός. Οι κριτικές αναφέρουν το track ανάμεσα στα no-wave-tinged art-rock highlights του δίσκου. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μία από τις πιο ανθρώπινες και συναισθηματικά ανοιχτές συνθέσεις του δίσκου. Ο τίτλος δεν εξηγείται μονοδιάστατα, οι “husbands” μπορεί να είναι ρόλοι, δεσμεύσεις, κοινωνικές προσδοκίες ή άνθρωποι που προσπαθούν να βρουν σταθερότητα μέσα σε έναν κόσμο που μοιάζει να διαλύεται. Ο Winter τραγουδά με ιδιαίτερα θεατρικό τρόπο, αλλά η θεατρικότητα εδώ δεν κρύβει συναίσθημα· το μεγεθύνει. Η μελωδία κινείται μέσα σε ακανόνιστη rock δομή και το refrain έχει την αίσθηση κάποιου που επαναλαμβάνει μια φράση για να πείσει τον εαυτό του. Το WERS το ξεχωρίζει ως ένα από τα καλύτερα tracks του album, και δικαίως, έχει την παράξενη μορφή των Geese, αλλά και πραγματικό emotional centre. </t>
+  </si>
+  <si>
+    <t>Το title track μετατρέπει την πιο σκληρή πιθανή φράση σε art-rock σκηνή άγχους, παρατήρησης και μαύρου χιούμορ. Δεν πρόκειται για κυριολεκτική αφήγηση βίας· η έννοια του “getting killed” λειτουργεί ως μεταφορά για την εξάντληση, την κοινωνική έκθεση, την αίσθηση ότι σε καταναλώνουν οι απαιτήσεις του κόσμου ή οι ίδιοι σου οι ρόλοι. Η παραγωγή του Kenny Beats δίνει στο τραγούδι κομμένες άκρες, απότομα dynamics και χώρο ώστε οι ενορχηστρωτικές κινήσεις να ακούγονται σαν νευρικές αντιδράσεις. Η μπάντα χρησιμοποιεί no-wave ένταση χωρίς να γίνεται χαοτική για το χάος. Είναι το κεντρικό αισθητικό statement του δίσκου, επιθετικό, παράξενο και ταυτόχρονα μελωδικά εύστοχο.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η μεγάλη A-side ανάπτυξη και ένα από τα πιο φιλόδοξα tracks του album. Τα «νησιά των ανθρώπων» είναι μια εικόνα απομόνωσης, άτομα που ζουν δίπλα-δίπλα αλλά παραμένουν χωριστά, αυτόνομοι κόσμοι χωρίς πραγματική επαφή. Η σύνθεση έχει μεγαλύτερη διάρκεια, πιο ανοιχτό χώρο και περισσότερη σταδιακή κλιμάκωση. Οι Geese αφήνουν τις κιθάρες, τα drums και τη φωνή να περάσουν από διαφορετικές διαθέσεις , art-rock αστάθεια, jazz-rock ένταση, σχεδόν ψυχεδελικό άνοιγμα , χωρίς να μοιάζει με απλή επίδειξη. Είναι τραγούδι που ανταμείβει την ακρόαση ως διαδρομή, όχι ως άμεσο hook, και το WERS το συγκαταλέγει στα κορυφαία του δίσκου. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πιο μελωδικό και πιο «ανοιχτό» στην εικόνα του, με τον τίτλο να φέρνει κίνηση, ορμή και μυθικό αριθμό. Τα εκατό άλογα μπορούν να διαβαστούν ως φαντασιακή ελευθερία, ως ανεξέλεγκτη δύναμη ή ως ονειρική φυγή. Η μουσική κρατά country/roots σκιές, αλλά τις περνά από το φίλτρο των Geese, παράξενη αρμονία, ρυθμική αστάθεια και φωνή που δεν επιλέγει ποτέ εύκολη λύση. Είναι από τα πιο προσβάσιμα τραγούδια του album χωρίς να θυσιάζει την αλλόκοτη προσωπικότητά του. Η θέση του στο τέλος της A πλευράς λειτουργεί ως μικρή έξοδος προς τον ανοιχτό χώρο, πριν η B πλευρά γίνει ξανά πιο νευρική και θραυσματική. </t>
+  </si>
+  <si>
+    <t>Η B πλευρά ξεκινά με την ιδέα μιας ταυτότητας που είναι μισή πραγματική και μισή κατασκευασμένη. Ο τίτλος ταιριάζει με τον τρόπο που οι Geese παίζουν, η σύνθεση μοιάζει διαρκώς να σταθεροποιείται και να διαλύεται, σαν να μην αποφασίζει ποτέ αν είναι rock τραγούδι, post-punk άσκηση ή θεατρική μονόλογος. Η μπάντα χρησιμοποιεί νευρικό rhythm section και ασύμμετρα guitar accents, ενώ ο Winter δίνει στην ερμηνεία μια αίσθηση ανθρώπου που προσπαθεί να συλλάβει τον εαυτό του μέσα από θραύσματα. Δεν είναι το πιο άμεσο song του δίσκου, αλλά έχει πολύ σωστή θέση, επαναφέρει την αβεβαιότητα μετά την πιο ανοιχτή ορμή του “100 Horses”.</t>
+  </si>
+  <si>
+    <t>Ο γαλλικός τίτλος , «στη χώρα της κοκαΐνης» , δημιουργεί αμέσως έναν φανταστικό χώρο υπερβολής, παρακμής και τεχνητής ευφορίας. Οι Geese αποφεύγουν την απλή εικόνα ενός drug song, η μουσική είναι περίεργη, ελαφρώς χορευτική σε σημεία, αλλά με διακοπές και παραμορφώσεις που εμποδίζουν την ευχαρίστηση να γίνει εύκολη. Το groove έχει ίχνη Latin/funk κίνησης, ενώ η φωνή του Winter κάνει τον τόπο του τίτλου να μοιάζει περισσότερο με ψυχική κατάσταση παρά με πραγματική χώρα. Είναι ένα από τα πιο surreal tracks του δίσκου και ενισχύει τον τρόπο με τον οποίο το album μετατρέπει τις pop εικόνες σε αλλόκοτες art-rock σκηνές.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μία από τις πιο καθαρές no-wave/art-punk κορυφές του album. Ο τίτλος είναι καθημερινός και πεζός, όμως ακριβώς αυτό τον κάνει αποτελεσματικό, οι φόροι γίνονται σύμβολο γραφειοκρατίας, εξουσίας, κοινωνικής ανταλλαγής και της αίσθησης ότι η ζωή μετατρέπεται σε λογαριασμό. Το groove είναι νευρικό και σχεδόν funk-leaning, αλλά οι κιθάρες και οι φωνητικές εκρήξεις το μετατρέπουν σε παράξενο, αιχμηρό rock κομμάτι. Το Metacritic το αναφέρει ειδικά ως ένα από τα “unnerving as they are affecting” tracks, και το WERS το περιλαμβάνει στα favourites του album. Δεν είναι παραδοσιακό single, αλλά είναι ένα από τα πιο συμπυκνωμένα δείγματα της νέας Geese αισθητικής. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το μεγάλο φινάλε, με διάρκεια πάνω από έξι λεπτά, λειτουργεί σαν επιστροφή σε τόπο αλλά και σαν ψυχική άφιξη. Το Long Island City είναι πραγματικός χώρος της Νέας Υόρκης, όμως στο τραγούδι γίνεται προορισμός μετά από μια διαδρομή που ήταν γεμάτη σύγχυση, ένταση και διαλυμένες εικόνες. Η σύνθεση επιτρέπει στη μπάντα να ανοίξει τον ήχο, μεγαλύτερη κλιμάκωση, πιο κινηματογραφικές αλλαγές και χώρος για τον Winter να περάσει από αφήγηση σε σχεδόν απελπισμένο croon. Δεν δίνει μια καθαρή, λυτρωτική κατάληξη. Αντίθετα, τελειώνει το album σαν μια πόλη που φαίνεται στον ορίζοντα αλλά ποτέ δεν γίνεται απόλυτα ασφαλές σπίτι. Η θέση του ως τελευταίο track και η διάρκεια 6,37 επιβεβαιώνονται από τις επίσημες tracklist πηγές. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13900,6 +14014,13 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -13964,7 +14085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -14051,6 +14172,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14363,7 +14487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -18279,6 +18403,38 @@
       </c>
       <c r="J122" s="11" t="s">
         <v>4150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>4148</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>4166</v>
+      </c>
+      <c r="D123" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E123" s="10">
+        <v>3.84</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>4179</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>4165</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>4164</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>4167</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>4168</v>
       </c>
     </row>
   </sheetData>
@@ -18522,6 +18678,8 @@
     <hyperlink ref="I121" r:id="rId237" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
     <hyperlink ref="I122" r:id="rId238" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
     <hyperlink ref="J122" r:id="rId239" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
+    <hyperlink ref="I123" r:id="rId240" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
+    <hyperlink ref="J123" r:id="rId241" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18529,7 +18687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1164"/>
+  <dimension ref="A1:I1175"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -50164,6 +50322,303 @@
       </c>
       <c r="I1164" s="6"/>
     </row>
+    <row r="1165" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1165" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1165" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1165" s="7" t="s">
+        <v>4169</v>
+      </c>
+      <c r="D1165" s="7" t="s">
+        <v>4180</v>
+      </c>
+      <c r="E1165" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F1165" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1165" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1165" s="30" t="s">
+        <v>4193</v>
+      </c>
+      <c r="I1165" s="6"/>
+    </row>
+    <row r="1166" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1166" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1166" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1166" s="7" t="s">
+        <v>4170</v>
+      </c>
+      <c r="D1166" s="7" t="s">
+        <v>4181</v>
+      </c>
+      <c r="E1166" s="20">
+        <v>4.26</v>
+      </c>
+      <c r="F1166" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1166" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1166" s="30" t="s">
+        <v>4191</v>
+      </c>
+      <c r="I1166" s="6"/>
+    </row>
+    <row r="1167" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1167" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1167" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1167" s="7" t="s">
+        <v>4171</v>
+      </c>
+      <c r="D1167" s="7" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E1167" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1167" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1167" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1167" s="30" t="s">
+        <v>4194</v>
+      </c>
+      <c r="I1167" s="6"/>
+    </row>
+    <row r="1168" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1168" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1168" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1168" s="7" t="s">
+        <v>4166</v>
+      </c>
+      <c r="D1168" s="7" t="s">
+        <v>4183</v>
+      </c>
+      <c r="E1168" s="20">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F1168" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1168" s="12">
+        <v>4.75</v>
+      </c>
+      <c r="H1168" s="30" t="s">
+        <v>4195</v>
+      </c>
+      <c r="I1168" s="6"/>
+    </row>
+    <row r="1169" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1169" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1169" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1169" s="7" t="s">
+        <v>4172</v>
+      </c>
+      <c r="D1169" s="7" t="s">
+        <v>4184</v>
+      </c>
+      <c r="E1169" s="20">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F1169" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1169" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="H1169" s="30" t="s">
+        <v>4196</v>
+      </c>
+      <c r="I1169" s="6"/>
+    </row>
+    <row r="1170" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1170" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1170" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1170" s="7" t="s">
+        <v>4173</v>
+      </c>
+      <c r="D1170" s="7" t="s">
+        <v>4185</v>
+      </c>
+      <c r="E1170" s="20">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F1170" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1170" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H1170" s="30" t="s">
+        <v>4197</v>
+      </c>
+      <c r="I1170" s="6"/>
+    </row>
+    <row r="1171" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1171" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1171" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1171" s="7" t="s">
+        <v>4174</v>
+      </c>
+      <c r="D1171" s="7" t="s">
+        <v>4186</v>
+      </c>
+      <c r="E1171" s="20">
+        <v>3.86</v>
+      </c>
+      <c r="F1171" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1171" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1171" s="30" t="s">
+        <v>4198</v>
+      </c>
+      <c r="I1171" s="6"/>
+    </row>
+    <row r="1172" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1172" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1172" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1172" s="7" t="s">
+        <v>4175</v>
+      </c>
+      <c r="D1172" s="7" t="s">
+        <v>4187</v>
+      </c>
+      <c r="E1172" s="20">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="F1172" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1172" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1172" s="30" t="s">
+        <v>4199</v>
+      </c>
+      <c r="I1172" s="6"/>
+    </row>
+    <row r="1173" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1173" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1173" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1173" s="7" t="s">
+        <v>4176</v>
+      </c>
+      <c r="D1173" s="7" t="s">
+        <v>4188</v>
+      </c>
+      <c r="E1173" s="20">
+        <v>4.24</v>
+      </c>
+      <c r="F1173" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1173" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1173" s="30" t="s">
+        <v>4192</v>
+      </c>
+      <c r="I1173" s="6"/>
+    </row>
+    <row r="1174" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1174" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1174" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1174" s="7" t="s">
+        <v>4177</v>
+      </c>
+      <c r="D1174" s="7" t="s">
+        <v>4189</v>
+      </c>
+      <c r="E1174" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F1174" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1174" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1174" s="30" t="s">
+        <v>4200</v>
+      </c>
+      <c r="I1174" s="6"/>
+    </row>
+    <row r="1175" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1175" s="6">
+        <v>35210866</v>
+      </c>
+      <c r="B1175" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1175" s="7" t="s">
+        <v>4178</v>
+      </c>
+      <c r="D1175" s="7" t="s">
+        <v>4190</v>
+      </c>
+      <c r="E1175" s="20">
+        <v>4.33</v>
+      </c>
+      <c r="F1175" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1175" s="12">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1175" s="30" t="s">
+        <v>4201</v>
+      </c>
+      <c r="I1175" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F12E01-E7F0-4B01-8A33-871BDE044089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F2961F-0E60-4CED-B8CD-2E5CDBF489DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4541" uniqueCount="4202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4593" uniqueCount="4254">
   <si>
     <t>No</t>
   </si>
@@ -13882,6 +13882,162 @@
   </si>
   <si>
     <t xml:space="preserve">Το μεγάλο φινάλε, με διάρκεια πάνω από έξι λεπτά, λειτουργεί σαν επιστροφή σε τόπο αλλά και σαν ψυχική άφιξη. Το Long Island City είναι πραγματικός χώρος της Νέας Υόρκης, όμως στο τραγούδι γίνεται προορισμός μετά από μια διαδρομή που ήταν γεμάτη σύγχυση, ένταση και διαλυμένες εικόνες. Η σύνθεση επιτρέπει στη μπάντα να ανοίξει τον ήχο, μεγαλύτερη κλιμάκωση, πιο κινηματογραφικές αλλαγές και χώρος για τον Winter να περάσει από αφήγηση σε σχεδόν απελπισμένο croon. Δεν δίνει μια καθαρή, λυτρωτική κατάληξη. Αντίθετα, τελειώνει το album σαν μια πόλη που φαίνεται στον ορίζοντα αλλά ποτέ δεν γίνεται απόλυτα ασφαλές σπίτι. Η θέση του ως τελευταίο track και η διάρκεια 6,37 επιβεβαιώνονται από τις επίσημες tracklist πηγές. </t>
+  </si>
+  <si>
+    <t>Kong (7) – KONG001LP (Worldwide, 2026, 2xLP, Album, Stereo). Κυκλοφόρησε στις 27 Φεβρουαρίου 2026 με συνοδευτικό obi strip (όπου αναγράφεται το barcode). Η κοπή του lacquer (Lacquer Cut) έγινε από τον Matt Colton στα Metropolis Mastering (=MATT@METROPOLIS=), ενώ η φυσική κατασκευή (pressing) έγινε στην Optimal Media GmbH (BP45543).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το पर्वत (The Mountain) αποτελεί το φιλόδοξο στούντιο άλμπουμ των Gorillaz που κυκλοφόρησε τον Φεβρουάριο του 2026 από την Kong Studios. Η παραγωγή υπογράφεται από τους Gorillaz, James Ford, Remi Kabaka Jr. και Samuel Eggleston, ενσωματώνοντας πλούσιες μουσικές επιρροές από την ινδική κλασική μουσική, την electronica, την hip hop και την world music. Το άλμπουμ διαθέτει εκτενείς συνεργασίες με καλλιτέχνες όπως οι Anoushka Shankar, Ajay Prasanna, Dennis Hopper, Sparks, Johnny Marr, IDLES, Yasiin Bey και πολλοί άλλοι.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/36520261-Gorillaz-%E0%A4%AA%E0%A4%B0%E0%A4%B5%E0%A4%A4-The-Mountain</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/7WrMOrloINPirZ8PwV21wqt-8-8--DKVjCh1Gp6Ml-8/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM2NTIw/MjYxLTE3ODMxMDMw/NDEtNzM5MC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Gorillaz</t>
+  </si>
+  <si>
+    <t>पर्वत (The Mountain)</t>
+  </si>
+  <si>
+    <t>The Mountain</t>
+  </si>
+  <si>
+    <t>The Moon Cave</t>
+  </si>
+  <si>
+    <t>The Happy Dictator</t>
+  </si>
+  <si>
+    <t>The Hardest Thing</t>
+  </si>
+  <si>
+    <t>Orange County</t>
+  </si>
+  <si>
+    <t>The God Of Lying</t>
+  </si>
+  <si>
+    <t>The Empty Dream Machine</t>
+  </si>
+  <si>
+    <t>The Manifesto</t>
+  </si>
+  <si>
+    <t>The Plastic Guru</t>
+  </si>
+  <si>
+    <t>Delirium</t>
+  </si>
+  <si>
+    <t>Damascus</t>
+  </si>
+  <si>
+    <t>The Shadowy Light</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>The Sweet Prince</t>
+  </si>
+  <si>
+    <t>The Sad God</t>
+  </si>
+  <si>
+    <t>Alternative Pop, World Music [Art Pop, Electronic Pop, Psychedelic Pop, Indian Classical Fusion, Trip-Hop, Global Pop]</t>
+  </si>
+  <si>
+    <t>Art Pop, World Music [Psychedelic Pop, Indian Classical Fusion, Spiritual Art Rock]</t>
+  </si>
+  <si>
+    <t>Art Pop, Hip-Hop [Psychedelic Soul, Alternative Hip-Hop, Global Art Pop]</t>
+  </si>
+  <si>
+    <t>Synth-Pop, Art Pop [Satirical Electro-Pop, New Wave, Theatrical Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Pop, Afrobeat [Afrobeat-tinged Art Pop, Posthumous Tony Allen groove, Reflective Pop]</t>
+  </si>
+  <si>
+    <t>Art Pop, World Music [Latin-tinged Pop, Indian Classical Fusion, Global Electronic Pop]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Art Rock [Dark Alternative Rock, Post-Punk, IDLES-influenced Art Rock]</t>
+  </si>
+  <si>
+    <t>Alternative Hip-Hop, Art Pop [Psychedelic Hip-Hop, Guitar Art Pop, Dreamlike Electronica]</t>
+  </si>
+  <si>
+    <t>Hip-Hop, World Music [Latin Rap, Alternative Hip-Hop, Global Beat Music]</t>
+  </si>
+  <si>
+    <t>Art Pop, Psychedelic Pop [Indian-Classical Psych Pop, Guitar Art Rock, Spiritual Pop]</t>
+  </si>
+  <si>
+    <t>Post-Punk, Experimental Rock [Spoken-Word Post-Punk, Mark E. Smith-style Art Rock, Sonic Collage]</t>
+  </si>
+  <si>
+    <t>World Music, Electronic Pop [Arabic Pop, Syrian Dabke influences, Alternative Hip-Hop, Global Electronica]</t>
+  </si>
+  <si>
+    <t>World Music, Art Pop [Indian Classical Fusion, Psychedelic Art Pop, Chamber World Music]</t>
+  </si>
+  <si>
+    <t>Art Rock, Post-Punk [Melodic Art Rock, Post-Punk Guitar Pop, Global Rock]</t>
+  </si>
+  <si>
+    <t>Art Pop, World Music [Indian Classical Pop, Psychedelic Ballad, Reflective Global Pop]</t>
+  </si>
+  <si>
+    <t>Alternative Hip-Hop, Art Pop [Spiritual Hip-Hop, Indian Classical Fusion, Epic Album Closer]</t>
+  </si>
+  <si>
+    <t>Η πιο άμεσα σατιρική στιγμή του album. Με τους Sparks, οι Gorillaz φτιάχνουν synth-pop/new-wave τραγούδι για μια φιγούρα εξουσίας που παρουσιάζεται ευτυχισμένη, γοητευτική ή διασκεδαστική, αλλά η χαρά της κρύβει έλεγχο και βία. Οι Sparks είναι ιδανικοί συνομιλητές επειδή η δική τους pop θεατρικότητα μπορεί να κάνει την πολιτική σάτιρα ταυτόχρονα ευχάριστη και ανησυχητική. Η σύνθεση έχει καθαρό hook και πιο pop άμεση δομή από το πρώτο δίπτυχο, όμως διατηρεί ειρωνικό τόνο. Είναι κομμάτι που θυμίζει τις καλύτερες Gorillaz στιγμές, όπου η ευκολία της μελωδίας λειτουργεί ως δούρειος ίππος για πιο σκοτεινό σχόλιο.</t>
+  </si>
+  <si>
+    <t>Πιο ήσυχο, πιο στοχαστικό και με σαφή αίσθηση μπαλάντας. Η «γλυκιά πρίγκιπας» φιγούρα μπορεί να είναι παιδί, νεκρός φίλος, χαμένη αθωότητα ή σύμβολο ενός κόσμου που χρειάζεται προστασία. Η παρουσία του Ajay Prasanna, του Johnny Marr και της Anoushka Shankar διατηρεί τη σύνθεση ανάμεσα σε Indian-classical χρώμα, κιθαριστική μελαγχολία και Gorillaz pop ευαισθησία. Δεν κυνηγά μεγάλη κορύφωση· η δύναμή του βρίσκεται στην οικονομία και στην αίσθηση αποχαιρετισμού που προετοιμάζει το τελικό track.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο guitar-led art rock, με Paul Simonon και Johnny Marr να προσθέτουν post-punk ιστορικό βάρος. Η Καζαμπλάνκα του τίτλου λειτουργεί ως λιμάνι, μυθικός τόπος συνάντησης και χώρος διασταύρωσης πολιτισμών. Μετά την έντονη C πλευρά, το τραγούδι δίνει μια πιο άμεση rock αίσθηση, χωρίς να εγκαταλείπει την παγκόσμια γεωγραφία του album. Οι κιθάρες προσφέρουν μελωδικό σκελετό και η σύνθεση θυμίζει ότι οι Gorillaz, ακόμη και όταν ταξιδεύουν σε πολλά είδη, παραμένουν στον πυρήνα τους art-pop/alternative-rock project.</t>
+  </si>
+  <si>
+    <t>Με μεταθανάτια παρουσία του Mark E. Smith, το “Delirium” είναι η πιο αποσπασματική και post-punk στιγμή του δίσκου. Η παραληρηματική κατάσταση του τίτλου μεταφράζεται σε broken structure, φωνητικό collage και αίσθηση ότι η σύνθεση μπορεί ανά πάσα στιγμή να καταρρεύσει. Ο Smith ενσαρκώνει την παράδοση της αντι-pop, αντι-καθαρότητας του post-punk, και η χρήση της φωνής του λειτουργεί σαν φάντασμα που διακόπτει την πιο εναρμονισμένη world-pop πλευρά του album. Δεν είναι εύκολο track, αλλά η δυσκολία του προσφέρει απαραίτητη αστάθεια πριν από το μεγάλο “Damascus”.</t>
+  </si>
+  <si>
+    <t>Η πιο άμεσα hip-hop/rap σύνθεση του πρώτου δίσκου. Με Trueno και Proof, το “manifesto” είναι δήλωση θέσης, όχι απλώς ακόμα ένα feature track. Η μουσική κρατά global beat λογική, ενώ οι φωνές δίνουν στην ιδέα του «μανιφέστου» χαρακτήρα συλλογικής διακήρυξης. Η παρουσία του Proof, μετά θάνατον, συνδέει ξανά τον δίσκο με τη μνήμη και την κληρονομιά καλλιτεχνών που δεν βρίσκονται πια εδώ. Δεν είναι το πιο μελωδικό κομμάτι του album, αλλά προσφέρει ρυθμική και θεματική αλλαγή πριν από τις πιο πνευματικές/ψυχεδελικές συνθέσεις της C πλευράς.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει το album σαν πνευματικό τοπίο. Το «βουνό» είναι ταυτόχρονα πραγματικός τόπος, εικόνα υπέρβασης και σύμβολο της απόστασης ανάμεσα στον άνθρωπο και σε ό,τι δεν μπορεί να ελέγξει , πένθος, θάνατος, μνήμη, πίστη. Η συμμετοχή του Dennis Hopper, του Ajay Prasanna και της Anoushka Shankar συνδέει spoken-word παράξενη αφήγηση, ινδική κλασική υφή και Gorillaz art-pop παραγωγή. Η σύνθεση δεν επιχειρεί να γίνει μεγάλο pop single· προτιμά να χτίσει ατμόσφαιρα και να δηλώσει ότι ο δίσκος θα λειτουργήσει σαν ταξίδι, όχι σαν απλή συλλογή συνεργασιών. Οι κριτικές επισημαίνουν ακριβώς αυτή την αίσθηση wonder που δημιουργεί το opening του album.</t>
+  </si>
+  <si>
+    <t>Με Bizarrap, Kara Jackson και Anoushka Shankar, το τραγούδι μεταφέρει το album σε πολυγλωσσικό, global-pop πεδίο. Το “Orange County” δεν λειτουργεί ως γεωγραφικό travelogue· είναι ένας τόπος όπου διαφορετικές μουσικές ταυτότητες συναντιούνται χωρίς να συγχωνεύονται πλήρως. Η παραγωγή κρατά electronic beat βάση, ενώ η sitar/ινδική κλασική παρουσία προσθέτει μελωδικό βάθος και η φωνή της Kara Jackson δίνει ποιητική ευαισθησία. Είναι ένα από τα tracks όπου η βασική ιδέα του album , παγκόσμια συνεργασία όχι ως διακοσμητικό στοιχείο αλλά ως δομή , γίνεται πιο καθαρή.</t>
+  </si>
+  <si>
+    <t>Πιο πυκνό και πιο γεμάτο φωνητικές προσωπικότητες, το “The Moon Cave” ενώνει Asha Puthli, Bobby Womack, Dave “Trugoy the Dove” Jolicoeur, Jalen Ngonda και Black Thought. Η «σπηλιά του φεγγαριού» είναι εικόνα εσωτερικής αναζήτησης και υπόγειας μνήμης, ένα μέρος όπου το φως υπάρχει, αλλά δεν είναι άμεσο. Η μουσική μετατρέπει αυτή την εικόνα σε ψυχεδελικό soul/hip-hop collage, με τις διαφορετικές φωνές να λειτουργούν σαν φαντάσματα, σχόλια και εναλλασσόμενες πλευρές μιας συλλογικής αφήγησης. Είναι ένα από τα πιο φιλόδοξα tracks της πρώτης πλευράς, επειδή η πολυφωνία του δεν μοιάζει τυχαία· υπηρετεί την ιδέα ότι ο δίσκος διασχίζει τόπους και εποχές.</t>
+  </si>
+  <si>
+    <t>Η παρουσία του Tony Allen δίνει στο track ιδιαίτερη ρυθμική βαρύτητα. Η «δυσκολότερη υπόθεση» του τίτλου δεν παρουσιάζεται ως απλή ερωτική δυσκολία, αλλά ως η ανάγκη να αποδεχτείς την απώλεια ή να συνεχίσεις όταν η ζωή επιμένει να αλλάζει. Το afrobeat-informed groove δημιουργεί κίνηση που δεν γίνεται ποτέ επιφανειακά χαρούμενη· έχει μια σταθερή, ώριμη μελαγχολία. Η επιλογή posthumous υλικού του Allen ενισχύει το βασικό θέμα του album, οι απουσίες δεν σβήνουν, συνεχίζουν να μιλούν μέσα από την τέχνη. Είναι διακριτικό track και όχι μεγάλο single, αλλά στη ροή της A πλευράς λειτουργεί ως συναισθηματικός σταθεροποιητής.</t>
+  </si>
+  <si>
+    <t>Με τους IDLES, το album αποκτά πιο βαρύ post-punk/alternative-rock σώμα. Ο τίτλος είναι μια σκοτεινή εικόνα, όχι απλώς κάποιος ψεύτης, αλλά μια σχεδόν θεϊκή αρχή παραπλάνησης. Η κιθάρα, η ένταση και η φωνητική αγριάδα των IDLES αντιπαραβάλλονται με τη συνήθως πιο αέρινη Gorillaz παραγωγή. Το αποτέλεσμα δεν είναι αμιγώς IDLES ούτε αμιγώς Gorillaz· είναι μια σύγκρουση δύο διαφορετικών energy levels. Δεν είναι το πιο αρμονικό track του δίσκου, αλλά αυτή η τριβή είναι ακριβώς η αξία του, σπάει την πιο πνευματική/παγκόσμια ατμόσφαιρα και εισάγει ωμή δυσπιστία.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο ψυχεδελικά και πιο ονειρικά tracks, με Black Thought, Johnny Marr και Anoushka Shankar. Η «άδεια μηχανή ονείρων» παραπέμπει σε έναν μηχανισμό που συνεχίζει να παράγει εικόνες, αλλά έχει χάσει την ανθρώπινη ουσία του , κατάλληλη μεταφορά για την εποχή της τεχνολογικής υπερφόρτωσης και της εξάντλησης. Ο Black Thought δίνει ρυθμική και λεκτική ακρίβεια, ο Johnny Marr προσθέτει μελωδικό guitar shimmer και η Anoushka Shankar δίνει την κλασική/πνευματική γραμμή. Το track λειτουργεί σαν αληθινό dream-machine, πολλά στοιχεία κινούνται ταυτόχρονα, όμως η ατμόσφαιρα μένει σταθερή και υπνωτική.</t>
+  </si>
+  <si>
+    <t>Ένα από τα πιο χαρακτηριστικά tracks της παγκόσμιας/ινδικής πλευράς του album. Ο “plastic guru” είναι μια προφανώς ειρωνική εικόνα, κάποιος που πουλά πνευματικότητα ως προϊόν, ένα ψεύτικο είδωλο που προσφέρει εύκολη λύτρωση. Η κιθάρα του Johnny Marr και η παρουσία της Anoushka Shankar προσφέρουν την αντίθεση ανάμεσα σε δυτικό art-rock και ινδική κλασική μελωδική παράδοση. Η μουσική δεν χλευάζει την πνευματικότητα· χλευάζει την εμπορευματοποίησή της. Αυτό κάνει το track κομβικό για τη θεματική του album, το οποίο χρησιμοποιεί το βουνό και το ταξίδι ως χώρο πραγματικής αναζήτησης, όχι τουριστικής ή εμπορικής εικόνας.</t>
+  </si>
+  <si>
+    <t>Από τα μεγαλύτερα highlights του δίσκου. Με Omar Souleyman και Yasiin Bey, οι Gorillaz συνδέουν Syrian dabke/Arabic-pop ενέργεια, ηλεκτρονική παραγωγή και alternative hip-hop φωνητική. Η Δαμασκός δεν εμφανίζεται ως εξωτικό σκηνικό· το τραγούδι κουβαλά τη βαρύτητα μιας αρχαίας πόλης που έχει πληγωθεί από πόλεμο, αλλά παραμένει πολιτισμικά ζωντανή. Η μουσική είναι χορευτική και σκοτεινή μαζί, τα rhythms σε καλούν να κινηθείς, όμως η ατμόσφαιρα έχει πένθος και ένταση. Αυτό το διπλό συναίσθημα , χαρά και απώλεια, επιβίωση και τραύμα , κάνει το “Damascus” μία από τις πιο ουσιαστικές global-pop συνθέσεις των Gorillaz.</t>
+  </si>
+  <si>
+    <t>Η κορυφή της πιο πνευματικής/κλασικής πλευράς του album. Με Asha Bhosle, Gruff Rhys, Ajay Prasanna, Amaan Ali Bangash και Ayaan Ali Bangash, το track γίνεται πραγματική συνάντηση φωνών, οργάνων και παραδόσεων. Το «σκιώδες φως» είναι αντίφαση που ταιριάζει στο album, η ελπίδα δεν είναι ποτέ πλήρως καθαρή, αλλά εμφανίζεται μέσα από πένθος, μνήμη και αβεβαιότητα. Η σύνθεση χρησιμοποιεί ινδικά κλασικά στοιχεία όχι ως sample decoration αλλά ως βασικό συναισθηματικό φορέα. Είναι η πιο πολυεπίπεδη στιγμή του δίσκου και εξηγεί καλύτερα γιατί η παγκόσμια προσέγγισή του έχει ουσία.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο συγκεντρώνει Black Thought, Ajay Prasanna και Anoushka Shankar σε ένα epic art-pop/hip-hop finale. Ο «λυπημένος θεός» είναι η πιο καθαρή θεματική εικόνα του album, θεότητα ή άνθρωπος που έχει δύναμη αλλά όχι λύση απέναντι στον θάνατο, στην απώλεια και στην ανθρώπινη βία. Η μουσική δεν προσφέρει εύκολη κάθαρση· χτίζει πνευματική ένταση, rap απαγγελία, κλασικά ινδικά μοτίβα και ατμοσφαιρική παραγωγή ώστε το τέλος να μοιάζει με παρατεταμένος διαλογισμός. Ως τελευταίο track, λειτουργεί σωστά, δεν λέει ότι το πένθος λύθηκε, αλλά ότι η αποδοχή του μπορεί να γίνει αφετηρία για συνεχιζόμενη ζωή.</t>
   </si>
 </sst>
 </file>
@@ -14487,7 +14643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -18405,7 +18561,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="84" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>35210866</v>
       </c>
@@ -18435,6 +18591,38 @@
       </c>
       <c r="J123" s="11" t="s">
         <v>4168</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>4206</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>4207</v>
+      </c>
+      <c r="D124" s="6">
+        <v>2026</v>
+      </c>
+      <c r="E124" s="10">
+        <v>3.48</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>4223</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>4203</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>4202</v>
+      </c>
+      <c r="I124" s="11" t="s">
+        <v>4204</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>4205</v>
       </c>
     </row>
   </sheetData>
@@ -18680,6 +18868,8 @@
     <hyperlink ref="J122" r:id="rId239" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
     <hyperlink ref="I123" r:id="rId240" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
     <hyperlink ref="J123" r:id="rId241" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
+    <hyperlink ref="I124" r:id="rId242" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
+    <hyperlink ref="J124" r:id="rId243" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18687,7 +18877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1175"/>
+  <dimension ref="A1:I1190"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -50619,6 +50809,411 @@
       </c>
       <c r="I1175" s="6"/>
     </row>
+    <row r="1176" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1176" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1176" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1176" s="7" t="s">
+        <v>4208</v>
+      </c>
+      <c r="D1176" s="7" t="s">
+        <v>4224</v>
+      </c>
+      <c r="E1176" s="20">
+        <v>3.82</v>
+      </c>
+      <c r="F1176" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1176" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1176" s="9" t="s">
+        <v>4244</v>
+      </c>
+      <c r="I1176" s="6"/>
+    </row>
+    <row r="1177" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1177" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1177" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1177" s="7" t="s">
+        <v>4209</v>
+      </c>
+      <c r="D1177" s="7" t="s">
+        <v>4225</v>
+      </c>
+      <c r="E1177" s="20">
+        <v>3.93</v>
+      </c>
+      <c r="F1177" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1177" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1177" s="9" t="s">
+        <v>4246</v>
+      </c>
+      <c r="I1177" s="6"/>
+    </row>
+    <row r="1178" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1178" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1178" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1178" s="7" t="s">
+        <v>4210</v>
+      </c>
+      <c r="D1178" s="7" t="s">
+        <v>4226</v>
+      </c>
+      <c r="E1178" s="20">
+        <v>4.03</v>
+      </c>
+      <c r="F1178" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1178" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1178" s="9" t="s">
+        <v>4239</v>
+      </c>
+      <c r="I1178" s="6"/>
+    </row>
+    <row r="1179" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1179" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1179" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1179" s="7" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1179" s="7" t="s">
+        <v>4227</v>
+      </c>
+      <c r="E1179" s="20">
+        <v>3.42</v>
+      </c>
+      <c r="F1179" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1179" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H1179" s="9" t="s">
+        <v>4247</v>
+      </c>
+      <c r="I1179" s="6"/>
+    </row>
+    <row r="1180" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1180" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1180" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1180" s="7" t="s">
+        <v>4212</v>
+      </c>
+      <c r="D1180" s="7" t="s">
+        <v>4228</v>
+      </c>
+      <c r="E1180" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F1180" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1180" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1180" s="9" t="s">
+        <v>4245</v>
+      </c>
+      <c r="I1180" s="6"/>
+    </row>
+    <row r="1181" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1181" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1181" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1181" s="7" t="s">
+        <v>4213</v>
+      </c>
+      <c r="D1181" s="7" t="s">
+        <v>4229</v>
+      </c>
+      <c r="E1181" s="20">
+        <v>3.41</v>
+      </c>
+      <c r="F1181" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1181" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1181" s="9" t="s">
+        <v>4248</v>
+      </c>
+      <c r="I1181" s="6"/>
+    </row>
+    <row r="1182" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1182" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1182" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1182" s="7" t="s">
+        <v>4214</v>
+      </c>
+      <c r="D1182" s="7" t="s">
+        <v>4230</v>
+      </c>
+      <c r="E1182" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F1182" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1182" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1182" s="9" t="s">
+        <v>4249</v>
+      </c>
+      <c r="I1182" s="6"/>
+    </row>
+    <row r="1183" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1183" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1183" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1183" s="7" t="s">
+        <v>4215</v>
+      </c>
+      <c r="D1183" s="7" t="s">
+        <v>4231</v>
+      </c>
+      <c r="E1183" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1183" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1183" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1183" s="9" t="s">
+        <v>4243</v>
+      </c>
+      <c r="I1183" s="6"/>
+    </row>
+    <row r="1184" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1184" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1184" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1184" s="7" t="s">
+        <v>4216</v>
+      </c>
+      <c r="D1184" s="7" t="s">
+        <v>4232</v>
+      </c>
+      <c r="E1184" s="20">
+        <v>3.56</v>
+      </c>
+      <c r="F1184" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1184" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1184" s="9" t="s">
+        <v>4250</v>
+      </c>
+      <c r="I1184" s="6"/>
+    </row>
+    <row r="1185" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1185" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1185" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1185" s="7" t="s">
+        <v>4217</v>
+      </c>
+      <c r="D1185" s="7" t="s">
+        <v>4233</v>
+      </c>
+      <c r="E1185" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F1185" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1185" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1185" s="9" t="s">
+        <v>4242</v>
+      </c>
+      <c r="I1185" s="6"/>
+    </row>
+    <row r="1186" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1186" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1186" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1186" s="7" t="s">
+        <v>4218</v>
+      </c>
+      <c r="D1186" s="7" t="s">
+        <v>4234</v>
+      </c>
+      <c r="E1186" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F1186" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1186" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1186" s="9" t="s">
+        <v>4251</v>
+      </c>
+      <c r="I1186" s="6"/>
+    </row>
+    <row r="1187" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1187" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1187" s="6">
+        <v>12</v>
+      </c>
+      <c r="C1187" s="7" t="s">
+        <v>4219</v>
+      </c>
+      <c r="D1187" s="7" t="s">
+        <v>4235</v>
+      </c>
+      <c r="E1187" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F1187" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1187" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1187" s="9" t="s">
+        <v>4252</v>
+      </c>
+      <c r="I1187" s="6"/>
+    </row>
+    <row r="1188" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1188" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1188" s="6">
+        <v>13</v>
+      </c>
+      <c r="C1188" s="7" t="s">
+        <v>4220</v>
+      </c>
+      <c r="D1188" s="7" t="s">
+        <v>4236</v>
+      </c>
+      <c r="E1188" s="20">
+        <v>3.39</v>
+      </c>
+      <c r="F1188" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1188" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1188" s="9" t="s">
+        <v>4241</v>
+      </c>
+      <c r="I1188" s="6"/>
+    </row>
+    <row r="1189" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1189" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1189" s="6">
+        <v>14</v>
+      </c>
+      <c r="C1189" s="7" t="s">
+        <v>4221</v>
+      </c>
+      <c r="D1189" s="7" t="s">
+        <v>4237</v>
+      </c>
+      <c r="E1189" s="20">
+        <v>3.53</v>
+      </c>
+      <c r="F1189" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1189" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1189" s="9" t="s">
+        <v>4240</v>
+      </c>
+      <c r="I1189" s="6"/>
+    </row>
+    <row r="1190" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1190" s="6">
+        <v>36520261</v>
+      </c>
+      <c r="B1190" s="6">
+        <v>15</v>
+      </c>
+      <c r="C1190" s="7" t="s">
+        <v>4222</v>
+      </c>
+      <c r="D1190" s="7" t="s">
+        <v>4238</v>
+      </c>
+      <c r="E1190" s="20">
+        <v>3.88</v>
+      </c>
+      <c r="F1190" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1190" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1190" s="9" t="s">
+        <v>4253</v>
+      </c>
+      <c r="I1190" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F2961F-0E60-4CED-B8CD-2E5CDBF489DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED50DFD-295C-4DE3-A4EF-B3537753BDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4593" uniqueCount="4254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4633" uniqueCount="4290">
   <si>
     <t>No</t>
   </si>
@@ -14038,6 +14038,114 @@
   </si>
   <si>
     <t>Το κλείσιμο συγκεντρώνει Black Thought, Ajay Prasanna και Anoushka Shankar σε ένα epic art-pop/hip-hop finale. Ο «λυπημένος θεός» είναι η πιο καθαρή θεματική εικόνα του album, θεότητα ή άνθρωπος που έχει δύναμη αλλά όχι λύση απέναντι στον θάνατο, στην απώλεια και στην ανθρώπινη βία. Η μουσική δεν προσφέρει εύκολη κάθαρση· χτίζει πνευματική ένταση, rap απαγγελία, κλασικά ινδικά μοτίβα και ατμοσφαιρική παραγωγή ώστε το τέλος να μοιάζει με παρατεταμένος διαλογισμός. Ως τελευταίο track, λειτουργεί σωστά, δεν λέει ότι το πένθος λύθηκε, αλλά ότι η αποδοχή του μπορεί να γίνει αφετηρία για συνεχιζόμενη ζωή.</t>
+  </si>
+  <si>
+    <t>Double Vision</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/16448232-Foreigner-Double-Vision</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/-1H62SPwUfDgiJc6zdgNk8gTmgqVm9IRc61sZHiKalE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTU2Nzc1/ODgtMTM5OTY3MjQ3/NS01ODk5LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Foreigner</t>
+  </si>
+  <si>
+    <t>Atlantic – 50476. Ελληνική έκδοση του 1978 (Greek Pressing), με τύπωμα εξωφύλλου στο Ηνωμένο Βασίλειο (Sleeve printed in the UK) και χωρίς λογότυπο WEA κάτω δεξιά στο πίσω μέρος (No WEA logo printed on the back sleeve bottom right). Η φυσική κοπή/κατασκευή (Pressed By) έγινε στην Columbia, Athens (με κωδικό 7160 στις ετικέτες). Το mastering και η χάραξη (Lacquer Cut) φέρουν τη σφραγίδα της ιστορικής Sterling Sound (STERLING).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Double Vision είναι το δεύτερο στούντιο άλμπουμ του βρετανο-αμερικανικού rock συγκροτήματος Foreigner, το οποίο κυκλοφόρησε τον Ιούνιο του 1978 από την Atlantic Records. Την παραγωγή υπέγραψαν οι Ian McDonald, Keith Olsen και Mick Jones, ενώ το Mastering έγινε από τον George Marino (με τα acetate/lacquer masters να χαράσσονται στη Sterling Sound). Ο δίσκος γνώρισε τεράστια εμπορική επιτυχία, γίνοντας πολυπλατινένιος, χάρη σε hard rock και arena rock ύμνους όπως το ομώνυμο κομμάτι και το "Hot Blooded".</t>
+  </si>
+  <si>
+    <t>Hot Blooded</t>
+  </si>
+  <si>
+    <t>Blue Morning, Blue Day</t>
+  </si>
+  <si>
+    <t>You’re All I Am</t>
+  </si>
+  <si>
+    <t>Back Where You Belong</t>
+  </si>
+  <si>
+    <t>Love Has Taken Its Toll</t>
+  </si>
+  <si>
+    <t>Tramontane</t>
+  </si>
+  <si>
+    <t>I Have Waited So Long</t>
+  </si>
+  <si>
+    <t>Lonely Children</t>
+  </si>
+  <si>
+    <t>Spellbinder</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Arena Rock, Pop Rock, Melodic Rock, Soft Rock, Progressive Rock touches]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Riff Rock, Arena Rock, Boogie Hard Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Rock, Keyboard Rock, Dramatic Arena Rock]</t>
+  </si>
+  <si>
+    <t>Soft Rock, AOR [Power Ballad, Piano Rock, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Hard Rock, Baroque Pop-Rock touches, Arena Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Soft Rock [Melodic Rock, Reflective Ballad, Pop Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Arena Rock Anthem, Riff Rock, Pop-Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Instrumental Rock [Progressive Instrumental, Keyboard Rock, Jazz-Rock touches]</t>
+  </si>
+  <si>
+    <t>Soft Rock, AOR [Late-Night Ballad, Melodic Rock, Reflective Pop Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Rock, Darker Arena Rock, Keyboard Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Hard Rock, Dramatic Album Closer, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Το album κλείνει με πιο δραματικό melodic hard rock. Ο “spellbinder” είναι κάποιος ή κάτι που μαγεύει, χειραγωγεί ή καθηλώνει τον αφηγητή· η μουσική δίνει σε αυτή την εικόνα περισσότερο σκοτάδι από ό,τι στις πιο φωτεινές AOR στιγμές του δίσκου. Οι κιθάρες και τα keyboards συνεργάζονται για να χτίσουν αίσθηση κλιμάκωσης, ενώ ο Gramm διατηρεί το χαρακτηριστικό μείγμα soulfulness και hard-rock έντασης. Δεν είναι τόσο κλασικό όσο το “Double Vision” ή το “Hot Blooded”, αλλά ως finale λειτουργεί σωστά: αφήνει το album να τελειώσει με μεγαλύτερη ατμοσφαιρική ένταση αντί με απλό party-rock κλείσιμο.</t>
+  </si>
+  <si>
+    <t>Πιο σκοτεινό και πιο ανήσυχο, με τίτλο που φέρνει εικόνες απομόνωσης και ανθρώπων που μένουν μόνοι μέσα σε μια φαινομενικά γεμάτη κοινωνία. Η μουσική ανεβάζει ξανά τον ρυθμό, με πιο νευρικό keyboard rock και κιθάρες που έχουν μεγαλύτερη ένταση. Ο Gramm δίνει στο refrain δραματικότητα, χωρίς να το αφήνει να γίνει πλήρης power ballad. Είναι από τα καλύτερα deep cuts του δίσκου, επειδή συνδυάζει το πιο σκληρό Foreigner momentum με τη μελαγχολική, αστική αίσθηση που εμφανίζεται σε αρκετά τραγούδια της περιόδου.</t>
+  </si>
+  <si>
+    <t>Late-night AOR ballad με τίτλο που δηλώνει μακρά αναμονή, προσδοκία και συναισθηματική κόπωση. Μετά την instrumentality του “Tramontane”, η μπάντα επιστρέφει σε πιο προσωπικό πεδίο. Ο Gramm τραγουδά σαν να βρίσκεται στο χαμηλότερο σημείο μετά από μια μεγάλη, άκαρπη αναμονή, ενώ η παραγωγή επιλέγει απαλές κιθάρες και keyboard layers. Δεν είναι το πιο δραματικό ή memorable ballad του δίσκου, αλλά έχει σωστή ατμόσφαιρα και λειτουργεί σαν ήρεμος διάδρομος πριν από τα πιο έντονα τελευταία τραγούδια.</t>
+  </si>
+  <si>
+    <t>Instrumental κομμάτι που δείχνει την λιγότερο προφανή, πιο progressive πλευρά της μπάντας. Ο τίτλος αναφέρεται σε ψυχρό, βόρειο άνεμο, και η μουσική δημιουργεί αντίστοιχη αίσθηση κίνησης και ατμοσφαιρικού χώρου. Τα keyboards του Al Greenwood και η κιθάρα του Mick Jones παίρνουν κεντρικό ρόλο, με τη σύνθεση να μετακινείται ανάμεσα σε rock drive, jazz-rock χρώματα και prog στιγμές. Δεν λειτουργεί ως hit ή sing-along, αλλά είναι πολύ χρήσιμο μέσα στο album: μετά την ακαριαία οικειότητα του title track, δίνει χώρο στην μπάντα να αποδείξει ότι δεν ήταν αποκλειστικά radio-rock machine. Η Apple Music το αναφέρει συγκεκριμένα ως “proggy instrumental”.</t>
+  </si>
+  <si>
+    <t>Η μεγάλη κορύφωση του album και ένα από τα πιο αποτελεσματικά arena-rock songs της δεκαετίας του 1970. Η “διπλή όραση” μπορεί να προέρχεται από ζάλη, υπερβολή ή ψυχολογική σύγχυση, και η μουσική την μετατρέπει σε σφιχτό, καθαρό riff anthem. Η κιθάρα του Mick Jones και τα keyboards δίνουν στον σκελετό του τραγουδιού μεγάλη αναγνωρισιμότητα, ενώ ο Gramm τραγουδά με απόλυτη αυτοπεποίθηση. Το κομμάτι είναι πιο pop-focused από το “Hot Blooded”, αλλά εξίσου σκληρό στην εκτέλεση. Έφτασε στο Νο. 2 του Billboard Hot 100 και παραμένει από τα defining Foreigner tracks.</t>
+  </si>
+  <si>
+    <t>Η A πλευρά κλείνει με πιο ήσυχη και αναστοχαστική ερωτική σύνθεση. Η αγάπη εδώ δεν παρουσιάζεται σαν λύτρωση· έχει αφήσει το τίμημά της, έχει εξαντλήσει ή πληγώσει τον αφηγητή. Η συμμετοχή του Ian McDonald στη σύνθεση βοηθά να υπάρχει ελαφρώς πιο πλούσια αρμονική υφή και λιγότερο ευθύ AOR formula. Ο Gramm τραγουδά συγκρατημένα, επιτρέποντας στο αίσθημα κούρασης να βγει μέσα από τη μελωδία και όχι μέσα από μεγάλη δραματική έκρηξη. Δεν είναι κορυφαίο highlight, αλλά έχει σωστή θέση: προσφέρει την απαραίτητη συναισθηματική χαλάρωση πριν από το δυναμικό ξεκίνημα της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Mid-tempo melodic hard rock με έντονη αίσθηση επιστροφής και συναισθηματικής διεκδίκησης. Ο τίτλος υπονοεί ότι κάποιος ή κάτι πρέπει να γυρίσει στη θέση όπου πραγματικά ανήκει — είτε πρόκειται για σχέση είτε για μια χαμένη ταυτότητα. Η μουσική έχει πιο επιμελημένο, σχεδόν baroque pop-rock backbone σε ορισμένες αρμονικές κινήσεις, αλλά οι κιθάρες και τα drums διατηρούν την απαιτούμενη hard-rock ένταση. Δεν έχει το άμεσο hit power του “Blue Morning, Blue Day”, όμως είναι καλό παράδειγμα της καθαρής, επαγγελματικής songwriting λογικής του Mick Jones: κάθε μέρος υπηρετεί το chorus και τίποτα δεν περισσεύει.</t>
+  </si>
+  <si>
+    <t>Η πρώτη πιο καθαρή ballad στιγμή του album. Ο τίτλος δηλώνει συναισθηματική εξάρτηση ή αφοσίωση: το άλλο πρόσωπο δεν είναι απλώς μέρος της ζωής του αφηγητή, είναι όλη του η ταυτότητα. Η σύνθεση χρησιμοποιεί πιάνο, πιο μαλακές κιθαριστικές γραμμές και φωνητική ερμηνεία που αφήνει τον Gramm να δείξει τη soulful πλευρά του. Το τραγούδι δεν γίνεται υπερβολικά γλυκό, επειδή η μπάντα κρατά το AOR υπόβαθρο πυκνό και η παραγωγή αποφεύγει τη σακχαρώδη ενορχήστρωση. Είναι λιγότερο ξεχωριστό από τις επόμενες μεγάλες Foreigner ballads της δεκαετίας, αλλά λειτουργεί ως πρώιμη απόδειξη ότι το συγκρότημα μπορούσε να σταθεί και έξω από το riff-driven rock.</t>
+  </si>
+  <si>
+    <t>Πιο δραματικό και πιο περίπλοκο σε ατμόσφαιρα από το “Hot Blooded”. Ο τίτλος φέρνει μια εικόνα πρωινού μετά από άγρυπνη, μοναχική ή ενοχική νύχτα· το “blue” είναι ταυτόχρονα χρώμα και συναισθηματική κατάσταση. Η μουσική κινείται με keyboard-led ένταση, ενώ η φωνή του Gramm γίνεται πιο ευάλωτη και θεατρική. Οι κιθάρες του Mick Jones κρατούν το τραγούδι σε hard-rock έδαφος, αλλά η μελωδία και η ενορχήστρωση του δίνουν σχεδόν Queen-like μεγαλοπρέπεια. Δεν είναι τόσο άμεσο όπως τα δύο μεγάλα riff anthems του album, όμως είναι εξαιρετικό παράδειγμα της ικανότητας των Foreigner να δίνουν σε ένα ραδιοφωνικό τραγούδι εσωτερικό δράμα. Έφτασε στο Νο. 15 του Billboard Hot 100.</t>
+  </si>
+  <si>
+    <t>Το album ξεκινά με ένα από τα πιο αναγνωρίσιμα riff των Foreigner. Το “Hot Blooded” είναι καθαρό hard-rock statement: boogie κίνηση, κοφτή κιθάρα, επιθετικό rhythm section και η φωνή του Lou Gramm να κινείται ανάμεσα σε bluesy swagger και arena-rock καθαρότητα. Οι στίχοι είναι γεμάτοι σεξουαλικά υπονοούμενα — ο αφηγητής βλέπει την επιθυμία σαν άμεση σωματική θερμότητα — όμως η δύναμη του τραγουδιού δεν είναι η στιχουργική λεπτότητα· είναι ο τρόπος που το riff και το chorus χτυπούν σαν ένα. Έφτασε στο Νο. 3 του Billboard Hot 100 και καθιέρωσε τους Foreigner ως μπάντα που μπορούσε να κάνει hard rock με pop-scale απήχηση.</t>
   </si>
 </sst>
 </file>
@@ -14643,7 +14751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -18623,6 +18731,38 @@
       </c>
       <c r="J124" s="11" t="s">
         <v>4205</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>4257</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>4254</v>
+      </c>
+      <c r="D125" s="6">
+        <v>1978</v>
+      </c>
+      <c r="E125" s="10">
+        <v>3.33</v>
+      </c>
+      <c r="F125" s="26" t="s">
+        <v>4269</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>4259</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>4258</v>
+      </c>
+      <c r="I125" s="11" t="s">
+        <v>4255</v>
+      </c>
+      <c r="J125" s="11" t="s">
+        <v>4256</v>
       </c>
     </row>
   </sheetData>
@@ -18870,6 +19010,8 @@
     <hyperlink ref="J123" r:id="rId241" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
     <hyperlink ref="I124" r:id="rId242" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
     <hyperlink ref="J124" r:id="rId243" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
+    <hyperlink ref="I125" r:id="rId244" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
+    <hyperlink ref="J125" r:id="rId245" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18877,7 +19019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1190"/>
+  <dimension ref="A1:I1200"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -51214,6 +51356,282 @@
       </c>
       <c r="I1190" s="6"/>
     </row>
+    <row r="1191" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1191" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1191" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1191" s="7" t="s">
+        <v>4260</v>
+      </c>
+      <c r="D1191" s="7" t="s">
+        <v>4270</v>
+      </c>
+      <c r="E1191" s="20">
+        <v>3.65</v>
+      </c>
+      <c r="F1191" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1191" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H1191" s="9" t="s">
+        <v>4289</v>
+      </c>
+      <c r="I1191" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1192" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1192" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1192" s="7" t="s">
+        <v>4261</v>
+      </c>
+      <c r="D1192" s="7" t="s">
+        <v>4271</v>
+      </c>
+      <c r="E1192" s="20">
+        <v>3.78</v>
+      </c>
+      <c r="F1192" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1192" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1192" s="9" t="s">
+        <v>4288</v>
+      </c>
+      <c r="I1192" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1193" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1193" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1193" s="7" t="s">
+        <v>4262</v>
+      </c>
+      <c r="D1193" s="7" t="s">
+        <v>4272</v>
+      </c>
+      <c r="E1193" s="20">
+        <v>2.99</v>
+      </c>
+      <c r="F1193" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1193" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1193" s="9" t="s">
+        <v>4287</v>
+      </c>
+      <c r="I1193" s="6"/>
+    </row>
+    <row r="1194" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1194" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1194" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1194" s="7" t="s">
+        <v>4263</v>
+      </c>
+      <c r="D1194" s="7" t="s">
+        <v>4273</v>
+      </c>
+      <c r="E1194" s="20">
+        <v>3.25</v>
+      </c>
+      <c r="F1194" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1194" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="H1194" s="9" t="s">
+        <v>4286</v>
+      </c>
+      <c r="I1194" s="6"/>
+    </row>
+    <row r="1195" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1195" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1195" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1195" s="7" t="s">
+        <v>4264</v>
+      </c>
+      <c r="D1195" s="7" t="s">
+        <v>4274</v>
+      </c>
+      <c r="E1195" s="20">
+        <v>3.13</v>
+      </c>
+      <c r="F1195" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1195" s="12">
+        <v>3.95</v>
+      </c>
+      <c r="H1195" s="9" t="s">
+        <v>4285</v>
+      </c>
+      <c r="I1195" s="6"/>
+    </row>
+    <row r="1196" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1196" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1196" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1196" s="7" t="s">
+        <v>4254</v>
+      </c>
+      <c r="D1196" s="7" t="s">
+        <v>4275</v>
+      </c>
+      <c r="E1196" s="20">
+        <v>3.97</v>
+      </c>
+      <c r="F1196" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1196" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="H1196" s="9" t="s">
+        <v>4284</v>
+      </c>
+      <c r="I1196" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1197" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1197" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1197" s="7" t="s">
+        <v>4265</v>
+      </c>
+      <c r="D1197" s="7" t="s">
+        <v>4276</v>
+      </c>
+      <c r="E1197" s="20">
+        <v>3.13</v>
+      </c>
+      <c r="F1197" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1197" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1197" s="9" t="s">
+        <v>4283</v>
+      </c>
+      <c r="I1197" s="6"/>
+    </row>
+    <row r="1198" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1198" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1198" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1198" s="7" t="s">
+        <v>4266</v>
+      </c>
+      <c r="D1198" s="7" t="s">
+        <v>4277</v>
+      </c>
+      <c r="E1198" s="20">
+        <v>3.22</v>
+      </c>
+      <c r="F1198" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1198" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1198" s="9" t="s">
+        <v>4282</v>
+      </c>
+      <c r="I1198" s="6"/>
+    </row>
+    <row r="1199" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1199" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1199" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1199" s="7" t="s">
+        <v>4267</v>
+      </c>
+      <c r="D1199" s="7" t="s">
+        <v>4278</v>
+      </c>
+      <c r="E1199" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F1199" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1199" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1199" s="9" t="s">
+        <v>4281</v>
+      </c>
+      <c r="I1199" s="6"/>
+    </row>
+    <row r="1200" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1200" s="6">
+        <v>16448232</v>
+      </c>
+      <c r="B1200" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1200" s="7" t="s">
+        <v>4268</v>
+      </c>
+      <c r="D1200" s="7" t="s">
+        <v>4279</v>
+      </c>
+      <c r="E1200" s="20">
+        <v>3.35</v>
+      </c>
+      <c r="F1200" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1200" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1200" s="9" t="s">
+        <v>4280</v>
+      </c>
+      <c r="I1200" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED50DFD-295C-4DE3-A4EF-B3537753BDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB90A04-37C9-4254-B2CB-257B9D92D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14049,9 +14049,6 @@
     <t>https://i.discogs.com/-1H62SPwUfDgiJc6zdgNk8gTmgqVm9IRc61sZHiKalE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTU2Nzc1/ODgtMTM5OTY3MjQ3/NS01ODk5LmpwZWc.jpeg</t>
   </si>
   <si>
-    <t xml:space="preserve">	Foreigner</t>
-  </si>
-  <si>
     <t>Atlantic – 50476. Ελληνική έκδοση του 1978 (Greek Pressing), με τύπωμα εξωφύλλου στο Ηνωμένο Βασίλειο (Sleeve printed in the UK) και χωρίς λογότυπο WEA κάτω δεξιά στο πίσω μέρος (No WEA logo printed on the back sleeve bottom right). Η φυσική κοπή/κατασκευή (Pressed By) έγινε στην Columbia, Athens (με κωδικό 7160 στις ετικέτες). Το mastering και η χάραξη (Lacquer Cut) φέρουν τη σφραγίδα της ιστορικής Sterling Sound (STERLING).</t>
   </si>
   <si>
@@ -14146,6 +14143,9 @@
   </si>
   <si>
     <t>Το album ξεκινά με ένα από τα πιο αναγνωρίσιμα riff των Foreigner. Το “Hot Blooded” είναι καθαρό hard-rock statement: boogie κίνηση, κοφτή κιθάρα, επιθετικό rhythm section και η φωνή του Lou Gramm να κινείται ανάμεσα σε bluesy swagger και arena-rock καθαρότητα. Οι στίχοι είναι γεμάτοι σεξουαλικά υπονοούμενα — ο αφηγητής βλέπει την επιθυμία σαν άμεση σωματική θερμότητα — όμως η δύναμη του τραγουδιού δεν είναι η στιχουργική λεπτότητα· είναι ο τρόπος που το riff και το chorus χτυπούν σαν ένα. Έφτασε στο Νο. 3 του Billboard Hot 100 και καθιέρωσε τους Foreigner ως μπάντα που μπορούσε να κάνει hard rock με pop-scale απήχηση.</t>
+  </si>
+  <si>
+    <t>Foreigner</t>
   </si>
 </sst>
 </file>
@@ -18738,7 +18738,7 @@
         <v>16448232</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>4257</v>
+        <v>4289</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>4254</v>
@@ -18750,13 +18750,13 @@
         <v>3.33</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>4269</v>
+        <v>4268</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>4259</v>
+        <v>4258</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
       <c r="I125" s="11" t="s">
         <v>4255</v>
@@ -51364,10 +51364,10 @@
         <v>1</v>
       </c>
       <c r="C1191" s="7" t="s">
-        <v>4260</v>
+        <v>4259</v>
       </c>
       <c r="D1191" s="7" t="s">
-        <v>4270</v>
+        <v>4269</v>
       </c>
       <c r="E1191" s="20">
         <v>3.65</v>
@@ -51379,7 +51379,7 @@
         <v>4.55</v>
       </c>
       <c r="H1191" s="9" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
       <c r="I1191" s="6" t="s">
         <v>240</v>
@@ -51393,10 +51393,10 @@
         <v>2</v>
       </c>
       <c r="C1192" s="7" t="s">
-        <v>4261</v>
+        <v>4260</v>
       </c>
       <c r="D1192" s="7" t="s">
-        <v>4271</v>
+        <v>4270</v>
       </c>
       <c r="E1192" s="20">
         <v>3.78</v>
@@ -51408,7 +51408,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1192" s="9" t="s">
-        <v>4288</v>
+        <v>4287</v>
       </c>
       <c r="I1192" s="6" t="s">
         <v>240</v>
@@ -51422,10 +51422,10 @@
         <v>3</v>
       </c>
       <c r="C1193" s="7" t="s">
-        <v>4262</v>
+        <v>4261</v>
       </c>
       <c r="D1193" s="7" t="s">
-        <v>4272</v>
+        <v>4271</v>
       </c>
       <c r="E1193" s="20">
         <v>2.99</v>
@@ -51437,7 +51437,7 @@
         <v>4.3</v>
       </c>
       <c r="H1193" s="9" t="s">
-        <v>4287</v>
+        <v>4286</v>
       </c>
       <c r="I1193" s="6"/>
     </row>
@@ -51449,10 +51449,10 @@
         <v>4</v>
       </c>
       <c r="C1194" s="7" t="s">
-        <v>4263</v>
+        <v>4262</v>
       </c>
       <c r="D1194" s="7" t="s">
-        <v>4273</v>
+        <v>4272</v>
       </c>
       <c r="E1194" s="20">
         <v>3.25</v>
@@ -51464,11 +51464,11 @@
         <v>3.8</v>
       </c>
       <c r="H1194" s="9" t="s">
-        <v>4286</v>
+        <v>4285</v>
       </c>
       <c r="I1194" s="6"/>
     </row>
-    <row r="1195" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A1195" s="6">
         <v>16448232</v>
       </c>
@@ -51476,10 +51476,10 @@
         <v>5</v>
       </c>
       <c r="C1195" s="7" t="s">
-        <v>4264</v>
+        <v>4263</v>
       </c>
       <c r="D1195" s="7" t="s">
-        <v>4274</v>
+        <v>4273</v>
       </c>
       <c r="E1195" s="20">
         <v>3.13</v>
@@ -51491,7 +51491,7 @@
         <v>3.95</v>
       </c>
       <c r="H1195" s="9" t="s">
-        <v>4285</v>
+        <v>4284</v>
       </c>
       <c r="I1195" s="6"/>
     </row>
@@ -51506,7 +51506,7 @@
         <v>4254</v>
       </c>
       <c r="D1196" s="7" t="s">
-        <v>4275</v>
+        <v>4274</v>
       </c>
       <c r="E1196" s="20">
         <v>3.97</v>
@@ -51518,7 +51518,7 @@
         <v>4.7</v>
       </c>
       <c r="H1196" s="9" t="s">
-        <v>4284</v>
+        <v>4283</v>
       </c>
       <c r="I1196" s="6" t="s">
         <v>240</v>
@@ -51532,10 +51532,10 @@
         <v>7</v>
       </c>
       <c r="C1197" s="7" t="s">
-        <v>4265</v>
+        <v>4264</v>
       </c>
       <c r="D1197" s="7" t="s">
-        <v>4276</v>
+        <v>4275</v>
       </c>
       <c r="E1197" s="20">
         <v>3.13</v>
@@ -51547,7 +51547,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H1197" s="9" t="s">
-        <v>4283</v>
+        <v>4282</v>
       </c>
       <c r="I1197" s="6"/>
     </row>
@@ -51559,10 +51559,10 @@
         <v>8</v>
       </c>
       <c r="C1198" s="7" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
       <c r="D1198" s="7" t="s">
-        <v>4277</v>
+        <v>4276</v>
       </c>
       <c r="E1198" s="20">
         <v>3.22</v>
@@ -51574,11 +51574,11 @@
         <v>4</v>
       </c>
       <c r="H1198" s="9" t="s">
-        <v>4282</v>
+        <v>4281</v>
       </c>
       <c r="I1198" s="6"/>
     </row>
-    <row r="1199" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A1199" s="6">
         <v>16448232</v>
       </c>
@@ -51586,10 +51586,10 @@
         <v>9</v>
       </c>
       <c r="C1199" s="7" t="s">
-        <v>4267</v>
+        <v>4266</v>
       </c>
       <c r="D1199" s="7" t="s">
-        <v>4278</v>
+        <v>4277</v>
       </c>
       <c r="E1199" s="20">
         <v>3.35</v>
@@ -51601,7 +51601,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H1199" s="9" t="s">
-        <v>4281</v>
+        <v>4280</v>
       </c>
       <c r="I1199" s="6"/>
     </row>
@@ -51613,10 +51613,10 @@
         <v>10</v>
       </c>
       <c r="C1200" s="7" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
       <c r="D1200" s="7" t="s">
-        <v>4279</v>
+        <v>4278</v>
       </c>
       <c r="E1200" s="20">
         <v>3.35</v>
@@ -51628,7 +51628,7 @@
         <v>4.2</v>
       </c>
       <c r="H1200" s="9" t="s">
-        <v>4280</v>
+        <v>4279</v>
       </c>
       <c r="I1200" s="6"/>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB90A04-37C9-4254-B2CB-257B9D92D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEC64C3-6A8C-4C36-9903-EB5301E34CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4633" uniqueCount="4290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4716" uniqueCount="4370">
   <si>
     <t>No</t>
   </si>
@@ -14146,6 +14146,246 @@
   </si>
   <si>
     <t>Foreigner</t>
+  </si>
+  <si>
+    <t>Fuzzy Duck</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/34592074-Fuzzy-Duck-Fuzzy-Duck</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Q2BY6-5bhJEw0E0z5sVfws1eaV1OcRg-TdI-gyHGbDw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0NTky/MDc0LTE3NTMwMjAw/ODYtMzkyMi5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Sun King (2) – SUN 20. Γερμανική επανέκδοση (Germany, Reissue) του 2025 σε βινύλιο, η οποία αποδίδει πιστά το θρυλικό και δυσεύρετο βρετανικό hard/prog rock underground ήχο των αρχών της δεκαετίας του '70.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το ομώνυμο άλμπουμ των Fuzzy Duck κυκλοφόρησε αρχικά το 1971 από τη MAM Records και αποτελεί ένα από τα πιο περιζήτητα «holy grails» του βρετανικού progressive και hard rock, γνωστό για τα βαριά πλήκτρα, τα κοφτερά κιθαριστικά riffs και την ψυχεδελική του ατμόσφαιρα. Η παραγωγή υπογράφεται από τους ίδιους τους Fuzzy Duck, με μηχανικό ήχου τον Keith Harwood. Η παρούσα σύγχρονη έκδοση (Sun King, 2025) προσφέρει εξαιρετική αναλογική αποκατάσταση, αναδεικνύοντας τις δυναμικές ενορχχρήστρωσεις της μπάντας (Mick Hawksworth, Grahame White, Roy Sharland, Paul Francis).</t>
+  </si>
+  <si>
+    <t>Time Will Be Your Doctor</t>
+  </si>
+  <si>
+    <t>Mrs. Prout</t>
+  </si>
+  <si>
+    <t>Just Look Around You</t>
+  </si>
+  <si>
+    <t>Afternoon Out</t>
+  </si>
+  <si>
+    <t>More Than I Am</t>
+  </si>
+  <si>
+    <t>In Our Time</t>
+  </si>
+  <si>
+    <t>A Word From Big D</t>
+  </si>
+  <si>
+    <t>Double Time Woman</t>
+  </si>
+  <si>
+    <t>Big Brass Band</t>
+  </si>
+  <si>
+    <t>One More Hour</t>
+  </si>
+  <si>
+    <t>No Name Face</t>
+  </si>
+  <si>
+    <t>Με πιο μελωδικό και ελαφρά πιο ανοιχτό mood, το “Afternoon Out” λειτουργεί σαν μια μικρή έξοδος από τη βαρύτητα των προηγούμενων tracks. Ο τίτλος παραπέμπει σε απλή καθημερινή απόδραση, όμως η μουσική παραμένει γεμάτη organ, κιθάρα και heavy-rock ένταση. Η σύνθεση διαθέτει καλύτερη ισορροπία ανάμεσα σε μελωδία και βάρος, με την κιθάρα να προσθέτει φωτεινότερες γραμμές πάνω από το Hammond. Είναι λιγότερο σκοτεινό και λιγότερο εκρηκτικό από τα βασικά epics του δίσκου, αλλά κρατά τη συνοχή της A πλευράς και επιβεβαιώνει ότι η μπάντα είχε αίσθηση τραγουδιού, όχι μόνο instrumental δύναμη.</t>
+  </si>
+  <si>
+    <t>Πιο playful και πιο rock ’n’ roll, με τίτλο που υπόσχεται brass-band ενέργεια, αλλά με τους Fuzzy Duck να τον μετατρέπουν σε σύντομο boogie/hard-rock cut. Η σύνθεση είναι λιγότερο βαριά, πιο άμεση και περισσότερο προσανατολισμένη στο fun. Ως extra track έχει ενδιαφέρον επειδή δείχνει ότι το σχήμα μπορούσε να κάνει και πιο light, commercial rock, χωρίς να χάνει εντελώς το Hammond-driven sound του. Ωστόσο, δεν έχει την ιδιαίτερη προοδευτική ταυτότητα του κύριου LP.</t>
+  </si>
+  <si>
+    <t>Σύντομο organ-based instrumental/interlude, με τίτλο που μοιάζει σαν μικρή παρέμβαση από έναν χαρακτήρα με το όνομα “Big D”. Δεν έχει την πλήρη ανάπτυξη ενός κανονικού τραγουδιού, γι’ αυτό η χαμηλότερη βαθμολογία αφορά την αυτονομία του και όχι την ποιότητα της εκτέλεσης. Μέσα στην αρχική ακολουθία λειτουργεί ως έξυπνη, ψυχεδελική ανάσα μετά το “In Our Time”, αλλά δεν παρέχει το μεγάλο κλείσιμο που ίσως θα περίμενε κανείς από heavy-prog LP. Στη δική σου expanded έκδοση, μάλιστα, ακολουθούν τα τέσσερα non-LP tracks, οπότε λειτουργεί περισσότερο ως τέλος του βασικού album programme παρά ως απόλυτο τέλος του δίσκου.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό psych-hard-rock τραγούδι με τίτλο που φέρνει εικόνα ανωνυμίας, αποξένωσης ή ανθρώπου χωρίς σταθερή ταυτότητα. Η μουσική έχει περισσότερη παράξενη ατμόσφαιρα από το “Big Brass Band”, με fuzz κιθάρα και Hammond που επαναφέρουν τη χαρακτηριστική heaviness της μπάντας. Λειτουργεί σωστά ως τελευταίο expanded-programme track, επειδή αφήνει μια πιο μυστηριώδη και ψυχεδελική τελική αίσθηση. Παρ’ όλα αυτά, για σκοπούς αρχειοθέτησης πρέπει να παραμείνει ξεχωριστό ως non-LP material και να μην επηρεάζει τη συνολική αξιολόγηση του αρχικού 1971 album.</t>
+  </si>
+  <si>
+    <t>Non-LP single track με πιο compact, boogie-heavy λογική. Η σύνθεση αφήνει το prog development στην άκρη και λειτουργεί ως σύντομο, riff-driven blues rocker. Ο τίτλος υπονοεί μια γυναίκα που κινείται σε “double time” , γρήγορα, υπερβολικά ή διπλά σε σχέση με τον αφηγητή , και η μουσική ανταποκρίνεται με πιο έντονο ρυθμό. Δεν έχει την ατμόσφαιρα των βασικών album tracks, αλλά δίνει χρήσιμη εικόνα για τη single-oriented πλευρά της μπάντας.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει ξανά με βαρύ organ-rock sound. Ο τίτλος , «περισσότερο από αυτό που είμαι» , υποδηλώνει αναζήτηση ταυτότητας ή επιθυμία να υπερβείς έναν περιορισμένο εαυτό. Η μουσική αναπτύσσεται με αρκετό χώρο για κιθάρα και όργανο, αλλά παραμένει εστιασμένη σε ένα στέρεο hard-rock groove. Ο Mick Hawksworth, που αναλαμβάνει τη φωνή και τη σύνθεση, δίνει στο track ελαφρώς διαφορετικό φωνητικό χρώμα από τα τραγούδια του Grahame White. Το αποτέλεσμα είναι πιο εσωτερικό, χωρίς να χάνει την ένταση. Είναι μία από τις καλύτερες B-side συνθέσεις και δείχνει ότι η μπάντα δεν βασιζόταν σε έναν μόνο songwriter ή frontman.</t>
+  </si>
+  <si>
+    <t>Το πιο ουσιαστικό από τα extra tracks, με περισσότερη bluesy βαρύτητα και πιο αναπτυγμένη hard-rock δομή. Ο τίτλος αφορά μια τελευταία ώρα , χρόνος που τελειώνει, ευκαιρία που χάνεται ή ερωτική παράταση , και η μπάντα δίνει στο θέμα μελωδικό βάρος. Το Hammond ξαναγίνεται πιο κεντρικό, οι κιθάρες έχουν περισσότερη ένταση και η σύνθεση θυμίζει περισσότερο τον βασικό album ήχο. Είναι η καλύτερη απόδειξη ότι τα bonus/single tracks δεν είναι απλές περιττές προσθήκες, αν και δεν έχουν ακριβώς το ίδιο συνεκτικό πλαίσιο με τα οκτώ tracks του αρχικού LP.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με τη βασική του συνταγή, Hammond organ μπροστά, hard-rock κιθάρα, bluesy φωνητικά και μια ρυθμική βάση που έχει μεγαλύτερο βάρος από το τυπικό prog της περιόδου. Ο τίτλος παρουσιάζει τον χρόνο ως γιατρό , η πληγή, η απογοήτευση ή η σύγχυση μπορεί να μην λυθεί άμεσα, αλλά ο χρόνος ίσως προσφέρει απόσταση και θεραπεία. Η μουσική δεν είναι μελαγχολική μπαλάντα· είναι δυναμική, heavy και γεμάτη οργανική κίνηση. Ο Roy Sharland δίνει στο Hammond καθοριστικό ρόλο, φέρνοντας το track κοντά σε Deep Purple/Uriah Heep, ενώ οι fuzzy κιθάρες εμποδίζουν τον ήχο να γίνει υπερβολικά καθαρός ή προοδευτικά εκλεπτυσμένος. Είναι ιδανικό opener και σαφής δήλωση heavy-prog ταυτότητας.</t>
+  </si>
+  <si>
+    <t>Πιο εκτεταμένο και πιο ψυχεδελικό, με τον παράξενο τίτλο να λειτουργεί ως character sketch ή absurdist αφήγηση. Το “Mrs. Prout” δεν επιδιώκει pop αμεσότητα, αφήνει τα όργανα να αναπτυχθούν, το Hammond να δημιουργήσει πυκνή ατμόσφαιρα και την κιθάρα να απαντά με heavy φράσεις. Η μπάντα δείχνει εδώ την prog πλευρά της όχι μέσα από περίπλοκες time signatures, αλλά μέσα από την ανάπτυξη των ιδεών και το χώρο που αφήνει στις αλλαγές διάθεσης. Η σύνθεση έχει 1960s psych residue, όμως ο ήχος είναι σαφώς 1971 heavy rock, πιο βαρύς, πιο χοντρός και με πραγματικό riff weight.</t>
+  </si>
+  <si>
+    <t>Πιο άμεσο blues-rock κομμάτι, με τον τίτλο να προσκαλεί τον ακροατή να κοιτάξει τον κόσμο γύρω του , ίσως να αναγνωρίσει μια αλήθεια που αγνοεί, ίσως να δει τη μοναξιά ή την ασχήμια κάτω από την επιφάνεια. Το τραγούδι έχει πιο απλή rock δομή, αλλά τα οργανικά layers του δίνουν χαρακτήρα. Η μπάντα βασίζεται σε guitar-and-organ dialogue και σε βαριά βρετανική hard-rock αίσθηση, αντί να κυνηγήσει μεγάλο chorus. Δεν είναι το πιο φιλόδοξο track, αλλά είναι ένα από τα πιο σφιχτά, αποδεικνύει ότι οι Fuzzy Duck μπορούσαν να γράψουν πειστικό, compact heavy rock χωρίς να χρειάζονται εκτεταμένα jams.</t>
+  </si>
+  <si>
+    <t>Παρά τον τίτλο, δεν είναι country song. Είναι heavy blues-rock με folkish/rootsy εικόνα, όπου ο «country boy» λειτουργεί ως σύμβολο μιας πιο απλής, γήινης ζωής απέναντι στην αστική ένταση. Το Hammond και η κιθάρα κρατούν τον ήχο κοντά σε heavy psych, ενώ ο ρυθμός αφήνει χώρο για πιο χαλαρή, bluesy κίνηση. Η μπάντα δεν προσπαθεί να μιμηθεί αμερικανικό Southern rock· παραμένει ξεκάθαρα βρετανική, με progressive ανάπτυξη και baroque organ χρώμα. Είναι από τα tracks που δείχνουν την ευρύτητα των Fuzzy Duck, μπορούν να κινηθούν από σκοτεινή βαρύτητα σε πιο γήινο groove χωρίς να χάνουν την ταυτότητά τους.</t>
+  </si>
+  <si>
+    <t>Η κορυφαία progressive/psychedelic στιγμή του βασικού LP. Με μεγαλύτερη διάρκεια, το track επιτρέπει στις ιδέες να αναπτυχθούν σε διαδοχικές φάσεις, ατμοσφαιρικό ξεκίνημα, heavy riffing, organ-led έκταση και κιθαριστικές κορυφώσεις. Ο τίτλος “In Our Time” έχει αίσθηση εποχικής δήλωσης , τι σημαίνει να ζεις μέσα στη συγκεκριμένη ταραγμένη ιστορική στιγμή , και η μουσική ανταποκρίνεται με ένα mood που είναι ταυτόχρονα αναστοχαστικό και δυναμικό. Η παρουσία electric cello και percussion προσθέτει texture χωρίς να μετατρέπει τη σύνθεση σε orchestral prog. Είναι το τραγούδι που δικαιολογεί περισσότερο το “heavy progressive rock” tag, μεγάλο, πολυεπίπεδο, αλλά πάντα γειωμένο σε riff και groove.</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Heavy Prog, Heavy Psych, Organ Rock, Blues Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Hammond Heavy Prog, Bluesy Organ Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Psych [Organ-led Heavy Prog, Psychedelic Hard Rock, Extended Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Bluesy Heavy Rock, Organ Rock, British Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Melodic Heavy Prog, Guitar-and-Organ Rock, Psych Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Non-LP Single, Bluesy Hard Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Non-LP Single, Boogie Rock, British Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Heavy Organ Rock, Melodic Prog, British Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Progressive Rock [Heavy Blues, Hammond Rock, Psychedelic Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Heavy Psych [Epic Heavy Prog, Psychedelic Rock, Organ-Guitar Jam]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Instrumental Rock [Short Instrumental, Organ Interlude, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Non-LP Single, Heavy Blues Rock, Organ Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Non-LP Single, Psych Hard Rock, Organ-Driven Rock]</t>
+  </si>
+  <si>
+    <t>Dirt Records (9) – DIRT 024. Αμερικανική έκδοση σε λευκό βινύλιο (White, κυκλοφορία 3 Νοεμβρίου 2023). Η κοπή/κατασκευή έγινε από την GZ Media (267769) και η υλοποίηση/κοπή από τη Vinyl Record Guru, ενώ το mastering υπογράφεται από τον Billy Bowers στη Casa de Amor και η ηχογράφηση έγινε στο Brooklet Recording με παραγωγό τον Nick DiDia.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Can't Find The Brakes είναι το δεύτερο ολοκληρωμένο στούντιο άλμπουμ των Dirty Honey. Συνδυάζει την κλασική hard-rock ενέργεια των 70s με σύγχρονα blues-rock στοιχεία, διαθέτοντας εξαιρετικά δυναμικά τύμπανα (Jajdon Bean), κοφτερά κιθαριστικά riffs (John Notto), στιβαρό μπάσο (Justin Smolian) και τα εκρηκτικά φωνητικά του Marc Labelle. Η συγκεκριμένη έκδοση σε λευκό βινύλιο διατέθηκε επίσης σε υπογεγραμμένα αντίτυπα κατά τη διάρκεια της περιοδείας τους το 2024.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/28792273-Dirty-Honey-Cant-Find-The-Brakes</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/fSLZMVe0dEjoipNxEUxDywC1MFVSh-8tfyptMgNeupE/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI4Nzky/MjczLTE2OTk3MDM4/NTQtMzYyMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Can't Find The Brakes</t>
+  </si>
+  <si>
+    <t>Dirty Honey</t>
+  </si>
+  <si>
+    <t>Don’t Put Out The Fire</t>
+  </si>
+  <si>
+    <t>Won’t Take Me Alive</t>
+  </si>
+  <si>
+    <t>Dirty Mind</t>
+  </si>
+  <si>
+    <t>Roam</t>
+  </si>
+  <si>
+    <t>Get A Little High</t>
+  </si>
+  <si>
+    <t>Coming Home (Ballad Of The Shire)</t>
+  </si>
+  <si>
+    <t>Can’t Find The Brakes</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Ride On</t>
+  </si>
+  <si>
+    <t>You Make It All Right</t>
+  </si>
+  <si>
+    <t>Rebel Son</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Modern Classic Rock, Southern Rock touches, Arena Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Classic Hard Rock, Bluesy Arena Rock, Guitar-led Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Rock [Fast Riff Rock, Arena Rock, Modern Classic Metal edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Sleaze Rock, Bluesy Riff Rock, Swagger Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Southern Rock [Road Rock, Roots Rock, Melodic Classic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Up-tempo Blues Rock, Boogie Rock, Party Rock]</t>
+  </si>
+  <si>
+    <t>Roots Rock, Hard Rock [Rustic Rock Ballad, Americana, Acoustic-tinged Classic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Driving Riff Rock, Modern Classic Rock, Road Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Bluesy Hard Rock, Soulful Rock, Mid-tempo Groove]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Fast Rocker, Boogie Hard Rock, Live-energy Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Epic Blues Rock, Southern Hard Rock, Dramatic Album Closer]</t>
+  </si>
+  <si>
+    <t>Road-rock τραγούδι με την περιπλάνηση ως βασική εικόνα. Το “roam” σημαίνει να κινείσαι χωρίς αυστηρό προορισμό, να αναζητάς κάτι έξω από μια σταθερή ζωή ή να επιλέγεις ελευθερία αντί για ασφάλεια. Η μουσική έχει πιο rootsy/Southern χρώμα, με κιθάρες που προτιμούν την αίσθηση του δρόμου από το βαρύ riff. Ο LaBelle τραγουδά με πιο ανοιχτή, λιγότερο επιθετική φωνητική γραμμή και έτσι το track λειτουργεί σαν ανάσα μετά τα πρώτα τρία πιο σκληρά cuts. Είναι ουσιαστικό για τη ροή του album επειδή δείχνει πως η μπάντα δεν ταυτίζει το classic rock μόνο με ένταση, αλλά και με κίνηση, χώρο και μελωδική ελευθερία.</t>
+  </si>
+  <si>
+    <t>Το πιο άμεσο party/boogie-rock κομμάτι της πρώτης πλευράς. Ο τίτλος μπορεί να διαβαστεί ως κάλεσμα για μέθη, ελευθερία ή απλή αποφόρτιση από το βάρος της καθημερινότητας. Το riff είναι απλό και προωθητικό, τα drums σπρώχνουν σταθερά και η κιθάρα προσθέτει bluesy φράσεις αντί για περίπλοκη δομή. Οι Dirty Honey δεν προσπαθούν να επανεφεύρουν το hard rock εδώ· το υπηρετούν με πειστική, live-ready ενέργεια. Είναι λιγότερο ιδιαίτερο από το “Won’t Take Me Alive”, αλλά λειτουργεί καλά ως κομμάτι που ανανεώνει τη διάθεση πριν από την πιο απρόσμενη “Coming Home”.</t>
+  </si>
+  <si>
+    <t>Η βασική power ballad του album, με πιο ώριμο blues-rock συναίσθημα από μια τυπική glam-metal slow song. Ο τίτλος μιλά για κάποιον που δίνει νόημα ή ισορροπία σε μια δύσκολη ζωή. Η σύνθεση ξεκινά πιο συγκρατημένα, αφήνει τη φωνή του LaBelle να βγει μπροστά και σταδιακά ανεβαίνει σε μεγαλύτερη κιθαριστική και φωνητική κορύφωση. Οι κριτικές αναφέρουν το “balladeering” της σύνθεσης ως σημαντική αλλαγή ρυθμού. Είναι από τις πιο καθαρές αποδείξεις ότι η μπάντα μπορεί να υπηρετήσει μελωδία και ευαλωτότητα χωρίς να χάσει την hard-rock αξιοπιστία της.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με κλασικό, κιθαριστικό hard-rock τρόπο. Η «φωτιά» του τίτλου είναι επιθυμία, δημιουργική ορμή και ένταση , κάτι που ο αφηγητής δεν θέλει να σβήσει, ακόμη κι αν είναι επικίνδυνο. Η κιθάρα του John Notto μπαίνει με riff που έχει bluesy bite, το rhythm section κρατά σταθερή arena-rock κίνηση και ο Marc LaBelle τραγουδά με υψηλή, ελαφρώς gritty χροιά. Δεν προσπαθεί να κρύψει τις επιρροές του από ’70s rock, όμως η παραγωγή το κρατά σύγχρονο και άμεσο. Είναι σωστό opener γιατί εισάγει την ισορροπία του δίσκου ανάμεσα σε retro feeling και μοντέρνα καθαρότητα.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τη B πλευρά με road-rock ορμή. Η αδυναμία να «βρεις τα φρένα» είναι ταυτόχρονα κυριολεκτική εικόνα ταχύτητας και μεταφορά για ζωή που τρέχει ανεξέλεγκτα , επιθυμία, επιτυχία, περιοδεία ή αυτοκαταστροφική κίνηση. Η κιθάρα έχει driving riff, τα drums κρατούν συνεχή πίεση και το chorus δίνει στη σύνθεση άμεση συναυλιακή λειτουργία. Δεν είναι τόσο βαρύ όσο το “Won’t Take Me Alive”, αλλά έχει πολύ καλή ισορροπία μεταξύ μελωδίας και momentum. Είναι από τα tracks που δείχνουν την ικανότητα της μπάντας να γράφει σύγχρονα classic rock χωρίς να ακούγεται ως απλή αναπαραγωγή παλιών φόρμων.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο hard-rock peak της A πλευράς και το πιο αδιαπραγμάτευτο riff track του δίσκου. Ο τίτλος δηλώνει άρνηση υποταγής, ο αφηγητής δεν πρόκειται να παραδοθεί, να συλληφθεί ή να χάσει την ελευθερία του χωρίς μάχη. Η μουσική μεταφράζει τη στάση αυτή με γρήγορο tempo, έντονο μπάσο από τον Justin Smolian, κοφτές κιθάρες και chorus που λειτουργεί σαν arena chant. Ο John Notto το περιέγραψε ως το πιο επιθετικό και «bad-ass» τραγούδι που είχαν γράψει μέχρι τότε, και οι κριτικές το ξεχωρίζουν σταθερά ως highlight. Είναι classic-rock songwriting με άμεση, σύγχρονη παραγωγική δύναμη.</t>
+  </si>
+  <si>
+    <t>Επιστροφή σε πιο sleazy, bluesy hard-rock territory. Ο τίτλος υποδηλώνει σκέψη, επιθυμία ή φαντασίωση που δεν επιδιώκει να είναι ευγενική, και η μπάντα το αντιμετωπίζει με swagger αντί για υπερβολική θεατρικότητα. Η κιθάρα έχει dirty groove, η φωνή του LaBelle κινείται με ερωτική αυτοπεποίθηση και το rhythm section αφήνει χώρο ώστε το τραγούδι να «κάθεται» σωστά. Δεν είναι τόσο εκρηκτικό όσο το “Won’t Take Me Alive”, αλλά η χαμηλότερη ταχύτητα λειτουργεί υπέρ του, δίνει στο album blues-rock βάθος και θυμίζει ότι οι Dirty Honey είναι αποτελεσματικότεροι όταν δεν τρέχουν διαρκώς προς το refrain.</t>
+  </si>
+  <si>
+    <t>Η πιο ξεχωριστή και rootsy στιγμή της A πλευράς. Το “Ballad of the Shire” δεν πρέπει να αντιμετωπιστεί σαν απλό fantasy-reference gimmick, λειτουργεί ως εικόνα επιστροφής σε ένα ασφαλές, οικείο μέρος, μετά από δρόμους, περιοδείες ή συναισθηματική περιπλάνηση. Η μουσική έχει rustic/acoustic υφή και Americana αίσθηση, με τη φωνή του LaBelle να γίνεται πιο ζεστή και αφηγηματική. Οι κριτικές το χαρακτηρίζουν “rustic curveball”, γιατί σπάει την κυριαρχία του riff rock και αποκαλύπτει άλλη πλευρά της μπάντας. Είναι σημαντικό γιατί προετοιμάζει τον ακροατή για την πιο συναισθηματική B πλευρά.</t>
+  </si>
+  <si>
+    <t>Mid-tempo bluesy hard rock με τίτλο που ακούγεται σαν δήλωση ολοκλήρωσης, αλλά η μουσική υποδηλώνει ότι η ικανοποίηση μπορεί να είναι προσωρινή ή ασταθής. Το groove είναι το κέντρο, ο Smolian και ο drummer Jaydon Bean κρατούν την σύνθεση χαμηλά και σταθερά, επιτρέποντας στην κιθάρα να δώσει χρώμα και στον LaBelle να κινηθεί πιο soulful. Δεν είναι μεγάλο anthem ούτε power ballad· είναι ένα καλό, ισορροπημένο album track που ενισχύει τη blues-rock αξιοπιστία της B πλευράς.</t>
+  </si>
+  <si>
+    <t>Γρήγορο, απλό και σχεδιασμένο για live ενέργεια. Ο τίτλος είναι κλασικό rock ’n’ roll κάλεσμα, συνέχισε να κινείσαι, μη σταματάς, βγες στον δρόμο. Η μουσική δεν επιδιώκει να έχει θεματική πολυπλοκότητα· βασίζεται σε boogie hard-rock riff, γρήγορα drums και φωνητικό refrain που μπορεί να ανταποκριθεί το κοινό. Αυτό το κάνει λιγότερο ιδιαίτερο από τα βασικά highlights, αλλά όχι αδύναμο. Έχει τη σωστή θέση πριν από την ballad και το finale, ανεβάζει προσωρινά την πίεση για να γίνει πιο έντονη η συναισθηματική αλλαγή που ακολουθεί.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο, σχεδόν επικό κλείσιμο. Ο “rebel son” είναι μια φιγούρα που φέρει κληρονομιά, σύγκρουση με την αυθεντία και ανάγκη να βρει δικό της δρόμο. Η μουσική ξεκινά με πιο δραματική βάση και αναπτύσσεται σε bluesy Southern hard rock, αφήνοντας χώρο για κιθάρα, vocal κορύφωση και πιο σύνθετη αφηγηματική αίσθηση. Η διάρκεια του , περίπου επτά λεπτά , επιτρέπει στην μπάντα να πάει πέρα από το compact radio-rock format που κυριαρχεί σε άλλα tracks. Ως finale λειτουργεί σωστά επειδή μαζεύει τα βασικά στοιχεία του album, riffing, blues, δρόμο, ελευθερία και μια φωνή που κινείται μεταξύ swagger και πραγματικού συναισθήματος.</t>
   </si>
 </sst>
 </file>
@@ -14751,7 +14991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
@@ -18763,6 +19003,70 @@
       </c>
       <c r="J125" s="11" t="s">
         <v>4256</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>4290</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>4290</v>
+      </c>
+      <c r="D126" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E126" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>4318</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>4294</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>4293</v>
+      </c>
+      <c r="I126" s="11" t="s">
+        <v>4291</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>4336</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>4335</v>
+      </c>
+      <c r="D127" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E127" s="10">
+        <v>3.47</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>4348</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>4332</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>4331</v>
+      </c>
+      <c r="I127" s="11" t="s">
+        <v>4333</v>
+      </c>
+      <c r="J127" s="11" t="s">
+        <v>4334</v>
       </c>
     </row>
   </sheetData>
@@ -19012,6 +19316,10 @@
     <hyperlink ref="J124" r:id="rId243" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
     <hyperlink ref="I125" r:id="rId244" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
     <hyperlink ref="J125" r:id="rId245" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
+    <hyperlink ref="I126" r:id="rId246" xr:uid="{F619EC4F-CE2B-4A3F-A177-258B37F94B75}"/>
+    <hyperlink ref="J126" r:id="rId247" xr:uid="{16154418-6F7F-4716-B182-4CD246E54171}"/>
+    <hyperlink ref="I127" r:id="rId248" xr:uid="{E9BFACD2-2358-4D6F-8475-85410D79F5A9}"/>
+    <hyperlink ref="J127" r:id="rId249" xr:uid="{EBB7510F-0BE0-4317-9B06-1D95171523D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19019,7 +19327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1200"/>
+  <dimension ref="A1:I1223"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
@@ -51632,6 +51940,627 @@
       </c>
       <c r="I1200" s="6"/>
     </row>
+    <row r="1201" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1201" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1201" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1201" s="7" t="s">
+        <v>4295</v>
+      </c>
+      <c r="D1201" s="7" t="s">
+        <v>4319</v>
+      </c>
+      <c r="E1201" s="20">
+        <v>4.05</v>
+      </c>
+      <c r="F1201" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1201" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1201" s="9" t="s">
+        <v>4313</v>
+      </c>
+      <c r="I1201" s="6"/>
+    </row>
+    <row r="1202" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1202" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1202" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1202" s="7" t="s">
+        <v>4296</v>
+      </c>
+      <c r="D1202" s="7" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E1202" s="20">
+        <v>3.91</v>
+      </c>
+      <c r="F1202" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1202" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1202" s="9" t="s">
+        <v>4314</v>
+      </c>
+      <c r="I1202" s="6"/>
+    </row>
+    <row r="1203" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1203" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1203" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1203" s="7" t="s">
+        <v>4297</v>
+      </c>
+      <c r="D1203" s="7" t="s">
+        <v>4321</v>
+      </c>
+      <c r="E1203" s="20">
+        <v>3.98</v>
+      </c>
+      <c r="F1203" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1203" s="12">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="H1203" s="9" t="s">
+        <v>4315</v>
+      </c>
+      <c r="I1203" s="6"/>
+    </row>
+    <row r="1204" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1204" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1204" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1204" s="7" t="s">
+        <v>4298</v>
+      </c>
+      <c r="D1204" s="7" t="s">
+        <v>4322</v>
+      </c>
+      <c r="E1204" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="F1204" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1204" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1204" s="9" t="s">
+        <v>4306</v>
+      </c>
+      <c r="I1204" s="6"/>
+    </row>
+    <row r="1205" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1205" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1205" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1205" s="7" t="s">
+        <v>4302</v>
+      </c>
+      <c r="D1205" s="7" t="s">
+        <v>4323</v>
+      </c>
+      <c r="E1205" s="20">
+        <v>3.64</v>
+      </c>
+      <c r="F1205" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1205" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1205" s="9" t="s">
+        <v>4310</v>
+      </c>
+      <c r="I1205" s="6"/>
+    </row>
+    <row r="1206" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1206" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1206" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1206" s="7" t="s">
+        <v>4303</v>
+      </c>
+      <c r="D1206" s="7" t="s">
+        <v>4324</v>
+      </c>
+      <c r="E1206" s="20">
+        <v>3.52</v>
+      </c>
+      <c r="F1206" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="G1206" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1206" s="9" t="s">
+        <v>4307</v>
+      </c>
+      <c r="I1206" s="6"/>
+    </row>
+    <row r="1207" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1207" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1207" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1207" s="7" t="s">
+        <v>4299</v>
+      </c>
+      <c r="D1207" s="7" t="s">
+        <v>4325</v>
+      </c>
+      <c r="E1207" s="20">
+        <v>3.74</v>
+      </c>
+      <c r="F1207" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1207" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1207" s="9" t="s">
+        <v>4311</v>
+      </c>
+      <c r="I1207" s="6"/>
+    </row>
+    <row r="1208" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1208" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1208" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1208" s="7" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D1208" s="7" t="s">
+        <v>4326</v>
+      </c>
+      <c r="E1208" s="20">
+        <v>3.95</v>
+      </c>
+      <c r="F1208" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1208" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="H1208" s="9" t="s">
+        <v>4316</v>
+      </c>
+      <c r="I1208" s="6"/>
+    </row>
+    <row r="1209" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A1209" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1209" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1209" s="7" t="s">
+        <v>4300</v>
+      </c>
+      <c r="D1209" s="7" t="s">
+        <v>4327</v>
+      </c>
+      <c r="E1209" s="20">
+        <v>3.92</v>
+      </c>
+      <c r="F1209" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1209" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1209" s="9" t="s">
+        <v>4317</v>
+      </c>
+      <c r="I1209" s="6"/>
+    </row>
+    <row r="1210" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1210" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1210" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1210" s="7" t="s">
+        <v>4301</v>
+      </c>
+      <c r="D1210" s="7" t="s">
+        <v>4328</v>
+      </c>
+      <c r="E1210" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F1210" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G1210" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1210" s="9" t="s">
+        <v>4308</v>
+      </c>
+      <c r="I1210" s="6"/>
+    </row>
+    <row r="1211" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1211" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1211" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1211" s="7" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D1211" s="7" t="s">
+        <v>4329</v>
+      </c>
+      <c r="E1211" s="20">
+        <v>3.67</v>
+      </c>
+      <c r="F1211" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1211" s="12">
+        <v>4</v>
+      </c>
+      <c r="H1211" s="9" t="s">
+        <v>4312</v>
+      </c>
+      <c r="I1211" s="6"/>
+    </row>
+    <row r="1212" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1212" s="6">
+        <v>34592074</v>
+      </c>
+      <c r="B1212" s="6">
+        <v>12</v>
+      </c>
+      <c r="C1212" s="7" t="s">
+        <v>4305</v>
+      </c>
+      <c r="D1212" s="7" t="s">
+        <v>4330</v>
+      </c>
+      <c r="E1212" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F1212" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="G1212" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H1212" s="9" t="s">
+        <v>4309</v>
+      </c>
+      <c r="I1212" s="6"/>
+    </row>
+    <row r="1213" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1213" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1213" s="6">
+        <v>1</v>
+      </c>
+      <c r="C1213" s="7" t="s">
+        <v>4337</v>
+      </c>
+      <c r="D1213" s="7" t="s">
+        <v>4349</v>
+      </c>
+      <c r="E1213" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F1213" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1213" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1213" s="9" t="s">
+        <v>4362</v>
+      </c>
+      <c r="I1213" s="6"/>
+    </row>
+    <row r="1214" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1214" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1214" s="6">
+        <v>2</v>
+      </c>
+      <c r="C1214" s="7" t="s">
+        <v>4338</v>
+      </c>
+      <c r="D1214" s="7" t="s">
+        <v>4350</v>
+      </c>
+      <c r="E1214" s="20">
+        <v>3.59</v>
+      </c>
+      <c r="F1214" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="G1214" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="H1214" s="9" t="s">
+        <v>4364</v>
+      </c>
+      <c r="I1214" s="6"/>
+    </row>
+    <row r="1215" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1215" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1215" s="6">
+        <v>3</v>
+      </c>
+      <c r="C1215" s="7" t="s">
+        <v>4339</v>
+      </c>
+      <c r="D1215" s="7" t="s">
+        <v>4351</v>
+      </c>
+      <c r="E1215" s="20">
+        <v>3.7</v>
+      </c>
+      <c r="F1215" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1215" s="12">
+        <v>1.35</v>
+      </c>
+      <c r="H1215" s="9" t="s">
+        <v>4365</v>
+      </c>
+      <c r="I1215" s="6"/>
+    </row>
+    <row r="1216" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1216" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1216" s="6">
+        <v>4</v>
+      </c>
+      <c r="C1216" s="7" t="s">
+        <v>4340</v>
+      </c>
+      <c r="D1216" s="7" t="s">
+        <v>4352</v>
+      </c>
+      <c r="E1216" s="20">
+        <v>3.57</v>
+      </c>
+      <c r="F1216" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1216" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1216" s="9" t="s">
+        <v>4359</v>
+      </c>
+      <c r="I1216" s="6"/>
+    </row>
+    <row r="1217" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1217" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1217" s="6">
+        <v>5</v>
+      </c>
+      <c r="C1217" s="7" t="s">
+        <v>4341</v>
+      </c>
+      <c r="D1217" s="7" t="s">
+        <v>4353</v>
+      </c>
+      <c r="E1217" s="20">
+        <v>3.89</v>
+      </c>
+      <c r="F1217" s="12">
+        <v>4</v>
+      </c>
+      <c r="G1217" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1217" s="9" t="s">
+        <v>4360</v>
+      </c>
+      <c r="I1217" s="6"/>
+    </row>
+    <row r="1218" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1218" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1218" s="6">
+        <v>6</v>
+      </c>
+      <c r="C1218" s="7" t="s">
+        <v>4342</v>
+      </c>
+      <c r="D1218" s="7" t="s">
+        <v>4354</v>
+      </c>
+      <c r="E1218" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="F1218" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1218" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H1218" s="9" t="s">
+        <v>4366</v>
+      </c>
+      <c r="I1218" s="6"/>
+    </row>
+    <row r="1219" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1219" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1219" s="6">
+        <v>7</v>
+      </c>
+      <c r="C1219" s="7" t="s">
+        <v>4343</v>
+      </c>
+      <c r="D1219" s="7" t="s">
+        <v>4355</v>
+      </c>
+      <c r="E1219" s="20">
+        <v>3.81</v>
+      </c>
+      <c r="F1219" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="G1219" s="12">
+        <v>4.55</v>
+      </c>
+      <c r="H1219" s="9" t="s">
+        <v>4363</v>
+      </c>
+      <c r="I1219" s="6"/>
+    </row>
+    <row r="1220" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1220" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1220" s="6">
+        <v>8</v>
+      </c>
+      <c r="C1220" s="7" t="s">
+        <v>4344</v>
+      </c>
+      <c r="D1220" s="7" t="s">
+        <v>4356</v>
+      </c>
+      <c r="E1220" s="20">
+        <v>3.68</v>
+      </c>
+      <c r="F1220" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1220" s="12">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1220" s="9" t="s">
+        <v>4367</v>
+      </c>
+      <c r="I1220" s="6"/>
+    </row>
+    <row r="1221" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1221" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1221" s="6">
+        <v>9</v>
+      </c>
+      <c r="C1221" s="7" t="s">
+        <v>4345</v>
+      </c>
+      <c r="D1221" s="7" t="s">
+        <v>4357</v>
+      </c>
+      <c r="E1221" s="20">
+        <v>3.72</v>
+      </c>
+      <c r="F1221" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G1221" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1221" s="9" t="s">
+        <v>4368</v>
+      </c>
+      <c r="I1221" s="6"/>
+    </row>
+    <row r="1222" spans="1:9" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A1222" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1222" s="6">
+        <v>10</v>
+      </c>
+      <c r="C1222" s="7" t="s">
+        <v>4346</v>
+      </c>
+      <c r="D1222" s="7" t="s">
+        <v>3791</v>
+      </c>
+      <c r="E1222" s="20">
+        <v>3.51</v>
+      </c>
+      <c r="F1222" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="G1222" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="H1222" s="9" t="s">
+        <v>4361</v>
+      </c>
+      <c r="I1222" s="6"/>
+    </row>
+    <row r="1223" spans="1:9" ht="84" x14ac:dyDescent="0.25">
+      <c r="A1223" s="6">
+        <v>28792273</v>
+      </c>
+      <c r="B1223" s="6">
+        <v>11</v>
+      </c>
+      <c r="C1223" s="7" t="s">
+        <v>4347</v>
+      </c>
+      <c r="D1223" s="7" t="s">
+        <v>4358</v>
+      </c>
+      <c r="E1223" s="20">
+        <v>3.61</v>
+      </c>
+      <c r="F1223" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1223" s="12">
+        <v>4.45</v>
+      </c>
+      <c r="H1223" s="9" t="s">
+        <v>4369</v>
+      </c>
+      <c r="I1223" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A584C-1BDD-4E0C-B205-4BA425FBE20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4C4211-AD29-4E0A-AC23-2E61B7EE9720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="4451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="4483">
   <si>
     <t>No</t>
   </si>
@@ -14595,6 +14595,124 @@
         <charset val="161"/>
       </rPr>
       <t xml:space="preserve"> Το πιο επιτυχημένο και άμεσα αναγνωρίσιμο τραγούδι του album. Το “rhythm of love” μετατρέπει την ερωτική έλξη σε σωματικό ρυθμό, και η μπάντα χτίζει γύρω από αυτή την ιδέα ένα γυαλισμένο, εξαιρετικά hook-driven melodic hard-rock single. Η κιθάρα έχει sleek late-’80s χαρακτήρα, οι harmony vocals δίνουν πλάτος και το refrain είναι σχεδιασμένο για radio και arena sing-along. Έγινε το πρώτο single του δίσκου και έφτασε στο No. 6 του Billboard Mainstream Rock chart, αποτελώντας το μεγαλύτερο αμερικανικό hit του album. Η επιτυχία του δεν είναι τυχαία, είναι Scorpions σε σχεδόν τέλεια ισορροπία μεταξύ hard-rock έντασης και pop αμεσότητας.</t>
+    </r>
+  </si>
+  <si>
+    <t>RCA Victor – RCLP 20164. Ελληνική έκδοση/επανέκδοση (Greece) του 1980. Η διανομή και κατασκευή έγιναν στην Ελλάδα από την Minos Matsas &amp; Son Co. Ltd.. Το εξώφυλλο είναι ματ (Matte sleeve), ενώ στα στοιχεία σημειώνεται η προηγούμενη κυκλοφορία (Previously releashed as AFL1-4225)</t>
+  </si>
+  <si>
+    <t>Το Virgin Killer κυκλοφόρησε αρχικά το 1976 και αποτελεί το τέταρτο στούντιο άλμπουμ των Scorpions, σηματοδοτώντας την καθιέρωση του χαρακτηριστικού, επιθετικού και μελωδικού hard-rock ήχου τους. Η παραγωγή ανήκει στον Dieter Dierks. Στη σύνθεση συμμετέχουν οι Klaus Meine, Rudolf Schenker, Ulrich Roth (ο οποίος ερμηνεύει και στα "Hell Cat" και "Polar Nights"), Francis Buchholz και Rudy Lenners. Η ελληνική έκδοση της RCA / Minos Matsas αποτελεί μια χαρακτηριστική τοπική κοπή της εποχής.</t>
+  </si>
+  <si>
+    <t>Pictured Life</t>
+  </si>
+  <si>
+    <t>Catch Your Train</t>
+  </si>
+  <si>
+    <t>In Your Park</t>
+  </si>
+  <si>
+    <t>Backstage Queen</t>
+  </si>
+  <si>
+    <t>Virgin Killer</t>
+  </si>
+  <si>
+    <t>Hell Cat</t>
+  </si>
+  <si>
+    <t>Crying Days</t>
+  </si>
+  <si>
+    <t>Polar Nights</t>
+  </si>
+  <si>
+    <t>Yellow Raven</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [German Hard Rock, Psychedelic Metal, Neo-Classical Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/oR2RQajyRxjVnURlqCdYKWLxkWYoILZL6ZgyHc47Qjc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTc5NDk2/NDQtMTc0NzU4MDU0/MS0zMzI4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/7949644-Scorpions-Virgin-Killer</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Heavy Rock, German Hard Rock, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Fast Riff Rock, Proto-Speed Metal, Arena Rock precursor]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Melodic Hard Rock, Moody Rock Ballad, Guitar-driven Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Riff Rock, Sleaze Rock precursor, Boogie Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Psychedelic Rock [Dark Heavy Rock, Neo-Classical Guitar Rock, Progressive Hard Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Hard Rock, Guitar Showcase, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Melodic Heavy Rock, Atmospheric Rock, Guitar Ballad]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Psychedelic Rock [Neo-Classical Metal, Spacey Heavy Rock, Guitar Epic]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Hard Rock [Eastern-tinged Rock, Acid Rock, Atmospheric Ballad]</t>
+  </si>
+  <si>
+    <t>Πιο μελαγχολικό και λιγότερο επιθετικό, με το “park” να λειτουργεί ως τόπος συνάντησης, μνήμης και ιδιωτικής απομόνωσης. Η μπάντα χαμηλώνει την ταχύτητα και αφήνει τον Meine να τραγουδήσει με πιο ευάλωτο τρόπο. Το κιθαριστικό παίξιμο παραμένει ουσιαστικό, όμως δεν κυνηγά την τεχνική κορύφωση· χτίζει ατμόσφαιρα και υποστηρίζει τη μελωδική γραμμή. Είναι από τις πιο “κλασικά Scorpions” μπαλαντικές στιγμές του early catalog, πριν οι power ballads τους πάρουν arena διαστάσεις. Αν και λιγότερο εντυπωσιακό από τα μεγάλα Roth tracks της B πλευράς, προσφέρει σημαντική δυναμική αλλαγή.</t>
+  </si>
+  <si>
+    <t>Από τις πρώτες πραγματικές proto-speed-metal στιγμές των Scorpions. Η μεταφορά του “catch your train” είναι επείγουσα, πάρε την ευκαιρία σου, φύγε, κινήσου προτού είναι αργά. Τα drums και η rhythm guitar δημιουργούν διαρκή forward motion, ενώ η lead κιθάρα του Roth δίνει εκρηκτικές, σχεδόν neoclassical φράσεις. Δεν είναι speed metal με την τυποποιημένη 1980s έννοια, όμως η ταχύτητα, η κοφτή δομή και η κιθαριστική επιθετικότητα εξηγούν γιατί το track ακούγεται ακόμη τόσο φρέσκο. Είναι ένα από τα tracks που ξεχωρίζουν συστηματικά στις κριτικές του δίσκου και ένα από τα καλύτερα early Scorpions rockers.</t>
+  </si>
+  <si>
+    <t>Σκληρό, σύντομο rock ’n’ roll τραγούδι με backstage setting και swagger. Η “queen” είναι η φιγούρα που κινείται γύρω από τη σκηνή, τη φήμη και την πρόσβαση σε μουσικούς , ένα rock-culture archetype της εποχής. Οι Scorpions δεν επιδιώκουν εδώ λογοτεχνικό βάθος, το riff, το groove και η ενέργεια είναι το κύριο ζητούμενο. Η κιθάρα του Roth κρατά bluesy bite και το rhythm section δίνει boogie υποδομή. Είναι ένα σωστό, άμεσο hard-rock cut, λιγότερο ξεχωριστό από τα epic tracks αλλά πολύ σωστά τοποθετημένο πριν το σκοτεινότερο title track.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο τραγούδι είναι μουσικά πολύ πιο σύνθετο από την εικόνα που έχει επισκιάσει τον τίτλο του. Το “virgin killer” αναφέρεται μεταφορικά στον χρόνο, η αθωότητα και η νεότητα “σκοτώνονται” αναπόφευκτα από τη φθορά του χρόνου. Η σύνθεση είναι σκοτεινή, με guitar motifs που πλησιάζουν το νεοκλασικό hard rock και ατμόσφαιρα που έχει σχεδόν progressive βάθος. Ο Uli Jon Roth δίνει πιο περίτεχνα leads, ενώ το rhythm section αποφεύγει την απλή straight-ahead φόρμα. Σημαντικό, η πρωτότυπη οπτική συσκευασία δημιούργησε δικαιολογημένη και μακροχρόνια κατακραυγή· ο μουσικός τίτλος, όμως, έχει διαφορετική θεματική σημασία.</t>
+  </si>
+  <si>
+    <t>Γρήγορο και επιθετικό, με τον τίτλο να υποδηλώνει επικίνδυνη, ανεξέλεγκτη παρουσία. Η κιθάρα του Roth κινείται πιο νευρικά, με flashes τεχνικής που θα ενέπνεαν αργότερα neoclassical metal guitarists, και ο Meine ακολουθεί με αυξημένη ένταση. Είναι από τα πιο metal-forward tracks του LP, λιγότερη bluesy χαλάρωση, περισσότερο riff attack και γρήγορη κλιμάκωση. Στο sequencing λειτουργεί ως B-side restart, επαναφέροντας αμέσως την αδρεναλίνη μετά το σκοτεινό title track.</t>
+  </si>
+  <si>
+    <t>Melodic heavy-rock ballad με τον τίτλο να περιγράφει εποχές απώλειας και συναισθηματικής απογοήτευσης. Η μπάντα συνδυάζει πιο ήρεμα verses με κιθαριστική ανάπτυξη που δεν επιτρέπει στο τραγούδι να γίνει απλή μπαλάντα. Η κιθάρα έχει psychedelic χρώμα, ενώ το vocal κρατά δραματικότητα χωρίς να μετατρέπεται σε υπερβολή. Είναι μια από τις πιο ισορροπημένες συνθέσεις, έχει μελωδία, συναίσθημα και αρκετή ηλεκτρική ένταση. Κάνει τη B πλευρά πιο πολυδιάστατη και προετοιμάζει την είσοδο στο μεγάλο κιθαριστικό epic.</t>
+  </si>
+  <si>
+    <r>
+      <t>A1. Pictured Life:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Δυνατό opening track με άμεσο hard-rock riff, καθαρό chorus και κιθαριστική μελωδία που αποκαλύπτει αμέσως τη μοναδική φωνή του Uli Jon Roth. Η “pictured life” είναι μια ζωή μεταφρασμένη σε εικόνες, κάτι που μοιάζει πλήρες ή όμορφο από μακριά, αλλά μπορεί να είναι επιφανειακό, παγιδευμένο ή εξιδανικευμένο. Ο Klaus Meine τραγουδά ακόμη με πιο raw, νεανική χροιά σε σχέση με την 1980s περίοδο, ενώ η μπάντα ισορροπεί ανάμεσα σε classic hard rock και ένα πιο ευρωπαϊκό, λυρικό metal στοιχείο. Είναι από τα πιο συμπυκνωμένα και επιτυχημένα τραγούδια του δίσκου , γρήγορο, μελωδικό και απολύτως χαρακτηριστικό της περιόδου Roth.</t>
+    </r>
+  </si>
+  <si>
+    <t>Η κορυφαία στιγμή του album και ίσως το απόλυτο Uli Jon Roth-era Scorpions track. Η “polar night” είναι εικόνα ακραίου σκοταδιού, απομόνωσης και ψυχρού, εξωτικού τοπίου , και η μουσική αντιστοιχεί με σκοτεινά riffs, ατμοσφαιρικά περάσματα και ένα από τα πιο χαρακτηριστικά guitar solos του Roth. Το κομμάτι ενοποιεί heavy metal, psychedelic rock και νεοκλασική μελωδική λογική χωρίς να γίνεται επίδειξη δεξιοτεχνίας. Η διάρκεια του επιτρέπει πραγματική ανάπτυξη, αλλά η σύνθεση παραμένει σαφής και memorable. Αν κάποιος θέλει να καταλάβει γιατί ο Uli Jon Roth θεωρείται προάγγελος του neo-classical metal, αυτό είναι το τραγούδι. Οι κριτικές το ξεχωρίζουν σταθερά ως μεγάλο deep cut της μπάντας.</t>
+  </si>
+  <si>
+    <r>
+      <t>B4. Yellow Raven:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Ατμοσφαιρικό, σχεδόν acid-rock κλείσιμο. Το “yellow raven” είναι μια ονειρική, ασυνήθιστη εικόνα , ένα πουλί ως σύμβολο αστάθειας, παράξενου οράματος ή πνευματικής αναζήτησης. Η μουσική χρησιμοποιεί ανατολίτικα/εξωτικά χρώματα, με κιθάρα που προτιμά ατμόσφαιρα από ωμή ταχύτητα. Ο Meine τραγουδά με ήπια, slightly mystical χροιά και το track λειτουργεί σαν υποχώρηση μετά την ένταση του “Polar Nights”. Δεν επιχειρεί να κλείσει τον δίσκο με ένα τελευταίο anthem· τον αφήνει να διαλυθεί σε αίσθηση και χρώμα. Αυτό το κάνει ιδιαίτερα ταιριαστό finale για την πιο ψυχεδελική και περιπετειώδη περίοδο των Scorpions.</t>
     </r>
   </si>
 </sst>
@@ -15164,7 +15282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -19303,6 +19421,38 @@
       </c>
       <c r="J129" s="7" t="s">
         <v>4421</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>4390</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D130" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E130" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>4462</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>4452</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>4451</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>4464</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>4463</v>
       </c>
     </row>
   </sheetData>
@@ -19564,6 +19714,8 @@
     <hyperlink ref="J128" r:id="rId251" xr:uid="{E96F8A50-A558-4AA1-834F-8D81423906C9}"/>
     <hyperlink ref="I129" r:id="rId252" xr:uid="{EFAA277E-33BA-4E31-8F6C-3D44B6838AB5}"/>
     <hyperlink ref="J129" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
+    <hyperlink ref="J130" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
+    <hyperlink ref="I130" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19571,7 +19723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1241"/>
+  <dimension ref="A1:I1250"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -53110,7 +53262,7 @@
         <v>3.82</v>
       </c>
       <c r="F1234" s="11">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="G1234" s="11">
         <v>4.5999999999999996</v>
@@ -53310,6 +53462,253 @@
         <v>4449</v>
       </c>
       <c r="I1241" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1242" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1242" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1242" s="4" t="s">
+        <v>4453</v>
+      </c>
+      <c r="D1242" s="4" t="s">
+        <v>4465</v>
+      </c>
+      <c r="E1242" s="14">
+        <v>4.01</v>
+      </c>
+      <c r="F1242" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1242" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1242" s="17" t="s">
+        <v>4480</v>
+      </c>
+      <c r="I1242" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1243" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1243" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1243" s="4" t="s">
+        <v>4454</v>
+      </c>
+      <c r="D1243" s="4" t="s">
+        <v>4466</v>
+      </c>
+      <c r="E1243" s="14">
+        <v>3.93</v>
+      </c>
+      <c r="F1243" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1243" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="H1243" s="6" t="s">
+        <v>4475</v>
+      </c>
+      <c r="I1243" s="3"/>
+    </row>
+    <row r="1244" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1244" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1244" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1244" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D1244" s="4" t="s">
+        <v>4467</v>
+      </c>
+      <c r="E1244" s="14">
+        <v>3.72</v>
+      </c>
+      <c r="F1244" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1244" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1244" s="6" t="s">
+        <v>4474</v>
+      </c>
+      <c r="I1244" s="3"/>
+    </row>
+    <row r="1245" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1245" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1245" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1245" s="4" t="s">
+        <v>4456</v>
+      </c>
+      <c r="D1245" s="4" t="s">
+        <v>4468</v>
+      </c>
+      <c r="E1245" s="14">
+        <v>3.47</v>
+      </c>
+      <c r="F1245" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1245" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1245" s="6" t="s">
+        <v>4476</v>
+      </c>
+      <c r="I1245" s="3"/>
+    </row>
+    <row r="1246" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1246" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1246" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1246" s="4" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D1246" s="4" t="s">
+        <v>4469</v>
+      </c>
+      <c r="E1246" s="14">
+        <v>3.56</v>
+      </c>
+      <c r="F1246" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1246" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1246" s="6" t="s">
+        <v>4477</v>
+      </c>
+      <c r="I1246" s="3"/>
+    </row>
+    <row r="1247" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1247" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1247" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1247" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="D1247" s="4" t="s">
+        <v>4470</v>
+      </c>
+      <c r="E1247" s="14">
+        <v>3.08</v>
+      </c>
+      <c r="F1247" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1247" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1247" s="6" t="s">
+        <v>4478</v>
+      </c>
+      <c r="I1247" s="3"/>
+    </row>
+    <row r="1248" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1248" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1248" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1248" s="4" t="s">
+        <v>4459</v>
+      </c>
+      <c r="D1248" s="4" t="s">
+        <v>4471</v>
+      </c>
+      <c r="E1248" s="14">
+        <v>3.66</v>
+      </c>
+      <c r="F1248" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1248" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1248" s="6" t="s">
+        <v>4479</v>
+      </c>
+      <c r="I1248" s="3"/>
+    </row>
+    <row r="1249" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1249" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1249" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1249" s="4" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D1249" s="4" t="s">
+        <v>4472</v>
+      </c>
+      <c r="E1249" s="14">
+        <v>3.49</v>
+      </c>
+      <c r="F1249" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G1249" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1249" s="6" t="s">
+        <v>4481</v>
+      </c>
+      <c r="I1249" s="3"/>
+    </row>
+    <row r="1250" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1250" s="3">
+        <v>7949644</v>
+      </c>
+      <c r="B1250" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1250" s="4" t="s">
+        <v>4461</v>
+      </c>
+      <c r="D1250" s="4" t="s">
+        <v>4473</v>
+      </c>
+      <c r="E1250" s="14">
+        <v>3.68</v>
+      </c>
+      <c r="F1250" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1250" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="H1250" s="17" t="s">
+        <v>4482</v>
+      </c>
+      <c r="I1250" s="3" t="s">
         <v>173</v>
       </c>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4C4211-AD29-4E0A-AC23-2E61B7EE9720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B237BA1-8D1D-4FFC-8AB8-BAA9FDA3D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="4483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="4518">
   <si>
     <t>No</t>
   </si>
@@ -14601,9 +14601,6 @@
     <t>RCA Victor – RCLP 20164. Ελληνική έκδοση/επανέκδοση (Greece) του 1980. Η διανομή και κατασκευή έγιναν στην Ελλάδα από την Minos Matsas &amp; Son Co. Ltd.. Το εξώφυλλο είναι ματ (Matte sleeve), ενώ στα στοιχεία σημειώνεται η προηγούμενη κυκλοφορία (Previously releashed as AFL1-4225)</t>
   </si>
   <si>
-    <t>Το Virgin Killer κυκλοφόρησε αρχικά το 1976 και αποτελεί το τέταρτο στούντιο άλμπουμ των Scorpions, σηματοδοτώντας την καθιέρωση του χαρακτηριστικού, επιθετικού και μελωδικού hard-rock ήχου τους. Η παραγωγή ανήκει στον Dieter Dierks. Στη σύνθεση συμμετέχουν οι Klaus Meine, Rudolf Schenker, Ulrich Roth (ο οποίος ερμηνεύει και στα "Hell Cat" και "Polar Nights"), Francis Buchholz και Rudy Lenners. Η ελληνική έκδοση της RCA / Minos Matsas αποτελεί μια χαρακτηριστική τοπική κοπή της εποχής.</t>
-  </si>
-  <si>
     <t>Pictured Life</t>
   </si>
   <si>
@@ -14713,6 +14710,191 @@
         <charset val="161"/>
       </rPr>
       <t xml:space="preserve"> Ατμοσφαιρικό, σχεδόν acid-rock κλείσιμο. Το “yellow raven” είναι μια ονειρική, ασυνήθιστη εικόνα , ένα πουλί ως σύμβολο αστάθειας, παράξενου οράματος ή πνευματικής αναζήτησης. Η μουσική χρησιμοποιεί ανατολίτικα/εξωτικά χρώματα, με κιθάρα που προτιμά ατμόσφαιρα από ωμή ταχύτητα. Ο Meine τραγουδά με ήπια, slightly mystical χροιά και το track λειτουργεί σαν υποχώρηση μετά την ένταση του “Polar Nights”. Δεν επιχειρεί να κλείσει τον δίσκο με ένα τελευταίο anthem· τον αφήνει να διαλυθεί σε αίσθηση και χρώμα. Αυτό το κάνει ιδιαίτερα ταιριαστό finale για την πιο ψυχεδελική και περιπετειώδη περίοδο των Scorpions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Best Of Scorpions</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/EpmN1IZ4YfCwcfotEhPbC1p_8S60JJXiHd2uJQarVmo/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3MDUw/NjMtMTQzMTg4OTEz/My03NTc2LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2705063-Scorpions-Best-Of-Scorpions</t>
+  </si>
+  <si>
+    <t>RCA – PL 28356, RCA – RCLP 20141. Ελληνική έκδοση (Greece) του 1979. Η διανομή και κατασκευή έγιναν στην Ελλάδα από την Minos Matsas &amp; Son Co. Ltd., ενώ η κοπή/τύπωση πραγματοποιήθηκε από την Fabelsound. Στις σημειώσεις αναφέρεται ως πιθανή αρχική ελληνική έκδοση του 1979 ("Probably this is the original 1979 Greek pressing") χωρίς ράχη ("No spine").</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Virgin Killer κυκλοφόρησε αρχικά το 1976 και αποτελεί το τέταρτο στούντιο άλμπουμ των Scorpions, σηματοδοτώντας την καθιέρωση του χαρακτηριστικού, επιθετικού και μελωδικού hard-rock ήχου τους. Η παραγωγή ανήκει στον Dieter Dierks. Στη σύνθεση συμμετέχουν οι Klaus Meine, Rudolf Schenker, Ulrich Roth (ο οποίος ερμηνεύει και στα "Hell Cat" και "Polar Nights"), Francis Buchholz και Rudy Lenners. Η ελληνική έκδοση της RCA / Minos Matsas αποτελεί μια χαρακτηριστική τοπική κοπή της εποχής.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Best Of Scorpions συγκεντρώνει τις κορυφαίες στιγμές των Scorpions από την "golden era" της δεκαετίας του '70 (εποχή RCA), περιλαμβάνοντας ύμνους όπως τα "Pictured Life", "Robot Man", "In Trance", "Dark Lady", "The Sails Of Charon" και "Virgin Killer". Η ελληνική κοπή της Minos Matsas / Fabelsound αποτελεί μια κλασική, ιστορική τοπική κυκλοφορία της εποχής.</t>
+  </si>
+  <si>
+    <t>Steamrock Fever</t>
+  </si>
+  <si>
+    <t>Robot Man</t>
+  </si>
+  <si>
+    <t>Speedy’s Coming</t>
+  </si>
+  <si>
+    <t>He’s A Woman, She’s A Man</t>
+  </si>
+  <si>
+    <t>In Trance</t>
+  </si>
+  <si>
+    <t>Dark Lady</t>
+  </si>
+  <si>
+    <t>The Sails Of Charon</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Uli Jon Roth Era, German Hard Rock, Psychedelic Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Riff Rock, Proto-Speed Metal, Live Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Heavy Rock, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Blues Rock [Heavy Blues Rock, Early Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Rock ’n’ Roll [Boogie Hard Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Proto-Metal, Fast Riff Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Guitar Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Proto-Speed Metal, Dual-Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Power Ballad precursor, Atmospheric Hard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Heavy Psych, Dark Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Psychedelic Rock [Neo-Classical Metal, Guitar Epic, Proto-Power Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Psychedelic Rock [Dark Hard Rock, Neo-Classical Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο επαναφέρει τη σκοτεινή, progressive πλευρά του 1976 album. Μουσικά, ο τίτλος αφορά τον χρόνο και τη φθορά της αθωότητας, όχι κυριολεκτικά το εξώφυλλο που προκάλεσε δικαιολογημένη και μακροχρόνια κατακραυγή. Η σύνθεση είναι πιο αργή, πιο βαριά και περισσότερο νεοκλασική από τα A-side rockers. Τα guitar motifs του Roth έχουν ελεγχόμενη δραματικότητα, η φωνή του Meine παραμένει μελαγχολική και το συνολικό αποτέλεσμα λειτουργεί ως σκοτεινό τέλος. Δεν είναι το πιο άμεσο track του compilation, αλλά μετά το “The Sails of Charon” προσφέρει ένα σωστό, βαρύ επίλογο αντί για εύκολο hit.</t>
+  </si>
+  <si>
+    <t>Riff-driven hard rock από το Virgin Killer, βασισμένο σε backstage rock ’n’ roll imagery. Η “queen” λειτουργεί ως σύμβολο της νυχτερινής, παρασκηνιακής πλευράς της φήμης, πρόσβαση, επιθυμία, performance και fleeting σχέσεις. Η μπάντα το κρατά απλό και επιθετικό, με boogie groove και lead guitar παρεμβάσεις. Δεν είναι τόσο ξεχωριστό όσο “Pictured Life” ή “The Sails of Charon”, αλλά είναι απαραίτητο για να αποτυπώσει τη σωματική, less cerebral πλευρά της μπάντας. Στην ακολουθία της A πλευράς λειτουργεί σαν αποσυμπίεση πριν το γρήγορο “Speedy’s Coming”.</t>
+  </si>
+  <si>
+    <t>Επιστροφή στο Virgin Killer και σε πιο γρήγορο, guitar-driven hard rock. Ο τίτλος ζωγραφίζει μια επικίνδυνη, ανεξέλεγκτη φιγούρα, ενώ η μουσική ανταποκρίνεται με ένταση και με lead guitar που φέρνει στοιχεία από το μελλοντικό neo-classical metal. Το rhythm section κρατά το τραγούδι κοντά σε tight heavy rock αντί να το αφήσει να γίνει πλήρες jam. Ως τελευταίο track της A πλευράς, λειτουργεί σωστά, ανεβάζει την αδρεναλίνη και προετοιμάζει την πιο βαριά, εμβληματική B πλευρά.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, ψυχεδελικό hard rock από το In Trance. Η “dark lady” είναι μια μυστηριώδης και απειλητική γυναικεία μορφή, ένα ροκ archetype που εδώ παίρνει πιο occult, ατμοσφαιρική διάσταση. Η κιθάρα δημιουργεί shadowy tone και η μπάντα δεν κυνηγά το γρήγορο hook· χτίζει mood. Είναι λιγότερο μελωδικά άμεσο από το “In Trance”, αλλά σημαντικό ως δείγμα της early, πιο σκοτεινής και ψυχεδελικής Scorpions αισθητικής. Στο sequencing είναι σωστά τοποθετημένο, διευρύνει την ατμόσφαιρα πριν την απόλυτη κιθαριστική κορύφωση.</t>
+  </si>
+  <si>
+    <r>
+      <t>B4. The Sails Of Charon:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Η κορυφαία στιγμή της συλλογής και ένα θεμελιώδες proto-neoclassical metal τραγούδι. Ο Χάρων, ο βαρκάρης του Άδη στην ελληνική μυθολογία, δίνει στον τίτλο μυθική και σκοτεινή βαρύτητα, ενώ η μουσική του Roth μετατρέπει αυτή την εικόνα σε περίπλοκο heavy riffing, δραματικές αρμονίες και ένα solo που έχει γίνει σημείο αναφοράς για κιθαρίστες όπως ο Yngwie Malmsteen. Το κομμάτι δεν ακούγεται σαν απλή επίδειξη τεχνικής, η μελωδία, η αίσθηση μοιραίας πορείας και η ένταση της μπάντας το κάνουν πλήρη σύνθεση. Για τη συλλογή, είναι το “must-have” κομμάτι , και πιθανώς ο σημαντικότερος λόγος για να θεωρηθεί το Best Of Scorpions ουσιαστική επισκόπηση της Roth περιόδου.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B2. In Trance: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Η μεγάλη power-ballad precursor στιγμή του 1975. Το “In Trance” δεν είναι ακόμη η stadium power ballad της δεκαετίας του 1980· έχει psychedelic haze, αργή κλιμάκωση, σκοτεινή αίσθηση και κιθαριστικές γραμμές που λειτουργούν σαν υπνωτική έλξη. Ο τίτλος σημαίνει ότι κάποιος βρίσκεται σε έκσταση ή ψυχική αιχμαλωσία, και ο Meine ερμηνεύει τη μελωδία με δραματική αλλά όχι υπερβολική χροιά. Η κιθάρα του Roth κάνει το τραγούδι να αιωρείται ανάμεσα σε blues-rock, heavy psych και πρώιμο metal. Είναι ένα από τα defining tracks των Scorpions, και σωστά εμφανίζεται στην καρδιά της B πλευράς.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B1. He’s A Woman, She’s A Man:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από το Taken by Force, ίσως το πιο καθαρά proto-speed-metal track των Scorpions της δεκαετίας του 1970. Η σύνθεση είναι γρήγορη, με δυνατή rhythm guitar, υψηλές φωνητικές γραμμές και lead guitar που δίνει ένταση χωρίς να χάνει την μελωδική αναγνωρισιμότητα. Οι στίχοι αντανακλούν σεξουαλικά και έμφυλα stereotypes της εποχής και σήμερα ακούγονται ξεπερασμένοι· μουσικά όμως το κομμάτι είναι κομβικό. Ενώνει το hard rock των μέσων ’70s με το speed/power metal που θα αναπτυχθεί αργότερα. Είναι ιδανικό B-side opener και ίσως ένα από τα πιο σημαντικά τραγούδια της συλλογής για την ιστορική εξέλιξη του heavy metal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A5. Speedy’s Coming:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από το Fly to the Rainbow, ένα από τα καθαρότερα proto-metal riffs των πρώιμων Scorpions. Ο “Speedy” είναι ο τύπος που έρχεται γρήγορα, με ταχύτητα και πιθανή απειλή/ανατροπή , η μουσική μεταφράζει αυτή τη δυναμική με driving tempo, κοφτή κιθάρα και προωθητική φωνητική γραμμή. Είναι παλαιότερο από τα υπόλοιπα tracks, όμως δεν ακούγεται ασθενέστερο. Αντίθετα, δείχνει ότι οι σπόροι του heavy sound υπήρχαν ήδη από το 1974. Η παρουσία του είναι σημαντική επειδή η συλλογή περιλαμβάνει μόνο ένα τραγούδι από το Fly to the Rainbow, άρα το “Speedy’s Coming” λειτουργεί ως μοναδικός εκπρόσωπος αυτής της πρώιμης φάσης.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A3. Robot Man:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από το In Trance, το “Robot Man” συνδέει early heavy rock με εικόνες αποξένωσης και μηχανοποίησης. Ο “robot man” είναι ο άνθρωπος που λειτουργεί χωρίς αυτονομία, όπως μηχανή μέσα σε σύστημα. Η μουσική είναι heavy blues rock, με πιο γήινο riff και λιγότερο ατμοσφαιρική ανάπτυξη από τα μεγάλα tracks του In Trance. Αυτό δεν είναι μειονέκτημα, προσφέρει στη συλλογή ένα compact, gritty cut ανάμεσα σε πιο μελωδικά ή σύνθετα τραγούδια. Είναι επίσης σημαντικό επειδή υπενθυμίζει ότι οι Scorpions της περιόδου 1975 δεν ήταν ακόμη μόνο νεοκλασικό guitar vehicle· είχαν ισχυρή blues-rock βάση.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A1. Steamrock Fever:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από το Taken by Force, το “Steamrock Fever” είναι ο ιδανικός τρόπος να ανοίξει μια early-Scorpions συλλογή. Το “steamrock” παραπέμπει στην υπερθερμασμένη, μηχανική ενέργεια του rock, ατμός, ταχύτητα και ένταση. Το riff είναι κοφτό, τα drums πιέζουν μπροστά και η κιθάρα του Uli Jon Roth προσθέτει μελωδικές γραμμές που ανεβάζουν το τραγούδι πάνω από ένα τυπικό boogie rocker. Είναι σύντομο, αποδοτικό και πολύ χαρακτηριστικό του transition των Scorpions από το ψυχεδελικό hard rock προς το πιο σαφές heavy metal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A2. Pictured Life:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από το Virgin Killer, ένα μελωδικό hard-rock track για την επιφανειακή, “εικονισμένη” ζωή , μια εικόνα επιτυχίας ή ευτυχίας που μπορεί να κρύβει ασφυξία. Ο Klaus Meine έχει ακόμη raw χροιά, ενώ ο Roth φέρνει εκείνη τη χαρακτηριστική λυρική κιθαριστική μελωδία που κάνει την early era τόσο διαφορετική από την πιο arena-rock εποχή της δεκαετίας του 1980. Η σύνθεση είναι απλή, αλλά όχι απλοϊκή, καλό riff, καθαρό refrain και κιθάρα που δημιουργεί δικό της αφηγηματικό χώρο. Είναι ένα από τα πιο ισορροπημένα tracks της συλλογής και δείχνει την εμπορική δυνατότητα της μπάντας πριν από τη διεθνή έκρηξή της.</t>
     </r>
   </si>
 </sst>
@@ -15282,7 +15464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -19431,7 +19613,7 @@
         <v>4390</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
       <c r="D130" s="3">
         <v>1976</v>
@@ -19440,19 +19622,51 @@
         <v>3.6</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>4462</v>
+        <v>4461</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>4452</v>
+        <v>4486</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>4451</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>4463</v>
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>4390</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D131" s="3">
+        <v>1979</v>
+      </c>
+      <c r="E131" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>4495</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>4487</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>4485</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>4484</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>4483</v>
       </c>
     </row>
   </sheetData>
@@ -19716,6 +19930,8 @@
     <hyperlink ref="J129" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
     <hyperlink ref="J130" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
     <hyperlink ref="I130" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
+    <hyperlink ref="J131" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
+    <hyperlink ref="I131" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19723,7 +19939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1250"/>
+  <dimension ref="A1:I1261"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -53473,10 +53689,10 @@
         <v>1</v>
       </c>
       <c r="C1242" s="4" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
       <c r="D1242" s="4" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="E1242" s="14">
         <v>4.01</v>
@@ -53488,7 +53704,7 @@
         <v>4.5</v>
       </c>
       <c r="H1242" s="17" t="s">
-        <v>4480</v>
+        <v>4479</v>
       </c>
       <c r="I1242" s="3" t="s">
         <v>173</v>
@@ -53502,10 +53718,10 @@
         <v>2</v>
       </c>
       <c r="C1243" s="4" t="s">
-        <v>4454</v>
+        <v>4453</v>
       </c>
       <c r="D1243" s="4" t="s">
-        <v>4466</v>
+        <v>4465</v>
       </c>
       <c r="E1243" s="14">
         <v>3.93</v>
@@ -53517,7 +53733,7 @@
         <v>4.45</v>
       </c>
       <c r="H1243" s="6" t="s">
-        <v>4475</v>
+        <v>4474</v>
       </c>
       <c r="I1243" s="3"/>
     </row>
@@ -53529,10 +53745,10 @@
         <v>3</v>
       </c>
       <c r="C1244" s="4" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
       <c r="D1244" s="4" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
       <c r="E1244" s="14">
         <v>3.72</v>
@@ -53544,7 +53760,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
       <c r="I1244" s="3"/>
     </row>
@@ -53556,10 +53772,10 @@
         <v>4</v>
       </c>
       <c r="C1245" s="4" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="D1245" s="4" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
       <c r="E1245" s="14">
         <v>3.47</v>
@@ -53571,7 +53787,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1245" s="6" t="s">
-        <v>4476</v>
+        <v>4475</v>
       </c>
       <c r="I1245" s="3"/>
     </row>
@@ -53583,10 +53799,10 @@
         <v>5</v>
       </c>
       <c r="C1246" s="4" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
       <c r="D1246" s="4" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
       <c r="E1246" s="14">
         <v>3.56</v>
@@ -53598,7 +53814,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1246" s="6" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
       <c r="I1246" s="3"/>
     </row>
@@ -53610,10 +53826,10 @@
         <v>6</v>
       </c>
       <c r="C1247" s="4" t="s">
-        <v>4458</v>
+        <v>4457</v>
       </c>
       <c r="D1247" s="4" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
       <c r="E1247" s="14">
         <v>3.08</v>
@@ -53625,7 +53841,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1247" s="6" t="s">
-        <v>4478</v>
+        <v>4477</v>
       </c>
       <c r="I1247" s="3"/>
     </row>
@@ -53637,10 +53853,10 @@
         <v>7</v>
       </c>
       <c r="C1248" s="4" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="D1248" s="4" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
       <c r="E1248" s="14">
         <v>3.66</v>
@@ -53652,7 +53868,7 @@
         <v>4.5</v>
       </c>
       <c r="H1248" s="6" t="s">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="I1248" s="3"/>
     </row>
@@ -53664,10 +53880,10 @@
         <v>8</v>
       </c>
       <c r="C1249" s="4" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
       <c r="D1249" s="4" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
       <c r="E1249" s="14">
         <v>3.49</v>
@@ -53679,7 +53895,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1249" s="6" t="s">
-        <v>4481</v>
+        <v>4480</v>
       </c>
       <c r="I1249" s="3"/>
     </row>
@@ -53691,10 +53907,10 @@
         <v>9</v>
       </c>
       <c r="C1250" s="4" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="D1250" s="4" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
       <c r="E1250" s="14">
         <v>3.68</v>
@@ -53706,11 +53922,322 @@
         <v>4.55</v>
       </c>
       <c r="H1250" s="17" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="I1250" s="3" t="s">
         <v>173</v>
       </c>
+    </row>
+    <row r="1251" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1251" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1251" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1251" s="4" t="s">
+        <v>4488</v>
+      </c>
+      <c r="D1251" s="4" t="s">
+        <v>4496</v>
+      </c>
+      <c r="E1251" s="14">
+        <v>3.83</v>
+      </c>
+      <c r="F1251" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1251" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1251" s="17" t="s">
+        <v>4516</v>
+      </c>
+      <c r="I1251" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1252" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1252" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1252" s="4" t="s">
+        <v>4452</v>
+      </c>
+      <c r="D1252" s="4" t="s">
+        <v>4497</v>
+      </c>
+      <c r="E1252" s="14">
+        <v>4.01</v>
+      </c>
+      <c r="F1252" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1252" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1252" s="17" t="s">
+        <v>4517</v>
+      </c>
+      <c r="I1252" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1253" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1253" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1253" s="4" t="s">
+        <v>4489</v>
+      </c>
+      <c r="D1253" s="4" t="s">
+        <v>4498</v>
+      </c>
+      <c r="E1253" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="F1253" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1253" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1253" s="17" t="s">
+        <v>4515</v>
+      </c>
+      <c r="I1253" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1254" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1254" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1254" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D1254" s="4" t="s">
+        <v>4499</v>
+      </c>
+      <c r="E1254" s="14">
+        <v>3.47</v>
+      </c>
+      <c r="F1254" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1254" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1254" s="6" t="s">
+        <v>4508</v>
+      </c>
+      <c r="I1254" s="3"/>
+    </row>
+    <row r="1255" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1255" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1255" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1255" s="4" t="s">
+        <v>4490</v>
+      </c>
+      <c r="D1255" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="E1255" s="14">
+        <v>3.89</v>
+      </c>
+      <c r="F1255" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1255" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="H1255" s="17" t="s">
+        <v>4514</v>
+      </c>
+      <c r="I1255" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1256" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1256" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1256" s="4" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D1256" s="4" t="s">
+        <v>4501</v>
+      </c>
+      <c r="E1256" s="14">
+        <v>3.08</v>
+      </c>
+      <c r="F1256" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1256" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1256" s="6" t="s">
+        <v>4509</v>
+      </c>
+      <c r="I1256" s="3"/>
+    </row>
+    <row r="1257" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1257" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1257" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1257" s="4" t="s">
+        <v>4491</v>
+      </c>
+      <c r="D1257" s="4" t="s">
+        <v>4502</v>
+      </c>
+      <c r="E1257" s="14">
+        <v>3.89</v>
+      </c>
+      <c r="F1257" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1257" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="H1257" s="17" t="s">
+        <v>4513</v>
+      </c>
+      <c r="I1257" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1258" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1258" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1258" s="4" t="s">
+        <v>4492</v>
+      </c>
+      <c r="D1258" s="4" t="s">
+        <v>4503</v>
+      </c>
+      <c r="E1258" s="14">
+        <v>4.21</v>
+      </c>
+      <c r="F1258" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G1258" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1258" s="17" t="s">
+        <v>4512</v>
+      </c>
+      <c r="I1258" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1259" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1259" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1259" s="4" t="s">
+        <v>4493</v>
+      </c>
+      <c r="D1259" s="4" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E1259" s="14">
+        <v>3.85</v>
+      </c>
+      <c r="F1259" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1259" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="H1259" s="6" t="s">
+        <v>4510</v>
+      </c>
+      <c r="I1259" s="3"/>
+    </row>
+    <row r="1260" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1260" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1260" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1260" s="4" t="s">
+        <v>4494</v>
+      </c>
+      <c r="D1260" s="4" t="s">
+        <v>4505</v>
+      </c>
+      <c r="E1260" s="14">
+        <v>4.28</v>
+      </c>
+      <c r="F1260" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1260" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1260" s="17" t="s">
+        <v>4511</v>
+      </c>
+      <c r="I1260" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1261" s="3">
+        <v>2705063</v>
+      </c>
+      <c r="B1261" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1261" s="4" t="s">
+        <v>4456</v>
+      </c>
+      <c r="D1261" s="4" t="s">
+        <v>4506</v>
+      </c>
+      <c r="E1261" s="14">
+        <v>3.56</v>
+      </c>
+      <c r="F1261" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1261" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1261" s="6" t="s">
+        <v>4507</v>
+      </c>
+      <c r="I1261" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B237BA1-8D1D-4FFC-8AB8-BAA9FDA3D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CA8D36-47E5-4DC8-8BB3-0C3AF351CAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="4518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="4596">
   <si>
     <t>No</t>
   </si>
@@ -14897,12 +14897,305 @@
       <t xml:space="preserve"> Από το Virgin Killer, ένα μελωδικό hard-rock track για την επιφανειακή, “εικονισμένη” ζωή , μια εικόνα επιτυχίας ή ευτυχίας που μπορεί να κρύβει ασφυξία. Ο Klaus Meine έχει ακόμη raw χροιά, ενώ ο Roth φέρνει εκείνη τη χαρακτηριστική λυρική κιθαριστική μελωδία που κάνει την early era τόσο διαφορετική από την πιο arena-rock εποχή της δεκαετίας του 1980. Η σύνθεση είναι απλή, αλλά όχι απλοϊκή, καλό riff, καθαρό refrain και κιθάρα που δημιουργεί δικό της αφηγηματικό χώρο. Είναι ένα από τα πιο ισορροπημένα tracks της συλλογής και δείχνει την εμπορική δυνατότητα της μπάντας πριν από τη διεθνή έκρηξή της.</t>
     </r>
   </si>
+  <si>
+    <t>Vertigo – 359 363-7, Mercury – 359 363-7, Universal Music Recordings – 359 363-7 (καθώς και οι αντίστοικοι barcode κωδικοί 00602435936376). Παγκόσμια έκδοση (Worldwide) διπλού βινυλίου (2 x LP), Remastered, κυκλοφορία 8 Νοεμβρίου 2024.</t>
+  </si>
+  <si>
+    <t>Aphrodite's Child</t>
+  </si>
+  <si>
+    <t>666 (The Apocalypse Of John 13/18)</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/31841081-Aphrodites-Child-666-The-Apocalypse-Of-John-1318-</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/L3Av1rUDSnivvdCrtRzdfFLcIM-Vkg_G0CnhgXxcIwc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMxODQx/MDgxLTE3Mzg1NzU5/MzAtNDQ3Ni5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>The System</t>
+  </si>
+  <si>
+    <t>Babylon</t>
+  </si>
+  <si>
+    <t>Loud, Loud, Loud</t>
+  </si>
+  <si>
+    <t>The Four Horsemen</t>
+  </si>
+  <si>
+    <t>The Lamb</t>
+  </si>
+  <si>
+    <t>The Seventh Seal</t>
+  </si>
+  <si>
+    <t>Aegean Sea</t>
+  </si>
+  <si>
+    <t>Seven Bowls</t>
+  </si>
+  <si>
+    <t>The Wakening Beast</t>
+  </si>
+  <si>
+    <t>Lament</t>
+  </si>
+  <si>
+    <t>The Marching Beast</t>
+  </si>
+  <si>
+    <t>The Battle Of The Locusts</t>
+  </si>
+  <si>
+    <t>Do It</t>
+  </si>
+  <si>
+    <t>Tribulation</t>
+  </si>
+  <si>
+    <t>Ofis</t>
+  </si>
+  <si>
+    <t>Seven Trumpets</t>
+  </si>
+  <si>
+    <t>Altamont</t>
+  </si>
+  <si>
+    <t>The Wedding Of The Lamb</t>
+  </si>
+  <si>
+    <t>The Capture Of The Beast</t>
+  </si>
+  <si>
+    <t>∞ (Infinity)</t>
+  </si>
+  <si>
+    <t>Hic Et Nunc</t>
+  </si>
+  <si>
+    <t>All The Seats Were Occupied</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Concept Album, Experimental Rock, Art Rock, Avant-Prog, Jazz Rock]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Concept Overture, Sound Collage, Apocalyptic Intro]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Psychedelic Pop, Art Rock, Apocalyptic Rock]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Progressive Rock [Choral Rock, Ritualistic Psych, Art Pop]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Dark Prog, Psychedelic Rock, Proto-Metal]</t>
+  </si>
+  <si>
+    <t>Psychedelic Rock, Progressive Rock [Psychedelic Pop, Baroque Pop, Art Rock]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Apocalyptic Interlude, Sound Design, Concept Piece]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Greek/Mediterranean Prog, Art Rock, Instrumental Mood Piece]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Apocalyptic Sound Collage, Concept Interlude]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Psychedelic Rock [Theatre Rock, Sound Effect Interlude]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Dark Ballad, Melodic Prog, Greek-inflected Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Experimental Rock [March-like Art Rock, Apocalyptic Procession]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Psychedelic Rock [Noise Collage, Apocalyptic Interlude]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Psychedelic Rock [Garage Rock, Proto-Punk, Acid Rock]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Brief Concept Transition, Sound Collage]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Dark Psychedelic Rock, Rhythm Rock, Vocal Character Piece]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Sound Collage [Miniature Interlude, Concept Fragment]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Apocalyptic Fanfare, Sound Design]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Dark Art Rock, Counterculture Critique, Heavy Psych]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Theatrical Prog, Ritual Rock, Choral Art Rock]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Progressive Rock [Dramatic Soundscape, Concept Rock]</t>
+  </si>
+  <si>
+    <t>Experimental Rock, Spoken Word [Avant-Garde, Free-Form Vocal Performance, Sound Art]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Psychedelic Rock, Saxophone-led Art Rock, Ritual Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Experimental Rock [Epic Avant-Prog, Sound Collage, Psychedelic Suite]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Dark Rock, Rhythmic Prog, Final Release]</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το 666 αποτελεί το το αδιαμφισβήτητο ορόσημο της progressive και psychedelic rock μουσικής, βασισμένο στην Αποκάλυψη του Ιωάννη, σε μουσική Vangelis και στίχους/έντυπο υλικό του Κώστα Φέρρη. Η παρούσα σύγχρονη έκδοση περιλαμβάνει gatefold εξώφυλλο, λευκό αυτοκόλλητο (white hype sticker) που πιστοποιεί την επανέκδοση υπό την επίβλεψη του Vangelis και κοπή (lacquer cut) στα Abbey Road Studios από τον Christian Wright. Η πίεση/κατασκευή έγινε στη Τσεχία (GZ Media).</t>
+  </si>
+  <si>
+    <t>Χορωδιακό, επαναληπτικό και deliberately υπερβολικό. Η λέξη “loud” επαναλαμβάνεται σαν συλλογική κραυγή, σαν η μάζα να φωνάζει χωρίς να αντιλαμβάνεται πλήρως τι έρχεται. Η χρήση της επανάληψης δημιουργεί μια τελετουργική, σχεδόν ειρωνική αίσθηση. Δεν είναι από τις πιο σύνθετες μουσικές ιδέες του δίσκου, αλλά τοποθετεί αποτελεσματικά τον ακροατή σε δημόσια, θορυβώδη και αποπροσωποποιημένη Αποκάλυψη.</t>
+  </si>
+  <si>
+    <t>Οι επτά σάλπιγγες είναι ένας ακόμη μηχανισμός κλιμάκωσης της Αποκάλυψης. Το track λειτουργεί ως σύντομο fanfare/alarm, με σκοπό να ξεκινήσει η C πλευρά σαν καινούργια πράξη του έργου. Δεν αναπτύσσει τραγούδι, αλλά ο τίτλος και η ηχητική χειρονομία μεταφέρουν άμεσα το concept σε επόμενο επίπεδο.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Με τον Lucas Sideras στα lead vocals, έχει διαφορετικό φωνητικό χρώμα από τα Demis-led tracks. Το τραγούδι κάνει το Θηρίο πιο σωματικό, πιο ρυθμικό και λιγότερο αφηρημένο. Η μουσική είναι dark psychedelic rock με έντονη groove βάση· δεν χρειάζεται μεγάλη διάρκεια για να δημιουργήσει απειλή. Η αλλαγή τραγουδιστή λειτουργεί σωστά δραματουργικά, σαν το ίδιο το Θηρίο να αποκτά δική του φωνή. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">Η “θλίψη” ή “δοκιμασία” γίνεται σύντομο, σχεδόν τελετουργικό πέρασμα. Δεν αναπτύσσει νέο μουσικό θέμα· λειτουργεί ως τίτλος-κατάσταση. Σε έναν conventional δίσκο ίσως θα φαινόταν ατελές, αλλά στο </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>666</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> είναι ένα ακόμη κεφάλαιο της θεατρικής sequence.</t>
+    </r>
+  </si>
+  <si>
+    <t>Εδώ η αποκαλυπτική απειλή αποκτά ρυθμό πορείας. Το Θηρίο δεν εμφανίζεται πια ως αόριστο σύμβολο, αλλά ως μηχανική, στρατιωτική και αναπόφευκτη δύναμη. Η επανάληψη και η march-like κίνηση συνδέουν το track με πολιτική, φασιστική και πολεμική εικονοποιία , χωρίς να χρειάζεται να εξηγήσει τα πάντα με στίχους. Είναι ένα από τα σημεία όπου το 666 λειτουργεί ως πολιτικό έργο του early-’70s κλίματος, πέρα από τη θρησκευτική πηγή του.</t>
+  </si>
+  <si>
+    <t>Ξαφνική έκρηξη garage/acid rock που σπάει τον θεατρικό ρυθμό της B πλευράς. Το “Do It” λειτουργεί σαν ωμή εντολή, χωρίς φιλοσοφική εξήγηση , δράσε, υπάκουσε ή παραδόσου στην επιθυμία/βία. Η μπάντα ακούγεται πιο γήινη και άμεση, σχεδόν proto-punk, προσφέροντας μία από τις πιο σωματικές στιγμές του album. Είναι σύντομο αλλά εξαιρετικά χρήσιμο για τη ροή, επειδή βάζει rock ’n’ roll ωμή ενέργεια μέσα στο μωσαϊκό των interludes.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ψυχρό overture που εισάγει την ιδέα ενός απρόσωπου μηχανισμού εξουσίας. Το “system” είναι η δομή που ρυθμίζει την πραγματικότητα πριν ακόμη εμφανιστούν οι βιβλικές εικόνες του δίσκου. Δεν είναι πλήρες τραγούδι, αλλά concept cue, ένας κόσμος οργανώνεται, παρακολουθεί και οδηγείται προς καταστροφή. Η ηχητική του λιτότητα είναι σκόπιμη, επειδή ανοίγει χώρο ώστε το “Babylon” να ακουστεί σαν πρώτη πραγματική εισβολή στον κόσμο της Αποκάλυψης.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το “Babylon” είναι η εικόνα μιας διεφθαρμένης, ηδονικής και κυριαρχικής πόλης , θρησκευτικό σύμβολο παρακμής που στο album γίνεται και σχόλιο για τον σύγχρονο πολιτισμό. Με τον Demis Roussos στα lead vocals και tenor saxophone του Michel Ripoche, το track συνδυάζει pop αμεσότητα, ψυχεδελική ενορχήστρωση και τελετουργικό χαρακτήρα. Η μελωδία είναι σχεδόν εύκολη, αλλά η ατμόσφαιρα μένει ανήσυχη, η “Βαβυλώνα” δεν είναι τόπος απόλαυσης αλλά μηχανισμός που οδηγεί στην κατάρρευση. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ψυχεδελικό pop-rock κομμάτι με σχεδόν παιδική, φωτεινή επιφάνεια. Το “Αρνί” είναι κεντρικό βιβλικό σύμβολο θυσίας, αθωότητας και αποκάλυψης, όμως η μπάντα το χειρίζεται με ανάλαφρη, πλούσια μελωδία αντί με βαρύτητα. Αυτή η αντίθεση είναι η δύναμή του, μια ευχάριστη μελωδία αποκτά ελαφρά ανατριχιαστική χροιά όταν τοποθετηθεί μέσα σε έναν κόσμο θηρίων, σαλπίγγων και καταστροφής. Η νεότερη κριτική της επανέκδοσης το χαρακτηρίζει “psych-pop nugget”, ακριβώς επειδή συμπυκνώνει pop ομορφιά και concept σκοτάδι. </t>
+  </si>
+  <si>
+    <t>Μικρό interlude πάνω στο άνοιγμα της Έβδομης Σφραγίδας. Είναι οριακό σημείο της βιβλικής αφήγησης, πριν από τη νέα σειρά συμφορών υπάρχει η αίσθηση αναμονής και σιωπής. Η σύνθεση λειτουργεί περισσότερο με ηχητικό design και δραματικό transition παρά με κανονική μελωδία. Δεν απαιτείται να «σταθεί» μόνη της· η αξία της βρίσκεται στο ότι μετακινεί το LP από τον λυρικό κόσμο του “The Lamb” στη σκοτεινότερη, σχεδόν κινηματογραφική B πλευρά.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Από τα πιο ελληνικά και μεσογειακά tracks του έργου. Ο τίτλος δεν χρησιμοποιεί το Αιγαίο ως τουριστική εικόνα, αλλά ως αρχαϊκό, ανοιχτό τοπίο που αντιπαρατίθεται στη Βαβυλώνα και στη βιομηχανική/πολεμική αποκαλυπτική φαντασία. Οι πληκτροφορικές υφές του Vangelis, το μπάσο και τα percussive χρώματα δημιουργούν μία αργή, κυματιστή αίσθηση. Είναι instrumental mood piece, αλλά όχι filler, επεκτείνει γεωγραφικά και ψυχικά το concept, συνδέοντας την ελληνική ταυτότητα των δημιουργών με το βιβλικό/παγκόσμιο πλαίσιο. </t>
+  </si>
+  <si>
+    <t>Τα επτά φιαλίδια της Αποκάλυψης προαναγγέλλουν θεϊκή οργή και διαδοχικές συμφορές. Εδώ η μουσική λειτουργεί σαν σύντομο sound-document, όχι αφήγηση, αλλά alarm. Η ένταση είναι συμπυκνωμένη και διακόπτει τη ροή του “Aegean Sea” ώστε να υπενθυμίσει ότι το album δεν είναι απλώς ψυχεδελικό ταξίδι, αλλά σκηνοθετημένη καταστροφή.</t>
+  </si>
+  <si>
+    <t>Η αφύπνιση του Θηρίου αποδίδεται με ανησυχία και θεατρικότητα. Το Θηρίο στο concept δεν είναι μόνο βιβλικό πρόσωπο· είναι σύμβολο εξουσίας, βίας, μαζικής υστερίας και ανθρώπινης πλευράς που απελευθερώνεται όταν ο “system” καταρρέει. Η διάρκεια μόλις ενός λεπτού ενισχύει την αίσθηση flash, μια ξαφνική εμφάνιση απειλής πριν συνεχιστεί η αποκαλυπτική πομπή.</t>
+  </si>
+  <si>
+    <t>Θρηνητικό, πιο μελωδικό και ανθρώπινο κομμάτι. Μετά τα σύντομα omen fragments, το “Lament” προσφέρει πραγματικό συναισθηματικό βάρος, πένθος για έναν κόσμο που χάνεται, για ανθρώπους που έχουν ήδη πληγεί από πόλεμο, εξουσία και καταστροφή. Η μουσική κινείται προς art rock και dark ballad, με μελωδία που αφήνει χώρο στη φωνή και στην ατμόσφαιρα. Είναι μια από τις πιο υποτιμημένες συνθέσεις του album, επειδή δεν έχει τη φήμη των “Four Horsemen” ή “Infinity”, αλλά δίνει στο concept μια απαραίτητη στιγμή συμπόνιας.</t>
+  </si>
+  <si>
+    <t>Μία σύντομη ηχητική αναπαράσταση σμήνους και εισβολής. Οι ακρίδες της Αποκάλυψης συνδέονται με ανεξέλεγκτη φυσική/υπερφυσική καταστροφή, και το κομμάτι χρησιμοποιεί noise, κίνηση και dissonance ως μικροσκοπική σκηνή καταστροφής. Η χαμηλή ατομική βαθμολογία αντανακλά τον micro-track χαρακτήρα, όχι έλλειψη λειτουργίας, μέσα στο concept είναι πολύ αποτελεσματικό transition.</t>
+  </si>
+  <si>
+    <t>Μόλις 14 δευτερόλεπτα, ερπετική, σχεδόν σατιρική miniature. Το “ofis” σημαίνει φίδι στα ελληνικά και λειτουργεί ως σύντομη παραπομπή στον πειρασμό, την απειλή και την ύπουλη μεταμόρφωση. Είναι μικρό, αλλά ταιριάζει στη λογική του δίσκου όπου τα μικρο-κομμάτια είναι δραματικά cuts, όχι άχρηστα αποσπάσματα.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Από τα πιο σημαντικά tracks θεματικά. Το Altamont Speedway Free Festival του 1969 είχε γίνει σύμβολο της βίαιης κατάρρευσης του ιδεαλισμού της counterculture, ιδίως μετά τον θάνατο του Meredith Hunter. Οι Aphrodite’s Child χρησιμοποιούν το όνομα ως σύμβολο μιας εποχής που χάνει την αθωότητά της. Η μουσική είναι σκοτεινή, βαριά και art-rock, όχι νοσταλγική, παρουσιάζει το Altamont ως ρήγμα, ως σημείο όπου η υπόσχεση της συλλογικής ελευθερίας γυρίζει σε φόβο και βία. </t>
+  </si>
+  <si>
+    <t>Θεατρική, τελετουργική σύνθεση γύρω από το βιβλικό μοτίβο της ένωσης/νίκης του Αρνίου. Μετά την πολιτική και κοινωνική σκοτεινιά του “Altamont”, επιστρέφει σε θρησκευτική εικόνα λύτρωσης, όμως η παραγωγή δεν είναι γαλήνια, διατηρεί μια υπόγεια ανησυχία. Η μελωδική/χορωδιακή προσέγγιση κάνει το track να μοιάζει με fragment από rock opera, ενισχύοντας τη συνολική θεατρική αρχιτεκτονική του double LP.</t>
+  </si>
+  <si>
+    <t>Η σύλληψη του Θηρίου είναι δραματουργικό σημείο αντιστροφής, η δύναμη που φαινόταν ακατανίκητη αντιμετωπίζεται και περιορίζεται. Η μουσική λειτουργεί ως soundscape/prog transition, με ένταση και κοφτές μεταβολές αντί για πλήρη pop μορφή. Δεν είναι σχεδιασμένο ως standalone song, αλλά ως prelude για την πιο ακραία και διαβόητη στιγμή του album.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ο λατινικός τίτλος σημαίνει «εδώ και τώρα». Με τον Michel Ripoche στο tenor saxophone και τον Demis Roussos στα lead vocals, το track επαναφέρει μουσική κίνηση και psychedelic rock σάρκα μετά την αφαιρετικότητα του “Infinity”. Η σύνθεση έχει ritual groove, σαξοφωνικές υφές και αποφασιστική αίσθηση παρουσίας, η αποκάλυψη δεν είναι μελλοντική προφητεία· συμβαίνει τώρα. Είναι από τα πιο αποτελεσματικά late-album tracks, ακριβώς επειδή συμπυκνώνει το conceptual βάρος σε ένα πραγματικό rock τραγούδι. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το 19λεπτο finale είναι το αποκορύφωμα του 666, ένα μεγάλο collage που ανακυκλώνει, διαλύει και μεταμορφώνει μοτίβα από όλο το album. Ο τίτλος δημιουργεί εικόνα ενός θεάτρου ή σταδίου όπου όλοι έχουν ήδη καθίσει , οι θεατές είναι παρόντες, άρα και συνένοχοι, στην καταστροφή που εκτυλίσσεται. Το track περνά από rock, ηλεκτρονικά textures, spoken fragments, ψυχεδελικές εκρήξεις και quasi-jazz αυτοσχεδιασμό. Δεν είναι “song” με συμβατικό verse/chorus, αλλά το σημείο όπου ο Vangelis αποκαλύπτει τον ρόλο του ως συνθέτη-σκηνοθέτη, ολόκληρος ο δίσκος επιστρέφει σαν θραύσματα μνήμης μέσα σε μία τεράστια αποκαλυπτική σουίτα. Η 2024 επανεκτίμηση το χαρακτηρίζει τελικό 19-minute “meltdown” με διαχρονική δύναμη. </t>
+  </si>
+  <si>
+    <t>Μετά το overload του “All the Seats Were Occupied”, το “Break” λειτουργεί ως απελευθέρωση και επίλογος. Ο τίτλος μπορεί να σημαίνει ρήξη, διάλειμμα ή τελική θραύση· όλες οι σημασίες ταιριάζουν. Με τον Lucas Sideras στα lead vocals, η μουσική επιστρέφει σε πιο άμεσο rock pulse, αλλά η αίσθηση παραμένει σκοτεινή. Δεν προσφέρει εύκολη κάθαρση, το album δεν κλείνει με λύση, αλλά με μια τελευταία κίνηση μετά την καταστροφή. Είναι σωστό τέλος, επειδή υπενθυμίζει ότι μετά την Αποκάλυψη υπάρχει πάντα κενό, θραύση και ανάγκη να αρχίσει κάτι νέο.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Το πιο ακραίο και αμφιλεγόμενο κομμάτι του δίσκου, με guest vocals της </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Irene Papas.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Δεν είναι συμβατικό τραγούδι, αποτελεί αυτοσχεδιαστική, avant-garde vocal performance όπου η επανάληψη της λέξης “I was, I am, I am to come” μετατρέπεται σταδιακά σε έκσταση, αναπνοές και κραυγές. Η ιδέα της αιωνιότητας , το άπειρο , γίνεται σωματική, όχι αφηρημένη, γέννηση, ερωτισμός, θάνατος και αποκαλυπτική μεταμόρφωση συμπλέκονται. Το κομμάτι υπήρξε ένας από τους λόγους έντασης με τη Vertigo κατά την αρχική κυκλοφορία, αλλά σήμερα είναι κρίσιμο για να καταλάβεις τη ριζοσπαστική φιλοδοξία του album. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A4. The Four Horsemen:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF27251E"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Μία από τις οριστικές συνθέσεις των Aphrodite’s Child και το πιο άμεσα αναγνωρίσιμο τραγούδι του album. Οι Τέσσερις Καβαλάρηδες , κατάκτηση, πόλεμος, πείνα και θάνατος , μετατρέπονται σε βαριά, υπνωτική prog-rock πορεία. Η μπάσα, σχεδόν απειλητική κίνηση, τα οργανικά χρώματα του Vangelis και η φωνή του Demis Roussos δημιουργούν έναν σκοτεινό, τελετουργικό groove. Η σύνθεση έχει αρκετή melodic σαφήνεια ώστε να λειτουργεί έξω από το concept, αλλά μέσα στο album αποκτά μεγαλύτερη δύναμη, είναι η στιγμή που η αποκαλυπτική αφήγηση παίρνει υλική μορφή.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15008,6 +15301,26 @@
       <name val="Roboto Condensed"/>
       <charset val="161"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Roboto Condensed"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Roboto Condensed"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF27251E"/>
+      <name val="Roboto Condensed"/>
+      <charset val="161"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -15072,7 +15385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15152,6 +15465,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15464,7 +15783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -19667,6 +19986,38 @@
       </c>
       <c r="J131" s="7" t="s">
         <v>4483</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>4519</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>4520</v>
+      </c>
+      <c r="D132" s="3">
+        <v>1972</v>
+      </c>
+      <c r="E132" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>4546</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>4571</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>4521</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>4522</v>
       </c>
     </row>
   </sheetData>
@@ -19932,6 +20283,8 @@
     <hyperlink ref="I130" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
     <hyperlink ref="J131" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
     <hyperlink ref="I131" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
+    <hyperlink ref="I132" r:id="rId258" xr:uid="{A1A2837E-B079-456D-84AB-6A1561328A15}"/>
+    <hyperlink ref="J132" r:id="rId259" xr:uid="{5B16694A-EF14-479B-83C7-4F9D8A886209}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19939,7 +20292,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1261"/>
+  <dimension ref="A1:I1285"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -54239,6 +54592,656 @@
       </c>
       <c r="I1261" s="3"/>
     </row>
+    <row r="1262" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1262" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1262" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1262" s="4" t="s">
+        <v>4523</v>
+      </c>
+      <c r="D1262" s="4" t="s">
+        <v>4547</v>
+      </c>
+      <c r="E1262" s="14">
+        <v>3.25</v>
+      </c>
+      <c r="F1262" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="G1262" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="H1262" s="30" t="s">
+        <v>4578</v>
+      </c>
+      <c r="I1262" s="3"/>
+    </row>
+    <row r="1263" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1263" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1263" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1263" s="4" t="s">
+        <v>4524</v>
+      </c>
+      <c r="D1263" s="4" t="s">
+        <v>4548</v>
+      </c>
+      <c r="E1263" s="14">
+        <v>4.12</v>
+      </c>
+      <c r="F1263" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1263" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1263" s="30" t="s">
+        <v>4579</v>
+      </c>
+      <c r="I1263" s="3"/>
+    </row>
+    <row r="1264" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1264" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1264" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1264" s="4" t="s">
+        <v>4525</v>
+      </c>
+      <c r="D1264" s="4" t="s">
+        <v>4549</v>
+      </c>
+      <c r="E1264" s="14">
+        <v>3.59</v>
+      </c>
+      <c r="F1264" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1264" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1264" s="30" t="s">
+        <v>4572</v>
+      </c>
+      <c r="I1264" s="3"/>
+    </row>
+    <row r="1265" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1265" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1265" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1265" s="4" t="s">
+        <v>4526</v>
+      </c>
+      <c r="D1265" s="4" t="s">
+        <v>4550</v>
+      </c>
+      <c r="E1265" s="14">
+        <v>4.45</v>
+      </c>
+      <c r="F1265" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1265" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="H1265" s="29" t="s">
+        <v>4595</v>
+      </c>
+      <c r="I1265" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1266" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1266" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1266" s="4" t="s">
+        <v>4527</v>
+      </c>
+      <c r="D1266" s="4" t="s">
+        <v>4551</v>
+      </c>
+      <c r="E1266" s="14">
+        <v>4.01</v>
+      </c>
+      <c r="F1266" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1266" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1266" s="30" t="s">
+        <v>4580</v>
+      </c>
+      <c r="I1266" s="3"/>
+    </row>
+    <row r="1267" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1267" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1267" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1267" s="4" t="s">
+        <v>4528</v>
+      </c>
+      <c r="D1267" s="4" t="s">
+        <v>4552</v>
+      </c>
+      <c r="E1267" s="14">
+        <v>3.53</v>
+      </c>
+      <c r="F1267" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1267" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1267" s="30" t="s">
+        <v>4581</v>
+      </c>
+      <c r="I1267" s="3"/>
+    </row>
+    <row r="1268" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1268" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1268" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1268" s="4" t="s">
+        <v>4529</v>
+      </c>
+      <c r="D1268" s="4" t="s">
+        <v>4553</v>
+      </c>
+      <c r="E1268" s="14">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="F1268" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1268" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1268" s="30" t="s">
+        <v>4582</v>
+      </c>
+      <c r="I1268" s="3"/>
+    </row>
+    <row r="1269" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1269" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1269" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1269" s="4" t="s">
+        <v>4530</v>
+      </c>
+      <c r="D1269" s="4" t="s">
+        <v>4554</v>
+      </c>
+      <c r="E1269" s="14">
+        <v>3.37</v>
+      </c>
+      <c r="F1269" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="G1269" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1269" s="30" t="s">
+        <v>4583</v>
+      </c>
+      <c r="I1269" s="3"/>
+    </row>
+    <row r="1270" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1270" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1270" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1270" s="4" t="s">
+        <v>4531</v>
+      </c>
+      <c r="D1270" s="4" t="s">
+        <v>4555</v>
+      </c>
+      <c r="E1270" s="14">
+        <v>3.21</v>
+      </c>
+      <c r="F1270" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G1270" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1270" s="30" t="s">
+        <v>4584</v>
+      </c>
+      <c r="I1270" s="3"/>
+    </row>
+    <row r="1271" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1271" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1271" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1271" s="4" t="s">
+        <v>4532</v>
+      </c>
+      <c r="D1271" s="4" t="s">
+        <v>4556</v>
+      </c>
+      <c r="E1271" s="14">
+        <v>3.36</v>
+      </c>
+      <c r="F1271" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1271" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="H1271" s="30" t="s">
+        <v>4585</v>
+      </c>
+      <c r="I1271" s="3"/>
+    </row>
+    <row r="1272" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1272" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1272" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1272" s="4" t="s">
+        <v>4533</v>
+      </c>
+      <c r="D1272" s="4" t="s">
+        <v>4557</v>
+      </c>
+      <c r="E1272" s="14">
+        <v>3.78</v>
+      </c>
+      <c r="F1272" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1272" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1272" s="30" t="s">
+        <v>4576</v>
+      </c>
+      <c r="I1272" s="3"/>
+    </row>
+    <row r="1273" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1273" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1273" s="3">
+        <v>12</v>
+      </c>
+      <c r="C1273" s="4" t="s">
+        <v>4534</v>
+      </c>
+      <c r="D1273" s="4" t="s">
+        <v>4558</v>
+      </c>
+      <c r="E1273" s="14">
+        <v>4</v>
+      </c>
+      <c r="F1273" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G1273" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="H1273" s="30" t="s">
+        <v>4586</v>
+      </c>
+      <c r="I1273" s="3"/>
+    </row>
+    <row r="1274" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1274" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1274" s="3">
+        <v>13</v>
+      </c>
+      <c r="C1274" s="4" t="s">
+        <v>4535</v>
+      </c>
+      <c r="D1274" s="4" t="s">
+        <v>4559</v>
+      </c>
+      <c r="E1274" s="14">
+        <v>4.01</v>
+      </c>
+      <c r="F1274" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1274" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1274" s="30" t="s">
+        <v>4577</v>
+      </c>
+      <c r="I1274" s="3"/>
+    </row>
+    <row r="1275" spans="1:9" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1275" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1275" s="3">
+        <v>14</v>
+      </c>
+      <c r="C1275" s="4" t="s">
+        <v>4536</v>
+      </c>
+      <c r="D1275" s="4" t="s">
+        <v>4560</v>
+      </c>
+      <c r="E1275" s="14">
+        <v>3.35</v>
+      </c>
+      <c r="F1275" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="G1275" s="11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H1275" s="30" t="s">
+        <v>4575</v>
+      </c>
+      <c r="I1275" s="3"/>
+    </row>
+    <row r="1276" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1276" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1276" s="3">
+        <v>15</v>
+      </c>
+      <c r="C1276" s="4" t="s">
+        <v>3196</v>
+      </c>
+      <c r="D1276" s="4" t="s">
+        <v>4561</v>
+      </c>
+      <c r="E1276" s="14">
+        <v>3.74</v>
+      </c>
+      <c r="F1276" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1276" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1276" s="30" t="s">
+        <v>4574</v>
+      </c>
+      <c r="I1276" s="3"/>
+    </row>
+    <row r="1277" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1277" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1277" s="3">
+        <v>16</v>
+      </c>
+      <c r="C1277" s="4" t="s">
+        <v>4537</v>
+      </c>
+      <c r="D1277" s="4" t="s">
+        <v>4562</v>
+      </c>
+      <c r="E1277" s="14">
+        <v>2.88</v>
+      </c>
+      <c r="F1277" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G1277" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="H1277" s="30" t="s">
+        <v>4587</v>
+      </c>
+      <c r="I1277" s="3"/>
+    </row>
+    <row r="1278" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1278" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1278" s="3">
+        <v>17</v>
+      </c>
+      <c r="C1278" s="4" t="s">
+        <v>4538</v>
+      </c>
+      <c r="D1278" s="4" t="s">
+        <v>4563</v>
+      </c>
+      <c r="E1278" s="14">
+        <v>3.16</v>
+      </c>
+      <c r="F1278" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G1278" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1278" s="30" t="s">
+        <v>4573</v>
+      </c>
+      <c r="I1278" s="3"/>
+    </row>
+    <row r="1279" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1279" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1279" s="3">
+        <v>18</v>
+      </c>
+      <c r="C1279" s="4" t="s">
+        <v>4539</v>
+      </c>
+      <c r="D1279" s="4" t="s">
+        <v>4564</v>
+      </c>
+      <c r="E1279" s="14">
+        <v>4.01</v>
+      </c>
+      <c r="F1279" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1279" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="H1279" s="30" t="s">
+        <v>4588</v>
+      </c>
+      <c r="I1279" s="3"/>
+    </row>
+    <row r="1280" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1280" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1280" s="3">
+        <v>19</v>
+      </c>
+      <c r="C1280" s="4" t="s">
+        <v>4540</v>
+      </c>
+      <c r="D1280" s="4" t="s">
+        <v>4565</v>
+      </c>
+      <c r="E1280" s="14">
+        <v>3.96</v>
+      </c>
+      <c r="F1280" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1280" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1280" s="30" t="s">
+        <v>4589</v>
+      </c>
+      <c r="I1280" s="3"/>
+    </row>
+    <row r="1281" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1281" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1281" s="3">
+        <v>20</v>
+      </c>
+      <c r="C1281" s="4" t="s">
+        <v>4541</v>
+      </c>
+      <c r="D1281" s="4" t="s">
+        <v>4566</v>
+      </c>
+      <c r="E1281" s="14">
+        <v>3.76</v>
+      </c>
+      <c r="F1281" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1281" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="H1281" s="30" t="s">
+        <v>4590</v>
+      </c>
+      <c r="I1281" s="3"/>
+    </row>
+    <row r="1282" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1282" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1282" s="3">
+        <v>21</v>
+      </c>
+      <c r="C1282" s="4" t="s">
+        <v>4542</v>
+      </c>
+      <c r="D1282" s="4" t="s">
+        <v>4567</v>
+      </c>
+      <c r="E1282" s="14">
+        <v>2.97</v>
+      </c>
+      <c r="F1282" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1282" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1282" s="18" t="s">
+        <v>4594</v>
+      </c>
+      <c r="I1282" s="3"/>
+    </row>
+    <row r="1283" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1283" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1283" s="3">
+        <v>22</v>
+      </c>
+      <c r="C1283" s="4" t="s">
+        <v>4543</v>
+      </c>
+      <c r="D1283" s="4" t="s">
+        <v>4568</v>
+      </c>
+      <c r="E1283" s="14">
+        <v>3.86</v>
+      </c>
+      <c r="F1283" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1283" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1283" s="30" t="s">
+        <v>4591</v>
+      </c>
+      <c r="I1283" s="3"/>
+    </row>
+    <row r="1284" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1284" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1284" s="3">
+        <v>23</v>
+      </c>
+      <c r="C1284" s="4" t="s">
+        <v>4544</v>
+      </c>
+      <c r="D1284" s="4" t="s">
+        <v>4569</v>
+      </c>
+      <c r="E1284" s="14">
+        <v>4.17</v>
+      </c>
+      <c r="F1284" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1284" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1284" s="30" t="s">
+        <v>4592</v>
+      </c>
+      <c r="I1284" s="3"/>
+    </row>
+    <row r="1285" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1285" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B1285" s="3">
+        <v>24</v>
+      </c>
+      <c r="C1285" s="4" t="s">
+        <v>4545</v>
+      </c>
+      <c r="D1285" s="4" t="s">
+        <v>4570</v>
+      </c>
+      <c r="E1285" s="14">
+        <v>3.97</v>
+      </c>
+      <c r="F1285" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1285" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1285" s="30" t="s">
+        <v>4593</v>
+      </c>
+      <c r="I1285" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CA8D36-47E5-4DC8-8BB3-0C3AF351CAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6DDE8A-F4D5-434D-8F5F-EC3EA39722A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4957" uniqueCount="4596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5027" uniqueCount="4658">
   <si>
     <t>No</t>
   </si>
@@ -15189,6 +15189,247 @@
       </rPr>
       <t xml:space="preserve"> Μία από τις οριστικές συνθέσεις των Aphrodite’s Child και το πιο άμεσα αναγνωρίσιμο τραγούδι του album. Οι Τέσσερις Καβαλάρηδες , κατάκτηση, πόλεμος, πείνα και θάνατος , μετατρέπονται σε βαριά, υπνωτική prog-rock πορεία. Η μπάσα, σχεδόν απειλητική κίνηση, τα οργανικά χρώματα του Vangelis και η φωνή του Demis Roussos δημιουργούν έναν σκοτεινό, τελετουργικό groove. Η σύνθεση έχει αρκετή melodic σαφήνεια ώστε να λειτουργεί έξω από το concept, αλλά μέσα στο album αποκτά μεγαλύτερη δύναμη, είναι η στιγμή που η αποκαλυπτική αφήγηση παίρνει υλική μορφή.</t>
     </r>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/37111626-Rory-Gallagher-Calling-Card</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/gzW15rS-NyOv1ih7vF6ICL1ewL_9G7W9sAX8cXgv5fw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3MTEx/NjI2LTE3NzY1ODE4/NjgtOTY0My5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Calling Card (κυκλοφορίας αρχικά του 1976) αποτελεί έναν από τους κορυφαίους δάκτυλους/σταθμούς του Rory Gallagher στην blues-rock ιστορία, σε παραγωγή του Roger Glover των Deep Purple. Η παρούσα επανέκδοση 50ής επετείου (50th Anniversary Edition) στα 180g περιέχει πιστοποιητικό mastering από τα Abbey Road Studios και κοπή μισής ταχύτητας (Half-Speed Master) με τη χαρακτηριστική σφραγίδα ROOM 30 στα αυλάκια.</t>
+  </si>
+  <si>
+    <t>Universal Music Recordings – 8818328, 00602488183284. Ευρωπαϊκή έκδοση (Europe), κυκλοφορία Record Store Day στις 18 Απριλίου 2026, Remastered &amp; Mastered at Abbey Road Studios – Half Speed Mastering, κοπή από τον Miles Showell, και πίεση στη Γαλλία από την MPO.</t>
+  </si>
+  <si>
+    <t>Gallagher, Rory</t>
+  </si>
+  <si>
+    <t>Calling Card</t>
+  </si>
+  <si>
+    <t>Do You Read Me</t>
+  </si>
+  <si>
+    <t>Country Mile</t>
+  </si>
+  <si>
+    <t>I’ll Admit You’re Gone</t>
+  </si>
+  <si>
+    <t>Secret Agent</t>
+  </si>
+  <si>
+    <t>Jack-Knife Beat</t>
+  </si>
+  <si>
+    <t>Edged In Blue</t>
+  </si>
+  <si>
+    <t>Barley And Grape Rag</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Electric Blues, Roots Rock, Jazz Rock, Folk Rock, Boogie Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Riff-driven Blues Rock, Funk Rock, Live-energy Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Roots Rock [Country Blues, Boogie Rock, Road Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Dark Blues Rock, Atmospheric Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Electric Blues, Dramatic Rock, Guitar-led Epic]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Slow Blues, Soul Ballad, Piano-led Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Spy-theme Rock, Funky Blues Rock, Jazz-tinged Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Extended Electric Blues, Guitar Jam, Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Slow Electric Blues, Jazz Blues, Late-night Ballad]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Ragtime [Acoustic Blues, Ragtime, Folk Blues]</t>
+  </si>
+  <si>
+    <t>Σύντομο, γρήγορο road song με country-blues/boogie ρίζες. Η “country mile” είναι μεγάλη απόσταση , συχνά μεγαλύτερη από όσο φαίνεται , και ο τίτλος γίνεται μεταφορά για ταξίδι, κόπο και απόσταση από ένα πρόσωπο ή από έναν στόχο. Ο Gallagher συνδυάζει electric guitar με rootsy αίσθηση, αφήνοντας το rhythm section να τρέχει σαν όχημα στον δρόμο. Το track δεν αναζητά την πολυπλοκότητα· η δύναμή του είναι η κίνηση, το ζωηρό groove και η εικόνα ενός μουσικού που μεταφέρει το folk/blues παρελθόν του σε rock ’n’ roll ταχύτητα. Η τοποθέτησή του μετά το “Do You Read Me” κρατά την A πλευρά σε συνεχή forward motion.</t>
+  </si>
+  <si>
+    <t>Η A πλευρά κλείνει με slow blues/soul ballad. Η παραδοχή του τίτλου , «θα το δεχτώ ότι έφυγες» , δεν είναι απλή λύση· είναι στάδιο πένθους, παραίτησης και δύσκολης αποδοχής. Ο Gallagher χαμηλώνει την κιθαριστική επίδειξη, αφήνει πιάνο, ρυθμό και φωνή να δημιουργήσουν νυχτερινή ατμόσφαιρα. Η κιθάρα μπαίνει με οικονομία και συναισθηματική ακρίβεια. Η σύνθεση συνδέει τη blues πλευρά του με soul και jazz-adjacent chords, ενώ η πιο καθαρή παραγωγή αναδεικνύει τη λεπτή δυναμική του band. Είναι σημαντική για τη ροή γιατί δίνει ανθρώπινο, ευάλωτο τέλος στην A πλευρά αντί για ακόμη ένα guitar climax.</t>
+  </si>
+  <si>
+    <t>Το ομώνυμο track είναι η κεντρική δήλωση του album. Μια “calling card” είναι κάρτα επίσκεψης ή διακριτικό σημάδι παρουσίας, εδώ γίνεται μουσικό αυτοπορτρέτο, ο τρόπος με τον οποίο ο Gallagher παρουσιάζει τον εαυτό του, την κιθάρα και την καλλιτεχνική του ταυτότητα. Το κομμάτι είναι electric blues με hard-rock βάρος, δραματικό build-up και soloing που αναπτύσσεται οργανικά μέσα στη σύνθεση. Δεν έχει μόνο “showcase” χαρακτήρα· η μελωδία και η ερμηνεία δίνουν πραγματικό συναίσθημα. Η εξωτερική παραγωγή βοήθησε να οργανωθεί η ένταση, το track ακούγεται μεγάλο, αλλά δεν χάνει την αμεσότητά του. Είναι δικαίως ένα από τα signature pieces του Gallagher.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με μια πιο funky, κινηματογραφική blues-rock σύνθεση. Ο “secret agent” είναι ένας αφηγητής σε κίνηση, με μυστικότητα, διπλή ζωή και αίσθηση κινδύνου , τίτλος που δίνει στον Gallagher αφορμή να χρησιμοποιήσει πιο κοφτό groove και κιθάρες που θυμίζουν soundtrack χωρίς να γίνονται pastiche. Ο Glover βοηθά ιδιαίτερα εδώ, η παραγωγή δίνει χώρο σε κάθε όργανο, με τα drums και το μπάσο να κρατούν tension ενώ η κιθάρα παρεμβαίνει με σύντομα, ελεγχόμενα leads. Το αποτέλεσμα είναι από τα πιο stylised cuts του album, αποδεικνύοντας ότι ο Gallagher μπορούσε να κινηθεί πέρα από τις παραδοσιακές blues φόρμες.</t>
+  </si>
+  <si>
+    <t>Το μεγαλύτερο electric-blues workout του δίσκου. Ο τίτλος παραπέμπει σε απότομο, κοφτερό χτύπημα ή επικίνδυνη κίνηση, και η μουσική το αποδίδει με riff που κόβει, έντονο groove και παρατεταμένη κιθαριστική ανάπτυξη. Σε πάνω από επτά λεπτά, το τραγούδι δίνει στον Gallagher χώρο να οδηγήσει το band σε heavy blues-rock jam, χωρίς να εγκαταλείπει τη δομή. Το soloing έχει bite, αλλά δεν είναι αυτοσκοπός, τα motifs επιστρέφουν και το rhythm section διατηρεί συνεχή ένταση. Είναι ίσως η κορυφαία εκδήλωση της live δύναμής του μέσα σε studio πλαίσιο και αποτελεί καθοριστικό highlight του album.</t>
+  </si>
+  <si>
+    <t>Αργό, μελαγχολικό electric blues με jazzy αρμονική αίσθηση. Το “edged in blue” σημαίνει ότι κάτι έχει άκρες βαμμένες από θλίψη, η μελαγχολία δεν καταπίνει τα πάντα, αλλά περιβάλλει κάθε σκέψη και συναίσθημα. Εδώ ο Gallagher δείχνει εντυπωσιακή αυτοσυγκράτηση. Η κιθάρα του δεν κραυγάζει· “μιλά” με μικρές φράσεις, vibrato και κενά, με τον Lou Martin στο πιάνο να προσθέτει βάθος. Είναι από τις πιο ώριμες blues ερμηνείες του, μακριά από στερεότυπο 12-bar jam. Η απλή αλλά προσεγμένη παραγωγή το κάνει να μοιάζει με late-night club performance, και είναι ένας από τους βασικούς λόγους που το Calling Card θεωρείται τόσο πολυδιάστατο.</t>
+  </si>
+  <si>
+    <t>Acoustic/ragtime finale, με “barley” και “grape” να παραπέμπουν σε μπύρα και κρασί , άρα σε ποτό, λαϊκή διασκέδαση και τις παλιές folk-blues φόρμες. Ο Gallagher κλείνει τον δίσκο με παιχνιδιάρικη δεξιοτεχνία αντί για βαριά κατάληξη. Η ακουστική κιθάρα, ο ragtime ρυθμός και η σχεδόν παλιομοδίτικη αίσθηση φέρνουν στο προσκήνιο τη βαθιά γνώση του για country blues, folk και pre-war μουσικές παραδόσεις. Είναι πολύ αποτελεσματικό closer, μετά τον ηλεκτρικό και συναισθηματικό όγκο του “Edged in Blue”, επιτρέπει στον δίσκο να φύγει με χαμόγελο και ανθρώπινη αμεσότητα.</t>
+  </si>
+  <si>
+    <r>
+      <t>A1. Do You Read Me:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το άνοιγμα του δίσκου είναι από τα πιο δυναμικά studio tracks του Gallagher. Η ερώτηση “Do You Read Me?” παραπέμπει σε ραδιοεπικοινωνία, αλλά λειτουργεί ως κάλεσμα, με ακούς πραγματικά, λαμβάνεις το μήνυμα ή χανόμαστε μέσα στον θόρυβο; Το riff έχει έντονο blues-rock drive, με funkier ρυθμική βάση και κιθάρα που κινείται νευρικά γύρω από τη φωνή. Η εκτέλεση είναι tight, σχεδόν live, χωρίς να ακούγεται πρόχειρη. Ο Gallagher δεν χρειάζεται παρατεταμένο solo για να επιβληθεί· βάζει μικρές κιθαριστικές εκρήξεις μέσα στη δομή, διατηρώντας το τραγούδι γρήγορο και άμεσο. Είναι από τα μεγάλα Rory openers και θέτει αμέσως την υψηλή ενέργεια του LP.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A3. Moonchild: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Πιο σκοτεινό και ατμοσφαιρικό blues-rock τραγούδι, με το “moonchild” να παρουσιάζεται ως μυστηριώδης, νυχτερινή και ασταθής ερωτική φιγούρα. Η κιθάρα δεν λειτουργεί απλώς ως riff machine, χτίζει σκιές, sustain και tension, ενώ το bass του Gerry McAvoy και τα drums του Rod de’Ath αφήνουν χώρο στην ατμόσφαιρα. Ο Gallagher παίζει με την blues παράδοση, αλλά αποφεύγει το απλό 12-bar framework , η παραγωγή του Glover δίνει μεγαλύτερο βάθος στα layers χωρίς να γυαλίζει υπερβολικά τον ήχο. Είναι ένα από τα tracks που αποκαλύπτουν την πιο nocturnal, cinematic πλευρά του δίσκου.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/7340202-Styx-The-Grand-Illusion</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/krgIuF_bYEZpQaR-qOmdvlCOxfwnBIcR0Wj2Dqbut-M/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTczNDAy/MDItMTQzOTI5MzI5/Ni0zOTY1LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Styx</t>
+  </si>
+  <si>
+    <t>The Grand Illusion</t>
+  </si>
+  <si>
+    <t>A&amp;M Records – B0022045-01, UMe – B0022045-01. Αμερικανική έκδοση (US), κυκλοφορία 2015, σε βινύλιο 180 γραμμαρίων, κομμένο στα The Mastering Lab και τυπωμένο από την United Record Pressing. Styx — The Grand Illusion — A&amp;M Records / UMe B0022045-01, US, 2015 reissue. 180g LP. Cut at The Mastering Lab; pressed by United Record Pressing. Barcode: 6 02547 04091 6. Matrices: B0026613-01 A KR (1241756) 01010105 / B0026613-01 B KR (1241757) 01010308. Original album released 7 July 1977.</t>
+  </si>
+  <si>
+    <t>Fooling Yourself (The Angry Young Man)</t>
+  </si>
+  <si>
+    <t>Superstars</t>
+  </si>
+  <si>
+    <t>Come Sail Away</t>
+  </si>
+  <si>
+    <t>Miss America</t>
+  </si>
+  <si>
+    <t>Man In The Wilderness</t>
+  </si>
+  <si>
+    <t>Castle Walls</t>
+  </si>
+  <si>
+    <t>The Grand Finale</t>
+  </si>
+  <si>
+    <t>Progressive Rock, AOR [Symphonic Rock, Art Rock, Arena Rock, Melodic Hard Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Theatrical Prog, Keyboard Rock, Concept Opener]</t>
+  </si>
+  <si>
+    <t>AOR, Hard Rock [Melodic Hard Rock, Arena Rock, Empowerment Anthem]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, AOR [Concept Rock, Pop-Prog, Spoken-Word Theatre Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, AOR [Symphonic Rock, Power Ballad, Arena Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Riff Rock, Social Commentary, Guitar-led Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Progressive Rock [Melodic Prog, Existential Rock, Arena Ballad]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Symphonic Prog, Theatrical Rock, Keyboard Epic]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Concept Reprise, Instrumental Coda, Symphonic Rock]</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental/concept reprise που επιστρέφει σε βασικά μοτίβα και κλείνει κυκλικά το έργο. Δεν επιδιώκει να ανταγωνιστεί το “Castle Walls” ως τραγούδι· λειτουργεί ως αυλαία, υπενθυμίζοντας ότι η ψευδαίσθηση είναι επαναλαμβανόμενος μηχανισμός. Με keyboard-led ενορχήστρωση και theatrical coda, αφήνει τον ακροατή όχι με απόλυτη λύση αλλά με μια τελευταία ματιά στο “θέαμα” που μόλις πέρασε. Είναι ιδανικό τέλος για album που θέλει να μοιάζει τόσο με προσωπική εξομολόγηση όσο και με σκηνική παράσταση.</t>
+  </si>
+  <si>
+    <t>Το album ανοίγει με μία άμεση αποδόμηση της επιτυχίας και του θεάματος. Η “μεγάλη ψευδαίσθηση” είναι η ιδέα ότι οι rock stars, οι celebrities και οι κοινωνικά επιτυχημένοι άνθρωποι είναι θεμελιωδώς διαφορετικοί ή ανώτεροι από τον ακροατή. Ο Dennis DeYoung χρησιμοποιεί πιάνο, synthesizers, χορωδιακά backing vocals και θεατρική ερμηνεία για να δώσει στο τραγούδι σχεδόν επιβλητική, καρναβαλική αίσθηση. Το μουσικό μεγαλείο είναι εσκεμμένα μέρος του σαρκασμού, η ίδια η ενορχήστρωση δημιουργεί “illusion” ενώ οι στίχοι ζητούν από τον ακροατή να μην εξαπατηθεί από αυτή. Είναι εξαιρετικό concept opener, που θεμελιώνει το βασικό ερώτημα του δίσκου, τι μένει όταν φύγει το προσωπείο;</t>
+  </si>
+  <si>
+    <t>Το μεγάλο Tommy Shaw anthem. Το “angry young man” είναι κάποιος που νιώθει εγκλωβισμένος, υποτιμημένος ή προδομένος, αλλά η βασική ιδέα του τραγουδιού είναι ότι μέρος της φυλακής είναι εσωτερικό, μπορεί να κοροϊδεύεις τον ίδιο σου τον εαυτό, αφήνοντας τις πληγές και τους φόβους να καθορίζουν τη ζωή σου. Με άμεσο riff, γρήγορη ρυθμική ώθηση, χαρακτηριστική φωνή του Shaw και μεγάλα harmony vocals, το κομμάτι συνδέει prog ακρίβεια με hard-rock αμεσότητα. Έγινε το δεύτερο Top 30 single του album, φτάνοντας στο No. 29, και παραμένει ένα από τα πιο αποτελεσματικά τραγούδια των Styx.</t>
+  </si>
+  <si>
+    <t>Σύντομη αλλά θεματικά κρίσιμη σύνθεση. Εξετάζει τη λατρεία των celebrities και τη γοητεία του να πιστεύεις ότι η φήμη προσφέρει λύση στην αμφιβολία ή στην έλλειψη ταυτότητας. Το spoken-word section του DeYoung λειτουργεί σαν αφήγηση ή “μάθημα” προς το κοινό, ενώ τα keyboards και τα vocal layers δίνουν pop-prog ύφος. Είναι λιγότερο ισχυρό ως αυτόνομο τραγούδι από το προηγούμενο, αλλά μέσα στο concept είναι απαραίτητο, μετακινεί τη συζήτηση από την ψευδαίσθηση της επιτυχίας στο πώς ο κόσμος τρέφει ενεργά αυτή την ψευδαίσθηση.</t>
+  </si>
+  <si>
+    <t>Η κορύφωση της A πλευράς και το μεγαλύτερο single των Styx. Ξεκινά ως piano ballad, με νοσταλγικό/ονειρικό lyric για απόδραση και ταξίδι, προτού περάσει σε πλήρη symphonic arena-rock έκρηξη με κιθάρες, synthesizers και πολυφωνίες. Το “sail away” είναι κάλεσμα ελευθερίας, να φύγεις από μια ζωή περιορισμών προς έναν άλλο ορίζοντα. Στο ευρύτερο concept, όμως, διατηρείται η αμφισημία, πρόκειται για αληθινή απελευθέρωση ή για άλλη μία φαντασίωση; Το τραγούδι έφτασε στο No. 8 του Billboard Hot 100 και συνέβαλε αποφασιστικά στο multi-platinum status του δίσκου.</t>
+  </si>
+  <si>
+    <r>
+      <t>B1. Miss America:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Η B πλευρά ανοίγει με πιο κιθαριστική, σκληρή πλευρά των Styx. Ο James Young χρησιμοποιεί τη φιγούρα της “Miss America” για να αναδείξει την εμπορευματοποίηση της ομορφιάς και τη μετατροπή ενός ανθρώπου σε προϊόν, σύμβολο ή δημόσιο θέαμα. Το τραγούδι έχει heavier riff, πιο επιθετικά vocals και μικρότερη έμφαση στη symphonic μεγαλοπρέπεια. Αυτό δημιουργεί χρήσιμη αντίθεση μετά το συναισθηματικό “Come Sail Away”, οι Styx υπενθυμίζουν ότι πίσω από τα μεγάλα keyboard hooks υπάρχει αληθινή hard-rock μπάντα.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B2. Man In The Wilderness:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Υπαρξιακή, μελωδική σύνθεση του Tommy Shaw. Ο “άνθρωπος στην ερημιά” είναι απομονωμένος από τις προσδοκίες, τους ρόλους και τους κοινωνικούς θορύβους , και ακριβώς γι’ αυτό μπορεί να βρει καθαρότερη ταυτότητα. Η μουσική ξεκινά πιο ήπια και σταδιακά ανοίγει σε ισχυρό chorus, με ακουστικές κιθάρες, ηλεκτρικά fills και αρμονίες που έχουν σχεδόν folk-rock ευαισθησία. Είναι από τα πιο ανθρώπινα τραγούδια του δίσκου, δεν σατιρίζει την ψευδαίσθηση, αλλά περιγράφει την αναζήτηση μιας αληθινής ζωής μετά από αυτή. Κριτικές του album συχνά το ξεχωρίζουν μαζί με “Castle Walls” ως βασικό deep cut της B πλευράς.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B3. Castle Walls:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το πιο symphonic και θεατρικό τραγούδι του album. Τα “κάστρα” είναι προστασία, φαντασίωση, πλούτος ή ψυχικό οχυρό , μια εντυπωσιακή κατασκευή που μπορεί να σε κρατά ασφαλή αλλά και φυλακισμένο. Ο DeYoung επιστρέφει σε πλούσια keyboards, δραματικές μεταβολές και φωνητική ερμηνεία που πλησιάζει rock-opera. Η σύνθεση έχει πραγματική prog ανάπτυξη, χωρίς να διαλύεται σε τεχνική επίδειξη, κάθε αλλαγή υπηρετεί την εικόνα εγκλωβισμού και την αναζήτηση εξόδου. Είναι το μεγάλο deep-cut jewel του album, συχνά υποτιμημένο επειδή βρίσκεται δίπλα στο “Come Sail Away”, αλλά εξίσου ουσιαστικό για το concept.</t>
+    </r>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το "The Grand Illusion" είναι ο δίσκος όπου οι Styx ενοποίησαν πλήρως τα τρία βασικά στοιχεία τους: τον Dennis DeYoung ως θεατρικό keyboard-pop συνθέτη, τον Tommy Shaw ως μελωδικό hard-rock τραγουδοποιό και τον J.Y. Young ως κιθαριστική, πιο σκληρή αντίβαρη δύναμη. Το αποτέλεσμα είναι προσβάσιμο prog χωρίς να απλοποιείται σε σκέτο AOR. Η 2015 US 180g έκδοση είναι μια καθαρά τεκμηριωμένη, σοβαρή αναλογική επανέκδοση. The Mastering Lab cut, United Record Pressing manufacture και πλήρη matrices που αντιστοιχούν στη συγκεκριμένη κοπή. Ως album είναι 4,5/5 με τα “Come Sail Away”, “Fooling Yourself”, “Man in the Wilderness” και “Castle Walls” ως θεμέλια της ακρόασης. Aποτελεί το πιο εμπορικό και καλλιτεχνικό ορόσημο των Styx, συνδυάζοντας το melodic hard rock με το progressive rock. Η συγκεκριμένη έκδοση του 2015 περιλαμβάνει remastered ήχο υψηλής πιστότητας, αφίσα του συγκροτήματος και κοπή/χαράξεις που εντοπίζονται στα runouts (με τα χαρακτηριστικά etchings των Ryan Smith / TML και τους κωδικούς πίεσης).</t>
   </si>
 </sst>
 </file>
@@ -15783,7 +16024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -20018,6 +20259,70 @@
       </c>
       <c r="J132" s="7" t="s">
         <v>4522</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>4600</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>4601</v>
+      </c>
+      <c r="D133" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E133" s="5">
+        <v>3.77</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>4609</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>4598</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>4599</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>4596</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>4630</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>4631</v>
+      </c>
+      <c r="D134" s="3">
+        <v>1977</v>
+      </c>
+      <c r="E134" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>4640</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>4657</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>4632</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>4628</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>4629</v>
       </c>
     </row>
   </sheetData>
@@ -20285,6 +20590,10 @@
     <hyperlink ref="I131" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
     <hyperlink ref="I132" r:id="rId258" xr:uid="{A1A2837E-B079-456D-84AB-6A1561328A15}"/>
     <hyperlink ref="J132" r:id="rId259" xr:uid="{5B16694A-EF14-479B-83C7-4F9D8A886209}"/>
+    <hyperlink ref="I133" r:id="rId260" xr:uid="{6AB6E69D-F1A6-4525-8E1D-E39B1043B707}"/>
+    <hyperlink ref="J133" r:id="rId261" xr:uid="{C3008C5E-7367-4D13-8A51-811BB64125E9}"/>
+    <hyperlink ref="I134" r:id="rId262" xr:uid="{C87BE13B-FF08-4594-91D4-2FC13EEEC8DA}"/>
+    <hyperlink ref="J134" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20292,7 +20601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1285"/>
+  <dimension ref="A1:I1302"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -55242,6 +55551,475 @@
       </c>
       <c r="I1285" s="3"/>
     </row>
+    <row r="1286" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1286" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1286" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1286" s="4" t="s">
+        <v>4602</v>
+      </c>
+      <c r="D1286" s="4" t="s">
+        <v>4610</v>
+      </c>
+      <c r="E1286" s="14">
+        <v>3.98</v>
+      </c>
+      <c r="F1286" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1286" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1286" s="17" t="s">
+        <v>4626</v>
+      </c>
+      <c r="I1286" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1287" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1287" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1287" s="4" t="s">
+        <v>4603</v>
+      </c>
+      <c r="D1287" s="4" t="s">
+        <v>4611</v>
+      </c>
+      <c r="E1287" s="14">
+        <v>3.63</v>
+      </c>
+      <c r="F1287" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1287" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="H1287" s="6" t="s">
+        <v>4619</v>
+      </c>
+      <c r="I1287" s="3"/>
+    </row>
+    <row r="1288" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1288" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1288" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1288" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D1288" s="4" t="s">
+        <v>4612</v>
+      </c>
+      <c r="E1288" s="14">
+        <v>4.16</v>
+      </c>
+      <c r="F1288" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1288" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="H1288" s="17" t="s">
+        <v>4627</v>
+      </c>
+      <c r="I1288" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1289" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1289" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1289" s="4" t="s">
+        <v>4601</v>
+      </c>
+      <c r="D1289" s="4" t="s">
+        <v>4613</v>
+      </c>
+      <c r="E1289" s="14">
+        <v>3.83</v>
+      </c>
+      <c r="F1289" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1289" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1289" s="6" t="s">
+        <v>4621</v>
+      </c>
+      <c r="I1289" s="3"/>
+    </row>
+    <row r="1290" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1290" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1290" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1290" s="4" t="s">
+        <v>4604</v>
+      </c>
+      <c r="D1290" s="4" t="s">
+        <v>4614</v>
+      </c>
+      <c r="E1290" s="14">
+        <v>3.34</v>
+      </c>
+      <c r="F1290" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1290" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1290" s="6" t="s">
+        <v>4620</v>
+      </c>
+      <c r="I1290" s="3"/>
+    </row>
+    <row r="1291" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1291" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1291" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1291" s="4" t="s">
+        <v>4605</v>
+      </c>
+      <c r="D1291" s="4" t="s">
+        <v>4615</v>
+      </c>
+      <c r="E1291" s="14">
+        <v>3.77</v>
+      </c>
+      <c r="F1291" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1291" s="11">
+        <v>4.75</v>
+      </c>
+      <c r="H1291" s="6" t="s">
+        <v>4622</v>
+      </c>
+      <c r="I1291" s="3"/>
+    </row>
+    <row r="1292" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1292" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1292" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1292" s="4" t="s">
+        <v>4606</v>
+      </c>
+      <c r="D1292" s="4" t="s">
+        <v>4616</v>
+      </c>
+      <c r="E1292" s="14">
+        <v>3.57</v>
+      </c>
+      <c r="F1292" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G1292" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1292" s="6" t="s">
+        <v>4623</v>
+      </c>
+      <c r="I1292" s="3"/>
+    </row>
+    <row r="1293" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1293" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1293" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1293" s="4" t="s">
+        <v>4607</v>
+      </c>
+      <c r="D1293" s="4" t="s">
+        <v>4617</v>
+      </c>
+      <c r="E1293" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="F1293" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1293" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1293" s="6" t="s">
+        <v>4624</v>
+      </c>
+      <c r="I1293" s="3"/>
+    </row>
+    <row r="1294" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1294" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B1294" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1294" s="4" t="s">
+        <v>4608</v>
+      </c>
+      <c r="D1294" s="4" t="s">
+        <v>4618</v>
+      </c>
+      <c r="E1294" s="14">
+        <v>3.33</v>
+      </c>
+      <c r="F1294" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1294" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1294" s="6" t="s">
+        <v>4625</v>
+      </c>
+      <c r="I1294" s="3"/>
+    </row>
+    <row r="1295" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1295" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1295" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1295" s="4" t="s">
+        <v>4631</v>
+      </c>
+      <c r="D1295" s="4" t="s">
+        <v>4641</v>
+      </c>
+      <c r="E1295" s="14">
+        <v>3.89</v>
+      </c>
+      <c r="F1295" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1295" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1295" s="6" t="s">
+        <v>4650</v>
+      </c>
+      <c r="I1295" s="3"/>
+    </row>
+    <row r="1296" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1296" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1296" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1296" s="4" t="s">
+        <v>4633</v>
+      </c>
+      <c r="D1296" s="4" t="s">
+        <v>4642</v>
+      </c>
+      <c r="E1296" s="14">
+        <v>3.92</v>
+      </c>
+      <c r="F1296" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G1296" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1296" s="6" t="s">
+        <v>4651</v>
+      </c>
+      <c r="I1296" s="3"/>
+    </row>
+    <row r="1297" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1297" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1297" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1297" s="4" t="s">
+        <v>4634</v>
+      </c>
+      <c r="D1297" s="4" t="s">
+        <v>4643</v>
+      </c>
+      <c r="E1297" s="14">
+        <v>3.33</v>
+      </c>
+      <c r="F1297" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1297" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1297" s="6" t="s">
+        <v>4652</v>
+      </c>
+      <c r="I1297" s="3"/>
+    </row>
+    <row r="1298" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1298" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1298" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1298" s="4" t="s">
+        <v>4635</v>
+      </c>
+      <c r="D1298" s="4" t="s">
+        <v>4644</v>
+      </c>
+      <c r="E1298" s="14">
+        <v>4.13</v>
+      </c>
+      <c r="F1298" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G1298" s="11">
+        <v>4.95</v>
+      </c>
+      <c r="H1298" s="6" t="s">
+        <v>4653</v>
+      </c>
+      <c r="I1298" s="3"/>
+    </row>
+    <row r="1299" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1299" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1299" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1299" s="4" t="s">
+        <v>4636</v>
+      </c>
+      <c r="D1299" s="4" t="s">
+        <v>4645</v>
+      </c>
+      <c r="E1299" s="14">
+        <v>3.67</v>
+      </c>
+      <c r="F1299" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1299" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1299" s="17" t="s">
+        <v>4654</v>
+      </c>
+      <c r="I1299" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1300" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1300" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1300" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="D1300" s="4" t="s">
+        <v>4646</v>
+      </c>
+      <c r="E1300" s="14">
+        <v>3.76</v>
+      </c>
+      <c r="F1300" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1300" s="11">
+        <v>4.75</v>
+      </c>
+      <c r="H1300" s="17" t="s">
+        <v>4655</v>
+      </c>
+      <c r="I1300" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1301" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1301" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1301" s="4" t="s">
+        <v>4638</v>
+      </c>
+      <c r="D1301" s="4" t="s">
+        <v>4647</v>
+      </c>
+      <c r="E1301" s="14">
+        <v>3.72</v>
+      </c>
+      <c r="F1301" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1301" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="H1301" s="17" t="s">
+        <v>4656</v>
+      </c>
+      <c r="I1301" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1302" s="3">
+        <v>7340202</v>
+      </c>
+      <c r="B1302" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1302" s="4" t="s">
+        <v>4639</v>
+      </c>
+      <c r="D1302" s="4" t="s">
+        <v>4648</v>
+      </c>
+      <c r="E1302" s="14">
+        <v>3.34</v>
+      </c>
+      <c r="F1302" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1302" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1302" s="6" t="s">
+        <v>4649</v>
+      </c>
+      <c r="I1302" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6DDE8A-F4D5-434D-8F5F-EC3EA39722A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD089153-9C74-4DBB-B85B-4A862F12BE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5027" uniqueCount="4658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="4701">
   <si>
     <t>No</t>
   </si>
@@ -15430,6 +15430,175 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το "The Grand Illusion" είναι ο δίσκος όπου οι Styx ενοποίησαν πλήρως τα τρία βασικά στοιχεία τους: τον Dennis DeYoung ως θεατρικό keyboard-pop συνθέτη, τον Tommy Shaw ως μελωδικό hard-rock τραγουδοποιό και τον J.Y. Young ως κιθαριστική, πιο σκληρή αντίβαρη δύναμη. Το αποτέλεσμα είναι προσβάσιμο prog χωρίς να απλοποιείται σε σκέτο AOR. Η 2015 US 180g έκδοση είναι μια καθαρά τεκμηριωμένη, σοβαρή αναλογική επανέκδοση. The Mastering Lab cut, United Record Pressing manufacture και πλήρη matrices που αντιστοιχούν στη συγκεκριμένη κοπή. Ως album είναι 4,5/5 με τα “Come Sail Away”, “Fooling Yourself”, “Man in the Wilderness” και “Castle Walls” ως θεμέλια της ακρόασης. Aποτελεί το πιο εμπορικό και καλλιτεχνικό ορόσημο των Styx, συνδυάζοντας το melodic hard rock με το progressive rock. Η συγκεκριμένη έκδοση του 2015 περιλαμβάνει remastered ήχο υψηλής πιστότητας, αφίσα του συγκροτήματος και κοπή/χαράξεις που εντοπίζονται στα runouts (με τα χαρακτηριστικά etchings των Ryan Smith / TML και τους κωδικούς πίεσης).</t>
+  </si>
+  <si>
+    <t>EMI – 00602475946410. Παγκόσμια έκδοση, κυκλοφορία 2025 (17 Οκτωβρίου 2025), σε βινύλιο 180 γραμμαρίων (Crystal Clear), κομμένο με Half-Speed Mastering στα Abbey Road Studios από τον Miles Showell και τυπωμένο από την Optimal Media GmbH.</t>
+  </si>
+  <si>
+    <t>Queen</t>
+  </si>
+  <si>
+    <t>A Night At The Opera</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/35392324-Queen-A-Night-At-The-Opera-50th-Anniversary-Edition-</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/wXMe5dNpXr7Cqw-JYm9pUqznBJUWjXBQ4w-ZzWAzB5w/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM1Mzky/MzI0LTE3NjA2MzY3/MTUtNzMzMC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Death On Two Legs (Dedicated To…)</t>
+  </si>
+  <si>
+    <t>Lazing On A Sunday Afternoon</t>
+  </si>
+  <si>
+    <t>I’m In Love With My Car</t>
+  </si>
+  <si>
+    <t>You’re My Best Friend</t>
+  </si>
+  <si>
+    <t>’39</t>
+  </si>
+  <si>
+    <t>Sweet Lady</t>
+  </si>
+  <si>
+    <t>Seaside Rendezvous</t>
+  </si>
+  <si>
+    <t>The Prophet’s Song</t>
+  </si>
+  <si>
+    <t>Love Of My Life</t>
+  </si>
+  <si>
+    <t>Good Company</t>
+  </si>
+  <si>
+    <t>Bohemian Rhapsody</t>
+  </si>
+  <si>
+    <t>God Save The Queen</t>
+  </si>
+  <si>
+    <t>Rock, Progressive Rock [Hard Rock, Art Rock, Glam Rock, Music Hall, Baroque Pop, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Art Rock [Piano Rock, Theatrical Rock, Acid-Tongued Rock]</t>
+  </si>
+  <si>
+    <t>Music Hall, Art Rock [Vaudeville Pop, Vintage Radio Effect, Miniature]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Glam Rock [Driving Rock, Garage-tinged Rock, Taylor Vocal]</t>
+  </si>
+  <si>
+    <t>Pop Rock, Soft Rock [Piano Pop, Warm Love Song, Deacon Classic]</t>
+  </si>
+  <si>
+    <t>Folk Rock, Progressive Rock [Sci-Fi Folk, Skiffle Rock, Acoustic Narrative]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Riff Rock, Odd-Meter Rock, May Guitar Track]</t>
+  </si>
+  <si>
+    <t>Music Hall, Pop Rock [Vaudeville, Jazz Pop, Multi-tracked Vocal Brass]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Prog Epic, Vocal Canon, Dark Fantasy Rock]</t>
+  </si>
+  <si>
+    <t>Baroque Pop, Soft Rock [Piano Ballad, Orchestral Pop, Romantic Art Rock]</t>
+  </si>
+  <si>
+    <t>Music Hall, Art Rock [Dixieland Pastiche, Vaudeville, Multi-tracked Guitar Orchestra]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Rock Opera, Piano Ballad, Hard Rock, Operatic Pop]</t>
+  </si>
+  <si>
+    <t>Art Rock, Instrumental Rock [Guitar Anthem, Ceremonial Coda, National-Anthem Rework]</t>
+  </si>
+  <si>
+    <t>Η πιο ζεστή και προσγειωμένη pop στιγμή του δίσκου. Γραμμένο από τον John Deacon για τη σύζυγό του Veronica Tetzlaff, το τραγούδι είναι μια απλή δήλωση αγάπης και συντροφικότητας, αντίβαρο στη μεγαλοπρέπεια που το περιβάλλει. Το ηλεκτρικό πιάνο του Deacon, τα αρμονικά φωνητικά και η ερμηνεία του Mercury φτιάχνουν ένα σχεδόν τέλειο pop-rock single. Δεν έχει τις τεράστιες θεατρικές στροφές του “Bohemian Rhapsody”, αλλά η οικονομία του είναι εξίσου δεξιοτεχνική. Έγινε επιτυχία και παραμένει μία από τις πιο αγαπημένες, ανθρώπινες συνθέσεις των Queen.</t>
+  </si>
+  <si>
+    <t>Vaudeville/jazz-pop καρτ ποστάλ, με τον Mercury να στήνει έναν επινοημένο παραθαλάσσιο κόσμο γεμάτο χορό, φλερτ και old-time entertainment. Η “μπάντα πνευστών” δημιουργείται κυρίως με πολυηχογραφημένες φωνές του Mercury και του Taylor, αποδεικνύοντας το studio imagination της μπάντας. Η σύνθεση έχει ελαφρότητα, αλλά τεχνικά είναι εξαιρετικά δουλεμένη. Ως κλείσιμο της A πλευράς προσφέρει χαμόγελο και αποσυμπίεση, πριν ο δίσκος εισέλθει στη σκοτεινότερη, πιο επική B πλευρά.</t>
+  </si>
+  <si>
+    <t>Μόλις λίγο πάνω από ένα λεπτό, αλλά πυκνό σε music-hall χαρακτήρα. Ο Mercury μιμείται παλιό γραμμόφωνο/ραδιοφωνική μετάδοση με παραμορφωμένη φωνή και πιάνο, παρουσιάζοντας την Κυριακάτικη ραστώνη σαν μικρή θεατρική σκηνή. Μετά το δηλητήριο του “Death on Two Legs”, η απότομη αλλαγή είναι σχεδόν κωμική. Αυτή η ικανότητα των Queen να πηδούν από το βαρύ hard rock σε vaudeville χωρίς να χάνουν την ταυτότητά τους είναι θεμελιώδης για το album. Δεν είναι “filler”, είναι η πρώτη απόδειξη ότι ο δίσκος θα λειτουργήσει σαν πλήρες θέατρο ή κινηματογραφική montage.</t>
+  </si>
+  <si>
+    <t>Ο Brian May γράφει ένα sci-fi folk τραγούδι για διαστρικό ταξίδι και χρονική διαστολή. Οι ήρωες επιστρέφουν στη Γη ύστερα από έναν χρόνο υποκειμενικού χρόνου, αλλά ανακαλύπτουν ότι έχουν περάσει εκατό χρόνια για όσους έμειναν πίσω. Η σύνθεση χρησιμοποιεί skiffle/folk ρυθμό, ακουστικές κιθάρες και lead vocals από τον May, μετατρέποντας μια σχετικιστική ιδέα σε απλό, συγκινητικό folk narrative. Είναι χαρακτηριστικό Queen paradox, επιστημονική φαντασία σε μορφή campfire τραγουδιού. Το θέμα της αποξένωσης από τον χρόνο δίνει στο album μια πιο σοβαρή, μελαγχολική διάσταση. 2299</t>
+  </si>
+  <si>
+    <t>Το πιο riff-heavy κομμάτι της A πλευράς. Ο May γράφει ένα hard-rock τραγούδι με περίεργη ρυθμική αίσθηση και κιθάρα που συνδυάζει heavy attack με μικρές προοδευτικές μετατοπίσεις. Το lyric είναι ερωτική σύγκρουση, μια σχέση που δεν λειτουργεί, παρότι υπάρχει ένταση και έλξη. Το chorus είναι λιγότερο άμεσο από άλλες Queen συνθέσεις, αλλά η αξία του βρίσκεται στην κιθαριστική εφευρετικότητα και στο γεγονός ότι κρατά τον δίσκο συνδεδεμένο με την σκληρή rock βάση του. Είναι το σημείο όπου οι Queen θυμίζουν ότι η πολυστυλιστικότητα τους δεν σημαίνει απομάκρυνση από τα riffs.</t>
+  </si>
+  <si>
+    <t>Το μεγάλο progressive epic του Brian May, περίπου οκτώ λεπτών, χτισμένο γύρω από όνειρο/προφητεία παγκόσμιας καταστροφής. Η σύνθεση περνά από βαριά κιθάρα και σκοτεινή αφήγηση σε πολυφωνικό vocal canon, όπου οι φωνές πολλαπλασιάζονται και συγκρούονται σαν τελετουργία. Το “prophet” δεν είναι απλός προφήτης· είναι η φωνή που προειδοποιεί έναν κόσμο που αρνείται να ακούσει. Η μουσική έχει πραγματική prog δομή, όχι μόνο μεγάλο μήκος, αλλά διαδοχικές ενότητες με διαφορετική ένταση, υφή και δραματική λειτουργία. Είναι η πιο καθαρή απόδειξη ότι οι Queen μπορούσαν να σταθούν δίπλα στο symphonic/progressive rock της εποχής, διατηρώντας ταυτόχρονα το δικό τους melodic drama.</t>
+  </si>
+  <si>
+    <t>Η πιο τρυφερή και εκτεθειμένη μπαλάντα του Mercury. Η απουσία ενός αγαπημένου προσώπου παρουσιάζεται χωρίς ειρωνεία ή θεατρική μάσκα, «φέρ’ το πίσω, μην μου το πάρεις». Το πιάνο, η άρπα και τα guitar orchestration στοιχεία του May δίνουν baroque/pop αίσθηση, ενώ η μελωδία κρατά σχεδόν κλασική απλότητα. Έγινε διαχρονικό live σημείο, ιδιαίτερα στη Νότια Αμερική, γιατί η συναισθηματική του καθαρότητα επιτρέπει στο κοινό να συμμετέχει άμεσα. Μετά την πολυπλοκότητα του “The Prophet’s Song”, λειτουργεί σαν γυμνή ανθρώπινη εξομολόγηση.</t>
+  </si>
+  <si>
+    <t>Ο Brian May επιστρέφει σε music-hall/Dixieland pastiche, αφηγούμενος έναν άνθρωπο που θυσιάζει οικογένεια και προσωπικές σχέσεις για την καριέρα και την οικονομική επιτυχία. Η ειρωνεία του τίτλου είναι θεμελιώδης, ο αφηγητής μπορεί να έχει “καλή παρέα” ή κοινωνικό κύρος, αλλά καταλήγει συναισθηματικά μόνος. Ο May κατασκευάζει σχεδόν ολόκληρη την ψεύτικη Dixieland μπάντα με layers ηλεκτρικής κιθάρας, πετυχαίνοντας κάτι ταυτόχρονα χαριτωμένο και τεχνικά εντυπωσιακό. Θεματικά συνδέεται άμεσα με τη “Grand Illusion” της καριέρας και της επιτυχίας , μια μικρή ιστορία που συνοψίζει την τιμή του προσωπικού ambition.</t>
+  </si>
+  <si>
+    <t>Σύντομο, τελετουργικό instrumental κλείσιμο, με τον Brian May να παίζει τον βρετανικό εθνικό ύμνο μέσα από πολυεπίπεδη ηλεκτρική κιθάρα. Δεν είναι εθνικιστική δήλωση· λειτουργεί περισσότερο ως θεατρική αυλαία μετά την υπερβολή της “Bohemian Rhapsody”. Η κιθάρα αντικαθιστά μια ολόκληρη ορχήστρα και αφήνει τον δίσκο να τελειώσει με μια αίσθηση επίσημου, παράξενου και ελαφρώς ειρωνικού θριάμβου. Είναι το σωστό τέλος, μετά από φωνές, όπερα, hard rock, folk, music hall και μπαλάντες, η μπάντα κλείνει σαν να κατεβάζει την αυλαία ενός φαντασμαγορικού θεάτρου.</t>
+  </si>
+  <si>
+    <r>
+      <t>A3. I’m In Love With My Car:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το τραγούδι του Roger Taylor είναι απλό και ειλικρινές σε σχέση με τις σύνθετες κατασκευές του Mercury και του May. Παρουσιάζει τον έρωτα με το αυτοκίνητο ως rock ’n’ roll εμμονή, μηχανή, δρόμος, ταχύτητα και ανδρική ταυτότητα. Ο Taylor αναλαμβάνει lead vocals, δίνοντας πιο τραχύ, garage-tinged χρώμα, ενώ η κιθάρα του May κρατά το heavy rock βάρος. Είναι σύντομο, αλλά λειτουργεί σαν ισχυρή ρυθμική επαναφορά μετά το vintage miniaturism. Η παρουσία του στο album είναι σημαντική γιατί υπενθυμίζει ότι οι Queen δεν ήταν μονάχα Mercury/May project , κάθε μέλος συνεισφέρει καθοριστικά στο ύφος.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A1. Death On Two Legs (Dedicated To…):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το album ανοίγει με ένα από τα πιο καυστικά τραγούδια του Freddie Mercury. Ο αφηγητής επιτίθεται σε έναν άνθρωπο που παρουσιάζεται ως εκμεταλλευτής, απατεώνας και παράσιτο , συνήθως συνδέεται με την οδυνηρή εμπειρία της μπάντας με τον πρώην manager Norman Sheffield, αν και ο Mercury δεν τον κατονομάζει στον δίσκο. Η μουσική είναι hard rock με πιάνο, κιθαριστικά χτυπήματα του Brian May και θεατρική κλιμάκωση. Η ένταση δεν είναι απλώς προσωπική· λειτουργεί σαν καθαρτήριο άνοιγμα πριν ο δίσκος περάσει στα πιο παιχνιδιάρικα και φανταστικά του πεδία. Το “Dedicated To…” στον τίτλο αφήνει την προσβολή να αιωρείται, κάνοντάς την ακόμη πιο δηλητηριώδη.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Bohemian Rhapsody:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το κεντρικό αριστούργημα, όχι επειδή είναι απλώς παράξενο ή μεγαλοπρεπές, αλλά επειδή ενώνει διαφορετικές μουσικές μορφές σε δραματική ενότητα, πιάνο ballad, a cappella/harmony section, mock-operatic σκηνή, hard-rock explosion και ήρεμη coda. Οι στίχοι αφήνουν σκόπιμα ανοιχτή την αφήγηση , ενοχή, καταδίκη, ταυτότητα, θάνατος και απελευθέρωση , χωρίς να επιτρέπουν μία οριστική ερμηνεία. Η παραγωγή χρειάστηκε μήνες για να χτιστεί, με τις πολυφωνίες να παράγονται μέσα από διαδοχικά overdubs. Το single έμεινε εννέα εβδομάδες στο No. 1 της Βρετανίας και επανακαθόρισε το τι μπορούσε να γίνει εμπορικά αποδεκτό ως rock single.</t>
+    </r>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το A Night At The Opera αποτελεί το πιο εμπορικό και φιλόδοξο αριστούργημα των Queen, συνδυάζοντας το hard rock με την όπερα και το βατεβίλ. Η επετειακή έκδοση των 50 ετών περιλαμβάνει remastered ήχο υψηλής πιστότητας, πολυτελές gatefold εξώφυλλο με ανάγλυφες χρυσοτυπίες και κοπή/χαράξεις που εντοπίζονται στα runouts (με τα χαρακτηριστικά etchings του Miles Showell και τις γεωμετρικές σημάνσεις της Optimal). Το A Night At The Opera είναι το σημείο όπου οι Queen έκαναν την υπερβολή τους συνθετική μέθοδο. Κάθε μέλος γράφει με διαφορετικό τρόπο, αλλά ο δίσκος δεν ακούγεται σαν ασύνδετη συλλογή. Η συνοχή προκύπτει από το κοινό production language: πλούσιες αρμονίες, studio λεπτομέρεια, χιούμορ, θεατρικότητα και άρνηση των στενών ειδών. Η 2025 crystal-clear 180g anniversary κόπια, με Optimal pressing και Miles Showell half-speed lacquer cutting, είναι premium, τεκμηριωμένη φυσική έκδοση ενός θεμελιώδους album. Ως μουσικό έργο η δίκαιη βαθμολογία είναι 4,8/5 — με “The Prophet’s Song”, “Love of My Life”, “’39”, “You’re My Best Friend” και, πάνω απ’ όλα, “Bohemian Rhapsody” να αιτιολογούν απόλυτα τη θέση του στον πυρήνα της rock δισκογραφίας. Queen — A Night At The Opera — EMI 00602475946410, Worldwide, 17 October 2025. 50th Anniversary Edition. LP, Album, Reissue, Crystal Clear heavyweight 180g vinyl, Half-Speed Mastered. Original master by Bob Ludwig; half-speed lacquer cut by Miles Showell at Abbey Road Studios; pressed by Optimal Media GmbH, BP 32334. Gatefold sleeve with embossed gold crest, debossed rear details, printed inner sleeve and gold hype sticker.</t>
   </si>
 </sst>
 </file>
@@ -16024,7 +16193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -16167,489 +16336,489 @@
         <v>4367</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
+        <v>31841081</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4519</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4520</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1972</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>4546</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>4571</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>4521</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>24362534</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="3">
         <v>2013</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <v>3.08</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>2475</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>31860245</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1801</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>1801</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1970</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3.4</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>1791</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>1805</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>1804</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>1802</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>28423156</v>
+        <v>31860245</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>4272</v>
+        <v>1801</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1941</v>
+        <v>1801</v>
       </c>
       <c r="D7" s="3">
-        <v>2009</v>
+        <v>1970</v>
       </c>
       <c r="E7" s="5">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1955</v>
+        <v>1791</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1959</v>
+        <v>1805</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1958</v>
+        <v>1804</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1956</v>
+        <v>1802</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>1957</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>32916789</v>
+        <v>28423156</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1895</v>
+        <v>4272</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1894</v>
+        <v>1941</v>
       </c>
       <c r="D8" s="3">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="E8" s="5">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1898</v>
+        <v>1955</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1908</v>
+        <v>1959</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1907</v>
+        <v>1958</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1896</v>
+        <v>1956</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>1897</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>14186441</v>
+        <v>32916789</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>4288</v>
+        <v>1895</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1806</v>
+        <v>1894</v>
       </c>
       <c r="D9" s="3">
-        <v>1969</v>
+        <v>2025</v>
       </c>
       <c r="E9" s="5">
-        <v>4.3099999999999996</v>
+        <v>3.25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1842</v>
+        <v>1898</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1810</v>
+        <v>1908</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1809</v>
+        <v>1907</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>1807</v>
+        <v>1896</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>1808</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
+        <v>14186441</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1969</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>15960193</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>4277</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>1916</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D11" s="3">
         <v>1976</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E11" s="5">
         <v>3.72</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>1929</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>1928</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>1927</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>1917</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>1918</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>25766467</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1995</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2019</v>
-      </c>
-      <c r="E11" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>1998</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1994</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>1993</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>1996</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>21826186</v>
+        <v>25766467</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>2074</v>
+        <v>1995</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2074</v>
+        <v>1986</v>
       </c>
       <c r="D12" s="3">
         <v>2019</v>
       </c>
       <c r="E12" s="5">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>2087</v>
+        <v>1998</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>4202</v>
+        <v>1994</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>2077</v>
+        <v>1993</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>2075</v>
+        <v>1996</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>2076</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>28699510</v>
+        <v>21826186</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2074</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3.46</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>2087</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>4202</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>28699510</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>2107</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D14" s="3">
         <v>2023</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E14" s="5">
         <v>3.33</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>2117</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>2116</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>2115</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I14" s="7" t="s">
         <v>2113</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>2114</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="15" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>24831386</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1971</v>
-      </c>
-      <c r="E14" s="5">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>2204</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>2203</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>15223559</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>215</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2054</v>
+        <v>216</v>
       </c>
       <c r="D15" s="3">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="E15" s="5">
-        <v>4.21</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>2053</v>
+        <v>2204</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>4201</v>
+        <v>227</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>2042</v>
+        <v>2203</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>2043</v>
+        <v>217</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>2044</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>9376449</v>
+        <v>15223559</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>215</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2754</v>
+        <v>2054</v>
       </c>
       <c r="D16" s="3">
         <v>1976</v>
       </c>
       <c r="E16" s="5">
+        <v>4.21</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>4201</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>2043</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>9376449</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>2754</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E17" s="5">
         <v>3.03</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>2764</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>2767</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>2755</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I17" s="7" t="s">
         <v>2766</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>2765</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>18001219</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1973</v>
-      </c>
-      <c r="E17" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>2020</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>2019</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>2017</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>926332</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1973</v>
+      </c>
+      <c r="E18" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D19" s="3">
         <v>1976</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="5">
         <v>3.29</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I19" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J19" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="20" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>2021194</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>4274</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>2353</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1977</v>
-      </c>
-      <c r="E19" s="5">
-        <v>2.85</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>2375</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>2355</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>2354</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>2366</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>2964464</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>4274</v>
@@ -16658,7 +16827,7 @@
         <v>2353</v>
       </c>
       <c r="D20" s="3">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E20" s="5">
         <v>2.85</v>
@@ -16667,3933 +16836,3967 @@
         <v>2375</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>2366</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>2964464</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>4274</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>2377</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>2376</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I21" s="7" t="s">
         <v>2379</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J21" s="7" t="s">
         <v>2378</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>23510192</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>2256</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2015</v>
-      </c>
-      <c r="E21" s="5">
-        <v>3.69</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>2276</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>2261</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>2260</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>2259</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>23506553</v>
+        <v>23510192</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2256</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2015</v>
+      </c>
+      <c r="E22" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>23506553</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>2285</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D23" s="3">
         <v>2017</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E23" s="5">
         <v>3.68</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>2305</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>2317</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>2316</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I23" s="7" t="s">
         <v>2287</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>2286</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>31604863</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>4280</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>2321</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D24" s="3">
         <v>2024</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E24" s="5">
         <v>3.56</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>2330</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>2319</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>2318</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I24" s="7" t="s">
         <v>2331</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>2332</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="25" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>8816501</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>4289</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>2511</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D25" s="3">
         <v>1979</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E25" s="5">
         <v>3.2</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>2525</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>2513</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>2512</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>2514</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>2515</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="26" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>2460844</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>3590</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>3574</v>
-      </c>
-      <c r="D25" s="3">
-        <v>1986</v>
-      </c>
-      <c r="E25" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>3589</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>3588</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>3584</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>3585</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>3403683</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>3590</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1986</v>
+      </c>
+      <c r="E26" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>3589</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>3588</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3584</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>3585</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>3403683</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>3590</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>3611</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D27" s="3">
         <v>1988</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>3.56</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F27" s="6" t="s">
         <v>3635</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>3615</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>3614</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I27" s="7" t="s">
         <v>3612</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J27" s="7" t="s">
         <v>3613</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>12282039</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>4271</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>2477</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1973</v>
-      </c>
-      <c r="E27" s="5">
-        <v>3.79</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>2481</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>2478</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>2479</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
+        <v>12282039</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1973</v>
+      </c>
+      <c r="E28" s="5">
+        <v>3.79</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>2480</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>2478</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>35389759</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>2222</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D29" s="3">
         <v>2025</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E29" s="5">
         <v>3.74</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>2245</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>2244</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>2223</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="30" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>22296643</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>2557</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>2553</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D30" s="3">
         <v>1994</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E30" s="5">
         <v>3.64</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>2562</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>2561</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>2560</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>2559</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>2558</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>11898961</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>4290</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D31" s="3">
         <v>1959</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E31" s="5">
         <v>3.94</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>2184</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>2164</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>2163</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>2153</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="32" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>1739129</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D32" s="3">
         <v>1975</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E32" s="5">
         <v>3.78</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>4318</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>4317</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>4316</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>22100377</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D32" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E32" s="5">
-        <v>3.39</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>1526</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>1516</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>1514</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
+        <v>22100377</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2022</v>
+      </c>
+      <c r="E33" s="5">
+        <v>3.39</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>29667079</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>4275</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C34" s="4" t="s">
         <v>2595</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D34" s="3">
         <v>1973</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E34" s="5">
         <v>3.51</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>2606</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>2605</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>2604</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I34" s="7" t="s">
         <v>2596</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>2597</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="35" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>28792273</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>4107</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>4106</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>2023</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E35" s="5">
         <v>3.47</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>4119</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>4103</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>4102</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I35" s="7" t="s">
         <v>4104</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J35" s="7" t="s">
         <v>4105</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>6503426</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D36" s="3">
         <v>1973</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>3.66</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>4334</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>4333</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I36" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J36" s="7" t="s">
         <v>4343</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="37" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>31106519</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D37" s="3">
         <v>1975</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E37" s="5">
         <v>3.69</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J37" s="7" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="38" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>920311</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D38" s="3">
         <v>1981</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E38" s="5">
         <v>3.45</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>4346</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>4345</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>4344</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J38" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="39" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>2138840</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D39" s="3">
         <v>1983</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E39" s="5">
         <v>3.48</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>2185</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I39" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J39" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="40" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>18813646</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>4282</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>2949</v>
-      </c>
-      <c r="D39" s="3">
-        <v>2021</v>
-      </c>
-      <c r="E39" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>2960</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>2972</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>2971</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>2948</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>28729798</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>4282</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2620</v>
+        <v>2949</v>
       </c>
       <c r="D40" s="3">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E40" s="5">
         <v>3.51</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>2635</v>
+        <v>2960</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2623</v>
+        <v>2972</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>2622</v>
+        <v>2971</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>2619</v>
+        <v>2948</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>2621</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>35342041</v>
+        <v>28729798</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4282</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E41" s="5">
+        <v>3.51</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>35342041</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>4282</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>2983</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D42" s="3">
         <v>2025</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E42" s="5">
         <v>3.6</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>3012</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>2995</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>2994</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I42" s="7" t="s">
         <v>2993</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>2992</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="43" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>34571488</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>2894</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>2881</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D43" s="3">
         <v>2024</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E43" s="5">
         <v>3.51</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>2895</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>2912</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>2911</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I43" s="7" t="s">
         <v>2896</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J43" s="7" t="s">
         <v>2897</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="44" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>16448232</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>4060</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>4025</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D44" s="3">
         <v>1978</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E44" s="5">
         <v>3.33</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F44" s="8" t="s">
         <v>4039</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>4029</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>4028</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I44" s="7" t="s">
         <v>4026</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J44" s="7" t="s">
         <v>4027</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>27663855</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>2655</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C45" s="4" t="s">
         <v>2656</v>
-      </c>
-      <c r="D44" s="3">
-        <v>1971</v>
-      </c>
-      <c r="E44" s="5">
-        <v>3.99</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>2667</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>2660</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>2659</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>2658</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>2657</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>34592074</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>4061</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>4061</v>
       </c>
       <c r="D45" s="3">
         <v>1971</v>
       </c>
       <c r="E45" s="5">
+        <v>3.99</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>2667</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>2659</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>2658</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>34592074</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1971</v>
+      </c>
+      <c r="E46" s="5">
         <v>3.7</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>4089</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>4065</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>4064</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I46" s="7" t="s">
         <v>4062</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J46" s="7" t="s">
         <v>4063</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="47" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>37111626</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>4600</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>4601</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3.77</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>4609</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>4598</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4599</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>4596</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>27342894</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>3927</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>3905</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D48" s="3">
         <v>2023</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E48" s="5">
         <v>3.85</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>3915</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>3931</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>3930</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="I48" s="7" t="s">
         <v>3928</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J48" s="7" t="s">
         <v>3929</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="49" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>35210866</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>3927</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>3944</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D49" s="3">
         <v>2025</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E49" s="5">
         <v>3.84</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F49" s="8" t="s">
         <v>3957</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>3943</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>3942</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I49" s="7" t="s">
         <v>3945</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J49" s="7" t="s">
         <v>3946</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="50" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>33790944</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D50" s="3">
         <v>2025</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E50" s="5">
         <v>3.11</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F50" s="6" t="s">
         <v>1754</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I50" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J50" s="7" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>34750368</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>2867</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>2866</v>
-      </c>
-      <c r="D49" s="3">
-        <v>2016</v>
-      </c>
-      <c r="E49" s="5">
-        <v>3.52</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>2936</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>2869</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>2868</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>2870</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>2871</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>36520261</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>3977</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>3978</v>
-      </c>
-      <c r="D50" s="3">
-        <v>2026</v>
-      </c>
-      <c r="E50" s="5">
-        <v>3.48</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>3994</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>3974</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>3973</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>3975</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>3976</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
+        <v>34750368</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2016</v>
+      </c>
+      <c r="E51" s="5">
+        <v>3.52</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>2936</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>2869</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>2868</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>36520261</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>3977</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>3978</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E52" s="5">
+        <v>3.48</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>3994</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>3974</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3973</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>3975</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>4216594</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>4281</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>1714</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D53" s="3">
         <v>1980</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E53" s="5">
         <v>3.39</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>1728</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>1718</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>1717</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I53" s="7" t="s">
         <v>1715</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="J53" s="7" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="54" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>28777768</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>1693</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>1694</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D54" s="3">
         <v>2023</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E54" s="5">
         <v>3.18</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>1699</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>1698</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>1697</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I54" s="7" t="s">
         <v>1695</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J54" s="7" t="s">
         <v>1696</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="55" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>8415848</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>3839</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>3838</v>
-      </c>
-      <c r="D53" s="3">
-        <v>1988</v>
-      </c>
-      <c r="E53" s="5">
-        <v>3.84</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>3853</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>3843</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>3842</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>3840</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>3841</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>33564954</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D54" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E54" s="5">
-        <v>2.72</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>1662</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>1675</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>1674</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>1660</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>2661964</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>3320</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>3321</v>
       </c>
       <c r="D55" s="3">
         <v>1988</v>
       </c>
       <c r="E55" s="5">
-        <v>4</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>3332</v>
+        <v>3.84</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>3853</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>3325</v>
+        <v>3843</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>3324</v>
+        <v>3842</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>3322</v>
+        <v>3840</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>3323</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
+        <v>33564954</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2022</v>
+      </c>
+      <c r="E56" s="5">
+        <v>2.72</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>1662</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>1660</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>2661964</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1988</v>
+      </c>
+      <c r="E57" s="5">
+        <v>4</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>3332</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>3325</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3324</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>3322</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>27606564</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>1567</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C58" s="4" t="s">
         <v>1542</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D58" s="3">
         <v>2023</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E58" s="5">
         <v>3.76</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F58" s="6" t="s">
         <v>1546</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>1545</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>1544</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I58" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J58" s="7" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="59" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>26012116</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B59" s="4" t="s">
         <v>1588</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>1589</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D59" s="3">
         <v>2022</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E59" s="5">
         <v>3.4</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F59" s="6" t="s">
         <v>1592</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>1594</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="I59" s="7" t="s">
         <v>1590</v>
       </c>
-      <c r="J57" s="7" t="s">
+      <c r="J59" s="7" t="s">
         <v>1591</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>11007106</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>1478</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>1479</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D60" s="3">
         <v>1978</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E60" s="5">
         <v>2.9</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F60" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>1483</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>1482</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="I60" s="7" t="s">
         <v>1481</v>
       </c>
-      <c r="J58" s="7" t="s">
+      <c r="J60" s="7" t="s">
         <v>1480</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="61" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>4684547</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>1478</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>3804</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D61" s="3">
         <v>1980</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E61" s="5">
         <v>3.47</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F61" s="8" t="s">
         <v>3816</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>3818</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H61" s="3" t="s">
         <v>3817</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="I61" s="7" t="s">
         <v>3805</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="J61" s="7" t="s">
         <v>3806</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="62" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>13795818</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B62" s="4" t="s">
         <v>1425</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D62" s="3">
         <v>1979</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E62" s="5">
         <v>3.96</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F62" s="6" t="s">
         <v>1446</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>1427</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I62" s="7" t="s">
         <v>1445</v>
       </c>
-      <c r="J60" s="7" t="s">
+      <c r="J62" s="7" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="63" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>30630553</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B63" s="4" t="s">
         <v>1381</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C63" s="4" t="s">
         <v>1382</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D63" s="3">
         <v>1995</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E63" s="5">
         <v>3.76</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F63" s="6" t="s">
         <v>1402</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>1401</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>1400</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="I63" s="7" t="s">
         <v>1384</v>
       </c>
-      <c r="J61" s="7" t="s">
+      <c r="J63" s="7" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="64" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>12991988</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B64" s="4" t="s">
         <v>3646</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C64" s="4" t="s">
         <v>3647</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D64" s="3">
         <v>1987</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E64" s="5">
         <v>3.29</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F64" s="6" t="s">
         <v>3659</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>3709</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>3648</v>
       </c>
-      <c r="I62" s="7" t="s">
+      <c r="I64" s="7" t="s">
         <v>3649</v>
       </c>
-      <c r="J62" s="7" t="s">
+      <c r="J64" s="7" t="s">
         <v>3650</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="65" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>3229841</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B65" s="4" t="s">
         <v>4270</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C65" s="4" t="s">
         <v>1360</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D65" s="3">
         <v>1981</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E65" s="5">
         <v>3.38</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F65" s="6" t="s">
         <v>1363</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>1373</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="I65" s="7" t="s">
         <v>1362</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="J65" s="7" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="66" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>7598060</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>4279</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C66" s="4" t="s">
         <v>1306</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D66" s="3">
         <v>1967</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E66" s="5">
         <v>3.65</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F66" s="6" t="s">
         <v>1321</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>1322</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>1320</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="I66" s="7" t="s">
         <v>1324</v>
       </c>
-      <c r="J64" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="67" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>28270285</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D67" s="3">
         <v>2023</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E67" s="5">
         <v>3.56</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F67" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I65" s="7" t="s">
+      <c r="I67" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="J65" s="7" t="s">
+      <c r="J67" s="7" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="68" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>35187877</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B68" s="4" t="s">
         <v>2820</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>2821</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D68" s="3">
         <v>1990</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E68" s="5">
         <v>3.44</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F68" s="6" t="s">
         <v>2839</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>2823</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>2822</v>
       </c>
-      <c r="I66" s="7" t="s">
+      <c r="I68" s="7" t="s">
         <v>2825</v>
       </c>
-      <c r="J66" s="7" t="s">
+      <c r="J68" s="7" t="s">
         <v>2824</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="69" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>7660097</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D69" s="3">
         <v>1976</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E69" s="5">
         <v>3.63</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F69" s="6" t="s">
         <v>1290</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>1305</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>1304</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I69" s="7" t="s">
         <v>1289</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="J69" s="7" t="s">
         <v>1288</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="70" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>10824930</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B70" s="4" t="s">
         <v>3677</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C70" s="4" t="s">
         <v>3678</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D70" s="3">
         <v>1983</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E70" s="5">
         <v>3.42</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F70" s="8" t="s">
         <v>3692</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>3710</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>3681</v>
       </c>
-      <c r="I68" s="7" t="s">
+      <c r="I70" s="7" t="s">
         <v>3680</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="J70" s="7" t="s">
         <v>3679</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="71" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>2589429</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B71" s="4" t="s">
         <v>3677</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C71" s="4" t="s">
         <v>3708</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D71" s="3">
         <v>1989</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E71" s="5">
         <v>3.3</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F71" s="8" t="s">
         <v>3722</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>3734</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>3733</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I71" s="7" t="s">
         <v>3711</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="J71" s="7" t="s">
         <v>3712</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>26832221</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B72" s="4" t="s">
         <v>4291</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C72" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D72" s="3">
         <v>2023</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E72" s="5">
         <v>2.82</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F72" s="6" t="s">
         <v>1258</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>1279</v>
       </c>
-      <c r="I70" s="7" t="s">
+      <c r="I72" s="7" t="s">
         <v>1249</v>
       </c>
-      <c r="J70" s="7" t="s">
+      <c r="J72" s="7" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="73" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>23803544</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B73" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C73" s="4" t="s">
         <v>1219</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D73" s="3">
         <v>1973</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E73" s="5">
         <v>3.63</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F73" s="6" t="s">
         <v>1231</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G73" s="4" t="s">
         <v>1240</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="I71" s="7" t="s">
+      <c r="I73" s="7" t="s">
         <v>1229</v>
       </c>
-      <c r="J71" s="7" t="s">
+      <c r="J73" s="7" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="74" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>29704561</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C74" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D74" s="3">
         <v>2024</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E74" s="5">
         <v>3.25</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F74" s="6" t="s">
         <v>1201</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>1200</v>
       </c>
-      <c r="I72" s="7" t="s">
+      <c r="I74" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="J72" s="7" t="s">
+      <c r="J74" s="7" t="s">
         <v>1188</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
-        <v>26909678</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D73" s="3">
-        <v>2018</v>
-      </c>
-      <c r="E73" s="5">
-        <v>3.24</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>1168</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>1156</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
-        <v>4418939</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D74" s="3">
-        <v>1977</v>
-      </c>
-      <c r="E74" s="5">
-        <v>3.55</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
+        <v>26909678</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2018</v>
+      </c>
+      <c r="E75" s="5">
+        <v>3.24</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>4418939</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1977</v>
+      </c>
+      <c r="E76" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>31216738</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B77" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C77" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D77" s="3">
         <v>2024</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E77" s="5">
         <v>3.44</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F77" s="6" t="s">
         <v>1100</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H77" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="I75" s="7" t="s">
+      <c r="I77" s="7" t="s">
         <v>1097</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="J77" s="7" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="78" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>37005303</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B78" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C78" s="4" t="s">
         <v>3872</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D78" s="3">
         <v>2026</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E78" s="5">
         <v>3.29</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F78" s="8" t="s">
         <v>3887</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>3876</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H78" s="3" t="s">
         <v>3875</v>
       </c>
-      <c r="I76" s="7" t="s">
+      <c r="I78" s="7" t="s">
         <v>3874</v>
       </c>
-      <c r="J76" s="7" t="s">
+      <c r="J78" s="7" t="s">
         <v>3873</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+    <row r="79" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>25895635</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B79" s="4" t="s">
         <v>1065</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C79" s="4" t="s">
         <v>1057</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D79" s="3">
         <v>2022</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E79" s="5">
         <v>3.58</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F79" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="I77" s="7" t="s">
+      <c r="I79" s="7" t="s">
         <v>1067</v>
       </c>
-      <c r="J77" s="7" t="s">
+      <c r="J79" s="7" t="s">
         <v>1066</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>25885156</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D78" s="3">
-        <v>1975</v>
-      </c>
-      <c r="E78" s="5">
-        <v>4.37</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>1039</v>
-      </c>
-      <c r="J78" s="7" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>4778774</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>3737</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>3763</v>
-      </c>
-      <c r="D79" s="3">
-        <v>1988</v>
-      </c>
-      <c r="E79" s="5">
-        <v>2.84</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>3752</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>3739</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>3738</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>3751</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>3750</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
+        <v>25885156</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1975</v>
+      </c>
+      <c r="E80" s="5">
+        <v>4.37</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>4778774</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>3737</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>3763</v>
+      </c>
+      <c r="D81" s="3">
+        <v>1988</v>
+      </c>
+      <c r="E81" s="5">
+        <v>2.84</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>3752</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>3739</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3738</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>3751</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>28426390</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B82" s="4" t="s">
         <v>1003</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C82" s="4" t="s">
         <v>1004</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D82" s="3">
         <v>2023</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E82" s="5">
         <v>3.42</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F82" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H82" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="I80" s="7" t="s">
+      <c r="I82" s="7" t="s">
         <v>1005</v>
       </c>
-      <c r="J80" s="7" t="s">
+      <c r="J82" s="7" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="83" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>31683230</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B83" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C83" s="4" t="s">
         <v>973</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D83" s="3">
         <v>2024</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E83" s="5">
         <v>3.33</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F83" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G83" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I83" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="J81" s="7" t="s">
+      <c r="J83" s="7" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>37452171</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>4278</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D82" s="3">
-        <v>2026</v>
-      </c>
-      <c r="E82" s="5">
-        <v>3.73</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>2140</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
-        <v>2027786</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" s="3">
-        <v>1976</v>
-      </c>
-      <c r="E83" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>4297</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4296</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>28117261</v>
+        <v>35392324</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>4276</v>
+        <v>4659</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>912</v>
+        <v>4660</v>
       </c>
       <c r="D84" s="3">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="E84" s="5">
-        <v>3.48</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>937</v>
+        <v>3.78</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>4675</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>921</v>
+        <v>4700</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>938</v>
+        <v>4658</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>919</v>
+        <v>4661</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>920</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
+        <v>37452171</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>4278</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E85" s="5">
+        <v>3.73</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>2140</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>2027786</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E86" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>4297</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>28117261</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>4276</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E87" s="5">
+        <v>3.48</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
         <v>1562086</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B88" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C88" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D88" s="3">
         <v>1982</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E88" s="5">
         <v>3.16</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F88" s="6" t="s">
         <v>952</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G88" s="4" t="s">
         <v>953</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>954</v>
       </c>
-      <c r="I85" s="7" t="s">
+      <c r="I88" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="J88" s="7" t="s">
         <v>950</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
-        <v>28649152</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="D86" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E86" s="5">
-        <v>3.47</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>786</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>25950673</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>4292</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="D87" s="3">
-        <v>2019</v>
-      </c>
-      <c r="E87" s="5">
-        <v>3.13</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>877</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>25412281</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>4292</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="D88" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E88" s="5">
-        <v>3.41</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>28518808</v>
+        <v>28649152</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>747</v>
+        <v>782</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>748</v>
+        <v>783</v>
       </c>
       <c r="D89" s="3">
         <v>2023</v>
       </c>
       <c r="E89" s="5">
+        <v>3.47</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>25950673</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D90" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E90" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>25412281</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="D91" s="3">
+        <v>2022</v>
+      </c>
+      <c r="E91" s="5">
+        <v>3.41</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>28518808</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D92" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E92" s="5">
         <v>3.08</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F92" s="6" t="s">
         <v>835</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H92" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="I89" s="7" t="s">
+      <c r="I92" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="J89" s="7" t="s">
+      <c r="J92" s="7" t="s">
         <v>750</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>24184766</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>4273</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D90" s="3">
-        <v>2020</v>
-      </c>
-      <c r="E90" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>33253932</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D91" s="3">
-        <v>1981</v>
-      </c>
-      <c r="E91" s="5">
-        <v>3.94</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>33653532</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>1861</v>
-      </c>
-      <c r="D92" s="3">
-        <v>1972</v>
-      </c>
-      <c r="E92" s="5">
-        <v>3.52</v>
-      </c>
-      <c r="F92" s="6"/>
-      <c r="G92" s="4" t="s">
-        <v>1871</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>1870</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>1862</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>6431834</v>
+        <v>24184766</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>3484</v>
+        <v>4273</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>3484</v>
+        <v>377</v>
       </c>
       <c r="D93" s="3">
-        <v>1979</v>
+        <v>2020</v>
       </c>
       <c r="E93" s="5">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>3526</v>
+        <v>378</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>3517</v>
+        <v>379</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>3516</v>
+        <v>380</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>3514</v>
+        <v>381</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>3515</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>385433</v>
+        <v>33253932</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>3484</v>
+        <v>728</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>3483</v>
+        <v>727</v>
       </c>
       <c r="D94" s="3">
         <v>1981</v>
       </c>
       <c r="E94" s="5">
+        <v>3.94</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>33653532</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D95" s="3">
+        <v>1972</v>
+      </c>
+      <c r="E95" s="5">
+        <v>3.52</v>
+      </c>
+      <c r="F95" s="6"/>
+      <c r="G95" s="4" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>6431834</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="D96" s="3">
+        <v>1979</v>
+      </c>
+      <c r="E96" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>3526</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>3517</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3516</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>3514</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>385433</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>3483</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1981</v>
+      </c>
+      <c r="E97" s="5">
         <v>3.67</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F97" s="6" t="s">
         <v>3497</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>3488</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H97" s="3" t="s">
         <v>3487</v>
       </c>
-      <c r="I94" s="7" t="s">
+      <c r="I97" s="7" t="s">
         <v>3485</v>
       </c>
-      <c r="J94" s="7" t="s">
+      <c r="J97" s="7" t="s">
         <v>3486</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+    <row r="98" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>5815845</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B98" s="4" t="s">
         <v>3484</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C98" s="4" t="s">
         <v>3543</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D98" s="3">
         <v>1986</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E98" s="5">
         <v>2.82</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F98" s="6" t="s">
         <v>3556</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G98" s="4" t="s">
         <v>3587</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H98" s="3" t="s">
         <v>3544</v>
       </c>
-      <c r="I95" s="7" t="s">
+      <c r="I98" s="7" t="s">
         <v>3554</v>
       </c>
-      <c r="J95" s="7" t="s">
+      <c r="J98" s="7" t="s">
         <v>3555</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
-        <v>3507697</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>4293</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="D96" s="3">
-        <v>1973</v>
-      </c>
-      <c r="E96" s="5">
-        <v>3.29</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
-        <v>26207852</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D97" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E97" s="5">
-        <v>3.29</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>693</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
-        <v>2782114</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>3114</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>3114</v>
-      </c>
-      <c r="D98" s="3">
-        <v>1989</v>
-      </c>
-      <c r="E98" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>3130</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>3127</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>3126</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>3128</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>3129</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>31880233</v>
+        <v>7949644</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>602</v>
+        <v>4390</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>601</v>
+        <v>4456</v>
       </c>
       <c r="D99" s="3">
         <v>1976</v>
       </c>
       <c r="E99" s="5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>628</v>
+        <v>4461</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>627</v>
+        <v>4486</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>605</v>
+        <v>4451</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>603</v>
+        <v>4463</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>28251457</v>
+        <v>2705063</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>651</v>
+        <v>4390</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>652</v>
+        <v>4482</v>
       </c>
       <c r="D100" s="3">
-        <v>2023</v>
+        <v>1979</v>
       </c>
       <c r="E100" s="5">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>663</v>
+        <v>4495</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>665</v>
+        <v>4487</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>664</v>
+        <v>4485</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>653</v>
+        <v>4484</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>10079558</v>
+        <v>4007367</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>4269</v>
+        <v>4390</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>102</v>
+        <v>4389</v>
       </c>
       <c r="D101" s="3">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="E101" s="5">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>4150</v>
+        <v>4399</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>4152</v>
+        <v>4386</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>4151</v>
+        <v>4384</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>103</v>
+        <v>4387</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>22420804</v>
+        <v>2874281</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>577</v>
+        <v>4390</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>575</v>
+        <v>4422</v>
       </c>
       <c r="D102" s="3">
-        <v>1970</v>
+        <v>1988</v>
       </c>
       <c r="E102" s="5">
-        <v>3.66</v>
+        <v>3.23</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>582</v>
+        <v>4432</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>581</v>
+        <v>4419</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>580</v>
+        <v>4418</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>578</v>
+        <v>4420</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>579</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>33527013</v>
+        <v>3507697</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>4286</v>
+        <v>4293</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>2718</v>
+        <v>715</v>
       </c>
       <c r="D103" s="3">
-        <v>2025</v>
+        <v>1973</v>
       </c>
       <c r="E103" s="5">
-        <v>3.47</v>
+        <v>3.29</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>2733</v>
+        <v>857</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>2720</v>
+        <v>716</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>2719</v>
+        <v>724</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>2731</v>
+        <v>725</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>2732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>28667458</v>
+        <v>26207852</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>529</v>
+        <v>680</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>530</v>
+        <v>681</v>
       </c>
       <c r="D104" s="3">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="E104" s="5">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>535</v>
+        <v>865</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>533</v>
+        <v>696</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>534</v>
+        <v>695</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>531</v>
+        <v>693</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>26857331</v>
+        <v>2782114</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>529</v>
+        <v>3114</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>547</v>
+        <v>3114</v>
       </c>
       <c r="D105" s="3">
+        <v>1989</v>
+      </c>
+      <c r="E105" s="5">
+        <v>3.51</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>3130</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>3127</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>3128</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>31880233</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="D106" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E106" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>28251457</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="D107" s="3">
         <v>2023</v>
       </c>
-      <c r="E105" s="5">
-        <v>3.48</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
-        <v>2598614</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>2783</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>2784</v>
-      </c>
-      <c r="D106" s="3">
-        <v>1988</v>
-      </c>
-      <c r="E106" s="5">
-        <v>3.59</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>2795</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>2797</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>2796</v>
-      </c>
-      <c r="I106" s="7" t="s">
-        <v>2798</v>
-      </c>
-      <c r="J106" s="7" t="s">
-        <v>2799</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
-        <v>11981817</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="D107" s="3">
-        <v>1996</v>
-      </c>
       <c r="E107" s="5">
-        <v>3.94</v>
+        <v>3.61</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>460</v>
+        <v>663</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>503</v>
+        <v>665</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>461</v>
+        <v>664</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>458</v>
+        <v>653</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>6748984</v>
+        <v>10079558</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>3013</v>
+        <v>4269</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>3013</v>
+        <v>102</v>
       </c>
       <c r="D108" s="3">
         <v>1978</v>
       </c>
       <c r="E108" s="5">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>3028</v>
+        <v>4150</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>3017</v>
+        <v>4152</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>3016</v>
+        <v>4151</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>3015</v>
+        <v>103</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>3014</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>29264422</v>
+        <v>22420804</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>498</v>
+        <v>577</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>498</v>
+        <v>575</v>
       </c>
       <c r="D109" s="3">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="E109" s="5">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>501</v>
+        <v>582</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>519</v>
+        <v>581</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>502</v>
+        <v>580</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>500</v>
+        <v>578</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>25695898</v>
+        <v>7340202</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>4283</v>
+        <v>4630</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>422</v>
+        <v>4631</v>
       </c>
       <c r="D110" s="3">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="E110" s="5">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>423</v>
+        <v>4640</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>418</v>
+        <v>4657</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>419</v>
+        <v>4632</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>420</v>
+        <v>4628</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>28074505</v>
+        <v>33527013</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>412</v>
+        <v>4286</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>388</v>
+        <v>2718</v>
       </c>
       <c r="D111" s="3">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E111" s="5">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>413</v>
+        <v>2733</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>416</v>
+        <v>2720</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>417</v>
+        <v>2719</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>414</v>
+        <v>2731</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>10933246</v>
+        <v>28667458</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>3154</v>
+        <v>529</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>3153</v>
+        <v>530</v>
       </c>
       <c r="D112" s="3">
-        <v>1982</v>
+        <v>2019</v>
       </c>
       <c r="E112" s="5">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>3155</v>
+        <v>535</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>3199</v>
+        <v>533</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>3150</v>
+        <v>534</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>3151</v>
+        <v>531</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>3152</v>
+        <v>532</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
+        <v>26857331</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="D113" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E113" s="5">
+        <v>3.48</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>2598614</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D114" s="3">
+        <v>1988</v>
+      </c>
+      <c r="E114" s="5">
+        <v>3.59</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>2797</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>2796</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>2798</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>11981817</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1996</v>
+      </c>
+      <c r="E115" s="5">
+        <v>3.94</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>6748984</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>3013</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E116" s="5">
+        <v>3.56</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>3028</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>3017</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>3016</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>3015</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>29264422</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1973</v>
+      </c>
+      <c r="E117" s="5">
+        <v>3.58</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>25695898</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>4283</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1974</v>
+      </c>
+      <c r="E118" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>28074505</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D119" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E119" s="5">
+        <v>3.57</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>10933246</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>3153</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1982</v>
+      </c>
+      <c r="E120" s="5">
+        <v>3.41</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>3155</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>3199</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>3151</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>646934</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B121" s="4" t="s">
         <v>3154</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C121" s="4" t="s">
         <v>3219</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D121" s="3">
         <v>1983</v>
       </c>
-      <c r="E113" s="5">
+      <c r="E121" s="5">
         <v>3.46</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F121" s="6" t="s">
         <v>3223</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G121" s="4" t="s">
         <v>4204</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="H121" s="3" t="s">
         <v>3220</v>
       </c>
-      <c r="I113" s="7" t="s">
+      <c r="I121" s="7" t="s">
         <v>3222</v>
       </c>
-      <c r="J113" s="7" t="s">
+      <c r="J121" s="7" t="s">
         <v>3221</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+    <row r="122" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
         <v>1382323</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B122" s="4" t="s">
         <v>3154</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C122" s="4" t="s">
         <v>3189</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D122" s="3">
         <v>1984</v>
       </c>
-      <c r="E114" s="5">
+      <c r="E122" s="5">
         <v>3.51</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F122" s="6" t="s">
         <v>3202</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G122" s="4" t="s">
         <v>4203</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H122" s="3" t="s">
         <v>3198</v>
       </c>
-      <c r="I114" s="7" t="s">
+      <c r="I122" s="7" t="s">
         <v>3200</v>
       </c>
-      <c r="J114" s="7" t="s">
+      <c r="J122" s="7" t="s">
         <v>3201</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
-        <v>1414305</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>3154</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>3289</v>
-      </c>
-      <c r="D115" s="3">
-        <v>1985</v>
-      </c>
-      <c r="E115" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>3301</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>4206</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>3288</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>3299</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
-        <v>4116216</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>3154</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>3254</v>
-      </c>
-      <c r="D116" s="3">
-        <v>1987</v>
-      </c>
-      <c r="E116" s="5">
-        <v>3</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>3257</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>4205</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>3258</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>3255</v>
-      </c>
-      <c r="J116" s="7" t="s">
-        <v>3256</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
-        <v>23148584</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>4284</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D117" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E117" s="5">
-        <v>3.39</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>2697</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>2686</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>2685</v>
-      </c>
-      <c r="I117" s="7" t="s">
-        <v>2683</v>
-      </c>
-      <c r="J117" s="7" t="s">
-        <v>2684</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
-        <v>4000501</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>3386</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>3414</v>
-      </c>
-      <c r="D118" s="3">
-        <v>1987</v>
-      </c>
-      <c r="E118" s="5">
-        <v>3.57</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>3426</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>4209</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>3415</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>4294</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>3389</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
-        <v>2903507</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>3386</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>3385</v>
-      </c>
-      <c r="D119" s="3">
-        <v>1989</v>
-      </c>
-      <c r="E119" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>3399</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>4208</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>3387</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>3388</v>
-      </c>
-      <c r="J119" s="7" t="s">
-        <v>3389</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>7830609</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>3446</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>3774</v>
-      </c>
-      <c r="D120" s="3">
-        <v>1985</v>
-      </c>
-      <c r="E120" s="5">
-        <v>3.38</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>3786</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>3778</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>3777</v>
-      </c>
-      <c r="I120" s="7" t="s">
-        <v>3776</v>
-      </c>
-      <c r="J120" s="7" t="s">
-        <v>3775</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
-        <v>8864393</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>3446</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>3447</v>
-      </c>
-      <c r="D121" s="3">
-        <v>1987</v>
-      </c>
-      <c r="E121" s="5">
-        <v>3.58</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>3470</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>3482</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>3481</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>3449</v>
-      </c>
-      <c r="J121" s="7" t="s">
-        <v>3448</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>2797526</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D122" s="3">
-        <v>1990</v>
-      </c>
-      <c r="E122" s="5">
-        <v>3.55</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>4295</v>
-      </c>
-      <c r="J122" s="7" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
-        <v>10867099</v>
+        <v>1414305</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>263</v>
+        <v>3154</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>264</v>
+        <v>3289</v>
       </c>
       <c r="D123" s="3">
-        <v>1992</v>
+        <v>1985</v>
       </c>
       <c r="E123" s="5">
-        <v>3.67</v>
+        <v>3.27</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>265</v>
+        <v>3301</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>266</v>
+        <v>4206</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>267</v>
+        <v>3288</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>268</v>
+        <v>3299</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <v>31700342</v>
+        <v>4116216</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>4285</v>
+        <v>3154</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>615</v>
+        <v>3254</v>
       </c>
       <c r="D124" s="3">
-        <v>2019</v>
+        <v>1987</v>
       </c>
       <c r="E124" s="5">
-        <v>3.73</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>631</v>
+        <v>3257</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>632</v>
+        <v>4205</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>633</v>
+        <v>3258</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>629</v>
+        <v>3255</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
-        <v>4428247</v>
+        <v>23148584</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>4207</v>
+        <v>4284</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>3349</v>
+        <v>2682</v>
       </c>
       <c r="D125" s="3">
-        <v>1981</v>
+        <v>2022</v>
       </c>
       <c r="E125" s="5">
         <v>3.39</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>3364</v>
+        <v>2697</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>3353</v>
+        <v>2686</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>3352</v>
+        <v>2685</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>3350</v>
+        <v>2683</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>3351</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
-        <v>12520978</v>
+        <v>4000501</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>3082</v>
+        <v>3386</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>3081</v>
+        <v>3414</v>
       </c>
       <c r="D126" s="3">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="E126" s="5">
         <v>3.57</v>
       </c>
-      <c r="F126" s="6" t="s">
-        <v>3095</v>
+      <c r="F126" s="8" t="s">
+        <v>3426</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>3086</v>
+        <v>4209</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>3083</v>
+        <v>3415</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>3084</v>
+        <v>4294</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>3085</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
-        <v>1939062</v>
+        <v>2903507</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>3051</v>
+        <v>3386</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>3051</v>
+        <v>3385</v>
       </c>
       <c r="D127" s="3">
-        <v>1977</v>
+        <v>1989</v>
       </c>
       <c r="E127" s="5">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>3062</v>
+        <v>3399</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>4385</v>
+        <v>4208</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>3052</v>
+        <v>3387</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>3049</v>
+        <v>3388</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>3050</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <v>4007367</v>
+        <v>7830609</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>4390</v>
+        <v>3446</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>4389</v>
+        <v>3774</v>
       </c>
       <c r="D128" s="3">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="E128" s="5">
-        <v>3.69</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>4399</v>
+        <v>3.38</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>3786</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>4386</v>
+        <v>3778</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>4384</v>
+        <v>3777</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>4387</v>
+        <v>3776</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>4388</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
-        <v>2874281</v>
+        <v>8864393</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>4390</v>
+        <v>3446</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>4422</v>
+        <v>3447</v>
       </c>
       <c r="D129" s="3">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E129" s="5">
-        <v>3.23</v>
+        <v>3.58</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>4432</v>
+        <v>3470</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>4419</v>
+        <v>3482</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>4418</v>
+        <v>3481</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>4420</v>
+        <v>3449</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>4421</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
-        <v>7949644</v>
+        <v>2797526</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>4390</v>
+        <v>263</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>4456</v>
+        <v>317</v>
       </c>
       <c r="D130" s="3">
-        <v>1976</v>
+        <v>1990</v>
       </c>
       <c r="E130" s="5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>4461</v>
+        <v>315</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>4486</v>
+        <v>333</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>4451</v>
+        <v>316</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>4463</v>
+        <v>4295</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>4462</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
-        <v>2705063</v>
+        <v>10867099</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>4390</v>
+        <v>263</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>4482</v>
+        <v>264</v>
       </c>
       <c r="D131" s="3">
-        <v>1979</v>
+        <v>1992</v>
       </c>
       <c r="E131" s="5">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>4495</v>
+        <v>265</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>4487</v>
+        <v>266</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>4485</v>
+        <v>267</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>4484</v>
+        <v>268</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>4483</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
-        <v>31841081</v>
+        <v>31700342</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>4519</v>
+        <v>4285</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>4520</v>
+        <v>615</v>
       </c>
       <c r="D132" s="3">
-        <v>1972</v>
+        <v>2019</v>
       </c>
       <c r="E132" s="5">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>4546</v>
+        <v>631</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>4571</v>
+        <v>632</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>4518</v>
+        <v>633</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>4521</v>
+        <v>629</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>4522</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
-        <v>37111626</v>
+        <v>4428247</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>4600</v>
+        <v>4207</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>4601</v>
+        <v>3349</v>
       </c>
       <c r="D133" s="3">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="E133" s="5">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>4609</v>
+        <v>3364</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>4598</v>
+        <v>3353</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>4599</v>
+        <v>3352</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>4596</v>
+        <v>3350</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>4597</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+        <v>3351</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
-        <v>7340202</v>
+        <v>12520978</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>4630</v>
+        <v>3082</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>4631</v>
+        <v>3081</v>
       </c>
       <c r="D134" s="3">
+        <v>1982</v>
+      </c>
+      <c r="E134" s="5">
+        <v>3.57</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>3095</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>3086</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>3083</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>3084</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>1939062</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>3051</v>
+      </c>
+      <c r="D135" s="3">
         <v>1977</v>
       </c>
-      <c r="E134" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>4640</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>4657</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>4632</v>
-      </c>
-      <c r="I134" s="7" t="s">
-        <v>4628</v>
-      </c>
-      <c r="J134" s="7" t="s">
-        <v>4629</v>
+      <c r="E135" s="5">
+        <v>3.21</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>3062</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>4385</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="I135" s="7" t="s">
+        <v>3049</v>
+      </c>
+      <c r="J135" s="7" t="s">
+        <v>3050</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J127">
-    <sortCondition ref="B2:B127"/>
-    <sortCondition ref="D2:D127"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J135">
+    <sortCondition ref="B2:B135"/>
+    <sortCondition ref="D2:D135"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="I82" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
-    <hyperlink ref="J82" r:id="rId2" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
-    <hyperlink ref="I48" r:id="rId3" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
-    <hyperlink ref="J48" r:id="rId4" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
-    <hyperlink ref="I18" r:id="rId5" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
-    <hyperlink ref="J18" r:id="rId6" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
-    <hyperlink ref="I101" r:id="rId7" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
-    <hyperlink ref="J101" r:id="rId8" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
-    <hyperlink ref="I83" r:id="rId9" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
-    <hyperlink ref="J83" r:id="rId10" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
+    <hyperlink ref="I85" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
+    <hyperlink ref="J85" r:id="rId2" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
+    <hyperlink ref="I50" r:id="rId3" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
+    <hyperlink ref="J50" r:id="rId4" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
+    <hyperlink ref="I19" r:id="rId5" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
+    <hyperlink ref="J19" r:id="rId6" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
+    <hyperlink ref="I108" r:id="rId7" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
+    <hyperlink ref="J108" r:id="rId8" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
+    <hyperlink ref="I86" r:id="rId9" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
+    <hyperlink ref="J86" r:id="rId10" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
     <hyperlink ref="I2" r:id="rId11" xr:uid="{7D09EF64-81E8-4700-B5A5-D38E3A5C492A}"/>
-    <hyperlink ref="I31" r:id="rId12" xr:uid="{BB1EEAD6-C614-40E2-A50B-1EEB4DCC9896}"/>
+    <hyperlink ref="I32" r:id="rId12" xr:uid="{BB1EEAD6-C614-40E2-A50B-1EEB4DCC9896}"/>
     <hyperlink ref="J2" r:id="rId13" xr:uid="{49D10AEE-6D1A-4296-92C2-D587EAECD209}"/>
-    <hyperlink ref="J31" r:id="rId14" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
-    <hyperlink ref="I36" r:id="rId15" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
-    <hyperlink ref="J36" r:id="rId16" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
+    <hyperlink ref="J32" r:id="rId14" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
+    <hyperlink ref="I37" r:id="rId15" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
+    <hyperlink ref="J37" r:id="rId16" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
     <hyperlink ref="I3" r:id="rId17" xr:uid="{41088898-623F-47B4-BF91-B4B1CD818D4E}"/>
     <hyperlink ref="J3" r:id="rId18" xr:uid="{E113C2CF-CD08-4D0D-B347-3943034BA748}"/>
-    <hyperlink ref="I5" r:id="rId19" xr:uid="{16FF05EB-D3D0-4933-A9A7-1991D2A4347A}"/>
-    <hyperlink ref="J5" r:id="rId20" xr:uid="{7F3FDF6A-4AF3-43DA-A4B5-C708BEBBC5AC}"/>
-    <hyperlink ref="I14" r:id="rId21" xr:uid="{9D7EA281-7164-4EC6-8613-E6D1AAA72828}"/>
-    <hyperlink ref="J14" r:id="rId22" xr:uid="{8EE506D2-8E16-47D1-A8EC-6F5329B2DA47}"/>
-    <hyperlink ref="I35" r:id="rId23" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
-    <hyperlink ref="I37" r:id="rId24" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
-    <hyperlink ref="J37" r:id="rId25" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
-    <hyperlink ref="I38" r:id="rId26" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
-    <hyperlink ref="J38" r:id="rId27" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
-    <hyperlink ref="J122" r:id="rId28" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
-    <hyperlink ref="I65" r:id="rId29" xr:uid="{21285B48-6B68-40F0-9B76-D4C8B9229EA4}"/>
-    <hyperlink ref="J65" r:id="rId30" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
-    <hyperlink ref="I90" r:id="rId31" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
-    <hyperlink ref="J90" r:id="rId32" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
-    <hyperlink ref="I111" r:id="rId33" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
-    <hyperlink ref="J111" r:id="rId34" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
-    <hyperlink ref="I110" r:id="rId35" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
-    <hyperlink ref="J110" r:id="rId36" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
-    <hyperlink ref="I107" r:id="rId37" xr:uid="{CA3FCADF-3756-4A65-8A98-0AB7143633F2}"/>
-    <hyperlink ref="J107" r:id="rId38" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
-    <hyperlink ref="J109" r:id="rId39" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
-    <hyperlink ref="I109" r:id="rId40" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
-    <hyperlink ref="I104" r:id="rId41" xr:uid="{DF641E30-EFBA-494C-88DD-76EF1F14F9A5}"/>
-    <hyperlink ref="J104" r:id="rId42" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
-    <hyperlink ref="J105" r:id="rId43" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
-    <hyperlink ref="I105" r:id="rId44" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
-    <hyperlink ref="I102" r:id="rId45" xr:uid="{87C4E708-9703-429B-AD5F-DAAD8F0949D0}"/>
-    <hyperlink ref="J102" r:id="rId46" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
-    <hyperlink ref="I99" r:id="rId47" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
-    <hyperlink ref="J99" r:id="rId48" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
-    <hyperlink ref="I124" r:id="rId49" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
-    <hyperlink ref="J124" r:id="rId50" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
-    <hyperlink ref="I100" r:id="rId51" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
-    <hyperlink ref="J100" r:id="rId52" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
-    <hyperlink ref="I97" r:id="rId53" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
-    <hyperlink ref="J97" r:id="rId54" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
-    <hyperlink ref="I96" r:id="rId55" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
-    <hyperlink ref="J96" r:id="rId56" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
-    <hyperlink ref="I91" r:id="rId57" xr:uid="{F3AD3E6F-CC74-49B0-ADE8-22126BE46225}"/>
-    <hyperlink ref="J91" r:id="rId58" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
-    <hyperlink ref="I89" r:id="rId59" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
-    <hyperlink ref="J89" r:id="rId60" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
-    <hyperlink ref="I86" r:id="rId61" xr:uid="{3089CEA5-B4D3-4CF8-8369-656AF5B6317D}"/>
-    <hyperlink ref="J86" r:id="rId62" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
-    <hyperlink ref="J88" r:id="rId63" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
-    <hyperlink ref="I88" r:id="rId64" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
-    <hyperlink ref="I87" r:id="rId65" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
-    <hyperlink ref="J87" r:id="rId66" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
-    <hyperlink ref="I84" r:id="rId67" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
-    <hyperlink ref="J84" r:id="rId68" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
-    <hyperlink ref="J85" r:id="rId69" xr:uid="{5DC2641E-2387-4BA6-9A88-B4A6B827B909}"/>
-    <hyperlink ref="I85" r:id="rId70" xr:uid="{91790331-D35E-4067-B038-263AEF6060A9}"/>
-    <hyperlink ref="J81" r:id="rId71" xr:uid="{F738125C-E6C4-4EEB-8C06-4A5232B3EE11}"/>
-    <hyperlink ref="I81" r:id="rId72" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
-    <hyperlink ref="I80" r:id="rId73" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
-    <hyperlink ref="J80" r:id="rId74" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
-    <hyperlink ref="I78" r:id="rId75" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
-    <hyperlink ref="J78" r:id="rId76" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
-    <hyperlink ref="J77" r:id="rId77" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
-    <hyperlink ref="I77" r:id="rId78" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
-    <hyperlink ref="J75" r:id="rId79" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
-    <hyperlink ref="I75" r:id="rId80" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
-    <hyperlink ref="I74" r:id="rId81" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
-    <hyperlink ref="J74" r:id="rId82" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
-    <hyperlink ref="J73" r:id="rId83" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
-    <hyperlink ref="I73" r:id="rId84" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
-    <hyperlink ref="J72" r:id="rId85" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
-    <hyperlink ref="I72" r:id="rId86" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
-    <hyperlink ref="I71" r:id="rId87" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
-    <hyperlink ref="J71" r:id="rId88" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
-    <hyperlink ref="I70" r:id="rId89" xr:uid="{0AECC585-C22C-466A-9DD8-680618CE482C}"/>
-    <hyperlink ref="J70" r:id="rId90" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
-    <hyperlink ref="J67" r:id="rId91" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
-    <hyperlink ref="I67" r:id="rId92" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
-    <hyperlink ref="J64" r:id="rId93" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
-    <hyperlink ref="I64" r:id="rId94" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
-    <hyperlink ref="J63" r:id="rId95" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
-    <hyperlink ref="I63" r:id="rId96" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
-    <hyperlink ref="J61" r:id="rId97" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
-    <hyperlink ref="I61" r:id="rId98" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
-    <hyperlink ref="J60" r:id="rId99" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
-    <hyperlink ref="I60" r:id="rId100" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
-    <hyperlink ref="J58" r:id="rId101" xr:uid="{36CEEA26-13A0-4AFA-8ED6-B4B6BC4B51BA}"/>
-    <hyperlink ref="I58" r:id="rId102" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
-    <hyperlink ref="J32" r:id="rId103" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
-    <hyperlink ref="I32" r:id="rId104" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
-    <hyperlink ref="I56" r:id="rId105" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
-    <hyperlink ref="J56" r:id="rId106" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
-    <hyperlink ref="I57" r:id="rId107" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
-    <hyperlink ref="J57" r:id="rId108" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
-    <hyperlink ref="I54" r:id="rId109" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
-    <hyperlink ref="J54" r:id="rId110" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
-    <hyperlink ref="I52" r:id="rId111" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
-    <hyperlink ref="J52" r:id="rId112" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
-    <hyperlink ref="I51" r:id="rId113" xr:uid="{721CF701-F1E2-4D7D-BC9E-45C800A11082}"/>
-    <hyperlink ref="J51" r:id="rId114" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
-    <hyperlink ref="I6" r:id="rId115" xr:uid="{460B13BE-9FBD-4212-989D-A38BF444C977}"/>
-    <hyperlink ref="J6" r:id="rId116" xr:uid="{F80F1184-6004-4DE3-A74B-2FA197532CAD}"/>
-    <hyperlink ref="I9" r:id="rId117" xr:uid="{4231DB13-C70E-4D21-B210-8DDD89D2EE71}"/>
-    <hyperlink ref="J9" r:id="rId118" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
-    <hyperlink ref="I92" r:id="rId119" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
-    <hyperlink ref="J92" r:id="rId120" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
-    <hyperlink ref="I8" r:id="rId121" xr:uid="{5C8F2870-5E10-4B34-8BCC-743C5F27272D}"/>
-    <hyperlink ref="J8" r:id="rId122" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
-    <hyperlink ref="I10" r:id="rId123" xr:uid="{B71FE562-A9A6-4B3C-AB49-50BB818D223D}"/>
-    <hyperlink ref="J10" r:id="rId124" xr:uid="{48B641A4-17C1-4191-8CED-5E5659D92591}"/>
-    <hyperlink ref="I7" r:id="rId125" xr:uid="{BF0EC9E5-8719-4153-9E86-32829F330A56}"/>
-    <hyperlink ref="J7" r:id="rId126" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
-    <hyperlink ref="I11" r:id="rId127" xr:uid="{1D827E8B-5090-4D3B-8D5D-D405D16061B2}"/>
-    <hyperlink ref="J11" r:id="rId128" xr:uid="{01F1AB04-96C0-4051-9DE9-1884E1425122}"/>
-    <hyperlink ref="I17" r:id="rId129" xr:uid="{1890E57B-E8F7-4840-9572-DFEA56597C1F}"/>
-    <hyperlink ref="J17" r:id="rId130" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
-    <hyperlink ref="I15" r:id="rId131" xr:uid="{AFDCBC25-6599-4F55-99D2-8913687FB136}"/>
-    <hyperlink ref="J15" r:id="rId132" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
-    <hyperlink ref="I12" r:id="rId133" xr:uid="{5E8073D0-D198-4EF7-B401-0DAE1D13CFF4}"/>
-    <hyperlink ref="J12" r:id="rId134" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
-    <hyperlink ref="I13" r:id="rId135" xr:uid="{BD740605-5FB0-4AEE-B015-353A212878C4}"/>
-    <hyperlink ref="J13" r:id="rId136" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
-    <hyperlink ref="I30" r:id="rId137" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
-    <hyperlink ref="J30" r:id="rId138" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
-    <hyperlink ref="I28" r:id="rId139" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
-    <hyperlink ref="J28" r:id="rId140" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
-    <hyperlink ref="J21" r:id="rId141" xr:uid="{0EA49793-A85B-4792-89B2-B1C8F3B131B4}"/>
-    <hyperlink ref="I21" r:id="rId142" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
-    <hyperlink ref="J22" r:id="rId143" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
-    <hyperlink ref="I22" r:id="rId144" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
-    <hyperlink ref="I23" r:id="rId145" xr:uid="{764AE888-2456-4D6C-B45F-9B2E88E39CFB}"/>
-    <hyperlink ref="I19" r:id="rId146" xr:uid="{67194D02-2892-4E14-8E03-07992EAC0C02}"/>
-    <hyperlink ref="J19" r:id="rId147" xr:uid="{C8E04EB8-2ACF-4142-A3C6-5AE9F3584ECD}"/>
-    <hyperlink ref="J20" r:id="rId148" xr:uid="{878F8657-2717-44A5-8B6C-025F2EE420EB}"/>
-    <hyperlink ref="I20" r:id="rId149" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
-    <hyperlink ref="I27" r:id="rId150" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
-    <hyperlink ref="J27" r:id="rId151" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
-    <hyperlink ref="I24" r:id="rId152" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
-    <hyperlink ref="J24" r:id="rId153" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
-    <hyperlink ref="J29" r:id="rId154" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
-    <hyperlink ref="I29" r:id="rId155" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
-    <hyperlink ref="I33" r:id="rId156" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
-    <hyperlink ref="J33" r:id="rId157" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
-    <hyperlink ref="I40" r:id="rId158" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
-    <hyperlink ref="J40" r:id="rId159" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
-    <hyperlink ref="J44" r:id="rId160" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
-    <hyperlink ref="I44" r:id="rId161" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
-    <hyperlink ref="I117" r:id="rId162" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
-    <hyperlink ref="J117" r:id="rId163" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
-    <hyperlink ref="I103" r:id="rId164" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
-    <hyperlink ref="J103" r:id="rId165" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
-    <hyperlink ref="J16" r:id="rId166" xr:uid="{76D67995-A6ED-43F5-90F5-FB88B787D5F1}"/>
-    <hyperlink ref="I16" r:id="rId167" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
-    <hyperlink ref="I106" r:id="rId168" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
-    <hyperlink ref="J106" r:id="rId169" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
-    <hyperlink ref="J66" r:id="rId170" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
-    <hyperlink ref="I66" r:id="rId171" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
-    <hyperlink ref="I49" r:id="rId172" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
-    <hyperlink ref="J49" r:id="rId173" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
-    <hyperlink ref="I42" r:id="rId174" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
-    <hyperlink ref="J42" r:id="rId175" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
-    <hyperlink ref="J39" r:id="rId176" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
-    <hyperlink ref="I39" r:id="rId177" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
-    <hyperlink ref="J41" r:id="rId178" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
-    <hyperlink ref="I41" r:id="rId179" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
-    <hyperlink ref="J108" r:id="rId180" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
-    <hyperlink ref="I108" r:id="rId181" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
-    <hyperlink ref="I127" r:id="rId182" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
-    <hyperlink ref="J127" r:id="rId183" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
-    <hyperlink ref="I126" r:id="rId184" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
-    <hyperlink ref="J126" r:id="rId185" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
-    <hyperlink ref="I98" r:id="rId186" xr:uid="{83583B05-7171-47AC-AF11-32B133FFE3DA}"/>
-    <hyperlink ref="J98" r:id="rId187" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
-    <hyperlink ref="I112" r:id="rId188" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
-    <hyperlink ref="J112" r:id="rId189" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
-    <hyperlink ref="I114" r:id="rId190" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
-    <hyperlink ref="J114" r:id="rId191" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
-    <hyperlink ref="J113" r:id="rId192" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
-    <hyperlink ref="I113" r:id="rId193" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
-    <hyperlink ref="I116" r:id="rId194" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
-    <hyperlink ref="J116" r:id="rId195" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
-    <hyperlink ref="I115" r:id="rId196" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
-    <hyperlink ref="J115" r:id="rId197" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
-    <hyperlink ref="I55" r:id="rId198" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
-    <hyperlink ref="J55" r:id="rId199" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
-    <hyperlink ref="I125" r:id="rId200" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
-    <hyperlink ref="J125" r:id="rId201" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
-    <hyperlink ref="I119" r:id="rId202" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
-    <hyperlink ref="J119" r:id="rId203" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
-    <hyperlink ref="J118" r:id="rId204" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
-    <hyperlink ref="J121" r:id="rId205" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
-    <hyperlink ref="I121" r:id="rId206" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
-    <hyperlink ref="I94" r:id="rId207" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
-    <hyperlink ref="J94" r:id="rId208" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
-    <hyperlink ref="I93" r:id="rId209" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
-    <hyperlink ref="J93" r:id="rId210" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
-    <hyperlink ref="I95" r:id="rId211" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
-    <hyperlink ref="J95" r:id="rId212" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
-    <hyperlink ref="I25" r:id="rId213" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
-    <hyperlink ref="J25" r:id="rId214" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
-    <hyperlink ref="I26" r:id="rId215" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
-    <hyperlink ref="J26" r:id="rId216" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
-    <hyperlink ref="I62" r:id="rId217" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
-    <hyperlink ref="J62" r:id="rId218" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
-    <hyperlink ref="J68" r:id="rId219" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
-    <hyperlink ref="I68" r:id="rId220" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
-    <hyperlink ref="I69" r:id="rId221" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
-    <hyperlink ref="J69" r:id="rId222" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
-    <hyperlink ref="J79" r:id="rId223" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
-    <hyperlink ref="I79" r:id="rId224" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
-    <hyperlink ref="J120" r:id="rId225" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
-    <hyperlink ref="I120" r:id="rId226" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
-    <hyperlink ref="I59" r:id="rId227" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
-    <hyperlink ref="J59" r:id="rId228" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
-    <hyperlink ref="I53" r:id="rId229" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
-    <hyperlink ref="J53" r:id="rId230" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
-    <hyperlink ref="J76" r:id="rId231" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
-    <hyperlink ref="I76" r:id="rId232" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
-    <hyperlink ref="I46" r:id="rId233" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
-    <hyperlink ref="J46" r:id="rId234" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
-    <hyperlink ref="I47" r:id="rId235" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
-    <hyperlink ref="J47" r:id="rId236" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
-    <hyperlink ref="I50" r:id="rId237" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
-    <hyperlink ref="J50" r:id="rId238" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
-    <hyperlink ref="I43" r:id="rId239" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
-    <hyperlink ref="J43" r:id="rId240" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
-    <hyperlink ref="I45" r:id="rId241" xr:uid="{F619EC4F-CE2B-4A3F-A177-258B37F94B75}"/>
-    <hyperlink ref="J45" r:id="rId242" xr:uid="{16154418-6F7F-4716-B182-4CD246E54171}"/>
-    <hyperlink ref="I34" r:id="rId243" xr:uid="{E9BFACD2-2358-4D6F-8475-85410D79F5A9}"/>
-    <hyperlink ref="J34" r:id="rId244" xr:uid="{EBB7510F-0BE0-4317-9B06-1D95171523D6}"/>
-    <hyperlink ref="I118" r:id="rId245" xr:uid="{45C41464-28AE-4668-AC10-B5CD2C5D57A9}"/>
-    <hyperlink ref="I122" r:id="rId246" xr:uid="{15ED860D-2D4B-4897-97C4-651CA00D92FA}"/>
-    <hyperlink ref="J35" r:id="rId247" xr:uid="{5CF69990-5819-4326-B945-ED2995B498CF}"/>
+    <hyperlink ref="I6" r:id="rId19" xr:uid="{16FF05EB-D3D0-4933-A9A7-1991D2A4347A}"/>
+    <hyperlink ref="J6" r:id="rId20" xr:uid="{7F3FDF6A-4AF3-43DA-A4B5-C708BEBBC5AC}"/>
+    <hyperlink ref="I15" r:id="rId21" xr:uid="{9D7EA281-7164-4EC6-8613-E6D1AAA72828}"/>
+    <hyperlink ref="J15" r:id="rId22" xr:uid="{8EE506D2-8E16-47D1-A8EC-6F5329B2DA47}"/>
+    <hyperlink ref="I36" r:id="rId23" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
+    <hyperlink ref="I38" r:id="rId24" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
+    <hyperlink ref="J38" r:id="rId25" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
+    <hyperlink ref="I39" r:id="rId26" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
+    <hyperlink ref="J39" r:id="rId27" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
+    <hyperlink ref="J130" r:id="rId28" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
+    <hyperlink ref="I67" r:id="rId29" xr:uid="{21285B48-6B68-40F0-9B76-D4C8B9229EA4}"/>
+    <hyperlink ref="J67" r:id="rId30" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
+    <hyperlink ref="I93" r:id="rId31" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
+    <hyperlink ref="J93" r:id="rId32" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
+    <hyperlink ref="I119" r:id="rId33" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
+    <hyperlink ref="J119" r:id="rId34" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
+    <hyperlink ref="I118" r:id="rId35" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
+    <hyperlink ref="J118" r:id="rId36" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
+    <hyperlink ref="I115" r:id="rId37" xr:uid="{CA3FCADF-3756-4A65-8A98-0AB7143633F2}"/>
+    <hyperlink ref="J115" r:id="rId38" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
+    <hyperlink ref="J117" r:id="rId39" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
+    <hyperlink ref="I117" r:id="rId40" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
+    <hyperlink ref="I112" r:id="rId41" xr:uid="{DF641E30-EFBA-494C-88DD-76EF1F14F9A5}"/>
+    <hyperlink ref="J112" r:id="rId42" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
+    <hyperlink ref="J113" r:id="rId43" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
+    <hyperlink ref="I113" r:id="rId44" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
+    <hyperlink ref="I109" r:id="rId45" xr:uid="{87C4E708-9703-429B-AD5F-DAAD8F0949D0}"/>
+    <hyperlink ref="J109" r:id="rId46" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
+    <hyperlink ref="I106" r:id="rId47" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
+    <hyperlink ref="J106" r:id="rId48" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
+    <hyperlink ref="I132" r:id="rId49" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
+    <hyperlink ref="J132" r:id="rId50" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
+    <hyperlink ref="I107" r:id="rId51" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
+    <hyperlink ref="J107" r:id="rId52" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
+    <hyperlink ref="I104" r:id="rId53" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
+    <hyperlink ref="J104" r:id="rId54" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
+    <hyperlink ref="I103" r:id="rId55" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
+    <hyperlink ref="J103" r:id="rId56" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
+    <hyperlink ref="I94" r:id="rId57" xr:uid="{F3AD3E6F-CC74-49B0-ADE8-22126BE46225}"/>
+    <hyperlink ref="J94" r:id="rId58" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
+    <hyperlink ref="I92" r:id="rId59" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
+    <hyperlink ref="J92" r:id="rId60" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
+    <hyperlink ref="I89" r:id="rId61" xr:uid="{3089CEA5-B4D3-4CF8-8369-656AF5B6317D}"/>
+    <hyperlink ref="J89" r:id="rId62" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
+    <hyperlink ref="J91" r:id="rId63" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
+    <hyperlink ref="I91" r:id="rId64" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
+    <hyperlink ref="I90" r:id="rId65" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
+    <hyperlink ref="J90" r:id="rId66" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
+    <hyperlink ref="I87" r:id="rId67" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
+    <hyperlink ref="J87" r:id="rId68" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
+    <hyperlink ref="J88" r:id="rId69" xr:uid="{5DC2641E-2387-4BA6-9A88-B4A6B827B909}"/>
+    <hyperlink ref="I88" r:id="rId70" xr:uid="{91790331-D35E-4067-B038-263AEF6060A9}"/>
+    <hyperlink ref="J83" r:id="rId71" xr:uid="{F738125C-E6C4-4EEB-8C06-4A5232B3EE11}"/>
+    <hyperlink ref="I83" r:id="rId72" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
+    <hyperlink ref="I82" r:id="rId73" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
+    <hyperlink ref="J82" r:id="rId74" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
+    <hyperlink ref="I80" r:id="rId75" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
+    <hyperlink ref="J80" r:id="rId76" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
+    <hyperlink ref="J79" r:id="rId77" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
+    <hyperlink ref="I79" r:id="rId78" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
+    <hyperlink ref="J77" r:id="rId79" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
+    <hyperlink ref="I77" r:id="rId80" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
+    <hyperlink ref="I76" r:id="rId81" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
+    <hyperlink ref="J76" r:id="rId82" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
+    <hyperlink ref="J75" r:id="rId83" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
+    <hyperlink ref="I75" r:id="rId84" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
+    <hyperlink ref="J74" r:id="rId85" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
+    <hyperlink ref="I74" r:id="rId86" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
+    <hyperlink ref="I73" r:id="rId87" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
+    <hyperlink ref="J73" r:id="rId88" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
+    <hyperlink ref="I72" r:id="rId89" xr:uid="{0AECC585-C22C-466A-9DD8-680618CE482C}"/>
+    <hyperlink ref="J72" r:id="rId90" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
+    <hyperlink ref="J69" r:id="rId91" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
+    <hyperlink ref="I69" r:id="rId92" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
+    <hyperlink ref="J66" r:id="rId93" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
+    <hyperlink ref="I66" r:id="rId94" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
+    <hyperlink ref="J65" r:id="rId95" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
+    <hyperlink ref="I65" r:id="rId96" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
+    <hyperlink ref="J63" r:id="rId97" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
+    <hyperlink ref="I63" r:id="rId98" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
+    <hyperlink ref="J62" r:id="rId99" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
+    <hyperlink ref="I62" r:id="rId100" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
+    <hyperlink ref="J60" r:id="rId101" xr:uid="{36CEEA26-13A0-4AFA-8ED6-B4B6BC4B51BA}"/>
+    <hyperlink ref="I60" r:id="rId102" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
+    <hyperlink ref="J33" r:id="rId103" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
+    <hyperlink ref="I33" r:id="rId104" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
+    <hyperlink ref="I58" r:id="rId105" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
+    <hyperlink ref="J58" r:id="rId106" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
+    <hyperlink ref="I59" r:id="rId107" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
+    <hyperlink ref="J59" r:id="rId108" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
+    <hyperlink ref="I56" r:id="rId109" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
+    <hyperlink ref="J56" r:id="rId110" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
+    <hyperlink ref="I54" r:id="rId111" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
+    <hyperlink ref="J54" r:id="rId112" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
+    <hyperlink ref="I53" r:id="rId113" xr:uid="{721CF701-F1E2-4D7D-BC9E-45C800A11082}"/>
+    <hyperlink ref="J53" r:id="rId114" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
+    <hyperlink ref="I7" r:id="rId115" xr:uid="{460B13BE-9FBD-4212-989D-A38BF444C977}"/>
+    <hyperlink ref="J7" r:id="rId116" xr:uid="{F80F1184-6004-4DE3-A74B-2FA197532CAD}"/>
+    <hyperlink ref="I10" r:id="rId117" xr:uid="{4231DB13-C70E-4D21-B210-8DDD89D2EE71}"/>
+    <hyperlink ref="J10" r:id="rId118" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
+    <hyperlink ref="I95" r:id="rId119" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
+    <hyperlink ref="J95" r:id="rId120" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
+    <hyperlink ref="I9" r:id="rId121" xr:uid="{5C8F2870-5E10-4B34-8BCC-743C5F27272D}"/>
+    <hyperlink ref="J9" r:id="rId122" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
+    <hyperlink ref="I11" r:id="rId123" xr:uid="{B71FE562-A9A6-4B3C-AB49-50BB818D223D}"/>
+    <hyperlink ref="J11" r:id="rId124" xr:uid="{48B641A4-17C1-4191-8CED-5E5659D92591}"/>
+    <hyperlink ref="I8" r:id="rId125" xr:uid="{BF0EC9E5-8719-4153-9E86-32829F330A56}"/>
+    <hyperlink ref="J8" r:id="rId126" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
+    <hyperlink ref="I12" r:id="rId127" xr:uid="{1D827E8B-5090-4D3B-8D5D-D405D16061B2}"/>
+    <hyperlink ref="J12" r:id="rId128" xr:uid="{01F1AB04-96C0-4051-9DE9-1884E1425122}"/>
+    <hyperlink ref="I18" r:id="rId129" xr:uid="{1890E57B-E8F7-4840-9572-DFEA56597C1F}"/>
+    <hyperlink ref="J18" r:id="rId130" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
+    <hyperlink ref="I16" r:id="rId131" xr:uid="{AFDCBC25-6599-4F55-99D2-8913687FB136}"/>
+    <hyperlink ref="J16" r:id="rId132" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
+    <hyperlink ref="I13" r:id="rId133" xr:uid="{5E8073D0-D198-4EF7-B401-0DAE1D13CFF4}"/>
+    <hyperlink ref="J13" r:id="rId134" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
+    <hyperlink ref="I14" r:id="rId135" xr:uid="{BD740605-5FB0-4AEE-B015-353A212878C4}"/>
+    <hyperlink ref="J14" r:id="rId136" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
+    <hyperlink ref="I31" r:id="rId137" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
+    <hyperlink ref="J31" r:id="rId138" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
+    <hyperlink ref="I29" r:id="rId139" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
+    <hyperlink ref="J29" r:id="rId140" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
+    <hyperlink ref="J22" r:id="rId141" xr:uid="{0EA49793-A85B-4792-89B2-B1C8F3B131B4}"/>
+    <hyperlink ref="I22" r:id="rId142" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
+    <hyperlink ref="J23" r:id="rId143" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
+    <hyperlink ref="I23" r:id="rId144" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
+    <hyperlink ref="I24" r:id="rId145" xr:uid="{764AE888-2456-4D6C-B45F-9B2E88E39CFB}"/>
+    <hyperlink ref="I20" r:id="rId146" xr:uid="{67194D02-2892-4E14-8E03-07992EAC0C02}"/>
+    <hyperlink ref="J20" r:id="rId147" xr:uid="{C8E04EB8-2ACF-4142-A3C6-5AE9F3584ECD}"/>
+    <hyperlink ref="J21" r:id="rId148" xr:uid="{878F8657-2717-44A5-8B6C-025F2EE420EB}"/>
+    <hyperlink ref="I21" r:id="rId149" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
+    <hyperlink ref="I28" r:id="rId150" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
+    <hyperlink ref="J28" r:id="rId151" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
+    <hyperlink ref="I25" r:id="rId152" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
+    <hyperlink ref="J25" r:id="rId153" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
+    <hyperlink ref="J30" r:id="rId154" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
+    <hyperlink ref="I30" r:id="rId155" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
+    <hyperlink ref="I34" r:id="rId156" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
+    <hyperlink ref="J34" r:id="rId157" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
+    <hyperlink ref="I41" r:id="rId158" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
+    <hyperlink ref="J41" r:id="rId159" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
+    <hyperlink ref="J45" r:id="rId160" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
+    <hyperlink ref="I45" r:id="rId161" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
+    <hyperlink ref="I125" r:id="rId162" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
+    <hyperlink ref="J125" r:id="rId163" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
+    <hyperlink ref="I111" r:id="rId164" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
+    <hyperlink ref="J111" r:id="rId165" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
+    <hyperlink ref="J17" r:id="rId166" xr:uid="{76D67995-A6ED-43F5-90F5-FB88B787D5F1}"/>
+    <hyperlink ref="I17" r:id="rId167" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
+    <hyperlink ref="I114" r:id="rId168" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
+    <hyperlink ref="J114" r:id="rId169" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
+    <hyperlink ref="J68" r:id="rId170" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
+    <hyperlink ref="I68" r:id="rId171" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
+    <hyperlink ref="I51" r:id="rId172" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
+    <hyperlink ref="J51" r:id="rId173" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
+    <hyperlink ref="I43" r:id="rId174" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
+    <hyperlink ref="J43" r:id="rId175" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
+    <hyperlink ref="J40" r:id="rId176" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
+    <hyperlink ref="I40" r:id="rId177" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
+    <hyperlink ref="J42" r:id="rId178" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
+    <hyperlink ref="I42" r:id="rId179" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
+    <hyperlink ref="J116" r:id="rId180" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
+    <hyperlink ref="I116" r:id="rId181" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
+    <hyperlink ref="I135" r:id="rId182" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
+    <hyperlink ref="J135" r:id="rId183" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
+    <hyperlink ref="I134" r:id="rId184" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
+    <hyperlink ref="J134" r:id="rId185" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
+    <hyperlink ref="I105" r:id="rId186" xr:uid="{83583B05-7171-47AC-AF11-32B133FFE3DA}"/>
+    <hyperlink ref="J105" r:id="rId187" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
+    <hyperlink ref="I120" r:id="rId188" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
+    <hyperlink ref="J120" r:id="rId189" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
+    <hyperlink ref="I122" r:id="rId190" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
+    <hyperlink ref="J122" r:id="rId191" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
+    <hyperlink ref="J121" r:id="rId192" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
+    <hyperlink ref="I121" r:id="rId193" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
+    <hyperlink ref="I124" r:id="rId194" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
+    <hyperlink ref="J124" r:id="rId195" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
+    <hyperlink ref="I123" r:id="rId196" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
+    <hyperlink ref="J123" r:id="rId197" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
+    <hyperlink ref="I57" r:id="rId198" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
+    <hyperlink ref="J57" r:id="rId199" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
+    <hyperlink ref="I133" r:id="rId200" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
+    <hyperlink ref="J133" r:id="rId201" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
+    <hyperlink ref="I127" r:id="rId202" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
+    <hyperlink ref="J127" r:id="rId203" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
+    <hyperlink ref="J126" r:id="rId204" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
+    <hyperlink ref="J129" r:id="rId205" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
+    <hyperlink ref="I129" r:id="rId206" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
+    <hyperlink ref="I97" r:id="rId207" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
+    <hyperlink ref="J97" r:id="rId208" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
+    <hyperlink ref="I96" r:id="rId209" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
+    <hyperlink ref="J96" r:id="rId210" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
+    <hyperlink ref="I98" r:id="rId211" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
+    <hyperlink ref="J98" r:id="rId212" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
+    <hyperlink ref="I26" r:id="rId213" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
+    <hyperlink ref="J26" r:id="rId214" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
+    <hyperlink ref="I27" r:id="rId215" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
+    <hyperlink ref="J27" r:id="rId216" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
+    <hyperlink ref="I64" r:id="rId217" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
+    <hyperlink ref="J64" r:id="rId218" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
+    <hyperlink ref="J70" r:id="rId219" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
+    <hyperlink ref="I70" r:id="rId220" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
+    <hyperlink ref="I71" r:id="rId221" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
+    <hyperlink ref="J71" r:id="rId222" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
+    <hyperlink ref="J81" r:id="rId223" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
+    <hyperlink ref="I81" r:id="rId224" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
+    <hyperlink ref="J128" r:id="rId225" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
+    <hyperlink ref="I128" r:id="rId226" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
+    <hyperlink ref="I61" r:id="rId227" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
+    <hyperlink ref="J61" r:id="rId228" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
+    <hyperlink ref="I55" r:id="rId229" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
+    <hyperlink ref="J55" r:id="rId230" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
+    <hyperlink ref="J78" r:id="rId231" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
+    <hyperlink ref="I78" r:id="rId232" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
+    <hyperlink ref="I48" r:id="rId233" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
+    <hyperlink ref="J48" r:id="rId234" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
+    <hyperlink ref="I49" r:id="rId235" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
+    <hyperlink ref="J49" r:id="rId236" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
+    <hyperlink ref="I52" r:id="rId237" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
+    <hyperlink ref="J52" r:id="rId238" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
+    <hyperlink ref="I44" r:id="rId239" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
+    <hyperlink ref="J44" r:id="rId240" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
+    <hyperlink ref="I46" r:id="rId241" xr:uid="{F619EC4F-CE2B-4A3F-A177-258B37F94B75}"/>
+    <hyperlink ref="J46" r:id="rId242" xr:uid="{16154418-6F7F-4716-B182-4CD246E54171}"/>
+    <hyperlink ref="I35" r:id="rId243" xr:uid="{E9BFACD2-2358-4D6F-8475-85410D79F5A9}"/>
+    <hyperlink ref="J35" r:id="rId244" xr:uid="{EBB7510F-0BE0-4317-9B06-1D95171523D6}"/>
+    <hyperlink ref="I126" r:id="rId245" xr:uid="{45C41464-28AE-4668-AC10-B5CD2C5D57A9}"/>
+    <hyperlink ref="I130" r:id="rId246" xr:uid="{15ED860D-2D4B-4897-97C4-651CA00D92FA}"/>
+    <hyperlink ref="J36" r:id="rId247" xr:uid="{5CF69990-5819-4326-B945-ED2995B498CF}"/>
     <hyperlink ref="I4" r:id="rId248" xr:uid="{7D3DCF5C-EF7C-4124-B5A1-25ADC1DFDADE}"/>
     <hyperlink ref="J4" r:id="rId249" xr:uid="{3265B707-A661-41E5-BD88-CD59552DEA1E}"/>
-    <hyperlink ref="I128" r:id="rId250" xr:uid="{A6C1D39E-0373-40B0-8016-2DC906697581}"/>
-    <hyperlink ref="J128" r:id="rId251" xr:uid="{E96F8A50-A558-4AA1-834F-8D81423906C9}"/>
-    <hyperlink ref="I129" r:id="rId252" xr:uid="{EFAA277E-33BA-4E31-8F6C-3D44B6838AB5}"/>
-    <hyperlink ref="J129" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
-    <hyperlink ref="J130" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
-    <hyperlink ref="I130" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
-    <hyperlink ref="J131" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
-    <hyperlink ref="I131" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
-    <hyperlink ref="I132" r:id="rId258" xr:uid="{A1A2837E-B079-456D-84AB-6A1561328A15}"/>
-    <hyperlink ref="J132" r:id="rId259" xr:uid="{5B16694A-EF14-479B-83C7-4F9D8A886209}"/>
-    <hyperlink ref="I133" r:id="rId260" xr:uid="{6AB6E69D-F1A6-4525-8E1D-E39B1043B707}"/>
-    <hyperlink ref="J133" r:id="rId261" xr:uid="{C3008C5E-7367-4D13-8A51-811BB64125E9}"/>
-    <hyperlink ref="I134" r:id="rId262" xr:uid="{C87BE13B-FF08-4594-91D4-2FC13EEEC8DA}"/>
-    <hyperlink ref="J134" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
+    <hyperlink ref="I101" r:id="rId250" xr:uid="{A6C1D39E-0373-40B0-8016-2DC906697581}"/>
+    <hyperlink ref="J101" r:id="rId251" xr:uid="{E96F8A50-A558-4AA1-834F-8D81423906C9}"/>
+    <hyperlink ref="I102" r:id="rId252" xr:uid="{EFAA277E-33BA-4E31-8F6C-3D44B6838AB5}"/>
+    <hyperlink ref="J102" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
+    <hyperlink ref="J99" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
+    <hyperlink ref="I99" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
+    <hyperlink ref="J100" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
+    <hyperlink ref="I100" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
+    <hyperlink ref="I5" r:id="rId258" xr:uid="{A1A2837E-B079-456D-84AB-6A1561328A15}"/>
+    <hyperlink ref="J5" r:id="rId259" xr:uid="{5B16694A-EF14-479B-83C7-4F9D8A886209}"/>
+    <hyperlink ref="I47" r:id="rId260" xr:uid="{6AB6E69D-F1A6-4525-8E1D-E39B1043B707}"/>
+    <hyperlink ref="J47" r:id="rId261" xr:uid="{C3008C5E-7367-4D13-8A51-811BB64125E9}"/>
+    <hyperlink ref="I110" r:id="rId262" xr:uid="{C87BE13B-FF08-4594-91D4-2FC13EEEC8DA}"/>
+    <hyperlink ref="J110" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
+    <hyperlink ref="I84" r:id="rId264" xr:uid="{65C8A524-1F2E-408F-9C4E-A8DCC7FE2AC3}"/>
+    <hyperlink ref="J84" r:id="rId265" xr:uid="{7354F640-B4B5-4D02-9DA0-17429462CBFC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20601,7 +20804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1302"/>
+  <dimension ref="A1:I1314"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -56020,6 +56223,336 @@
       </c>
       <c r="I1302" s="3"/>
     </row>
+    <row r="1303" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1303" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1303" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1303" s="4" t="s">
+        <v>4663</v>
+      </c>
+      <c r="D1303" s="8" t="s">
+        <v>4676</v>
+      </c>
+      <c r="E1303" s="14">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F1303" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1303" s="11">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="H1303" s="17" t="s">
+        <v>4698</v>
+      </c>
+      <c r="I1303" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1304" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1304" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1304" s="4" t="s">
+        <v>4664</v>
+      </c>
+      <c r="D1304" s="8" t="s">
+        <v>4677</v>
+      </c>
+      <c r="E1304" s="14">
+        <v>3.67</v>
+      </c>
+      <c r="F1304" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1304" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1304" s="6" t="s">
+        <v>4690</v>
+      </c>
+      <c r="I1304" s="3"/>
+    </row>
+    <row r="1305" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1305" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1305" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1305" s="4" t="s">
+        <v>4665</v>
+      </c>
+      <c r="D1305" s="8" t="s">
+        <v>4678</v>
+      </c>
+      <c r="E1305" s="14">
+        <v>3.55</v>
+      </c>
+      <c r="F1305" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G1305" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1305" s="17" t="s">
+        <v>4697</v>
+      </c>
+      <c r="I1305" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1306" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1306" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1306" s="4" t="s">
+        <v>4666</v>
+      </c>
+      <c r="D1306" s="8" t="s">
+        <v>4679</v>
+      </c>
+      <c r="E1306" s="14">
+        <v>4.12</v>
+      </c>
+      <c r="F1306" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G1306" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="H1306" s="6" t="s">
+        <v>4688</v>
+      </c>
+      <c r="I1306" s="3"/>
+    </row>
+    <row r="1307" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1307" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1307" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1307" s="4" t="s">
+        <v>4667</v>
+      </c>
+      <c r="D1307" s="8" t="s">
+        <v>4680</v>
+      </c>
+      <c r="E1307" s="14">
+        <v>3.96</v>
+      </c>
+      <c r="F1307" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1307" s="11">
+        <v>4.75</v>
+      </c>
+      <c r="H1307" s="6" t="s">
+        <v>4691</v>
+      </c>
+      <c r="I1307" s="3"/>
+    </row>
+    <row r="1308" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1308" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1308" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1308" s="4" t="s">
+        <v>4668</v>
+      </c>
+      <c r="D1308" s="8" t="s">
+        <v>4681</v>
+      </c>
+      <c r="E1308" s="14">
+        <v>3.39</v>
+      </c>
+      <c r="F1308" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1308" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1308" s="6" t="s">
+        <v>4692</v>
+      </c>
+      <c r="I1308" s="3"/>
+    </row>
+    <row r="1309" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1309" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1309" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1309" s="4" t="s">
+        <v>4669</v>
+      </c>
+      <c r="D1309" s="8" t="s">
+        <v>4682</v>
+      </c>
+      <c r="E1309" s="14">
+        <v>3.62</v>
+      </c>
+      <c r="F1309" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1309" s="11">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H1309" s="6" t="s">
+        <v>4689</v>
+      </c>
+      <c r="I1309" s="3"/>
+    </row>
+    <row r="1310" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1310" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1310" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1310" s="4" t="s">
+        <v>4670</v>
+      </c>
+      <c r="D1310" s="8" t="s">
+        <v>4683</v>
+      </c>
+      <c r="E1310" s="14">
+        <v>4</v>
+      </c>
+      <c r="F1310" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G1310" s="11">
+        <v>4.95</v>
+      </c>
+      <c r="H1310" s="6" t="s">
+        <v>4693</v>
+      </c>
+      <c r="I1310" s="3"/>
+    </row>
+    <row r="1311" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1311" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1311" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1311" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="D1311" s="8" t="s">
+        <v>4684</v>
+      </c>
+      <c r="E1311" s="14">
+        <v>4.09</v>
+      </c>
+      <c r="F1311" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G1311" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1311" s="6" t="s">
+        <v>4694</v>
+      </c>
+      <c r="I1311" s="3"/>
+    </row>
+    <row r="1312" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1312" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1312" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1312" s="4" t="s">
+        <v>4672</v>
+      </c>
+      <c r="D1312" s="8" t="s">
+        <v>4685</v>
+      </c>
+      <c r="E1312" s="14">
+        <v>3.43</v>
+      </c>
+      <c r="F1312" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1312" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="H1312" s="6" t="s">
+        <v>4695</v>
+      </c>
+      <c r="I1312" s="3"/>
+    </row>
+    <row r="1313" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1313" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1313" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1313" s="4" t="s">
+        <v>4673</v>
+      </c>
+      <c r="D1313" s="8" t="s">
+        <v>4686</v>
+      </c>
+      <c r="E1313" s="14">
+        <v>4.62</v>
+      </c>
+      <c r="F1313" s="11">
+        <v>5</v>
+      </c>
+      <c r="G1313" s="11">
+        <v>5</v>
+      </c>
+      <c r="H1313" s="6" t="s">
+        <v>4699</v>
+      </c>
+      <c r="I1313" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1314" s="3">
+        <v>35392324</v>
+      </c>
+      <c r="B1314" s="3">
+        <v>12</v>
+      </c>
+      <c r="C1314" s="4" t="s">
+        <v>4674</v>
+      </c>
+      <c r="D1314" s="8" t="s">
+        <v>4687</v>
+      </c>
+      <c r="E1314" s="14">
+        <v>3.31</v>
+      </c>
+      <c r="F1314" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G1314" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1314" s="6" t="s">
+        <v>4696</v>
+      </c>
+      <c r="I1314" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD089153-9C74-4DBB-B85B-4A862F12BE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7AE182-DA0D-4A45-8ED2-94237FAE3D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13983,9 +13983,6 @@
     <t>https://www.discogs.com/release/2797526-Warrior-Soul-Last-Decade-Dead-Century</t>
   </si>
   <si>
-    <t>Racing Cars — Downtown Tonight — Chrysalis CHR 1099, UK Orlake pressing, 1976. Lacquer cut by Harry T. Moss (HTM). Matrices: CHR 1099 A EG ⥛ HTM I-4 / CHR 1099 B EG ⥛ HTM I-5.Chrysalis – CHR 1099. Βρετανική έκδοση (UK Pressing) του 1976, τυπωμένη στο Ηνωμένο Βασίλειο. Η κοπή/κατασκευή έγινε από την Orlake Records (Orlake Pressing / OR στα runouts). Το mastering και η χάραξη (Lacquer Cut) φέρουν τις σφραγίδες των HTM (Harry T. Moss) και EG.</t>
-  </si>
-  <si>
     <t>Roots Rock, Soft Rock [Soul Rock, Funk Rock, Pop Rock, Welsh Rock]</t>
   </si>
   <si>
@@ -15599,6 +15596,9 @@
   </si>
   <si>
     <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το A Night At The Opera αποτελεί το πιο εμπορικό και φιλόδοξο αριστούργημα των Queen, συνδυάζοντας το hard rock με την όπερα και το βατεβίλ. Η επετειακή έκδοση των 50 ετών περιλαμβάνει remastered ήχο υψηλής πιστότητας, πολυτελές gatefold εξώφυλλο με ανάγλυφες χρυσοτυπίες και κοπή/χαράξεις που εντοπίζονται στα runouts (με τα χαρακτηριστικά etchings του Miles Showell και τις γεωμετρικές σημάνσεις της Optimal). Το A Night At The Opera είναι το σημείο όπου οι Queen έκαναν την υπερβολή τους συνθετική μέθοδο. Κάθε μέλος γράφει με διαφορετικό τρόπο, αλλά ο δίσκος δεν ακούγεται σαν ασύνδετη συλλογή. Η συνοχή προκύπτει από το κοινό production language: πλούσιες αρμονίες, studio λεπτομέρεια, χιούμορ, θεατρικότητα και άρνηση των στενών ειδών. Η 2025 crystal-clear 180g anniversary κόπια, με Optimal pressing και Miles Showell half-speed lacquer cutting, είναι premium, τεκμηριωμένη φυσική έκδοση ενός θεμελιώδους album. Ως μουσικό έργο η δίκαιη βαθμολογία είναι 4,8/5 — με “The Prophet’s Song”, “Love of My Life”, “’39”, “You’re My Best Friend” και, πάνω απ’ όλα, “Bohemian Rhapsody” να αιτιολογούν απόλυτα τη θέση του στον πυρήνα της rock δισκογραφίας. Queen — A Night At The Opera — EMI 00602475946410, Worldwide, 17 October 2025. 50th Anniversary Edition. LP, Album, Reissue, Crystal Clear heavyweight 180g vinyl, Half-Speed Mastered. Original master by Bob Ludwig; half-speed lacquer cut by Miles Showell at Abbey Road Studios; pressed by Optimal Media GmbH, BP 32334. Gatefold sleeve with embossed gold crest, debossed rear details, printed inner sleeve and gold hype sticker.</t>
+  </si>
+  <si>
+    <t>Chrysalis – CHR 1099. Βρετανική έκδοση (UK), κυκλοφορία 31 Αυγούστου 1976, σε στερεοφωνικό βινύλιο, με κοπή/mastering από τους EG (Pecko Duck) και Harry T. Moss (HTM), και εκτύπωση/πίεση από την Island Records Manufacturing Ltd.</t>
   </si>
 </sst>
 </file>
@@ -16321,19 +16321,19 @@
         <v>2.84</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>4369</v>
+        <v>4368</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>4377</v>
+        <v>4376</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>4376</v>
+        <v>4375</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>4368</v>
+        <v>4367</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>4367</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
@@ -16341,10 +16341,10 @@
         <v>31841081</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>4519</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>4520</v>
       </c>
       <c r="D5" s="3">
         <v>1972</v>
@@ -16353,19 +16353,19 @@
         <v>3.74</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>4571</v>
+        <v>4570</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
       <c r="I5" s="7" t="s">
+        <v>4520</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>4521</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>4522</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="90" x14ac:dyDescent="0.25">
@@ -17217,13 +17217,13 @@
         <v>3.78</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>4318</v>
+        <v>4317</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>4317</v>
+        <v>4316</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>4316</v>
+        <v>4315</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>37</v>
@@ -17348,16 +17348,16 @@
         <v>229</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>4334</v>
+        <v>4333</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>4343</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
@@ -17409,13 +17409,13 @@
         <v>3.45</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>4345</v>
+        <v>4344</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>4344</v>
+        <v>4343</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>246</v>
@@ -17456,7 +17456,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>18813646</v>
       </c>
@@ -17552,7 +17552,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>34571488</v>
       </c>
@@ -17685,10 +17685,10 @@
         <v>37111626</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>4599</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>4600</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>4601</v>
       </c>
       <c r="D47" s="3">
         <v>1976</v>
@@ -17697,22 +17697,22 @@
         <v>3.77</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>4609</v>
+        <v>4608</v>
       </c>
       <c r="G47" s="4" t="s">
+        <v>4597</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>4598</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4599</v>
-      </c>
       <c r="I47" s="7" t="s">
+        <v>4595</v>
+      </c>
+      <c r="J47" s="7" t="s">
         <v>4596</v>
       </c>
-      <c r="J47" s="7" t="s">
-        <v>4597</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>27342894</v>
       </c>
@@ -18869,10 +18869,10 @@
         <v>35392324</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>4658</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>4659</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>4660</v>
       </c>
       <c r="D84" s="3">
         <v>1975</v>
@@ -18881,19 +18881,19 @@
         <v>3.78</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>4675</v>
+        <v>4674</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>4700</v>
+        <v>4699</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>4658</v>
+        <v>4657</v>
       </c>
       <c r="I84" s="7" t="s">
+        <v>4660</v>
+      </c>
+      <c r="J84" s="7" t="s">
         <v>4661</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>4662</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
@@ -18928,9 +18928,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>113</v>
@@ -18945,13 +18945,13 @@
         <v>3.45</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>4297</v>
+        <v>4296</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>115</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>4296</v>
+        <v>4700</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>116</v>
@@ -19347,10 +19347,10 @@
         <v>7949644</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>4390</v>
+        <v>4389</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="D99" s="3">
         <v>1976</v>
@@ -19359,19 +19359,19 @@
         <v>3.6</v>
       </c>
       <c r="F99" s="6" t="s">
+        <v>4460</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>4485</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>4450</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>4462</v>
+      </c>
+      <c r="J99" s="7" t="s">
         <v>4461</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>4486</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>4451</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>4463</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>4462</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
@@ -19379,10 +19379,10 @@
         <v>2705063</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>4390</v>
+        <v>4389</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="D100" s="3">
         <v>1979</v>
@@ -19391,19 +19391,19 @@
         <v>3.85</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>4485</v>
+        <v>4484</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>4484</v>
+        <v>4483</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
@@ -19411,10 +19411,10 @@
         <v>4007367</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>4390</v>
+        <v>4389</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>4389</v>
+        <v>4388</v>
       </c>
       <c r="D101" s="3">
         <v>1982</v>
@@ -19423,19 +19423,19 @@
         <v>3.69</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>4399</v>
+        <v>4398</v>
       </c>
       <c r="G101" s="4" t="s">
+        <v>4385</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="I101" s="7" t="s">
         <v>4386</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4384</v>
-      </c>
-      <c r="I101" s="7" t="s">
+      <c r="J101" s="7" t="s">
         <v>4387</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>4388</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
@@ -19443,10 +19443,10 @@
         <v>2874281</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>4390</v>
+        <v>4389</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>4422</v>
+        <v>4421</v>
       </c>
       <c r="D102" s="3">
         <v>1988</v>
@@ -19455,19 +19455,19 @@
         <v>3.23</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>4432</v>
+        <v>4431</v>
       </c>
       <c r="G102" s="4" t="s">
+        <v>4418</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4417</v>
+      </c>
+      <c r="I102" s="7" t="s">
         <v>4419</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>4418</v>
-      </c>
-      <c r="I102" s="7" t="s">
+      <c r="J102" s="7" t="s">
         <v>4420</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>4421</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
@@ -19699,10 +19699,10 @@
         <v>7340202</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>4630</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>4631</v>
       </c>
       <c r="D110" s="3">
         <v>1977</v>
@@ -19711,19 +19711,19 @@
         <v>3.5</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>4640</v>
+        <v>4639</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>4657</v>
+        <v>4656</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>4632</v>
+        <v>4631</v>
       </c>
       <c r="I110" s="7" t="s">
+        <v>4627</v>
+      </c>
+      <c r="J110" s="7" t="s">
         <v>4628</v>
-      </c>
-      <c r="J110" s="7" t="s">
-        <v>4629</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
@@ -20514,7 +20514,7 @@
         <v>3062</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>4385</v>
+        <v>4384</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>3052</v>
@@ -21129,7 +21129,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="E12" s="10">
         <v>4.22</v>
@@ -21141,7 +21141,7 @@
         <v>4.5</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -21156,7 +21156,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>4320</v>
+        <v>4319</v>
       </c>
       <c r="E13" s="10">
         <v>3.96</v>
@@ -21168,7 +21168,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>4328</v>
+        <v>4327</v>
       </c>
       <c r="I13" s="3"/>
     </row>
@@ -21183,7 +21183,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>4321</v>
+        <v>4320</v>
       </c>
       <c r="E14" s="10">
         <v>4.0199999999999996</v>
@@ -21195,7 +21195,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>4329</v>
+        <v>4328</v>
       </c>
       <c r="I14" s="3"/>
     </row>
@@ -21210,7 +21210,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
       <c r="E15" s="10">
         <v>3.83</v>
@@ -21222,7 +21222,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>4330</v>
+        <v>4329</v>
       </c>
       <c r="I15" s="3"/>
     </row>
@@ -21237,7 +21237,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>4323</v>
+        <v>4322</v>
       </c>
       <c r="E16" s="10">
         <v>3.9</v>
@@ -21249,7 +21249,7 @@
         <v>4.55</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="I16" s="3"/>
     </row>
@@ -21264,7 +21264,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>4324</v>
+        <v>4323</v>
       </c>
       <c r="E17" s="10">
         <v>3.93</v>
@@ -21276,7 +21276,7 @@
         <v>4.45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>4331</v>
+        <v>4330</v>
       </c>
       <c r="I17" s="3"/>
     </row>
@@ -21291,7 +21291,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="E18" s="10">
         <v>4.43</v>
@@ -21303,7 +21303,7 @@
         <v>4.7</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>4332</v>
+        <v>4331</v>
       </c>
       <c r="I18" s="3"/>
     </row>
@@ -22314,7 +22314,7 @@
     </row>
     <row r="56" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -22323,7 +22323,7 @@
         <v>118</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>4298</v>
+        <v>4297</v>
       </c>
       <c r="E56" s="10">
         <v>3.6</v>
@@ -22335,7 +22335,7 @@
         <v>4.5</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>4309</v>
+        <v>4308</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>173</v>
@@ -22343,7 +22343,7 @@
     </row>
     <row r="57" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B57" s="3">
         <v>2</v>
@@ -22352,7 +22352,7 @@
         <v>119</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>4299</v>
+        <v>4298</v>
       </c>
       <c r="E57" s="10">
         <v>3.42</v>
@@ -22364,13 +22364,13 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>4310</v>
+        <v>4309</v>
       </c>
       <c r="I57" s="3"/>
     </row>
     <row r="58" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B58" s="3">
         <v>3</v>
@@ -22379,7 +22379,7 @@
         <v>120</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>4300</v>
+        <v>4299</v>
       </c>
       <c r="E58" s="10">
         <v>3.05</v>
@@ -22391,13 +22391,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>4311</v>
+        <v>4310</v>
       </c>
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B59" s="3">
         <v>4</v>
@@ -22406,7 +22406,7 @@
         <v>114</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>4301</v>
+        <v>4300</v>
       </c>
       <c r="E59" s="10">
         <v>3.44</v>
@@ -22418,13 +22418,13 @@
         <v>4.5</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>4312</v>
+        <v>4311</v>
       </c>
       <c r="I59" s="3"/>
     </row>
     <row r="60" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B60" s="3">
         <v>5</v>
@@ -22433,7 +22433,7 @@
         <v>121</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>4302</v>
+        <v>4301</v>
       </c>
       <c r="E60" s="10">
         <v>3.34</v>
@@ -22445,13 +22445,13 @@
         <v>4.2</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="I60" s="3"/>
     </row>
     <row r="61" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B61" s="3">
         <v>6</v>
@@ -22460,7 +22460,7 @@
         <v>122</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>4303</v>
+        <v>4302</v>
       </c>
       <c r="E61" s="10">
         <v>3.31</v>
@@ -22472,13 +22472,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>4308</v>
+        <v>4307</v>
       </c>
       <c r="I61" s="3"/>
     </row>
     <row r="62" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B62" s="3">
         <v>7</v>
@@ -22487,7 +22487,7 @@
         <v>123</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="E62" s="10">
         <v>2.97</v>
@@ -22499,13 +22499,13 @@
         <v>4</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>4313</v>
+        <v>4312</v>
       </c>
       <c r="I62" s="3"/>
     </row>
     <row r="63" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B63" s="3">
         <v>8</v>
@@ -22514,7 +22514,7 @@
         <v>124</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>4305</v>
+        <v>4304</v>
       </c>
       <c r="E63" s="10">
         <v>2.96</v>
@@ -22526,13 +22526,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>4314</v>
+        <v>4313</v>
       </c>
       <c r="I63" s="3"/>
     </row>
     <row r="64" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>2027786</v>
+        <v>21177118</v>
       </c>
       <c r="B64" s="3">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>125</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>4306</v>
+        <v>4305</v>
       </c>
       <c r="E64" s="10">
         <v>2.99</v>
@@ -22553,7 +22553,7 @@
         <v>4.75</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>4315</v>
+        <v>4314</v>
       </c>
       <c r="I64" s="3"/>
     </row>
@@ -22568,7 +22568,7 @@
         <v>126</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>4370</v>
+        <v>4369</v>
       </c>
       <c r="E65" s="10">
         <v>3.07</v>
@@ -22580,7 +22580,7 @@
         <v>4.5</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>4383</v>
+        <v>4382</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>173</v>
@@ -22597,7 +22597,7 @@
         <v>127</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>4371</v>
+        <v>4370</v>
       </c>
       <c r="E66" s="10">
         <v>2.81</v>
@@ -22609,7 +22609,7 @@
         <v>4.3</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>4378</v>
+        <v>4377</v>
       </c>
       <c r="I66" s="3"/>
     </row>
@@ -22624,7 +22624,7 @@
         <v>128</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>4372</v>
+        <v>4371</v>
       </c>
       <c r="E67" s="10">
         <v>3.31</v>
@@ -22636,7 +22636,7 @@
         <v>4.2</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>4379</v>
+        <v>4378</v>
       </c>
       <c r="I67" s="3"/>
     </row>
@@ -22651,7 +22651,7 @@
         <v>129</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>4373</v>
+        <v>4372</v>
       </c>
       <c r="E68" s="10">
         <v>3.24</v>
@@ -22663,7 +22663,7 @@
         <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>4380</v>
+        <v>4379</v>
       </c>
       <c r="I68" s="3"/>
     </row>
@@ -22678,7 +22678,7 @@
         <v>130</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>4374</v>
+        <v>4373</v>
       </c>
       <c r="E69" s="10">
         <v>3.27</v>
@@ -22690,7 +22690,7 @@
         <v>4.2</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>4381</v>
+        <v>4380</v>
       </c>
       <c r="I69" s="3"/>
     </row>
@@ -22705,7 +22705,7 @@
         <v>131</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>4375</v>
+        <v>4374</v>
       </c>
       <c r="E70" s="10">
         <v>3.51</v>
@@ -22717,7 +22717,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>4382</v>
+        <v>4381</v>
       </c>
       <c r="I70" s="3"/>
     </row>
@@ -23639,7 +23639,7 @@
         <v>228</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>4335</v>
+        <v>4334</v>
       </c>
       <c r="E104" s="10">
         <v>3.87</v>
@@ -23651,7 +23651,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>4339</v>
+        <v>4338</v>
       </c>
       <c r="I104" s="3"/>
     </row>
@@ -23666,7 +23666,7 @@
         <v>230</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>4336</v>
+        <v>4335</v>
       </c>
       <c r="E105" s="10">
         <v>3.82</v>
@@ -23678,7 +23678,7 @@
         <v>4.5</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>4340</v>
+        <v>4339</v>
       </c>
       <c r="I105" s="3"/>
     </row>
@@ -23693,7 +23693,7 @@
         <v>231</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>4337</v>
+        <v>4336</v>
       </c>
       <c r="E106" s="10">
         <v>3.65</v>
@@ -23705,7 +23705,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>4341</v>
+        <v>4340</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>173</v>
@@ -23722,7 +23722,7 @@
         <v>232</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>4338</v>
+        <v>4337</v>
       </c>
       <c r="E107" s="10">
         <v>3.57</v>
@@ -23734,7 +23734,7 @@
         <v>4.5</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>4342</v>
+        <v>4341</v>
       </c>
       <c r="I107" s="3"/>
     </row>
@@ -23749,7 +23749,7 @@
         <v>236</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="E108" s="10">
         <v>4.25</v>
@@ -23761,7 +23761,7 @@
         <v>4.45</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>4359</v>
+        <v>4358</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -23776,7 +23776,7 @@
         <v>237</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>4348</v>
+        <v>4347</v>
       </c>
       <c r="E109" s="10">
         <v>4.25</v>
@@ -23788,7 +23788,7 @@
         <v>4.5</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>173</v>
@@ -23805,7 +23805,7 @@
         <v>238</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>4349</v>
+        <v>4348</v>
       </c>
       <c r="E110" s="10">
         <v>3.5</v>
@@ -23817,7 +23817,7 @@
         <v>4</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>4360</v>
+        <v>4359</v>
       </c>
       <c r="I110" s="3"/>
     </row>
@@ -23832,7 +23832,7 @@
         <v>239</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="E111" s="10">
         <v>3.5</v>
@@ -23844,7 +23844,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>4361</v>
+        <v>4360</v>
       </c>
       <c r="I111" s="3"/>
     </row>
@@ -23859,7 +23859,7 @@
         <v>240</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>4351</v>
+        <v>4350</v>
       </c>
       <c r="E112" s="10">
         <v>4.33</v>
@@ -23871,7 +23871,7 @@
         <v>4.2</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="I112" s="3"/>
     </row>
@@ -23886,7 +23886,7 @@
         <v>241</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>4352</v>
+        <v>4351</v>
       </c>
       <c r="E113" s="10">
         <v>4</v>
@@ -23898,7 +23898,7 @@
         <v>4.3</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>4357</v>
+        <v>4356</v>
       </c>
       <c r="I113" s="3"/>
     </row>
@@ -23913,7 +23913,7 @@
         <v>242</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="E114" s="10">
         <v>4.25</v>
@@ -23925,7 +23925,7 @@
         <v>4.2</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>4358</v>
+        <v>4357</v>
       </c>
       <c r="I114" s="3"/>
     </row>
@@ -23940,7 +23940,7 @@
         <v>243</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
       <c r="E115" s="10">
         <v>4</v>
@@ -23952,7 +23952,7 @@
         <v>4.5</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>4363</v>
+        <v>4362</v>
       </c>
       <c r="I115" s="3"/>
     </row>
@@ -23967,7 +23967,7 @@
         <v>244</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>4355</v>
+        <v>4354</v>
       </c>
       <c r="E116" s="10">
         <v>3.5</v>
@@ -23979,7 +23979,7 @@
         <v>3.8</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="I116" s="3"/>
     </row>
@@ -23994,7 +23994,7 @@
         <v>245</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
       <c r="E117" s="10">
         <v>3.75</v>
@@ -24006,7 +24006,7 @@
         <v>4.3</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="I117" s="3"/>
     </row>
@@ -54048,10 +54048,10 @@
         <v>1</v>
       </c>
       <c r="C1224" s="4" t="s">
-        <v>4389</v>
+        <v>4388</v>
       </c>
       <c r="D1224" s="4" t="s">
-        <v>4400</v>
+        <v>4399</v>
       </c>
       <c r="E1224" s="14">
         <v>4.1100000000000003</v>
@@ -54063,7 +54063,7 @@
         <v>4.5</v>
       </c>
       <c r="H1224" s="28" t="s">
-        <v>4409</v>
+        <v>4408</v>
       </c>
       <c r="I1224" s="3" t="s">
         <v>173</v>
@@ -54077,10 +54077,10 @@
         <v>2</v>
       </c>
       <c r="C1225" s="4" t="s">
-        <v>4391</v>
+        <v>4390</v>
       </c>
       <c r="D1225" s="4" t="s">
-        <v>4401</v>
+        <v>4400</v>
       </c>
       <c r="E1225" s="14">
         <v>3.64</v>
@@ -54092,7 +54092,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1225" s="28" t="s">
-        <v>4410</v>
+        <v>4409</v>
       </c>
       <c r="I1225" s="3" t="s">
         <v>173</v>
@@ -54106,10 +54106,10 @@
         <v>3</v>
       </c>
       <c r="C1226" s="4" t="s">
-        <v>4392</v>
+        <v>4391</v>
       </c>
       <c r="D1226" s="4" t="s">
-        <v>4402</v>
+        <v>4401</v>
       </c>
       <c r="E1226" s="14">
         <v>4.21</v>
@@ -54121,7 +54121,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1226" s="28" t="s">
-        <v>4411</v>
+        <v>4410</v>
       </c>
       <c r="I1226" s="3" t="s">
         <v>173</v>
@@ -54135,10 +54135,10 @@
         <v>4</v>
       </c>
       <c r="C1227" s="4" t="s">
-        <v>4393</v>
+        <v>4392</v>
       </c>
       <c r="D1227" s="4" t="s">
-        <v>4403</v>
+        <v>4402</v>
       </c>
       <c r="E1227" s="14">
         <v>3.67</v>
@@ -54150,7 +54150,7 @@
         <v>4.3</v>
       </c>
       <c r="H1227" s="28" t="s">
-        <v>4412</v>
+        <v>4411</v>
       </c>
       <c r="I1227" s="3" t="s">
         <v>173</v>
@@ -54164,10 +54164,10 @@
         <v>5</v>
       </c>
       <c r="C1228" s="4" t="s">
-        <v>4394</v>
+        <v>4393</v>
       </c>
       <c r="D1228" s="4" t="s">
-        <v>4404</v>
+        <v>4403</v>
       </c>
       <c r="E1228" s="14">
         <v>3.62</v>
@@ -54179,7 +54179,7 @@
         <v>4.45</v>
       </c>
       <c r="H1228" s="28" t="s">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="I1228" s="3" t="s">
         <v>173</v>
@@ -54193,10 +54193,10 @@
         <v>6</v>
       </c>
       <c r="C1229" s="4" t="s">
-        <v>4395</v>
+        <v>4394</v>
       </c>
       <c r="D1229" s="4" t="s">
-        <v>4405</v>
+        <v>4404</v>
       </c>
       <c r="E1229" s="14">
         <v>3.96</v>
@@ -54208,7 +54208,7 @@
         <v>4.55</v>
       </c>
       <c r="H1229" s="28" t="s">
-        <v>4414</v>
+        <v>4413</v>
       </c>
       <c r="I1229" s="3" t="s">
         <v>173</v>
@@ -54222,10 +54222,10 @@
         <v>7</v>
       </c>
       <c r="C1230" s="4" t="s">
-        <v>4396</v>
+        <v>4395</v>
       </c>
       <c r="D1230" s="4" t="s">
-        <v>4406</v>
+        <v>4405</v>
       </c>
       <c r="E1230" s="14">
         <v>3.53</v>
@@ -54237,7 +54237,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1230" s="28" t="s">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="I1230" s="3"/>
     </row>
@@ -54249,10 +54249,10 @@
         <v>8</v>
       </c>
       <c r="C1231" s="4" t="s">
-        <v>4397</v>
+        <v>4396</v>
       </c>
       <c r="D1231" s="4" t="s">
-        <v>4407</v>
+        <v>4406</v>
       </c>
       <c r="E1231" s="14">
         <v>3.8</v>
@@ -54264,7 +54264,7 @@
         <v>4.5</v>
       </c>
       <c r="H1231" s="28" t="s">
-        <v>4416</v>
+        <v>4415</v>
       </c>
       <c r="I1231" s="3" t="s">
         <v>173</v>
@@ -54278,10 +54278,10 @@
         <v>9</v>
       </c>
       <c r="C1232" s="4" t="s">
-        <v>4398</v>
+        <v>4397</v>
       </c>
       <c r="D1232" s="4" t="s">
-        <v>4408</v>
+        <v>4407</v>
       </c>
       <c r="E1232" s="14">
         <v>3.97</v>
@@ -54293,7 +54293,7 @@
         <v>4.7</v>
       </c>
       <c r="H1232" s="28" t="s">
-        <v>4417</v>
+        <v>4416</v>
       </c>
       <c r="I1232" s="3" t="s">
         <v>173</v>
@@ -54307,10 +54307,10 @@
         <v>1</v>
       </c>
       <c r="C1233" s="4" t="s">
-        <v>4423</v>
+        <v>4422</v>
       </c>
       <c r="D1233" s="4" t="s">
-        <v>4433</v>
+        <v>4432</v>
       </c>
       <c r="E1233" s="14">
         <v>3.8</v>
@@ -54322,7 +54322,7 @@
         <v>4.3</v>
       </c>
       <c r="H1233" s="6" t="s">
-        <v>4443</v>
+        <v>4442</v>
       </c>
       <c r="I1233" s="3"/>
     </row>
@@ -54334,10 +54334,10 @@
         <v>2</v>
       </c>
       <c r="C1234" s="4" t="s">
-        <v>4424</v>
+        <v>4423</v>
       </c>
       <c r="D1234" s="4" t="s">
-        <v>4434</v>
+        <v>4433</v>
       </c>
       <c r="E1234" s="14">
         <v>3.82</v>
@@ -54349,7 +54349,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1234" s="17" t="s">
-        <v>4450</v>
+        <v>4449</v>
       </c>
       <c r="I1234" s="3" t="s">
         <v>173</v>
@@ -54363,10 +54363,10 @@
         <v>3</v>
       </c>
       <c r="C1235" s="4" t="s">
-        <v>4425</v>
+        <v>4424</v>
       </c>
       <c r="D1235" s="4" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
       <c r="E1235" s="14">
         <v>3.63</v>
@@ -54378,7 +54378,7 @@
         <v>4.2</v>
       </c>
       <c r="H1235" s="6" t="s">
-        <v>4444</v>
+        <v>4443</v>
       </c>
       <c r="I1235" s="3"/>
     </row>
@@ -54390,10 +54390,10 @@
         <v>4</v>
       </c>
       <c r="C1236" s="4" t="s">
-        <v>4426</v>
+        <v>4425</v>
       </c>
       <c r="D1236" s="4" t="s">
-        <v>4436</v>
+        <v>4435</v>
       </c>
       <c r="E1236" s="14">
         <v>3.37</v>
@@ -54405,7 +54405,7 @@
         <v>3.95</v>
       </c>
       <c r="H1236" s="6" t="s">
-        <v>4445</v>
+        <v>4444</v>
       </c>
       <c r="I1236" s="3"/>
     </row>
@@ -54417,10 +54417,10 @@
         <v>5</v>
       </c>
       <c r="C1237" s="4" t="s">
-        <v>4427</v>
+        <v>4426</v>
       </c>
       <c r="D1237" s="4" t="s">
-        <v>4437</v>
+        <v>4436</v>
       </c>
       <c r="E1237" s="14">
         <v>3.43</v>
@@ -54432,7 +54432,7 @@
         <v>4.2</v>
       </c>
       <c r="H1237" s="6" t="s">
-        <v>4446</v>
+        <v>4445</v>
       </c>
       <c r="I1237" s="3"/>
     </row>
@@ -54444,10 +54444,10 @@
         <v>6</v>
       </c>
       <c r="C1238" s="4" t="s">
-        <v>4428</v>
+        <v>4427</v>
       </c>
       <c r="D1238" s="4" t="s">
-        <v>4438</v>
+        <v>4437</v>
       </c>
       <c r="E1238" s="14">
         <v>3.32</v>
@@ -54459,7 +54459,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H1238" s="6" t="s">
-        <v>4447</v>
+        <v>4446</v>
       </c>
       <c r="I1238" s="3"/>
     </row>
@@ -54471,10 +54471,10 @@
         <v>7</v>
       </c>
       <c r="C1239" s="4" t="s">
-        <v>4429</v>
+        <v>4428</v>
       </c>
       <c r="D1239" s="4" t="s">
-        <v>4439</v>
+        <v>4438</v>
       </c>
       <c r="E1239" s="14">
         <v>3.4</v>
@@ -54486,7 +54486,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="H1239" s="6" t="s">
-        <v>4448</v>
+        <v>4447</v>
       </c>
       <c r="I1239" s="3"/>
     </row>
@@ -54498,10 +54498,10 @@
         <v>8</v>
       </c>
       <c r="C1240" s="4" t="s">
-        <v>4430</v>
+        <v>4429</v>
       </c>
       <c r="D1240" s="4" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
       <c r="E1240" s="14">
         <v>3.35</v>
@@ -54513,7 +54513,7 @@
         <v>4</v>
       </c>
       <c r="H1240" s="6" t="s">
-        <v>4442</v>
+        <v>4441</v>
       </c>
       <c r="I1240" s="3"/>
     </row>
@@ -54525,10 +54525,10 @@
         <v>9</v>
       </c>
       <c r="C1241" s="4" t="s">
-        <v>4431</v>
+        <v>4430</v>
       </c>
       <c r="D1241" s="4" t="s">
-        <v>4441</v>
+        <v>4440</v>
       </c>
       <c r="E1241" s="14">
         <v>3.62</v>
@@ -54540,7 +54540,7 @@
         <v>4.5</v>
       </c>
       <c r="H1241" s="6" t="s">
-        <v>4449</v>
+        <v>4448</v>
       </c>
       <c r="I1241" s="3" t="s">
         <v>173</v>
@@ -54554,10 +54554,10 @@
         <v>1</v>
       </c>
       <c r="C1242" s="4" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
       <c r="D1242" s="4" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
       <c r="E1242" s="14">
         <v>4.01</v>
@@ -54569,7 +54569,7 @@
         <v>4.5</v>
       </c>
       <c r="H1242" s="17" t="s">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="I1242" s="3" t="s">
         <v>173</v>
@@ -54583,10 +54583,10 @@
         <v>2</v>
       </c>
       <c r="C1243" s="4" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
       <c r="D1243" s="4" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="E1243" s="14">
         <v>3.93</v>
@@ -54598,7 +54598,7 @@
         <v>4.45</v>
       </c>
       <c r="H1243" s="6" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
       <c r="I1243" s="3"/>
     </row>
@@ -54610,10 +54610,10 @@
         <v>3</v>
       </c>
       <c r="C1244" s="4" t="s">
-        <v>4454</v>
+        <v>4453</v>
       </c>
       <c r="D1244" s="4" t="s">
-        <v>4466</v>
+        <v>4465</v>
       </c>
       <c r="E1244" s="14">
         <v>3.72</v>
@@ -54625,7 +54625,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1244" s="6" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
       <c r="I1244" s="3"/>
     </row>
@@ -54637,10 +54637,10 @@
         <v>4</v>
       </c>
       <c r="C1245" s="4" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
       <c r="D1245" s="4" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
       <c r="E1245" s="14">
         <v>3.47</v>
@@ -54652,7 +54652,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1245" s="6" t="s">
-        <v>4475</v>
+        <v>4474</v>
       </c>
       <c r="I1245" s="3"/>
     </row>
@@ -54664,10 +54664,10 @@
         <v>5</v>
       </c>
       <c r="C1246" s="4" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="D1246" s="4" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
       <c r="E1246" s="14">
         <v>3.56</v>
@@ -54679,7 +54679,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1246" s="6" t="s">
-        <v>4476</v>
+        <v>4475</v>
       </c>
       <c r="I1246" s="3"/>
     </row>
@@ -54691,10 +54691,10 @@
         <v>6</v>
       </c>
       <c r="C1247" s="4" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
       <c r="D1247" s="4" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
       <c r="E1247" s="14">
         <v>3.08</v>
@@ -54706,7 +54706,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1247" s="6" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
       <c r="I1247" s="3"/>
     </row>
@@ -54718,10 +54718,10 @@
         <v>7</v>
       </c>
       <c r="C1248" s="4" t="s">
-        <v>4458</v>
+        <v>4457</v>
       </c>
       <c r="D1248" s="4" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
       <c r="E1248" s="14">
         <v>3.66</v>
@@ -54733,7 +54733,7 @@
         <v>4.5</v>
       </c>
       <c r="H1248" s="6" t="s">
-        <v>4478</v>
+        <v>4477</v>
       </c>
       <c r="I1248" s="3"/>
     </row>
@@ -54745,10 +54745,10 @@
         <v>8</v>
       </c>
       <c r="C1249" s="4" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="D1249" s="4" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
       <c r="E1249" s="14">
         <v>3.49</v>
@@ -54760,7 +54760,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1249" s="6" t="s">
-        <v>4480</v>
+        <v>4479</v>
       </c>
       <c r="I1249" s="3"/>
     </row>
@@ -54772,10 +54772,10 @@
         <v>9</v>
       </c>
       <c r="C1250" s="4" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
       <c r="D1250" s="4" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
       <c r="E1250" s="14">
         <v>3.68</v>
@@ -54787,7 +54787,7 @@
         <v>4.55</v>
       </c>
       <c r="H1250" s="17" t="s">
-        <v>4481</v>
+        <v>4480</v>
       </c>
       <c r="I1250" s="3" t="s">
         <v>173</v>
@@ -54801,10 +54801,10 @@
         <v>1</v>
       </c>
       <c r="C1251" s="4" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="D1251" s="4" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
       <c r="E1251" s="14">
         <v>3.83</v>
@@ -54816,7 +54816,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1251" s="17" t="s">
-        <v>4516</v>
+        <v>4515</v>
       </c>
       <c r="I1251" s="3" t="s">
         <v>173</v>
@@ -54830,10 +54830,10 @@
         <v>2</v>
       </c>
       <c r="C1252" s="4" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
       <c r="D1252" s="4" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
       <c r="E1252" s="14">
         <v>4.01</v>
@@ -54845,7 +54845,7 @@
         <v>4.5</v>
       </c>
       <c r="H1252" s="17" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
       <c r="I1252" s="3" t="s">
         <v>173</v>
@@ -54859,10 +54859,10 @@
         <v>3</v>
       </c>
       <c r="C1253" s="4" t="s">
-        <v>4489</v>
+        <v>4488</v>
       </c>
       <c r="D1253" s="4" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
       <c r="E1253" s="14">
         <v>3.8</v>
@@ -54874,7 +54874,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1253" s="17" t="s">
-        <v>4515</v>
+        <v>4514</v>
       </c>
       <c r="I1253" s="3" t="s">
         <v>173</v>
@@ -54888,10 +54888,10 @@
         <v>4</v>
       </c>
       <c r="C1254" s="4" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
       <c r="D1254" s="4" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
       <c r="E1254" s="14">
         <v>3.47</v>
@@ -54903,7 +54903,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1254" s="6" t="s">
-        <v>4508</v>
+        <v>4507</v>
       </c>
       <c r="I1254" s="3"/>
     </row>
@@ -54915,10 +54915,10 @@
         <v>5</v>
       </c>
       <c r="C1255" s="4" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
       <c r="D1255" s="4" t="s">
-        <v>4500</v>
+        <v>4499</v>
       </c>
       <c r="E1255" s="14">
         <v>3.89</v>
@@ -54930,7 +54930,7 @@
         <v>4.45</v>
       </c>
       <c r="H1255" s="17" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
       <c r="I1255" s="3" t="s">
         <v>173</v>
@@ -54944,10 +54944,10 @@
         <v>6</v>
       </c>
       <c r="C1256" s="4" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
       <c r="D1256" s="4" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
       <c r="E1256" s="14">
         <v>3.08</v>
@@ -54959,7 +54959,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1256" s="6" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="I1256" s="3"/>
     </row>
@@ -54971,10 +54971,10 @@
         <v>7</v>
       </c>
       <c r="C1257" s="4" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
       <c r="D1257" s="4" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="E1257" s="14">
         <v>3.89</v>
@@ -54986,7 +54986,7 @@
         <v>4.55</v>
       </c>
       <c r="H1257" s="17" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
       <c r="I1257" s="3" t="s">
         <v>173</v>
@@ -55000,10 +55000,10 @@
         <v>8</v>
       </c>
       <c r="C1258" s="4" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
       <c r="D1258" s="4" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
       <c r="E1258" s="14">
         <v>4.21</v>
@@ -55015,7 +55015,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1258" s="17" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="I1258" s="3" t="s">
         <v>173</v>
@@ -55029,10 +55029,10 @@
         <v>9</v>
       </c>
       <c r="C1259" s="4" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
       <c r="D1259" s="4" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
       <c r="E1259" s="14">
         <v>3.85</v>
@@ -55044,7 +55044,7 @@
         <v>4.45</v>
       </c>
       <c r="H1259" s="6" t="s">
-        <v>4510</v>
+        <v>4509</v>
       </c>
       <c r="I1259" s="3"/>
     </row>
@@ -55056,10 +55056,10 @@
         <v>10</v>
       </c>
       <c r="C1260" s="4" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
       <c r="D1260" s="4" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="E1260" s="14">
         <v>4.28</v>
@@ -55071,7 +55071,7 @@
         <v>4.7</v>
       </c>
       <c r="H1260" s="17" t="s">
-        <v>4511</v>
+        <v>4510</v>
       </c>
       <c r="I1260" s="3" t="s">
         <v>173</v>
@@ -55085,10 +55085,10 @@
         <v>11</v>
       </c>
       <c r="C1261" s="4" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
       <c r="D1261" s="4" t="s">
-        <v>4506</v>
+        <v>4505</v>
       </c>
       <c r="E1261" s="14">
         <v>3.56</v>
@@ -55100,7 +55100,7 @@
         <v>4.5</v>
       </c>
       <c r="H1261" s="6" t="s">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="I1261" s="3"/>
     </row>
@@ -55112,10 +55112,10 @@
         <v>1</v>
       </c>
       <c r="C1262" s="4" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
       <c r="D1262" s="4" t="s">
-        <v>4547</v>
+        <v>4546</v>
       </c>
       <c r="E1262" s="14">
         <v>3.25</v>
@@ -55127,7 +55127,7 @@
         <v>4.3</v>
       </c>
       <c r="H1262" s="30" t="s">
-        <v>4578</v>
+        <v>4577</v>
       </c>
       <c r="I1262" s="3"/>
     </row>
@@ -55139,10 +55139,10 @@
         <v>2</v>
       </c>
       <c r="C1263" s="4" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
       <c r="D1263" s="4" t="s">
-        <v>4548</v>
+        <v>4547</v>
       </c>
       <c r="E1263" s="14">
         <v>4.12</v>
@@ -55154,7 +55154,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1263" s="30" t="s">
-        <v>4579</v>
+        <v>4578</v>
       </c>
       <c r="I1263" s="3"/>
     </row>
@@ -55166,10 +55166,10 @@
         <v>3</v>
       </c>
       <c r="C1264" s="4" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
       <c r="D1264" s="4" t="s">
-        <v>4549</v>
+        <v>4548</v>
       </c>
       <c r="E1264" s="14">
         <v>3.59</v>
@@ -55181,7 +55181,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1264" s="30" t="s">
-        <v>4572</v>
+        <v>4571</v>
       </c>
       <c r="I1264" s="3"/>
     </row>
@@ -55193,10 +55193,10 @@
         <v>4</v>
       </c>
       <c r="C1265" s="4" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
       <c r="D1265" s="4" t="s">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="E1265" s="14">
         <v>4.45</v>
@@ -55208,7 +55208,7 @@
         <v>4.8</v>
       </c>
       <c r="H1265" s="29" t="s">
-        <v>4595</v>
+        <v>4594</v>
       </c>
       <c r="I1265" s="3" t="s">
         <v>173</v>
@@ -55222,10 +55222,10 @@
         <v>5</v>
       </c>
       <c r="C1266" s="4" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
       <c r="D1266" s="4" t="s">
-        <v>4551</v>
+        <v>4550</v>
       </c>
       <c r="E1266" s="14">
         <v>4.01</v>
@@ -55237,7 +55237,7 @@
         <v>4.5</v>
       </c>
       <c r="H1266" s="30" t="s">
-        <v>4580</v>
+        <v>4579</v>
       </c>
       <c r="I1266" s="3"/>
     </row>
@@ -55249,10 +55249,10 @@
         <v>6</v>
       </c>
       <c r="C1267" s="4" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
       <c r="D1267" s="4" t="s">
-        <v>4552</v>
+        <v>4551</v>
       </c>
       <c r="E1267" s="14">
         <v>3.53</v>
@@ -55264,7 +55264,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1267" s="30" t="s">
-        <v>4581</v>
+        <v>4580</v>
       </c>
       <c r="I1267" s="3"/>
     </row>
@@ -55276,10 +55276,10 @@
         <v>7</v>
       </c>
       <c r="C1268" s="4" t="s">
-        <v>4529</v>
+        <v>4528</v>
       </c>
       <c r="D1268" s="4" t="s">
-        <v>4553</v>
+        <v>4552</v>
       </c>
       <c r="E1268" s="14">
         <v>4.2699999999999996</v>
@@ -55291,7 +55291,7 @@
         <v>4.7</v>
       </c>
       <c r="H1268" s="30" t="s">
-        <v>4582</v>
+        <v>4581</v>
       </c>
       <c r="I1268" s="3"/>
     </row>
@@ -55303,10 +55303,10 @@
         <v>8</v>
       </c>
       <c r="C1269" s="4" t="s">
-        <v>4530</v>
+        <v>4529</v>
       </c>
       <c r="D1269" s="4" t="s">
-        <v>4554</v>
+        <v>4553</v>
       </c>
       <c r="E1269" s="14">
         <v>3.37</v>
@@ -55318,7 +55318,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1269" s="30" t="s">
-        <v>4583</v>
+        <v>4582</v>
       </c>
       <c r="I1269" s="3"/>
     </row>
@@ -55330,10 +55330,10 @@
         <v>9</v>
       </c>
       <c r="C1270" s="4" t="s">
-        <v>4531</v>
+        <v>4530</v>
       </c>
       <c r="D1270" s="4" t="s">
-        <v>4555</v>
+        <v>4554</v>
       </c>
       <c r="E1270" s="14">
         <v>3.21</v>
@@ -55345,7 +55345,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1270" s="30" t="s">
-        <v>4584</v>
+        <v>4583</v>
       </c>
       <c r="I1270" s="3"/>
     </row>
@@ -55357,10 +55357,10 @@
         <v>10</v>
       </c>
       <c r="C1271" s="4" t="s">
-        <v>4532</v>
+        <v>4531</v>
       </c>
       <c r="D1271" s="4" t="s">
-        <v>4556</v>
+        <v>4555</v>
       </c>
       <c r="E1271" s="14">
         <v>3.36</v>
@@ -55372,7 +55372,7 @@
         <v>4.55</v>
       </c>
       <c r="H1271" s="30" t="s">
-        <v>4585</v>
+        <v>4584</v>
       </c>
       <c r="I1271" s="3"/>
     </row>
@@ -55384,10 +55384,10 @@
         <v>11</v>
       </c>
       <c r="C1272" s="4" t="s">
-        <v>4533</v>
+        <v>4532</v>
       </c>
       <c r="D1272" s="4" t="s">
-        <v>4557</v>
+        <v>4556</v>
       </c>
       <c r="E1272" s="14">
         <v>3.78</v>
@@ -55399,7 +55399,7 @@
         <v>4.5</v>
       </c>
       <c r="H1272" s="30" t="s">
-        <v>4576</v>
+        <v>4575</v>
       </c>
       <c r="I1272" s="3"/>
     </row>
@@ -55411,10 +55411,10 @@
         <v>12</v>
       </c>
       <c r="C1273" s="4" t="s">
-        <v>4534</v>
+        <v>4533</v>
       </c>
       <c r="D1273" s="4" t="s">
-        <v>4558</v>
+        <v>4557</v>
       </c>
       <c r="E1273" s="14">
         <v>4</v>
@@ -55426,7 +55426,7 @@
         <v>4.45</v>
       </c>
       <c r="H1273" s="30" t="s">
-        <v>4586</v>
+        <v>4585</v>
       </c>
       <c r="I1273" s="3"/>
     </row>
@@ -55438,10 +55438,10 @@
         <v>13</v>
       </c>
       <c r="C1274" s="4" t="s">
-        <v>4535</v>
+        <v>4534</v>
       </c>
       <c r="D1274" s="4" t="s">
-        <v>4559</v>
+        <v>4558</v>
       </c>
       <c r="E1274" s="14">
         <v>4.01</v>
@@ -55453,7 +55453,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1274" s="30" t="s">
-        <v>4577</v>
+        <v>4576</v>
       </c>
       <c r="I1274" s="3"/>
     </row>
@@ -55465,10 +55465,10 @@
         <v>14</v>
       </c>
       <c r="C1275" s="4" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="D1275" s="4" t="s">
-        <v>4560</v>
+        <v>4559</v>
       </c>
       <c r="E1275" s="14">
         <v>3.35</v>
@@ -55480,7 +55480,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="H1275" s="30" t="s">
-        <v>4575</v>
+        <v>4574</v>
       </c>
       <c r="I1275" s="3"/>
     </row>
@@ -55495,7 +55495,7 @@
         <v>3196</v>
       </c>
       <c r="D1276" s="4" t="s">
-        <v>4561</v>
+        <v>4560</v>
       </c>
       <c r="E1276" s="14">
         <v>3.74</v>
@@ -55507,7 +55507,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1276" s="30" t="s">
-        <v>4574</v>
+        <v>4573</v>
       </c>
       <c r="I1276" s="3"/>
     </row>
@@ -55519,10 +55519,10 @@
         <v>16</v>
       </c>
       <c r="C1277" s="4" t="s">
-        <v>4537</v>
+        <v>4536</v>
       </c>
       <c r="D1277" s="4" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="E1277" s="14">
         <v>2.88</v>
@@ -55534,7 +55534,7 @@
         <v>4.3</v>
       </c>
       <c r="H1277" s="30" t="s">
-        <v>4587</v>
+        <v>4586</v>
       </c>
       <c r="I1277" s="3"/>
     </row>
@@ -55546,10 +55546,10 @@
         <v>17</v>
       </c>
       <c r="C1278" s="4" t="s">
-        <v>4538</v>
+        <v>4537</v>
       </c>
       <c r="D1278" s="4" t="s">
-        <v>4563</v>
+        <v>4562</v>
       </c>
       <c r="E1278" s="14">
         <v>3.16</v>
@@ -55561,7 +55561,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H1278" s="30" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
       <c r="I1278" s="3"/>
     </row>
@@ -55573,10 +55573,10 @@
         <v>18</v>
       </c>
       <c r="C1279" s="4" t="s">
-        <v>4539</v>
+        <v>4538</v>
       </c>
       <c r="D1279" s="4" t="s">
-        <v>4564</v>
+        <v>4563</v>
       </c>
       <c r="E1279" s="14">
         <v>4.01</v>
@@ -55588,7 +55588,7 @@
         <v>4.55</v>
       </c>
       <c r="H1279" s="30" t="s">
-        <v>4588</v>
+        <v>4587</v>
       </c>
       <c r="I1279" s="3"/>
     </row>
@@ -55600,10 +55600,10 @@
         <v>19</v>
       </c>
       <c r="C1280" s="4" t="s">
-        <v>4540</v>
+        <v>4539</v>
       </c>
       <c r="D1280" s="4" t="s">
-        <v>4565</v>
+        <v>4564</v>
       </c>
       <c r="E1280" s="14">
         <v>3.96</v>
@@ -55615,7 +55615,7 @@
         <v>4.5</v>
       </c>
       <c r="H1280" s="30" t="s">
-        <v>4589</v>
+        <v>4588</v>
       </c>
       <c r="I1280" s="3"/>
     </row>
@@ -55627,10 +55627,10 @@
         <v>20</v>
       </c>
       <c r="C1281" s="4" t="s">
-        <v>4541</v>
+        <v>4540</v>
       </c>
       <c r="D1281" s="4" t="s">
-        <v>4566</v>
+        <v>4565</v>
       </c>
       <c r="E1281" s="14">
         <v>3.76</v>
@@ -55642,7 +55642,7 @@
         <v>4.45</v>
       </c>
       <c r="H1281" s="30" t="s">
-        <v>4590</v>
+        <v>4589</v>
       </c>
       <c r="I1281" s="3"/>
     </row>
@@ -55654,10 +55654,10 @@
         <v>21</v>
       </c>
       <c r="C1282" s="4" t="s">
-        <v>4542</v>
+        <v>4541</v>
       </c>
       <c r="D1282" s="4" t="s">
-        <v>4567</v>
+        <v>4566</v>
       </c>
       <c r="E1282" s="14">
         <v>2.97</v>
@@ -55669,7 +55669,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H1282" s="18" t="s">
-        <v>4594</v>
+        <v>4593</v>
       </c>
       <c r="I1282" s="3"/>
     </row>
@@ -55681,10 +55681,10 @@
         <v>22</v>
       </c>
       <c r="C1283" s="4" t="s">
-        <v>4543</v>
+        <v>4542</v>
       </c>
       <c r="D1283" s="4" t="s">
-        <v>4568</v>
+        <v>4567</v>
       </c>
       <c r="E1283" s="14">
         <v>3.86</v>
@@ -55696,7 +55696,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1283" s="30" t="s">
-        <v>4591</v>
+        <v>4590</v>
       </c>
       <c r="I1283" s="3"/>
     </row>
@@ -55708,10 +55708,10 @@
         <v>23</v>
       </c>
       <c r="C1284" s="4" t="s">
-        <v>4544</v>
+        <v>4543</v>
       </c>
       <c r="D1284" s="4" t="s">
-        <v>4569</v>
+        <v>4568</v>
       </c>
       <c r="E1284" s="14">
         <v>4.17</v>
@@ -55723,7 +55723,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H1284" s="30" t="s">
-        <v>4592</v>
+        <v>4591</v>
       </c>
       <c r="I1284" s="3"/>
     </row>
@@ -55735,10 +55735,10 @@
         <v>24</v>
       </c>
       <c r="C1285" s="4" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
       <c r="D1285" s="4" t="s">
-        <v>4570</v>
+        <v>4569</v>
       </c>
       <c r="E1285" s="14">
         <v>3.97</v>
@@ -55750,7 +55750,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1285" s="30" t="s">
-        <v>4593</v>
+        <v>4592</v>
       </c>
       <c r="I1285" s="3"/>
     </row>
@@ -55762,10 +55762,10 @@
         <v>1</v>
       </c>
       <c r="C1286" s="4" t="s">
-        <v>4602</v>
+        <v>4601</v>
       </c>
       <c r="D1286" s="4" t="s">
-        <v>4610</v>
+        <v>4609</v>
       </c>
       <c r="E1286" s="14">
         <v>3.98</v>
@@ -55777,7 +55777,7 @@
         <v>4.7</v>
       </c>
       <c r="H1286" s="17" t="s">
-        <v>4626</v>
+        <v>4625</v>
       </c>
       <c r="I1286" s="3" t="s">
         <v>173</v>
@@ -55791,10 +55791,10 @@
         <v>2</v>
       </c>
       <c r="C1287" s="4" t="s">
-        <v>4603</v>
+        <v>4602</v>
       </c>
       <c r="D1287" s="4" t="s">
-        <v>4611</v>
+        <v>4610</v>
       </c>
       <c r="E1287" s="14">
         <v>3.63</v>
@@ -55806,7 +55806,7 @@
         <v>4.55</v>
       </c>
       <c r="H1287" s="6" t="s">
-        <v>4619</v>
+        <v>4618</v>
       </c>
       <c r="I1287" s="3"/>
     </row>
@@ -55821,7 +55821,7 @@
         <v>1063</v>
       </c>
       <c r="D1288" s="4" t="s">
-        <v>4612</v>
+        <v>4611</v>
       </c>
       <c r="E1288" s="14">
         <v>4.16</v>
@@ -55833,7 +55833,7 @@
         <v>4.8</v>
       </c>
       <c r="H1288" s="17" t="s">
-        <v>4627</v>
+        <v>4626</v>
       </c>
       <c r="I1288" s="3" t="s">
         <v>173</v>
@@ -55847,10 +55847,10 @@
         <v>4</v>
       </c>
       <c r="C1289" s="4" t="s">
-        <v>4601</v>
+        <v>4600</v>
       </c>
       <c r="D1289" s="4" t="s">
-        <v>4613</v>
+        <v>4612</v>
       </c>
       <c r="E1289" s="14">
         <v>3.83</v>
@@ -55862,7 +55862,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H1289" s="6" t="s">
-        <v>4621</v>
+        <v>4620</v>
       </c>
       <c r="I1289" s="3"/>
     </row>
@@ -55874,10 +55874,10 @@
         <v>5</v>
       </c>
       <c r="C1290" s="4" t="s">
-        <v>4604</v>
+        <v>4603</v>
       </c>
       <c r="D1290" s="4" t="s">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="E1290" s="14">
         <v>3.34</v>
@@ -55889,7 +55889,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1290" s="6" t="s">
-        <v>4620</v>
+        <v>4619</v>
       </c>
       <c r="I1290" s="3"/>
     </row>
@@ -55901,10 +55901,10 @@
         <v>6</v>
       </c>
       <c r="C1291" s="4" t="s">
-        <v>4605</v>
+        <v>4604</v>
       </c>
       <c r="D1291" s="4" t="s">
-        <v>4615</v>
+        <v>4614</v>
       </c>
       <c r="E1291" s="14">
         <v>3.77</v>
@@ -55916,7 +55916,7 @@
         <v>4.75</v>
       </c>
       <c r="H1291" s="6" t="s">
-        <v>4622</v>
+        <v>4621</v>
       </c>
       <c r="I1291" s="3"/>
     </row>
@@ -55928,10 +55928,10 @@
         <v>7</v>
       </c>
       <c r="C1292" s="4" t="s">
-        <v>4606</v>
+        <v>4605</v>
       </c>
       <c r="D1292" s="4" t="s">
-        <v>4616</v>
+        <v>4615</v>
       </c>
       <c r="E1292" s="14">
         <v>3.57</v>
@@ -55943,7 +55943,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1292" s="6" t="s">
-        <v>4623</v>
+        <v>4622</v>
       </c>
       <c r="I1292" s="3"/>
     </row>
@@ -55955,10 +55955,10 @@
         <v>8</v>
       </c>
       <c r="C1293" s="4" t="s">
-        <v>4607</v>
+        <v>4606</v>
       </c>
       <c r="D1293" s="4" t="s">
-        <v>4617</v>
+        <v>4616</v>
       </c>
       <c r="E1293" s="14">
         <v>3.8</v>
@@ -55970,7 +55970,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H1293" s="6" t="s">
-        <v>4624</v>
+        <v>4623</v>
       </c>
       <c r="I1293" s="3"/>
     </row>
@@ -55982,10 +55982,10 @@
         <v>9</v>
       </c>
       <c r="C1294" s="4" t="s">
-        <v>4608</v>
+        <v>4607</v>
       </c>
       <c r="D1294" s="4" t="s">
-        <v>4618</v>
+        <v>4617</v>
       </c>
       <c r="E1294" s="14">
         <v>3.33</v>
@@ -55997,7 +55997,7 @@
         <v>4.5</v>
       </c>
       <c r="H1294" s="6" t="s">
-        <v>4625</v>
+        <v>4624</v>
       </c>
       <c r="I1294" s="3"/>
     </row>
@@ -56009,10 +56009,10 @@
         <v>1</v>
       </c>
       <c r="C1295" s="4" t="s">
-        <v>4631</v>
+        <v>4630</v>
       </c>
       <c r="D1295" s="4" t="s">
-        <v>4641</v>
+        <v>4640</v>
       </c>
       <c r="E1295" s="14">
         <v>3.89</v>
@@ -56024,7 +56024,7 @@
         <v>4.7</v>
       </c>
       <c r="H1295" s="6" t="s">
-        <v>4650</v>
+        <v>4649</v>
       </c>
       <c r="I1295" s="3"/>
     </row>
@@ -56036,10 +56036,10 @@
         <v>2</v>
       </c>
       <c r="C1296" s="4" t="s">
-        <v>4633</v>
+        <v>4632</v>
       </c>
       <c r="D1296" s="4" t="s">
-        <v>4642</v>
+        <v>4641</v>
       </c>
       <c r="E1296" s="14">
         <v>3.92</v>
@@ -56051,7 +56051,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H1296" s="6" t="s">
-        <v>4651</v>
+        <v>4650</v>
       </c>
       <c r="I1296" s="3"/>
     </row>
@@ -56063,10 +56063,10 @@
         <v>3</v>
       </c>
       <c r="C1297" s="4" t="s">
-        <v>4634</v>
+        <v>4633</v>
       </c>
       <c r="D1297" s="4" t="s">
-        <v>4643</v>
+        <v>4642</v>
       </c>
       <c r="E1297" s="14">
         <v>3.33</v>
@@ -56078,7 +56078,7 @@
         <v>4.5</v>
       </c>
       <c r="H1297" s="6" t="s">
-        <v>4652</v>
+        <v>4651</v>
       </c>
       <c r="I1297" s="3"/>
     </row>
@@ -56090,10 +56090,10 @@
         <v>4</v>
       </c>
       <c r="C1298" s="4" t="s">
-        <v>4635</v>
+        <v>4634</v>
       </c>
       <c r="D1298" s="4" t="s">
-        <v>4644</v>
+        <v>4643</v>
       </c>
       <c r="E1298" s="14">
         <v>4.13</v>
@@ -56105,7 +56105,7 @@
         <v>4.95</v>
       </c>
       <c r="H1298" s="6" t="s">
-        <v>4653</v>
+        <v>4652</v>
       </c>
       <c r="I1298" s="3"/>
     </row>
@@ -56117,10 +56117,10 @@
         <v>5</v>
       </c>
       <c r="C1299" s="4" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
       <c r="D1299" s="4" t="s">
-        <v>4645</v>
+        <v>4644</v>
       </c>
       <c r="E1299" s="14">
         <v>3.67</v>
@@ -56132,7 +56132,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1299" s="17" t="s">
-        <v>4654</v>
+        <v>4653</v>
       </c>
       <c r="I1299" s="3" t="s">
         <v>173</v>
@@ -56146,10 +56146,10 @@
         <v>6</v>
       </c>
       <c r="C1300" s="4" t="s">
-        <v>4637</v>
+        <v>4636</v>
       </c>
       <c r="D1300" s="4" t="s">
-        <v>4646</v>
+        <v>4645</v>
       </c>
       <c r="E1300" s="14">
         <v>3.76</v>
@@ -56161,7 +56161,7 @@
         <v>4.75</v>
       </c>
       <c r="H1300" s="17" t="s">
-        <v>4655</v>
+        <v>4654</v>
       </c>
       <c r="I1300" s="3" t="s">
         <v>173</v>
@@ -56175,10 +56175,10 @@
         <v>7</v>
       </c>
       <c r="C1301" s="4" t="s">
-        <v>4638</v>
+        <v>4637</v>
       </c>
       <c r="D1301" s="4" t="s">
-        <v>4647</v>
+        <v>4646</v>
       </c>
       <c r="E1301" s="14">
         <v>3.72</v>
@@ -56190,7 +56190,7 @@
         <v>4.8</v>
       </c>
       <c r="H1301" s="17" t="s">
-        <v>4656</v>
+        <v>4655</v>
       </c>
       <c r="I1301" s="3" t="s">
         <v>173</v>
@@ -56204,10 +56204,10 @@
         <v>8</v>
       </c>
       <c r="C1302" s="4" t="s">
-        <v>4639</v>
+        <v>4638</v>
       </c>
       <c r="D1302" s="4" t="s">
-        <v>4648</v>
+        <v>4647</v>
       </c>
       <c r="E1302" s="14">
         <v>3.34</v>
@@ -56219,7 +56219,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1302" s="6" t="s">
-        <v>4649</v>
+        <v>4648</v>
       </c>
       <c r="I1302" s="3"/>
     </row>
@@ -56231,10 +56231,10 @@
         <v>1</v>
       </c>
       <c r="C1303" s="4" t="s">
-        <v>4663</v>
+        <v>4662</v>
       </c>
       <c r="D1303" s="8" t="s">
-        <v>4676</v>
+        <v>4675</v>
       </c>
       <c r="E1303" s="14">
         <v>4.2300000000000004</v>
@@ -56246,7 +56246,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H1303" s="17" t="s">
-        <v>4698</v>
+        <v>4697</v>
       </c>
       <c r="I1303" s="3" t="s">
         <v>173</v>
@@ -56260,10 +56260,10 @@
         <v>2</v>
       </c>
       <c r="C1304" s="4" t="s">
-        <v>4664</v>
+        <v>4663</v>
       </c>
       <c r="D1304" s="8" t="s">
-        <v>4677</v>
+        <v>4676</v>
       </c>
       <c r="E1304" s="14">
         <v>3.67</v>
@@ -56275,7 +56275,7 @@
         <v>4.5</v>
       </c>
       <c r="H1304" s="6" t="s">
-        <v>4690</v>
+        <v>4689</v>
       </c>
       <c r="I1304" s="3"/>
     </row>
@@ -56287,10 +56287,10 @@
         <v>3</v>
       </c>
       <c r="C1305" s="4" t="s">
-        <v>4665</v>
+        <v>4664</v>
       </c>
       <c r="D1305" s="8" t="s">
-        <v>4678</v>
+        <v>4677</v>
       </c>
       <c r="E1305" s="14">
         <v>3.55</v>
@@ -56302,7 +56302,7 @@
         <v>4.7</v>
       </c>
       <c r="H1305" s="17" t="s">
-        <v>4697</v>
+        <v>4696</v>
       </c>
       <c r="I1305" s="3" t="s">
         <v>173</v>
@@ -56316,10 +56316,10 @@
         <v>4</v>
       </c>
       <c r="C1306" s="4" t="s">
-        <v>4666</v>
+        <v>4665</v>
       </c>
       <c r="D1306" s="8" t="s">
-        <v>4679</v>
+        <v>4678</v>
       </c>
       <c r="E1306" s="14">
         <v>4.12</v>
@@ -56331,7 +56331,7 @@
         <v>4.8</v>
       </c>
       <c r="H1306" s="6" t="s">
-        <v>4688</v>
+        <v>4687</v>
       </c>
       <c r="I1306" s="3"/>
     </row>
@@ -56343,10 +56343,10 @@
         <v>5</v>
       </c>
       <c r="C1307" s="4" t="s">
-        <v>4667</v>
+        <v>4666</v>
       </c>
       <c r="D1307" s="8" t="s">
-        <v>4680</v>
+        <v>4679</v>
       </c>
       <c r="E1307" s="14">
         <v>3.96</v>
@@ -56358,7 +56358,7 @@
         <v>4.75</v>
       </c>
       <c r="H1307" s="6" t="s">
-        <v>4691</v>
+        <v>4690</v>
       </c>
       <c r="I1307" s="3"/>
     </row>
@@ -56370,10 +56370,10 @@
         <v>6</v>
       </c>
       <c r="C1308" s="4" t="s">
-        <v>4668</v>
+        <v>4667</v>
       </c>
       <c r="D1308" s="8" t="s">
-        <v>4681</v>
+        <v>4680</v>
       </c>
       <c r="E1308" s="14">
         <v>3.39</v>
@@ -56385,7 +56385,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1308" s="6" t="s">
-        <v>4692</v>
+        <v>4691</v>
       </c>
       <c r="I1308" s="3"/>
     </row>
@@ -56397,10 +56397,10 @@
         <v>7</v>
       </c>
       <c r="C1309" s="4" t="s">
-        <v>4669</v>
+        <v>4668</v>
       </c>
       <c r="D1309" s="8" t="s">
-        <v>4682</v>
+        <v>4681</v>
       </c>
       <c r="E1309" s="14">
         <v>3.62</v>
@@ -56412,7 +56412,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="H1309" s="6" t="s">
-        <v>4689</v>
+        <v>4688</v>
       </c>
       <c r="I1309" s="3"/>
     </row>
@@ -56424,10 +56424,10 @@
         <v>8</v>
       </c>
       <c r="C1310" s="4" t="s">
-        <v>4670</v>
+        <v>4669</v>
       </c>
       <c r="D1310" s="8" t="s">
-        <v>4683</v>
+        <v>4682</v>
       </c>
       <c r="E1310" s="14">
         <v>4</v>
@@ -56439,7 +56439,7 @@
         <v>4.95</v>
       </c>
       <c r="H1310" s="6" t="s">
-        <v>4693</v>
+        <v>4692</v>
       </c>
       <c r="I1310" s="3"/>
     </row>
@@ -56451,10 +56451,10 @@
         <v>9</v>
       </c>
       <c r="C1311" s="4" t="s">
-        <v>4671</v>
+        <v>4670</v>
       </c>
       <c r="D1311" s="8" t="s">
-        <v>4684</v>
+        <v>4683</v>
       </c>
       <c r="E1311" s="14">
         <v>4.09</v>
@@ -56466,7 +56466,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="H1311" s="6" t="s">
-        <v>4694</v>
+        <v>4693</v>
       </c>
       <c r="I1311" s="3"/>
     </row>
@@ -56478,10 +56478,10 @@
         <v>10</v>
       </c>
       <c r="C1312" s="4" t="s">
-        <v>4672</v>
+        <v>4671</v>
       </c>
       <c r="D1312" s="8" t="s">
-        <v>4685</v>
+        <v>4684</v>
       </c>
       <c r="E1312" s="14">
         <v>3.43</v>
@@ -56493,7 +56493,7 @@
         <v>4.7</v>
       </c>
       <c r="H1312" s="6" t="s">
-        <v>4695</v>
+        <v>4694</v>
       </c>
       <c r="I1312" s="3"/>
     </row>
@@ -56505,10 +56505,10 @@
         <v>11</v>
       </c>
       <c r="C1313" s="4" t="s">
-        <v>4673</v>
+        <v>4672</v>
       </c>
       <c r="D1313" s="8" t="s">
-        <v>4686</v>
+        <v>4685</v>
       </c>
       <c r="E1313" s="14">
         <v>4.62</v>
@@ -56520,7 +56520,7 @@
         <v>5</v>
       </c>
       <c r="H1313" s="6" t="s">
-        <v>4699</v>
+        <v>4698</v>
       </c>
       <c r="I1313" s="3" t="s">
         <v>173</v>
@@ -56534,10 +56534,10 @@
         <v>12</v>
       </c>
       <c r="C1314" s="4" t="s">
-        <v>4674</v>
+        <v>4673</v>
       </c>
       <c r="D1314" s="8" t="s">
-        <v>4687</v>
+        <v>4686</v>
       </c>
       <c r="E1314" s="14">
         <v>3.31</v>
@@ -56549,7 +56549,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="H1314" s="6" t="s">
-        <v>4696</v>
+        <v>4695</v>
       </c>
       <c r="I1314" s="3"/>
     </row>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7AE182-DA0D-4A45-8ED2-94237FAE3D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B5F2C6-BDBB-409C-83D8-91638A44E339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="4701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5112" uniqueCount="4735">
   <si>
     <t>No</t>
   </si>
@@ -15599,6 +15599,145 @@
   </si>
   <si>
     <t>Chrysalis – CHR 1099. Βρετανική έκδοση (UK), κυκλοφορία 31 Αυγούστου 1976, σε στερεοφωνικό βινύλιο, με κοπή/mastering από τους EG (Pecko Duck) και Harry T. Moss (HTM), και εκτύπωση/πίεση από την Island Records Manufacturing Ltd.</t>
+  </si>
+  <si>
+    <t>Great White Hope</t>
+  </si>
+  <si>
+    <t>I’m O.K.</t>
+  </si>
+  <si>
+    <t>Sing For The Day</t>
+  </si>
+  <si>
+    <t>The Message</t>
+  </si>
+  <si>
+    <t>Lords Of The Ring</t>
+  </si>
+  <si>
+    <t>Blue Collar Man (Long Nights)</t>
+  </si>
+  <si>
+    <t>Queen Of Spades</t>
+  </si>
+  <si>
+    <t>Renegade</t>
+  </si>
+  <si>
+    <t>Pieces Of Eight</t>
+  </si>
+  <si>
+    <t>Aku-Aku</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Theatrical Hard Rock, Political Rock, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, AOR [Piano-led Prog, Melodic Rock, Self-affirmation Anthem]</t>
+  </si>
+  <si>
+    <t>Soft Rock, Progressive Rock [Folk-pop, Melodic Rock, Acoustic Art Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Spoken Interlude, Concept Transition, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Fantasy Prog, Symphonic Rock, Heavy Art Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Arena Rock, Working-class Rock, Keyboard-Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Symphonic Prog, Dark Theatrical Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Acoustic-to-Arena Rock, Outlaw Rock, Power Ballad]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Concept Rock, Symphonic Rock, Theatrical Ballad]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Instrumental Prog, Polynesian-inspired Rock, Suite Coda]</t>
+  </si>
+  <si>
+    <t>A&amp;M Records – AMLH 64724 (AMLH 19-64724). Ελληνική έκδοση (Greek pressing) του 1978, κατασκευασμένη στην Ελλάδα για τη Diski CBS AEBE, χρησιμοποιώντας ωστόσο ολλανδικές μήτρες (Pressed by CBS, Haarlem) και ευρωπαϊκό υλικό κοπής. Το mastering και η χάραξη (Lacquer Cut) έγιναν από τον Ted Jensen στη Sterling Sound.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Pieces Of Eight είναι η φυσική συνέχεια του The Grand Illusion, αλλά όχι απλή επανάληψή του. Οι Styx κρατούν το μείγμα prog + pomp + hard rock, το κάνουν καθαρότερο και προσθέτουν περισσότερο κοινωνικό περιεχόμενο. Ο δίσκος είναι λιγότερο ενιαίος ως concept από τον προκάτοχό του, αλλά έχει μεγαλύτερη ποικιλία και δύο εξαιρετικά singles: “Blue Collar Man” και “Renegade”.
+Η κόπια έχει ιδιαίτερο ενδιαφέρον επειδή είναι ελληνικό pressing με ευρωπαϊκό Sterling/Holland metalwork. Τα SP 5185 / SP 5186, STERLING TJ, HOLLAND και το trumpet mark εξηγούν γιατί τα matrices μοιάζουν με την ευρωπαϊκή έκδοση, ενώ το label και η σημείωση “Manufactured in Greece for Diski CBS AEBE” επιβεβαιώνουν την τελική ελληνική κατασκευή. Ως album αξίζει 4,4/5, με “Renegade”, “Blue Collar Man”, “I’m O.K.” και “Sing For The Day” ως βασικούς πυλώνες. </t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/2715995-Styx-Pieces-Of-Eight</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/DLsirmWc96G_Xjaj-aqupRKd8HPTnawjl84j3FsZRB4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTI3MTU5/OTUtMTQwNzc1MDkz/Mi0xNTcyLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Instrumental/cinematic finale με πολυνησιακές ή εξωτικές αναφορές. Το “Aku-Aku” παραπέμπει στα πνευματικά/προστατευτικά όντα της Rapa Nui, και η μουσική δημιουργεί αίσθηση απομακρυσμένου νησιού, τελετουργίας και μυστηρίου. Τα keyboards και οι κιθάρες λειτουργούν περισσότερο σαν soundtrack παρά σαν συμβατικό rock τραγούδι. Ως closing coda απομακρύνεται από το κοινωνικό δράμα του “Blue Collar Man” και την αφηγηματική ένταση του “Renegade”, αφήνοντας το album σε ονειρικό, σχεδόν κινηματογραφικό χώρο. Δεν είναι το πιο ισχυρό standalone κομμάτι, αλλά κλείνει σωστά το LP επειδή επιστρέφει την προσοχή από το καθημερινό στο μυθικό.</t>
+  </si>
+  <si>
+    <t>Η A πλευρά ανοίγει με κοινωνικό και πολιτικό hard rock. Ο τίτλος παραπέμπει στη ρατσιστική/εξουσιαστική εικόνα του “great white hope” , του λευκού σωτήρα ή πρωταθλητή που παρουσιάζεται ως λύση για μια κοινωνία που αρνείται να αντιμετωπίσει τις πραγματικές της ανισότητες. Η μουσική συνδυάζει κιθάρα, πλήκτρα και θεατρική ανάπτυξη, ενώ οι Styx αποφεύγουν να το κάνουν απλό protest song. Υπάρχει αρκετή pomp-rock μεγαλοπρέπεια, αλλά και αίσθηση σαρκασμού, το “hope” μπορεί να είναι τόσο κατασκευασμένο όσο η ίδια η εικόνα της εξουσίας. Ως opener προετοιμάζει το album για θέματα κοινωνικού ρόλου, προσωπικής ταυτότητας και κατασκευασμένων μύθων.</t>
+  </si>
+  <si>
+    <t>Piano-led, μελωδικό prog τραγούδι με αφηγητή που προσπαθεί να πείσει τον εαυτό του , και τους άλλους , ότι αντέχει. Το “I’m OK” είναι φράση που μπορεί να σημαίνει πραγματική αυτοπεποίθηση, αλλά και άρνηση, όσο περισσότερο επαναλαμβάνεται, τόσο περισσότερο μοιάζει να κρύβει δυσκολία. Η σύνθεση του Dennis DeYoung έχει theatrical verse/chorus ανάπτυξη, πλούσιες αρμονίες και keyboard χρώματα, χωρίς να γίνεται υπερβολικά σύνθετη. Είναι από τα πιο ώριμα songs του album, επειδή αντιμετωπίζει την προσωπική ανασφάλεια όχι με μελοδραματισμό, αλλά με σταδιακή αποκάλυψη.</t>
+  </si>
+  <si>
+    <t>Η πιο φωτεινή και folk-pop στιγμή της A πλευράς. Το τραγούδι παρουσιάζει το τραγούδι ως μορφή παρηγοριάς και επικοινωνίας, όταν ο κόσμος είναι δύσκολος, η μουσική δημιουργεί μια μικρή καθημερινή τελετουργία. Η ακουστική υφή, η μελωδία και οι φωνητικές αρμονίες το κάνουν πιο τρυφερό από τα προηγούμενα tracks. Δεν είναι απλώς soft-rock ανάπαυση· λειτουργεί ως δήλωση του ρόλου της τέχνης μέσα στο album. Οι Styx δείχνουν ότι η prog αισθητική τους μπορεί να εκφραστεί με απλότητα, χωρίς μεγάλες ενορχηστρωτικές εκρήξεις.</t>
+  </si>
+  <si>
+    <t>Σύντομο concept interlude που διακόπτει τη ροή για να εισαγάγει ένα ηχητικό/θεατρικό μήνυμα. Δεν είναι πλήρης σύνθεση, αλλά λειτουργεί όπως ένα spoken transition σε rock theatre, μετακινεί τον ακροατή από την προσωπική εξομολόγηση του “Sing for the Day” προς τον fantasy/symphonic κόσμο του “Lords of the Ring”. Η αξιολόγηση 3,9/5 είναι σκόπιμα πιο χαμηλή μόνο επειδή πρόκειται για miniature. Στη συνολική αρχιτεκτονική του LP, όμως, είναι χρήσιμο και σωστά τοποθετημένο.</t>
+  </si>
+  <si>
+    <t>Fantasy-inflected progressive rock με εικόνα αρχόντων, εξουσίας και κύκλου κυριαρχίας. Ο τίτλος δημιουργεί μια μυθική σκηνή, όμως το τραγούδι μπορεί να διαβαστεί και πολιτικά, ποιοι γίνονται “lords”, ποιος τους υπηρετεί και πώς η δύναμη παρουσιάζεται ως φυσική ή αναπόφευκτη. Τα keyboards φέρνουν symphonic χρώμα, ενώ οι κιθάρες κρατούν το track στο hard-rock έδαφος. Δεν είναι τόσο άμεσο όσο τα μεγάλα singles της B πλευράς, αλλά προσφέρει την πιο καθαρή prog/fantasy διάσταση του πρώτου μισού.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, θεατρικό και πιο σύνθετο τραγούδι. Η “Queen of Spades” μπορεί να διαβαστεί ως επικίνδυνη γυναίκα, τυχερό/μοιραίο χαρτί ή προσωποποίηση της τύχης που ελέγχει τον αφηγητή. Η μουσική χρησιμοποιεί symphonic πλήκτρα, κιθαριστικά accents και dramatic vocal movement, διατηρώντας μια αίσθηση power ballad χωρίς να γίνεται συμβατική. Είναι από τις πιο χαρακτηριστικές DeYoung συνθέσεις του album, συναισθηματική αλλά και theatrical, με αρκετή σκοτεινιά ώστε να ξεφύγει από το ασφαλές AOR. Η B πλευρά αρχίζει εδώ να παίρνει μεγαλύτερο δραματικό βάρος.</t>
+  </si>
+  <si>
+    <t>Το title track χρησιμοποιεί το “pieces of eight” , τα ασημένια νομίσματα/θησαυρό των πειρατών , ως μεταφορά για υλικό πλούτο, απληστία και την αξία που δίνουμε στα αντικείμενα. Η μουσική είναι πιο ατμοσφαιρική και conceptual από το “Renegade”, με keyboards και χορωδιακά layers να δημιουργούν αίσθηση παλιού μύθου ή θαλασσινής ιστορίας. Κάτω από το fantasy surface υπάρχει η βασική ερώτηση του δίσκου, τι αγοράζει πραγματικά ο πλούτος; Η σύνθεση δεν είναι τόσο άμεση, αλλά λειτουργεί ως θεματική επιστροφή στο ζήτημα των κοινωνικών ρόλων και της επίπλαστης επιτυχίας που είχε εισαχθεί στο The Grand Illusion.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">B3. Renegade: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Το πιο επιτυχημένο τραγούδι του album και μία από τις οριστικές συνθέσεις των Styx. Ο “renegade” είναι ο παράνομος/φυγάς που βρίσκεται ανάμεσα στην ελευθερία και στην καταδίωξη, ενώ ο στίχος κινείται προς το αναπόφευκτο της σύλληψης και της τιμωρίας. Η σύνθεση ξεκινά σχετικά ήρεμα, με acoustic/folk-rock αίσθηση, και ανεβαίνει σε μεγάλο, σχεδόν κινηματογραφικό chorus. Αυτή η αντίθεση είναι η δύναμή του, η ιστορία είναι προσωπική και αφηγηματική, αλλά η μουσική αποκτά arena κλίμακα. Έφτασε στο No. 16 και παραμένει κλασικό live staple των Styx.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">B1. Blue Collar Man (Long Nights): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Το βασικό εργατικό/working-class anthem του album. Ο “blue collar man” είναι ο άνθρωπος της χειρωνακτικής εργασίας, των χαμηλών αμοιβών, της κόπωσης και των “long nights” που περνούν στη δουλειά ή στην αγωνία. Ο Tommy Shaw δίνει το κατάλληλο vocal edge, ενώ κιθάρα και keyboards δημιουργούν ένα από τα πιο ισχυρά arena-rock arrangements των Styx. Το τραγούδι δεν παρουσιάζει τον εργαζόμενο ως θύμα χωρίς δύναμη, έχει περηφάνια, θυμό και αποφασιστικότητα. Αυτό εξηγεί γιατί έγινε τόσο σταθερό live track , συνδέει κοινωνικό περιεχόμενο με άμεσο, συναυλιακό chorus.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -16193,7 +16332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -20524,6 +20663,38 @@
       </c>
       <c r="J135" s="7" t="s">
         <v>3050</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>4709</v>
+      </c>
+      <c r="D136" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E136" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>4639</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>4722</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>4721</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>4723</v>
+      </c>
+      <c r="J136" s="7" t="s">
+        <v>4724</v>
       </c>
     </row>
   </sheetData>
@@ -20797,6 +20968,8 @@
     <hyperlink ref="J110" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
     <hyperlink ref="I84" r:id="rId264" xr:uid="{65C8A524-1F2E-408F-9C4E-A8DCC7FE2AC3}"/>
     <hyperlink ref="J84" r:id="rId265" xr:uid="{7354F640-B4B5-4D02-9DA0-17429462CBFC}"/>
+    <hyperlink ref="I136" r:id="rId266" xr:uid="{F7F90A0C-1255-4B1C-B6C5-A3741DBF44D9}"/>
+    <hyperlink ref="J136" r:id="rId267" xr:uid="{C08BA9FA-1885-4E4A-A596-729CCFBD9D8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20804,7 +20977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1314"/>
+  <dimension ref="A1:I1324"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -56553,6 +56726,280 @@
       </c>
       <c r="I1314" s="3"/>
     </row>
+    <row r="1315" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1315" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1315" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1315" s="4" t="s">
+        <v>4701</v>
+      </c>
+      <c r="D1315" s="8" t="s">
+        <v>4711</v>
+      </c>
+      <c r="E1315" s="14">
+        <v>3.51</v>
+      </c>
+      <c r="F1315" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G1315" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1315" s="6" t="s">
+        <v>4726</v>
+      </c>
+      <c r="I1315" s="3"/>
+    </row>
+    <row r="1316" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1316" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1316" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1316" s="4" t="s">
+        <v>4702</v>
+      </c>
+      <c r="D1316" s="8" t="s">
+        <v>4712</v>
+      </c>
+      <c r="E1316" s="14">
+        <v>3.32</v>
+      </c>
+      <c r="F1316" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="G1316" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1316" s="6" t="s">
+        <v>4727</v>
+      </c>
+      <c r="I1316" s="3"/>
+    </row>
+    <row r="1317" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1317" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1317" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1317" s="4" t="s">
+        <v>4703</v>
+      </c>
+      <c r="D1317" s="8" t="s">
+        <v>4713</v>
+      </c>
+      <c r="E1317" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="F1317" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="G1317" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="H1317" s="6" t="s">
+        <v>4728</v>
+      </c>
+      <c r="I1317" s="3"/>
+    </row>
+    <row r="1318" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1318" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1318" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1318" s="4" t="s">
+        <v>4704</v>
+      </c>
+      <c r="D1318" s="8" t="s">
+        <v>4714</v>
+      </c>
+      <c r="E1318" s="14">
+        <v>2.99</v>
+      </c>
+      <c r="F1318" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G1318" s="11">
+        <v>4</v>
+      </c>
+      <c r="H1318" s="6" t="s">
+        <v>4729</v>
+      </c>
+      <c r="I1318" s="3"/>
+    </row>
+    <row r="1319" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1319" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1319" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1319" s="4" t="s">
+        <v>4705</v>
+      </c>
+      <c r="D1319" s="8" t="s">
+        <v>4715</v>
+      </c>
+      <c r="E1319" s="14">
+        <v>3.46</v>
+      </c>
+      <c r="F1319" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G1319" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1319" s="6" t="s">
+        <v>4730</v>
+      </c>
+      <c r="I1319" s="3"/>
+    </row>
+    <row r="1320" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1320" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1320" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1320" s="4" t="s">
+        <v>4706</v>
+      </c>
+      <c r="D1320" s="8" t="s">
+        <v>4716</v>
+      </c>
+      <c r="E1320" s="14">
+        <v>4.13</v>
+      </c>
+      <c r="F1320" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1320" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1320" s="6" t="s">
+        <v>4734</v>
+      </c>
+      <c r="I1320" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1321" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1321" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1321" s="4" t="s">
+        <v>4707</v>
+      </c>
+      <c r="D1321" s="8" t="s">
+        <v>4717</v>
+      </c>
+      <c r="E1321" s="14">
+        <v>3.81</v>
+      </c>
+      <c r="F1321" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1321" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="H1321" s="6" t="s">
+        <v>4731</v>
+      </c>
+      <c r="I1321" s="3"/>
+    </row>
+    <row r="1322" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1322" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1322" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1322" s="4" t="s">
+        <v>4708</v>
+      </c>
+      <c r="D1322" s="8" t="s">
+        <v>4718</v>
+      </c>
+      <c r="E1322" s="14">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F1322" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1322" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H1322" s="6" t="s">
+        <v>4733</v>
+      </c>
+      <c r="I1322" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1323" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1323" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1323" s="4" t="s">
+        <v>4709</v>
+      </c>
+      <c r="D1323" s="8" t="s">
+        <v>4719</v>
+      </c>
+      <c r="E1323" s="14">
+        <v>3.68</v>
+      </c>
+      <c r="F1323" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1323" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1323" s="6" t="s">
+        <v>4732</v>
+      </c>
+      <c r="I1323" s="3"/>
+    </row>
+    <row r="1324" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1324" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B1324" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1324" s="4" t="s">
+        <v>4710</v>
+      </c>
+      <c r="D1324" s="8" t="s">
+        <v>4720</v>
+      </c>
+      <c r="E1324" s="14">
+        <v>3.19</v>
+      </c>
+      <c r="F1324" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G1324" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1324" s="6" t="s">
+        <v>4725</v>
+      </c>
+      <c r="I1324" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B5F2C6-BDBB-409C-83D8-91638A44E339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89730581-9438-40E2-BDF4-1F210FE9C03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5112" uniqueCount="4735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="4768">
   <si>
     <t>No</t>
   </si>
@@ -15737,6 +15737,138 @@
         <charset val="161"/>
       </rPr>
       <t>Το βασικό εργατικό/working-class anthem του album. Ο “blue collar man” είναι ο άνθρωπος της χειρωνακτικής εργασίας, των χαμηλών αμοιβών, της κόπωσης και των “long nights” που περνούν στη δουλειά ή στην αγωνία. Ο Tommy Shaw δίνει το κατάλληλο vocal edge, ενώ κιθάρα και keyboards δημιουργούν ένα από τα πιο ισχυρά arena-rock arrangements των Styx. Το τραγούδι δεν παρουσιάζει τον εργαζόμενο ως θύμα χωρίς δύναμη, έχει περηφάνια, θυμό και αποφασιστικότητα. Αυτό εξηγεί γιατί έγινε τόσο σταθερό live track , συνδέει κοινωνικό περιεχόμενο με άμεσο, συναυλιακό chorus.</t>
+    </r>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Fire of Unknown Origin (Ιούλιος 1981) σηματοδότησε την εντυπωσιακή αναγέννηση των Blue Öyster Cult μετά από μια περίοδο εμπορικής αβεβαιότητας. Η παραγωγή του θρυλικού Martin Birch (γνωστού από τη δουλειά του με Deep Purple, Black Sabbath και Iron Maiden) έφερε έναν αέρα απόλυτης ηχητικής συνοχής: ο ήχος απέκτησε όγκο, τα τύμπανα του Albert Bouchard punchy ατάκα και οι κιθάρες του Donald "Buck Dharma" Roeser κρυστάλλινο διαχωρισμό, διατηρώντας ακέραια τη σκοτεινή, αινιγματική αύρα του σχήματος. Αρχικά, μεγάλο μέρος του υλικού προοριζόταν για το soundtrack της cult animated ταινίας επιστημονικής φαντασίας Heavy Metal (1981), αν και τελικά μόνο ένα κομμάτι συμπεριλήφθηκε στην ταινία. Στιχουργικά και θεματικά, ο δίσκος αποτελεί ένα απαράμιλλο πάντρεμα pulp φαντασίας, cosmic τρόμου, δυστοπικών οραμάτων και σκοτεινού ρομαντισμού, με τη συμμετοχή του κορυφαίου συγγραφέα επιστημονικής φαντασίας Michael Moorcock, της ποιήτριας Patti Smith και του τακτικού συνεργάτη Richard Meltzer. Η συγκεκριμένη έκδοση της Music On Vinyl προσφέρει εξαιρετικά ποιοτικό audiophile remastering στα 180g, αποδίδοντας πλήρως τη σκοτεινή, πολυστρωματική ατμόσφαιρα και την κορυφαία κιθαριστική παραγωγή του Birch.</t>
+  </si>
+  <si>
+    <t>Blue Öyster Cult</t>
+  </si>
+  <si>
+    <t>Fire Of Unknown Origin</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/16313565-Blue-%C3%96yster-Cult-Fire-Of-Unknown-Origin</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Er9kEnAvQ7SjuQyB_yv6V1F6dsg0U9DcA906Vyy88c4/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE2MzEz/NTY1LTE2MDcwMDc4/MjAtODAwNC5wbmc.jpeg</t>
+  </si>
+  <si>
+    <t>Music On Vinyl – MOVLP2569, Columbia – MOVLP2569. Ευρωπαϊκή επανέκδοση (Reissue, Stereo) σε βινύλιο 180 γραμμαρίων, κυκλοφορημένη στις 4 Δεκεμβρίου 2020 (Made in the EU). Mastered από τον Paul Stubblebine στο The Automatt.</t>
+  </si>
+  <si>
+    <t>Burnin’ For You</t>
+  </si>
+  <si>
+    <t>Veteran Of The Psychic Wars</t>
+  </si>
+  <si>
+    <t>Sole Survivor</t>
+  </si>
+  <si>
+    <t>Heavy Metal: The Black And Silver</t>
+  </si>
+  <si>
+    <t>Vengeance (The Pact)</t>
+  </si>
+  <si>
+    <t>After Dark</t>
+  </si>
+  <si>
+    <t>Joan Crawford</t>
+  </si>
+  <si>
+    <t>Don’t Turn Your Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard Rock, Heavy Metal [AOR, Occult Rock, Sci-Fi Rock, Psychedelic Hard Rock] </t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Dark AOR, Occult Hard Rock, Art Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Power Pop edge, Classic Rock Anthem]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Science-Fiction Rock [Dark Fantasy Rock, Occult Rock, Moody AOR]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Arena Rock, Guitar Pop]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Film Soundtrack Rock, Straight Metal, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Heavy Rock, Occult Metal, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Dark Melodic Rock, Night Rock, Psychedelic Edge]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Gothic Rock, Horror Rock, Dark AOR]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Philosophical Rock, Album Closer]</t>
+  </si>
+  <si>
+    <t>Κλείσιμο με πιο μελωδικό αλλά προειδοποιητικό τόνο. Ο τίτλος είναι προσταγή να μην αποστρέψεις το βλέμμα από έναν κίνδυνο, από μια σχέση ή από το εσωτερικό σκοτάδι που σε ακολουθεί. Μουσικά είναι polished hard rock με AOR στοιχείο, καλές αρμονίες και κιθάρα που ολοκληρώνει τον δίσκο χωρίς υπερβολική κορύφωση. Δεν είναι ισοδύναμο με το “Joan Crawford” σε ιδιοσυγκρασία, αλλά ως finale συνδέει σωστά την προσιτή, μελωδική πλευρά της μπάντας με τις υπόγειες απειλές του concept.</t>
+  </si>
+  <si>
+    <t>Νυχτερινό, ατμοσφαιρικό melodic hard rock με τίτλο που συνδέει την απελευθέρωση με το σκοτάδι. “After dark” είναι ο χρόνος όπου κανόνες και ταυτότητες γίνονται πιο ασταθείς, και η μπάντα χτίζει πάνω σε mid-tempo groove, dark keyboards και συγκρατημένα guitar fills. Δεν είναι τόσο επιθετικό όσο το “Vengeance”, αλλά έχει γοητευτική late-night αίσθηση. Λειτουργεί σωστά ως bridge προς το horror/gothic “Joan Crawford”.</t>
+  </si>
+  <si>
+    <t>Σκοτεινό, θεατρικό heavy rock με έμφαση σε εκδίκηση, όρκο και αναπόφευκτες συνέπειες. Ο “pact” υπονοεί συμφωνία με σκοτεινή δύναμη ή μια δέσμευση που δεν μπορείς να ανακαλέσεις. Οι BÖC αξιοποιούν πιο βαριά κιθάρα και ρυθμική ένταση, δημιουργώντας το κατάλληλο fantasy/occult setting. Είναι από τα καλύτερα B-side cuts, επειδή επαναφέρει τον απειλητικό χαρακτήρα που σε μερικά AOR-leaning tracks μπορεί να έχει εξομαλυνθεί. Δεν είχε το radio impact των singles, αλλά ως album track προσφέρει ουσιαστική ιδιοσυγκρασία.</t>
+  </si>
+  <si>
+    <t>Το title track ανοίγει τον δίσκο με ατμόσφαιρα μυστηρίου και απειλής. Η “φωτιά άγνωστης προέλευσης” λειτουργεί σαν ανεξήγητη καταστροφή , επιστημονικό φαινόμενο, υπερφυσική δύναμη ή ψυχική κρίση , και οι BÖC τη χειρίζονται με βαρύ, μεθοδικό hard-rock groove. Ο Eric Bloom δίνει θεατρικό, σχεδόν αφηγηματικό vocal χαρακτήρα, ενώ τα keyboards και η κιθάρα του Buck Dharma προσθέτουν art-rock βάθος. Δεν είναι τόσο άμεσο όσο το “Burnin’ for You”, αλλά θέτει ιδανικά το sci-fi/occult πλαίσιο του album.</t>
+  </si>
+  <si>
+    <t>Γραμμένο για την ταινία Heavy Metal, είναι πιο ευθύ, ταχύ και μεταλλικό. Ο τίτλος λειτουργεί σαν αυτοαναφορική δήλωση για την αισθητική του είδους , «μαύρο και ασημί» ως δέρμα, μέταλλο, μηχανή και σκοτεινή φαντασία. Η σύνθεση έχει drive και αγκιστρωτικό riff, αλλά δεν διαθέτει τη λογοτεχνική/ατμοσφαιρική ιδιαιτερότητα των καλύτερων BÖC tracks. Παραμένει χρήσιμο ως A-side closer, επειδή ανεβάζει την ένταση και δένει το album με τη science-fiction/cult κινηματογραφική κουλτούρα της εποχής.</t>
+  </si>
+  <si>
+    <t>Μελωδικό AOR/hard-rock τραγούδι για τον επιζώντα που κουβαλά το βάρος μιας μάχης ή μιας καταστροφής. Η σύνθεση έχει έντονο chorus και καθαρή production, με την κιθάρα του Dharma να λειτουργεί περισσότερο υποστηρικτικά παρά με προωθημένο mystique. Είναι καλό album cut, με σωστή θέση μετά το βαρύ “Veteran”, αλλά λιγότερο διακριτό σε σχέση με τα κορυφαία τραγούδια της A πλευράς. Η χαμηλότερη βαθμολογία δεν είναι αρνητική, δείχνει ότι η μπάντα μπορεί να γράψει ποιοτικό melodic rock, απλώς εδώ δεν φτάνει την ιδιαίτερη ταυτότητα του “Burnin’ for You”.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B3. Joan Crawford: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Από τα πιο περίεργα και διασκεδαστικά τραγούδια της μπάντας, Gothic/horror rock όπου η dead Hollywood icon επιστρέφει συμβολικά ως εκδικητική παρουσία. Η Joan Crawford λειτουργεί σαν αρχέτυπο εξουσίας, celebrity glamour και κρυμμένης βίας. Η μουσική διαθέτει sinister keyboards, hard-rock riffing και θεατρική ερμηνεία που μετατρέπει το concept σε μικρή horror-film σκηνή. Η Apple Music επισημαίνει τη doom-laden πλευρά του τραγουδιού ως την σκοτεινή αντίθεση στο “Burnin’ for You”. Αποτέλεσε επίσης δεύτερο radio track, φτάνοντας στο No. 49 του Mainstream Rock chart.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A3. Veteran Of The Psychic Wars: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Σκοτεινή, αργή και βαριά σύνθεση, γραμμένη με τη συμμετοχή του Michael Moorcock. Ο “βετεράνος των ψυχικών πολέμων” είναι ένας ήρωας που έχει επιβιώσει από συγκρούσεις όχι μόνο εξωτερικές αλλά και νοητικές, πόλεμο, προφητείες, ενοχή, απομόνωση και ψυχική εξάντληση. Η σύνθεση συνδυάζει fantasy/sci-fi αφήγηση με πυκνή hard-rock ατμόσφαιρα. Ο Bloom έχει την κατάλληλη κουρασμένη, δραματική χροιά, ενώ η κιθάρα και τα πλήκτρα δημιουργούν απειλητικό χώρο αντί για γρήγορο riff attack. Είναι από τα πιο αντιπροσωπευτικά BÖC tracks της περιόδου, γιατί διατηρεί το λογοτεχνικό occult στοιχείο ακόμα μέσα σε έναν πιο εμπορικό δίσκο. Η Music On Vinyl το κατατάσσει ρητά ανάμεσα στα “Cult classics” του album.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A2. Burnin’ For You: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Η μεγαλύτερη επιτυχία της μπάντας μετά το “(Don’t Fear) The Reaper” και ένα από τα πιο ολοκληρωμένα melodic hard-rock singles της δεκαετίας. Ο Buck Dharma συνδυάζει ονειρική φωνητική γραμμή, μεγάλη μελωδία και διακριτικές αλλά εξαιρετικά εύστοχες κιθαριστικές φράσεις. Ο τίτλος έχει ερωτική αλλά και υπαρξιακή αμφισημία, μπορεί να σημαίνει αφοσίωση, λαχτάρα, αυτοκαταστροφή ή απλώς μια φωτιά που καίει μέσα στον αφηγητή. Η παραγωγή του Martin Birch κάνει το τραγούδι εξαιρετικά καθαρό χωρίς να το αποστειρώνει. Έφτασε στο No. 40 του Billboard Hot 100, έμεινε τρεις εβδομάδες στο Top 40 και έφτασε στο No. 1 του Mainstream Rock chart· η MTV έκθεσή του βοήθησε να γίνει signature BÖC track και classic-rock radio staple.</t>
     </r>
   </si>
 </sst>
@@ -15934,7 +16066,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16021,6 +16153,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16332,7 +16467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -20695,6 +20830,38 @@
       </c>
       <c r="J136" s="7" t="s">
         <v>4724</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>4737</v>
+      </c>
+      <c r="D137" s="3">
+        <v>1981</v>
+      </c>
+      <c r="E137" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>4749</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>4735</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>4740</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>4738</v>
+      </c>
+      <c r="J137" s="7" t="s">
+        <v>4739</v>
       </c>
     </row>
   </sheetData>
@@ -20970,6 +21137,8 @@
     <hyperlink ref="J84" r:id="rId265" xr:uid="{7354F640-B4B5-4D02-9DA0-17429462CBFC}"/>
     <hyperlink ref="I136" r:id="rId266" xr:uid="{F7F90A0C-1255-4B1C-B6C5-A3741DBF44D9}"/>
     <hyperlink ref="J136" r:id="rId267" xr:uid="{C08BA9FA-1885-4E4A-A596-729CCFBD9D8D}"/>
+    <hyperlink ref="I137" r:id="rId268" xr:uid="{67C7E615-CBFE-48F9-AA14-F14A0188E638}"/>
+    <hyperlink ref="J137" r:id="rId269" xr:uid="{D57BF95E-7B0F-40EF-9E3A-010F0E80480A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20977,7 +21146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1324"/>
+  <dimension ref="A1:I1333"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -57000,6 +57169,255 @@
       </c>
       <c r="I1324" s="3"/>
     </row>
+    <row r="1325" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1325" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1325" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1325" s="4" t="s">
+        <v>4737</v>
+      </c>
+      <c r="D1325" s="8" t="s">
+        <v>4750</v>
+      </c>
+      <c r="E1325" s="14">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F1325" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1325" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="H1325" s="6" t="s">
+        <v>4762</v>
+      </c>
+      <c r="I1325" s="3"/>
+    </row>
+    <row r="1326" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1326" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1326" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1326" s="4" t="s">
+        <v>4741</v>
+      </c>
+      <c r="D1326" s="8" t="s">
+        <v>4751</v>
+      </c>
+      <c r="E1326" s="14">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F1326" s="11">
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="G1326" s="31">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1326" s="17" t="s">
+        <v>4767</v>
+      </c>
+      <c r="I1326" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A1327" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1327" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1327" s="4" t="s">
+        <v>4742</v>
+      </c>
+      <c r="D1327" s="8" t="s">
+        <v>4752</v>
+      </c>
+      <c r="E1327" s="14">
+        <v>4.12</v>
+      </c>
+      <c r="F1327" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1327" s="31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1327" s="17" t="s">
+        <v>4766</v>
+      </c>
+      <c r="I1327" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1328" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1328" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1328" s="4" t="s">
+        <v>4743</v>
+      </c>
+      <c r="D1328" s="8" t="s">
+        <v>4753</v>
+      </c>
+      <c r="E1328" s="14">
+        <v>3.89</v>
+      </c>
+      <c r="F1328" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="G1328" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="H1328" s="6" t="s">
+        <v>4764</v>
+      </c>
+      <c r="I1328" s="3"/>
+    </row>
+    <row r="1329" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1329" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1329" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1329" s="4" t="s">
+        <v>4744</v>
+      </c>
+      <c r="D1329" s="8" t="s">
+        <v>4754</v>
+      </c>
+      <c r="E1329" s="14">
+        <v>3.53</v>
+      </c>
+      <c r="F1329" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="G1329" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1329" s="6" t="s">
+        <v>4763</v>
+      </c>
+      <c r="I1329" s="3"/>
+    </row>
+    <row r="1330" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1330" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1330" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1330" s="4" t="s">
+        <v>4745</v>
+      </c>
+      <c r="D1330" s="8" t="s">
+        <v>4755</v>
+      </c>
+      <c r="E1330" s="14">
+        <v>3.92</v>
+      </c>
+      <c r="F1330" s="11">
+        <v>4.05</v>
+      </c>
+      <c r="G1330" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="H1330" s="6" t="s">
+        <v>4761</v>
+      </c>
+      <c r="I1330" s="3"/>
+    </row>
+    <row r="1331" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A1331" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1331" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1331" s="4" t="s">
+        <v>4746</v>
+      </c>
+      <c r="D1331" s="8" t="s">
+        <v>4756</v>
+      </c>
+      <c r="E1331" s="14">
+        <v>3.82</v>
+      </c>
+      <c r="F1331" s="11">
+        <v>4</v>
+      </c>
+      <c r="G1331" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1331" s="6" t="s">
+        <v>4760</v>
+      </c>
+      <c r="I1331" s="3"/>
+    </row>
+    <row r="1332" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1332" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1332" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1332" s="4" t="s">
+        <v>4747</v>
+      </c>
+      <c r="D1332" s="8" t="s">
+        <v>4757</v>
+      </c>
+      <c r="E1332" s="14">
+        <v>4.09</v>
+      </c>
+      <c r="F1332" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1332" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="H1332" s="17" t="s">
+        <v>4765</v>
+      </c>
+      <c r="I1332" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1333" s="3">
+        <v>16313565</v>
+      </c>
+      <c r="B1333" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1333" s="4" t="s">
+        <v>4748</v>
+      </c>
+      <c r="D1333" s="8" t="s">
+        <v>4758</v>
+      </c>
+      <c r="E1333" s="14">
+        <v>3.6</v>
+      </c>
+      <c r="F1333" s="11">
+        <v>3.8499999999999996</v>
+      </c>
+      <c r="G1333" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="H1333" s="6" t="s">
+        <v>4759</v>
+      </c>
+      <c r="I1333" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89730581-9438-40E2-BDF4-1F210FE9C03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627F54F-C871-4708-9339-4C96A7D57EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="4768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="4798">
   <si>
     <t>No</t>
   </si>
@@ -15869,6 +15869,118 @@
         <charset val="161"/>
       </rPr>
       <t>Η μεγαλύτερη επιτυχία της μπάντας μετά το “(Don’t Fear) The Reaper” και ένα από τα πιο ολοκληρωμένα melodic hard-rock singles της δεκαετίας. Ο Buck Dharma συνδυάζει ονειρική φωνητική γραμμή, μεγάλη μελωδία και διακριτικές αλλά εξαιρετικά εύστοχες κιθαριστικές φράσεις. Ο τίτλος έχει ερωτική αλλά και υπαρξιακή αμφισημία, μπορεί να σημαίνει αφοσίωση, λαχτάρα, αυτοκαταστροφή ή απλώς μια φωτιά που καίει μέσα στον αφηγητή. Η παραγωγή του Martin Birch κάνει το τραγούδι εξαιρετικά καθαρό χωρίς να το αποστειρώνει. Έφτασε στο No. 40 του Billboard Hot 100, έμεινε τρεις εβδομάδες στο Top 40 και έφτασε στο No. 1 του Mainstream Rock chart· η MTV έκθεσή του βοήθησε να γίνει signature BÖC track και classic-rock radio staple.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/34956980-Supertramp-Crime-Of-The-Century</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/wWfZ7gos8cbj2Jpkj6Vfv8GC_IGnetvU3JMV2cmwcjc/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM0OTU2/OTgwLTE3NTg5Mzgw/NTQtNTc0OC5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Crime Of The Century</t>
+  </si>
+  <si>
+    <t>Supertramp</t>
+  </si>
+  <si>
+    <t>A&amp;M Records – 00602475450924. Επετειακή έκδοση 50ής επετείου (50th Anniversary Edition, Half Speed Mastered, Reissue, Remastered, Stereo) σε βινύλιο 180 γραμμαρίων, κυκλοφορημένη στις 29 Αυγούστου 2025 (Made in Germany, Pressed by Schallplattenfabrik Pallas GmbH – 65856). Remastered στα Abbey Road Studios από τους Ken Scott και Miles Showell, με lacquer cut (half-speed mastering) από τον Miles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Το Crime of the Century είναι το τρίτο στούντιο άλμπουμ των Supertramp το οποίο κυκλοφόρησε το 1974. Αποτελεί ορόσημο στην ιστορία του art/prog rock με εξαιρετική μηχανική ήχου (Ken Scott, John Jansen). Η συγκεκριμένη έκδοση Half-Speed Mastering από τα Abbey Road Studios απογειώνει τη δυναμική, την καθαρότητα και τη στερεοφωνική εικόνα αυτού του αριστουργήματος. Το Crime of the Century (Σεπτέμβριος 1974) αποτελεί την απόλυτη καλλιτεχνική αναγέννηση των Supertramp και ένα από τα διαχρονικά ορόσημα της audiophile δισκογραφίας παγκοσμίως. Μετά την εμπορική αποτυχία των δύο πρώτων τους δίσκων, οι Rick Davies και Roger Hodgson ανασυγκρότησαν πλήρως το σχήμα (προσθέτοντας τους John Helliwell, Dougie Thomson και Bob Siebenberg) και κλείστηκαν στα Trident, Ramport και Scorpio Sound studios με συμπαραγωγό και ηχολήπτη τον σπουδαίο Ken Scott (The Beatles, David Bowie).   Το αποτέλεσμα ήταν ένα μνημειώδες ηχητικό επίτευγμα. Η δυναμική περιοχή της ηχογράφησης, η απίστευτη αληθοφάνεια του ηλεκτρικού πιάνου Wurlitzer, ο κρυστάλλινος διαχωρισμός των ακουστικών οργάνων και η φυσικότητα των τυμπάνων δημιούργησαν έναν δίσκο αναφοράς για τη δοκιμή ηχοσυστημάτων. Στιχουργικά, το άλμπουμ πραγματεύεται την αποξένωση, την καταπίεση του εκπαιδευτικού και κοινωνικού συστήματος, την ψυχική κατάρρευση και την απώλεια της αθωότητας — θέματα που αποτυπώθηκαν αριστουργηματικά στο διαστημικό κάγκελο φυλακής του Paul Wakefield στο εξώφυλλο.   </t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Bloody Well Right</t>
+  </si>
+  <si>
+    <t>Hide In Your Shell</t>
+  </si>
+  <si>
+    <t>Asylum</t>
+  </si>
+  <si>
+    <t>Dreamer</t>
+  </si>
+  <si>
+    <t>Rudy</t>
+  </si>
+  <si>
+    <t>If Everyone Was Listening</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Piano Rock, Symphonic Rock, Art Pop, Jazz Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Piano-led Prog, Dynamic Rock, Concept Opener]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Piano Rock [Blues Rock, Wurlitzer Rock, British Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Progressive Rock [Piano Ballad, Symphonic Pop, Emotional Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Dark Theatrical Rock, Piano Prog, Concept Epic]</t>
+  </si>
+  <si>
+    <t>Art Pop, Progressive Rock [Wurlitzer Pop, Piano Rock, Art Pop Single]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Jazz Rock, Narrative Prog, Saxophone Rock]</t>
+  </si>
+  <si>
+    <t>Art Rock, Pop Rock [Theatrical Pop, Chamber Rock, Social Satire]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Symphonic Prog, Dark Rock, Album Finale]</t>
+  </si>
+  <si>
+    <t>Η συναισθηματική καρδιά του album. Ο τίτλος απευθύνεται σε κάποιον που κρύβεται μέσα στο “κέλυφός” του , από φόβο, κοινωνική ντροπή, ψυχικό τραύμα ή αίσθηση ότι δεν χωρά πουθενά. Η μελωδία του Hodgson αρχίζει τρυφερά και έπειτα ανοίγει σε πλούσια πιάνα, φωνητικές αρμονίες και μία σχεδόν συμφωνική κορύφωση. Η σύνθεση κατορθώνει να είναι συγκινητική χωρίς να καταλήγει μελοδραματική, επειδή η ενορχήστρωση στηρίζει σταδιακά το θέμα της εσωτερικής απομόνωσης. Δεν υπήρξε single, όμως ως album track είναι από τα πιο αγαπημένα και καλλιτεχνικά καθοριστικά κομμάτια τους. Η Louder την αντιμετωπίζει ως μέρος του δίσκου που όρισε τον signature sound των Supertramp.</t>
+  </si>
+  <si>
+    <t>Η πιο σκοτεινή και θεατρική σύνθεση της A πλευράς. Ο Davies αφηγείται έναν άνθρωπο που έχει απομονωθεί, παγιδευτεί ή χαρακτηριστεί “τρελός” επειδή αρνήθηκε να συμμορφωθεί. Η λέξη “asylum” λειτουργεί και ως ίδρυμα εγκλεισμού και ως τόπος που θα μπορούσε υποτίθεται να προσφέρει άσυλο , μια διπλή σημασία που ταιριάζει στο concept του album. Τα πιάνα, οι αλλαγές δυναμικής, το saxophone και η απειλητική αφηγηματική φωνή δημιουργούν μια small-scale rock opera. Η σύνθεση δεν στηρίζεται σε single-hook, αλλά σε δραματική εξέλιξη, γι’ αυτό παραμένει essential deep cut για όσους ακούν τον δίσκο ως πλήρες έργο.</t>
+  </si>
+  <si>
+    <t>Το πιο bluesy και σαρκαστικό track της A πλευράς. Ο Rick Davies τραγουδά με rough, ειρωνικό τόνο για κάποιον που αρνείται να δεχθεί το κοινωνικό κατεστημένο και δηλώνει ότι οφείλει να παίξει με τους δικούς του όρους. Το Wurlitzer electric piano είναι η καρδιά του τραγουδιού, δίνει percussive attack, συνδέοντας blues rock, piano rock και early AOR. Η σύνθεση είναι πιο compact από το “School”, αλλά εξίσου ισχυρή, επειδή έχει ακριβές groove, άμεσο hook και αίσθηση αντισυμβατικής αυτοπεποίθησης. Στις ΗΠΑ, ως B-side του “Dreamer”, έγινε το πραγματικό breakthrough single των Supertramp, φτάνοντας στο No. 35 του Billboard Hot 100.</t>
+  </si>
+  <si>
+    <t>Το πρώτο πραγματικό UK hit των Supertramp και ένα από τα πιο αναγνωρίσιμα τραγούδια τους. Η φωνή του Hodgson, το Wurlitzer, οι πολυφωνίες και η pop οικονομία δημιουργούν art-pop τραγούδι που έχει αθωότητα αλλά και υπόγεια ειρωνεία, ο “dreamer” μπορεί να είναι κάποιος που φαντάζεται ελευθερία, αλλά μπορεί και να αδυνατεί να αναλάβει τη ζωή του. Το single έφτασε στο No. 13 του UK Singles Chart τον Φεβρουάριο του 1975 και άνοιξε την μπάντα προς κοινό πέρα από τον prog-rock χώρο. Η επιτυχία του είναι ουσιαστική για την ιστορική βαρύτητα, όμως η υψηλή βαθμολογία του βασίζεται και στο γεγονός ότι μεταφέρει την complex Supertramp ταυτότητα σε τρεισήμισι λεπτά art pop.</t>
+  </si>
+  <si>
+    <t>Κινηματογραφικό narrative track για έναν νεαρό που προσπαθεί να φύγει από μια ασφυκτική ζωή, με τον σταθμό/τρένο ως χώρο μετάβασης, κίνησης και μοναξιάς. Τα jazz-rock στοιχεία, το saxophone του John Helliwell, οι εναλλαγές πιάνο–κιθάρας και οι θεατρικές φωνές μετατρέπουν το τραγούδι σε μικρή αστική ταινία. Ο “Rudy” έχει πιο ανοιχτή prog δομή και ίσως δεν είναι τόσο άμεσος όσο το “Dreamer”, αλλά είναι κομβικός για την ενότητα του concept, δείχνει τη στιγμή της απόδρασης από το “school” και το “asylum” προς έναν άγνωστο κόσμο. Αποτελεί δείγμα της ικανότητας του Davies και του Hodgson να ενσωματώνουν saxophone και narrative songwriting χωρίς να χάνουν τον pop πυρήνα.</t>
+  </si>
+  <si>
+    <t>Θεατρικό, ελαφρώς σκοτεινό art-pop τραγούδι για την δημόσια παρακολούθηση, την ανάγκη να σε ακούσουν και την αβεβαιότητα ανάμεσα στην ατομική φωνή και στη μαζική αποδοχή. Ο τίτλος μπορεί να διαβαστεί ως ειρωνική ερώτηση, αν όντως όλοι άκουγαν, θα άλλαζε η αλήθεια ή απλώς θα αυξανόταν η πίεση του να παίζεις έναν ρόλο; Η ενορχήστρωση συνδέει πιάνο, φωνές και θεατρικά touches, με το τραγούδι να λειτουργεί σαν μικρό stage number μέσα στην ευρύτερη “ψυχιατρική”/κοινωνική αφήγηση του album. Είναι κάπως λιγότερο δυναμικό από τα αμέσως γειτονικά “Rudy” και title track, αλλά πολύ σωστό ως προτελευταίο κεφάλαιο επειδή φέρνει ξανά τον ακροατή στο ζήτημα του κοινού και της κρίσης.</t>
+  </si>
+  <si>
+    <r>
+      <t>B4. Crime Of The Century:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το finale συγκεντρώνει το μεγάλο θέμα του album, ποιο είναι το πραγματικό έγκλημα του αιώνα; Η κοινωνική ασφυξία, ο εγκλεισμός, η απώλεια ατομικότητας ή η συστηματική μετατροπή των ανθρώπων σε απομονωμένους “περίεργους”; Η σύνθεση έχει σκοτεινό, συμφωνικό βάρος, με saxophone, πιάνο, κλιμακωτή κιθάρα και ένα outro που μοιάζει με απομάκρυνση από τον κόσμο του δίσκου. Ο Davies τραγουδά με δραματική, σχεδόν απελπισμένη χροιά και η μπάντα κλείνει χωρίς εύκολη λύτρωση. Δεν είναι τόσο εμπορικό όσο “Dreamer”, αλλά ως καλλιτεχνικό τέλος είναι εξαιρετικό, επιστρέφει στο concept και δίνει στον δίσκο αίσθηση ολοκληρωμένης διαδρομής.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A1. School:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Από τα πιο χαρακτηριστικά Supertramp openings, ξεκινά με ήχους παιδικής αυλής, σφυρίχτρα και σταδιακή αίσθηση καταπίεσης, πριν εκραγεί σε electric-piano και κιθαριστική ένταση. Το “school” δεν αφορά απλώς το εκπαιδευτικό σύστημα· αφορά την κοινωνική διαμόρφωση, τις εντολές που δέχεται κανείς από παιδί και την προσπάθεια να ξεφύγει από μια ζωή όπου άλλοι ορίζουν την επιτυχία, τη συμπεριφορά και το μέλλον του. Η εναλλαγή Hodgson/Davies φωνητικών και η δραματική ανάπτυξη κάνουν το κομμάτι μικρή prog suite χωρίς να χάνει την άμεση μελωδία. Είναι ιδανικό concept opener, γιατί παρουσιάζει την αρχική “φυλακή” από την οποία θα προσπαθήσουν να διαφύγουν οι χαρακτήρες του δίσκου.</t>
     </r>
   </si>
 </sst>
@@ -16467,7 +16579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -17026,105 +17138,105 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>18001219</v>
+        <v>16313565</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>96</v>
+        <v>4736</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2016</v>
+        <v>4737</v>
       </c>
       <c r="D18" s="3">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="E18" s="5">
         <v>3.82</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>2034</v>
+        <v>4749</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2020</v>
+        <v>4735</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>2019</v>
+        <v>4740</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>2017</v>
+        <v>4738</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>4739</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>926332</v>
+        <v>18001219</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1973</v>
+      </c>
+      <c r="E19" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>926332</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D20" s="3">
         <v>1976</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E20" s="5">
         <v>3.29</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="21" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>2021194</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>4274</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>2353</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1977</v>
-      </c>
-      <c r="E20" s="5">
-        <v>2.85</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>2375</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>2355</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>2354</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>2366</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>2964464</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>4274</v>
@@ -17133,7 +17245,7 @@
         <v>2353</v>
       </c>
       <c r="D21" s="3">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E21" s="5">
         <v>2.85</v>
@@ -17142,3854 +17254,3886 @@
         <v>2375</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>2366</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>2964464</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>4274</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>2377</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>2376</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I22" s="7" t="s">
         <v>2379</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J22" s="7" t="s">
         <v>2378</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>23510192</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>2256</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2015</v>
-      </c>
-      <c r="E22" s="5">
-        <v>3.69</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>2276</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>2261</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>2260</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>2259</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>23506553</v>
+        <v>23510192</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2256</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2015</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23506553</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>2285</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D24" s="3">
         <v>2017</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E24" s="5">
         <v>3.68</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>2305</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>2317</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>2316</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I24" s="7" t="s">
         <v>2287</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>2286</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>31604863</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>4280</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>2321</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D25" s="3">
         <v>2024</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E25" s="5">
         <v>3.56</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>2330</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>2319</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>2318</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>2331</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>2332</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="26" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>8816501</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>4289</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>2511</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D26" s="3">
         <v>1979</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E26" s="5">
         <v>3.2</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>2525</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>2513</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>2512</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I26" s="7" t="s">
         <v>2514</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>2515</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="27" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>2460844</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>3590</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>3574</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1986</v>
-      </c>
-      <c r="E26" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>3589</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>3588</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3584</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>3585</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>3403683</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3590</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1986</v>
+      </c>
+      <c r="E27" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>3589</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>3588</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3584</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>3585</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>3403683</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>3590</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>3611</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D28" s="3">
         <v>1988</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E28" s="5">
         <v>3.56</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>3635</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>3615</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>3614</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I28" s="7" t="s">
         <v>3612</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J28" s="7" t="s">
         <v>3613</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>12282039</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>4271</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>2477</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1973</v>
-      </c>
-      <c r="E28" s="5">
-        <v>3.79</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>2491</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>2481</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>2478</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>2479</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
+        <v>12282039</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1973</v>
+      </c>
+      <c r="E29" s="5">
+        <v>3.79</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>2491</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>2480</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>2478</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>35389759</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>2222</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>2221</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D30" s="3">
         <v>2025</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E30" s="5">
         <v>3.74</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>2245</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>2244</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>2243</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>2223</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="31" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>22296643</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>2557</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>2553</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D31" s="3">
         <v>1994</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E31" s="5">
         <v>3.64</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>2562</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>2561</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>2560</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>2559</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>2558</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>11898961</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>4290</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D32" s="3">
         <v>1959</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E32" s="5">
         <v>3.94</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>2184</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>2164</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>2163</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I32" s="7" t="s">
         <v>2153</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="33" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>1739129</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D33" s="3">
         <v>1975</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E33" s="5">
         <v>3.78</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>4317</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>4316</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>4315</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J33" s="7" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>22100377</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D33" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E33" s="5">
-        <v>3.39</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>1526</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>1516</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>1514</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
+        <v>22100377</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2022</v>
+      </c>
+      <c r="E34" s="5">
+        <v>3.39</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>29667079</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>4275</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>2595</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>1973</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E35" s="5">
         <v>3.51</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>2606</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>2605</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>2604</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I35" s="7" t="s">
         <v>2596</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J35" s="7" t="s">
         <v>2597</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="36" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>28792273</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>4107</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>4106</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D36" s="3">
         <v>2023</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>3.47</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F36" s="8" t="s">
         <v>4119</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>4103</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>4102</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I36" s="7" t="s">
         <v>4104</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J36" s="7" t="s">
         <v>4105</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="37" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>6503426</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D37" s="3">
         <v>1973</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E37" s="5">
         <v>3.66</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>4333</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>4332</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J37" s="7" t="s">
         <v>4342</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="38" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>31106519</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D38" s="3">
         <v>1975</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E38" s="5">
         <v>3.69</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J38" s="7" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="39" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>920311</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D39" s="3">
         <v>1981</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E39" s="5">
         <v>3.45</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>4345</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>4344</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>4343</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I39" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J39" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="40" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>2138840</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D40" s="3">
         <v>1983</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E40" s="5">
         <v>3.48</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>2185</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I40" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J40" s="7" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="41" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>18813646</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>4282</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>2949</v>
-      </c>
-      <c r="D40" s="3">
-        <v>2021</v>
-      </c>
-      <c r="E40" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>2960</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>2972</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>2971</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>2948</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>2947</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>28729798</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>4282</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2620</v>
+        <v>2949</v>
       </c>
       <c r="D41" s="3">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E41" s="5">
         <v>3.51</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>2635</v>
+        <v>2960</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2623</v>
+        <v>2972</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>2622</v>
+        <v>2971</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>2619</v>
+        <v>2948</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>2621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>35342041</v>
+        <v>28729798</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>4282</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E42" s="5">
+        <v>3.51</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>35342041</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>4282</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>2983</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D43" s="3">
         <v>2025</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E43" s="5">
         <v>3.6</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>3012</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>2995</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>2994</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I43" s="7" t="s">
         <v>2993</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J43" s="7" t="s">
         <v>2992</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="44" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>34571488</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>2894</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>2881</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D44" s="3">
         <v>2024</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E44" s="5">
         <v>3.51</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>2895</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>2912</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>2911</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I44" s="7" t="s">
         <v>2896</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J44" s="7" t="s">
         <v>2897</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="45" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>16448232</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>4060</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C45" s="4" t="s">
         <v>4025</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D45" s="3">
         <v>1978</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E45" s="5">
         <v>3.33</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F45" s="8" t="s">
         <v>4039</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>4029</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>4028</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I45" s="7" t="s">
         <v>4026</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J45" s="7" t="s">
         <v>4027</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>27663855</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B46" s="4" t="s">
         <v>2655</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>2656</v>
-      </c>
-      <c r="D45" s="3">
-        <v>1971</v>
-      </c>
-      <c r="E45" s="5">
-        <v>3.99</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>2667</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>2660</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>2659</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>2658</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>2657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>34592074</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>4061</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>4061</v>
       </c>
       <c r="D46" s="3">
         <v>1971</v>
       </c>
       <c r="E46" s="5">
-        <v>3.7</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>4089</v>
+        <v>3.99</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>2667</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>4065</v>
+        <v>2660</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>4064</v>
+        <v>2659</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>4062</v>
+        <v>2658</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>4063</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
+        <v>34592074</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1971</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>4089</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>4065</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>4062</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>37111626</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>4599</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>4600</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D48" s="3">
         <v>1976</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E48" s="5">
         <v>3.77</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F48" s="6" t="s">
         <v>4608</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>4597</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>4598</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I48" s="7" t="s">
         <v>4595</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J48" s="7" t="s">
         <v>4596</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="49" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>27342894</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>3927</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>3905</v>
-      </c>
-      <c r="D48" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E48" s="5">
-        <v>3.85</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>3915</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>3931</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3930</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>3928</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>3929</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>35210866</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>3927</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>3905</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E49" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>3915</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>3931</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3930</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>3928</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>35210866</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>3927</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>3944</v>
-      </c>
-      <c r="D49" s="3">
-        <v>2025</v>
-      </c>
-      <c r="E49" s="5">
-        <v>3.84</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>3957</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>3943</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3942</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>3945</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>3946</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>33790944</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="D50" s="3">
         <v>2025</v>
       </c>
       <c r="E50" s="5">
-        <v>3.11</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>1754</v>
+        <v>3.84</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>3957</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>70</v>
+        <v>3943</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>75</v>
+        <v>3942</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>71</v>
+        <v>3945</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>72</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
+        <v>33790944</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E51" s="5">
+        <v>3.11</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>34750368</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B52" s="4" t="s">
         <v>2867</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C52" s="4" t="s">
         <v>2866</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D52" s="3">
         <v>2016</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E52" s="5">
         <v>3.52</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F52" s="6" t="s">
         <v>2936</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>2869</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I52" s="7" t="s">
         <v>2870</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="J52" s="7" t="s">
         <v>2871</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="53" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>36520261</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>3977</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>3978</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D53" s="3">
         <v>2026</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E53" s="5">
         <v>3.48</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>3994</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>3974</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>3973</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I53" s="7" t="s">
         <v>3975</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J53" s="7" t="s">
         <v>3976</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="54" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>4216594</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>4281</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>1714</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D54" s="3">
         <v>1980</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E54" s="5">
         <v>3.39</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>1728</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>1718</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>1717</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I54" s="7" t="s">
         <v>1715</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J54" s="7" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="55" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>28777768</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B55" s="4" t="s">
         <v>1693</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>1694</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D55" s="3">
         <v>2023</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E55" s="5">
         <v>3.18</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F55" s="6" t="s">
         <v>1699</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>1698</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>1697</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="I55" s="7" t="s">
         <v>1695</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="J55" s="7" t="s">
         <v>1696</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="56" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>8415848</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B56" s="4" t="s">
         <v>3839</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C56" s="4" t="s">
         <v>3838</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D56" s="3">
         <v>1988</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E56" s="5">
         <v>3.84</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>3853</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>3843</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>3842</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I56" s="7" t="s">
         <v>3840</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="J56" s="7" t="s">
         <v>3841</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="57" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>33564954</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>1647</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C57" s="4" t="s">
         <v>1648</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D57" s="3">
         <v>2022</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E57" s="5">
         <v>2.72</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F57" s="6" t="s">
         <v>1662</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G57" s="4" t="s">
         <v>1675</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>1674</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I57" s="7" t="s">
         <v>1660</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J57" s="7" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="58" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>2661964</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>3320</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C58" s="4" t="s">
         <v>3321</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D58" s="3">
         <v>1988</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E58" s="5">
         <v>4</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F58" s="6" t="s">
         <v>3332</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>3325</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>3324</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="I58" s="7" t="s">
         <v>3322</v>
       </c>
-      <c r="J57" s="7" t="s">
+      <c r="J58" s="7" t="s">
         <v>3323</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>27606564</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D58" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E58" s="5">
-        <v>3.76</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>1546</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>1545</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>1544</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>1543</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
+        <v>27606564</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D59" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E59" s="5">
+        <v>3.76</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>26012116</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>1588</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>1589</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D60" s="3">
         <v>2022</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E60" s="5">
         <v>3.4</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F60" s="6" t="s">
         <v>1592</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>1594</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="I60" s="7" t="s">
         <v>1590</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="J60" s="7" t="s">
         <v>1591</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>11007106</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D60" s="3">
-        <v>1978</v>
-      </c>
-      <c r="E60" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>1501</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>1483</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>1482</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>1481</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
-        <v>4684547</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>1478</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D61" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>4684547</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>3804</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D62" s="3">
         <v>1980</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E62" s="5">
         <v>3.47</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F62" s="8" t="s">
         <v>3816</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>3818</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>3817</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="I62" s="7" t="s">
         <v>3805</v>
       </c>
-      <c r="J61" s="7" t="s">
+      <c r="J62" s="7" t="s">
         <v>3806</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
-        <v>13795818</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D62" s="3">
-        <v>1979</v>
-      </c>
-      <c r="E62" s="5">
-        <v>3.96</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>1446</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1477</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>1445</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
+        <v>13795818</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1979</v>
+      </c>
+      <c r="E63" s="5">
+        <v>3.96</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>30630553</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B64" s="4" t="s">
         <v>1381</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C64" s="4" t="s">
         <v>1382</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D64" s="3">
         <v>1995</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E64" s="5">
         <v>3.76</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F64" s="6" t="s">
         <v>1402</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>1401</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>1400</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="I64" s="7" t="s">
         <v>1384</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="J64" s="7" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="65" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>12991988</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B65" s="4" t="s">
         <v>3646</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C65" s="4" t="s">
         <v>3647</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D65" s="3">
         <v>1987</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E65" s="5">
         <v>3.29</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F65" s="6" t="s">
         <v>3659</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>3709</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>3648</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="I65" s="7" t="s">
         <v>3649</v>
       </c>
-      <c r="J64" s="7" t="s">
+      <c r="J65" s="7" t="s">
         <v>3650</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>3229841</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>4270</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C66" s="4" t="s">
         <v>1360</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D66" s="3">
         <v>1981</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E66" s="5">
         <v>3.38</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F66" s="6" t="s">
         <v>1363</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>1373</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="I65" s="7" t="s">
+      <c r="I66" s="7" t="s">
         <v>1362</v>
       </c>
-      <c r="J65" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>1361</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="67" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>7598060</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B67" s="4" t="s">
         <v>4279</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C67" s="4" t="s">
         <v>1306</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D67" s="3">
         <v>1967</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E67" s="5">
         <v>3.65</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F67" s="6" t="s">
         <v>1321</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>1322</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>1320</v>
       </c>
-      <c r="I66" s="7" t="s">
+      <c r="I67" s="7" t="s">
         <v>1324</v>
       </c>
-      <c r="J66" s="7" t="s">
+      <c r="J67" s="7" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="68" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>28270285</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B68" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C68" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D68" s="3">
         <v>2023</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E68" s="5">
         <v>3.56</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F68" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I68" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="J68" s="7" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="69" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>35187877</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B69" s="4" t="s">
         <v>2820</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>2821</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D69" s="3">
         <v>1990</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E69" s="5">
         <v>3.44</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F69" s="6" t="s">
         <v>2839</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>2823</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>2822</v>
       </c>
-      <c r="I68" s="7" t="s">
+      <c r="I69" s="7" t="s">
         <v>2825</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="J69" s="7" t="s">
         <v>2824</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="70" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>7660097</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B70" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C70" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D70" s="3">
         <v>1976</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E70" s="5">
         <v>3.63</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F70" s="6" t="s">
         <v>1290</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>1305</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>1304</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I70" s="7" t="s">
         <v>1289</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="J70" s="7" t="s">
         <v>1288</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="71" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>10824930</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>3677</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>3678</v>
-      </c>
-      <c r="D70" s="3">
-        <v>1983</v>
-      </c>
-      <c r="E70" s="5">
-        <v>3.42</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>3692</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>3710</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>3681</v>
-      </c>
-      <c r="I70" s="7" t="s">
-        <v>3680</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>3679</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>2589429</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>3677</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>3678</v>
+      </c>
+      <c r="D71" s="3">
+        <v>1983</v>
+      </c>
+      <c r="E71" s="5">
+        <v>3.42</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>3692</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>3710</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>3681</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>3680</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>2589429</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>3677</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>3708</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D72" s="3">
         <v>1989</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E72" s="5">
         <v>3.3</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F72" s="8" t="s">
         <v>3722</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>3734</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>3733</v>
       </c>
-      <c r="I71" s="7" t="s">
+      <c r="I72" s="7" t="s">
         <v>3711</v>
       </c>
-      <c r="J71" s="7" t="s">
+      <c r="J72" s="7" t="s">
         <v>3712</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
-        <v>26832221</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>4291</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D72" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E72" s="5">
-        <v>2.82</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>1249</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
+        <v>26832221</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>4291</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D73" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E73" s="5">
+        <v>2.82</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>23803544</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C74" s="4" t="s">
         <v>1219</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D74" s="3">
         <v>1973</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E74" s="5">
         <v>3.63</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F74" s="6" t="s">
         <v>1231</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>1240</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="I73" s="7" t="s">
+      <c r="I74" s="7" t="s">
         <v>1229</v>
       </c>
-      <c r="J73" s="7" t="s">
+      <c r="J74" s="7" t="s">
         <v>1230</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
-        <v>29704561</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D74" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E74" s="5">
-        <v>3.25</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>1189</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
+        <v>29704561</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E75" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>26909678</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B76" s="4" t="s">
         <v>1153</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C76" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D76" s="3">
         <v>2018</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E76" s="5">
         <v>3.24</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F76" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="I75" s="7" t="s">
+      <c r="I76" s="7" t="s">
         <v>1156</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="J76" s="7" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="77" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>4418939</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B77" s="4" t="s">
         <v>1121</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C77" s="4" t="s">
         <v>1122</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D77" s="3">
         <v>1977</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E77" s="5">
         <v>3.55</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F77" s="6" t="s">
         <v>1133</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H77" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="I76" s="7" t="s">
+      <c r="I77" s="7" t="s">
         <v>1130</v>
       </c>
-      <c r="J76" s="7" t="s">
+      <c r="J77" s="7" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+    <row r="78" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>31216738</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D77" s="3">
-        <v>2024</v>
-      </c>
-      <c r="E77" s="5">
-        <v>3.44</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>1120</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>1097</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>37005303</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>1098</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D78" s="3">
+        <v>2024</v>
+      </c>
+      <c r="E78" s="5">
+        <v>3.44</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>37005303</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>3872</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D79" s="3">
         <v>2026</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E79" s="5">
         <v>3.29</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F79" s="8" t="s">
         <v>3887</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>3876</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>3875</v>
       </c>
-      <c r="I78" s="7" t="s">
+      <c r="I79" s="7" t="s">
         <v>3874</v>
       </c>
-      <c r="J78" s="7" t="s">
+      <c r="J79" s="7" t="s">
         <v>3873</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>25895635</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D79" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E79" s="5">
-        <v>3.58</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>1070</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
+        <v>25895635</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D80" s="3">
+        <v>2022</v>
+      </c>
+      <c r="E80" s="5">
+        <v>3.58</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>25885156</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B81" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C81" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D81" s="3">
         <v>1975</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E81" s="5">
         <v>4.37</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F81" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>1051</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H81" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="I80" s="7" t="s">
+      <c r="I81" s="7" t="s">
         <v>1039</v>
       </c>
-      <c r="J80" s="7" t="s">
+      <c r="J81" s="7" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="82" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>4778774</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B82" s="4" t="s">
         <v>3737</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C82" s="4" t="s">
         <v>3763</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D82" s="3">
         <v>1988</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E82" s="5">
         <v>2.84</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F82" s="8" t="s">
         <v>3752</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>3739</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H82" s="3" t="s">
         <v>3738</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I82" s="7" t="s">
         <v>3751</v>
       </c>
-      <c r="J81" s="7" t="s">
+      <c r="J82" s="7" t="s">
         <v>3750</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
-        <v>28426390</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D82" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E82" s="5">
-        <v>3.42</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
+        <v>28426390</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D83" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E83" s="5">
+        <v>3.42</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>31683230</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B84" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C84" s="4" t="s">
         <v>973</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D84" s="3">
         <v>2024</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E84" s="5">
         <v>3.33</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F84" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="H84" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="I83" s="7" t="s">
+      <c r="I84" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="J83" s="7" t="s">
+      <c r="J84" s="7" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="191.25" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+    <row r="85" spans="1:10" ht="191.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
         <v>35392324</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B85" s="4" t="s">
         <v>4658</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C85" s="4" t="s">
         <v>4659</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D85" s="3">
         <v>1975</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E85" s="5">
         <v>3.78</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F85" s="8" t="s">
         <v>4674</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G85" s="4" t="s">
         <v>4699</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="H85" s="3" t="s">
         <v>4657</v>
       </c>
-      <c r="I84" s="7" t="s">
+      <c r="I85" s="7" t="s">
         <v>4660</v>
       </c>
-      <c r="J84" s="7" t="s">
+      <c r="J85" s="7" t="s">
         <v>4661</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+    <row r="86" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
         <v>37452171</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B86" s="4" t="s">
         <v>4278</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C86" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D86" s="3">
         <v>2026</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E86" s="5">
         <v>3.73</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F86" s="6" t="s">
         <v>2140</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G86" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H86" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I85" s="7" t="s">
+      <c r="I86" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="J86" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+    <row r="87" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
         <v>21177118</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B87" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C87" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D87" s="3">
         <v>1976</v>
       </c>
-      <c r="E86" s="5">
+      <c r="E87" s="5">
         <v>3.45</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F87" s="6" t="s">
         <v>4296</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G87" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H87" s="3" t="s">
         <v>4700</v>
       </c>
-      <c r="I86" s="7" t="s">
+      <c r="I87" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J86" s="7" t="s">
+      <c r="J87" s="7" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>28117261</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>4276</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="D87" s="3">
-        <v>1978</v>
-      </c>
-      <c r="E87" s="5">
-        <v>3.48</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>938</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>1562086</v>
+        <v>28117261</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>949</v>
+        <v>4276</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
       <c r="D88" s="3">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="E88" s="5">
-        <v>3.16</v>
+        <v>3.48</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>953</v>
+        <v>921</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>951</v>
+        <v>919</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>950</v>
+        <v>920</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
+        <v>1562086</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D89" s="3">
+        <v>1982</v>
+      </c>
+      <c r="E89" s="5">
+        <v>3.16</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
         <v>28649152</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B90" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C90" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D90" s="3">
         <v>2023</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E90" s="5">
         <v>3.47</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F90" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G90" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="I89" s="7" t="s">
+      <c r="I90" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="J89" s="7" t="s">
+      <c r="J90" s="7" t="s">
         <v>785</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>25950673</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>4292</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="D90" s="3">
-        <v>2019</v>
-      </c>
-      <c r="E90" s="5">
-        <v>3.13</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>877</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="J90" s="7" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>25412281</v>
+        <v>25950673</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>4292</v>
       </c>
       <c r="C91" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D91" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E91" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>25412281</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D92" s="3">
         <v>2022</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E92" s="5">
         <v>3.41</v>
       </c>
-      <c r="F91" s="6" t="s">
+      <c r="F92" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="H92" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="I91" s="7" t="s">
+      <c r="I92" s="7" t="s">
         <v>796</v>
       </c>
-      <c r="J91" s="7" t="s">
+      <c r="J92" s="7" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+    <row r="93" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
         <v>28518808</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B93" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C93" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D93" s="3">
         <v>2023</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E93" s="5">
         <v>3.08</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F93" s="6" t="s">
         <v>835</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G93" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="I92" s="7" t="s">
+      <c r="I93" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="J92" s="7" t="s">
+      <c r="J93" s="7" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+    <row r="94" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>24184766</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B94" s="4" t="s">
         <v>4273</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C94" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D94" s="3">
         <v>2020</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E94" s="5">
         <v>3.51</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F94" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G94" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="I93" s="7" t="s">
+      <c r="I94" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="J93" s="7" t="s">
+      <c r="J94" s="7" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+    <row r="95" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>33253932</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B95" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C95" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D95" s="3">
         <v>1981</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E95" s="5">
         <v>3.94</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F95" s="6" t="s">
         <v>849</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G95" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="I94" s="7" t="s">
+      <c r="I95" s="7" t="s">
         <v>729</v>
       </c>
-      <c r="J94" s="7" t="s">
+      <c r="J95" s="7" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+    <row r="96" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
         <v>33653532</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B96" s="4" t="s">
         <v>1860</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C96" s="4" t="s">
         <v>1861</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D96" s="3">
         <v>1972</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E96" s="5">
         <v>3.52</v>
       </c>
-      <c r="F95" s="6"/>
-      <c r="G95" s="4" t="s">
+      <c r="F96" s="6"/>
+      <c r="G96" s="4" t="s">
         <v>1871</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>1870</v>
       </c>
-      <c r="I95" s="7" t="s">
+      <c r="I96" s="7" t="s">
         <v>1862</v>
       </c>
-      <c r="J95" s="7" t="s">
+      <c r="J96" s="7" t="s">
         <v>1863</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
-        <v>6431834</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>3484</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>3484</v>
-      </c>
-      <c r="D96" s="3">
-        <v>1979</v>
-      </c>
-      <c r="E96" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>3526</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>3517</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>3516</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>3514</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>3515</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>385433</v>
+        <v>6431834</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>3484</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="D97" s="3">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="E97" s="5">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>3497</v>
+        <v>3526</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>3488</v>
+        <v>3517</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>3487</v>
+        <v>3516</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>3485</v>
+        <v>3514</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>3486</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>5815845</v>
+        <v>385433</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>3484</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>3483</v>
+      </c>
+      <c r="D98" s="3">
+        <v>1981</v>
+      </c>
+      <c r="E98" s="5">
+        <v>3.67</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>3497</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>3488</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>3487</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>3485</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>5815845</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>3543</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D99" s="3">
         <v>1986</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E99" s="5">
         <v>2.82</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F99" s="6" t="s">
         <v>3556</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G99" s="4" t="s">
         <v>3587</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>3544</v>
       </c>
-      <c r="I98" s="7" t="s">
+      <c r="I99" s="7" t="s">
         <v>3554</v>
       </c>
-      <c r="J98" s="7" t="s">
+      <c r="J99" s="7" t="s">
         <v>3555</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+    <row r="100" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
         <v>7949644</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>4389</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>4455</v>
-      </c>
-      <c r="D99" s="3">
-        <v>1976</v>
-      </c>
-      <c r="E99" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>4460</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>4485</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>4450</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>4462</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>4461</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
-        <v>2705063</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>4389</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>4481</v>
+        <v>4455</v>
       </c>
       <c r="D100" s="3">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="E100" s="5">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>4494</v>
+        <v>4460</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>4486</v>
+        <v>4485</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>4484</v>
+        <v>4450</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>4483</v>
+        <v>4462</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>4482</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>4007367</v>
+        <v>2705063</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>4389</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>4388</v>
+        <v>4481</v>
       </c>
       <c r="D101" s="3">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="E101" s="5">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>4398</v>
+        <v>4494</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>4385</v>
+        <v>4486</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>4383</v>
+        <v>4484</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>4386</v>
+        <v>4483</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>4387</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>2874281</v>
+        <v>4007367</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>4389</v>
       </c>
       <c r="C102" s="4" t="s">
+        <v>4388</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1982</v>
+      </c>
+      <c r="E102" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>4398</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>4385</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>4386</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>2874281</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>4389</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>4421</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D103" s="3">
         <v>1988</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E103" s="5">
         <v>3.23</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F103" s="6" t="s">
         <v>4431</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G103" s="4" t="s">
         <v>4418</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="H103" s="3" t="s">
         <v>4417</v>
       </c>
-      <c r="I102" s="7" t="s">
+      <c r="I103" s="7" t="s">
         <v>4419</v>
       </c>
-      <c r="J102" s="7" t="s">
+      <c r="J103" s="7" t="s">
         <v>4420</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+    <row r="104" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
         <v>3507697</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B104" s="4" t="s">
         <v>4293</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C104" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D104" s="3">
         <v>1973</v>
-      </c>
-      <c r="E103" s="5">
-        <v>3.29</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="I103" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="J103" s="7" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
-        <v>26207852</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D104" s="3">
-        <v>2023</v>
       </c>
       <c r="E104" s="5">
         <v>3.29</v>
       </c>
       <c r="F104" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>26207852</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D105" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E105" s="5">
+        <v>3.29</v>
+      </c>
+      <c r="F105" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G105" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="H105" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="I104" s="7" t="s">
+      <c r="I105" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="J104" s="7" t="s">
+      <c r="J105" s="7" t="s">
         <v>694</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
-        <v>2782114</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>3114</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>3114</v>
-      </c>
-      <c r="D105" s="3">
-        <v>1989</v>
-      </c>
-      <c r="E105" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>3130</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>3127</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>3126</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>3128</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>3129</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>31880233</v>
+        <v>2782114</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>602</v>
+        <v>3114</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>601</v>
+        <v>3114</v>
       </c>
       <c r="D106" s="3">
-        <v>1976</v>
+        <v>1989</v>
       </c>
       <c r="E106" s="5">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>628</v>
+        <v>3130</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>627</v>
+        <v>3127</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>605</v>
+        <v>3126</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>603</v>
+        <v>3128</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>604</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
+        <v>31880233</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="D107" s="3">
+        <v>1976</v>
+      </c>
+      <c r="E107" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
         <v>28251457</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B108" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C108" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D108" s="3">
         <v>2023</v>
       </c>
-      <c r="E107" s="5">
+      <c r="E108" s="5">
         <v>3.61</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F108" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="G107" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="H107" s="3" t="s">
+      <c r="H108" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="I107" s="7" t="s">
+      <c r="I108" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="J107" s="7" t="s">
+      <c r="J108" s="7" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+    <row r="109" spans="1:10" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
         <v>10079558</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B109" s="4" t="s">
         <v>4269</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C109" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D109" s="3">
         <v>1978</v>
       </c>
-      <c r="E108" s="5">
+      <c r="E109" s="5">
         <v>3.6</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F109" s="6" t="s">
         <v>4150</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>4152</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="H109" s="3" t="s">
         <v>4151</v>
       </c>
-      <c r="I108" s="7" t="s">
+      <c r="I109" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J108" s="7" t="s">
+      <c r="J109" s="7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+    <row r="110" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
         <v>22420804</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B110" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C110" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D110" s="3">
         <v>1970</v>
       </c>
-      <c r="E109" s="5">
+      <c r="E110" s="5">
         <v>3.66</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F110" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G110" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="H110" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="I109" s="7" t="s">
+      <c r="I110" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="J109" s="7" t="s">
+      <c r="J110" s="7" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+    <row r="111" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
         <v>7340202</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B111" s="4" t="s">
         <v>4629</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C111" s="4" t="s">
         <v>4630</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D111" s="3">
         <v>1977</v>
       </c>
-      <c r="E110" s="5">
+      <c r="E111" s="5">
         <v>3.5</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F111" s="6" t="s">
         <v>4639</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G111" s="4" t="s">
         <v>4656</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="H111" s="3" t="s">
         <v>4631</v>
       </c>
-      <c r="I110" s="7" t="s">
+      <c r="I111" s="7" t="s">
         <v>4627</v>
       </c>
-      <c r="J110" s="7" t="s">
+      <c r="J111" s="7" t="s">
         <v>4628</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+    <row r="112" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>2715995</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>4709</v>
+      </c>
+      <c r="D112" s="3">
+        <v>1978</v>
+      </c>
+      <c r="E112" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>4639</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>4722</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>4721</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>4723</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="168.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>4771</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>4770</v>
+      </c>
+      <c r="D113" s="3">
+        <v>1974</v>
+      </c>
+      <c r="E113" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>4781</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>4773</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>4772</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>4768</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
         <v>33527013</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B114" s="4" t="s">
         <v>4286</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C114" s="4" t="s">
         <v>2718</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D114" s="3">
         <v>2025</v>
       </c>
-      <c r="E111" s="5">
+      <c r="E114" s="5">
         <v>3.47</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F114" s="6" t="s">
         <v>2733</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>2720</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="H114" s="3" t="s">
         <v>2719</v>
       </c>
-      <c r="I111" s="7" t="s">
+      <c r="I114" s="7" t="s">
         <v>2731</v>
       </c>
-      <c r="J111" s="7" t="s">
+      <c r="J114" s="7" t="s">
         <v>2732</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
-        <v>28667458</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="D112" s="3">
-        <v>2019</v>
-      </c>
-      <c r="E112" s="5">
-        <v>3.49</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="I112" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="J112" s="7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
-        <v>26857331</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="D113" s="3">
-        <v>2023</v>
-      </c>
-      <c r="E113" s="5">
-        <v>3.48</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="I113" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="J113" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
-        <v>2598614</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>2783</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>2784</v>
-      </c>
-      <c r="D114" s="3">
-        <v>1988</v>
-      </c>
-      <c r="E114" s="5">
-        <v>3.59</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>2795</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>2797</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>2796</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>2798</v>
-      </c>
-      <c r="J114" s="7" t="s">
-        <v>2799</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>11981817</v>
+        <v>28667458</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>456</v>
+        <v>529</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>457</v>
+        <v>530</v>
       </c>
       <c r="D115" s="3">
-        <v>1996</v>
+        <v>2019</v>
       </c>
       <c r="E115" s="5">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>460</v>
+        <v>535</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>461</v>
+        <v>534</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>459</v>
+        <v>532</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
+        <v>26857331</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="D116" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E116" s="5">
+        <v>3.48</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>2598614</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1988</v>
+      </c>
+      <c r="E117" s="5">
+        <v>3.59</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>2797</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>2796</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>2798</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>11981817</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1996</v>
+      </c>
+      <c r="E118" s="5">
+        <v>3.94</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
         <v>6748984</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B119" s="4" t="s">
         <v>3013</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C119" s="4" t="s">
         <v>3013</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D119" s="3">
         <v>1978</v>
       </c>
-      <c r="E116" s="5">
+      <c r="E119" s="5">
         <v>3.56</v>
       </c>
-      <c r="F116" s="6" t="s">
+      <c r="F119" s="6" t="s">
         <v>3028</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G119" s="4" t="s">
         <v>3017</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="H119" s="3" t="s">
         <v>3016</v>
       </c>
-      <c r="I116" s="7" t="s">
+      <c r="I119" s="7" t="s">
         <v>3015</v>
       </c>
-      <c r="J116" s="7" t="s">
+      <c r="J119" s="7" t="s">
         <v>3014</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+    <row r="120" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
         <v>29264422</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B120" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C120" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D120" s="3">
         <v>1973</v>
       </c>
-      <c r="E117" s="5">
+      <c r="E120" s="5">
         <v>3.58</v>
       </c>
-      <c r="F117" s="6" t="s">
+      <c r="F120" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G120" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H120" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I117" s="7" t="s">
+      <c r="I120" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="J117" s="7" t="s">
+      <c r="J120" s="7" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+    <row r="121" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>25695898</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B121" s="4" t="s">
         <v>4283</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C121" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D121" s="3">
         <v>1974</v>
       </c>
-      <c r="E118" s="5">
+      <c r="E121" s="5">
         <v>3.8</v>
       </c>
-      <c r="F118" s="6" t="s">
+      <c r="F121" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G121" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H121" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="I118" s="7" t="s">
+      <c r="I121" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="J118" s="7" t="s">
+      <c r="J121" s="7" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+    <row r="122" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
         <v>28074505</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B122" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C122" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D122" s="3">
         <v>2023</v>
       </c>
-      <c r="E119" s="5">
+      <c r="E122" s="5">
         <v>3.57</v>
       </c>
-      <c r="F119" s="6" t="s">
+      <c r="F122" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="G119" s="4" t="s">
+      <c r="G122" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="H122" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="I119" s="7" t="s">
+      <c r="I122" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="J119" s="7" t="s">
+      <c r="J122" s="7" t="s">
         <v>415</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>10933246</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>3154</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>3153</v>
-      </c>
-      <c r="D120" s="3">
-        <v>1982</v>
-      </c>
-      <c r="E120" s="5">
-        <v>3.41</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>3155</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>3199</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>3150</v>
-      </c>
-      <c r="I120" s="7" t="s">
-        <v>3151</v>
-      </c>
-      <c r="J120" s="7" t="s">
-        <v>3152</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
-        <v>646934</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>3154</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>3219</v>
-      </c>
-      <c r="D121" s="3">
-        <v>1983</v>
-      </c>
-      <c r="E121" s="5">
-        <v>3.46</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>3223</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>4204</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>3220</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>3222</v>
-      </c>
-      <c r="J121" s="7" t="s">
-        <v>3221</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
-        <v>1382323</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>3154</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>3189</v>
-      </c>
-      <c r="D122" s="3">
-        <v>1984</v>
-      </c>
-      <c r="E122" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>3202</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>4203</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>3198</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>3200</v>
-      </c>
-      <c r="J122" s="7" t="s">
-        <v>3201</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
-        <v>1414305</v>
+        <v>10933246</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>3154</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>3289</v>
+        <v>3153</v>
       </c>
       <c r="D123" s="3">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E123" s="5">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>3301</v>
+        <v>3155</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>4206</v>
+        <v>3199</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>3288</v>
+        <v>3150</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>3299</v>
+        <v>3151</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <v>4116216</v>
+        <v>646934</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>3154</v>
       </c>
       <c r="C124" s="4" t="s">
+        <v>3219</v>
+      </c>
+      <c r="D124" s="3">
+        <v>1983</v>
+      </c>
+      <c r="E124" s="5">
+        <v>3.46</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>3223</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>4204</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>3220</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>3222</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>1382323</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>3189</v>
+      </c>
+      <c r="D125" s="3">
+        <v>1984</v>
+      </c>
+      <c r="E125" s="5">
+        <v>3.51</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>3202</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>4203</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>3198</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>3200</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>1414305</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>3289</v>
+      </c>
+      <c r="D126" s="3">
+        <v>1985</v>
+      </c>
+      <c r="E126" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>3301</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>4206</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>3288</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>3299</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>4116216</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>3254</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D127" s="3">
         <v>1987</v>
       </c>
-      <c r="E124" s="5">
+      <c r="E127" s="5">
         <v>3</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F127" s="6" t="s">
         <v>3257</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G127" s="4" t="s">
         <v>4205</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H127" s="3" t="s">
         <v>3258</v>
       </c>
-      <c r="I124" s="7" t="s">
+      <c r="I127" s="7" t="s">
         <v>3255</v>
       </c>
-      <c r="J124" s="7" t="s">
+      <c r="J127" s="7" t="s">
         <v>3256</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
-        <v>23148584</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>4284</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D125" s="3">
-        <v>2022</v>
-      </c>
-      <c r="E125" s="5">
-        <v>3.39</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>2697</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>2686</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>2685</v>
-      </c>
-      <c r="I125" s="7" t="s">
-        <v>2683</v>
-      </c>
-      <c r="J125" s="7" t="s">
-        <v>2684</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
-        <v>4000501</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>3386</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>3414</v>
-      </c>
-      <c r="D126" s="3">
-        <v>1987</v>
-      </c>
-      <c r="E126" s="5">
-        <v>3.57</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>3426</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>4209</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>3415</v>
-      </c>
-      <c r="I126" s="7" t="s">
-        <v>4294</v>
-      </c>
-      <c r="J126" s="7" t="s">
-        <v>3389</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
-        <v>2903507</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>3386</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>3385</v>
-      </c>
-      <c r="D127" s="3">
-        <v>1989</v>
-      </c>
-      <c r="E127" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>3399</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>4208</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>3387</v>
-      </c>
-      <c r="I127" s="7" t="s">
-        <v>3388</v>
-      </c>
-      <c r="J127" s="7" t="s">
-        <v>3389</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <v>7830609</v>
+        <v>23148584</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>3446</v>
+        <v>4284</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>3774</v>
+        <v>2682</v>
       </c>
       <c r="D128" s="3">
-        <v>1985</v>
+        <v>2022</v>
       </c>
       <c r="E128" s="5">
-        <v>3.38</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>3786</v>
+        <v>3.39</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>2697</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>3778</v>
+        <v>2686</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>3777</v>
+        <v>2685</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>3776</v>
+        <v>2683</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>3775</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
-        <v>8864393</v>
+        <v>4000501</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>3446</v>
+        <v>3386</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>3447</v>
+        <v>3414</v>
       </c>
       <c r="D129" s="3">
         <v>1987</v>
       </c>
       <c r="E129" s="5">
+        <v>3.57</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>3426</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>4209</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>3415</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>4294</v>
+      </c>
+      <c r="J129" s="7" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>2903507</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>3386</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>3385</v>
+      </c>
+      <c r="D130" s="3">
+        <v>1989</v>
+      </c>
+      <c r="E130" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>3399</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>3388</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>7830609</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>3774</v>
+      </c>
+      <c r="D131" s="3">
+        <v>1985</v>
+      </c>
+      <c r="E131" s="5">
+        <v>3.38</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>3786</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>3778</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>3777</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>3776</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>8864393</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>3447</v>
+      </c>
+      <c r="D132" s="3">
+        <v>1987</v>
+      </c>
+      <c r="E132" s="5">
         <v>3.58</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F132" s="6" t="s">
         <v>3470</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G132" s="4" t="s">
         <v>3482</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="H132" s="3" t="s">
         <v>3481</v>
       </c>
-      <c r="I129" s="7" t="s">
+      <c r="I132" s="7" t="s">
         <v>3449</v>
       </c>
-      <c r="J129" s="7" t="s">
+      <c r="J132" s="7" t="s">
         <v>3448</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+    <row r="133" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
         <v>2797526</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B133" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C133" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D133" s="3">
         <v>1990</v>
       </c>
-      <c r="E130" s="5">
+      <c r="E133" s="5">
         <v>3.55</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F133" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G133" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="H133" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="I130" s="7" t="s">
+      <c r="I133" s="7" t="s">
         <v>4295</v>
       </c>
-      <c r="J130" s="7" t="s">
+      <c r="J133" s="7" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+    <row r="134" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
         <v>10867099</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B134" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C134" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D134" s="3">
         <v>1992</v>
       </c>
-      <c r="E131" s="5">
+      <c r="E134" s="5">
         <v>3.67</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F134" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G134" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="H134" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I131" s="7" t="s">
+      <c r="I134" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="J131" s="7" t="s">
+      <c r="J134" s="7" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+    <row r="135" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
         <v>31700342</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B135" s="4" t="s">
         <v>4285</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C135" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D135" s="3">
         <v>2019</v>
       </c>
-      <c r="E132" s="5">
+      <c r="E135" s="5">
         <v>3.73</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="F135" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G135" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H135" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="I132" s="7" t="s">
+      <c r="I135" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="J132" s="7" t="s">
+      <c r="J135" s="7" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+    <row r="136" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
         <v>4428247</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B136" s="4" t="s">
         <v>4207</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C136" s="4" t="s">
         <v>3349</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D136" s="3">
         <v>1981</v>
       </c>
-      <c r="E133" s="5">
+      <c r="E136" s="5">
         <v>3.39</v>
       </c>
-      <c r="F133" s="6" t="s">
+      <c r="F136" s="6" t="s">
         <v>3364</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G136" s="4" t="s">
         <v>3353</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="H136" s="3" t="s">
         <v>3352</v>
       </c>
-      <c r="I133" s="7" t="s">
+      <c r="I136" s="7" t="s">
         <v>3350</v>
       </c>
-      <c r="J133" s="7" t="s">
+      <c r="J136" s="7" t="s">
         <v>3351</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+    <row r="137" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
         <v>12520978</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B137" s="4" t="s">
         <v>3082</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C137" s="4" t="s">
         <v>3081</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D137" s="3">
         <v>1982</v>
       </c>
-      <c r="E134" s="5">
+      <c r="E137" s="5">
         <v>3.57</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F137" s="6" t="s">
         <v>3095</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G137" s="4" t="s">
         <v>3086</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="H137" s="3" t="s">
         <v>3083</v>
       </c>
-      <c r="I134" s="7" t="s">
+      <c r="I137" s="7" t="s">
         <v>3084</v>
       </c>
-      <c r="J134" s="7" t="s">
+      <c r="J137" s="7" t="s">
         <v>3085</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+    <row r="138" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
         <v>1939062</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B138" s="4" t="s">
         <v>3051</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C138" s="4" t="s">
         <v>3051</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D138" s="3">
         <v>1977</v>
       </c>
-      <c r="E135" s="5">
+      <c r="E138" s="5">
         <v>3.21</v>
       </c>
-      <c r="F135" s="6" t="s">
+      <c r="F138" s="6" t="s">
         <v>3062</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G138" s="4" t="s">
         <v>4384</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="H138" s="3" t="s">
         <v>3052</v>
       </c>
-      <c r="I135" s="7" t="s">
+      <c r="I138" s="7" t="s">
         <v>3049</v>
       </c>
-      <c r="J135" s="7" t="s">
+      <c r="J138" s="7" t="s">
         <v>3050</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
-        <v>2715995</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>4629</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>4709</v>
-      </c>
-      <c r="D136" s="3">
-        <v>1978</v>
-      </c>
-      <c r="E136" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>4639</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>4722</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>4721</v>
-      </c>
-      <c r="I136" s="7" t="s">
-        <v>4723</v>
-      </c>
-      <c r="J136" s="7" t="s">
-        <v>4724</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
-        <v>16313565</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>4736</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>4737</v>
-      </c>
-      <c r="D137" s="3">
-        <v>1981</v>
-      </c>
-      <c r="E137" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>4749</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>4735</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>4740</v>
-      </c>
-      <c r="I137" s="7" t="s">
-        <v>4738</v>
-      </c>
-      <c r="J137" s="7" t="s">
-        <v>4739</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J135">
-    <sortCondition ref="B2:B135"/>
-    <sortCondition ref="D2:D135"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J138">
+    <sortCondition ref="B2:B138"/>
+    <sortCondition ref="D2:D138"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="I85" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
-    <hyperlink ref="J85" r:id="rId2" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
-    <hyperlink ref="I50" r:id="rId3" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
-    <hyperlink ref="J50" r:id="rId4" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
-    <hyperlink ref="I19" r:id="rId5" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
-    <hyperlink ref="J19" r:id="rId6" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
-    <hyperlink ref="I108" r:id="rId7" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
-    <hyperlink ref="J108" r:id="rId8" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
-    <hyperlink ref="I86" r:id="rId9" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
-    <hyperlink ref="J86" r:id="rId10" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
+    <hyperlink ref="I86" r:id="rId1" xr:uid="{B8F43599-8636-4878-AA63-74EF8E8FA4A0}"/>
+    <hyperlink ref="J86" r:id="rId2" xr:uid="{0383213A-C9D8-4706-B4BC-090F4D744EE5}"/>
+    <hyperlink ref="I51" r:id="rId3" xr:uid="{AB95816D-AFF8-4769-B964-AFEE7801899B}"/>
+    <hyperlink ref="J51" r:id="rId4" xr:uid="{25A0AA85-7925-4EA8-8C8E-F60C69923F4F}"/>
+    <hyperlink ref="I20" r:id="rId5" xr:uid="{5AE9F467-1B53-498C-B81D-02660B01BCA7}"/>
+    <hyperlink ref="J20" r:id="rId6" xr:uid="{AC0A6553-0986-4BB7-9D5A-C231F8C231FF}"/>
+    <hyperlink ref="I109" r:id="rId7" xr:uid="{24D188DA-4F4D-40DC-9308-931FFF6A0E7F}"/>
+    <hyperlink ref="J109" r:id="rId8" xr:uid="{B14913EA-FB65-4D7E-A85A-5BFD89D186DD}"/>
+    <hyperlink ref="I87" r:id="rId9" xr:uid="{84F45C40-1251-4DE1-88F3-8BC3CD9CE503}"/>
+    <hyperlink ref="J87" r:id="rId10" xr:uid="{2916FB00-92B8-41FF-873A-2CB7478D6FC5}"/>
     <hyperlink ref="I2" r:id="rId11" xr:uid="{7D09EF64-81E8-4700-B5A5-D38E3A5C492A}"/>
-    <hyperlink ref="I32" r:id="rId12" xr:uid="{BB1EEAD6-C614-40E2-A50B-1EEB4DCC9896}"/>
+    <hyperlink ref="I33" r:id="rId12" xr:uid="{BB1EEAD6-C614-40E2-A50B-1EEB4DCC9896}"/>
     <hyperlink ref="J2" r:id="rId13" xr:uid="{49D10AEE-6D1A-4296-92C2-D587EAECD209}"/>
-    <hyperlink ref="J32" r:id="rId14" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
-    <hyperlink ref="I37" r:id="rId15" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
-    <hyperlink ref="J37" r:id="rId16" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
+    <hyperlink ref="J33" r:id="rId14" xr:uid="{2470A1B8-40B8-42E7-9CB8-1E35669D6179}"/>
+    <hyperlink ref="I38" r:id="rId15" xr:uid="{538D88B9-C4FF-4DC8-B052-5482F535D3F2}"/>
+    <hyperlink ref="J38" r:id="rId16" xr:uid="{BA6CBFDC-FFDE-41CF-AA5C-8D87A3AF9F62}"/>
     <hyperlink ref="I3" r:id="rId17" xr:uid="{41088898-623F-47B4-BF91-B4B1CD818D4E}"/>
     <hyperlink ref="J3" r:id="rId18" xr:uid="{E113C2CF-CD08-4D0D-B347-3943034BA748}"/>
     <hyperlink ref="I6" r:id="rId19" xr:uid="{16FF05EB-D3D0-4933-A9A7-1991D2A4347A}"/>
     <hyperlink ref="J6" r:id="rId20" xr:uid="{7F3FDF6A-4AF3-43DA-A4B5-C708BEBBC5AC}"/>
     <hyperlink ref="I15" r:id="rId21" xr:uid="{9D7EA281-7164-4EC6-8613-E6D1AAA72828}"/>
     <hyperlink ref="J15" r:id="rId22" xr:uid="{8EE506D2-8E16-47D1-A8EC-6F5329B2DA47}"/>
-    <hyperlink ref="I36" r:id="rId23" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
-    <hyperlink ref="I38" r:id="rId24" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
-    <hyperlink ref="J38" r:id="rId25" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
-    <hyperlink ref="I39" r:id="rId26" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
-    <hyperlink ref="J39" r:id="rId27" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
-    <hyperlink ref="J130" r:id="rId28" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
-    <hyperlink ref="I67" r:id="rId29" xr:uid="{21285B48-6B68-40F0-9B76-D4C8B9229EA4}"/>
-    <hyperlink ref="J67" r:id="rId30" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
-    <hyperlink ref="I93" r:id="rId31" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
-    <hyperlink ref="J93" r:id="rId32" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
-    <hyperlink ref="I119" r:id="rId33" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
-    <hyperlink ref="J119" r:id="rId34" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
-    <hyperlink ref="I118" r:id="rId35" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
-    <hyperlink ref="J118" r:id="rId36" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
-    <hyperlink ref="I115" r:id="rId37" xr:uid="{CA3FCADF-3756-4A65-8A98-0AB7143633F2}"/>
-    <hyperlink ref="J115" r:id="rId38" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
-    <hyperlink ref="J117" r:id="rId39" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
-    <hyperlink ref="I117" r:id="rId40" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
-    <hyperlink ref="I112" r:id="rId41" xr:uid="{DF641E30-EFBA-494C-88DD-76EF1F14F9A5}"/>
-    <hyperlink ref="J112" r:id="rId42" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
-    <hyperlink ref="J113" r:id="rId43" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
-    <hyperlink ref="I113" r:id="rId44" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
-    <hyperlink ref="I109" r:id="rId45" xr:uid="{87C4E708-9703-429B-AD5F-DAAD8F0949D0}"/>
-    <hyperlink ref="J109" r:id="rId46" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
-    <hyperlink ref="I106" r:id="rId47" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
-    <hyperlink ref="J106" r:id="rId48" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
-    <hyperlink ref="I132" r:id="rId49" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
-    <hyperlink ref="J132" r:id="rId50" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
-    <hyperlink ref="I107" r:id="rId51" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
-    <hyperlink ref="J107" r:id="rId52" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
-    <hyperlink ref="I104" r:id="rId53" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
-    <hyperlink ref="J104" r:id="rId54" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
-    <hyperlink ref="I103" r:id="rId55" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
-    <hyperlink ref="J103" r:id="rId56" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
-    <hyperlink ref="I94" r:id="rId57" xr:uid="{F3AD3E6F-CC74-49B0-ADE8-22126BE46225}"/>
-    <hyperlink ref="J94" r:id="rId58" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
-    <hyperlink ref="I92" r:id="rId59" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
-    <hyperlink ref="J92" r:id="rId60" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
-    <hyperlink ref="I89" r:id="rId61" xr:uid="{3089CEA5-B4D3-4CF8-8369-656AF5B6317D}"/>
-    <hyperlink ref="J89" r:id="rId62" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
-    <hyperlink ref="J91" r:id="rId63" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
-    <hyperlink ref="I91" r:id="rId64" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
-    <hyperlink ref="I90" r:id="rId65" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
-    <hyperlink ref="J90" r:id="rId66" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
-    <hyperlink ref="I87" r:id="rId67" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
-    <hyperlink ref="J87" r:id="rId68" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
-    <hyperlink ref="J88" r:id="rId69" xr:uid="{5DC2641E-2387-4BA6-9A88-B4A6B827B909}"/>
-    <hyperlink ref="I88" r:id="rId70" xr:uid="{91790331-D35E-4067-B038-263AEF6060A9}"/>
-    <hyperlink ref="J83" r:id="rId71" xr:uid="{F738125C-E6C4-4EEB-8C06-4A5232B3EE11}"/>
-    <hyperlink ref="I83" r:id="rId72" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
-    <hyperlink ref="I82" r:id="rId73" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
-    <hyperlink ref="J82" r:id="rId74" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
-    <hyperlink ref="I80" r:id="rId75" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
-    <hyperlink ref="J80" r:id="rId76" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
-    <hyperlink ref="J79" r:id="rId77" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
-    <hyperlink ref="I79" r:id="rId78" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
-    <hyperlink ref="J77" r:id="rId79" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
-    <hyperlink ref="I77" r:id="rId80" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
-    <hyperlink ref="I76" r:id="rId81" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
-    <hyperlink ref="J76" r:id="rId82" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
-    <hyperlink ref="J75" r:id="rId83" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
-    <hyperlink ref="I75" r:id="rId84" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
-    <hyperlink ref="J74" r:id="rId85" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
-    <hyperlink ref="I74" r:id="rId86" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
-    <hyperlink ref="I73" r:id="rId87" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
-    <hyperlink ref="J73" r:id="rId88" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
-    <hyperlink ref="I72" r:id="rId89" xr:uid="{0AECC585-C22C-466A-9DD8-680618CE482C}"/>
-    <hyperlink ref="J72" r:id="rId90" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
-    <hyperlink ref="J69" r:id="rId91" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
-    <hyperlink ref="I69" r:id="rId92" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
-    <hyperlink ref="J66" r:id="rId93" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
-    <hyperlink ref="I66" r:id="rId94" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
-    <hyperlink ref="J65" r:id="rId95" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
-    <hyperlink ref="I65" r:id="rId96" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
-    <hyperlink ref="J63" r:id="rId97" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
-    <hyperlink ref="I63" r:id="rId98" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
-    <hyperlink ref="J62" r:id="rId99" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
-    <hyperlink ref="I62" r:id="rId100" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
-    <hyperlink ref="J60" r:id="rId101" xr:uid="{36CEEA26-13A0-4AFA-8ED6-B4B6BC4B51BA}"/>
-    <hyperlink ref="I60" r:id="rId102" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
-    <hyperlink ref="J33" r:id="rId103" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
-    <hyperlink ref="I33" r:id="rId104" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
-    <hyperlink ref="I58" r:id="rId105" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
-    <hyperlink ref="J58" r:id="rId106" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
-    <hyperlink ref="I59" r:id="rId107" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
-    <hyperlink ref="J59" r:id="rId108" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
-    <hyperlink ref="I56" r:id="rId109" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
-    <hyperlink ref="J56" r:id="rId110" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
-    <hyperlink ref="I54" r:id="rId111" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
-    <hyperlink ref="J54" r:id="rId112" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
-    <hyperlink ref="I53" r:id="rId113" xr:uid="{721CF701-F1E2-4D7D-BC9E-45C800A11082}"/>
-    <hyperlink ref="J53" r:id="rId114" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
+    <hyperlink ref="I37" r:id="rId23" xr:uid="{D99AD04E-22D7-4523-A906-354DCA3D59B8}"/>
+    <hyperlink ref="I39" r:id="rId24" xr:uid="{866AD757-F7B0-4150-A72D-D36A6753C9D2}"/>
+    <hyperlink ref="J39" r:id="rId25" xr:uid="{653E9D3F-45EA-4E17-836F-D51F97914679}"/>
+    <hyperlink ref="I40" r:id="rId26" xr:uid="{78E3F96C-2AC2-4B9F-A821-519BF5B5CA6A}"/>
+    <hyperlink ref="J40" r:id="rId27" xr:uid="{0D92D6CB-079F-4183-8D1A-1BFEDEE2C7D0}"/>
+    <hyperlink ref="J133" r:id="rId28" xr:uid="{63686497-3E87-4FD7-8A7E-EAC076C0B3FF}"/>
+    <hyperlink ref="I68" r:id="rId29" xr:uid="{21285B48-6B68-40F0-9B76-D4C8B9229EA4}"/>
+    <hyperlink ref="J68" r:id="rId30" xr:uid="{BAB202AA-F491-4E39-A1A2-D6EBCE96D971}"/>
+    <hyperlink ref="I94" r:id="rId31" xr:uid="{6F630CCD-C8C5-48E5-BF62-170422F60808}"/>
+    <hyperlink ref="J94" r:id="rId32" xr:uid="{84319BCE-7BDE-4F59-BC89-A927A5EE3AFD}"/>
+    <hyperlink ref="I122" r:id="rId33" xr:uid="{457FA6A6-590F-4091-90C9-097732A21B44}"/>
+    <hyperlink ref="J122" r:id="rId34" xr:uid="{820070CD-F89D-439E-8345-B1B8BD267685}"/>
+    <hyperlink ref="I121" r:id="rId35" xr:uid="{98CBE1F2-7113-4F22-A79D-E2DA1CA84C81}"/>
+    <hyperlink ref="J121" r:id="rId36" xr:uid="{F2F8B5E7-6D7A-4F6F-8D25-76E610D168E1}"/>
+    <hyperlink ref="I118" r:id="rId37" xr:uid="{CA3FCADF-3756-4A65-8A98-0AB7143633F2}"/>
+    <hyperlink ref="J118" r:id="rId38" xr:uid="{3575A396-31E6-40CA-9AE5-93286E535880}"/>
+    <hyperlink ref="J120" r:id="rId39" xr:uid="{6E0506A5-8A8E-4A23-BB64-838F694F517F}"/>
+    <hyperlink ref="I120" r:id="rId40" xr:uid="{0D6B3B88-F335-416B-8E1F-865D3DD5E2F0}"/>
+    <hyperlink ref="I115" r:id="rId41" xr:uid="{DF641E30-EFBA-494C-88DD-76EF1F14F9A5}"/>
+    <hyperlink ref="J115" r:id="rId42" xr:uid="{B55C32BD-FFA8-408C-863E-BCB03FB8FFD1}"/>
+    <hyperlink ref="J116" r:id="rId43" xr:uid="{2DFEA5CA-9CDD-4810-92E5-A269F3F622EB}"/>
+    <hyperlink ref="I116" r:id="rId44" xr:uid="{FF32A1D1-1E55-466C-95A9-BFC960641343}"/>
+    <hyperlink ref="I110" r:id="rId45" xr:uid="{87C4E708-9703-429B-AD5F-DAAD8F0949D0}"/>
+    <hyperlink ref="J110" r:id="rId46" xr:uid="{643189D3-04E5-4DA0-A6BD-DA1BBD36408B}"/>
+    <hyperlink ref="I107" r:id="rId47" xr:uid="{B401C0DB-140A-4490-819B-6D614FC8CCEE}"/>
+    <hyperlink ref="J107" r:id="rId48" xr:uid="{E3F5F8FC-7DEE-4BE0-BFCA-A5C70ADD094D}"/>
+    <hyperlink ref="I135" r:id="rId49" xr:uid="{78B04016-E4AE-47A7-8B46-35766B77AFB8}"/>
+    <hyperlink ref="J135" r:id="rId50" xr:uid="{CCEBFF18-4053-4C24-817D-27646BE05EBD}"/>
+    <hyperlink ref="I108" r:id="rId51" xr:uid="{94D10AC9-6F43-4F0A-B43B-92E95070FCCE}"/>
+    <hyperlink ref="J108" r:id="rId52" xr:uid="{2A30FB6F-21B9-49D1-B22B-53BACDF84062}"/>
+    <hyperlink ref="I105" r:id="rId53" xr:uid="{2B4FAB2A-D7A8-44D8-B205-AB8D67EAA1A2}"/>
+    <hyperlink ref="J105" r:id="rId54" xr:uid="{6E83A0B5-25C8-4527-A2C1-368E190DF4BF}"/>
+    <hyperlink ref="I104" r:id="rId55" xr:uid="{AC32B278-CEC9-4643-B124-1F81CDC65266}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{CCA851C3-A0FC-424B-8F6D-38C0FDFC9C81}"/>
+    <hyperlink ref="I95" r:id="rId57" xr:uid="{F3AD3E6F-CC74-49B0-ADE8-22126BE46225}"/>
+    <hyperlink ref="J95" r:id="rId58" xr:uid="{3631FC2C-D978-4762-A2EC-CC8A5C60C54C}"/>
+    <hyperlink ref="I93" r:id="rId59" xr:uid="{809285F3-BBBD-48F0-BD7A-A1302B4236FA}"/>
+    <hyperlink ref="J93" r:id="rId60" xr:uid="{2CD14492-8591-4F36-9885-7C3437E6E821}"/>
+    <hyperlink ref="I90" r:id="rId61" xr:uid="{3089CEA5-B4D3-4CF8-8369-656AF5B6317D}"/>
+    <hyperlink ref="J90" r:id="rId62" xr:uid="{9D002A99-727C-4388-B0E6-A0286BC1AB53}"/>
+    <hyperlink ref="J92" r:id="rId63" xr:uid="{2575D056-1912-4177-AEBE-B4E01DCEF8FA}"/>
+    <hyperlink ref="I92" r:id="rId64" xr:uid="{209C362D-EC30-4A00-A0B8-501F369CD679}"/>
+    <hyperlink ref="I91" r:id="rId65" xr:uid="{E5F32912-DA70-4F56-BFA1-AD945B01A5B7}"/>
+    <hyperlink ref="J91" r:id="rId66" xr:uid="{7EE8F5E1-FCE9-4B2E-8ABD-58D13EC6925F}"/>
+    <hyperlink ref="I88" r:id="rId67" xr:uid="{E39EA436-D938-4A1F-B12C-BC75152F540A}"/>
+    <hyperlink ref="J88" r:id="rId68" xr:uid="{434446FF-52A2-4990-B9E8-4AC6733C6C33}"/>
+    <hyperlink ref="J89" r:id="rId69" xr:uid="{5DC2641E-2387-4BA6-9A88-B4A6B827B909}"/>
+    <hyperlink ref="I89" r:id="rId70" xr:uid="{91790331-D35E-4067-B038-263AEF6060A9}"/>
+    <hyperlink ref="J84" r:id="rId71" xr:uid="{F738125C-E6C4-4EEB-8C06-4A5232B3EE11}"/>
+    <hyperlink ref="I84" r:id="rId72" xr:uid="{B1E3FDF7-1E6A-4CD0-9059-589E76913A9D}"/>
+    <hyperlink ref="I83" r:id="rId73" xr:uid="{DD98C381-1D2F-4129-BF2B-416B9F6B51C6}"/>
+    <hyperlink ref="J83" r:id="rId74" xr:uid="{61899882-82A0-4494-9A50-48D3406AC8FA}"/>
+    <hyperlink ref="I81" r:id="rId75" xr:uid="{1A7FCE72-5D02-4E89-93C9-DE53A362CFED}"/>
+    <hyperlink ref="J81" r:id="rId76" xr:uid="{0E5A0CB2-B773-4C6B-B1DB-498BA4E6F6E5}"/>
+    <hyperlink ref="J80" r:id="rId77" xr:uid="{39E05B2F-F184-40CE-87F6-5680777D3441}"/>
+    <hyperlink ref="I80" r:id="rId78" xr:uid="{A866AB9A-F5F8-4F0F-BEC5-94DAC48A3202}"/>
+    <hyperlink ref="J78" r:id="rId79" xr:uid="{FB2A51A6-1F57-4CB7-9467-FEECDE5EA7F8}"/>
+    <hyperlink ref="I78" r:id="rId80" xr:uid="{2E158044-3989-4614-A77D-7F99C6C2356D}"/>
+    <hyperlink ref="I77" r:id="rId81" xr:uid="{9EF8A064-D187-433B-89BB-274CB08879EF}"/>
+    <hyperlink ref="J77" r:id="rId82" xr:uid="{EABAADF0-EDBF-4DA8-9418-3D6076A68A9D}"/>
+    <hyperlink ref="J76" r:id="rId83" xr:uid="{398D0B82-5507-4F19-8987-F81B81EABEEA}"/>
+    <hyperlink ref="I76" r:id="rId84" xr:uid="{CD08D7F6-9889-458F-B1D7-B11EC371B1DB}"/>
+    <hyperlink ref="J75" r:id="rId85" xr:uid="{F8E2C3AC-0723-47E2-B70F-5BE2142A8C3F}"/>
+    <hyperlink ref="I75" r:id="rId86" xr:uid="{3F7A8B1D-1B9A-44F4-AFFC-EB39B6A43F6E}"/>
+    <hyperlink ref="I74" r:id="rId87" xr:uid="{BA233FB6-5839-41E1-AC06-8D9949B461AC}"/>
+    <hyperlink ref="J74" r:id="rId88" xr:uid="{B7D5820B-1F3D-4D0E-A47D-20072EB8BBBE}"/>
+    <hyperlink ref="I73" r:id="rId89" xr:uid="{0AECC585-C22C-466A-9DD8-680618CE482C}"/>
+    <hyperlink ref="J73" r:id="rId90" xr:uid="{C3A3F0A6-33F1-4328-BF10-E113DBBEF38F}"/>
+    <hyperlink ref="J70" r:id="rId91" xr:uid="{68B72E20-33B9-4DEC-9ED1-60B37506BCDD}"/>
+    <hyperlink ref="I70" r:id="rId92" xr:uid="{C736AAB1-9716-4350-A6EB-A381CE4E7CCD}"/>
+    <hyperlink ref="J67" r:id="rId93" xr:uid="{752C2683-11F4-4130-9245-211B37841510}"/>
+    <hyperlink ref="I67" r:id="rId94" xr:uid="{EA51E579-73B3-4A35-B724-480050ED921C}"/>
+    <hyperlink ref="J66" r:id="rId95" xr:uid="{3C9E633D-16AC-41F4-9319-FDDB83D97349}"/>
+    <hyperlink ref="I66" r:id="rId96" xr:uid="{3E32E8C7-A58A-4A22-A76D-04BAE7EC648B}"/>
+    <hyperlink ref="J64" r:id="rId97" xr:uid="{78696536-2EE3-4E1E-BE35-3104DCC74F14}"/>
+    <hyperlink ref="I64" r:id="rId98" xr:uid="{1357F0CA-ED11-4C8F-A624-FF42D1B7FDB5}"/>
+    <hyperlink ref="J63" r:id="rId99" xr:uid="{F0EEEEEF-EBE5-4544-B8BA-8E931925B446}"/>
+    <hyperlink ref="I63" r:id="rId100" xr:uid="{4334CF94-C610-4B1A-A4D2-6CD9050589CA}"/>
+    <hyperlink ref="J61" r:id="rId101" xr:uid="{36CEEA26-13A0-4AFA-8ED6-B4B6BC4B51BA}"/>
+    <hyperlink ref="I61" r:id="rId102" xr:uid="{D4FD42AF-DC0B-41B1-A1CF-67D8689FA322}"/>
+    <hyperlink ref="J34" r:id="rId103" xr:uid="{879099B2-2A0C-40A7-8A67-6C10CBF856D5}"/>
+    <hyperlink ref="I34" r:id="rId104" xr:uid="{39AA173B-82EA-49C0-AB10-59F5102644AE}"/>
+    <hyperlink ref="I59" r:id="rId105" xr:uid="{AF006A7D-90EE-4043-B23C-FCFA92E4B64D}"/>
+    <hyperlink ref="J59" r:id="rId106" xr:uid="{54C8F634-D910-413C-87D6-1278DAF31A3D}"/>
+    <hyperlink ref="I60" r:id="rId107" xr:uid="{0DB723D1-7E83-4837-BD4C-0EE522F370EB}"/>
+    <hyperlink ref="J60" r:id="rId108" xr:uid="{F7626FDC-49F2-48D7-8AB4-747CB4E5205A}"/>
+    <hyperlink ref="I57" r:id="rId109" xr:uid="{1A6A9BEB-14DD-452B-B093-004CC31CBC62}"/>
+    <hyperlink ref="J57" r:id="rId110" xr:uid="{0352086C-B63D-43D9-94F4-B89DC5E6CD8F}"/>
+    <hyperlink ref="I55" r:id="rId111" xr:uid="{F9FB0BA6-17D5-4EE4-8FFB-18A226B39AE5}"/>
+    <hyperlink ref="J55" r:id="rId112" xr:uid="{C6E3E414-6FFD-4591-BCD5-A87CCCA662DE}"/>
+    <hyperlink ref="I54" r:id="rId113" xr:uid="{721CF701-F1E2-4D7D-BC9E-45C800A11082}"/>
+    <hyperlink ref="J54" r:id="rId114" xr:uid="{578E24F6-6EF4-4106-AC34-2EB032E5DBAC}"/>
     <hyperlink ref="I7" r:id="rId115" xr:uid="{460B13BE-9FBD-4212-989D-A38BF444C977}"/>
     <hyperlink ref="J7" r:id="rId116" xr:uid="{F80F1184-6004-4DE3-A74B-2FA197532CAD}"/>
     <hyperlink ref="I10" r:id="rId117" xr:uid="{4231DB13-C70E-4D21-B210-8DDD89D2EE71}"/>
     <hyperlink ref="J10" r:id="rId118" xr:uid="{8AA4738F-FC96-41CA-87DA-4152EF3852B8}"/>
-    <hyperlink ref="I95" r:id="rId119" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
-    <hyperlink ref="J95" r:id="rId120" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
+    <hyperlink ref="I96" r:id="rId119" xr:uid="{1DCFFFE2-22E0-443E-BB64-562E9F90ECA3}"/>
+    <hyperlink ref="J96" r:id="rId120" xr:uid="{29F51A9E-C7A9-4814-94D0-D5E6DC71A5C1}"/>
     <hyperlink ref="I9" r:id="rId121" xr:uid="{5C8F2870-5E10-4B34-8BCC-743C5F27272D}"/>
     <hyperlink ref="J9" r:id="rId122" xr:uid="{628D75D8-9DA8-4D3C-8F1C-F2FF0AFE9CD7}"/>
     <hyperlink ref="I11" r:id="rId123" xr:uid="{B71FE562-A9A6-4B3C-AB49-50BB818D223D}"/>
@@ -20998,147 +21142,149 @@
     <hyperlink ref="J8" r:id="rId126" xr:uid="{82F38111-DBC6-4CEB-AC91-8779B5919A35}"/>
     <hyperlink ref="I12" r:id="rId127" xr:uid="{1D827E8B-5090-4D3B-8D5D-D405D16061B2}"/>
     <hyperlink ref="J12" r:id="rId128" xr:uid="{01F1AB04-96C0-4051-9DE9-1884E1425122}"/>
-    <hyperlink ref="I18" r:id="rId129" xr:uid="{1890E57B-E8F7-4840-9572-DFEA56597C1F}"/>
-    <hyperlink ref="J18" r:id="rId130" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
+    <hyperlink ref="I19" r:id="rId129" xr:uid="{1890E57B-E8F7-4840-9572-DFEA56597C1F}"/>
+    <hyperlink ref="J19" r:id="rId130" xr:uid="{67050336-EA4B-4356-8517-166EC5C5D269}"/>
     <hyperlink ref="I16" r:id="rId131" xr:uid="{AFDCBC25-6599-4F55-99D2-8913687FB136}"/>
     <hyperlink ref="J16" r:id="rId132" xr:uid="{411646F0-69D3-4EDF-9126-2F65597A7EFA}"/>
     <hyperlink ref="I13" r:id="rId133" xr:uid="{5E8073D0-D198-4EF7-B401-0DAE1D13CFF4}"/>
     <hyperlink ref="J13" r:id="rId134" xr:uid="{2B75F78E-758A-4053-AE75-07DCB5BE6D3E}"/>
     <hyperlink ref="I14" r:id="rId135" xr:uid="{BD740605-5FB0-4AEE-B015-353A212878C4}"/>
     <hyperlink ref="J14" r:id="rId136" xr:uid="{C15841C1-57C4-460F-B85E-70AD289D0DB2}"/>
-    <hyperlink ref="I31" r:id="rId137" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
-    <hyperlink ref="J31" r:id="rId138" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
-    <hyperlink ref="I29" r:id="rId139" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
-    <hyperlink ref="J29" r:id="rId140" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
-    <hyperlink ref="J22" r:id="rId141" xr:uid="{0EA49793-A85B-4792-89B2-B1C8F3B131B4}"/>
-    <hyperlink ref="I22" r:id="rId142" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
-    <hyperlink ref="J23" r:id="rId143" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
-    <hyperlink ref="I23" r:id="rId144" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
-    <hyperlink ref="I24" r:id="rId145" xr:uid="{764AE888-2456-4D6C-B45F-9B2E88E39CFB}"/>
-    <hyperlink ref="I20" r:id="rId146" xr:uid="{67194D02-2892-4E14-8E03-07992EAC0C02}"/>
-    <hyperlink ref="J20" r:id="rId147" xr:uid="{C8E04EB8-2ACF-4142-A3C6-5AE9F3584ECD}"/>
-    <hyperlink ref="J21" r:id="rId148" xr:uid="{878F8657-2717-44A5-8B6C-025F2EE420EB}"/>
-    <hyperlink ref="I21" r:id="rId149" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
-    <hyperlink ref="I28" r:id="rId150" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
-    <hyperlink ref="J28" r:id="rId151" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
-    <hyperlink ref="I25" r:id="rId152" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
-    <hyperlink ref="J25" r:id="rId153" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
-    <hyperlink ref="J30" r:id="rId154" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
-    <hyperlink ref="I30" r:id="rId155" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
-    <hyperlink ref="I34" r:id="rId156" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
-    <hyperlink ref="J34" r:id="rId157" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
-    <hyperlink ref="I41" r:id="rId158" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
-    <hyperlink ref="J41" r:id="rId159" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
-    <hyperlink ref="J45" r:id="rId160" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
-    <hyperlink ref="I45" r:id="rId161" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
-    <hyperlink ref="I125" r:id="rId162" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
-    <hyperlink ref="J125" r:id="rId163" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
-    <hyperlink ref="I111" r:id="rId164" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
-    <hyperlink ref="J111" r:id="rId165" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
+    <hyperlink ref="I32" r:id="rId137" xr:uid="{00289898-76D1-487C-BD85-6F5E4366363B}"/>
+    <hyperlink ref="J32" r:id="rId138" xr:uid="{15FF9A37-B212-4ED6-A513-C5B683682229}"/>
+    <hyperlink ref="I30" r:id="rId139" xr:uid="{26A09476-022E-49A1-8D96-8F51CBE08EDA}"/>
+    <hyperlink ref="J30" r:id="rId140" xr:uid="{89FDA199-13C2-4B65-9BBF-977C7BB3C8EA}"/>
+    <hyperlink ref="J23" r:id="rId141" xr:uid="{0EA49793-A85B-4792-89B2-B1C8F3B131B4}"/>
+    <hyperlink ref="I23" r:id="rId142" xr:uid="{32B3A064-5AF0-43BA-8764-5164DE064242}"/>
+    <hyperlink ref="J24" r:id="rId143" xr:uid="{BE127895-EF0A-4C7B-8AE7-D2A893C0E771}"/>
+    <hyperlink ref="I24" r:id="rId144" xr:uid="{BA87EF61-770E-4130-94EE-9E0859AF00A3}"/>
+    <hyperlink ref="I25" r:id="rId145" xr:uid="{764AE888-2456-4D6C-B45F-9B2E88E39CFB}"/>
+    <hyperlink ref="I21" r:id="rId146" xr:uid="{67194D02-2892-4E14-8E03-07992EAC0C02}"/>
+    <hyperlink ref="J21" r:id="rId147" xr:uid="{C8E04EB8-2ACF-4142-A3C6-5AE9F3584ECD}"/>
+    <hyperlink ref="J22" r:id="rId148" xr:uid="{878F8657-2717-44A5-8B6C-025F2EE420EB}"/>
+    <hyperlink ref="I22" r:id="rId149" xr:uid="{02D8BFEE-7401-43E3-9165-3BA3B3E8930A}"/>
+    <hyperlink ref="I29" r:id="rId150" xr:uid="{AE0B7994-7107-4ABA-95CB-F46EAF061BBC}"/>
+    <hyperlink ref="J29" r:id="rId151" xr:uid="{9B4E4F3B-EAB8-4062-AAA3-3F39F59EFC1F}"/>
+    <hyperlink ref="I26" r:id="rId152" xr:uid="{2791B754-BE67-4D87-91CB-E615980D812F}"/>
+    <hyperlink ref="J26" r:id="rId153" xr:uid="{E6E87C18-F25B-4A09-BB1B-6FF0020CCC32}"/>
+    <hyperlink ref="J31" r:id="rId154" xr:uid="{F5D48171-0885-469F-80BD-43B4BAD3B32A}"/>
+    <hyperlink ref="I31" r:id="rId155" xr:uid="{0B52C307-D1AB-4CA1-AF35-A7A73EDB2E5B}"/>
+    <hyperlink ref="I35" r:id="rId156" xr:uid="{AD1FC901-2777-4489-936F-339740BF67AD}"/>
+    <hyperlink ref="J35" r:id="rId157" xr:uid="{8ECC528D-31A0-4488-AE02-BF273C795577}"/>
+    <hyperlink ref="I42" r:id="rId158" xr:uid="{704B7425-D2D7-4C0E-B8F8-16E36817744A}"/>
+    <hyperlink ref="J42" r:id="rId159" xr:uid="{9B55309C-58EE-494C-8F13-0B8DA894FFFD}"/>
+    <hyperlink ref="J46" r:id="rId160" xr:uid="{29981086-6890-419B-A8D2-FBB1158A6C4B}"/>
+    <hyperlink ref="I46" r:id="rId161" xr:uid="{49AB5A4C-9429-4E42-9092-ACEA7A37AF66}"/>
+    <hyperlink ref="I128" r:id="rId162" xr:uid="{7CEBF0BB-4505-41A5-BD5F-1C5F7632DB37}"/>
+    <hyperlink ref="J128" r:id="rId163" xr:uid="{8682DB90-6FE7-401C-B9C1-2559333E6C2A}"/>
+    <hyperlink ref="I114" r:id="rId164" xr:uid="{E68EAFAD-3CF9-44BD-838C-CFEED5144C58}"/>
+    <hyperlink ref="J114" r:id="rId165" xr:uid="{40CF4723-E290-4426-93A9-8C01EC2BD1A4}"/>
     <hyperlink ref="J17" r:id="rId166" xr:uid="{76D67995-A6ED-43F5-90F5-FB88B787D5F1}"/>
     <hyperlink ref="I17" r:id="rId167" xr:uid="{D26D60C2-4D17-4B90-A20B-BA8D811177C8}"/>
-    <hyperlink ref="I114" r:id="rId168" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
-    <hyperlink ref="J114" r:id="rId169" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
-    <hyperlink ref="J68" r:id="rId170" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
-    <hyperlink ref="I68" r:id="rId171" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
-    <hyperlink ref="I51" r:id="rId172" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
-    <hyperlink ref="J51" r:id="rId173" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
-    <hyperlink ref="I43" r:id="rId174" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
-    <hyperlink ref="J43" r:id="rId175" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
-    <hyperlink ref="J40" r:id="rId176" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
-    <hyperlink ref="I40" r:id="rId177" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
-    <hyperlink ref="J42" r:id="rId178" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
-    <hyperlink ref="I42" r:id="rId179" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
-    <hyperlink ref="J116" r:id="rId180" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
-    <hyperlink ref="I116" r:id="rId181" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
-    <hyperlink ref="I135" r:id="rId182" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
-    <hyperlink ref="J135" r:id="rId183" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
-    <hyperlink ref="I134" r:id="rId184" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
-    <hyperlink ref="J134" r:id="rId185" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
-    <hyperlink ref="I105" r:id="rId186" xr:uid="{83583B05-7171-47AC-AF11-32B133FFE3DA}"/>
-    <hyperlink ref="J105" r:id="rId187" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
-    <hyperlink ref="I120" r:id="rId188" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
-    <hyperlink ref="J120" r:id="rId189" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
-    <hyperlink ref="I122" r:id="rId190" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
-    <hyperlink ref="J122" r:id="rId191" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
-    <hyperlink ref="J121" r:id="rId192" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
-    <hyperlink ref="I121" r:id="rId193" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
-    <hyperlink ref="I124" r:id="rId194" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
-    <hyperlink ref="J124" r:id="rId195" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
-    <hyperlink ref="I123" r:id="rId196" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
-    <hyperlink ref="J123" r:id="rId197" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
-    <hyperlink ref="I57" r:id="rId198" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
-    <hyperlink ref="J57" r:id="rId199" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
-    <hyperlink ref="I133" r:id="rId200" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
-    <hyperlink ref="J133" r:id="rId201" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
-    <hyperlink ref="I127" r:id="rId202" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
-    <hyperlink ref="J127" r:id="rId203" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
-    <hyperlink ref="J126" r:id="rId204" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
-    <hyperlink ref="J129" r:id="rId205" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
-    <hyperlink ref="I129" r:id="rId206" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
-    <hyperlink ref="I97" r:id="rId207" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
-    <hyperlink ref="J97" r:id="rId208" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
-    <hyperlink ref="I96" r:id="rId209" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
-    <hyperlink ref="J96" r:id="rId210" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
-    <hyperlink ref="I98" r:id="rId211" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
-    <hyperlink ref="J98" r:id="rId212" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
-    <hyperlink ref="I26" r:id="rId213" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
-    <hyperlink ref="J26" r:id="rId214" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
-    <hyperlink ref="I27" r:id="rId215" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
-    <hyperlink ref="J27" r:id="rId216" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
-    <hyperlink ref="I64" r:id="rId217" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
-    <hyperlink ref="J64" r:id="rId218" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
-    <hyperlink ref="J70" r:id="rId219" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
-    <hyperlink ref="I70" r:id="rId220" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
-    <hyperlink ref="I71" r:id="rId221" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
-    <hyperlink ref="J71" r:id="rId222" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
-    <hyperlink ref="J81" r:id="rId223" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
-    <hyperlink ref="I81" r:id="rId224" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
-    <hyperlink ref="J128" r:id="rId225" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
-    <hyperlink ref="I128" r:id="rId226" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
-    <hyperlink ref="I61" r:id="rId227" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
-    <hyperlink ref="J61" r:id="rId228" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
-    <hyperlink ref="I55" r:id="rId229" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
-    <hyperlink ref="J55" r:id="rId230" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
-    <hyperlink ref="J78" r:id="rId231" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
-    <hyperlink ref="I78" r:id="rId232" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
-    <hyperlink ref="I48" r:id="rId233" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
-    <hyperlink ref="J48" r:id="rId234" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
-    <hyperlink ref="I49" r:id="rId235" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
-    <hyperlink ref="J49" r:id="rId236" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
-    <hyperlink ref="I52" r:id="rId237" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
-    <hyperlink ref="J52" r:id="rId238" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
-    <hyperlink ref="I44" r:id="rId239" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
-    <hyperlink ref="J44" r:id="rId240" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
-    <hyperlink ref="I46" r:id="rId241" xr:uid="{F619EC4F-CE2B-4A3F-A177-258B37F94B75}"/>
-    <hyperlink ref="J46" r:id="rId242" xr:uid="{16154418-6F7F-4716-B182-4CD246E54171}"/>
-    <hyperlink ref="I35" r:id="rId243" xr:uid="{E9BFACD2-2358-4D6F-8475-85410D79F5A9}"/>
-    <hyperlink ref="J35" r:id="rId244" xr:uid="{EBB7510F-0BE0-4317-9B06-1D95171523D6}"/>
-    <hyperlink ref="I126" r:id="rId245" xr:uid="{45C41464-28AE-4668-AC10-B5CD2C5D57A9}"/>
-    <hyperlink ref="I130" r:id="rId246" xr:uid="{15ED860D-2D4B-4897-97C4-651CA00D92FA}"/>
-    <hyperlink ref="J36" r:id="rId247" xr:uid="{5CF69990-5819-4326-B945-ED2995B498CF}"/>
+    <hyperlink ref="I117" r:id="rId168" xr:uid="{167182BD-69C0-437E-9CF5-54C2058AEFC9}"/>
+    <hyperlink ref="J117" r:id="rId169" xr:uid="{F9DC6B86-FDA2-4B9F-A391-520A33B699A5}"/>
+    <hyperlink ref="J69" r:id="rId170" xr:uid="{FD9507D8-0A63-4248-8274-A037A2C94EA6}"/>
+    <hyperlink ref="I69" r:id="rId171" xr:uid="{C0C512AC-E1AC-4636-906A-D80F35D8EF88}"/>
+    <hyperlink ref="I52" r:id="rId172" xr:uid="{72775C65-BCFE-4EAA-A095-83016A66219B}"/>
+    <hyperlink ref="J52" r:id="rId173" xr:uid="{F1230CE8-6838-4503-9B59-6D8B10FFBA4C}"/>
+    <hyperlink ref="I44" r:id="rId174" xr:uid="{A1551B8F-122E-4A01-A624-537D3FF3BC86}"/>
+    <hyperlink ref="J44" r:id="rId175" xr:uid="{8EBE9170-4ED2-48BB-8597-7E08858771B0}"/>
+    <hyperlink ref="J41" r:id="rId176" xr:uid="{8A354218-7A3E-4F0D-B53C-D1400D47250C}"/>
+    <hyperlink ref="I41" r:id="rId177" xr:uid="{BDBB4C08-FED3-43A6-A047-95F66D3DD2DE}"/>
+    <hyperlink ref="J43" r:id="rId178" xr:uid="{11AB11CE-9AFE-4D1E-A5C7-5E14ACC3783B}"/>
+    <hyperlink ref="I43" r:id="rId179" xr:uid="{D0F7E8F4-418A-43CD-952C-22515E908228}"/>
+    <hyperlink ref="J119" r:id="rId180" xr:uid="{DA4040B9-E67A-4A93-A16D-210AFB8891A7}"/>
+    <hyperlink ref="I119" r:id="rId181" xr:uid="{781A3461-AA34-43E9-A051-045FFD079918}"/>
+    <hyperlink ref="I138" r:id="rId182" xr:uid="{F5FB8545-3358-4D42-AEA7-18131E191D00}"/>
+    <hyperlink ref="J138" r:id="rId183" xr:uid="{DF7BAAE3-570C-4F1D-8E47-C219B2446D02}"/>
+    <hyperlink ref="I137" r:id="rId184" xr:uid="{E8947EEF-92DD-4F08-8EA4-AB2E21EDACAA}"/>
+    <hyperlink ref="J137" r:id="rId185" xr:uid="{3956496B-9948-43E1-A5FC-DC2FA40209A1}"/>
+    <hyperlink ref="I106" r:id="rId186" xr:uid="{83583B05-7171-47AC-AF11-32B133FFE3DA}"/>
+    <hyperlink ref="J106" r:id="rId187" xr:uid="{78C8868A-AF67-440C-BB47-7E95AF4D7CDC}"/>
+    <hyperlink ref="I123" r:id="rId188" xr:uid="{B3310608-2270-4375-A1F8-A3829C1AC272}"/>
+    <hyperlink ref="J123" r:id="rId189" xr:uid="{C990AE76-0667-4DFF-8ACB-3BACDA84E4A4}"/>
+    <hyperlink ref="I125" r:id="rId190" xr:uid="{235688FE-3563-4C29-8A34-439C000C44FF}"/>
+    <hyperlink ref="J125" r:id="rId191" xr:uid="{F5D5F47B-7CC4-4706-8554-40749FBDA692}"/>
+    <hyperlink ref="J124" r:id="rId192" xr:uid="{AA716769-7D69-4187-85DA-367E3745CD50}"/>
+    <hyperlink ref="I124" r:id="rId193" xr:uid="{40F0F7AF-85EB-4D19-8E56-0EF602391081}"/>
+    <hyperlink ref="I127" r:id="rId194" xr:uid="{1BB3D366-EC82-4BC7-AA54-603B1F623203}"/>
+    <hyperlink ref="J127" r:id="rId195" xr:uid="{CC55B3E5-6C87-47F5-A90F-48468AFE28D5}"/>
+    <hyperlink ref="I126" r:id="rId196" xr:uid="{529DA521-5BF2-4FC0-8E26-6F7E7B8296E0}"/>
+    <hyperlink ref="J126" r:id="rId197" xr:uid="{4A9EF431-1AFB-4EEA-93F2-C74CD1FB813B}"/>
+    <hyperlink ref="I58" r:id="rId198" xr:uid="{49E947B7-83D6-41C9-B69C-CAB5C5AEC39A}"/>
+    <hyperlink ref="J58" r:id="rId199" xr:uid="{FB595B99-C912-4D67-9DF5-7D02CD3534C7}"/>
+    <hyperlink ref="I136" r:id="rId200" xr:uid="{C0505347-3BD6-41B7-AC6C-05C60895A89E}"/>
+    <hyperlink ref="J136" r:id="rId201" xr:uid="{42F626B2-7D55-42A7-A2A4-F512AB0412AF}"/>
+    <hyperlink ref="I130" r:id="rId202" xr:uid="{77988EB9-32CD-4E17-AAEF-924054969DFB}"/>
+    <hyperlink ref="J130" r:id="rId203" xr:uid="{787C4EC8-5046-4CC9-B80D-9108F8C78F34}"/>
+    <hyperlink ref="J129" r:id="rId204" xr:uid="{1DE31FA9-566E-4F69-A1CD-357489485E4D}"/>
+    <hyperlink ref="J132" r:id="rId205" xr:uid="{36372F47-50E3-4668-92B8-FA48D59E1E3F}"/>
+    <hyperlink ref="I132" r:id="rId206" xr:uid="{A271F274-015F-46E9-9F64-737F6D2AE706}"/>
+    <hyperlink ref="I98" r:id="rId207" xr:uid="{A79F4AEC-48D8-4C14-8BED-83BF177DF3D5}"/>
+    <hyperlink ref="J98" r:id="rId208" xr:uid="{B08A2DD0-B311-4BDE-941E-96DFA5ADE854}"/>
+    <hyperlink ref="I97" r:id="rId209" xr:uid="{1782304D-E4B5-4A13-BCB7-D7C04B2563D4}"/>
+    <hyperlink ref="J97" r:id="rId210" xr:uid="{CD2BE59B-DDA4-42E1-ADF3-F83EF71EAD9A}"/>
+    <hyperlink ref="I99" r:id="rId211" xr:uid="{8F8B10ED-8F10-4D91-9D78-382CDB5DB10C}"/>
+    <hyperlink ref="J99" r:id="rId212" xr:uid="{226C7FD3-970D-4762-B807-3BC705E1535D}"/>
+    <hyperlink ref="I27" r:id="rId213" xr:uid="{15D5A75D-4DA8-4E1D-90CF-CE7479B1BE2C}"/>
+    <hyperlink ref="J27" r:id="rId214" xr:uid="{71314C7C-9808-47D3-8671-15530046443E}"/>
+    <hyperlink ref="I28" r:id="rId215" xr:uid="{4DEE5057-A4A1-4CB8-8F9B-04CC70E6B6C6}"/>
+    <hyperlink ref="J28" r:id="rId216" xr:uid="{AD960EF2-6147-470E-B89A-18BC4523F2E8}"/>
+    <hyperlink ref="I65" r:id="rId217" xr:uid="{2226B77B-0F7B-4CB5-99FC-497B0C7E5B0E}"/>
+    <hyperlink ref="J65" r:id="rId218" xr:uid="{0200F84C-A2E7-45F1-964F-231BE02D328E}"/>
+    <hyperlink ref="J71" r:id="rId219" xr:uid="{A93D7AB8-13FE-4F10-ACE3-E13010659511}"/>
+    <hyperlink ref="I71" r:id="rId220" xr:uid="{E28E71AF-AD06-4024-A3C3-15A154D577A1}"/>
+    <hyperlink ref="I72" r:id="rId221" xr:uid="{E69F1727-8B94-4B05-BCAD-E5CF84978DA3}"/>
+    <hyperlink ref="J72" r:id="rId222" xr:uid="{812E0B96-C965-4DD1-B1C4-5F452683DCC0}"/>
+    <hyperlink ref="J82" r:id="rId223" xr:uid="{1D827CE8-5A84-4885-9E49-DB3C850610A8}"/>
+    <hyperlink ref="I82" r:id="rId224" xr:uid="{B1721EF0-26E2-4479-8D4F-B42689B14CB5}"/>
+    <hyperlink ref="J131" r:id="rId225" xr:uid="{DD7F5317-6015-4283-AC32-E72F536FC3C5}"/>
+    <hyperlink ref="I131" r:id="rId226" xr:uid="{F79E9E23-2DB5-4421-BFA2-679378875B4D}"/>
+    <hyperlink ref="I62" r:id="rId227" xr:uid="{8C75AB6A-369A-457E-96CC-09F311B9D1B1}"/>
+    <hyperlink ref="J62" r:id="rId228" xr:uid="{784BCF3B-1179-4E11-A7BA-F49DEDF943B6}"/>
+    <hyperlink ref="I56" r:id="rId229" xr:uid="{6967513D-3736-47D4-8FF2-1C2AFE06086A}"/>
+    <hyperlink ref="J56" r:id="rId230" xr:uid="{B93C0ECD-A7D4-49DD-849B-ADD887E97AF7}"/>
+    <hyperlink ref="J79" r:id="rId231" xr:uid="{21B57A45-13EB-45D5-B9C7-3B9F07AD7EE3}"/>
+    <hyperlink ref="I79" r:id="rId232" xr:uid="{FEE6DBC5-A1A3-474F-9ABA-FB9242102CAA}"/>
+    <hyperlink ref="I49" r:id="rId233" xr:uid="{46897E6A-7571-4E9E-AAB3-8403783511EB}"/>
+    <hyperlink ref="J49" r:id="rId234" xr:uid="{BDF65722-1595-4D01-8E29-38CE7C892593}"/>
+    <hyperlink ref="I50" r:id="rId235" xr:uid="{B96FFB57-BD0D-42F2-9273-C34D69FB09EF}"/>
+    <hyperlink ref="J50" r:id="rId236" xr:uid="{AB614987-EB33-461A-A951-E658B5B6B01C}"/>
+    <hyperlink ref="I53" r:id="rId237" xr:uid="{6320ADA9-08B3-4F61-89D3-E8C47402CCEB}"/>
+    <hyperlink ref="J53" r:id="rId238" xr:uid="{D674523E-69B2-403D-AB5F-98662D47CDC9}"/>
+    <hyperlink ref="I45" r:id="rId239" xr:uid="{31695CB4-CD72-49E0-B154-04DD500F517D}"/>
+    <hyperlink ref="J45" r:id="rId240" xr:uid="{A86FECE6-3A33-4B91-84CA-1E0141FC447F}"/>
+    <hyperlink ref="I47" r:id="rId241" xr:uid="{F619EC4F-CE2B-4A3F-A177-258B37F94B75}"/>
+    <hyperlink ref="J47" r:id="rId242" xr:uid="{16154418-6F7F-4716-B182-4CD246E54171}"/>
+    <hyperlink ref="I36" r:id="rId243" xr:uid="{E9BFACD2-2358-4D6F-8475-85410D79F5A9}"/>
+    <hyperlink ref="J36" r:id="rId244" xr:uid="{EBB7510F-0BE0-4317-9B06-1D95171523D6}"/>
+    <hyperlink ref="I129" r:id="rId245" xr:uid="{45C41464-28AE-4668-AC10-B5CD2C5D57A9}"/>
+    <hyperlink ref="I133" r:id="rId246" xr:uid="{15ED860D-2D4B-4897-97C4-651CA00D92FA}"/>
+    <hyperlink ref="J37" r:id="rId247" xr:uid="{5CF69990-5819-4326-B945-ED2995B498CF}"/>
     <hyperlink ref="I4" r:id="rId248" xr:uid="{7D3DCF5C-EF7C-4124-B5A1-25ADC1DFDADE}"/>
     <hyperlink ref="J4" r:id="rId249" xr:uid="{3265B707-A661-41E5-BD88-CD59552DEA1E}"/>
-    <hyperlink ref="I101" r:id="rId250" xr:uid="{A6C1D39E-0373-40B0-8016-2DC906697581}"/>
-    <hyperlink ref="J101" r:id="rId251" xr:uid="{E96F8A50-A558-4AA1-834F-8D81423906C9}"/>
-    <hyperlink ref="I102" r:id="rId252" xr:uid="{EFAA277E-33BA-4E31-8F6C-3D44B6838AB5}"/>
-    <hyperlink ref="J102" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
-    <hyperlink ref="J99" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
-    <hyperlink ref="I99" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
-    <hyperlink ref="J100" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
-    <hyperlink ref="I100" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
+    <hyperlink ref="I102" r:id="rId250" xr:uid="{A6C1D39E-0373-40B0-8016-2DC906697581}"/>
+    <hyperlink ref="J102" r:id="rId251" xr:uid="{E96F8A50-A558-4AA1-834F-8D81423906C9}"/>
+    <hyperlink ref="I103" r:id="rId252" xr:uid="{EFAA277E-33BA-4E31-8F6C-3D44B6838AB5}"/>
+    <hyperlink ref="J103" r:id="rId253" xr:uid="{8056DABE-32D9-4ACE-B43B-46C52475599A}"/>
+    <hyperlink ref="J100" r:id="rId254" xr:uid="{121194D4-D234-4253-A8F1-B456A77A6C00}"/>
+    <hyperlink ref="I100" r:id="rId255" xr:uid="{007C2137-087C-44CA-B0A9-E33381B006C6}"/>
+    <hyperlink ref="J101" r:id="rId256" xr:uid="{3DFA5488-1B32-42B9-974B-DAC0305C2404}"/>
+    <hyperlink ref="I101" r:id="rId257" xr:uid="{990E2484-295C-47D0-964D-A876E469F9B2}"/>
     <hyperlink ref="I5" r:id="rId258" xr:uid="{A1A2837E-B079-456D-84AB-6A1561328A15}"/>
     <hyperlink ref="J5" r:id="rId259" xr:uid="{5B16694A-EF14-479B-83C7-4F9D8A886209}"/>
-    <hyperlink ref="I47" r:id="rId260" xr:uid="{6AB6E69D-F1A6-4525-8E1D-E39B1043B707}"/>
-    <hyperlink ref="J47" r:id="rId261" xr:uid="{C3008C5E-7367-4D13-8A51-811BB64125E9}"/>
-    <hyperlink ref="I110" r:id="rId262" xr:uid="{C87BE13B-FF08-4594-91D4-2FC13EEEC8DA}"/>
-    <hyperlink ref="J110" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
-    <hyperlink ref="I84" r:id="rId264" xr:uid="{65C8A524-1F2E-408F-9C4E-A8DCC7FE2AC3}"/>
-    <hyperlink ref="J84" r:id="rId265" xr:uid="{7354F640-B4B5-4D02-9DA0-17429462CBFC}"/>
-    <hyperlink ref="I136" r:id="rId266" xr:uid="{F7F90A0C-1255-4B1C-B6C5-A3741DBF44D9}"/>
-    <hyperlink ref="J136" r:id="rId267" xr:uid="{C08BA9FA-1885-4E4A-A596-729CCFBD9D8D}"/>
-    <hyperlink ref="I137" r:id="rId268" xr:uid="{67C7E615-CBFE-48F9-AA14-F14A0188E638}"/>
-    <hyperlink ref="J137" r:id="rId269" xr:uid="{D57BF95E-7B0F-40EF-9E3A-010F0E80480A}"/>
+    <hyperlink ref="I48" r:id="rId260" xr:uid="{6AB6E69D-F1A6-4525-8E1D-E39B1043B707}"/>
+    <hyperlink ref="J48" r:id="rId261" xr:uid="{C3008C5E-7367-4D13-8A51-811BB64125E9}"/>
+    <hyperlink ref="I111" r:id="rId262" xr:uid="{C87BE13B-FF08-4594-91D4-2FC13EEEC8DA}"/>
+    <hyperlink ref="J111" r:id="rId263" xr:uid="{26B6DF74-28B1-4422-876E-87A4A1A6C590}"/>
+    <hyperlink ref="I85" r:id="rId264" xr:uid="{65C8A524-1F2E-408F-9C4E-A8DCC7FE2AC3}"/>
+    <hyperlink ref="J85" r:id="rId265" xr:uid="{7354F640-B4B5-4D02-9DA0-17429462CBFC}"/>
+    <hyperlink ref="I112" r:id="rId266" xr:uid="{F7F90A0C-1255-4B1C-B6C5-A3741DBF44D9}"/>
+    <hyperlink ref="J112" r:id="rId267" xr:uid="{C08BA9FA-1885-4E4A-A596-729CCFBD9D8D}"/>
+    <hyperlink ref="I18" r:id="rId268" xr:uid="{67C7E615-CBFE-48F9-AA14-F14A0188E638}"/>
+    <hyperlink ref="J18" r:id="rId269" xr:uid="{D57BF95E-7B0F-40EF-9E3A-010F0E80480A}"/>
+    <hyperlink ref="I113" r:id="rId270" xr:uid="{DECA6A92-1D33-42D7-B77F-7AF5137B58FA}"/>
+    <hyperlink ref="J113" r:id="rId271" xr:uid="{413366AD-81D0-45B9-BF11-46059D16B4E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21146,7 +21292,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1333"/>
+  <dimension ref="A1:I1341"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -57418,6 +57564,226 @@
       </c>
       <c r="I1333" s="3"/>
     </row>
+    <row r="1334" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1334" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1334" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1334" s="4" t="s">
+        <v>4774</v>
+      </c>
+      <c r="D1334" s="8" t="s">
+        <v>4782</v>
+      </c>
+      <c r="E1334" s="14">
+        <v>4.28</v>
+      </c>
+      <c r="F1334" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G1334" s="31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1334" s="17" t="s">
+        <v>4797</v>
+      </c>
+      <c r="I1334" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1335" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1335" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1335" s="4" t="s">
+        <v>4775</v>
+      </c>
+      <c r="D1335" s="8" t="s">
+        <v>4783</v>
+      </c>
+      <c r="E1335" s="14">
+        <v>4.09</v>
+      </c>
+      <c r="F1335" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1335" s="31">
+        <v>4.7</v>
+      </c>
+      <c r="H1335" s="6" t="s">
+        <v>4792</v>
+      </c>
+      <c r="I1335" s="3"/>
+    </row>
+    <row r="1336" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1336" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1336" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1336" s="4" t="s">
+        <v>4776</v>
+      </c>
+      <c r="D1336" s="8" t="s">
+        <v>4784</v>
+      </c>
+      <c r="E1336" s="14">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F1336" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1336" s="31">
+        <v>4.8</v>
+      </c>
+      <c r="H1336" s="6" t="s">
+        <v>4790</v>
+      </c>
+      <c r="I1336" s="3"/>
+    </row>
+    <row r="1337" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1337" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1337" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1337" s="4" t="s">
+        <v>4777</v>
+      </c>
+      <c r="D1337" s="8" t="s">
+        <v>4785</v>
+      </c>
+      <c r="E1337" s="14">
+        <v>3.81</v>
+      </c>
+      <c r="F1337" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G1337" s="31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1337" s="6" t="s">
+        <v>4791</v>
+      </c>
+      <c r="I1337" s="3"/>
+    </row>
+    <row r="1338" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1338" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1338" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1338" s="4" t="s">
+        <v>4778</v>
+      </c>
+      <c r="D1338" s="8" t="s">
+        <v>4786</v>
+      </c>
+      <c r="E1338" s="14">
+        <v>3.86</v>
+      </c>
+      <c r="F1338" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1338" s="31">
+        <v>4.7</v>
+      </c>
+      <c r="H1338" s="6" t="s">
+        <v>4793</v>
+      </c>
+      <c r="I1338" s="3"/>
+    </row>
+    <row r="1339" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1339" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1339" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1339" s="4" t="s">
+        <v>4779</v>
+      </c>
+      <c r="D1339" s="8" t="s">
+        <v>4787</v>
+      </c>
+      <c r="E1339" s="14">
+        <v>3.98</v>
+      </c>
+      <c r="F1339" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G1339" s="31">
+        <v>5</v>
+      </c>
+      <c r="H1339" s="6" t="s">
+        <v>4794</v>
+      </c>
+      <c r="I1339" s="3"/>
+    </row>
+    <row r="1340" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1340" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1340" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1340" s="4" t="s">
+        <v>4780</v>
+      </c>
+      <c r="D1340" s="8" t="s">
+        <v>4788</v>
+      </c>
+      <c r="E1340" s="14">
+        <v>3.73</v>
+      </c>
+      <c r="F1340" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G1340" s="31">
+        <v>4.7</v>
+      </c>
+      <c r="H1340" s="6" t="s">
+        <v>4795</v>
+      </c>
+      <c r="I1340" s="3"/>
+    </row>
+    <row r="1341" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1341" s="3">
+        <v>34956980</v>
+      </c>
+      <c r="B1341" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1341" s="4" t="s">
+        <v>4770</v>
+      </c>
+      <c r="D1341" s="8" t="s">
+        <v>4789</v>
+      </c>
+      <c r="E1341" s="14">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F1341" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G1341" s="31">
+        <v>5</v>
+      </c>
+      <c r="H1341" s="17" t="s">
+        <v>4796</v>
+      </c>
+      <c r="I1341" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6627F54F-C871-4708-9339-4C96A7D57EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4A0FF6-5F26-4179-81B3-9072D68D3162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="4798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="4865">
   <si>
     <t>No</t>
   </si>
@@ -15981,6 +15981,229 @@
         <charset val="161"/>
       </rPr>
       <t xml:space="preserve"> Από τα πιο χαρακτηριστικά Supertramp openings, ξεκινά με ήχους παιδικής αυλής, σφυρίχτρα και σταδιακή αίσθηση καταπίεσης, πριν εκραγεί σε electric-piano και κιθαριστική ένταση. Το “school” δεν αφορά απλώς το εκπαιδευτικό σύστημα· αφορά την κοινωνική διαμόρφωση, τις εντολές που δέχεται κανείς από παιδί και την προσπάθεια να ξεφύγει από μια ζωή όπου άλλοι ορίζουν την επιτυχία, τη συμπεριφορά και το μέλλον του. Η εναλλαγή Hodgson/Davies φωνητικών και η δραματική ανάπτυξη κάνουν το κομμάτι μικρή prog suite χωρίς να χάνει την άμεση μελωδία. Είναι ιδανικό concept opener, γιατί παρουσιάζει την αρχική “φυλακή” από την οποία θα προσπαθήσουν να διαφύγουν οι χαρακτήρες του δίσκου.</t>
+    </r>
+  </si>
+  <si>
+    <t>Island In The Sun</t>
+  </si>
+  <si>
+    <t>General Hospital</t>
+  </si>
+  <si>
+    <t>Jet To Jet</t>
+  </si>
+  <si>
+    <t>Hiroshima Mon Amour</t>
+  </si>
+  <si>
+    <t>Kree Nakoorie</t>
+  </si>
+  <si>
+    <t>Incubus</t>
+  </si>
+  <si>
+    <t>Too Young To Die, Too Drunk To Live</t>
+  </si>
+  <si>
+    <t>Big Foot</t>
+  </si>
+  <si>
+    <t>Starcarr Lane</t>
+  </si>
+  <si>
+    <t>Suffer Me</t>
+  </si>
+  <si>
+    <t>Kree Nakoorie (Instrumental)</t>
+  </si>
+  <si>
+    <t>Starcarr Lane (Instrumental)</t>
+  </si>
+  <si>
+    <t>Island In The Sun (Instrumental)</t>
+  </si>
+  <si>
+    <t>Big Foot (Instrumental)</t>
+  </si>
+  <si>
+    <t>Hiroshima Mon Amour (Instrumental)</t>
+  </si>
+  <si>
+    <t>General Hospital (Instrumental)</t>
+  </si>
+  <si>
+    <t>Incubus (Instrumental)</t>
+  </si>
+  <si>
+    <t>Suffer Me (Instrumental)</t>
+  </si>
+  <si>
+    <t>Too Young To Die, Too Drunk To Live (Instrumental)</t>
+  </si>
+  <si>
+    <t>Jet To Jet (Instrumental)</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Melodic Metal, AOR, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Riff Metal, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Neoclassical Metal [Fast Metal, Shred Guitar, Melodic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Dark Melodic Metal, Neo-Classical Rock, Arena Metal]</t>
+  </si>
+  <si>
+    <t>Neoclassical Metal, Instrumental Rock [Guitar Instrumental, Shred, Baroque Metal]</t>
+  </si>
+  <si>
+    <t>Neoclassical Metal, Instrumental Rock [Guitar Showcase, Neo-Classical Shred, Metal Instrumental]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Fast Melodic Metal, Street Metal, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Heavy Metal [Mid-tempo Metal, Riff Rock, AOR Metal]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Hard Rock, Keyboard Rock, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Neoclassical Metal [Dark Metal, Guitar Epic, Melodic Heavy Rock]</t>
+  </si>
+  <si>
+    <t>Neoclassical Metal, Instrumental Rock [Neoclassical Guitar, Shred, Baroque Metal]</t>
+  </si>
+  <si>
+    <t>AOR, Instrumental Rock [Melodic Rock, Keyboard Rock, Backing Track]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Melodic Guitar Rock, Keyboard Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Instrumental Rock [Mid-tempo Riff Rock, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Neoclassical Metal [Dark Guitar Rock, Shred, Melodic Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Rock [Riff Metal, Keyboard Metal, Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Neoclassical Metal, Instrumental Rock [Guitar Showcase, Shred, Neo-Classical Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Rock [Dark Guitar Rock, Neoclassical Metal]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Rock [Fast Melodic Metal, Shred Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Instrumental Rock [Speed Metal, Neoclassical Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Heavy Metal, Hard Rock [Neoclassical Metal, Shred Guitar, Melodic Metal, AOR]</t>
+  </si>
+  <si>
+    <t>No Parole From Rock 'N' Roll</t>
+  </si>
+  <si>
+    <t>Alcatrazz</t>
+  </si>
+  <si>
+    <t>Culture Factory – CF784097. Πρόκειται για ειδική διπλή έκδοση (Deluxe Edition, Reissue, Record Store Day 2026, 2-LP) που κυκλοφόρησε στις 18 Απριλίου 2026 στην Ευρώπη. Περιλαμβάνει έναν δίσκο σε κόκκινο βινύλιο (red marble effect) και έναν σε κίτρινο βινύλιο (yellow marble effect), με συνοδευτικό OBI strip και εσωτερικά sleeves.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/37070553-Alcatrazz-No-Parole-From-Rock-N-Roll</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/DnaRAobU0AS21ufWvoZ_BHoDdoc-F1rDQ6Ok4cED1eg/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTM3MDcw/NTUzLTE3NzYzNTU3/MDUtMjMyOS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Η συγκεκριμένη επανέκδοση του No Parole from Rock 'N' Roll από την Culture Factory (κωδικός: CF784097, Barcode: 3700477840976) κυκλοφόρησε στο πλαίσιο του Record Store Day (RSD 2026) ως Deluxe Edition 2LP. Δεν αποτελεί μια απλή επανεκτύπωση του κλασικού δίσκου του 1983, αλλά μια διευρυμένη αρχειακή έκδοση που απευθύνεται τόσο σε συλλέκτες όσο και σε απαιτητικούς κιθαριστικούς ακροατές. Το πακέτο περιλαμβάνει μονό εξώφυλλο με το αυθεντικό εικαστικό, τυπωμένα inner sleeves και ράχη τύπου OBI strip. Το οπτικό ενδιαφέρον επικεντρώνεται στο πρεσάρισμα δύο διαφορετικών χρωματικών δίσκων: ενός σε Red Marble Effect (LP 1) και ενός σε Orange/Yellow Marble Effect (LP 2). Η κατασκευή και η κοπή των μητρών πραγματοποιήθηκε στο γαλλικό εργοστάσιο της MPO (μήτρες: MPO V61182 01 CF784097 A/B/C/D).   Στο ηχητικό και παραγωγικό σκέλος, το LP 1 διατηρεί την αρχική δεκάδα τραγουδιών με τα επιβλητικά, τραχιά φωνητικά του Graham Bonnet και τη σφιχτή παραγωγή του Dennis MacKay. Η ουσιαστική διαφοροποίηση και η πραγματική audiophile προστιθέμενη αξία της συγκεκριμένης έκδοσης βρίσκεται στο LP 2 (πλευρές C &amp; D). Εκεί παρουσιάζονται για πρώτη φορά σε βινύλιο τα πλήρη Instrumental Mixes και των 10 κομματιών του άλμπουμ.   Η αφαίρεση του κεντρικού καναλιού της φωνής αλλάζει δραστικά την ακουστική εμπειρία. Χωρίς τη φυσική κάλυψη και τη συμπίεση των έντονων ερμηνειών του Bonnet, αποκαλύπτεται όλο το βάθος της στερεοφωνικής εικόνας: οι ρυθμικές κιθάρες, τα διακριτικά περάσματα στα πλήκτρα του Jimmy Waldo, το μπάσο του Gary Shea και, πρωτίστως, η απαράμιλλη τεχνική και η άρθρωση των neoclassical σόλο του 20χρονου τότε Yngwie J. Malmsteen. Στην αναλογική σου αλυσίδα, το LP 2 λειτουργεί πρακτικά ως ένας απομονωμένος οδηγός δεξιοτεχνίας, αναδεικνύοντας μικρολεπτομέρειες στην πένα και στη φυσική αντήχηση του ενισχυτή που στην αρχική μίξη παρέμεναν στο παρασκήνιο.</t>
+  </si>
+  <si>
+    <t>Εδώ το album ανεβάζει ταχύτητα. Ο τίτλος υποδηλώνει μηχανική κίνηση, αεροπορική ταχύτητα και έναν ανταγωνισμό που εξελίσσεται “jet to jet”. Το τραγούδι μεταφράζει αυτή την εικόνα σε fast melodic metal με sharp riffs, γρήγορο picking και κιθαριστικές στροφές που είναι πιο πολύπλοκες από ένα τυπικό speed-metal rocker. Ο Malmsteen χρησιμοποιεί νεοκλασικά runs και arpeggios, αλλά η σύνθεση κρατά ένα στιβαρό chorus και ο Bonnet δεν αφήνει την κιθάρα να γίνει αποκλειστικός πρωταγωνιστής. Είναι σημαντική early ένδειξη του τρόπου με τον οποίο το shred μπορούσε να ενσωματωθεί σε κανονικό heavy-rock τραγούδι αντί να λειτουργεί μόνο ως σόλο επίδειξη.</t>
+  </si>
+  <si>
+    <r>
+      <t>A4. Hiroshima Mon Amour:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το κορυφαίο τραγούδι του album και ίσως η πιο πλήρης συνάντηση του Graham Bonnet με τον νεαρό Yngwie Malmsteen. Ο τίτλος δανείζεται το όνομα από την ταινία του Alain Resnais, χρησιμοποιώντας το Hiroshima περισσότερο ως εικόνα μνήμης, τραύματος και αδυναμίας επικοινωνίας παρά ως απλή ιστορική αναφορά στην ατομική βόμβα. Η μουσική έχει σκούρο, απειλητικό riff, δυναμικά keyboards και χορταστική κιθάρα που κινείται ανάμεσα σε Blackmore-like μελωδικότητα και Malmsteen neoclassical πυροτεχνήματα. Ο Bonnet δίνει δραματική ερμηνεία που δεν χάνεται μέσα στην παραγωγή. Το κομμάτι έλαβε δεύτερο video και απέκτησε ιδιαίτερη δημοφιλία στην Ιαπωνία, ενώ αναφέρεται σταθερά ως ένα από τα κλασικά τραγούδια της μπάντας.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mid-tempo hard-metal track με τον Bigfoot ως μυθική, απειλητική και ελαφρώς παιχνιδιάρικη φιγούρα. Το βασικό του όπλο είναι το riff και όχι η περίτεχνη δραματουργία. Η μπάντα ακούγεται σφιχτή, ο Bonnet κρατά τη σύνθεση με την χαρακτηριστική του φωνή και ο Malmsteen πετά σωστά lead accents, αλλά το τραγούδι δεν έχει την άμεση ταυτότητα των δύο μεγάλων singles/standouts. Η θέση του μετά το “Too Young to Die…” είναι χρήσιμη, γιατί κατεβάζει ελαφρά την ταχύτητα και επιτρέπει στη B πλευρά να αλλάξει διάθεση, χωρίς όμως να σπάει την heavy-metal συνοχή της.</t>
+  </si>
+  <si>
+    <t>Το πιο AOR/keyboard-oriented τραγούδι της B πλευράς. Ο τίτλος δημιουργεί ένα αστικό, νυχτερινό σκηνικό, και η σύνθεση προτιμά μελωδική ανάπτυξη, γυαλισμένα keyboards και πιο χαμηλή κιθαριστική πίεση. Ο Bonnet είναι το κέντρο, με τη φωνή του να δίνει σε μια σχετικά conventional σύνθεση τη δραματική προσωπικότητα που χρειάζεται. Δεν είναι από τα πιο αναγνωρίσιμα Alcatrazz tracks, αλλά δείχνει τη σημαντική συμβολή του Jimmy Waldo και εξηγεί γιατί το group ήταν περισσότερο από “η πρώτη μπάντα του Malmsteen”. Λειτουργεί ως απαραίτητη μελωδική ανάσα πριν από το πιο σκοτεινό κλείσιμο.</t>
+  </si>
+  <si>
+    <t>Η φωνή του Bonnet στην κανονική εκδοχή είναι σημαντική για τη θεατρικότητα του τραγουδιού, αλλά το instrumental αποκαλύπτει ότι η σύνθεση έχει αρκετό βάθος από μόνη της. Τα heavy riffs, οι μελωδικές αλλαγές και το Blackmore-influenced lead playing λειτουργούν σαν dark guitar suite. Η απουσία στίχων αφήνει περισσότερο χώρο στη tension-and-release λογική των κιθάρων, ενώ τα keyboards δεν περιορίζονται πλέον σε υποστηρικτικό ρόλο. Δεν ξεπερνά τη vocal εκδοχή συναισθηματικά, αλλά λειτουργεί πολύ καλά ως εναλλακτική ακρόαση και ως ανατομία της κιθαριστικής ενορχήστρωσης.</t>
+  </si>
+  <si>
+    <t>Η instrumental version αναδεικνύει το πραγματικό βάρος του riff και των keyboards. Στην vocal εκδοχή, ο Bonnet δίνει έντονη θεατρικότητα· χωρίς τη φωνή, το τραγούδι αποκτά πιο μηχανική, σχεδόν soundtrack-like αίσθηση. Η κίνηση της κιθάρας και η rhythm βάση ακούγονται πιο καθαρά, ιδιαίτερα στα transitions, αλλά η απουσία του lead vocal μειώνει το στοιχείο άμεσης ταυτότητας. Παραμένει χρήσιμο και αρκετά ισχυρό ως bonus, γιατί αποκαλύπτει μια πιο σκοτεινή instrumental βάση από ό,τι αφήνει αρχικά να φανεί η standard version.</t>
+  </si>
+  <si>
+    <t>Εδώ η αφαίρεση της φωνής φανερώνει έναν riff-centric πυρήνα. Η κιθάρα του Malmsteen, το μπάσο και τα drums κρατούν το track σε mid-tempo heavy-rock έδαφος, όμως το κομμάτι χάνει περισσότερο από άλλα όταν απουσιάζει ο Bonnet, επειδή η αρχική του αξία εξαρτάται σημαντικά από το vocal personality και το refrain. Ως bonus είναι χρήσιμο για να δεις τις rhythm-guitar στρώσεις και τις μικρές lead παρεμβάσεις, αλλά δεν έχει το ίδιο αυθύπαρκτο ενδιαφέρον με τα instrumentals που γράφτηκαν εξαρχής ως κιθαριστικά showcases.</t>
+  </si>
+  <si>
+    <t>Στη vocal version, η πιασάρικη μελωδία και η παρουσία του Bonnet δίνουν το βασικό στίγμα. Χωρίς αυτά, προκύπτει ένα καθαρό melodic-rock backing track όπου οι κιθάρες και τα keyboards μοιράζονται ισότιμα τον χώρο. Η εκδοχή βοηθά να ακούσεις πόσο tight είναι το arrangement και πόσο προσεκτικά το soloing του Malmsteen ενσωματώνεται στις pop-metal αρμονίες. Δεν έχει την πλήρη συναισθηματική/εμπορική ολοκλήρωση της vocal εκδοχής, αλλά είναι ευχάριστη και επιβεβαιώνει ότι η σύνθεση είχε γερή μουσική βάση πριν προστεθούν τα lead vocals.</t>
+  </si>
+  <si>
+    <t>Το “Suffer Me” είναι δραματικό, σκοτεινό closing track που επαναφέρει το πιο απειλητικό ύφος της μπάντας. Ο τίτλος εκφράζει μια σχέση ή κατάσταση βασανισμού, πρόκλησης και παράδοσης, ενώ η μουσική αποφεύγει το εύκολο anthem finale. Τα riffs έχουν Blackmore-influenced βάρος, η φωνή του Bonnet είναι θεατρική και το soloing του Malmsteen αφήνεται να αναπτυχθεί με μεγαλύτερη υπομονή. Είναι σωστό κλείσιμο του original LP, επειδή συνδέει το hard rock, το neoclassical metal και το σκοτεινό dramatic element που διατρέχει όλο τον δίσκο.</t>
+  </si>
+  <si>
+    <t>Η εισαγωγή του album είναι η πιο άμεση και μελωδική πλευρά των Alcatrazz. Ο τίτλος φέρνει εικόνα απόδρασης, φωτός και ελευθερίας, αλλά η μουσική δεν είναι soft ή καλοκαιρινή pop, είναι καθαρό early-’80s melodic hard rock, με τραγανές κιθάρες, γυαλισμένα keyboards και chorus προσανατολισμένο στο radio/MTV κοινό. Ο Graham Bonnet τραγουδά με καθαρό, επιβλητικό και ελαφρώς theatrical ύφος, ενώ ο Malmsteen περιορίζει αρχικά την τεχνική επίδειξη και υπηρετεί τη μελωδία. Λειτουργεί σωστά ως opener και lead single, επειδή παρουσιάζει τη δυνατότητα της μπάντας να ενώσει την Rainbow παράδοση με την ανερχόμενη αμερικανική melodic-metal αισθητική. Το video του τραγουδιού έλαβε σημαντική MTV προβολή, βοηθώντας την πρώτη δημόσια εικόνα του νέου σχήματος.</t>
+  </si>
+  <si>
+    <t>Το “General Hospital” μειώνει τη φωτεινότητα του opener και περνά σε πιο πυκνό, σκληρό heavy-metal riffing. Ο τίτλος παραπέμπει σε χώρο κρίσης, φθοράς και ανθρώπινης πίεσης, όμως η σύνθεση δεν επιλέγει δραματικό slow tempo, κινείται με αποφασιστική κιθαριστική ένταση, σταθερό rhythm section και keyboards που ενισχύουν την ανησυχία. Ο Bonnet χρησιμοποιεί τη φωνή του πιο κοφτά και επιθετικά, ενώ ο Malmsteen αρχίζει να δείχνει πιο καθαρά τα νεοκλασικά licks και την ταχύτητα που θα γίνονταν σύντομα σήμα κατατεθέν του. Είναι καλό, πυκνό album track, αν και λιγότερο ευδιάκριτο ως μεμονωμένη σύνθεση από τα “Jet to Jet” και “Hiroshima Mon Amour”.</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental που ανοίγει χώρο για τον Malmsteen χωρίς να χρειάζεται να στηριχθεί σε συμβατικό verse/chorus. Ο παράξενος, φανταστικός τίτλος ταιριάζει με το pseudo-mythic ύφος της μουσικής, νεοκλασικές κλίμακες, baroque χρώματα, γρήγορες αρπίσεις και κιθαριστικές αναδιπλώσεις. Δεν έχει την πλήρη ανάπτυξη του “Incubus”, όμως υπηρετεί σωστά τη ροή της A πλευράς, μετά τη δραματική πλήρωση του “Hiroshima Mon Amour”, δίνει μια πιο καθαρή, σύντομη guitar-centric εκτόνωση. Είναι δείγμα της μουσικής γλώσσας που θα αναπτύξει ο Malmsteen στο Rising Force, σε πιο συμπυκνωμένη μορφή.</t>
+  </si>
+  <si>
+    <t>Το δεύτερο instrumental είναι πιο ολοκληρωμένο και περισσότερο καθοριστικό για την ιστορική θέση του album. Ο “incubus” είναι δαιμονική, εφιαλτική μορφή, και η μουσική χτίζει σκοτεινή νεοκλασική ατμόσφαιρα πριν οδηγηθεί σε γρήγορο picking, arpeggios και ηλεκτρικές κλιμακώσεις. Η τεχνική του Malmsteen δεν είναι ακόμη πλήρως “Yngwie formula” όπως θα ακουστεί στα σόλο albums του, αλλά η βασική του ταυτότητα είναι ήδη απολύτως καθαρή, Bach/Paganini αρμονίες, Ritchie Blackmore βάρος, βιρτουοζική ταχύτητα και dramatic phrasing. Το κομμάτι λειτουργεί ως πρόλογος του νεοκλασικού metal που θα άνθιζε στα μέσα της δεκαετίας.</t>
+  </si>
+  <si>
+    <t>Από τα πιο άμεσα, γρήγορα και memorable κομμάτια του δίσκου. Ο τίτλος κινείται στη rock ’n’ roll υπερβολή, ένας ήρωας ζει τόσο γρήγορα, ώστε είναι «πολύ νέος για να πεθάνει και πολύ μεθυσμένος για να ζήσει». Ο Bonnet δίνει ένα μεγάλο, σχεδόν απειλητικό chorus, η μπάντα παίζει με compact ένταση και ο Malmsteen προσθέτει δεξιοτεχνία χωρίς να θυσιάζει το hook. Είναι από τα τραγούδια που απέκτησαν διαχρονική θέση στον κατάλογο των Alcatrazz και συνέχισαν να λειτουργούν σε live context, επειδή η δομή του είναι πιο άμεση από τα fantasy/occult cuts. Οι αναδρομικές λίστες καλύτερων τραγουδιών των Alcatrazz το ξεχωρίζουν σταθερά.</t>
+  </si>
+  <si>
+    <t>Εφόσον η αρχική εκδοχή του “Kree Nakoorie” είναι ήδη instrumental, εδώ δεν ακούμε απλώς “τραγούδι χωρίς φωνή”, αλλά μια δεύτερη παρουσίαση/μίξη του κιθαριστικού υλικού. Η αξία της βρίσκεται στη δυνατότητα να απομονώσεις τις λεπτομέρειες, πώς οι κιθάρες του Malmsteen κάνουν call-and-response με τα keyboards και πώς το rhythm section κρατά τις αλλαγές χωρίς να ακούγεται άκαμπτο. Ως δεύτερη εκδοχή δεν διαθέτει την έκπληξη της original A5 θέσης, όμως είναι σημαντική για τη συγκεκριμένη deluxe έκδοση, επειδή επιβεβαιώνει τον αναλυτικό χαρακτήρα της δεύτερης LP.</t>
+  </si>
+  <si>
+    <t>Η αφαίρεση της φωνής του Bonnet μετατοπίζει την προσοχή από τη μελωδία στη δομή. Τα keyboards του Waldo, το μπάσο του Gary Shea και οι κιθαριστικές υποστηρικτικές γραμμές αποκαλύπτουν ένα πιο προσεγμένο AOR arrangement απ’ όσο φαίνεται στην vocal version. Ταυτόχρονα, γίνεται σαφές πόσο κεντρικός είναι ο Bonnet στο να δίνει δραματική ταυτότητα στο κομμάτι, χωρίς τη φωνή του, το track είναι καλοφτιαγμένο αλλά λιγότερο ξεχωριστό. Γι’ αυτό η instrumental εκδοχή έχει ελαφρώς χαμηλότερη ανεξάρτητη βαθμολογία, χωρίς να χάνει την αξία της ως ακουστικό “x-ray” του arrangement.</t>
+  </si>
+  <si>
+    <t>Όπως και το “Kree Nakoorie”, το “Incubus” ήταν ήδη instrumental στο original album, άρα εδώ η δεύτερη παρουσίαση έχει κυρίως συλλεκτική και συγκριτική αξία. Η σύνθεση διατηρεί το νεοκλασικό της impact, σκοτεινή εισαγωγή, κιθαριστικές κλιμακώσεις, γρήγορα runs και δραματικά pauses. Αν η συγκεκριμένη version παρουσιάζει διαφορετική μίξη ή καθαρότερο separation, τότε η αξία της είναι ιδιαίτερα υψηλή για τον συλλέκτη και για όποιον θέλει να μελετήσει τον Malmsteen πριν από τη σόλο περίοδο. Ως αυτόνομη επανάληψη, όμως, δεν υπερβαίνει το original B1, επειδή η αρχική θέση του μέσα στο LP έχει μεγαλύτερη δραματική δύναμη.</t>
+  </si>
+  <si>
+    <t>Η instrumental εκδοχή κρατά την ταχύτητα, το riff και το high-energy momentum του original, όμως το μεγάλο chorus του Bonnet είναι μέρος του λόγου που η βασική version είναι τόσο αξέχαστη. Χωρίς φωνή, το track μετατρέπεται σε δυνατό speed/melodic-metal workout, τα rhythm guitars, οι αλλαγές και τα lead fills του Malmsteen ακούγονται με εντυπωσιακή καθαρότητα. Είναι από τα πιο απολαυστικά instrumentals του πακέτου, γιατί η σύνθεση έχει γερή ρυθμική βάση, αλλά παραμένει λίγο χαμηλότερα από την vocal version, όπου το riff και η φωνή συνδυάζονται σε πραγματικό anthem.</t>
+  </si>
+  <si>
+    <t>Το κλείσιμο του instrumental LP είναι εύστοχο, επειδή το “Jet to Jet” διαθέτει ήδη γρήγορη, μηχανική και κιθαριστικά σύνθετη ενέργεια. Χωρίς τη φωνή, η σύνθεση μοιάζει περισσότερο με pure neoclassical speed-metal exercise, γρήγορες γραμμές, ακριβές rhythm section και κιθάρα που αλλάζει από riffing σε runs με μεγάλη ευκολία. Το bonus track αποκαλύπτει την τεχνική αρχιτεκτονική του τραγουδιού και κλείνει τον companion δίσκο με ορμή. Η vocal version παραμένει ελαφρώς ανώτερη ως ολοκληρωμένο τραγούδι, αλλά η instrumental παραλλαγή είναι δικαιολογημένα υψηλής αξίας για αυτή την έκδοση.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C5. Hiroshima Mon Amour (Instrumental): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Μία από τις ισχυρότερες instrumental versions του δεύτερου δίσκου. Χωρίς vocals, το σκοτεινό staccato riff, η keyboard ατμόσφαιρα και το guitar phrasing του Malmsteen έρχονται στο προσκήνιο, κάνοντας το τραγούδι να μοιάζει ακόμη περισσότερο με σκοτεινή κινηματογραφική σύνθεση. Χάνει μέρος από την ανθρώπινη δραματικότητα που φέρνει ο Bonnet, αλλά κερδίζει σε tension και λεπτομέρεια ενορχήστρωσης. Είναι ουσιαστικό bonus, όχι απλή karaoke παραλλαγή, και δικαιολογεί το υψηλό score του companion LP.</t>
     </r>
   </si>
 </sst>
@@ -16579,7 +16802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -17874,7 +18097,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>18813646</v>
       </c>
@@ -17970,7 +18193,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>34571488</v>
       </c>
@@ -18130,7 +18353,7 @@
         <v>4596</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="123.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>27342894</v>
       </c>
@@ -21006,6 +21229,38 @@
       </c>
       <c r="J138" s="7" t="s">
         <v>3050</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>4840</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>4839</v>
+      </c>
+      <c r="D139" s="3">
+        <v>1983</v>
+      </c>
+      <c r="E139" s="5">
+        <v>3.51</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>4838</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>4844</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>4841</v>
+      </c>
+      <c r="I139" s="7" t="s">
+        <v>4842</v>
+      </c>
+      <c r="J139" s="7" t="s">
+        <v>4843</v>
       </c>
     </row>
   </sheetData>
@@ -21285,6 +21540,8 @@
     <hyperlink ref="J18" r:id="rId269" xr:uid="{D57BF95E-7B0F-40EF-9E3A-010F0E80480A}"/>
     <hyperlink ref="I113" r:id="rId270" xr:uid="{DECA6A92-1D33-42D7-B77F-7AF5137B58FA}"/>
     <hyperlink ref="J113" r:id="rId271" xr:uid="{413366AD-81D0-45B9-BF11-46059D16B4E3}"/>
+    <hyperlink ref="I139" r:id="rId272" xr:uid="{25163CEA-A1CA-4E58-B675-5A40A81FF185}"/>
+    <hyperlink ref="J139" r:id="rId273" xr:uid="{4888C6D4-A7FB-411F-BA80-D47FC1727FFC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21292,7 +21549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1341"/>
+  <dimension ref="A1:I1361"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -57784,6 +58041,508 @@
         <v>173</v>
       </c>
     </row>
+    <row r="1342" spans="1:9" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A1342" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1342" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1342" s="4" t="s">
+        <v>4798</v>
+      </c>
+      <c r="D1342" s="6" t="s">
+        <v>4818</v>
+      </c>
+      <c r="E1342" s="14"/>
+      <c r="F1342" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1342" s="31">
+        <v>4</v>
+      </c>
+      <c r="H1342" s="6" t="s">
+        <v>4854</v>
+      </c>
+      <c r="I1342" s="3"/>
+    </row>
+    <row r="1343" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1343" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1343" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1343" s="4" t="s">
+        <v>4799</v>
+      </c>
+      <c r="D1343" s="6" t="s">
+        <v>4819</v>
+      </c>
+      <c r="E1343" s="14"/>
+      <c r="F1343" s="31">
+        <v>4</v>
+      </c>
+      <c r="G1343" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="H1343" s="6" t="s">
+        <v>4855</v>
+      </c>
+      <c r="I1343" s="3"/>
+    </row>
+    <row r="1344" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1344" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1344" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1344" s="4" t="s">
+        <v>4800</v>
+      </c>
+      <c r="D1344" s="6" t="s">
+        <v>4820</v>
+      </c>
+      <c r="E1344" s="14"/>
+      <c r="F1344" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1344" s="31">
+        <v>3.8</v>
+      </c>
+      <c r="H1344" s="6" t="s">
+        <v>4845</v>
+      </c>
+      <c r="I1344" s="3"/>
+    </row>
+    <row r="1345" spans="1:9" ht="101.25" x14ac:dyDescent="0.25">
+      <c r="A1345" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1345" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1345" s="4" t="s">
+        <v>4801</v>
+      </c>
+      <c r="D1345" s="6" t="s">
+        <v>4821</v>
+      </c>
+      <c r="E1345" s="14"/>
+      <c r="F1345" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="G1345" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1345" s="17" t="s">
+        <v>4846</v>
+      </c>
+      <c r="I1345" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1346" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1346" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1346" s="4" t="s">
+        <v>4802</v>
+      </c>
+      <c r="D1346" s="6" t="s">
+        <v>4822</v>
+      </c>
+      <c r="E1346" s="14"/>
+      <c r="F1346" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1346" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1346" s="6" t="s">
+        <v>4856</v>
+      </c>
+      <c r="I1346" s="3"/>
+    </row>
+    <row r="1347" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1347" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1347" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1347" s="4" t="s">
+        <v>4803</v>
+      </c>
+      <c r="D1347" s="6" t="s">
+        <v>4823</v>
+      </c>
+      <c r="E1347" s="14"/>
+      <c r="F1347" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="G1347" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="H1347" s="6" t="s">
+        <v>4857</v>
+      </c>
+      <c r="I1347" s="3"/>
+    </row>
+    <row r="1348" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1348" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1348" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1348" s="4" t="s">
+        <v>4804</v>
+      </c>
+      <c r="D1348" s="6" t="s">
+        <v>4824</v>
+      </c>
+      <c r="E1348" s="14"/>
+      <c r="F1348" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="G1348" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="H1348" s="6" t="s">
+        <v>4858</v>
+      </c>
+      <c r="I1348" s="3"/>
+    </row>
+    <row r="1349" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1349" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1349" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1349" s="4" t="s">
+        <v>4805</v>
+      </c>
+      <c r="D1349" s="6" t="s">
+        <v>4825</v>
+      </c>
+      <c r="E1349" s="14"/>
+      <c r="F1349" s="31">
+        <v>3.8</v>
+      </c>
+      <c r="G1349" s="31">
+        <v>3.8</v>
+      </c>
+      <c r="H1349" s="6" t="s">
+        <v>4847</v>
+      </c>
+      <c r="I1349" s="3"/>
+    </row>
+    <row r="1350" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1350" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1350" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1350" s="4" t="s">
+        <v>4806</v>
+      </c>
+      <c r="D1350" s="6" t="s">
+        <v>4826</v>
+      </c>
+      <c r="E1350" s="14"/>
+      <c r="F1350" s="31">
+        <v>3.8</v>
+      </c>
+      <c r="G1350" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="H1350" s="6" t="s">
+        <v>4848</v>
+      </c>
+      <c r="I1350" s="3"/>
+    </row>
+    <row r="1351" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1351" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1351" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1351" s="4" t="s">
+        <v>4807</v>
+      </c>
+      <c r="D1351" s="6" t="s">
+        <v>4827</v>
+      </c>
+      <c r="E1351" s="14"/>
+      <c r="F1351" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1351" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="H1351" s="6" t="s">
+        <v>4853</v>
+      </c>
+      <c r="I1351" s="3"/>
+    </row>
+    <row r="1352" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1352" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1352" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1352" s="4" t="s">
+        <v>4808</v>
+      </c>
+      <c r="D1352" s="6" t="s">
+        <v>4828</v>
+      </c>
+      <c r="E1352" s="14"/>
+      <c r="F1352" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1352" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="H1352" s="6" t="s">
+        <v>4859</v>
+      </c>
+      <c r="I1352" s="3"/>
+    </row>
+    <row r="1353" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1353" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1353" s="3">
+        <v>12</v>
+      </c>
+      <c r="C1353" s="4" t="s">
+        <v>4809</v>
+      </c>
+      <c r="D1353" s="6" t="s">
+        <v>4829</v>
+      </c>
+      <c r="E1353" s="14"/>
+      <c r="F1353" s="31">
+        <v>3.7</v>
+      </c>
+      <c r="G1353" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1353" s="6" t="s">
+        <v>4860</v>
+      </c>
+      <c r="I1353" s="3"/>
+    </row>
+    <row r="1354" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1354" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1354" s="3">
+        <v>13</v>
+      </c>
+      <c r="C1354" s="4" t="s">
+        <v>4810</v>
+      </c>
+      <c r="D1354" s="6" t="s">
+        <v>4830</v>
+      </c>
+      <c r="E1354" s="14"/>
+      <c r="F1354" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="G1354" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="H1354" s="6" t="s">
+        <v>4852</v>
+      </c>
+      <c r="I1354" s="3"/>
+    </row>
+    <row r="1355" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1355" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1355" s="3">
+        <v>14</v>
+      </c>
+      <c r="C1355" s="4" t="s">
+        <v>4811</v>
+      </c>
+      <c r="D1355" s="6" t="s">
+        <v>4831</v>
+      </c>
+      <c r="E1355" s="14"/>
+      <c r="F1355" s="31">
+        <v>3.5</v>
+      </c>
+      <c r="G1355" s="31">
+        <v>4</v>
+      </c>
+      <c r="H1355" s="6" t="s">
+        <v>4851</v>
+      </c>
+      <c r="I1355" s="3"/>
+    </row>
+    <row r="1356" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1356" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1356" s="3">
+        <v>15</v>
+      </c>
+      <c r="C1356" s="4" t="s">
+        <v>4812</v>
+      </c>
+      <c r="D1356" s="6" t="s">
+        <v>4832</v>
+      </c>
+      <c r="E1356" s="14"/>
+      <c r="F1356" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="G1356" s="31">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1356" s="17" t="s">
+        <v>4864</v>
+      </c>
+      <c r="I1356" s="3"/>
+    </row>
+    <row r="1357" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1357" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1357" s="3">
+        <v>16</v>
+      </c>
+      <c r="C1357" s="4" t="s">
+        <v>4813</v>
+      </c>
+      <c r="D1357" s="6" t="s">
+        <v>4833</v>
+      </c>
+      <c r="E1357" s="14"/>
+      <c r="F1357" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="G1357" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1357" s="6" t="s">
+        <v>4850</v>
+      </c>
+      <c r="I1357" s="3"/>
+    </row>
+    <row r="1358" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1358" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1358" s="3">
+        <v>17</v>
+      </c>
+      <c r="C1358" s="4" t="s">
+        <v>4814</v>
+      </c>
+      <c r="D1358" s="6" t="s">
+        <v>4834</v>
+      </c>
+      <c r="E1358" s="14"/>
+      <c r="F1358" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1358" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="H1358" s="6" t="s">
+        <v>4861</v>
+      </c>
+      <c r="I1358" s="3"/>
+    </row>
+    <row r="1359" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1359" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1359" s="3">
+        <v>18</v>
+      </c>
+      <c r="C1359" s="4" t="s">
+        <v>4815</v>
+      </c>
+      <c r="D1359" s="6" t="s">
+        <v>4835</v>
+      </c>
+      <c r="E1359" s="14"/>
+      <c r="F1359" s="31">
+        <v>4</v>
+      </c>
+      <c r="G1359" s="31">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H1359" s="6" t="s">
+        <v>4849</v>
+      </c>
+      <c r="I1359" s="3"/>
+    </row>
+    <row r="1360" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1360" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1360" s="3">
+        <v>19</v>
+      </c>
+      <c r="C1360" s="4" t="s">
+        <v>4816</v>
+      </c>
+      <c r="D1360" s="6" t="s">
+        <v>4836</v>
+      </c>
+      <c r="E1360" s="14"/>
+      <c r="F1360" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1360" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1360" s="6" t="s">
+        <v>4862</v>
+      </c>
+      <c r="I1360" s="3"/>
+    </row>
+    <row r="1361" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1361" s="3">
+        <v>37070553</v>
+      </c>
+      <c r="B1361" s="3">
+        <v>20</v>
+      </c>
+      <c r="C1361" s="4" t="s">
+        <v>4817</v>
+      </c>
+      <c r="D1361" s="6" t="s">
+        <v>4837</v>
+      </c>
+      <c r="E1361" s="14"/>
+      <c r="F1361" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G1361" s="31">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H1361" s="6" t="s">
+        <v>4863</v>
+      </c>
+      <c r="I1361" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4A0FF6-5F26-4179-81B3-9072D68D3162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F5F14C-E978-421C-AE15-8E480AC0F7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5250" uniqueCount="4865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5285" uniqueCount="4897">
   <si>
     <t>No</t>
   </si>
@@ -16204,6 +16204,113 @@
         <charset val="161"/>
       </rPr>
       <t>Μία από τις ισχυρότερες instrumental versions του δεύτερου δίσκου. Χωρίς vocals, το σκοτεινό staccato riff, η keyboard ατμόσφαιρα και το guitar phrasing του Malmsteen έρχονται στο προσκήνιο, κάνοντας το τραγούδι να μοιάζει ακόμη περισσότερο με σκοτεινή κινηματογραφική σύνθεση. Χάνει μέρος από την ανθρώπινη δραματικότητα που φέρνει ο Bonnet, αλλά κερδίζει σε tension και λεπτομέρεια ενορχήστρωσης. Είναι ουσιαστικό bonus, όχι απλή karaoke παραλλαγή, και δικαιολογεί το υψηλό score του companion LP.</t>
+    </r>
+  </si>
+  <si>
+    <t>In City Dreams</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/Gp5uoaDzwPVOMqFbCaB6in1k1vCbBQXy1YWtmibBkho/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE2OTk1/MjctMTI3NTU0OTU3/My5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1699527-Robin-Trower-In-City-Dreams</t>
+  </si>
+  <si>
+    <t>Chrysalis – CHR 1148. Βρετανική έκδοση (UK) που κυκλοφόρησε στις 30 Σεπτεμβρίου 1977. Το άλμπουμ ηχογραφήθηκε στα Criteria Recording Studios στο Μαϊάμι και η κοπή της λάκας (lacquer cut) έγινε στα Ardent Mastering από τον L. Nix.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το In City Dreams (Σεπτέμβριος 1977) αποτελεί τον πέμπτο προσωπικό δίσκο του Robin Trower και σημείο ουσιαστικής στυλιστικής στροφής στην πορεία του. Μετά τους καταιγιστικούς, έντονα ψυχεδελικούς και βαρείς ήχους του Bridge of Sighs, ο Trower επέλεξε να ενσωματώσει βαθιές funk και R&amp;B επιρροές. Η κομβική αλλαγή ήταν η προσθήκη του μπασίστα Rustee Allen (προερχόμενου από τους Sly &amp; the Family Stone), γεγονός που επέτρεψε στον James Dewar να επικεντρωθεί αποκλειστικά στα εκπληκτικά, γεμάτα soul και βάθος φωνητικά του. Η παραγωγή ανατέθηκε στον Don Davis (γνωστό από τις soul παραγωγές της Stax Records) και οι ηχογραφήσεις πραγματοποιήθηκαν στα ιστορικά Criteria Recording Studios στο Μαϊάμι από τους Alex Sadkin και Don Gehman. Ο ήχος απέκτησε μοναδικό groove, ευρυχωρία και εξαιρετικό dynamic range: η Fender Stratocaster του Trower, συνδεδεμένη με τα κλασικά Uni-Vibe, fuzz και wah-wah πετάλια, διατηρεί τον αναγνωρίσιμο "υγρό" και ατμοσφαιρικό της τόνο, αλλά πλέον πατά πάνω σε ένα εξαιρετικά σφιχτό, funky ρυθμικό section. Στιχουργικά, το άλμπουμ κινείται σε πιο γήινα μονοπάτια, αστική απομόνωση, ερωτική προσμονή, μελαγχολία και συναισθηματική λύτρωση.</t>
+  </si>
+  <si>
+    <t>Somebody Calling</t>
+  </si>
+  <si>
+    <t>Sweet Wine Of Love</t>
+  </si>
+  <si>
+    <t>Bluebird</t>
+  </si>
+  <si>
+    <t>Falling Star</t>
+  </si>
+  <si>
+    <t>Farther On Up The Road</t>
+  </si>
+  <si>
+    <t>Smile</t>
+  </si>
+  <si>
+    <t>Little Girl</t>
+  </si>
+  <si>
+    <t>Love’s Gonna Bring You Round</t>
+  </si>
+  <si>
+    <t>Blues Rock, Funk Rock [Soulful Blues Rock, Funky Bass Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Melodic Blues Rock, Soulful Rock, Guitar-led Pop Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock [Dreamy Blues Rock, Psychedelic Soul, Guitar Atmosphere]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Compact Guitar Rock, Melodic Blues, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, R&amp;B [Electric Blues, Blues Standard, Raucous Barroom Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Slow Blues, Soul Ballad, Expressive Guitar Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Heavy Blues Rock, Guitar Jam, Psychedelic Rock]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Soul Rock [Soulful Blues Rock, Mid-tempo Rock, Guitar-led Song]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Psychedelic Rock [Atmospheric Blues Rock, Urban Psychedelia, Guitar Epic]</t>
+  </si>
+  <si>
+    <t>Blues Rock, Hard Rock [Psychedelic Blues Rock, Soul Rock, Funk Rock, Classic Rock]</t>
+  </si>
+  <si>
+    <t>Mid-tempo soul-inflected blues rock για την αναπόφευκτη δύναμη της αγάπης να σε αλλάξει, να σε γυρίσει πίσω ή να σε αναγκάσει να δεις κάτι που απέφευγες. Η ερμηνεία του Dewar είναι ζεστή και πειστική, ενώ η κιθάρα του Trower δουλεύει με λιγότερο distortion και περισσότερες μικρές μελωδικές απαντήσεις. Δεν είναι τόσο άμεσο όσο “Somebody Calling” ούτε τόσο ατμοσφαιρικό όσο “Bluebird”, αλλά είναι συνεπές με τον πιο soulful, τραγουδοκεντρικό προσανατολισμό του δίσκου. Λειτουργεί καλά στη ροή του LP, παρότι ως αυτόνομο τραγούδι είναι λιγότερο διακριτό.</t>
+  </si>
+  <si>
+    <t>Σύντομο, πιο compact guitar-rock τραγούδι. Το “falling star” μπορεί να είναι χαμένη ευχή, πρόσωπο που καίγεται γρήγορα ή μια απρόσμενη πτώση από την λάμψη στην πραγματικότητα. Η μουσική διατηρεί το blues-rock χρώμα, αλλά δεν έχει την ατμοσφαιρική ανάπτυξη του “Bluebird” ούτε το αβίαστο hook του “Sweet Wine of Love”. Ο Trower παίζει σωστά και ο Dewar κρατά τη μελωδία, αλλά το track λειτουργεί περισσότερο ως σύντομη γέφυρα προς την blues cover που ακολουθεί. Η βαθμολογία του αντικατοπτρίζει ένα καλό, ευχάριστο album cut που όμως δεν είναι από τους πυλώνες του δίσκου.</t>
+  </si>
+  <si>
+    <t>Το πιο αέρινο και ονειρικό τραγούδι της A πλευράς. Το bluebird λειτουργεί ως σύμβολο καρδιάς, ελπίδας, φυσικής ελευθερίας ή μιας ήρεμης εσωτερικής φωνής που προσπαθεί να ακουστεί. Η κιθάρα του Trower δεν επιτίθεται· αιωρείται, με sustain, wah-tinged χρώματα και πιο ρευστή phrasing. Ο Dewar τραγουδά με soulfulness, όμως το τραγούδι κρατά psychedelic haze, κάνοντάς το περισσότερο από απλή soft-rock μπαλάντα. Η σύνθεση αποκαλύπτει τη δύναμη του album όταν συνδέει μελωδική οικονομία με την ατμοσφαιρική πλευρά του Trower. Παρότι ένας κριτικός θεώρησε τους στίχους υπερβολικά “hippy-dippy”, άλλες αναδρομικές πηγές το αναφέρουν ρητά ανάμεσα στα καλύτερα τραγούδια του album.</t>
+  </si>
+  <si>
+    <t>Πιο σύντομο και πιο άμεσο melodic blues-rock τραγούδι. Το “γλυκό κρασί της αγάπης” είναι παραδοσιακή blues/rock μεταφορά για έλξη, μέθη και συναισθηματική παράδοση. Η σύνθεση στηρίζεται σε hummable μελωδία και ένα φωτεινό, uplifting guitar solo, με τον Dewar να τραγουδά με ζεστή soul χροιά. Ο Trower προτιμά καθαρές, τραγουδιστές φράσεις αντί για μεγάλη ψυχεδελική περιπλάνηση. Αυτή ακριβώς η επιλογή εξηγεί γιατί ο δίσκος διαβάζεται ως προσπάθεια μεγαλύτερης προσβασιμότητας, έχει single-like concision, χωρίς όμως να αποκόπτεται από το blues-rock core. Κριτικές το ξεχωρίζουν ως ιδιαίτερα εύστοχο και μελωδικό cut, παρότι άλλες το θεωρούν υπερβολικά AOR-leaning.</t>
+  </si>
+  <si>
+    <t>Η εκδοχή του Trower στο blues standard των Don Robey και Joe Veasey επαναφέρει τη μπάντα σε πιο γήινο electric-blues έδαφος. Το τραγούδι έχει ισχυρή ιστορία μέσα από τον Bobby Bland και πολλούς άλλους ερμηνευτές, και οι Trower/Dewar δεν προσπαθούν να το μετατρέψουν σε ριζική επανεγγραφή· το παίζουν με ένταση, rough groove και “raucous” κιθάρα. Η φωνή του Dewar ταιριάζει ιδιαίτερα στο υλικό, ενώ ο Trower αξιοποιεί την πιο άμεση δομή για να βγάλει blues phrasing και distorted attack. Το αποτέλεσμα είναι σύντομο, δυναμικό και σωστά τοποθετημένο ως A-side closer, θυμίζει ότι κάτω από το soul/funk polish του 1977, το group παραμένει blues-rock power trio στην καρδιά του.</t>
+  </si>
+  <si>
+    <t>Η B πλευρά ανοίγει με slow blues/soul ballad. Ένας τίτλος τόσο απλός όσο το “Smile” συχνά καλύπτει πιο σύνθετη συναισθηματική κατάσταση, χαμόγελο ως ελπίδα, άμυνα ή προσπάθεια να επιβιώσεις μετά από απώλεια. Η σύνθεση αφήνει χώρο στον Dewar να δώσει μια εκφραστική, ευάλωτη ερμηνεία, ενώ ο Trower απαντά με μελωδικές, υπομονετικές κιθαριστικές γραμμές. Δεν κυνηγά την αμεσότητα ενός single, αλλά χτίζει σταδιακά mood. Είναι από τα πιο ώριμα κομμάτια του δίσκου, γιατί δείχνει τον κιθαρίστα να υπηρετεί το τραγούδι και όχι μόνο την προσωπική του tone/solo αισθητική.</t>
+  </si>
+  <si>
+    <t>Το “Little Girl” επιστρέφει σε βαρύτερο, πιο electric blues-rock territory. Ο τίτλος χρησιμοποιεί κλασικό blues idiom, όμως η μουσική δεν παίζει σαν retro revival, τα heavy riffs, το thick guitar tone και το driving rhythm section το μετατρέπουν σε psychedelic hard-rock statement. Ο Trower επιτρέπει στην κιθάρα να κινηθεί πιο ελεύθερα, με extended lines και bends που φέρνουν στο νου Hendrix, αλλά η μπάντα παραμένει συμπαγής. Είναι από τα καλύτερα tracks για όποιον θέλει την πιο αναγνωρίσιμη, guitar-dominant πλευρά του Trower και δίνει στη B πλευρά την απαραίτητη ένταση πριν την επιστροφή σε πιο soulful songwriting.</t>
+  </si>
+  <si>
+    <t>Το title track κλείνει τον δίσκο με την πιο ατμοσφαιρική, αστική και ψυχεδελική του στιγμή. Τα “city dreams” είναι όνειρα διαμορφωμένα από τη νυχτερινή πόλη, επιθυμία, απομόνωση, θόρυβος, φώτα και φαντασία. Ο Trower αφήνει την κιθάρα να αναπνεύσει, με πιο αργή ανάπτυξη, thick tone και φράσεις που χτίζουν εικόνα αντί να προσπαθούν να αποδείξουν τεχνική υπεροχή. Ο Dewar δίνει μελαγχολικό και soulful κέντρο, ενώ το rhythm section διατηρεί μια υποβόσκουσα κίνηση. Είναι το τραγούδι που συνδέει καλύτερα την κλασική ψυχεδελική blues-rock εποχή του Trower με τη μελωδική/σoul ανανέωση του album. Είναι δικαιολογημένα από τα καλύτερα cuts του δίσκου και πολύ σωστό finale.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A1. Somebody Calling: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Το album ανοίγει με groove που δείχνει αμέσως την αλλαγή της ρυθμικής βάσης. Ο Rustee Allen, με funk/soul background, δίνει στο μπάσο μεγαλύτερη κινητικότητα και punch, ενώ ο Trower τοποθετεί τις κιθαριστικές φράσεις του πάνω σε πιο party-oriented αλλά ακόμη bluesy θεμέλιο. Ο τίτλος υποδηλώνει κάλεσμα , ερωτικό, πνευματικό ή υπαρξιακό , και η φωνή του James Dewar μεταφέρει σωστά την αίσθηση ότι ο αφηγητής ακούει κάτι να τον τραβά. Η σύνθεση θυμίζει Bad Company-style soul shuffle, αλλά το heavily distorted lead guitar του Trower διατηρεί τη δική του αναγνωρίσιμη σφραγίδα. Είναι ιδανικό opener, ευθύ, δυναμικό και πιο εξωστρεφές από την προηγούμενη περίοδο του κιθαρίστα.</t>
     </r>
   </si>
 </sst>
@@ -16802,7 +16909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -21261,6 +21368,38 @@
       </c>
       <c r="J139" s="7" t="s">
         <v>4843</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>4283</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>4865</v>
+      </c>
+      <c r="D140" s="3">
+        <v>1977</v>
+      </c>
+      <c r="E140" s="5">
+        <v>3.42</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>4887</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>4869</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>4868</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>4867</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>4866</v>
       </c>
     </row>
   </sheetData>
@@ -21542,6 +21681,8 @@
     <hyperlink ref="J113" r:id="rId271" xr:uid="{413366AD-81D0-45B9-BF11-46059D16B4E3}"/>
     <hyperlink ref="I139" r:id="rId272" xr:uid="{25163CEA-A1CA-4E58-B675-5A40A81FF185}"/>
     <hyperlink ref="J139" r:id="rId273" xr:uid="{4888C6D4-A7FB-411F-BA80-D47FC1727FFC}"/>
+    <hyperlink ref="J140" r:id="rId274" xr:uid="{438627CB-F3D7-40D2-BBF9-0F4017DD4A26}"/>
+    <hyperlink ref="I140" r:id="rId275" xr:uid="{92585BDD-A39F-4248-A81B-9B81A5D7DCBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21549,7 +21690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1361"/>
+  <dimension ref="A1:I1370"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="9" customWidth="1"/>
@@ -58543,6 +58684,251 @@
       </c>
       <c r="I1361" s="3"/>
     </row>
+    <row r="1362" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1362" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1362" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1362" s="4" t="s">
+        <v>4870</v>
+      </c>
+      <c r="D1362" s="6" t="s">
+        <v>4878</v>
+      </c>
+      <c r="E1362" s="14">
+        <v>3.52</v>
+      </c>
+      <c r="F1362" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1362" s="31">
+        <v>4.7</v>
+      </c>
+      <c r="H1362" s="17" t="s">
+        <v>4896</v>
+      </c>
+      <c r="I1362" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1363" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1363" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1363" s="4" t="s">
+        <v>4871</v>
+      </c>
+      <c r="D1363" s="6" t="s">
+        <v>4879</v>
+      </c>
+      <c r="E1363" s="14">
+        <v>3.43</v>
+      </c>
+      <c r="F1363" s="31">
+        <v>4</v>
+      </c>
+      <c r="G1363" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="H1363" s="6" t="s">
+        <v>4891</v>
+      </c>
+      <c r="I1363" s="3"/>
+    </row>
+    <row r="1364" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1364" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1364" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1364" s="4" t="s">
+        <v>4872</v>
+      </c>
+      <c r="D1364" s="6" t="s">
+        <v>4880</v>
+      </c>
+      <c r="E1364" s="14">
+        <v>3.55</v>
+      </c>
+      <c r="F1364" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1364" s="31">
+        <v>4.8</v>
+      </c>
+      <c r="H1364" s="6" t="s">
+        <v>4890</v>
+      </c>
+      <c r="I1364" s="3"/>
+    </row>
+    <row r="1365" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1365" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1365" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1365" s="4" t="s">
+        <v>4873</v>
+      </c>
+      <c r="D1365" s="6" t="s">
+        <v>4881</v>
+      </c>
+      <c r="E1365" s="14">
+        <v>3.33</v>
+      </c>
+      <c r="F1365" s="31">
+        <v>3.8</v>
+      </c>
+      <c r="G1365" s="31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1365" s="6" t="s">
+        <v>4889</v>
+      </c>
+      <c r="I1365" s="3"/>
+    </row>
+    <row r="1366" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1366" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1366" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1366" s="4" t="s">
+        <v>4874</v>
+      </c>
+      <c r="D1366" s="6" t="s">
+        <v>4882</v>
+      </c>
+      <c r="E1366" s="14">
+        <v>3.33</v>
+      </c>
+      <c r="F1366" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="G1366" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="H1366" s="6" t="s">
+        <v>4892</v>
+      </c>
+      <c r="I1366" s="3"/>
+    </row>
+    <row r="1367" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1367" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1367" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1367" s="4" t="s">
+        <v>4875</v>
+      </c>
+      <c r="D1367" s="6" t="s">
+        <v>4883</v>
+      </c>
+      <c r="E1367" s="14">
+        <v>3.38</v>
+      </c>
+      <c r="F1367" s="31">
+        <v>4.2</v>
+      </c>
+      <c r="G1367" s="31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1367" s="6" t="s">
+        <v>4893</v>
+      </c>
+      <c r="I1367" s="3"/>
+    </row>
+    <row r="1368" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1368" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1368" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1368" s="4" t="s">
+        <v>4876</v>
+      </c>
+      <c r="D1368" s="6" t="s">
+        <v>4884</v>
+      </c>
+      <c r="E1368" s="14">
+        <v>3.22</v>
+      </c>
+      <c r="F1368" s="31">
+        <v>4</v>
+      </c>
+      <c r="G1368" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="H1368" s="6" t="s">
+        <v>4894</v>
+      </c>
+      <c r="I1368" s="3"/>
+    </row>
+    <row r="1369" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A1369" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1369" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1369" s="4" t="s">
+        <v>4877</v>
+      </c>
+      <c r="D1369" s="6" t="s">
+        <v>4885</v>
+      </c>
+      <c r="E1369" s="14">
+        <v>3.26</v>
+      </c>
+      <c r="F1369" s="31">
+        <v>3.9</v>
+      </c>
+      <c r="G1369" s="31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H1369" s="6" t="s">
+        <v>4888</v>
+      </c>
+      <c r="I1369" s="3"/>
+    </row>
+    <row r="1370" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A1370" s="3">
+        <v>1699527</v>
+      </c>
+      <c r="B1370" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1370" s="4" t="s">
+        <v>4865</v>
+      </c>
+      <c r="D1370" s="6" t="s">
+        <v>4886</v>
+      </c>
+      <c r="E1370" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="F1370" s="31">
+        <v>4.3</v>
+      </c>
+      <c r="G1370" s="31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H1370" s="6" t="s">
+        <v>4895</v>
+      </c>
+      <c r="I1370" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/albums_analysis_fixed.xlsx
+++ b/albums_analysis_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MusicApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DA8007-0A24-421F-B486-895C294165EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B46F44-160D-489D-A858-CE6B10446C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="albums" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5312" uniqueCount="4922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5410" uniqueCount="5012">
   <si>
     <t>No</t>
   </si>
@@ -16435,6 +16435,366 @@
         <charset val="161"/>
       </rPr>
       <t>: κιθάρα, φωνητική ένταση, prog δομή και απροθυμία να καταλήξει σε συμβατικό rock κλείσιμο.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bronze – ILPS 9265. Πρώτη βρετανική έκδοση (First UK Pressing, Stereo, Gatefold) που κυκλοφόρησε στις 30 Νοεμβρίου 1973. Η κατασκευή και διανομή έγινε από την Island Records Ltd., η εκτύπωση του εξωφύλλου από τη MacNeill Press Ltd. και η πίεση από την EMI Records. Την κοπή της λάκας (lacquer cut) ανέλαβε ο θρυλικός Dennis O'Brien (Bilbo).</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Solar Fire (Νοέμβριος 1973) αποτελεί το αδιαμφισβήτητο καλλιτεχνικό απόγειο των Manfred Mann's Earth Band και ένα από τα πιο επιδραστικά concept άλμπουμ του βρετανικού space/progressive rock. Ηχογραφήθηκε στα θρυλικά The Workhouse Studios στην Old Kent Road του Λονδίνου, με παραγωγούς την ίδια την μπάντα και βασικό ηχολήπτη τον John Pantry. Ο δίσκος συνδυάζει αριστοτεχνικά την κλασική παιδεία και τον αυτοσχεδιαστικό οίστρο του Manfred Mann στα synthesizers (Minimoog) και το Hammond όργανο, τα εκρηκτικά blues-rock riffs και φωνητικά του Mick Rogers, το ακλόνητο rhythm section των Colin Pattenden και Chris Slade, καθώς και τα πολυεπίπεδα χορωδιακά περάσματα των Chanter Sisters και των Grove Singers. Στιχουργικά και θεματικά, το άλμπουμ εμπνέεται από την αστρονομία, την κλασική μυθολογία, την κοσμογονία και το μνημειώδες ορχηστρικό έργο The Planets του Gustav Holst, εξερευνώντας τη θέση του ανθρώπου απέναντι στο άπειρο του σύμπαντος και τις πρωταρχικές δυνάμεις της φύσης. Το Solar Fire είναι το τέταρτο στούντιο άλμπουμ των Manfred Mann's Earth Band, κυκλοφορημένο το 1973. Αποτελεί σταθμό του progressive και symphonic rock, συνδυάζοντας την ηλεκτρονική και progressive αισθητική με τις χαρακτηριστικές ενορχηστρώσεις του Manfred Mann και τη διασκευή στον Bob Dylan ("Father Of Day, Father Of Night").</t>
+  </si>
+  <si>
+    <t>Father Of Day, Father Of Night</t>
+  </si>
+  <si>
+    <t>In The Beginning, Darkness</t>
+  </si>
+  <si>
+    <t>Pluto The Dog</t>
+  </si>
+  <si>
+    <t>Solar Fire</t>
+  </si>
+  <si>
+    <t>Saturn, Lord Of The Ring / Mercury, The Winged Messenger</t>
+  </si>
+  <si>
+    <t>Earth: The Circle Part Two</t>
+  </si>
+  <si>
+    <t>Earth: The Circle Part One</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Symphonic Rock [Art Rock, Psychedelic Rock, Hard Rock, Space Rock]</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/1578653-Manfred-Manns-Earth-Band-Solar-Fire</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/jKvXLxbswsA89RHMk-pl-CH1PCRex0zRpUekf0U8_xk/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTE1Nzg2/NTMtMTIyOTg4Mzk0/OS5qcGVn.jpeg</t>
+  </si>
+  <si>
+    <t>Manfred Mann's Earth Band</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Symphonic Rock [Dylan Cover, Cosmic Prog, Organ-led Rock Epic]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Instrumental Prog, Space Rock, Organ-Guitar Jam]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Organ Rock, Psychedelic Hard Rock, Riff Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Symphonic Rock [Cosmic Prog, Organ Rock, Theatrical Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Classical Rock [Symphonic Prog, Classical Adaptation, Organ-led Suite]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Cosmic Rock, Atmospheric Prog, Concept Fragment]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Psychedelic Rock [Atmospheric Prog, Cosmic Coda, Reprise]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>A1. Father Of Day, Father Of Night:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Η μεγάλη είσοδος του δίσκου και μία από τις πιο επιτυχημένες διασκευές του Manfred Mann’s Earth Band. Το τραγούδι του Bob Dylan αποκτά εντελώς διαφορετική κλίμακα, από σύντομη folk σύνθεση μετατρέπεται σε σχεδόν δεκάλεπτη cosmic-prog λειτουργία. Ο Manfred Mann χτίζει την αίσθηση με Hammond, synthesizer και αργή κλιμάκωση, ενώ ο Mick Rogers δίνει κιθάρες που προχωρούν από διακριτικό χρώμα σε heavy κορύφωση. Ο τίτλος αντιμετωπίζει τον Θεό ως πατέρα της ημέρας και της νύχτας , μια μορφή που περιλαμβάνει αντίθετα, φως και σκοτάδι, ύπαρξη και απουσία. Η Earth Band το χρησιμοποιεί ως κοσμογονικό overture, αργό, τελετουργικό, πλούσιο σε φωνητικές στρώσεις και τελικά εκρηκτικό. Είναι η κορυφαία σύνθεση του album και εξηγεί γιατί ο Mann θεωρείται από τους πιο δημιουργικούς rearrangers της rock εποχής.</t>
+    </r>
+  </si>
+  <si>
+    <t>Το title παραπέμπει σε κοσμογονία, πριν από το φως, πριν από τον ήλιο και τους πλανήτες, υπάρχει μόνο σκοτάδι. Το instrumental αναπτύσσεται μέσα από organ, synthesizer, κιθάρα και ελεγχόμενη ρυθμική κίνηση. Δεν προσπαθεί να προσφέρει ένα μεγάλο chorus· λειτουργεί ως ακουστική αναπαράσταση γέννησης μιας κοσμικής τάξης. Η εναλλαγή ψυχεδελικής ατμόσφαιρας και hard-rock έντασης κάνει το track κάτι περισσότερο από interlude. Παρότι είναι λιγότερο άμεσο από τον προκάτοχό του, αναδεικνύει την ικανότητα της μπάντας να γράφει instrumental prog με συγκεκριμένη εικόνα και δραματική κατεύθυνση.</t>
+  </si>
+  <si>
+    <t>Το πιο σύντομο και πιο riff-oriented τραγούδι της A πλευράς. Ο τίτλος είναι παράξενος, σχεδόν παιδικός ή absurdist, και η μπάντα ανταποκρίνεται με πιο σκληρό, γήινο hard-rock groove. Τα Hammond/organ parts παραμένουν κεντρικά, αλλά ο Mick Rogers δίνει heavy guitar attack και ο Chris Slade οδηγεί με δυναμικά drums. Μετά την ατμοσφαιρική ανάπτυξη των δύο πρώτων tracks, το “Pluto the Dog” λειτουργεί σαν συμπαγές, διασκεδαστικό release. Δεν έχει τη μεγάλη conceptual πυκνότητα του “Father of Day, Father of Night”, αλλά η απλότητά του είναι λειτουργικό πλεονέκτημα, προσφέρει ξεκούραση χωρίς να βγαίνει από τον cosmic/psychedelic κόσμο του album.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Solar Fire:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το title track επιστρέφει στην εικόνα της ηλιακής ενέργειας ως δημιουργικής και καταστροφικής δύναμης. Η “solar fire” είναι ζωή, φως και κίνηση, αλλά και μια καυτή δύναμη που μπορεί να υπερβεί τον ανθρώπινο έλεγχο. Ο Manfred Mann χτίζει πάνω σε οργανικό, ρυθμικό μοτίβο, με keyboards και κιθάρα να λειτουργούν σαν ακτίνες που κινούνται γύρω από ένα σταθερό πυρήνα. Είναι πιο σύντομο και song-oriented από το μεγάλο A1, αλλά έχει αρκετή θεατρικότητα ώστε να κρατήσει τον δίσκο στο symphonic-prog πλαίσιο. Ως άνοιγμα της B πλευράς, προσφέρει σωστή επανεκκίνηση, πριν η μπάντα περάσει στη μεγάλη classical suite.</t>
+    </r>
+  </si>
+  <si>
+    <t>Η πιο φιλόδοξη και σύνθετη στιγμή της B πλευράς. Οι τίτλοι παραπέμπουν στα δύο μέρη του The Planets του Gustav Holst, “Saturn, the Bringer of Old Age” και “Mercury, the Winged Messenger”. Η Earth Band δεν κάνει απλή πιστή εκτέλεση Holst, αλλά μετατρέπει τα συμφωνικά μοτίβα σε organ-driven progressive rock. Ο “Saturn” δίνει αργό, βαρύ και τελετουργικό βάρος , ηλικία, χρόνος, βαρύτητα , ενώ ο “Mercury” κινείται πιο γρήγορα και νευρικά, ακολουθώντας την εικόνα του φτερωτού αγγελιαφόρου. Το αποτέλεσμα είναι πραγματική symphonic-prog suite, όπου η classical πηγή λειτουργεί ως υλικό για νέα rock σύνθεση και όχι ως μουσειακό δάνειο. Είναι από τους καλλιτεχνικούς πυλώνες του album.</t>
+  </si>
+  <si>
+    <t>Το “Part Two” εμφανίζεται πριν από το “Part One”, κάτι που υπογραμμίζει την κυκλική, μη γραμμική λογική της σύνθεσης. Η Γη δεν παρουσιάζεται ως απλό αστρονομικό αντικείμενο αλλά ως κύκλος ζωής, επιστροφής και διασύνδεσης. Η μουσική είναι πιο ατμοσφαιρική, με spacey keyboards και χαμηλότερη ένταση, λειτουργώντας ως αποσυμπίεση μετά το “Saturn/Mercury”. Το μικρό μήκος του και ο fragment χαρακτήρας σημαίνουν ότι δεν έχει την αυτονομία ενός μεγάλου τραγουδιού, αλλά μέσα στην B πλευρά λειτουργεί σαν αναγκαίο contemplative passage.</t>
+  </si>
+  <si>
+    <t>Το album κλείνει επιστρέφοντας στο “Part One”, ολοκληρώνοντας το concept με μια ιδιότυπη αντιστροφή. Η συνθετική κίνηση υποδηλώνει ότι η αρχή και το τέλος δεν είναι απόλυτα διαχωρισμένα, ο κύκλος της Γης, της ημέρας, της νύχτας και της κοσμικής ενέργειας συνεχίζεται. Η μουσική είναι atmospheric prog coda, με οργάνωση που προτιμά mood, synthesizer/organ texture και σταδιακή απομάκρυνση αντί για conventional finale. Δεν είναι ο πιο ισχυρός αυτόνομος τίτλος του δίσκου, αλλά είναι σωστό κλείσιμο για album που ξεκινά με τη δημιουργία φωτός και τελειώνει με τη διαρκή κυκλικότητα του κόσμου.</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/5647555-Manfred-Manns-Earth-Band-Nightingales-Bombers</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/xLhN_xD-dViYVbqxYVprRdhb6sk_4oVJnATgnDaUjrw/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTU2NDc1/NTUtMTM5ODg4NDA3/OC0xNzkyLmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Nightingales &amp; Bombers</t>
+  </si>
+  <si>
+    <t>Bronze – ILPS 9337. Πρώτη βρετανική έκδοση (First UK release) σε ματ εξώφυλλο, η οποία κυκλοφόρησε τον Αύγουστο του 1975. Η ηχογράφηση πραγματοποιήθηκε στα The Workhouse Studios, το mastering και η κοπή της λάκας (lacquer cut) έγιναν στα I.B.C. Studios από τον Melys (Melvyn Abrahams), η πίεση από την EMI Records και η κατασκευή/διανομή από την Island Records Ltd.</t>
+  </si>
+  <si>
+    <t>**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Nightingales &amp; Bombers (Αύγουστος 1975) είναι το έκτο στούντιο άλμπουμ των Manfred Mann's Earth Band και σηματοδοτεί το τέλος της πρώτης κλασικής περιόδου της μπάντας, καθώς υπήρξε ο τελευταίος δίσκος με τον Mick Rogers ως βασικό κιθαρίστα και lead τραγουδιστή. Ηχογραφήθηκε στα The Workhouse Studios στο Λονδίνο, με ηχολήπτη τον Laurence Latham και παραγωγούς τα ίδια τα μέλη της Earth Band. Ηχητικά, το άλμπουμ εμβαθύνει στο μείγμα βρετανικού space rock, jazz fusion περασμάτων και hard rock ενέργειας. Τα αναλογικά Minimoog synthesizers του Manfred Mann, το βαρύ drumming του Chris Slade και οι εκφραστικές blues/heavy κιθάρες του Rogers πλαισιώνονται από κουαρτέτο εγχόρδων και πολυφωνικά γυναικεία φωνητικά (Doreen Chanter, Martha Smith, Ruby James). Ο τίτλος του άλμπουμ προήλθε από μια ιστορική ηχογράφηση πεδίου (field recording) του BBC από τον Β' Παγκόσμιο Πόλεμο (1942), όπου ένας ορνιθολόγος ηχογραφούσε αηδόνια στο Surrey ενώ από πάνω πετούσαν βρετανικά βομβαρδιστικά Lancaster με προορισμό τη Γερμανία. Αυτή η έντονη αντίθεση ανάμεσα στη γαλήνη της φύσης και την ανθρώπινη καταστροφή διατρέχει νοηματικά ολόκληρο το άλμπουμ.</t>
+  </si>
+  <si>
+    <t>Spirits In The Night</t>
+  </si>
+  <si>
+    <t>Countdown</t>
+  </si>
+  <si>
+    <t>Time Is Right</t>
+  </si>
+  <si>
+    <t>Crossfade</t>
+  </si>
+  <si>
+    <t>Visionary Mountains</t>
+  </si>
+  <si>
+    <t>Nightingales And Bombers</t>
+  </si>
+  <si>
+    <t>Fat Nelly</t>
+  </si>
+  <si>
+    <t>As Above So Below (Recorded “Live”)</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Symphonic Rock, Space Rock, Funk Rock, Art Rock, Blues Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Springsteen Cover, Organ Rock, Dramatic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Organ Rock, Moog Rock, Driving Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Funk Rock [Funky Prog, Synth Rock, Heavy Drum Break]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Space Rock [Moog Stomp, Heavy Prog, Guitar-Synth Duel]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Atmospheric Cover, Spacey Symphonic Rock, Soulful Prog]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Space Rock [Atmospheric Prog, Field Recording, Cosmic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Funk Rock [Funky Rock, Heavy Riff Rock, Organ Groove]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Live Prog, Extended Rock Jam, Heavy Organ Rock]</t>
+  </si>
+  <si>
+    <t>Το live κλείσιμο είναι η μεγάλη τελική δήλωση του δίσκου. Ο τίτλος προέρχεται από την ερμητική αρχή “as above, so below”, αυτό που συμβαίνει στο επάνω/κοσμικό επίπεδο αντανακλάται στο κάτω/ανθρώπινο ή γήινο επίπεδο. Η σύνθεση αξιοποιεί την ιδέα ως πλαίσιο για extended heavy-prog workout, με κιθάρα, organ, synth και drums να κινούνται σε συλλογική κλιμάκωση. Η live ηχογράφηση προσθέτει αμεσότητα, παραπάνω ένταση και ελαφρώς πιο ανοιχτή δομή από τα studio tracks. Δεν είναι απλώς bonus live cut· λειτουργεί ως ουσιαστικό finale, επειδή συμπυκνώνει τη βασική Earth Band εξίσωση, φιλοσοφική/κοσμική ιδέα, βαριά rock εκτέλεση και δεξιοτεχνική αλλά όχι ψυχρή ομαδική δυναμική.</t>
+  </si>
+  <si>
+    <t>Μετά την ατμόσφαιρα του title track, το “Fat Nelly” επιστρέφει σε πιο γήινο, funky heavy rock. Η ονομασία μοιάζει με character piece ή playful band narrative, και η μουσική ανταποκρίνεται με riff, groove και πιο άμεση ενέργεια. Δεν είναι από τα πιο σημαντικά concept tracks, αλλά η λειτουργία του στη B πλευρά είναι χρήσιμη, σπάει τη βαρύτητα και επαναφέρει το στοιχείο της rock διασκέδασης. Τα πλήκτρα του Mann και η κιθάρα του Rogers κρατούν τον αναγνωρίσιμο Earth Band χαρακτήρα, ενώ η ρυθμική βάση το κάνει πιο κοντά σε funk rock από την πιο συμφωνική πλευρά του δίσκου.</t>
+  </si>
+  <si>
+    <t>Το title track έχει ιδιαίτερη ιστορία, ενσωματώνει πραγματική field recording με νυχτερινά πουλιά και ήχους βομβαρδιστικών, η οποία έγινε στο Surrey το 1942. Η αντιπαράθεση της φυσικής ομορφιάς , τα αηδόνια , με τη βία και την τεχνολογική καταστροφή , τα βομβαρδιστικά , είναι ο πυρήνας του album title. Η μουσική της Earth Band περιβάλλει αυτή την αντίθεση με atmospheric keyboards και κιθάρα, δημιουργώντας ένα κομμάτι που είναι λιγότερο conventional song και περισσότερο ηχητική σκέψη πάνω σε πόλεμο, μνήμη και την παράξενη συνύπαρξη ομορφιάς και τρόμου. Η σύνθεση αποφεύγει τη ρητορική υπερβολή· η ίδια η ηχογράφηση κάνει το πολιτικό/αντιπολεμικό νόημα να προκύπτει φυσικά.</t>
+  </si>
+  <si>
+    <t>Η διασκευή των Joan Armatrading και Pam Nestor αποκτά μεγαλύτερο χώρο και κοσμική ατμόσφαιρα. Τα “visionary mountains” μπορούν να διαβαστούν ως υψηλά σημεία πνευματικής όρασης, απομόνωσης ή επιθυμίας για υπέρβαση. Η Earth Band αντιμετωπίζει το τραγούδι με spacious arrangement, πλούσια keyboards και κιθάρα που δεν πιέζει διαρκώς αλλά δημιουργεί τοπίο. Η ενορχήστρωση περιλαμβάνει strings , cello, viola και violin , κάτι που προσθέτει συμφωνικό βάθος χωρίς να γίνεται υπερβολικά ornate. Είναι πιο χαμηλότονο από την A πλευρά, αλλά αποτελεί πολύ καλό παράδειγμα της ικανότητας του Mann να δίνει σε singer-songwriter υλικό prog/art-rock κλίμακα.</t>
+  </si>
+  <si>
+    <t>Από τις πιο ενδιαφέρουσες και ρυθμικά ζωντανές συνθέσεις του album. Ο τίτλος μιλά για τη στιγμή που πρέπει να δράσεις , το σωστό timing, η κατάλληλη ώρα για αλλαγή ή απόφαση. Η μουσική ξεκινά με έντονο drum break του Chris Slade και στη συνέχεια συνδυάζει pulsating synths, funky bass movement και glissando guitar από τον Rogers. Δεν είναι απλώς prog, έχει πραγματικό funk pulse, κάτι που βοηθά τον δίσκο να αποφύγει τη μονοτονία του μεγαλοπρεπούς symphonic rock. Το track δείχνει πόσο καλή ήταν η Earth Band στο να μετατρέπει την τεχνική και την ατμόσφαιρα σε σωματικό groove. Οι περιγραφές της έκδοσης το ξεχωρίζουν ειδικά για το throbbing funk feeling, τα synths και το heavy drum-break opening.</t>
+  </si>
+  <si>
+    <t>Το “crossfade” είναι τεχνικός όρος για τη σταδιακή μετάβαση από ένα ηχητικό σήμα σε άλλο. Η μπάντα τον μετατρέπει σε μουσική ιδέα, κιθάρα και Moog εναλλάσσονται, μπλέκονται και περνούν από τη μία υφή στην άλλη. Το αποτέλεσμα είναι heavy space-rock stomp, με galloping drums και έντονο οργανικό διάλογο. Δεν έχει μεγάλη λυρική αφήγηση· η ουσία του είναι το momentum και η αντιπαράθεση guitar–synth. Είναι από τα πιο “μουσικά” tracks του LP, δηλαδή το νόημά του βρίσκεται κυρίως στο arrangement και στην αίσθηση κίνησης. Ως A-side closer λειτουργεί άριστα, γιατί ολοκληρώνει την πλευρά με τεχνική ενέργεια αντί για ballad ή εύκολη μελωδική κατάληξη.</t>
+  </si>
+  <si>
+    <t>Σύντομο, ισχυρό και πλήρως βασισμένο στη δυναμική της μπάντας. Το “countdown” είναι αντίστροφη μέτρηση προς εκτόξευση, καταστροφή, αλλαγή ή στιγμή μη επιστροφής. Τα Moog/synth parts του Mann και το driving rhythm section δημιουργούν μηχανική, προωθητική αίσθηση, ενώ η κιθάρα του Rogers λειτουργεί σαν αντίβαρο στον ηλεκτρονικό παλμό. Είναι πιο κοντά σε heavy organ rock παρά σε περίπλοκο symphonic prog, αλλά αυτό αποτελεί πλεονέκτημα, η σύνθεση είναι σφιχτή, σκοτεινή και αποτελεσματική. Η Discogs κριτική την αναφέρει ρητά μαζί με το “Crossfade” ως από τα πιο heavy cuts του δίσκου.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">A1. Spirits In The Night: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Η διασκευή του Bruce Springsteen γίνεται σχεδόν άλλη σύνθεση στα χέρια της Earth Band. Εκεί όπου το original έχει πιο δρόμο, νεότητα και Jersey storytelling, ο Manfred Mann μεταφέρει το κομμάτι σε πιο θεατρικό, organ-led prog-rock περιβάλλον. Η νύχτα του τίτλου είναι τόπος ελευθερίας, περιπλάνησης και πνευματικής έντασης, άνθρωποι κινούνται έξω από τους κανόνες της ημέρας, αναζητώντας εμπειρία και κοινότητα. Τα πλήκτρα, η κιθάρα του Mick Rogers και η δυναμική κλιμάκωση προσδίδουν μεγαλύτερη δραματική βαρύτητα, ενώ το τραγούδι διατηρεί την αφηγηματική του ενέργεια. Είναι ένα από τα πιο επιτυχημένα παραδείγματα του τρόπου με τον οποίο ο Mann δεν “καλύπτει” απλώς ένα τραγούδι αλλά το ξαναχτίζει στο προσωπικό του σύμπαν.</t>
+    </r>
+  </si>
+  <si>
+    <t>Angel Station</t>
+  </si>
+  <si>
+    <t>https://www.discogs.com/release/3089610-Manfred-Manns-Earth-Band-Angel-Station</t>
+  </si>
+  <si>
+    <t>https://i.discogs.com/eWJvML-3dqNTYVI83aDnLZIrtgiJm3O_AfekDfHl9oI/rs:fit/g:sm/q:40/h:300/w:300/czM6Ly9kaXNjb2dz/LWRhdGFiYXNlLWlt/YWdlcy9SLTMwODk2/MTAtMTYwODk4NzI4/NC0xOTk4LmpwZWc.jpeg</t>
+  </si>
+  <si>
+    <t>Bronze – BRON 516. Πρώτη βρετανική έκδοση (First UK pressing) σε στερεοφωνικό βινύλιο, η οποία κυκλοφόρησε στις 9 Μαρτίου 1979. Η ηχογράφηση έγινε στα The Workhouse Studios και Noel's House, η κοπή της λάκας (lacquer cut) από τον Rays, η πίεση από την EMI Records και η εκτύπωση του εξωφύλλου από τη Robert Stace. Συνοδεύεται από εσωτερικό ένθετο με τους στίχους (lyric sheet).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Ιστορικό Πλαίσιο &amp; Παραγωγή:** Το Angel Station (Μάρτιος 1979) αποτελεί το ένατο studio άλμπουμ των Manfred Mann's Earth Band και μια από τις πιο εκλεπτυσμένες, μεταβατικές στιγμές στη δισκογραφία τους. Ακολουθώντας τον εμπορικό θρίαμβο των The Roaring Silence και Watch, ο Manfred Mann ανανέωσε ριζικά το σχήμα: στη θέση των αποχωρησάντων Colin Pattenden και Chris Slade προστέθηκαν ο μπασίστας Pat King και ο ντράμερ Geoff Britton (πρώην Wings), ενώ ο κιθαρίστας Steve Waller και ο τραγουδιστής Chris Thompson δημιούργησαν ένα πολυδιάστατο φωνητικό δίδυμο.   Η παραγωγή πραγματοποιήθηκε στα The Workhouse Studios στο Λονδίνο με συμπαραγωγό τον Anthony Moore (συνιδρυτή των θρυλικών Slapp Happy και συνεργάτη των Pink Floyd). Ο Moore έφερε μια ευρωπαϊκή avant-pop/art rock αισθητική, με έξυπνη χρήση sequencing και synthesizers, μεταμορφώνοντας τον ήχο της μπάντας χωρίς να θυσιάσει την αναλογική progressive μαεστρία της. Στιχουργικά, το άλμπουμ περιστρέφεται γύρω από έναν σουρεαλιστικό, αστικό μυστικισμό, τη σύγκρουση πνευματικότητας και καταναλωτισμού, την τεχνολογία και την έννοια της αναγέννησης, στοιχεία που αποτυπώθηκαν αριστουργηματικά στο art deco εξώφυλλο του Martin Poole και τη φωτογραφία του John Shaw. Η συγκεκριμένη κόπια φέρει το γνωστό τυπογραφικό λάθος στις ετικέτες του δίσκου: στο πρώτο κομμάτι της πλευράς B, η ετικέτα αναγράφει "ANGELZ AT MY GATE", ενώ το εξώφυλλο και το ένθετο στίχων αναγράφουν σωστά "ANGELS AT MY GATE".   </t>
+  </si>
+  <si>
+    <t>Don’t Kill It Carol</t>
+  </si>
+  <si>
+    <t>You Angel You</t>
+  </si>
+  <si>
+    <t>Hollywood Town</t>
+  </si>
+  <si>
+    <t>“Belle” Of The Earth</t>
+  </si>
+  <si>
+    <t>Platform End</t>
+  </si>
+  <si>
+    <t>Angels At My Gate</t>
+  </si>
+  <si>
+    <t>You Are – I Am</t>
+  </si>
+  <si>
+    <t>Waiting For The Rain</t>
+  </si>
+  <si>
+    <t>Resurrection</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Hard Rock [Symphonic Rock, AOR, Art Rock, Keyboard Rock, Melodic Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Heavy Keyboard Rock, Symphonic Rock, Dramatic AOR]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, AOR [Dylan Cover, Melodic Rock, Keyboard-driven Rock]</t>
+  </si>
+  <si>
+    <t>Hard Rock, AOR [Urban Rock, Melodic Hard Rock, Arena Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Atmospheric Prog, Keyboard Instrumental, Cosmic Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Short Concept Interlude, Soundscape, Transition Piece]</t>
+  </si>
+  <si>
+    <t>Hard Rock, Progressive Rock [Dramatic Hard Rock, Keyboard Rock, Dark AOR]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Art Rock [Atmospheric Symphonic Rock, Concept Prog, Keyboard Rock]</t>
+  </si>
+  <si>
+    <t>AOR, Progressive Rock [Melodic Rock Ballad, Symphonic AOR, Emotional Rock]</t>
+  </si>
+  <si>
+    <t>Progressive Rock, Symphonic Rock [Instrumental Coda, Keyboard Prog, Album Finale]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>A1. Don’t Kill It Carol:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve"> Το album ανοίγει με μία από τις πιο επιβλητικές διασκευές των Earth Band. Το original του Mike Heron μεταμορφώνεται σε έξι λεπτά heavy, keyboard-driven rock, με έντονα drums, μεγάλα synth/organ layers και κιθάρα που αναπτύσσεται σε δραματικές κορυφώσεις. Ο τίτλος ακούγεται σαν προσταγή απέναντι σε βία, εμμονή ή συναισθηματική καταστροφή, ο αφηγητής ζητά να μη «σκοτώσεις» την Carol, κυριολεκτικά ή συμβολικά, +H1392,H1398δηλαδή να μην καταστρέψεις την αθωότητα, τη σχέση ή την ανθρώπινη δυνατότητα που εκπροσωπεί. Η μπάντα αποφεύγει την folk ευαισθησία του original και το κάνει symphonic hard-rock epic. Η κριτική αναγνώριση το θεωρεί σταθερά ένα από τα τρία μεγάλα tracks του δίσκου.</t>
+    </r>
+  </si>
+  <si>
+    <t>Η έβδομη Bob Dylan διασκευή των Earth Band και μια από τις πιο επιτυχημένες τους μεταμορφώσεις. Η αρχική Dylan εκδοχή είναι σύντομη και folk-rock προσανατολισμένη, ενώ ο Manfred Mann τη διευρύνει σε πιο hymn-like, keyboard-led melodic rock τραγούδι. Η “angel” του τίτλου μπορεί να είναι ερωτικό πρόσωπο, εξιδανικευμένη παρουσία ή δύναμη παρηγοριάς που τραβά τον αφηγητή έξω από τη σύγχυση. Ο Chris Thompson δίνει καθαρά και υψίφωνα vocals, τα keyboards προσθέτουν symphonic πλάτος και η κιθάρα του Steve Waller κρατά μια διακριτική but effective hard-rock ένταση. Το “You Angel You” έφτασε στο No. 58 του Billboard Hot 100 και αποτελεί το πιο σαφές crossover point του album προς το αμερικανικό AOR/radio rock.</t>
+  </si>
+  <si>
+    <t>Urban melodic hard rock με τίτλο που παρουσιάζει το Hollywood ως πόλη ονείρου, λάμψης, ευκαιρίας αλλά και επιφανειακού θεάματος. Το track αποφεύγει τη θεατρική έκταση των δύο πρώτων και επιλέγει πιο compact, direct song form. Οι κιθάρες και τα keyboards δημιουργούν late-’70s arena-rock χρώμα, ενώ τα vocals κινούνται ανάμεσα σε αυτοπεποίθηση και ελαφρά ειρωνεία απέναντι στη βιομηχανία της εικόνας. Δεν έχει το ίδιο ξεχωριστό hook ή ιστορική θέση με τις διασκευές, όμως ως album cut είναι σφιχτό και αποτελεσματικό, και λειτουργεί ως πιο γήινη ενότητα μέσα σε έναν δίσκο με αρκετά κοσμική/συμφωνική ατμόσφαιρα.</t>
+  </si>
+  <si>
+    <t>Σύντομο αλλά ατμοσφαιρικό instrumental/keyboard-centered piece. Η “Belle” λειτουργεί ως ποιητική μορφή της Γης , ομορφιά, φύση, θηλυκή αρχή και εύθραυστο περιβάλλον. Ο Mann χρησιμοποιεί synth textures και μελωδικά μοτίβα που μοιάζουν να αιωρούνται, δημιουργώντας μια μικρή cosmic prog σκηνή. Δεν είναι πλήρης song-form σύνθεση και αυτό περιορίζει την αυτοτελή του ισχύ, αλλά ως μέρος της A πλευράς λειτουργεί σαν αναπνοή μετά το πιο άμεσο “Hollywood Town”. Η θέση του πριν από το “Platform End” είναι σκόπιμη, ανοίγει μια σειρά από συντομότερα concept fragments πριν η B πλευρά επιστρέψει σε πλήρεις rock συνθέσεις.</t>
+  </si>
+  <si>
+    <t>Μικρό soundscape/interlude, όχι conventional τραγούδι. Ο τίτλος δημιουργεί εικόνα αποβάθρας στο τέλος της γραμμής, τόπος αναμονής, αποχωρισμού, μετάβασης ή επιλογής. Η σύντομη διάρκειά του σημαίνει ότι δεν πρέπει να αξιολογηθεί με το ίδιο κριτήριο με ένα πλήρες five-minute track· η λειτουργία του είναι να δημιουργήσει κινηματογραφική μετάβαση από την A στη B πλευρά. Η σχετικά χαμηλή βαθμολογία 3,6/5 αναγνωρίζει αυτή τη λειτουργικότητα, χωρίς να υπερτιμά ένα fragment ως αυτόνομη σύνθεση.</t>
+  </si>
+  <si>
+    <t>Σύντομο instrumental finale που μετατρέπει την έννοια της «ανάστασης» σε synthesizer/keyboard coda. Ο τίτλος υποδηλώνει επανεκκίνηση, πνευματική επιστροφή ή έξοδο από μια κατάσταση ακινησίας. Ο Mann δεν προσφέρει μεγάλο rock climax, αφήνει τη μουσική να απομακρυνθεί με spacey textures και μια αίσθηση ότι ο κύκλος παραμένει ανοιχτός. Ως αυτοτελές track είναι μικρό, αλλά ως επίλογος λειτουργεί σωστά, επειδή ολοκληρώνει θεματικά τη διαδρομή από τους αγγέλους, την ταυτότητα και την αναμονή προς μια μορφή επανόδου. Είναι το είδος του μικρού atmospheric coda που διατηρεί την progressive ταυτότητα του album ακόμη και μέσα στην πιο AOR κατεύθυνση του 1979.</t>
+  </si>
+  <si>
+    <t>Μελωδική, συναισθηματικά ανοιχτή AOR/prog μπαλάντα. Η “βροχή” λειτουργεί ως εικόνα αναμονής για κάθαρση, αλλαγή ή συναισθηματική λύση μετά από ξηρασία και πίεση. Τα keyboards δίνουν symphonic ύψος, η φωνή του Thompson κρατά μελαγχολική καθαρότητα και η κιθάρα λειτουργεί υποστηρικτικά, δίνοντας χώρο στη μελωδία. Δεν είναι υπερβολικά εμπορική ballad· διαθέτει αρκετή ανάπτυξη και σκοτεινή χροιά ώστε να παραμένει Earth Band. Η θέση της πριν το “Resurrection” την κάνει να μοιάζει με αναμονή πριν από μια τελική αναγέννηση.</t>
+  </si>
+  <si>
+    <t>Atmospheric, keyboards-led prog track με τίτλο που μιλά για σχέση ταυτότητας, καθρέφτη και αλληλεξάρτησης. Το “you are, I am” μπορεί να δηλώνει ότι δύο άνθρωποι ορίζονται ο ένας μέσα από τον άλλο ή ότι η ατομική ταυτότητα είναι ασταθής. Η μουσική δεν ακολουθεί καθαρό single format· προτιμά πιο υπόγεια ανάπτυξη, με synthesizer μοτίβα, κιθάρα και ρυθμό να χτίζουν αργά ένα συμπαγές sound field. Είναι από τα tracks που κρατούν τη σύνδεση του album με την πιο προηγούμενη, art-rock Earth Band περίοδο. Δεν έχει τόσο instant chorus όσο τα μεγάλα singles, αλλά έχει μεγαλύτερο βάθος όταν ακούγεται στο πλαίσιο της B πλευράς.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t xml:space="preserve">B1. Angels At My Gate: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Roboto Condensed"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Το σκοτεινό, δραματικό άνοιγμα της B πλευράς. Στη δική σου έκδοση υπάρχει ως Angelz At My Gate στο label, αλλά “Angels At My Gate” στο sleeve και στο lyric sheet , η τελευταία είναι η κανονική μορφή για αρχειοθέτηση. Οι “άγγελοι στην πύλη” μπορούν να είναι σωτήρες, αγγελιοφόροι, ενοχή που πλησιάζει ή απειλητικές δυνάμεις που περιμένουν να εισέλθουν. Η σύνθεση έχει προωθητικό heavy-rock riff, σκοτεινά keyboards και μεγάλο chorus, ενώ ο Chris Thompson προσθέτει πολύ πιο έντονο, δραματικό vocal από ό,τι στο “You Angel You”. Είναι από τα ισχυρότερα originals του album και μία από τις βασικές αιτίες που το Angel Station διατηρεί progressive/hard-rock βάρος κάτω από την πιο εμπορική επιφάνειά του.</t>
     </r>
   </si>
 </sst>
@@ -16632,7 +16992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -16717,26 +17077,14 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17048,7 +17396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C0DF49-F4B5-4628-97FA-CB9E84E433D3}">
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
@@ -17063,4532 +17411,4628 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="225" x14ac:dyDescent="0.2">
-      <c r="A2" s="31">
+    <row r="2" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>37070553</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="4" t="s">
         <v>4840</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="4" t="s">
         <v>4839</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="3">
         <v>1983</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="30">
         <v>3.51</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="5" t="s">
         <v>4838</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="4" t="s">
         <v>4844</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="3" t="s">
         <v>4841</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="31" t="s">
         <v>4842</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="31" t="s">
         <v>4843</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A3" s="31">
+    <row r="3" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>37467900</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="3">
         <v>2026</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="30">
         <v>3.37</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="5" t="s">
         <v>1577</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="90" x14ac:dyDescent="0.2">
-      <c r="A4" s="31">
+    <row r="4" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>28392787</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="4" t="s">
         <v>4287</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="3">
         <v>1969</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="30">
         <v>3.8</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="3" t="s">
         <v>2476</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="31" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="146.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="31">
+    <row r="5" spans="1:10" ht="146.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>29151724</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="3">
         <v>1977</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="30">
         <v>2.84</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="5" t="s">
         <v>4368</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="4" t="s">
         <v>4376</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="3" t="s">
         <v>4375</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="31" t="s">
         <v>4367</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="31" t="s">
         <v>4366</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="31">
+    <row r="6" spans="1:10" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>31841081</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="4" t="s">
         <v>4518</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="4" t="s">
         <v>4519</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="3">
         <v>1972</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="30">
         <v>3.7